--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="375">
   <si>
     <t>trade_time</t>
   </si>
@@ -1133,6 +1133,12 @@
   </si>
   <si>
     <t>2021-05-10</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>2021-05-12</t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P536"/>
+  <dimension ref="A1:P538"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28290,6 +28296,106 @@
         <v>372</v>
       </c>
     </row>
+    <row r="537" spans="1:16">
+      <c r="A537" s="1">
+        <v>0</v>
+      </c>
+      <c r="B537" t="s">
+        <v>69</v>
+      </c>
+      <c r="C537">
+        <v>-3.067435364143786</v>
+      </c>
+      <c r="D537" t="s">
+        <v>159</v>
+      </c>
+      <c r="E537">
+        <v>-2.57005517331759</v>
+      </c>
+      <c r="F537">
+        <v>1</v>
+      </c>
+      <c r="G537">
+        <v>0.01150743536414378</v>
+      </c>
+      <c r="H537">
+        <v>0.01095005517331759</v>
+      </c>
+      <c r="I537">
+        <v>0.4973801908261954</v>
+      </c>
+      <c r="J537">
+        <v>2.397182685573614</v>
+      </c>
+      <c r="K537">
+        <v>3.04</v>
+      </c>
+      <c r="L537">
+        <v>4.22</v>
+      </c>
+      <c r="M537">
+        <v>2.82</v>
+      </c>
+      <c r="N537">
+        <v>4.19</v>
+      </c>
+      <c r="O537">
+        <v>1</v>
+      </c>
+      <c r="P537" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="538" spans="1:16">
+      <c r="A538" s="1">
+        <v>0</v>
+      </c>
+      <c r="B538" t="s">
+        <v>69</v>
+      </c>
+      <c r="C538">
+        <v>-3.089535962632947</v>
+      </c>
+      <c r="D538" t="s">
+        <v>159</v>
+      </c>
+      <c r="E538">
+        <v>-2.590556386389772</v>
+      </c>
+      <c r="F538">
+        <v>1</v>
+      </c>
+      <c r="G538">
+        <v>0.01152953596263295</v>
+      </c>
+      <c r="H538">
+        <v>0.01097055638638977</v>
+      </c>
+      <c r="I538">
+        <v>0.4989795762431752</v>
+      </c>
+      <c r="J538">
+        <v>2.404452619287154</v>
+      </c>
+      <c r="K538">
+        <v>3.04</v>
+      </c>
+      <c r="L538">
+        <v>4.22</v>
+      </c>
+      <c r="M538">
+        <v>2.82</v>
+      </c>
+      <c r="N538">
+        <v>4.19</v>
+      </c>
+      <c r="O538">
+        <v>1</v>
+      </c>
+      <c r="P538" t="s">
+        <v>374</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="376">
   <si>
     <t>trade_time</t>
   </si>
@@ -1139,6 +1139,9 @@
   </si>
   <si>
     <t>2021-05-12</t>
+  </si>
+  <si>
+    <t>2021-05-13</t>
   </si>
 </sst>
 </file>
@@ -1496,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P538"/>
+  <dimension ref="A1:P539"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28396,6 +28399,56 @@
         <v>374</v>
       </c>
     </row>
+    <row r="539" spans="1:16">
+      <c r="A539" s="1">
+        <v>0</v>
+      </c>
+      <c r="B539" t="s">
+        <v>69</v>
+      </c>
+      <c r="C539">
+        <v>-3.034510811938273</v>
+      </c>
+      <c r="D539" t="s">
+        <v>159</v>
+      </c>
+      <c r="E539">
+        <v>-2.539513318969055</v>
+      </c>
+      <c r="F539">
+        <v>1</v>
+      </c>
+      <c r="G539">
+        <v>0.01147451081193827</v>
+      </c>
+      <c r="H539">
+        <v>0.01091951331896906</v>
+      </c>
+      <c r="I539">
+        <v>0.494997492969218</v>
+      </c>
+      <c r="J539">
+        <v>2.386352240769169</v>
+      </c>
+      <c r="K539">
+        <v>3.04</v>
+      </c>
+      <c r="L539">
+        <v>4.22</v>
+      </c>
+      <c r="M539">
+        <v>2.82</v>
+      </c>
+      <c r="N539">
+        <v>4.19</v>
+      </c>
+      <c r="O539">
+        <v>1</v>
+      </c>
+      <c r="P539" t="s">
+        <v>375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="382">
   <si>
     <t>trade_time</t>
   </si>
@@ -226,6 +226,9 @@
     <t>2021-06-30</t>
   </si>
   <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2017-06-30</t>
   </si>
   <si>
@@ -496,6 +499,9 @@
     <t>2021-07-05</t>
   </si>
   <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
     <t>2016-10-28</t>
   </si>
   <si>
@@ -1142,6 +1148,18 @@
   </si>
   <si>
     <t>2021-05-13</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>2021-06-10</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P539"/>
+  <dimension ref="A1:P543"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1560,7 +1578,7 @@
         <v>6.869727715272395</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>6.050137140894572</v>
@@ -1596,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1610,7 +1628,7 @@
         <v>6.844463593057311</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3">
         <v>6.050137140894572</v>
@@ -1646,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1660,7 +1678,7 @@
         <v>6.857637482930865</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>6.039233803242143</v>
@@ -1696,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1710,7 +1728,7 @@
         <v>6.83283604847594</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E5">
         <v>6.039233803242143</v>
@@ -1746,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1760,7 +1778,7 @@
         <v>6.826153414303063</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6">
         <v>6.01084051672589</v>
@@ -1796,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1810,7 +1828,7 @@
         <v>6.802556861010267</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7">
         <v>6.01084051672589</v>
@@ -1846,7 +1864,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1860,7 +1878,7 @@
         <v>6.794839943414579</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8">
         <v>5.98260108041714</v>
@@ -1896,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1910,7 +1928,7 @@
         <v>6.77244174258507</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E9">
         <v>5.98260108041714</v>
@@ -1946,7 +1964,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1960,7 +1978,7 @@
         <v>6.763675289556306</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10">
         <v>5.95449585181284</v>
@@ -1996,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2010,7 +2028,7 @@
         <v>6.742469746029192</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11">
         <v>5.95449585181284</v>
@@ -2046,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2060,7 +2078,7 @@
         <v>6.730117010025435</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>5.924231979091157</v>
@@ -2096,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2110,7 +2128,7 @@
         <v>6.710195726779869</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13">
         <v>5.924231979091157</v>
@@ -2146,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2160,7 +2178,7 @@
         <v>6.693046966006446</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14">
         <v>5.890801090807809</v>
@@ -2196,7 +2214,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2210,7 +2228,7 @@
         <v>6.674544336691723</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15">
         <v>5.890801090807809</v>
@@ -2246,7 +2264,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2260,7 +2278,7 @@
         <v>6.644553392998862</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16">
         <v>5.847068118145396</v>
@@ -2296,7 +2314,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2310,7 +2328,7 @@
         <v>6.627906590937341</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17">
         <v>5.847068118145396</v>
@@ -2346,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2360,7 +2378,7 @@
         <v>6.617128166636995</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18">
         <v>5.822335218497922</v>
@@ -2396,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2410,7 +2428,7 @@
         <v>6.601530915667526</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19">
         <v>5.822335218497922</v>
@@ -2446,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2460,7 +2478,7 @@
         <v>6.581803978417834</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20">
         <v>5.790478795844368</v>
@@ -2496,7 +2514,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2510,7 +2528,7 @@
         <v>6.567558568262076</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21">
         <v>5.790478795844368</v>
@@ -2546,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2560,7 +2578,7 @@
         <v>6.554001439910648</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>5.765405624678154</v>
@@ -2596,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2610,7 +2628,7 @@
         <v>6.540820020413236</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E23">
         <v>5.765405624678154</v>
@@ -2646,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2660,7 +2678,7 @@
         <v>6.529894038726229</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E24">
         <v>5.743664840248944</v>
@@ -2696,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2710,7 +2728,7 @@
         <v>6.517635198641864</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E25">
         <v>5.743664840248944</v>
@@ -2746,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2760,7 +2778,7 @@
         <v>6.493137342079</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E26">
         <v>5.710516538114505</v>
@@ -2796,7 +2814,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2810,7 +2828,7 @@
         <v>6.482285164262333</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E27">
         <v>5.710516538114505</v>
@@ -2846,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2860,7 +2878,7 @@
         <v>6.444477546138163</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28">
         <v>5.666633660577178</v>
@@ -2896,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2910,7 +2928,7 @@
         <v>6.435487556851677</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E29">
         <v>5.666633660577178</v>
@@ -2946,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2960,7 +2978,7 @@
         <v>6.395287017911711</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E30">
         <v>5.62227215259259</v>
@@ -2996,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3010,7 +3028,7 @@
         <v>6.388179528041545</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E31">
         <v>5.62227215259259</v>
@@ -3046,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3060,7 +3078,7 @@
         <v>6.391868530229962</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E32">
         <v>5.619189256879599</v>
@@ -3096,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3110,7 +3128,7 @@
         <v>6.384891864347617</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E33">
         <v>5.619189256879599</v>
@@ -3146,7 +3164,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3160,7 +3178,7 @@
         <v>6.396520135507044</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E34">
         <v>5.623384215382392</v>
@@ -3196,7 +3214,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3210,7 +3228,7 @@
         <v>6.389365454780485</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E35">
         <v>5.623384215382392</v>
@@ -3246,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3260,7 +3278,7 @@
         <v>6.403506732043612</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E36">
         <v>5.629684939713206</v>
@@ -3296,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3310,7 +3328,7 @@
         <v>6.396084677406335</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E37">
         <v>5.629684939713206</v>
@@ -3346,7 +3364,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3360,7 +3378,7 @@
         <v>6.390454186369448</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E38">
         <v>5.617913758755807</v>
@@ -3396,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3410,7 +3428,7 @@
         <v>6.38353164679125</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E39">
         <v>5.617913758755807</v>
@@ -3446,7 +3464,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3460,7 +3478,7 @@
         <v>6.385694652927858</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E40">
         <v>5.613621467365888</v>
@@ -3496,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3510,7 +3528,7 @@
         <v>6.378954258556243</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E41">
         <v>5.613621467365888</v>
@@ -3546,7 +3564,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3560,7 +3578,7 @@
         <v>6.398324700271503</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E42">
         <v>5.625011626534365</v>
@@ -3596,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3610,7 +3628,7 @@
         <v>6.39110095966211</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E43">
         <v>5.625011626534365</v>
@@ -3646,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3660,7 +3678,7 @@
         <v>6.406965992917668</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E44">
         <v>5.63280460592575</v>
@@ -3696,7 +3714,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3710,7 +3728,7 @@
         <v>6.399411553920818</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E45">
         <v>5.63280460592575</v>
@@ -3746,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3760,7 +3778,7 @@
         <v>6.400651203652978</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E46">
         <v>5.627109737736961</v>
@@ -3796,7 +3814,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3810,7 +3828,7 @@
         <v>6.393338428804362</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E47">
         <v>5.627109737736961</v>
@@ -3846,7 +3864,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3860,7 +3878,7 @@
         <v>6.421264387742685</v>
       </c>
       <c r="D48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E48">
         <v>5.645699331375265</v>
@@ -3896,7 +3914,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3910,7 +3928,7 @@
         <v>6.413162755599453</v>
       </c>
       <c r="D49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E49">
         <v>5.645699331375265</v>
@@ -3946,7 +3964,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3960,7 +3978,7 @@
         <v>6.463467063219744</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E50">
         <v>5.68375898213827</v>
@@ -3996,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4010,7 +4028,7 @@
         <v>6.45375035364561</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E51">
         <v>5.68375898213827</v>
@@ -4046,7 +4064,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4060,7 +4078,7 @@
         <v>6.488418927255035</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E52">
         <v>5.706261328739149</v>
@@ -4096,7 +4114,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4110,7 +4128,7 @@
         <v>6.477747321053927</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E53">
         <v>5.706261328739149</v>
@@ -4146,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4160,7 +4178,7 @@
         <v>6.583255790923473</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E54">
         <v>5.791788084326992</v>
@@ -4196,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4210,7 +4228,7 @@
         <v>6.440394668218746</v>
       </c>
       <c r="D55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E55">
         <v>5.791788084326992</v>
@@ -4246,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4260,7 +4278,7 @@
         <v>6.568954820555353</v>
       </c>
       <c r="D56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E56">
         <v>5.791788084326992</v>
@@ -4296,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4310,7 +4328,7 @@
         <v>6.628230185262845</v>
       </c>
       <c r="D57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E57">
         <v>5.83234735509561</v>
@@ -4346,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4360,7 +4378,7 @@
         <v>6.484920066940753</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E58">
         <v>5.83234735509561</v>
@@ -4396,7 +4414,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4410,7 +4428,7 @@
         <v>6.61220806502816</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E59">
         <v>5.83234735509561</v>
@@ -4446,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4460,7 +4478,7 @@
         <v>6.646411890511949</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E60">
         <v>5.84874416748332</v>
@@ -4496,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4510,7 +4528,7 @@
         <v>6.50292025766158</v>
       </c>
       <c r="D61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E61">
         <v>5.84874416748332</v>
@@ -4546,7 +4564,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4560,7 +4578,7 @@
         <v>6.629693964585535</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E62">
         <v>5.84874416748332</v>
@@ -4596,7 +4614,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4610,7 +4628,7 @@
         <v>6.642559529608892</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E63">
         <v>5.84526999176043</v>
@@ -4646,7 +4664,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4660,7 +4678,7 @@
         <v>6.499106356268371</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>5.84526999176043</v>
@@ -4696,7 +4714,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4710,7 +4728,7 @@
         <v>6.625989031803559</v>
       </c>
       <c r="D65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E65">
         <v>5.84526999176043</v>
@@ -4746,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4760,7 +4778,7 @@
         <v>6.645390633912061</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E66">
         <v>5.847823167354969</v>
@@ -4796,7 +4814,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4810,7 +4828,7 @@
         <v>6.501909196635068</v>
       </c>
       <c r="D67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E67">
         <v>5.847823167354969</v>
@@ -4846,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4860,7 +4878,7 @@
         <v>6.628711791016923</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E68">
         <v>5.847823167354969</v>
@@ -4896,7 +4914,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4910,7 +4928,7 @@
         <v>6.628009372010197</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E69">
         <v>5.832148219017515</v>
@@ -4946,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4960,7 +4978,7 @@
         <v>6.611995702199492</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E70">
         <v>5.832148219017515</v>
@@ -4996,7 +5014,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5010,7 +5028,7 @@
         <v>6.616738911804213</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E71">
         <v>5.821984176701968</v>
@@ -5046,7 +5064,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5060,7 +5078,7 @@
         <v>6.601156557442321</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E72">
         <v>5.821984176701968</v>
@@ -5096,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5110,7 +5128,7 @@
         <v>6.626158243616882</v>
       </c>
       <c r="D73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E73">
         <v>5.830478815374958</v>
@@ -5146,7 +5164,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5160,7 +5178,7 @@
         <v>6.610215415658166</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E74">
         <v>5.830478815374958</v>
@@ -5196,7 +5214,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5210,7 +5228,7 @@
         <v>6.650940043106316</v>
       </c>
       <c r="D75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E75">
         <v>5.85282779261834</v>
@@ -5246,7 +5264,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5260,7 +5278,7 @@
         <v>6.634048826814393</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E76">
         <v>5.85282779261834</v>
@@ -5296,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5310,7 +5328,7 @@
         <v>6.655761178830648</v>
       </c>
       <c r="D77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E77">
         <v>5.857175638812331</v>
@@ -5346,7 +5364,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5360,7 +5378,7 @@
         <v>6.638685459840457</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E78">
         <v>5.857175638812331</v>
@@ -5396,7 +5414,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5410,7 +5428,7 @@
         <v>6.682065765134389</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E79">
         <v>5.880897911319199</v>
@@ -5446,7 +5464,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5460,7 +5478,7 @@
         <v>6.663983381443721</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E80">
         <v>5.880897911319199</v>
@@ -5496,7 +5514,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5510,7 +5528,7 @@
         <v>6.734829447046008</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E81">
         <v>5.928481797502389</v>
@@ -5546,7 +5564,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5560,7 +5578,7 @@
         <v>6.714727820952732</v>
       </c>
       <c r="D82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E82">
         <v>5.928481797502389</v>
@@ -5596,7 +5614,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5610,7 +5628,7 @@
         <v>6.744601630625527</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E83">
         <v>5.937294648584086</v>
@@ -5646,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5660,7 +5678,7 @@
         <v>6.72412602745683</v>
       </c>
       <c r="D84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E84">
         <v>5.937294648584086</v>
@@ -5696,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5710,7 +5728,7 @@
         <v>6.868996803282632</v>
       </c>
       <c r="D85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E85">
         <v>6.049477982328097</v>
@@ -5746,7 +5764,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5760,7 +5778,7 @@
         <v>6.723283024880476</v>
       </c>
       <c r="D86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E86">
         <v>6.049477982328097</v>
@@ -5796,7 +5814,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5810,7 +5828,7 @@
         <v>6.843760652741033</v>
       </c>
       <c r="D87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E87">
         <v>6.049477982328097</v>
@@ -5846,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5860,7 +5878,7 @@
         <v>7.461980748234559</v>
       </c>
       <c r="D88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E88">
         <v>6.584248861136657</v>
@@ -5896,7 +5914,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5910,7 +5928,7 @@
         <v>7.310346997004264</v>
       </c>
       <c r="D89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E89">
         <v>6.584248861136657</v>
@@ -5946,7 +5964,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5960,7 +5978,7 @@
         <v>7.414051368518428</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E90">
         <v>6.584248861136657</v>
@@ -5996,7 +6014,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6010,7 +6028,7 @@
         <v>7.503790226406835</v>
       </c>
       <c r="D91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E91">
         <v>6.621953914663068</v>
@@ -6046,7 +6064,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6060,7 +6078,7 @@
         <v>7.351739076060011</v>
       </c>
       <c r="D92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E92">
         <v>6.621953914663068</v>
@@ -6096,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6110,7 +6128,7 @@
         <v>7.454260816744011</v>
       </c>
       <c r="D93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E93">
         <v>6.621953914663068</v>
@@ -6146,7 +6164,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6160,7 +6178,7 @@
         <v>7.442891522635139</v>
       </c>
       <c r="D94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E94">
         <v>6.567033619414717</v>
@@ -6196,7 +6214,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6210,7 +6228,7 @@
         <v>7.291448346036452</v>
       </c>
       <c r="D95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E95">
         <v>6.567033619414717</v>
@@ -6246,7 +6264,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6260,7 +6278,7 @@
         <v>7.39569267900684</v>
       </c>
       <c r="D96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E96">
         <v>6.567033619414717</v>
@@ -6296,7 +6314,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6310,7 +6328,7 @@
         <v>7.440682840908001</v>
       </c>
       <c r="D97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E97">
         <v>6.56504176334798</v>
@@ -6346,7 +6364,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6360,7 +6378,7 @@
         <v>7.289261714376473</v>
       </c>
       <c r="D98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E98">
         <v>6.56504176334798</v>
@@ -6396,7 +6414,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6410,7 +6428,7 @@
         <v>7.393568522537145</v>
       </c>
       <c r="D99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E99">
         <v>6.56504176334798</v>
@@ -6446,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6460,7 +6478,7 @@
         <v>7.424306444365878</v>
       </c>
       <c r="D100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E100">
         <v>6.550273033022139</v>
@@ -6496,7 +6514,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6510,7 +6528,7 @@
         <v>7.377818843333573</v>
       </c>
       <c r="D101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E101">
         <v>6.550273033022139</v>
@@ -6546,7 +6564,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6560,7 +6578,7 @@
         <v>7.534499875331724</v>
       </c>
       <c r="D102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E102">
         <v>6.649648806039591</v>
@@ -6596,7 +6614,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6610,7 +6628,7 @@
         <v>7.483795221200893</v>
       </c>
       <c r="D103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E103">
         <v>6.649648806039591</v>
@@ -6646,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6660,7 +6678,7 @@
         <v>7.561436426814521</v>
       </c>
       <c r="D104" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E104">
         <v>6.673941003882645</v>
@@ -6696,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6710,7 +6728,7 @@
         <v>7.509700922959722</v>
       </c>
       <c r="D105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E105">
         <v>6.673941003882645</v>
@@ -6746,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6760,7 +6778,7 @@
         <v>7.578789061755105</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E106">
         <v>6.689590135559512</v>
@@ -6796,7 +6814,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6810,7 +6828,7 @@
         <v>7.526389480356823</v>
       </c>
       <c r="D107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E107">
         <v>6.689590135559512</v>
@@ -6846,7 +6864,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6860,7 +6878,7 @@
         <v>6.876779630058808</v>
       </c>
       <c r="D108" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E108">
         <v>6.056496771201121</v>
@@ -6896,7 +6914,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6910,7 +6928,7 @@
         <v>6.85124563423293</v>
       </c>
       <c r="D109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E109">
         <v>6.056496771201121</v>
@@ -6946,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6960,7 +6978,7 @@
         <v>6.803309666682317</v>
       </c>
       <c r="D110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E110">
         <v>5.990239333347446</v>
@@ -6996,7 +7014,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7010,7 +7028,7 @@
         <v>6.780587333348385</v>
       </c>
       <c r="D111" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E111">
         <v>5.990239333347446</v>
@@ -7046,7 +7064,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7060,7 +7078,7 @@
         <v>6.690125588143431</v>
       </c>
       <c r="D112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E112">
         <v>5.88816650378326</v>
@@ -7096,7 +7114,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7110,7 +7128,7 @@
         <v>6.671734758647093</v>
       </c>
       <c r="D113" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E113">
         <v>5.88816650378326</v>
@@ -7146,7 +7164,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7160,7 +7178,7 @@
         <v>6.546850371675455</v>
       </c>
       <c r="D114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E114">
         <v>5.758956574788845</v>
@@ -7196,7 +7214,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7210,7 +7228,7 @@
         <v>6.533942620346777</v>
       </c>
       <c r="D115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E115">
         <v>5.758956574788845</v>
@@ -7246,7 +7264,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7260,7 +7278,7 @@
         <v>6.36581543133911</v>
       </c>
       <c r="D116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E116">
         <v>5.595693783337433</v>
@@ -7296,7 +7314,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7310,7 +7328,7 @@
         <v>6.359835805846931</v>
       </c>
       <c r="D117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E117">
         <v>5.595693783337433</v>
@@ -7346,7 +7364,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7360,7 +7378,7 @@
         <v>5.655118426801266</v>
       </c>
       <c r="D118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E118">
         <v>4.954765702705966</v>
@@ -7396,7 +7414,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7410,7 +7428,7 @@
         <v>5.676336856391234</v>
       </c>
       <c r="D119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E119">
         <v>4.954765702705966</v>
@@ -7446,7 +7464,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7460,7 +7478,7 @@
         <v>4.385984132295935</v>
       </c>
       <c r="D120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E120">
         <v>4.515964100132926</v>
@@ -7496,7 +7514,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7510,7 +7528,7 @@
         <v>5.520410496630564</v>
       </c>
       <c r="D121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E121">
         <v>4.833282011936382</v>
@@ -7546,7 +7564,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7560,7 +7578,7 @@
         <v>5.54678413819046</v>
       </c>
       <c r="D122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E122">
         <v>4.833282011936382</v>
@@ -7596,7 +7614,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7646,7 +7664,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7660,7 +7678,7 @@
         <v>5.300818351460203</v>
       </c>
       <c r="D124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E124">
         <v>4.635247165543143</v>
@@ -7696,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7710,7 +7728,7 @@
         <v>5.335595685763722</v>
       </c>
       <c r="D125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E125">
         <v>4.635247165543143</v>
@@ -7746,7 +7764,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7796,7 +7814,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7846,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7860,7 +7878,7 @@
         <v>5.067644558031954</v>
       </c>
       <c r="D128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E128">
         <v>4.254963977459765</v>
@@ -7896,7 +7914,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7910,7 +7928,7 @@
         <v>5.111345348656355</v>
       </c>
       <c r="D129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E129">
         <v>4.254963977459765</v>
@@ -7946,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7960,7 +7978,7 @@
         <v>3.765802729769834</v>
       </c>
       <c r="D130" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E130">
         <v>3.674881815638774</v>
@@ -7996,7 +8014,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8010,7 +8028,7 @@
         <v>4.618291357603566</v>
       </c>
       <c r="D131" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E131">
         <v>3.650865136965114</v>
@@ -8046,7 +8064,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8060,7 +8078,7 @@
         <v>4.268167177296843</v>
       </c>
       <c r="D132" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E132">
         <v>3.514053115333852</v>
@@ -8096,7 +8114,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8110,7 +8128,7 @@
         <v>4.254037078744074</v>
       </c>
       <c r="D133" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E133">
         <v>3.510852837781765</v>
@@ -8146,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8160,7 +8178,7 @@
         <v>4.264789106547418</v>
       </c>
       <c r="D134" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E134">
         <v>3.510852837781765</v>
@@ -8196,7 +8214,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8210,7 +8228,7 @@
         <v>4.267776501761822</v>
       </c>
       <c r="D135" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E135">
         <v>3.523940390364364</v>
@@ -8246,7 +8264,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8260,7 +8278,7 @@
         <v>4.278603745384606</v>
       </c>
       <c r="D136" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E136">
         <v>3.523940390364364</v>
@@ -8296,7 +8314,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8310,7 +8328,7 @@
         <v>4.280771326539147</v>
       </c>
       <c r="D137" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E137">
         <v>3.485420289185799</v>
@@ -8346,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8360,7 +8378,7 @@
         <v>4.291669709713632</v>
       </c>
       <c r="D138" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E138">
         <v>3.485420289185799</v>
@@ -8396,7 +8414,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8410,7 +8428,7 @@
         <v>4.295828187834458</v>
       </c>
       <c r="D139" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E139">
         <v>3.499680345777525</v>
@@ -8446,7 +8464,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8460,7 +8478,7 @@
         <v>4.306808999081727</v>
       </c>
       <c r="D140" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E140">
         <v>3.499680345777525</v>
@@ -8496,7 +8514,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8510,7 +8528,7 @@
         <v>4.311022789612967</v>
       </c>
       <c r="D141" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E141">
         <v>3.503649415261579</v>
@@ -8560,7 +8578,7 @@
         <v>4.306094254478001</v>
       </c>
       <c r="D142" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E142">
         <v>3.499007110842255</v>
@@ -8596,7 +8614,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8610,7 +8628,7 @@
         <v>4.306502251029037</v>
       </c>
       <c r="D143" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E143">
         <v>3.499391412493775</v>
@@ -8646,7 +8664,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8660,7 +8678,7 @@
         <v>4.318153845587818</v>
       </c>
       <c r="D144" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E144">
         <v>3.510366326424823</v>
@@ -8696,7 +8714,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8746,7 +8764,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8796,7 +8814,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8846,7 +8864,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8860,7 +8878,7 @@
         <v>2.959973514323903</v>
       </c>
       <c r="D148" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E148">
         <v>2.331565797970563</v>
@@ -8896,7 +8914,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8910,7 +8928,7 @@
         <v>2.954681081546583</v>
       </c>
       <c r="D149" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E149">
         <v>2.325889855571697</v>
@@ -8946,7 +8964,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8960,7 +8978,7 @@
         <v>2.952436806561317</v>
       </c>
       <c r="D150" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E150">
         <v>2.323482951964311</v>
@@ -8996,7 +9014,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9010,7 +9028,7 @@
         <v>2.939220179650368</v>
       </c>
       <c r="D151" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E151">
         <v>2.309308598465612</v>
@@ -9046,7 +9064,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9060,7 +9078,7 @@
         <v>2.885800805603528</v>
       </c>
       <c r="D152" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E152">
         <v>2.285985098138231</v>
@@ -9096,7 +9114,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9110,7 +9128,7 @@
         <v>2.882518664640946</v>
       </c>
       <c r="D153" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E153">
         <v>2.285985098138231</v>
@@ -9146,7 +9164,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9160,7 +9178,7 @@
         <v>2.871759791100637</v>
       </c>
       <c r="D154" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E154">
         <v>2.270895377157946</v>
@@ -9196,7 +9214,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9210,7 +9228,7 @@
         <v>2.868186342783224</v>
       </c>
       <c r="D155" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E155">
         <v>2.270895377157946</v>
@@ -9246,7 +9264,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9260,7 +9278,7 @@
         <v>2.851373977249472</v>
       </c>
       <c r="D156" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E156">
         <v>2.248986971400885</v>
@@ -9296,7 +9314,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9310,7 +9328,7 @@
         <v>2.813597099989564</v>
       </c>
       <c r="D157" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E157">
         <v>2.215446285791325</v>
@@ -9346,7 +9364,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9360,7 +9378,7 @@
         <v>2.783887421732515</v>
       </c>
       <c r="D158" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E158">
         <v>2.183719283702006</v>
@@ -9396,7 +9414,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9410,7 +9428,7 @@
         <v>2.721632856402064</v>
       </c>
       <c r="D159" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E159">
         <v>2.127916568873808</v>
@@ -9446,7 +9464,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9460,7 +9478,7 @@
         <v>2.678525715783303</v>
       </c>
       <c r="D160" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E160">
         <v>2.09532033365037</v>
@@ -9496,7 +9514,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9510,7 +9528,7 @@
         <v>2.69110921416971</v>
       </c>
       <c r="D161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E161">
         <v>2.09532033365037</v>
@@ -9546,7 +9564,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9646,7 +9664,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9696,7 +9714,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9746,7 +9764,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9896,7 +9914,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9946,7 +9964,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9996,7 +10014,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10046,7 +10064,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10096,7 +10114,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10146,7 +10164,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10196,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10210,7 +10228,7 @@
         <v>0.9328900239147986</v>
       </c>
       <c r="D175" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E175">
         <v>0.9481209772972727</v>
@@ -10246,7 +10264,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10260,7 +10278,7 @@
         <v>0.8361716558948933</v>
       </c>
       <c r="D176" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E176">
         <v>0.9453648051842674</v>
@@ -10310,7 +10328,7 @@
         <v>1.860133746163766</v>
       </c>
       <c r="D177" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E177">
         <v>1.319668494742769</v>
@@ -10346,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10360,7 +10378,7 @@
         <v>0.8121110647030001</v>
       </c>
       <c r="D178" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E178">
         <v>0.9618784389925015</v>
@@ -10396,7 +10414,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10410,7 +10428,7 @@
         <v>1.83652515616036</v>
       </c>
       <c r="D179" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E179">
         <v>1.296242563075947</v>
@@ -10446,7 +10464,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10460,7 +10478,7 @@
         <v>0.787726176769115</v>
       </c>
       <c r="D180" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E180">
         <v>1.126454507889258</v>
@@ -10496,7 +10514,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10510,7 +10528,7 @@
         <v>1.791439637530079</v>
       </c>
       <c r="D181" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E181">
         <v>1.27124240240025</v>
@@ -10546,7 +10564,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10560,7 +10578,7 @@
         <v>1.811330062457952</v>
       </c>
       <c r="D182" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E182">
         <v>1.27124240240025</v>
@@ -10596,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10610,7 +10628,7 @@
         <v>1.791373892486802</v>
       </c>
       <c r="D183" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E183">
         <v>1.27124240240025</v>
@@ -10646,7 +10664,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10660,7 +10678,7 @@
         <v>0.7617026177031843</v>
       </c>
       <c r="D184" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E184">
         <v>1.161198572371399</v>
@@ -10696,7 +10714,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10710,7 +10728,7 @@
         <v>1.756679227858482</v>
       </c>
       <c r="D185" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E185">
         <v>1.246983702650287</v>
@@ -10746,7 +10764,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10760,7 +10778,7 @@
         <v>1.786882211053019</v>
       </c>
       <c r="D186" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E186">
         <v>1.246983702650287</v>
@@ -10796,7 +10814,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10810,7 +10828,7 @@
         <v>1.766831465254384</v>
       </c>
       <c r="D187" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E187">
         <v>1.246983702650287</v>
@@ -10846,7 +10864,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10860,7 +10878,7 @@
         <v>0.7364508717646272</v>
       </c>
       <c r="D188" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E188">
         <v>1.146806092355067</v>
@@ -10896,7 +10914,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10910,7 +10928,7 @@
         <v>1.727529637465925</v>
       </c>
       <c r="D189" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E189">
         <v>1.218500388609561</v>
@@ -10946,7 +10964,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10960,7 +10978,7 @@
         <v>1.758176804895015</v>
       </c>
       <c r="D190" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E190">
         <v>1.218500388609561</v>
@@ -10996,7 +11014,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11010,7 +11028,7 @@
         <v>1.738015013037742</v>
       </c>
       <c r="D191" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E191">
         <v>1.218500388609561</v>
@@ -11046,7 +11064,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11060,7 +11078,7 @@
         <v>0.735911718893199</v>
       </c>
       <c r="D192" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E192">
         <v>1.39631619853638</v>
@@ -11096,7 +11114,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11110,7 +11128,7 @@
         <v>0.7068015741081979</v>
       </c>
       <c r="D193" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E193">
         <v>1.39631619853638</v>
@@ -11146,7 +11164,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11160,7 +11178,7 @@
         <v>1.69440254301529</v>
       </c>
       <c r="D194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>1.186130484889226</v>
@@ -11196,7 +11214,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11210,7 +11228,7 @@
         <v>1.725554504264581</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E195">
         <v>1.186130484889226</v>
@@ -11246,7 +11264,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11260,7 +11278,7 @@
         <v>1.705266513952258</v>
       </c>
       <c r="D196" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E196">
         <v>1.186130484889226</v>
@@ -11296,7 +11314,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11310,7 +11328,7 @@
         <v>0.7015226398920635</v>
       </c>
       <c r="D197" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E197">
         <v>1.362242615672869</v>
@@ -11346,7 +11364,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11360,7 +11378,7 @@
         <v>0.6731065866098378</v>
       </c>
       <c r="D198" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E198">
         <v>1.362242615672869</v>
@@ -11396,7 +11414,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11410,7 +11428,7 @@
         <v>1.672556215816603</v>
       </c>
       <c r="D199" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E199">
         <v>1.164783502312224</v>
@@ -11446,7 +11464,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11460,7 +11478,7 @@
         <v>1.70404107348035</v>
       </c>
       <c r="D200" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E200">
         <v>1.164783502312224</v>
@@ -11496,7 +11514,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11510,7 +11528,7 @@
         <v>1.683669859064413</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E201">
         <v>1.164783502312224</v>
@@ -11546,7 +11564,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11560,7 +11578,7 @@
         <v>0.6788440716572364</v>
       </c>
       <c r="D202" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E202">
         <v>1.339772107697077</v>
@@ -11596,7 +11614,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11610,7 +11628,7 @@
         <v>0.6508857509448882</v>
       </c>
       <c r="D203" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E203">
         <v>1.339772107697077</v>
@@ -11646,7 +11664,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11660,7 +11678,7 @@
         <v>1.643503437868948</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E204">
         <v>1.136394787860515</v>
@@ -11696,7 +11714,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11710,7 +11728,7 @@
         <v>1.675431004529993</v>
       </c>
       <c r="D205" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E205">
         <v>1.136394787860515</v>
@@ -11746,7 +11764,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11760,7 +11778,7 @@
         <v>1.654949112864731</v>
       </c>
       <c r="D206" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E206">
         <v>1.136394787860515</v>
@@ -11796,7 +11814,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11810,7 +11828,7 @@
         <v>0.648684521216337</v>
       </c>
       <c r="D207" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E207">
         <v>1.309889250379489</v>
@@ -11846,7 +11864,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11860,7 +11878,7 @@
         <v>0.6213349253752734</v>
       </c>
       <c r="D208" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E208">
         <v>1.309889250379489</v>
@@ -11896,7 +11914,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11910,7 +11928,7 @@
         <v>1.629688879456757</v>
       </c>
       <c r="D209" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E209">
         <v>1.122895990783459</v>
@@ -11960,7 +11978,7 @@
         <v>1.661826953674558</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E210">
         <v>1.122895990783459</v>
@@ -12010,7 +12028,7 @@
         <v>1.623163250060685</v>
       </c>
       <c r="D211" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E211">
         <v>1.122895990783459</v>
@@ -12060,7 +12078,7 @@
         <v>0.6343436939122524</v>
       </c>
       <c r="D212" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E212">
         <v>1.295679990298378</v>
@@ -12110,7 +12128,7 @@
         <v>0.6072835459617298</v>
       </c>
       <c r="D213" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E213">
         <v>1.295679990298378</v>
@@ -12160,7 +12178,7 @@
         <v>1.607589133113905</v>
       </c>
       <c r="D214" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E214">
         <v>1.101301381499872</v>
@@ -12196,7 +12214,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12210,7 +12228,7 @@
         <v>1.640063965371216</v>
       </c>
       <c r="D215" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E215">
         <v>1.101301381499872</v>
@@ -12246,7 +12264,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12260,7 +12278,7 @@
         <v>1.619445257306888</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E216">
         <v>1.101301381499872</v>
@@ -12296,7 +12314,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12310,7 +12328,7 @@
         <v>0.6114020524706252</v>
       </c>
       <c r="D217" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E217">
         <v>1.272948822631444</v>
@@ -12346,7 +12364,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12360,7 +12378,7 @@
         <v>0.5848049468244287</v>
       </c>
       <c r="D218" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>1.272948822631444</v>
@@ -12396,7 +12414,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12410,7 +12428,7 @@
         <v>1.581012843353852</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E219">
         <v>1.075332549791479</v>
@@ -12446,7 +12464,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12460,7 +12478,7 @@
         <v>1.613892647645603</v>
       </c>
       <c r="D220" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E220">
         <v>1.075332549791479</v>
@@ -12496,7 +12514,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12510,7 +12528,7 @@
         <v>1.593172696572664</v>
       </c>
       <c r="D221" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E221">
         <v>1.075332549791479</v>
@@ -12546,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12560,7 +12578,7 @@
         <v>0.5838133326244757</v>
       </c>
       <c r="D222" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E222">
         <v>1.245613210306819</v>
@@ -12596,7 +12614,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12610,7 +12628,7 @@
         <v>0.5577730635256328</v>
       </c>
       <c r="D223" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E223">
         <v>1.245613210306819</v>
@@ -12646,7 +12664,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12660,7 +12678,7 @@
         <v>1.084913495598071</v>
       </c>
       <c r="D224" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E224">
         <v>1.231364667854545</v>
@@ -12696,7 +12714,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12710,7 +12728,7 @@
         <v>1.091978143921128</v>
       </c>
       <c r="D225" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E225">
         <v>1.231364667854545</v>
@@ -12746,7 +12764,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12796,7 +12814,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12810,7 +12828,7 @@
         <v>1.21869175173632</v>
       </c>
       <c r="D227" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E227">
         <v>1.069755686141992</v>
@@ -12846,7 +12864,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12860,7 +12878,7 @@
         <v>1.184556198440929</v>
       </c>
       <c r="D228" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E228">
         <v>1.069755686141992</v>
@@ -12896,7 +12914,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12910,7 +12928,7 @@
         <v>1.060519812222489</v>
       </c>
       <c r="D229" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E229">
         <v>0.9907313015562922</v>
@@ -12946,7 +12964,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12960,7 +12978,7 @@
         <v>1.017939761129645</v>
       </c>
       <c r="D230" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E230">
         <v>0.9907313015562922</v>
@@ -12996,7 +13014,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13010,7 +13028,7 @@
         <v>1.755318635505916</v>
       </c>
       <c r="D231" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E231">
         <v>1.003833585600265</v>
@@ -13046,7 +13064,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13060,7 +13078,7 @@
         <v>1.894053096403</v>
       </c>
       <c r="D232" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E232">
         <v>1.003833585600265</v>
@@ -13096,7 +13114,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13110,7 +13128,7 @@
         <v>1.97376040323609</v>
       </c>
       <c r="D233" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E233">
         <v>1.250262419204153</v>
@@ -13146,7 +13164,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13160,7 +13178,7 @@
         <v>2.034815821986728</v>
       </c>
       <c r="D234" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E234">
         <v>1.357988243685597</v>
@@ -13196,7 +13214,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13210,7 +13228,7 @@
         <v>2.10245468159479</v>
       </c>
       <c r="D235" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E235">
         <v>1.356708020256039</v>
@@ -13246,7 +13264,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13260,7 +13278,7 @@
         <v>2.160736912923812</v>
       </c>
       <c r="D236" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E236">
         <v>1.515238926320149</v>
@@ -13296,7 +13314,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13310,7 +13328,7 @@
         <v>2.25315272423952</v>
       </c>
       <c r="D237" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E237">
         <v>1.696228284995405</v>
@@ -13346,7 +13364,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13360,7 +13378,7 @@
         <v>2.36943391560179</v>
       </c>
       <c r="D238" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E238">
         <v>1.892500425794016</v>
@@ -13396,7 +13414,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13410,7 +13428,7 @@
         <v>2.474058411102812</v>
       </c>
       <c r="D239" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E239">
         <v>1.89058438855279</v>
@@ -13446,7 +13464,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13460,7 +13478,7 @@
         <v>2.503056313450243</v>
       </c>
       <c r="D240" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E240">
         <v>1.996322171701399</v>
@@ -13496,7 +13514,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13510,7 +13528,7 @@
         <v>2.525264172262913</v>
       </c>
       <c r="D241" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E241">
         <v>1.973847066177296</v>
@@ -13546,7 +13564,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13560,7 +13578,7 @@
         <v>2.554243076596262</v>
       </c>
       <c r="D242" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E242">
         <v>1.938989294196617</v>
@@ -13596,7 +13614,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13610,7 +13628,7 @@
         <v>2.598334390223854</v>
       </c>
       <c r="D243" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E243">
         <v>2.028465786771591</v>
@@ -13646,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13660,7 +13678,7 @@
         <v>2.670586589154834</v>
       </c>
       <c r="D244" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E244">
         <v>1.994395774818371</v>
@@ -13710,7 +13728,7 @@
         <v>2.717624878766997</v>
       </c>
       <c r="D245" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E245">
         <v>2.20711354567414</v>
@@ -13760,7 +13778,7 @@
         <v>2.768201130893359</v>
       </c>
       <c r="D246" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E246">
         <v>2.294068506214541</v>
@@ -13796,7 +13814,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13810,7 +13828,7 @@
         <v>2.800856629280805</v>
       </c>
       <c r="D247" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E247">
         <v>2.225122088576691</v>
@@ -13846,7 +13864,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13860,7 +13878,7 @@
         <v>2.80951643088527</v>
       </c>
       <c r="D248" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E248">
         <v>2.242646460311337</v>
@@ -13896,7 +13914,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13910,7 +13928,7 @@
         <v>2.799569806125956</v>
       </c>
       <c r="D249" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E249">
         <v>2.14320981989216</v>
@@ -13960,7 +13978,7 @@
         <v>2.819828844666985</v>
       </c>
       <c r="D250" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E250">
         <v>2.18506309598321</v>
@@ -13996,7 +14014,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14010,7 +14028,7 @@
         <v>2.819851650007405</v>
       </c>
       <c r="D251" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E251">
         <v>2.072484872689354</v>
@@ -14060,7 +14078,7 @@
         <v>2.840423697083499</v>
       </c>
       <c r="D252" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E252">
         <v>2.262963564508703</v>
@@ -14110,7 +14128,7 @@
         <v>2.908629147129241</v>
       </c>
       <c r="D253" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E253">
         <v>2.216875943157096</v>
@@ -14146,7 +14164,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14160,7 +14178,7 @@
         <v>3.004384252257208</v>
       </c>
       <c r="D254" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E254">
         <v>2.339997391123474</v>
@@ -14196,7 +14214,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14210,7 +14228,7 @@
         <v>3.088901753172625</v>
       </c>
       <c r="D255" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E255">
         <v>2.06246025697973</v>
@@ -14246,7 +14264,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14260,7 +14278,7 @@
         <v>3.179054845713715</v>
       </c>
       <c r="D256" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E256">
         <v>2.414075593575115</v>
@@ -14296,7 +14314,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14310,7 +14328,7 @@
         <v>3.299462923221598</v>
       </c>
       <c r="D257" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E257">
         <v>2.237378699869055</v>
@@ -14346,7 +14364,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14360,7 +14378,7 @@
         <v>3.418692237363245</v>
       </c>
       <c r="D258" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E258">
         <v>2.342027703405609</v>
@@ -14396,7 +14414,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14410,7 +14428,7 @@
         <v>3.512759057977069</v>
       </c>
       <c r="D259" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E259">
         <v>2.424591283628788</v>
@@ -14446,7 +14464,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14460,7 +14478,7 @@
         <v>3.645345160280047</v>
       </c>
       <c r="D260" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E260">
         <v>2.540963700837517</v>
@@ -14496,7 +14514,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14510,7 +14528,7 @@
         <v>3.815771971902112</v>
       </c>
       <c r="D261" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E261">
         <v>2.690549363898303</v>
@@ -14546,7 +14564,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14560,7 +14578,7 @@
         <v>4.010037470388323</v>
       </c>
       <c r="D262" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E262">
         <v>2.861058529236299</v>
@@ -14596,7 +14614,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14610,7 +14628,7 @@
         <v>4.152500561307447</v>
       </c>
       <c r="D263" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E263">
         <v>2.986100098188981</v>
@@ -14646,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14660,7 +14678,7 @@
         <v>4.227000299262723</v>
       </c>
       <c r="D264" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E264">
         <v>3.05148941454026</v>
@@ -14696,7 +14714,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14710,7 +14728,7 @@
         <v>3.628868452425993</v>
       </c>
       <c r="D265" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E265">
         <v>3.018868452425993</v>
@@ -14746,7 +14764,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14760,7 +14778,7 @@
         <v>3.56416211054958</v>
       </c>
       <c r="D266" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E266">
         <v>2.954162110549579</v>
@@ -14796,7 +14814,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14810,7 +14828,7 @@
         <v>3.491997735810393</v>
       </c>
       <c r="D267" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E267">
         <v>2.881997735810393</v>
@@ -14846,7 +14864,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14860,7 +14878,7 @@
         <v>3.304014584160329</v>
       </c>
       <c r="D268" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E268">
         <v>2.694014584160328</v>
@@ -14896,7 +14914,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14910,7 +14928,7 @@
         <v>3.180251695694135</v>
       </c>
       <c r="D269" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E269">
         <v>2.570251695694135</v>
@@ -14946,7 +14964,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14960,7 +14978,7 @@
         <v>3.152401945865307</v>
       </c>
       <c r="D270" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E270">
         <v>2.542401945865306</v>
@@ -14996,7 +15014,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15010,7 +15028,7 @@
         <v>2.145825454055195</v>
       </c>
       <c r="D271" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E271">
         <v>2.567272076620798</v>
@@ -15046,7 +15064,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15060,7 +15078,7 @@
         <v>3.117834193471839</v>
       </c>
       <c r="D272" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E272">
         <v>2.507834193471838</v>
@@ -15096,7 +15114,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15110,7 +15128,7 @@
         <v>2.068689520733654</v>
       </c>
       <c r="D273" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E273">
         <v>2.489975777533515</v>
@@ -15146,7 +15164,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15160,7 +15178,7 @@
         <v>3.048235451140136</v>
       </c>
       <c r="D274" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E274">
         <v>2.438235451140136</v>
@@ -15196,7 +15214,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15210,7 +15228,7 @@
         <v>1.98934486068918</v>
       </c>
       <c r="D275" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E275">
         <v>2.539161477129087</v>
@@ -15246,7 +15264,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15260,7 +15278,7 @@
         <v>2.976643803615602</v>
       </c>
       <c r="D276" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E276">
         <v>2.366643803615601</v>
@@ -15296,7 +15314,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15310,7 +15328,7 @@
         <v>1.910228381091732</v>
       </c>
       <c r="D277" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E277">
         <v>2.463005697391833</v>
@@ -15346,7 +15364,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15360,7 +15378,7 @@
         <v>2.905258040319775</v>
       </c>
       <c r="D278" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E278">
         <v>2.295258040319774</v>
@@ -15396,7 +15414,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15410,7 +15428,7 @@
         <v>1.737565923958936</v>
       </c>
       <c r="D279" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E279">
         <v>2.268709795269682</v>
@@ -15446,7 +15464,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15460,7 +15478,7 @@
         <v>1.733986526635413</v>
       </c>
       <c r="D280" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E280">
         <v>2.293359172208309</v>
@@ -15496,7 +15514,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15510,7 +15528,7 @@
         <v>2.746237323409084</v>
       </c>
       <c r="D281" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E281">
         <v>2.136237323409084</v>
@@ -15546,7 +15564,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15560,7 +15578,7 @@
         <v>1.537618654463894</v>
       </c>
       <c r="D282" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E282">
         <v>2.074713337366754</v>
@@ -15596,7 +15614,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15610,7 +15628,7 @@
         <v>1.543163834914946</v>
       </c>
       <c r="D283" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E283">
         <v>2.109677454398378</v>
@@ -15646,7 +15664,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15660,7 +15678,7 @@
         <v>2.574060508010575</v>
       </c>
       <c r="D284" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E284">
         <v>1.964060508010575</v>
@@ -15696,7 +15714,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15710,7 +15728,7 @@
         <v>1.32861267508225</v>
       </c>
       <c r="D285" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E285">
         <v>1.871927774038136</v>
@@ -15746,7 +15764,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15760,7 +15778,7 @@
         <v>1.343695826814607</v>
       </c>
       <c r="D286" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E286">
         <v>1.91767394556167</v>
@@ -15796,7 +15814,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15810,7 +15828,7 @@
         <v>2.394083136876382</v>
       </c>
       <c r="D287" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E287">
         <v>1.784083136876382</v>
@@ -15846,7 +15864,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15860,7 +15878,7 @@
         <v>1.270355943810468</v>
       </c>
       <c r="D288" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E288">
         <v>1.815404874054204</v>
@@ -15896,7 +15914,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15910,7 +15928,7 @@
         <v>1.288097636850863</v>
       </c>
       <c r="D289" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E289">
         <v>1.864156353143347</v>
@@ -15946,7 +15964,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15960,7 +15978,7 @@
         <v>2.343917618281236</v>
       </c>
       <c r="D290" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E290">
         <v>1.733917618281236</v>
@@ -15996,7 +16014,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16010,7 +16028,7 @@
         <v>1.164376800206434</v>
       </c>
       <c r="D291" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E291">
         <v>1.712579871628862</v>
@@ -16046,7 +16064,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16060,7 +16078,7 @@
         <v>1.186954843054156</v>
       </c>
       <c r="D292" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E292">
         <v>1.76679852876107</v>
@@ -16096,7 +16114,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16110,7 +16128,7 @@
         <v>2.252657800177763</v>
       </c>
       <c r="D293" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E293">
         <v>1.642657800177763</v>
@@ -16146,7 +16164,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16160,7 +16178,7 @@
         <v>1.095337982971794</v>
       </c>
       <c r="D294" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E294">
         <v>1.645595781097634</v>
@@ -16196,7 +16214,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16210,7 +16228,7 @@
         <v>1.121066606764748</v>
       </c>
       <c r="D295" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E295">
         <v>1.703375964515756</v>
@@ -16246,7 +16264,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16260,7 +16278,7 @@
         <v>2.193207707559045</v>
       </c>
       <c r="D296" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E296">
         <v>1.583207707559045</v>
@@ -16296,7 +16314,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16310,7 +16328,7 @@
         <v>0.875155284260706</v>
       </c>
       <c r="D297" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E297">
         <v>1.489897717173242</v>
@@ -16346,7 +16364,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16360,7 +16378,7 @@
         <v>0.9109319280345227</v>
       </c>
       <c r="D298" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E298">
         <v>1.501104953596641</v>
@@ -16396,7 +16414,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16410,7 +16428,7 @@
         <v>2.003605939224497</v>
       </c>
       <c r="D299" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E299">
         <v>1.393605939224496</v>
@@ -16446,7 +16464,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16460,7 +16478,7 @@
         <v>0.7877632879655483</v>
       </c>
       <c r="D300" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E300">
         <v>1.407881022237508</v>
@@ -16496,7 +16514,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16510,7 +16528,7 @@
         <v>0.8275280585544227</v>
       </c>
       <c r="D301" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E301">
         <v>1.420822226841367</v>
@@ -16546,7 +16564,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16560,7 +16578,7 @@
         <v>1.928351720192556</v>
       </c>
       <c r="D302" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E302">
         <v>1.318351720192555</v>
@@ -16596,7 +16614,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16610,7 +16628,7 @@
         <v>0.6445889510900153</v>
       </c>
       <c r="D303" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E303">
         <v>1.273513043384081</v>
@@ -16646,7 +16664,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16660,7 +16678,7 @@
         <v>0.6908874711791615</v>
       </c>
       <c r="D304" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E304">
         <v>1.289295008640233</v>
@@ -16696,7 +16714,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16710,7 +16728,7 @@
         <v>1.805062707883069</v>
       </c>
       <c r="D305" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E305">
         <v>1.195062707883069</v>
@@ -16746,7 +16764,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16760,7 +16778,7 @@
         <v>0.5834745700515587</v>
       </c>
       <c r="D306" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E306">
         <v>1.216157681814259</v>
@@ -16796,7 +16814,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16810,7 +16828,7 @@
         <v>0.6325620400690468</v>
       </c>
       <c r="D307" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E307">
         <v>1.233152233995777</v>
@@ -16846,7 +16864,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16860,7 +16878,7 @@
         <v>1.752436435322175</v>
       </c>
       <c r="D308" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E308">
         <v>1.142436435322175</v>
@@ -16896,7 +16914,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16910,7 +16928,7 @@
         <v>0.6410588642705362</v>
       </c>
       <c r="D309" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E309">
         <v>1.24133108972403</v>
@@ -16946,7 +16964,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16960,7 +16978,7 @@
         <v>0.6556505260902954</v>
       </c>
       <c r="D310" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E310">
         <v>1.24133108972403</v>
@@ -16996,7 +17014,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17010,7 +17028,7 @@
         <v>1.760103008510213</v>
       </c>
       <c r="D311" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E311">
         <v>1.150103008510213</v>
@@ -17046,7 +17064,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17060,7 +17078,7 @@
         <v>0.6538601304024763</v>
       </c>
       <c r="D312" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E312">
         <v>1.253653306395731</v>
@@ -17096,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17110,7 +17128,7 @@
         <v>0.6691703664125939</v>
       </c>
       <c r="D313" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E313">
         <v>1.253653306395731</v>
@@ -17146,7 +17164,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17160,7 +17178,7 @@
         <v>1.771653423273752</v>
       </c>
       <c r="D314" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E314">
         <v>1.161653423273751</v>
@@ -17196,7 +17214,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17210,7 +17228,7 @@
         <v>0.5994681371241404</v>
       </c>
       <c r="D315" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E315">
         <v>1.201296772325317</v>
@@ -17246,7 +17264,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17260,7 +17278,7 @@
         <v>0.6117251843223768</v>
       </c>
       <c r="D316" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E316">
         <v>1.201296772325317</v>
@@ -17296,7 +17314,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17310,7 +17328,7 @@
         <v>1.722576240149433</v>
       </c>
       <c r="D317" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E317">
         <v>1.112576240149433</v>
@@ -17346,7 +17364,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17360,7 +17378,7 @@
         <v>0.6080222404361217</v>
       </c>
       <c r="D318" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E318">
         <v>1.209530763663045</v>
@@ -17396,7 +17414,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17410,7 +17428,7 @@
         <v>0.6207594555957376</v>
       </c>
       <c r="D319" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E319">
         <v>1.209530763663045</v>
@@ -17446,7 +17464,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17460,7 +17478,7 @@
         <v>1.730294495528642</v>
       </c>
       <c r="D320" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E320">
         <v>1.120294495528642</v>
@@ -17496,7 +17514,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17510,7 +17528,7 @@
         <v>0.5618859798618736</v>
       </c>
       <c r="D321" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E321">
         <v>1.165121015958519</v>
@@ -17546,7 +17564,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17560,7 +17578,7 @@
         <v>0.5720334257169055</v>
       </c>
       <c r="D322" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E322">
         <v>1.165121015958519</v>
@@ -17596,7 +17614,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17610,7 +17628,7 @@
         <v>1.688666351892003</v>
       </c>
       <c r="D323" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E323">
         <v>1.078666351892003</v>
@@ -17646,7 +17664,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17660,7 +17678,7 @@
         <v>0.508437810595022</v>
       </c>
       <c r="D324" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E324">
         <v>1.11367298608211</v>
@@ -17696,7 +17714,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17710,7 +17728,7 @@
         <v>0.5155850473643886</v>
       </c>
       <c r="D325" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E325">
         <v>1.11367298608211</v>
@@ -17746,7 +17764,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17760,7 +17778,7 @@
         <v>1.640440768811309</v>
       </c>
       <c r="D326" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E326">
         <v>1.030440768811308</v>
@@ -17796,7 +17814,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17810,7 +17828,7 @@
         <v>0.4164767378858123</v>
       </c>
       <c r="D327" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E327">
         <v>1.025153284077196</v>
@@ -17846,7 +17864,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17860,7 +17878,7 @@
         <v>0.4184619185987364</v>
       </c>
       <c r="D328" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E328">
         <v>1.025153284077196</v>
@@ -17896,7 +17914,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17910,7 +17928,7 @@
         <v>1.557465497385535</v>
       </c>
       <c r="D329" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E329">
         <v>0.9474654973855348</v>
@@ -17946,7 +17964,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17960,7 +17978,7 @@
         <v>0.3644704529510241</v>
       </c>
       <c r="D330" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E330">
         <v>0.9750931802834177</v>
@@ -17996,7 +18014,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18010,7 +18028,7 @@
         <v>0.3635363619524323</v>
       </c>
       <c r="D331" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E331">
         <v>0.9750931802834177</v>
@@ -18046,7 +18064,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18060,7 +18078,7 @@
         <v>1.565054544022541</v>
       </c>
       <c r="D332" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E332">
         <v>0.9005409076522746</v>
@@ -18096,7 +18114,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18110,7 +18128,7 @@
         <v>0.2866150347691372</v>
       </c>
       <c r="D333" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E333">
         <v>0.9143380680881883</v>
@@ -18146,7 +18164,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18160,7 +18178,7 @@
         <v>0.2813106812114787</v>
       </c>
       <c r="D334" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E334">
         <v>0.9143380680881883</v>
@@ -18196,7 +18214,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18210,7 +18228,7 @@
         <v>0.3483831526216896</v>
       </c>
       <c r="D335" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E335">
         <v>0.9143380680881883</v>
@@ -18246,7 +18264,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18260,7 +18278,7 @@
         <v>1.495130343077478</v>
       </c>
       <c r="D336" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E336">
         <v>0.8302929835546884</v>
@@ -18296,7 +18314,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18310,7 +18328,7 @@
         <v>0.2225831635998929</v>
       </c>
       <c r="D337" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E337">
         <v>0.8619688447062037</v>
@@ -18360,7 +18378,7 @@
         <v>0.2987488573747035</v>
       </c>
       <c r="D338" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E338">
         <v>0.8619688447062037</v>
@@ -18410,7 +18428,7 @@
         <v>0.2938174275967516</v>
       </c>
       <c r="D339" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E339">
         <v>0.8619688447062037</v>
@@ -18460,7 +18478,7 @@
         <v>1.445188832037704</v>
       </c>
       <c r="D340" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E340">
         <v>0.7801202618156564</v>
@@ -18510,7 +18528,7 @@
         <v>0.3281392211768228</v>
       </c>
       <c r="D341" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E341">
         <v>0.8803786785285439</v>
@@ -18546,7 +18564,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18560,7 +18578,7 @@
         <v>0.3180121272020529</v>
       </c>
       <c r="D342" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E342">
         <v>0.8803786785285439</v>
@@ -18596,7 +18614,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18610,7 +18628,7 @@
         <v>0.3129994178045763</v>
       </c>
       <c r="D343" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E343">
         <v>0.8803786785285439</v>
@@ -18646,7 +18664,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18660,7 +18678,7 @@
         <v>1.462745229855035</v>
       </c>
       <c r="D344" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E344">
         <v>0.7977579392525129</v>
@@ -18696,7 +18714,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18710,7 +18728,7 @@
         <v>0.3459316339300287</v>
       </c>
       <c r="D345" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E345">
         <v>0.8966943930572944</v>
@@ -18746,7 +18764,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18760,7 +18778,7 @@
         <v>0.3350841993579632</v>
       </c>
       <c r="D346" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E346">
         <v>0.8966943930572944</v>
@@ -18796,7 +18814,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18810,7 +18828,7 @@
         <v>0.3299994559007571</v>
       </c>
       <c r="D347" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E347">
         <v>0.8966943930572944</v>
@@ -18846,7 +18864,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18860,7 +18878,7 @@
         <v>1.478304586756625</v>
       </c>
       <c r="D348" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E348">
         <v>0.8133893302138313</v>
@@ -18896,7 +18914,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18910,7 +18928,7 @@
         <v>0.3746816311597856</v>
       </c>
       <c r="D349" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E349">
         <v>0.9230582569137313</v>
@@ -18946,7 +18964,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18960,7 +18978,7 @@
         <v>0.3626702290885397</v>
       </c>
       <c r="D350" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E350">
         <v>0.9230582569137313</v>
@@ -18996,7 +19014,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19010,7 +19028,7 @@
         <v>0.357469088881416</v>
       </c>
       <c r="D351" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E351">
         <v>0.9230582569137313</v>
@@ -19046,7 +19064,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19060,7 +19078,7 @@
         <v>1.503446284738923</v>
       </c>
       <c r="D352" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E352">
         <v>0.8386474249460472</v>
@@ -19096,7 +19114,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19110,7 +19128,7 @@
         <v>0.3609903029368784</v>
       </c>
       <c r="D353" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E353">
         <v>0.9727726579916833</v>
@@ -19160,7 +19178,7 @@
         <v>0.4278925267560636</v>
       </c>
       <c r="D354" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E354">
         <v>0.9853909591149721</v>
@@ -19210,7 +19228,7 @@
         <v>0.4224161869807217</v>
       </c>
       <c r="D355" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E355">
         <v>0.9853909591149721</v>
@@ -19260,7 +19278,7 @@
         <v>1.508365731249223</v>
       </c>
       <c r="D356" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E356">
         <v>0.898365731249223</v>
@@ -19310,7 +19328,7 @@
         <v>0.5369709001154694</v>
       </c>
       <c r="D357" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E357">
         <v>1.089636746312885</v>
@@ -19360,7 +19378,7 @@
         <v>0.531034314039033</v>
       </c>
       <c r="D358" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E358">
         <v>1.089636746312885</v>
@@ -19410,7 +19428,7 @@
         <v>1.608239178586738</v>
       </c>
       <c r="D359" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E359">
         <v>0.9982391785867382</v>
@@ -19460,7 +19478,7 @@
         <v>0.5385854937585846</v>
       </c>
       <c r="D360" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E360">
         <v>0.634839149452838</v>
@@ -19510,7 +19528,7 @@
         <v>2.009812451983092</v>
       </c>
       <c r="D361" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E361">
         <v>1.399812451983092</v>
@@ -19546,7 +19564,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19560,7 +19578,7 @@
         <v>0.9230051396340304</v>
       </c>
       <c r="D362" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E362">
         <v>0.9850070169538339</v>
@@ -19596,7 +19614,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19610,7 +19628,7 @@
         <v>0.8994749023453439</v>
       </c>
       <c r="D363" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E363">
         <v>0.9850070169538339</v>
@@ -19646,7 +19664,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19660,7 +19678,7 @@
         <v>2.109691017081675</v>
       </c>
       <c r="D364" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E364">
         <v>1.499691017081674</v>
@@ -19696,7 +19714,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19710,7 +19728,7 @@
         <v>1.015979656453909</v>
       </c>
       <c r="D365" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E365">
         <v>1.231185799135601</v>
@@ -19746,7 +19764,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19760,7 +19778,7 @@
         <v>0.9827837515750368</v>
       </c>
       <c r="D366" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E366">
         <v>1.231185799135601</v>
@@ -19796,7 +19814,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19810,7 +19828,7 @@
         <v>2.200993423621709</v>
       </c>
       <c r="D367" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E367">
         <v>1.590993423621708</v>
@@ -19846,7 +19864,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19860,7 +19878,7 @@
         <v>1.100970836735415</v>
       </c>
       <c r="D368" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E368">
         <v>1.303589318044656</v>
@@ -19896,7 +19914,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19910,7 +19928,7 @@
         <v>1.058939215094605</v>
       </c>
       <c r="D369" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E369">
         <v>1.303589318044656</v>
@@ -19946,7 +19964,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19960,7 +19978,7 @@
         <v>2.329644706282916</v>
       </c>
       <c r="D370" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E370">
         <v>1.719644706282915</v>
@@ -19996,7 +20014,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20010,7 +20028,7 @@
         <v>1.220729173590548</v>
       </c>
       <c r="D371" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E371">
         <v>1.321050696987874</v>
@@ -20046,7 +20064,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20060,7 +20078,7 @@
         <v>2.471463589779925</v>
       </c>
       <c r="D372" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E372">
         <v>1.861463589779925</v>
@@ -20096,7 +20114,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20146,7 +20164,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20160,7 +20178,7 @@
         <v>2.497443975683849</v>
       </c>
       <c r="D374" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E374">
         <v>1.887443975683849</v>
@@ -20196,7 +20214,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20246,7 +20264,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20296,7 +20314,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20310,7 +20328,7 @@
         <v>2.512308244184901</v>
       </c>
       <c r="D377" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E377">
         <v>1.9023082441849</v>
@@ -20346,7 +20364,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20360,7 +20378,7 @@
         <v>1.390766199655991</v>
       </c>
       <c r="D378" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E378">
         <v>1.47783631505106</v>
@@ -20396,7 +20414,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20410,7 +20428,7 @@
         <v>1.39783631505106</v>
       </c>
       <c r="D379" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E379">
         <v>1.47783631505106</v>
@@ -20446,7 +20464,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20460,7 +20478,7 @@
         <v>2.5135497431605</v>
       </c>
       <c r="D380" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E380">
         <v>1.903549743160499</v>
@@ -20496,7 +20514,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20510,7 +20528,7 @@
         <v>1.39192188073005</v>
       </c>
       <c r="D381" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E381">
         <v>1.488828942112197</v>
@@ -20546,7 +20564,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20560,7 +20578,7 @@
         <v>1.319642873327421</v>
       </c>
       <c r="D382" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E382">
         <v>1.488828942112197</v>
@@ -20596,7 +20614,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20610,7 +20628,7 @@
         <v>1.388828942112196</v>
       </c>
       <c r="D383" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E383">
         <v>1.488828942112197</v>
@@ -20646,7 +20664,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20660,7 +20678,7 @@
         <v>2.501566998394471</v>
       </c>
       <c r="D384" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E384">
         <v>1.891566998394471</v>
@@ -20696,7 +20714,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20710,7 +20728,7 @@
         <v>1.279594745212004</v>
       </c>
       <c r="D385" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E385">
         <v>1.519061703811337</v>
@@ -20746,7 +20764,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20760,7 +20778,7 @@
         <v>1.30964804935207</v>
       </c>
       <c r="D386" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E386">
         <v>1.519061703811337</v>
@@ -20796,7 +20814,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20810,7 +20828,7 @@
         <v>2.48573721583752</v>
       </c>
       <c r="D387" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E387">
         <v>1.875737215837519</v>
@@ -20846,7 +20864,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20860,7 +20878,7 @@
         <v>1.266464050003473</v>
       </c>
       <c r="D388" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E388">
         <v>1.59667031375327</v>
@@ -20896,7 +20914,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20910,7 +20928,7 @@
         <v>1.296444405836825</v>
       </c>
       <c r="D389" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E389">
         <v>1.59667031375327</v>
@@ -20946,7 +20964,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20960,7 +20978,7 @@
         <v>2.454303876936348</v>
       </c>
       <c r="D390" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E390">
         <v>1.844303876936348</v>
@@ -20996,7 +21014,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21010,7 +21028,7 @@
         <v>1.240390312666095</v>
       </c>
       <c r="D391" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E391">
         <v>1.592199793558723</v>
@@ -21046,7 +21064,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21060,7 +21078,7 @@
         <v>1.270225814403128</v>
       </c>
       <c r="D392" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E392">
         <v>1.592199793558723</v>
@@ -21096,7 +21114,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21110,7 +21128,7 @@
         <v>2.438801816749918</v>
       </c>
       <c r="D393" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E393">
         <v>1.828801816749918</v>
@@ -21146,7 +21164,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21160,7 +21178,7 @@
         <v>1.227531460898549</v>
       </c>
       <c r="D394" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E394">
         <v>1.611306442152011</v>
@@ -21196,7 +21214,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21210,7 +21228,7 @@
         <v>1.257295524570208</v>
       </c>
       <c r="D395" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E395">
         <v>1.611306442152011</v>
@@ -21246,7 +21264,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21260,7 +21278,7 @@
         <v>2.435888213210831</v>
       </c>
       <c r="D396" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E396">
         <v>1.825888213210831</v>
@@ -21296,7 +21314,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21310,7 +21328,7 @@
         <v>1.225114646902994</v>
       </c>
       <c r="D397" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E397">
         <v>1.589727863749075</v>
@@ -21346,7 +21364,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21360,7 +21378,7 @@
         <v>1.254865283830232</v>
       </c>
       <c r="D398" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E398">
         <v>1.589727863749075</v>
@@ -21396,7 +21414,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21410,7 +21428,7 @@
         <v>2.394557671241156</v>
       </c>
       <c r="D399" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E399">
         <v>1.784557671241155</v>
@@ -21446,7 +21464,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21460,7 +21478,7 @@
         <v>1.190831248034139</v>
       </c>
       <c r="D400" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E400">
         <v>1.609187949630535</v>
@@ -21496,7 +21514,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21510,7 +21528,7 @@
         <v>1.220391421634328</v>
       </c>
       <c r="D401" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E401">
         <v>1.609187949630535</v>
@@ -21546,7 +21564,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21560,7 +21578,7 @@
         <v>2.366135904185318</v>
       </c>
       <c r="D402" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E402">
         <v>1.756135904185318</v>
@@ -21596,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21610,7 +21628,7 @@
         <v>1.167255588725149</v>
       </c>
       <c r="D403" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E403">
         <v>1.578100832137494</v>
@@ -21646,7 +21664,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21660,7 +21678,7 @@
         <v>1.196684786440288</v>
       </c>
       <c r="D404" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E404">
         <v>1.578100832137494</v>
@@ -21696,7 +21714,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21710,7 +21728,7 @@
         <v>2.396096253709469</v>
       </c>
       <c r="D405" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E405">
         <v>1.786096253709469</v>
@@ -21746,7 +21764,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21760,7 +21778,7 @@
         <v>1.192107491556242</v>
       </c>
       <c r="D406" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E406">
         <v>1.492060423190722</v>
@@ -21796,7 +21814,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21810,7 +21828,7 @@
         <v>1.221674755398221</v>
       </c>
       <c r="D407" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E407">
         <v>1.492060423190722</v>
@@ -21846,7 +21864,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21860,7 +21878,7 @@
         <v>2.341003521520614</v>
       </c>
       <c r="D408" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E408">
         <v>1.731003521520614</v>
@@ -21896,7 +21914,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21910,7 +21928,7 @@
         <v>1.146408451030924</v>
       </c>
       <c r="D409" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E409">
         <v>1.603573943943295</v>
@@ -21946,7 +21964,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21960,7 +21978,7 @@
         <v>1.175721831314429</v>
       </c>
       <c r="D410" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E410">
         <v>1.603573943943295</v>
@@ -21996,7 +22014,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22010,7 +22028,7 @@
         <v>2.3387346635889</v>
       </c>
       <c r="D411" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E411">
         <v>1.7287346635889</v>
@@ -22046,7 +22064,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22060,7 +22078,7 @@
         <v>1.144526449059917</v>
       </c>
       <c r="D412" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E412">
         <v>1.601256255851928</v>
@@ -22096,7 +22114,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22110,7 +22128,7 @@
         <v>1.173829373776917</v>
       </c>
       <c r="D413" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E413">
         <v>1.601256255851928</v>
@@ -22146,7 +22164,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22160,7 +22178,7 @@
         <v>2.321864997704619</v>
       </c>
       <c r="D414" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E414">
         <v>1.711864997704619</v>
@@ -22196,7 +22214,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22210,7 +22228,7 @@
         <v>1.130533177819499</v>
       </c>
       <c r="D415" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E415">
         <v>1.628353938431452</v>
@@ -22246,7 +22264,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22260,7 +22278,7 @@
         <v>1.159758362140719</v>
       </c>
       <c r="D416" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E416">
         <v>1.628353938431452</v>
@@ -22296,7 +22314,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22310,7 +22328,7 @@
         <v>2.329307629672357</v>
       </c>
       <c r="D417" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E417">
         <v>1.719307629672357</v>
@@ -22346,7 +22364,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22360,7 +22378,7 @@
         <v>1.136706789589973</v>
       </c>
       <c r="D418" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E418">
         <v>1.641887405220004</v>
@@ -22396,7 +22414,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22410,7 +22428,7 @@
         <v>1.165966271754362</v>
       </c>
       <c r="D419" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E419">
         <v>1.641887405220004</v>
@@ -22446,7 +22464,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22460,7 +22478,7 @@
         <v>2.283832828965951</v>
       </c>
       <c r="D420" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E420">
         <v>1.673832828965951</v>
@@ -22510,7 +22528,7 @@
         <v>1.09898575674595</v>
       </c>
       <c r="D421" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E421">
         <v>1.611312616281895</v>
@@ -22560,7 +22578,7 @@
         <v>1.128035677616761</v>
       </c>
       <c r="D422" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E422">
         <v>1.611312616281895</v>
@@ -22610,7 +22628,7 @@
         <v>2.182831733767929</v>
       </c>
       <c r="D423" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E423">
         <v>1.572831733767929</v>
@@ -22646,7 +22664,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22660,7 +22678,7 @@
         <v>1.084064563230975</v>
       </c>
       <c r="D424" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E424">
         <v>1.514840661441129</v>
@@ -22696,7 +22714,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22710,7 +22728,7 @@
         <v>1.04379052447924</v>
       </c>
       <c r="D425" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E425">
         <v>1.514840661441129</v>
@@ -22746,7 +22764,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22760,7 +22778,7 @@
         <v>1.987186684521362</v>
       </c>
       <c r="D426" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E426">
         <v>1.377186684521361</v>
@@ -22796,7 +22814,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22810,7 +22828,7 @@
         <v>0.9019433653148159</v>
       </c>
       <c r="D427" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E427">
         <v>1.471274636039009</v>
@@ -22846,7 +22864,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22860,7 +22878,7 @@
         <v>0.8806027184256511</v>
       </c>
       <c r="D428" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E428">
         <v>1.471274636039009</v>
@@ -22896,7 +22914,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22910,7 +22928,7 @@
         <v>1.871503922012645</v>
       </c>
       <c r="D429" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E429">
         <v>1.261503922012645</v>
@@ -22960,7 +22978,7 @@
         <v>0.8271315762745894</v>
       </c>
       <c r="D430" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E430">
         <v>1.39104304268619</v>
@@ -23010,7 +23028,7 @@
         <v>0.784111566287045</v>
       </c>
       <c r="D431" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E431">
         <v>1.39104304268619</v>
@@ -23060,7 +23078,7 @@
         <v>1.725043908638261</v>
       </c>
       <c r="D432" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E432">
         <v>1.115043908638261</v>
@@ -23096,7 +23114,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23110,7 +23128,7 @@
         <v>0.6891081996153199</v>
       </c>
       <c r="D433" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E433">
         <v>1.208315076967225</v>
@@ -23146,7 +23164,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23160,7 +23178,7 @@
         <v>0.6619490666521894</v>
       </c>
       <c r="D434" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E434">
         <v>1.208315076967225</v>
@@ -23196,7 +23214,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23210,7 +23228,7 @@
         <v>1.603418511347999</v>
       </c>
       <c r="D435" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E435">
         <v>0.9934185113479987</v>
@@ -23246,7 +23264,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23260,7 +23278,7 @@
         <v>0.574488873597538</v>
       </c>
       <c r="D436" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E436">
         <v>1.108556250145786</v>
@@ -23296,7 +23314,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23310,7 +23328,7 @@
         <v>0.5605011546266709</v>
       </c>
       <c r="D437" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E437">
         <v>1.108556250145786</v>
@@ -23346,7 +23364,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23360,7 +23378,7 @@
         <v>1.504487777527864</v>
       </c>
       <c r="D438" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E438">
         <v>0.8944877775278632</v>
@@ -23396,7 +23414,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23410,7 +23428,7 @@
         <v>0.4812569147670418</v>
       </c>
       <c r="D439" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E439">
         <v>1.036979636275919</v>
@@ -23446,7 +23464,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23460,7 +23478,7 @@
         <v>0.4779828927766969</v>
       </c>
       <c r="D440" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E440">
         <v>1.036979636275919</v>
@@ -23496,7 +23514,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23510,7 +23528,7 @@
         <v>1.414501209603441</v>
       </c>
       <c r="D441" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E441">
         <v>0.9219355330393615</v>
@@ -23546,7 +23564,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23560,7 +23578,7 @@
         <v>0.3964539049027813</v>
       </c>
       <c r="D442" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E442">
         <v>0.9417865782881711</v>
@@ -23596,7 +23614,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23610,7 +23628,7 @@
         <v>0.4029249720655423</v>
       </c>
       <c r="D443" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E443">
         <v>0.9417865782881711</v>
@@ -23646,7 +23664,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23660,7 +23678,7 @@
         <v>1.374244075534095</v>
       </c>
       <c r="D444" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E444">
         <v>0.8269425846185072</v>
@@ -23696,7 +23714,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23710,7 +23728,7 @@
         <v>0.3063097844755669</v>
       </c>
       <c r="D445" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E445">
         <v>0.873462183832336</v>
@@ -23746,7 +23764,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23760,7 +23778,7 @@
         <v>0.3231397114429218</v>
       </c>
       <c r="D446" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E446">
         <v>0.873462183832336</v>
@@ -23796,7 +23814,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23810,7 +23828,7 @@
         <v>1.297276604707491</v>
       </c>
       <c r="D447" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E447">
         <v>0.7916599773381927</v>
@@ -23846,7 +23864,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23860,7 +23878,7 @@
         <v>0.233440118808713</v>
       </c>
       <c r="D448" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E448">
         <v>0.818230896896579</v>
@@ -23896,7 +23914,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23910,7 +23928,7 @@
         <v>0.2586438215372961</v>
       </c>
       <c r="D449" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E449">
         <v>0.818230896896579</v>
@@ -23946,7 +23964,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23996,7 +24014,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24010,7 +24028,7 @@
         <v>1.228322830557575</v>
       </c>
       <c r="D451" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E451">
         <v>0.7235042792779742</v>
@@ -24046,7 +24064,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24060,7 +24078,7 @@
         <v>0.1681574946714077</v>
       </c>
       <c r="D452" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E452">
         <v>0.7687501793352967</v>
@@ -24096,7 +24114,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24110,7 +24128,7 @@
         <v>0.2008631126431526</v>
       </c>
       <c r="D453" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E453">
         <v>0.7687501793352967</v>
@@ -24146,7 +24164,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24160,7 +24178,7 @@
         <v>1.23967353577152</v>
       </c>
       <c r="D454" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E454">
         <v>1.163072722956397</v>
@@ -24196,7 +24214,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24210,7 +24228,7 @@
         <v>1.225596128630588</v>
       </c>
       <c r="D455" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E455">
         <v>0.6905047055753135</v>
@@ -24246,7 +24264,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24260,7 +24278,7 @@
         <v>0.136549003700944</v>
       </c>
       <c r="D456" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E456">
         <v>0.7447926433919125</v>
@@ -24296,7 +24314,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24310,7 +24328,7 @@
         <v>0.172886893251202</v>
       </c>
       <c r="D457" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E457">
         <v>0.7447926433919125</v>
@@ -24346,7 +24364,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24396,7 +24414,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24410,7 +24428,7 @@
         <v>1.220200273962068</v>
       </c>
       <c r="D459" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E459">
         <v>0.6852080850156392</v>
@@ -24446,7 +24464,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24460,7 +24478,7 @@
         <v>0.1314756598861742</v>
       </c>
       <c r="D460" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E460">
         <v>0.7409473216741169</v>
@@ -24496,7 +24514,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24510,7 +24528,7 @@
         <v>0.1683965498259044</v>
       </c>
       <c r="D461" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E461">
         <v>0.7409473216741169</v>
@@ -24546,7 +24564,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24560,7 +24578,7 @@
         <v>1.216624069904026</v>
       </c>
       <c r="D462" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E462">
         <v>1.236624069904027</v>
@@ -24596,7 +24614,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24610,7 +24628,7 @@
         <v>1.283513715629472</v>
       </c>
       <c r="D463" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E463">
         <v>1.236624069904027</v>
@@ -24646,7 +24664,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24660,7 +24678,7 @@
         <v>1.245299916107382</v>
       </c>
       <c r="D464" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E464">
         <v>0.7098461245467869</v>
@@ -24696,7 +24714,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24710,7 +24728,7 @@
         <v>0.155075093535447</v>
       </c>
       <c r="D465" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E465">
         <v>0.7588344229730764</v>
@@ -24746,7 +24764,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24760,7 +24778,7 @@
         <v>0.1892840681169474</v>
       </c>
       <c r="D466" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E466">
         <v>0.7588344229730764</v>
@@ -24796,7 +24814,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24810,7 +24828,7 @@
         <v>1.346682022872791</v>
       </c>
       <c r="D467" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E467">
         <v>1.156906845444727</v>
@@ -24846,7 +24864,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24860,7 +24878,7 @@
         <v>1.297477194708015</v>
       </c>
       <c r="D468" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E468">
         <v>1.156906845444727</v>
@@ -24896,7 +24914,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24910,7 +24928,7 @@
         <v>1.297810076779093</v>
       </c>
       <c r="D469" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E469">
         <v>0.761390581114191</v>
@@ -24946,7 +24964,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24960,7 +24978,7 @@
         <v>0.2044467158681593</v>
       </c>
       <c r="D470" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E470">
         <v>0.7962554570149853</v>
@@ -24996,7 +25014,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25010,7 +25028,7 @@
         <v>0.2329821788368545</v>
       </c>
       <c r="D471" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E471">
         <v>0.7962554570149853</v>
@@ -25046,7 +25064,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25060,7 +25078,7 @@
         <v>1.375532432988972</v>
       </c>
       <c r="D472" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E472">
         <v>1.038262852606697</v>
@@ -25096,7 +25114,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25110,7 +25128,7 @@
         <v>1.326689743863311</v>
       </c>
       <c r="D473" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E473">
         <v>1.038262852606697</v>
@@ -25146,7 +25164,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25160,7 +25178,7 @@
         <v>1.316058735434172</v>
       </c>
       <c r="D474" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E474">
         <v>0.7793036322537743</v>
@@ -25196,7 +25214,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25210,7 +25228,7 @@
         <v>0.221604650097877</v>
       </c>
       <c r="D475" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E475">
         <v>0.8092602482404443</v>
@@ -25246,7 +25264,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25260,7 +25278,7 @@
         <v>0.2481684189130346</v>
       </c>
       <c r="D476" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E476">
         <v>0.8092602482404443</v>
@@ -25296,7 +25314,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25310,7 +25328,7 @@
         <v>1.385558707514407</v>
       </c>
       <c r="D477" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E477">
         <v>1.0151454476213</v>
@@ -25346,7 +25364,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25360,7 +25378,7 @@
         <v>1.336841871207057</v>
       </c>
       <c r="D478" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E478">
         <v>1.0151454476213</v>
@@ -25396,7 +25414,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25410,7 +25428,7 @@
         <v>1.357255810174356</v>
       </c>
       <c r="D479" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E479">
         <v>0.8197430596424145</v>
@@ -25446,7 +25464,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25460,7 +25478,7 @@
         <v>0.2603393709455446</v>
       </c>
       <c r="D480" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E480">
         <v>0.8673754583787305</v>
@@ -25496,7 +25514,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25510,7 +25528,7 @@
         <v>0.2824519615703833</v>
       </c>
       <c r="D481" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E481">
         <v>0.8673754583787305</v>
@@ -25546,7 +25564,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25560,7 +25578,7 @@
         <v>1.408193422141772</v>
       </c>
       <c r="D482" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E482">
         <v>1.092946268617976</v>
@@ -25596,7 +25614,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25610,7 +25628,7 @@
         <v>1.359760703591251</v>
       </c>
       <c r="D483" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E483">
         <v>1.092946268617976</v>
@@ -25646,7 +25664,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25660,7 +25678,7 @@
         <v>1.400693800028334</v>
       </c>
       <c r="D484" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E484">
         <v>0.8623821899128705</v>
@@ -25696,7 +25714,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25710,7 +25728,7 @@
         <v>0.3011810671530766</v>
       </c>
       <c r="D485" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E485">
         <v>0.898730697031946</v>
@@ -25746,7 +25764,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25760,7 +25778,7 @@
         <v>0.3186003577247281</v>
       </c>
       <c r="D486" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E486">
         <v>0.898730697031946</v>
@@ -25796,7 +25814,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25810,7 +25828,7 @@
         <v>1.432059352199475</v>
       </c>
       <c r="D487" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E487">
         <v>0.9910848179499889</v>
@@ -25846,7 +25864,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25860,7 +25878,7 @@
         <v>1.383926205992774</v>
       </c>
       <c r="D488" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E488">
         <v>0.9910848179499889</v>
@@ -25896,7 +25914,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25910,7 +25928,7 @@
         <v>1.389878787820437</v>
       </c>
       <c r="D489" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E489">
         <v>0.851766074481211</v>
@@ -25946,7 +25964,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25960,7 +25978,7 @@
         <v>0.291012469467951</v>
       </c>
       <c r="D490" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E490">
         <v>0.8909239985646367</v>
@@ -25996,7 +26014,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26010,7 +26028,7 @@
         <v>0.3096002785999952</v>
       </c>
       <c r="D491" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E491">
         <v>0.8909239985646367</v>
@@ -26046,7 +26064,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26060,7 +26078,7 @@
         <v>1.426117311009389</v>
       </c>
       <c r="D492" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E492">
         <v>1.145927272692262</v>
@@ -26096,7 +26114,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26110,7 +26128,7 @@
         <v>1.377909578511599</v>
       </c>
       <c r="D493" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E493">
         <v>1.145927272692262</v>
@@ -26146,7 +26164,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26160,7 +26178,7 @@
         <v>1.390470377742177</v>
       </c>
       <c r="D494" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E494">
         <v>0.8523467845882973</v>
@@ -26196,7 +26214,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26210,7 +26228,7 @@
         <v>0.2915686999920695</v>
       </c>
       <c r="D495" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E495">
         <v>0.8913510312897541</v>
@@ -26246,7 +26264,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26260,7 +26278,7 @@
         <v>0.3100925902130296</v>
       </c>
       <c r="D496" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E496">
         <v>0.8913510312897541</v>
@@ -26296,7 +26314,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26310,7 +26328,7 @@
         <v>1.426442345472138</v>
       </c>
       <c r="D497" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E497">
         <v>1.04260947236648</v>
@@ -26346,7 +26364,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26360,7 +26378,7 @@
         <v>1.4090266167915</v>
       </c>
       <c r="D498" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E498">
         <v>0.8705617594711974</v>
@@ -26396,7 +26414,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26410,7 +26428,7 @@
         <v>0.3090158305005142</v>
       </c>
       <c r="D499" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E499">
         <v>0.9047456498219102</v>
@@ -26446,7 +26464,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26460,7 +26478,7 @@
         <v>0.3255347937437314</v>
       </c>
       <c r="D500" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E500">
         <v>0.9047456498219102</v>
@@ -26496,7 +26514,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26510,7 +26528,7 @@
         <v>1.436637612444065</v>
       </c>
       <c r="D501" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E501">
         <v>1.0174159700749</v>
@@ -26546,7 +26564,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26560,7 +26578,7 @@
         <v>1.481023111428944</v>
       </c>
       <c r="D502" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E502">
         <v>0.9412341806440443</v>
@@ -26596,7 +26614,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26610,7 +26628,7 @@
         <v>0.3767090863780185</v>
       </c>
       <c r="D503" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E503">
         <v>0.9692419169592172</v>
@@ -26646,7 +26664,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26660,7 +26678,7 @@
         <v>0.3854491180167301</v>
       </c>
       <c r="D504" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E504">
         <v>0.9692419169592172</v>
@@ -26696,7 +26714,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26710,7 +26728,7 @@
         <v>1.476194307198891</v>
       </c>
       <c r="D505" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E505">
         <v>1.037981948597929</v>
@@ -26746,7 +26764,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26760,7 +26778,7 @@
         <v>1.566896676462016</v>
       </c>
       <c r="D506" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E506">
         <v>1.019149230451688</v>
@@ -26796,7 +26814,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26810,7 +26828,7 @@
         <v>0.4887054182244546</v>
       </c>
       <c r="D507" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E507">
         <v>1.141981249108951</v>
@@ -26846,7 +26864,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26860,7 +26878,7 @@
         <v>0.4845754557390034</v>
       </c>
       <c r="D508" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E508">
         <v>1.141981249108951</v>
@@ -26896,7 +26914,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26910,7 +26928,7 @@
         <v>1.575427906313638</v>
       </c>
       <c r="D509" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E509">
         <v>0.9905476528404038</v>
@@ -26946,7 +26964,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26960,7 +26978,7 @@
         <v>1.651922146792429</v>
       </c>
       <c r="D510" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E510">
         <v>1.103977882563743</v>
@@ -26996,7 +27014,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27010,7 +27028,7 @@
         <v>0.5692040695326464</v>
       </c>
       <c r="D511" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E511">
         <v>1.20122353283454</v>
@@ -27046,7 +27064,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27060,7 +27078,7 @@
         <v>0.5558236507843963</v>
       </c>
       <c r="D512" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E512">
         <v>1.20122353283454</v>
@@ -27096,7 +27114,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27110,7 +27128,7 @@
         <v>1.619515187225704</v>
       </c>
       <c r="D513" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E513">
         <v>1.044672662888699</v>
@@ -27146,7 +27164,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27160,7 +27178,7 @@
         <v>1.713538754440068</v>
       </c>
       <c r="D514" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E514">
         <v>1.21890599807297</v>
@@ -27196,7 +27214,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27210,7 +27228,7 @@
         <v>0.6782657847142568</v>
       </c>
       <c r="D515" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E515">
         <v>1.281486555498756</v>
@@ -27246,7 +27264,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27260,7 +27278,7 @@
         <v>0.6523526016297332</v>
       </c>
       <c r="D516" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E516">
         <v>1.281486555498756</v>
@@ -27296,7 +27314,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27310,7 +27328,7 @@
         <v>1.849941600908833</v>
       </c>
       <c r="D517" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E517">
         <v>1.239941600908833</v>
@@ -27346,7 +27364,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27360,7 +27378,7 @@
         <v>0.8068113243587849</v>
       </c>
       <c r="D518" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E518">
         <v>1.376088529662578</v>
@@ -27396,7 +27414,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27410,7 +27428,7 @@
         <v>0.7661264044446945</v>
       </c>
       <c r="D519" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E519">
         <v>1.376088529662578</v>
@@ -27446,7 +27464,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27460,7 +27478,7 @@
         <v>2.41237924775196</v>
       </c>
       <c r="D520" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E520">
         <v>1.720876564407629</v>
@@ -27496,7 +27514,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27510,7 +27528,7 @@
         <v>1.615923807921956</v>
       </c>
       <c r="D521" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E521">
         <v>1.035548815721295</v>
@@ -27546,7 +27564,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27560,7 +27578,7 @@
         <v>-0.6818907905012779</v>
       </c>
       <c r="D522" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E522">
         <v>-0.357148693820263</v>
@@ -27596,7 +27614,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27610,7 +27628,7 @@
         <v>-1.152815314629065</v>
       </c>
       <c r="D523" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E523">
         <v>-0.79399315370196</v>
@@ -27646,7 +27664,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27660,7 +27678,7 @@
         <v>-1.228488383499212</v>
       </c>
       <c r="D524" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E524">
         <v>-0.8641898820617673</v>
@@ -27696,7 +27714,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27710,7 +27728,7 @@
         <v>-1.29306060430628</v>
       </c>
       <c r="D525" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E525">
         <v>-0.9240891132051665</v>
@@ -27746,7 +27764,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27760,7 +27778,7 @@
         <v>-1.362823987486787</v>
       </c>
       <c r="D526" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E526">
         <v>-0.988803830497611</v>
@@ -27796,7 +27814,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27810,7 +27828,7 @@
         <v>-1.446771238461646</v>
       </c>
       <c r="D527" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E527">
         <v>-1.06667595146771</v>
@@ -27846,7 +27864,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27860,7 +27878,7 @@
         <v>-1.55778001938641</v>
       </c>
       <c r="D528" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E528">
         <v>-1.169651202193972</v>
@@ -27896,7 +27914,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27910,7 +27928,7 @@
         <v>-1.675411230839367</v>
       </c>
       <c r="D529" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E529">
         <v>-1.278769628607569</v>
@@ -27946,7 +27964,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27960,7 +27978,7 @@
         <v>-1.976515141630071</v>
       </c>
       <c r="D530" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E530">
         <v>-1.558083124801579</v>
@@ -27996,7 +28014,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28010,7 +28028,7 @@
         <v>-2.248289351143409</v>
       </c>
       <c r="D531" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E531">
         <v>-1.810189463889609</v>
@@ -28046,7 +28064,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28060,7 +28078,7 @@
         <v>-2.353293759761697</v>
       </c>
       <c r="D532" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E532">
         <v>-1.907594869252626</v>
@@ -28096,7 +28114,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28110,7 +28128,7 @@
         <v>-2.526299327422145</v>
       </c>
       <c r="D533" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E533">
         <v>-2.068080297148173</v>
@@ -28146,7 +28164,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28160,7 +28178,7 @@
         <v>-2.743107768168906</v>
       </c>
       <c r="D534" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E534">
         <v>-2.269198653367208</v>
@@ -28196,7 +28214,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28210,7 +28228,7 @@
         <v>-2.900537245558254</v>
       </c>
       <c r="D535" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E535">
         <v>-2.415235208050748</v>
@@ -28246,7 +28264,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28260,7 +28278,7 @@
         <v>-3.035837006849226</v>
       </c>
       <c r="D536" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E536">
         <v>-2.540743539248294</v>
@@ -28296,7 +28314,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28310,7 +28328,7 @@
         <v>-3.067435364143786</v>
       </c>
       <c r="D537" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E537">
         <v>-2.57005517331759</v>
@@ -28346,7 +28364,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28360,7 +28378,7 @@
         <v>-3.089535962632947</v>
       </c>
       <c r="D538" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E538">
         <v>-2.590556386389772</v>
@@ -28396,7 +28414,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28410,7 +28428,7 @@
         <v>-3.034510811938273</v>
       </c>
       <c r="D539" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E539">
         <v>-2.539513318969055</v>
@@ -28446,7 +28464,207 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>375</v>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="540" spans="1:16">
+      <c r="A540" s="1">
+        <v>0</v>
+      </c>
+      <c r="B540" t="s">
+        <v>69</v>
+      </c>
+      <c r="C540">
+        <v>-2.988299063792063</v>
+      </c>
+      <c r="D540" t="s">
+        <v>160</v>
+      </c>
+      <c r="E540">
+        <v>-2.496645842070268</v>
+      </c>
+      <c r="F540">
+        <v>1</v>
+      </c>
+      <c r="G540">
+        <v>0.01142829906379206</v>
+      </c>
+      <c r="H540">
+        <v>0.01087664584207027</v>
+      </c>
+      <c r="I540">
+        <v>0.491653221721795</v>
+      </c>
+      <c r="J540">
+        <v>2.371151007826336</v>
+      </c>
+      <c r="K540">
+        <v>3.04</v>
+      </c>
+      <c r="L540">
+        <v>4.22</v>
+      </c>
+      <c r="M540">
+        <v>2.82</v>
+      </c>
+      <c r="N540">
+        <v>4.19</v>
+      </c>
+      <c r="O540">
+        <v>1</v>
+      </c>
+      <c r="P540" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="541" spans="1:16">
+      <c r="A541" s="1">
+        <v>0</v>
+      </c>
+      <c r="B541" t="s">
+        <v>69</v>
+      </c>
+      <c r="C541">
+        <v>-2.940809558076165</v>
+      </c>
+      <c r="D541" t="s">
+        <v>160</v>
+      </c>
+      <c r="E541">
+        <v>-2.452593076899599</v>
+      </c>
+      <c r="F541">
+        <v>1</v>
+      </c>
+      <c r="G541">
+        <v>0.01138080955807616</v>
+      </c>
+      <c r="H541">
+        <v>0.0108325930768996</v>
+      </c>
+      <c r="I541">
+        <v>0.4882164811765657</v>
+      </c>
+      <c r="J541">
+        <v>2.355529459893475</v>
+      </c>
+      <c r="K541">
+        <v>3.04</v>
+      </c>
+      <c r="L541">
+        <v>4.22</v>
+      </c>
+      <c r="M541">
+        <v>2.82</v>
+      </c>
+      <c r="N541">
+        <v>4.19</v>
+      </c>
+      <c r="O541">
+        <v>1</v>
+      </c>
+      <c r="P541" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="542" spans="1:16">
+      <c r="A542" s="1">
+        <v>0</v>
+      </c>
+      <c r="B542" t="s">
+        <v>70</v>
+      </c>
+      <c r="C542">
+        <v>-1.484070927407007</v>
+      </c>
+      <c r="D542" t="s">
+        <v>161</v>
+      </c>
+      <c r="E542">
+        <v>-1.738165050312543</v>
+      </c>
+      <c r="F542">
+        <v>-1</v>
+      </c>
+      <c r="G542">
+        <v>0.009364070927407006</v>
+      </c>
+      <c r="H542">
+        <v>0.009278165050312544</v>
+      </c>
+      <c r="I542">
+        <v>0.2540941229055358</v>
+      </c>
+      <c r="J542">
+        <v>2.102353072638375</v>
+      </c>
+      <c r="K542">
+        <v>2.58</v>
+      </c>
+      <c r="L542">
+        <v>3.94</v>
+      </c>
+      <c r="M542">
+        <v>2.62</v>
+      </c>
+      <c r="N542">
+        <v>3.77</v>
+      </c>
+      <c r="O542">
+        <v>1</v>
+      </c>
+      <c r="P542" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="543" spans="1:16">
+      <c r="A543" s="1">
+        <v>0</v>
+      </c>
+      <c r="B543" t="s">
+        <v>70</v>
+      </c>
+      <c r="C543">
+        <v>-1.073545579884814</v>
+      </c>
+      <c r="D543" t="s">
+        <v>161</v>
+      </c>
+      <c r="E543">
+        <v>-1.321274968720238</v>
+      </c>
+      <c r="F543">
+        <v>-1</v>
+      </c>
+      <c r="G543">
+        <v>0.008953545579884814</v>
+      </c>
+      <c r="H543">
+        <v>0.008861274968720238</v>
+      </c>
+      <c r="I543">
+        <v>0.2477293888354239</v>
+      </c>
+      <c r="J543">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K543">
+        <v>2.58</v>
+      </c>
+      <c r="L543">
+        <v>3.94</v>
+      </c>
+      <c r="M543">
+        <v>2.62</v>
+      </c>
+      <c r="N543">
+        <v>3.77</v>
+      </c>
+      <c r="O543">
+        <v>1</v>
+      </c>
+      <c r="P543" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="383">
   <si>
     <t>trade_time</t>
   </si>
@@ -499,7 +499,7 @@
     <t>2021-07-05</t>
   </si>
   <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -1154,6 +1154,9 @@
   </si>
   <si>
     <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-05-18</t>
   </si>
   <si>
     <t>2021-06-02</t>
@@ -1517,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P543"/>
+  <dimension ref="A1:P544"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28572,43 +28575,43 @@
         <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C542">
-        <v>-1.484070927407007</v>
+        <v>-2.921222246718158</v>
       </c>
       <c r="D542" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E542">
-        <v>-1.738165050312543</v>
+        <v>-2.434423268337238</v>
       </c>
       <c r="F542">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G542">
-        <v>0.009364070927407006</v>
+        <v>0.01136122224671816</v>
       </c>
       <c r="H542">
-        <v>0.009278165050312544</v>
+        <v>0.01081442326833724</v>
       </c>
       <c r="I542">
-        <v>0.2540941229055358</v>
+        <v>0.4867989783809206</v>
       </c>
       <c r="J542">
-        <v>2.102353072638375</v>
+        <v>2.349086265367815</v>
       </c>
       <c r="K542">
-        <v>2.58</v>
+        <v>3.04</v>
       </c>
       <c r="L542">
-        <v>3.94</v>
+        <v>4.22</v>
       </c>
       <c r="M542">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="N542">
-        <v>3.77</v>
+        <v>4.19</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28625,28 +28628,28 @@
         <v>70</v>
       </c>
       <c r="C543">
-        <v>-1.073545579884814</v>
+        <v>-1.484070927407007</v>
       </c>
       <c r="D543" t="s">
         <v>161</v>
       </c>
       <c r="E543">
-        <v>-1.321274968720238</v>
+        <v>-1.72021211176531</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.008953545579884814</v>
+        <v>0.009364070927407006</v>
       </c>
       <c r="H543">
-        <v>0.008861274968720238</v>
+        <v>0.009380212111765311</v>
       </c>
       <c r="I543">
-        <v>0.2477293888354239</v>
+        <v>0.2361411843583032</v>
       </c>
       <c r="J543">
-        <v>1.943234720885587</v>
+        <v>2.102353072638375</v>
       </c>
       <c r="K543">
         <v>2.58</v>
@@ -28655,16 +28658,66 @@
         <v>3.94</v>
       </c>
       <c r="M543">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="N543">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
         <v>381</v>
+      </c>
+    </row>
+    <row r="544" spans="1:16">
+      <c r="A544" s="1">
+        <v>0</v>
+      </c>
+      <c r="B544" t="s">
+        <v>70</v>
+      </c>
+      <c r="C544">
+        <v>-1.073545579884814</v>
+      </c>
+      <c r="D544" t="s">
+        <v>161</v>
+      </c>
+      <c r="E544">
+        <v>-1.300139663137949</v>
+      </c>
+      <c r="F544">
+        <v>-1</v>
+      </c>
+      <c r="G544">
+        <v>0.008953545579884814</v>
+      </c>
+      <c r="H544">
+        <v>0.008960139663137948</v>
+      </c>
+      <c r="I544">
+        <v>0.226594083253135</v>
+      </c>
+      <c r="J544">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K544">
+        <v>2.58</v>
+      </c>
+      <c r="L544">
+        <v>3.94</v>
+      </c>
+      <c r="M544">
+        <v>2.64</v>
+      </c>
+      <c r="N544">
+        <v>3.83</v>
+      </c>
+      <c r="O544">
+        <v>1</v>
+      </c>
+      <c r="P544" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -499,7 +499,7 @@
     <t>2021-07-05</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-08-03</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -28634,7 +28634,7 @@
         <v>161</v>
       </c>
       <c r="E543">
-        <v>-1.72021211176531</v>
+        <v>-1.906588603387449</v>
       </c>
       <c r="F543">
         <v>-1</v>
@@ -28643,10 +28643,10 @@
         <v>0.009364070927407006</v>
       </c>
       <c r="H543">
-        <v>0.009380212111765311</v>
+        <v>0.009866588603387448</v>
       </c>
       <c r="I543">
-        <v>0.2361411843583032</v>
+        <v>0.4225176759804423</v>
       </c>
       <c r="J543">
         <v>2.102353072638375</v>
@@ -28658,10 +28658,10 @@
         <v>3.94</v>
       </c>
       <c r="M543">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="N543">
-        <v>3.83</v>
+        <v>3.98</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28684,7 +28684,7 @@
         <v>161</v>
       </c>
       <c r="E544">
-        <v>-1.300139663137949</v>
+        <v>-1.461057218479642</v>
       </c>
       <c r="F544">
         <v>-1</v>
@@ -28693,10 +28693,10 @@
         <v>0.008953545579884814</v>
       </c>
       <c r="H544">
-        <v>0.008960139663137948</v>
+        <v>0.009421057218479642</v>
       </c>
       <c r="I544">
-        <v>0.226594083253135</v>
+        <v>0.3875116385948285</v>
       </c>
       <c r="J544">
         <v>1.943234720885587</v>
@@ -28708,10 +28708,10 @@
         <v>3.94</v>
       </c>
       <c r="M544">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="N544">
-        <v>3.83</v>
+        <v>3.98</v>
       </c>
       <c r="O544">
         <v>1</v>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="380">
   <si>
     <t>trade_time</t>
   </si>
@@ -1096,9 +1096,6 @@
     <t>2020-11-23</t>
   </si>
   <si>
-    <t>2021-04-08</t>
-  </si>
-  <si>
     <t>2021-04-16</t>
   </si>
   <si>
@@ -1151,12 +1148,6 @@
   </si>
   <si>
     <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-05-18</t>
   </si>
   <si>
     <t>2021-06-02</t>
@@ -1520,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P544"/>
+  <dimension ref="A1:P541"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -27578,28 +27569,28 @@
         <v>69</v>
       </c>
       <c r="C522">
-        <v>-0.6818907905012779</v>
+        <v>-1.152815314629065</v>
       </c>
       <c r="D522" t="s">
         <v>160</v>
       </c>
       <c r="E522">
-        <v>-0.357148693820263</v>
+        <v>-0.79399315370196</v>
       </c>
       <c r="F522">
         <v>1</v>
       </c>
       <c r="G522">
-        <v>0.009121890790501278</v>
+        <v>0.009592815314629063</v>
       </c>
       <c r="H522">
-        <v>0.008737148693820264</v>
+        <v>0.009173993153701961</v>
       </c>
       <c r="I522">
-        <v>0.3247420966810148</v>
+        <v>0.3588221609271045</v>
       </c>
       <c r="J522">
-        <v>1.612464075822789</v>
+        <v>1.767373458759561</v>
       </c>
       <c r="K522">
         <v>3.04</v>
@@ -27628,28 +27619,28 @@
         <v>69</v>
       </c>
       <c r="C523">
-        <v>-1.152815314629065</v>
+        <v>-1.228488383499212</v>
       </c>
       <c r="D523" t="s">
         <v>160</v>
       </c>
       <c r="E523">
-        <v>-0.79399315370196</v>
+        <v>-0.8641898820617673</v>
       </c>
       <c r="F523">
         <v>1</v>
       </c>
       <c r="G523">
-        <v>0.009592815314629063</v>
+        <v>0.009668488383499211</v>
       </c>
       <c r="H523">
-        <v>0.009173993153701961</v>
+        <v>0.009244189882061769</v>
       </c>
       <c r="I523">
-        <v>0.3588221609271045</v>
+        <v>0.3642985014374442</v>
       </c>
       <c r="J523">
-        <v>1.767373458759561</v>
+        <v>1.79226591562474</v>
       </c>
       <c r="K523">
         <v>3.04</v>
@@ -27678,28 +27669,28 @@
         <v>69</v>
       </c>
       <c r="C524">
-        <v>-1.228488383499212</v>
+        <v>-1.29306060430628</v>
       </c>
       <c r="D524" t="s">
         <v>160</v>
       </c>
       <c r="E524">
-        <v>-0.8641898820617673</v>
+        <v>-0.9240891132051665</v>
       </c>
       <c r="F524">
         <v>1</v>
       </c>
       <c r="G524">
-        <v>0.009668488383499211</v>
+        <v>0.00973306060430628</v>
       </c>
       <c r="H524">
-        <v>0.009244189882061769</v>
+        <v>0.009304089113205167</v>
       </c>
       <c r="I524">
-        <v>0.3642985014374442</v>
+        <v>0.3689714911011137</v>
       </c>
       <c r="J524">
-        <v>1.79226591562474</v>
+        <v>1.813506777732329</v>
       </c>
       <c r="K524">
         <v>3.04</v>
@@ -27728,28 +27719,28 @@
         <v>69</v>
       </c>
       <c r="C525">
-        <v>-1.29306060430628</v>
+        <v>-1.362823987486787</v>
       </c>
       <c r="D525" t="s">
         <v>160</v>
       </c>
       <c r="E525">
-        <v>-0.9240891132051665</v>
+        <v>-0.988803830497611</v>
       </c>
       <c r="F525">
         <v>1</v>
       </c>
       <c r="G525">
-        <v>0.00973306060430628</v>
+        <v>0.009802823987486785</v>
       </c>
       <c r="H525">
-        <v>0.009304089113205167</v>
+        <v>0.009368803830497612</v>
       </c>
       <c r="I525">
-        <v>0.3689714911011137</v>
+        <v>0.3740201569891761</v>
       </c>
       <c r="J525">
-        <v>1.813506777732329</v>
+        <v>1.836455259041706</v>
       </c>
       <c r="K525">
         <v>3.04</v>
@@ -27778,28 +27769,28 @@
         <v>69</v>
       </c>
       <c r="C526">
-        <v>-1.362823987486787</v>
+        <v>-1.446771238461646</v>
       </c>
       <c r="D526" t="s">
         <v>160</v>
       </c>
       <c r="E526">
-        <v>-0.988803830497611</v>
+        <v>-1.06667595146771</v>
       </c>
       <c r="F526">
         <v>1</v>
       </c>
       <c r="G526">
-        <v>0.009802823987486785</v>
+        <v>0.009886771238461645</v>
       </c>
       <c r="H526">
-        <v>0.009368803830497612</v>
+        <v>0.009446675951467712</v>
       </c>
       <c r="I526">
-        <v>0.3740201569891761</v>
+        <v>0.380095286993936</v>
       </c>
       <c r="J526">
-        <v>1.836455259041706</v>
+        <v>1.864069486336068</v>
       </c>
       <c r="K526">
         <v>3.04</v>
@@ -27828,28 +27819,28 @@
         <v>69</v>
       </c>
       <c r="C527">
-        <v>-1.446771238461646</v>
+        <v>-1.55778001938641</v>
       </c>
       <c r="D527" t="s">
         <v>160</v>
       </c>
       <c r="E527">
-        <v>-1.06667595146771</v>
+        <v>-1.169651202193972</v>
       </c>
       <c r="F527">
         <v>1</v>
       </c>
       <c r="G527">
-        <v>0.009886771238461645</v>
+        <v>0.00999778001938641</v>
       </c>
       <c r="H527">
-        <v>0.009446675951467712</v>
+        <v>0.009549651202193973</v>
       </c>
       <c r="I527">
-        <v>0.380095286993936</v>
+        <v>0.3881288171924382</v>
       </c>
       <c r="J527">
-        <v>1.864069486336068</v>
+        <v>1.900585532692898</v>
       </c>
       <c r="K527">
         <v>3.04</v>
@@ -27878,28 +27869,28 @@
         <v>69</v>
       </c>
       <c r="C528">
-        <v>-1.55778001938641</v>
+        <v>-1.675411230839367</v>
       </c>
       <c r="D528" t="s">
         <v>160</v>
       </c>
       <c r="E528">
-        <v>-1.169651202193972</v>
+        <v>-1.278769628607569</v>
       </c>
       <c r="F528">
         <v>1</v>
       </c>
       <c r="G528">
-        <v>0.00999778001938641</v>
+        <v>0.01011541123083937</v>
       </c>
       <c r="H528">
-        <v>0.009549651202193973</v>
+        <v>0.00965876962860757</v>
       </c>
       <c r="I528">
-        <v>0.3881288171924382</v>
+        <v>0.3966416022317976</v>
       </c>
       <c r="J528">
-        <v>1.900585532692898</v>
+        <v>1.939280010144528</v>
       </c>
       <c r="K528">
         <v>3.04</v>
@@ -27928,28 +27919,28 @@
         <v>69</v>
       </c>
       <c r="C529">
-        <v>-1.675411230839367</v>
+        <v>-1.976515141630071</v>
       </c>
       <c r="D529" t="s">
         <v>160</v>
       </c>
       <c r="E529">
-        <v>-1.278769628607569</v>
+        <v>-1.558083124801579</v>
       </c>
       <c r="F529">
         <v>1</v>
       </c>
       <c r="G529">
-        <v>0.01011541123083937</v>
+        <v>0.01041651514163007</v>
       </c>
       <c r="H529">
-        <v>0.00965876962860757</v>
+        <v>0.009938083124801579</v>
       </c>
       <c r="I529">
-        <v>0.3966416022317976</v>
+        <v>0.4184320168284925</v>
       </c>
       <c r="J529">
-        <v>1.939280010144528</v>
+        <v>2.038327349220418</v>
       </c>
       <c r="K529">
         <v>3.04</v>
@@ -27978,28 +27969,28 @@
         <v>69</v>
       </c>
       <c r="C530">
-        <v>-1.976515141630071</v>
+        <v>-2.248289351143409</v>
       </c>
       <c r="D530" t="s">
         <v>160</v>
       </c>
       <c r="E530">
-        <v>-1.558083124801579</v>
+        <v>-1.810189463889609</v>
       </c>
       <c r="F530">
         <v>1</v>
       </c>
       <c r="G530">
-        <v>0.01041651514163007</v>
+        <v>0.01068828935114341</v>
       </c>
       <c r="H530">
-        <v>0.009938083124801579</v>
+        <v>0.01019018946388961</v>
       </c>
       <c r="I530">
-        <v>0.4184320168284925</v>
+        <v>0.4380998872538004</v>
       </c>
       <c r="J530">
-        <v>2.038327349220418</v>
+        <v>2.127726760244542</v>
       </c>
       <c r="K530">
         <v>3.04</v>
@@ -28028,28 +28019,28 @@
         <v>69</v>
       </c>
       <c r="C531">
-        <v>-2.248289351143409</v>
+        <v>-2.353293759761697</v>
       </c>
       <c r="D531" t="s">
         <v>160</v>
       </c>
       <c r="E531">
-        <v>-1.810189463889609</v>
+        <v>-1.907594869252626</v>
       </c>
       <c r="F531">
         <v>1</v>
       </c>
       <c r="G531">
-        <v>0.01068828935114341</v>
+        <v>0.0107932937597617</v>
       </c>
       <c r="H531">
-        <v>0.01019018946388961</v>
+        <v>0.01028759486925263</v>
       </c>
       <c r="I531">
-        <v>0.4380998872538004</v>
+        <v>0.4456988905090711</v>
       </c>
       <c r="J531">
-        <v>2.127726760244542</v>
+        <v>2.162267684132137</v>
       </c>
       <c r="K531">
         <v>3.04</v>
@@ -28078,28 +28069,28 @@
         <v>69</v>
       </c>
       <c r="C532">
-        <v>-2.353293759761697</v>
+        <v>-2.526299327422145</v>
       </c>
       <c r="D532" t="s">
         <v>160</v>
       </c>
       <c r="E532">
-        <v>-1.907594869252626</v>
+        <v>-2.068080297148173</v>
       </c>
       <c r="F532">
         <v>1</v>
       </c>
       <c r="G532">
-        <v>0.0107932937597617</v>
+        <v>0.01096629932742215</v>
       </c>
       <c r="H532">
-        <v>0.01028759486925263</v>
+        <v>0.01044808029714817</v>
       </c>
       <c r="I532">
-        <v>0.4456988905090711</v>
+        <v>0.4582190302739724</v>
       </c>
       <c r="J532">
-        <v>2.162267684132137</v>
+        <v>2.219177410336232</v>
       </c>
       <c r="K532">
         <v>3.04</v>
@@ -28128,28 +28119,28 @@
         <v>69</v>
       </c>
       <c r="C533">
-        <v>-2.526299327422145</v>
+        <v>-2.743107768168906</v>
       </c>
       <c r="D533" t="s">
         <v>160</v>
       </c>
       <c r="E533">
-        <v>-2.068080297148173</v>
+        <v>-2.269198653367208</v>
       </c>
       <c r="F533">
         <v>1</v>
       </c>
       <c r="G533">
-        <v>0.01096629932742215</v>
+        <v>0.01118310776816891</v>
       </c>
       <c r="H533">
-        <v>0.01044808029714817</v>
+        <v>0.01064919865336721</v>
       </c>
       <c r="I533">
-        <v>0.4582190302739724</v>
+        <v>0.4739091148016978</v>
       </c>
       <c r="J533">
-        <v>2.219177410336232</v>
+        <v>2.29049597637135</v>
       </c>
       <c r="K533">
         <v>3.04</v>
@@ -28178,28 +28169,28 @@
         <v>69</v>
       </c>
       <c r="C534">
-        <v>-2.743107768168906</v>
+        <v>-2.900537245558254</v>
       </c>
       <c r="D534" t="s">
         <v>160</v>
       </c>
       <c r="E534">
-        <v>-2.269198653367208</v>
+        <v>-2.415235208050748</v>
       </c>
       <c r="F534">
         <v>1</v>
       </c>
       <c r="G534">
-        <v>0.01118310776816891</v>
+        <v>0.01134053724555825</v>
       </c>
       <c r="H534">
-        <v>0.01064919865336721</v>
+        <v>0.01079523520805075</v>
       </c>
       <c r="I534">
-        <v>0.4739091148016978</v>
+        <v>0.4853020375075054</v>
       </c>
       <c r="J534">
-        <v>2.29049597637135</v>
+        <v>2.342281988670478</v>
       </c>
       <c r="K534">
         <v>3.04</v>
@@ -28228,28 +28219,28 @@
         <v>69</v>
       </c>
       <c r="C535">
-        <v>-2.900537245558254</v>
+        <v>-3.035837006849226</v>
       </c>
       <c r="D535" t="s">
         <v>160</v>
       </c>
       <c r="E535">
-        <v>-2.415235208050748</v>
+        <v>-2.540743539248294</v>
       </c>
       <c r="F535">
         <v>1</v>
       </c>
       <c r="G535">
-        <v>0.01134053724555825</v>
+        <v>0.01147583700684923</v>
       </c>
       <c r="H535">
-        <v>0.01079523520805075</v>
+        <v>0.0109207435392483</v>
       </c>
       <c r="I535">
-        <v>0.4853020375075054</v>
+        <v>0.495093467600932</v>
       </c>
       <c r="J535">
-        <v>2.342281988670478</v>
+        <v>2.38678848909514</v>
       </c>
       <c r="K535">
         <v>3.04</v>
@@ -28278,28 +28269,28 @@
         <v>69</v>
       </c>
       <c r="C536">
-        <v>-3.035837006849226</v>
+        <v>-3.067435364143786</v>
       </c>
       <c r="D536" t="s">
         <v>160</v>
       </c>
       <c r="E536">
-        <v>-2.540743539248294</v>
+        <v>-2.57005517331759</v>
       </c>
       <c r="F536">
         <v>1</v>
       </c>
       <c r="G536">
-        <v>0.01147583700684923</v>
+        <v>0.01150743536414378</v>
       </c>
       <c r="H536">
-        <v>0.0109207435392483</v>
+        <v>0.01095005517331759</v>
       </c>
       <c r="I536">
-        <v>0.495093467600932</v>
+        <v>0.4973801908261954</v>
       </c>
       <c r="J536">
-        <v>2.38678848909514</v>
+        <v>2.397182685573614</v>
       </c>
       <c r="K536">
         <v>3.04</v>
@@ -28328,28 +28319,28 @@
         <v>69</v>
       </c>
       <c r="C537">
-        <v>-3.067435364143786</v>
+        <v>-3.089535962632947</v>
       </c>
       <c r="D537" t="s">
         <v>160</v>
       </c>
       <c r="E537">
-        <v>-2.57005517331759</v>
+        <v>-2.590556386389772</v>
       </c>
       <c r="F537">
         <v>1</v>
       </c>
       <c r="G537">
-        <v>0.01150743536414378</v>
+        <v>0.01152953596263295</v>
       </c>
       <c r="H537">
-        <v>0.01095005517331759</v>
+        <v>0.01097055638638977</v>
       </c>
       <c r="I537">
-        <v>0.4973801908261954</v>
+        <v>0.4989795762431752</v>
       </c>
       <c r="J537">
-        <v>2.397182685573614</v>
+        <v>2.404452619287154</v>
       </c>
       <c r="K537">
         <v>3.04</v>
@@ -28378,28 +28369,28 @@
         <v>69</v>
       </c>
       <c r="C538">
-        <v>-3.089535962632947</v>
+        <v>-3.034510811938273</v>
       </c>
       <c r="D538" t="s">
         <v>160</v>
       </c>
       <c r="E538">
-        <v>-2.590556386389772</v>
+        <v>-2.539513318969055</v>
       </c>
       <c r="F538">
         <v>1</v>
       </c>
       <c r="G538">
-        <v>0.01152953596263295</v>
+        <v>0.01147451081193827</v>
       </c>
       <c r="H538">
-        <v>0.01097055638638977</v>
+        <v>0.01091951331896906</v>
       </c>
       <c r="I538">
-        <v>0.4989795762431752</v>
+        <v>0.494997492969218</v>
       </c>
       <c r="J538">
-        <v>2.404452619287154</v>
+        <v>2.386352240769169</v>
       </c>
       <c r="K538">
         <v>3.04</v>
@@ -28428,28 +28419,28 @@
         <v>69</v>
       </c>
       <c r="C539">
-        <v>-3.034510811938273</v>
+        <v>-2.988299063792063</v>
       </c>
       <c r="D539" t="s">
         <v>160</v>
       </c>
       <c r="E539">
-        <v>-2.539513318969055</v>
+        <v>-2.496645842070268</v>
       </c>
       <c r="F539">
         <v>1</v>
       </c>
       <c r="G539">
-        <v>0.01147451081193827</v>
+        <v>0.01142829906379206</v>
       </c>
       <c r="H539">
-        <v>0.01091951331896906</v>
+        <v>0.01087664584207027</v>
       </c>
       <c r="I539">
-        <v>0.494997492969218</v>
+        <v>0.491653221721795</v>
       </c>
       <c r="J539">
-        <v>2.386352240769169</v>
+        <v>2.371151007826336</v>
       </c>
       <c r="K539">
         <v>3.04</v>
@@ -28475,43 +28466,43 @@
         <v>0</v>
       </c>
       <c r="B540" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C540">
-        <v>-2.988299063792063</v>
+        <v>-1.484070927407007</v>
       </c>
       <c r="D540" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E540">
-        <v>-2.496645842070268</v>
+        <v>-1.906588603387449</v>
       </c>
       <c r="F540">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.01142829906379206</v>
+        <v>0.009364070927407006</v>
       </c>
       <c r="H540">
-        <v>0.01087664584207027</v>
+        <v>0.009866588603387448</v>
       </c>
       <c r="I540">
-        <v>0.491653221721795</v>
+        <v>0.4225176759804423</v>
       </c>
       <c r="J540">
-        <v>2.371151007826336</v>
+        <v>2.102353072638375</v>
       </c>
       <c r="K540">
-        <v>3.04</v>
+        <v>2.58</v>
       </c>
       <c r="L540">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
       <c r="M540">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N540">
-        <v>4.19</v>
+        <v>3.98</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28525,199 +28516,49 @@
         <v>0</v>
       </c>
       <c r="B541" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C541">
-        <v>-2.940809558076165</v>
+        <v>-1.073545579884814</v>
       </c>
       <c r="D541" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E541">
-        <v>-2.452593076899599</v>
+        <v>-1.461057218479642</v>
       </c>
       <c r="F541">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.01138080955807616</v>
+        <v>0.008953545579884814</v>
       </c>
       <c r="H541">
-        <v>0.0108325930768996</v>
+        <v>0.009421057218479642</v>
       </c>
       <c r="I541">
-        <v>0.4882164811765657</v>
+        <v>0.3875116385948285</v>
       </c>
       <c r="J541">
-        <v>2.355529459893475</v>
+        <v>1.943234720885587</v>
       </c>
       <c r="K541">
-        <v>3.04</v>
+        <v>2.58</v>
       </c>
       <c r="L541">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
       <c r="M541">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N541">
-        <v>4.19</v>
+        <v>3.98</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
         <v>379</v>
-      </c>
-    </row>
-    <row r="542" spans="1:16">
-      <c r="A542" s="1">
-        <v>0</v>
-      </c>
-      <c r="B542" t="s">
-        <v>69</v>
-      </c>
-      <c r="C542">
-        <v>-2.921222246718158</v>
-      </c>
-      <c r="D542" t="s">
-        <v>160</v>
-      </c>
-      <c r="E542">
-        <v>-2.434423268337238</v>
-      </c>
-      <c r="F542">
-        <v>1</v>
-      </c>
-      <c r="G542">
-        <v>0.01136122224671816</v>
-      </c>
-      <c r="H542">
-        <v>0.01081442326833724</v>
-      </c>
-      <c r="I542">
-        <v>0.4867989783809206</v>
-      </c>
-      <c r="J542">
-        <v>2.349086265367815</v>
-      </c>
-      <c r="K542">
-        <v>3.04</v>
-      </c>
-      <c r="L542">
-        <v>4.22</v>
-      </c>
-      <c r="M542">
-        <v>2.82</v>
-      </c>
-      <c r="N542">
-        <v>4.19</v>
-      </c>
-      <c r="O542">
-        <v>1</v>
-      </c>
-      <c r="P542" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="543" spans="1:16">
-      <c r="A543" s="1">
-        <v>0</v>
-      </c>
-      <c r="B543" t="s">
-        <v>70</v>
-      </c>
-      <c r="C543">
-        <v>-1.484070927407007</v>
-      </c>
-      <c r="D543" t="s">
-        <v>161</v>
-      </c>
-      <c r="E543">
-        <v>-1.906588603387449</v>
-      </c>
-      <c r="F543">
-        <v>-1</v>
-      </c>
-      <c r="G543">
-        <v>0.009364070927407006</v>
-      </c>
-      <c r="H543">
-        <v>0.009866588603387448</v>
-      </c>
-      <c r="I543">
-        <v>0.4225176759804423</v>
-      </c>
-      <c r="J543">
-        <v>2.102353072638375</v>
-      </c>
-      <c r="K543">
-        <v>2.58</v>
-      </c>
-      <c r="L543">
-        <v>3.94</v>
-      </c>
-      <c r="M543">
-        <v>2.8</v>
-      </c>
-      <c r="N543">
-        <v>3.98</v>
-      </c>
-      <c r="O543">
-        <v>1</v>
-      </c>
-      <c r="P543" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="544" spans="1:16">
-      <c r="A544" s="1">
-        <v>0</v>
-      </c>
-      <c r="B544" t="s">
-        <v>70</v>
-      </c>
-      <c r="C544">
-        <v>-1.073545579884814</v>
-      </c>
-      <c r="D544" t="s">
-        <v>161</v>
-      </c>
-      <c r="E544">
-        <v>-1.461057218479642</v>
-      </c>
-      <c r="F544">
-        <v>-1</v>
-      </c>
-      <c r="G544">
-        <v>0.008953545579884814</v>
-      </c>
-      <c r="H544">
-        <v>0.009421057218479642</v>
-      </c>
-      <c r="I544">
-        <v>0.3875116385948285</v>
-      </c>
-      <c r="J544">
-        <v>1.943234720885587</v>
-      </c>
-      <c r="K544">
-        <v>2.58</v>
-      </c>
-      <c r="L544">
-        <v>3.94</v>
-      </c>
-      <c r="M544">
-        <v>2.8</v>
-      </c>
-      <c r="N544">
-        <v>3.98</v>
-      </c>
-      <c r="O544">
-        <v>1</v>
-      </c>
-      <c r="P544" t="s">
-        <v>382</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="360">
   <si>
     <t>trade_time</t>
   </si>
@@ -223,9 +223,6 @@
     <t>2020-11-26</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>2021-07-27</t>
   </si>
   <si>
@@ -496,9 +493,6 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
     <t>2021-08-03</t>
   </si>
   <si>
@@ -1094,60 +1088,6 @@
   </si>
   <si>
     <t>2020-11-23</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>2021-05-10</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>2021-05-12</t>
-  </si>
-  <si>
-    <t>2021-05-13</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
   </si>
   <si>
     <t>2021-06-02</t>
@@ -1511,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P541"/>
+  <dimension ref="A1:P523"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1572,7 +1512,7 @@
         <v>6.869727715272395</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2">
         <v>6.050137140894572</v>
@@ -1608,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1622,7 +1562,7 @@
         <v>6.844463593057311</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3">
         <v>6.050137140894572</v>
@@ -1658,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1672,7 +1612,7 @@
         <v>6.857637482930865</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4">
         <v>6.039233803242143</v>
@@ -1708,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1722,7 +1662,7 @@
         <v>6.83283604847594</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5">
         <v>6.039233803242143</v>
@@ -1758,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1772,7 +1712,7 @@
         <v>6.826153414303063</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6">
         <v>6.01084051672589</v>
@@ -1808,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1822,7 +1762,7 @@
         <v>6.802556861010267</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7">
         <v>6.01084051672589</v>
@@ -1858,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1872,7 +1812,7 @@
         <v>6.794839943414579</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8">
         <v>5.98260108041714</v>
@@ -1908,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1922,7 +1862,7 @@
         <v>6.77244174258507</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9">
         <v>5.98260108041714</v>
@@ -1958,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1972,7 +1912,7 @@
         <v>6.763675289556306</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10">
         <v>5.95449585181284</v>
@@ -2008,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2022,7 +1962,7 @@
         <v>6.742469746029192</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11">
         <v>5.95449585181284</v>
@@ -2058,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2072,7 +2012,7 @@
         <v>6.730117010025435</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12">
         <v>5.924231979091157</v>
@@ -2108,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2122,7 +2062,7 @@
         <v>6.710195726779869</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13">
         <v>5.924231979091157</v>
@@ -2158,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2172,7 +2112,7 @@
         <v>6.693046966006446</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14">
         <v>5.890801090807809</v>
@@ -2208,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2222,7 +2162,7 @@
         <v>6.674544336691723</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15">
         <v>5.890801090807809</v>
@@ -2258,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2272,7 +2212,7 @@
         <v>6.644553392998862</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16">
         <v>5.847068118145396</v>
@@ -2308,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2322,7 +2262,7 @@
         <v>6.627906590937341</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17">
         <v>5.847068118145396</v>
@@ -2358,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2372,7 +2312,7 @@
         <v>6.617128166636995</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18">
         <v>5.822335218497922</v>
@@ -2408,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2422,7 +2362,7 @@
         <v>6.601530915667526</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19">
         <v>5.822335218497922</v>
@@ -2458,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2472,7 +2412,7 @@
         <v>6.581803978417834</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20">
         <v>5.790478795844368</v>
@@ -2508,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2522,7 +2462,7 @@
         <v>6.567558568262076</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21">
         <v>5.790478795844368</v>
@@ -2558,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2572,7 +2512,7 @@
         <v>6.554001439910648</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22">
         <v>5.765405624678154</v>
@@ -2608,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2622,7 +2562,7 @@
         <v>6.540820020413236</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23">
         <v>5.765405624678154</v>
@@ -2658,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2672,7 +2612,7 @@
         <v>6.529894038726229</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24">
         <v>5.743664840248944</v>
@@ -2708,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2722,7 +2662,7 @@
         <v>6.517635198641864</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25">
         <v>5.743664840248944</v>
@@ -2758,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2772,7 +2712,7 @@
         <v>6.493137342079</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26">
         <v>5.710516538114505</v>
@@ -2808,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2822,7 +2762,7 @@
         <v>6.482285164262333</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>5.710516538114505</v>
@@ -2858,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2872,7 +2812,7 @@
         <v>6.444477546138163</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E28">
         <v>5.666633660577178</v>
@@ -2908,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2922,7 +2862,7 @@
         <v>6.435487556851677</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E29">
         <v>5.666633660577178</v>
@@ -2958,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2972,7 +2912,7 @@
         <v>6.395287017911711</v>
       </c>
       <c r="D30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E30">
         <v>5.62227215259259</v>
@@ -3008,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3022,7 +2962,7 @@
         <v>6.388179528041545</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31">
         <v>5.62227215259259</v>
@@ -3058,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3072,7 +3012,7 @@
         <v>6.391868530229962</v>
       </c>
       <c r="D32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E32">
         <v>5.619189256879599</v>
@@ -3108,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3122,7 +3062,7 @@
         <v>6.384891864347617</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E33">
         <v>5.619189256879599</v>
@@ -3158,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3172,7 +3112,7 @@
         <v>6.396520135507044</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E34">
         <v>5.623384215382392</v>
@@ -3208,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3222,7 +3162,7 @@
         <v>6.389365454780485</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E35">
         <v>5.623384215382392</v>
@@ -3258,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3272,7 +3212,7 @@
         <v>6.403506732043612</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E36">
         <v>5.629684939713206</v>
@@ -3308,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3322,7 +3262,7 @@
         <v>6.396084677406335</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E37">
         <v>5.629684939713206</v>
@@ -3358,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3372,7 +3312,7 @@
         <v>6.390454186369448</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E38">
         <v>5.617913758755807</v>
@@ -3408,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3422,7 +3362,7 @@
         <v>6.38353164679125</v>
       </c>
       <c r="D39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E39">
         <v>5.617913758755807</v>
@@ -3458,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3472,7 +3412,7 @@
         <v>6.385694652927858</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E40">
         <v>5.613621467365888</v>
@@ -3508,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3522,7 +3462,7 @@
         <v>6.378954258556243</v>
       </c>
       <c r="D41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41">
         <v>5.613621467365888</v>
@@ -3558,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3572,7 +3512,7 @@
         <v>6.398324700271503</v>
       </c>
       <c r="D42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E42">
         <v>5.625011626534365</v>
@@ -3608,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3622,7 +3562,7 @@
         <v>6.39110095966211</v>
       </c>
       <c r="D43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E43">
         <v>5.625011626534365</v>
@@ -3658,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3672,7 +3612,7 @@
         <v>6.406965992917668</v>
       </c>
       <c r="D44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E44">
         <v>5.63280460592575</v>
@@ -3708,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3722,7 +3662,7 @@
         <v>6.399411553920818</v>
       </c>
       <c r="D45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E45">
         <v>5.63280460592575</v>
@@ -3758,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3772,7 +3712,7 @@
         <v>6.400651203652978</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E46">
         <v>5.627109737736961</v>
@@ -3808,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3822,7 +3762,7 @@
         <v>6.393338428804362</v>
       </c>
       <c r="D47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E47">
         <v>5.627109737736961</v>
@@ -3858,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3872,7 +3812,7 @@
         <v>6.421264387742685</v>
       </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E48">
         <v>5.645699331375265</v>
@@ -3908,7 +3848,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3922,7 +3862,7 @@
         <v>6.413162755599453</v>
       </c>
       <c r="D49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E49">
         <v>5.645699331375265</v>
@@ -3958,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3972,7 +3912,7 @@
         <v>6.463467063219744</v>
       </c>
       <c r="D50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E50">
         <v>5.68375898213827</v>
@@ -4008,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4022,7 +3962,7 @@
         <v>6.45375035364561</v>
       </c>
       <c r="D51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E51">
         <v>5.68375898213827</v>
@@ -4058,7 +3998,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4072,7 +4012,7 @@
         <v>6.488418927255035</v>
       </c>
       <c r="D52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E52">
         <v>5.706261328739149</v>
@@ -4108,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4122,7 +4062,7 @@
         <v>6.477747321053927</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E53">
         <v>5.706261328739149</v>
@@ -4158,7 +4098,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4172,7 +4112,7 @@
         <v>6.583255790923473</v>
       </c>
       <c r="D54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E54">
         <v>5.791788084326992</v>
@@ -4208,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4222,7 +4162,7 @@
         <v>6.440394668218746</v>
       </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E55">
         <v>5.791788084326992</v>
@@ -4258,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4272,7 +4212,7 @@
         <v>6.568954820555353</v>
       </c>
       <c r="D56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E56">
         <v>5.791788084326992</v>
@@ -4308,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4322,7 +4262,7 @@
         <v>6.628230185262845</v>
       </c>
       <c r="D57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E57">
         <v>5.83234735509561</v>
@@ -4358,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4372,7 +4312,7 @@
         <v>6.484920066940753</v>
       </c>
       <c r="D58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E58">
         <v>5.83234735509561</v>
@@ -4408,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4422,7 +4362,7 @@
         <v>6.61220806502816</v>
       </c>
       <c r="D59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E59">
         <v>5.83234735509561</v>
@@ -4458,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4472,7 +4412,7 @@
         <v>6.646411890511949</v>
       </c>
       <c r="D60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E60">
         <v>5.84874416748332</v>
@@ -4508,7 +4448,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4522,7 +4462,7 @@
         <v>6.50292025766158</v>
       </c>
       <c r="D61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E61">
         <v>5.84874416748332</v>
@@ -4558,7 +4498,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4572,7 +4512,7 @@
         <v>6.629693964585535</v>
       </c>
       <c r="D62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E62">
         <v>5.84874416748332</v>
@@ -4608,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4622,7 +4562,7 @@
         <v>6.642559529608892</v>
       </c>
       <c r="D63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E63">
         <v>5.84526999176043</v>
@@ -4658,7 +4598,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4672,7 +4612,7 @@
         <v>6.499106356268371</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E64">
         <v>5.84526999176043</v>
@@ -4708,7 +4648,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4722,7 +4662,7 @@
         <v>6.625989031803559</v>
       </c>
       <c r="D65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E65">
         <v>5.84526999176043</v>
@@ -4758,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4772,7 +4712,7 @@
         <v>6.645390633912061</v>
       </c>
       <c r="D66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E66">
         <v>5.847823167354969</v>
@@ -4808,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4822,7 +4762,7 @@
         <v>6.501909196635068</v>
       </c>
       <c r="D67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E67">
         <v>5.847823167354969</v>
@@ -4858,7 +4798,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4872,7 +4812,7 @@
         <v>6.628711791016923</v>
       </c>
       <c r="D68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E68">
         <v>5.847823167354969</v>
@@ -4908,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4922,7 +4862,7 @@
         <v>6.628009372010197</v>
       </c>
       <c r="D69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E69">
         <v>5.832148219017515</v>
@@ -4958,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4972,7 +4912,7 @@
         <v>6.611995702199492</v>
       </c>
       <c r="D70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E70">
         <v>5.832148219017515</v>
@@ -5008,7 +4948,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5022,7 +4962,7 @@
         <v>6.616738911804213</v>
       </c>
       <c r="D71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E71">
         <v>5.821984176701968</v>
@@ -5058,7 +4998,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5072,7 +5012,7 @@
         <v>6.601156557442321</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E72">
         <v>5.821984176701968</v>
@@ -5108,7 +5048,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5122,7 +5062,7 @@
         <v>6.626158243616882</v>
       </c>
       <c r="D73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E73">
         <v>5.830478815374958</v>
@@ -5158,7 +5098,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5172,7 +5112,7 @@
         <v>6.610215415658166</v>
       </c>
       <c r="D74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E74">
         <v>5.830478815374958</v>
@@ -5208,7 +5148,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5222,7 +5162,7 @@
         <v>6.650940043106316</v>
       </c>
       <c r="D75" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E75">
         <v>5.85282779261834</v>
@@ -5258,7 +5198,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5272,7 +5212,7 @@
         <v>6.634048826814393</v>
       </c>
       <c r="D76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E76">
         <v>5.85282779261834</v>
@@ -5308,7 +5248,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5322,7 +5262,7 @@
         <v>6.655761178830648</v>
       </c>
       <c r="D77" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E77">
         <v>5.857175638812331</v>
@@ -5358,7 +5298,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5372,7 +5312,7 @@
         <v>6.638685459840457</v>
       </c>
       <c r="D78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E78">
         <v>5.857175638812331</v>
@@ -5408,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5422,7 +5362,7 @@
         <v>6.682065765134389</v>
       </c>
       <c r="D79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E79">
         <v>5.880897911319199</v>
@@ -5458,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5472,7 +5412,7 @@
         <v>6.663983381443721</v>
       </c>
       <c r="D80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E80">
         <v>5.880897911319199</v>
@@ -5508,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5522,7 +5462,7 @@
         <v>6.734829447046008</v>
       </c>
       <c r="D81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E81">
         <v>5.928481797502389</v>
@@ -5558,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5572,7 +5512,7 @@
         <v>6.714727820952732</v>
       </c>
       <c r="D82" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E82">
         <v>5.928481797502389</v>
@@ -5608,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5622,7 +5562,7 @@
         <v>6.744601630625527</v>
       </c>
       <c r="D83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E83">
         <v>5.937294648584086</v>
@@ -5658,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5672,7 +5612,7 @@
         <v>6.72412602745683</v>
       </c>
       <c r="D84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E84">
         <v>5.937294648584086</v>
@@ -5708,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5722,7 +5662,7 @@
         <v>6.868996803282632</v>
       </c>
       <c r="D85" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E85">
         <v>6.049477982328097</v>
@@ -5758,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5772,7 +5712,7 @@
         <v>6.723283024880476</v>
       </c>
       <c r="D86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E86">
         <v>6.049477982328097</v>
@@ -5808,7 +5748,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5822,7 +5762,7 @@
         <v>6.843760652741033</v>
       </c>
       <c r="D87" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E87">
         <v>6.049477982328097</v>
@@ -5858,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5872,7 +5812,7 @@
         <v>7.461980748234559</v>
       </c>
       <c r="D88" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E88">
         <v>6.584248861136657</v>
@@ -5908,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5922,7 +5862,7 @@
         <v>7.310346997004264</v>
       </c>
       <c r="D89" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E89">
         <v>6.584248861136657</v>
@@ -5958,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5972,7 +5912,7 @@
         <v>7.414051368518428</v>
       </c>
       <c r="D90" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E90">
         <v>6.584248861136657</v>
@@ -6008,7 +5948,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6022,7 +5962,7 @@
         <v>7.503790226406835</v>
       </c>
       <c r="D91" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E91">
         <v>6.621953914663068</v>
@@ -6058,7 +5998,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6072,7 +6012,7 @@
         <v>7.351739076060011</v>
       </c>
       <c r="D92" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E92">
         <v>6.621953914663068</v>
@@ -6108,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6122,7 +6062,7 @@
         <v>7.454260816744011</v>
       </c>
       <c r="D93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E93">
         <v>6.621953914663068</v>
@@ -6158,7 +6098,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6172,7 +6112,7 @@
         <v>7.442891522635139</v>
       </c>
       <c r="D94" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E94">
         <v>6.567033619414717</v>
@@ -6208,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6222,7 +6162,7 @@
         <v>7.291448346036452</v>
       </c>
       <c r="D95" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E95">
         <v>6.567033619414717</v>
@@ -6258,7 +6198,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6272,7 +6212,7 @@
         <v>7.39569267900684</v>
       </c>
       <c r="D96" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E96">
         <v>6.567033619414717</v>
@@ -6308,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6322,7 +6262,7 @@
         <v>7.440682840908001</v>
       </c>
       <c r="D97" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E97">
         <v>6.56504176334798</v>
@@ -6358,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6372,7 +6312,7 @@
         <v>7.289261714376473</v>
       </c>
       <c r="D98" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E98">
         <v>6.56504176334798</v>
@@ -6408,7 +6348,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6422,7 +6362,7 @@
         <v>7.393568522537145</v>
       </c>
       <c r="D99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E99">
         <v>6.56504176334798</v>
@@ -6458,7 +6398,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6472,7 +6412,7 @@
         <v>7.424306444365878</v>
       </c>
       <c r="D100" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E100">
         <v>6.550273033022139</v>
@@ -6508,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6522,7 +6462,7 @@
         <v>7.377818843333573</v>
       </c>
       <c r="D101" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E101">
         <v>6.550273033022139</v>
@@ -6558,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6572,7 +6512,7 @@
         <v>7.534499875331724</v>
       </c>
       <c r="D102" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E102">
         <v>6.649648806039591</v>
@@ -6608,7 +6548,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6622,7 +6562,7 @@
         <v>7.483795221200893</v>
       </c>
       <c r="D103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E103">
         <v>6.649648806039591</v>
@@ -6658,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6672,7 +6612,7 @@
         <v>7.561436426814521</v>
       </c>
       <c r="D104" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E104">
         <v>6.673941003882645</v>
@@ -6708,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6722,7 +6662,7 @@
         <v>7.509700922959722</v>
       </c>
       <c r="D105" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E105">
         <v>6.673941003882645</v>
@@ -6758,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6772,7 +6712,7 @@
         <v>7.578789061755105</v>
       </c>
       <c r="D106" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E106">
         <v>6.689590135559512</v>
@@ -6808,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6822,7 +6762,7 @@
         <v>7.526389480356823</v>
       </c>
       <c r="D107" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E107">
         <v>6.689590135559512</v>
@@ -6858,7 +6798,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6872,7 +6812,7 @@
         <v>6.876779630058808</v>
       </c>
       <c r="D108" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E108">
         <v>6.056496771201121</v>
@@ -6908,7 +6848,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6922,7 +6862,7 @@
         <v>6.85124563423293</v>
       </c>
       <c r="D109" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E109">
         <v>6.056496771201121</v>
@@ -6958,7 +6898,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6972,7 +6912,7 @@
         <v>6.803309666682317</v>
       </c>
       <c r="D110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E110">
         <v>5.990239333347446</v>
@@ -7008,7 +6948,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7022,7 +6962,7 @@
         <v>6.780587333348385</v>
       </c>
       <c r="D111" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E111">
         <v>5.990239333347446</v>
@@ -7058,7 +6998,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7072,7 +7012,7 @@
         <v>6.690125588143431</v>
       </c>
       <c r="D112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E112">
         <v>5.88816650378326</v>
@@ -7108,7 +7048,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7122,7 +7062,7 @@
         <v>6.671734758647093</v>
       </c>
       <c r="D113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E113">
         <v>5.88816650378326</v>
@@ -7158,7 +7098,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7172,7 +7112,7 @@
         <v>6.546850371675455</v>
       </c>
       <c r="D114" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E114">
         <v>5.758956574788845</v>
@@ -7208,7 +7148,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7222,7 +7162,7 @@
         <v>6.533942620346777</v>
       </c>
       <c r="D115" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E115">
         <v>5.758956574788845</v>
@@ -7258,7 +7198,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7272,7 +7212,7 @@
         <v>6.36581543133911</v>
       </c>
       <c r="D116" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E116">
         <v>5.595693783337433</v>
@@ -7308,7 +7248,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7322,7 +7262,7 @@
         <v>6.359835805846931</v>
       </c>
       <c r="D117" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E117">
         <v>5.595693783337433</v>
@@ -7358,7 +7298,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7372,7 +7312,7 @@
         <v>5.655118426801266</v>
       </c>
       <c r="D118" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E118">
         <v>4.954765702705966</v>
@@ -7408,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7422,7 +7362,7 @@
         <v>5.676336856391234</v>
       </c>
       <c r="D119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E119">
         <v>4.954765702705966</v>
@@ -7458,7 +7398,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7472,7 +7412,7 @@
         <v>4.385984132295935</v>
       </c>
       <c r="D120" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E120">
         <v>4.515964100132926</v>
@@ -7508,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7522,7 +7462,7 @@
         <v>5.520410496630564</v>
       </c>
       <c r="D121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E121">
         <v>4.833282011936382</v>
@@ -7558,7 +7498,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7572,7 +7512,7 @@
         <v>5.54678413819046</v>
       </c>
       <c r="D122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E122">
         <v>4.833282011936382</v>
@@ -7608,7 +7548,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7658,7 +7598,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7672,7 +7612,7 @@
         <v>5.300818351460203</v>
       </c>
       <c r="D124" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E124">
         <v>4.635247165543143</v>
@@ -7708,7 +7648,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7722,7 +7662,7 @@
         <v>5.335595685763722</v>
       </c>
       <c r="D125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E125">
         <v>4.635247165543143</v>
@@ -7758,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7808,7 +7748,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7858,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7872,7 +7812,7 @@
         <v>5.067644558031954</v>
       </c>
       <c r="D128" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E128">
         <v>4.254963977459765</v>
@@ -7908,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7922,7 +7862,7 @@
         <v>5.111345348656355</v>
       </c>
       <c r="D129" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E129">
         <v>4.254963977459765</v>
@@ -7958,7 +7898,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7972,7 +7912,7 @@
         <v>3.765802729769834</v>
       </c>
       <c r="D130" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E130">
         <v>3.674881815638774</v>
@@ -8008,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8022,7 +7962,7 @@
         <v>4.618291357603566</v>
       </c>
       <c r="D131" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E131">
         <v>3.650865136965114</v>
@@ -8058,7 +7998,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8072,7 +8012,7 @@
         <v>4.268167177296843</v>
       </c>
       <c r="D132" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E132">
         <v>3.514053115333852</v>
@@ -8108,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8122,7 +8062,7 @@
         <v>4.254037078744074</v>
       </c>
       <c r="D133" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E133">
         <v>3.510852837781765</v>
@@ -8158,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8172,7 +8112,7 @@
         <v>4.264789106547418</v>
       </c>
       <c r="D134" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E134">
         <v>3.510852837781765</v>
@@ -8208,7 +8148,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8222,7 +8162,7 @@
         <v>4.267776501761822</v>
       </c>
       <c r="D135" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E135">
         <v>3.523940390364364</v>
@@ -8258,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8272,7 +8212,7 @@
         <v>4.278603745384606</v>
       </c>
       <c r="D136" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E136">
         <v>3.523940390364364</v>
@@ -8308,7 +8248,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8322,7 +8262,7 @@
         <v>4.280771326539147</v>
       </c>
       <c r="D137" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E137">
         <v>3.485420289185799</v>
@@ -8358,7 +8298,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8372,7 +8312,7 @@
         <v>4.291669709713632</v>
       </c>
       <c r="D138" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E138">
         <v>3.485420289185799</v>
@@ -8408,7 +8348,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8422,7 +8362,7 @@
         <v>4.295828187834458</v>
       </c>
       <c r="D139" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E139">
         <v>3.499680345777525</v>
@@ -8458,7 +8398,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8472,7 +8412,7 @@
         <v>4.306808999081727</v>
       </c>
       <c r="D140" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E140">
         <v>3.499680345777525</v>
@@ -8508,7 +8448,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8522,7 +8462,7 @@
         <v>4.311022789612967</v>
       </c>
       <c r="D141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E141">
         <v>3.503649415261579</v>
@@ -8572,7 +8512,7 @@
         <v>4.306094254478001</v>
       </c>
       <c r="D142" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E142">
         <v>3.499007110842255</v>
@@ -8608,7 +8548,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8622,7 +8562,7 @@
         <v>4.306502251029037</v>
       </c>
       <c r="D143" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E143">
         <v>3.499391412493775</v>
@@ -8658,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8672,7 +8612,7 @@
         <v>4.318153845587818</v>
       </c>
       <c r="D144" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E144">
         <v>3.510366326424823</v>
@@ -8708,7 +8648,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8758,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8808,7 +8748,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8858,7 +8798,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8872,7 +8812,7 @@
         <v>2.959973514323903</v>
       </c>
       <c r="D148" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E148">
         <v>2.331565797970563</v>
@@ -8908,7 +8848,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8922,7 +8862,7 @@
         <v>2.954681081546583</v>
       </c>
       <c r="D149" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E149">
         <v>2.325889855571697</v>
@@ -8958,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8972,7 +8912,7 @@
         <v>2.952436806561317</v>
       </c>
       <c r="D150" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E150">
         <v>2.323482951964311</v>
@@ -9008,7 +8948,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9022,7 +8962,7 @@
         <v>2.939220179650368</v>
       </c>
       <c r="D151" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E151">
         <v>2.309308598465612</v>
@@ -9058,7 +8998,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9072,7 +9012,7 @@
         <v>2.885800805603528</v>
       </c>
       <c r="D152" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E152">
         <v>2.285985098138231</v>
@@ -9108,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9122,7 +9062,7 @@
         <v>2.882518664640946</v>
       </c>
       <c r="D153" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E153">
         <v>2.285985098138231</v>
@@ -9158,7 +9098,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9172,7 +9112,7 @@
         <v>2.871759791100637</v>
       </c>
       <c r="D154" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E154">
         <v>2.270895377157946</v>
@@ -9208,7 +9148,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9222,7 +9162,7 @@
         <v>2.868186342783224</v>
       </c>
       <c r="D155" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E155">
         <v>2.270895377157946</v>
@@ -9258,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9272,7 +9212,7 @@
         <v>2.851373977249472</v>
       </c>
       <c r="D156" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E156">
         <v>2.248986971400885</v>
@@ -9308,7 +9248,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9322,7 +9262,7 @@
         <v>2.813597099989564</v>
       </c>
       <c r="D157" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E157">
         <v>2.215446285791325</v>
@@ -9358,7 +9298,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9372,7 +9312,7 @@
         <v>2.783887421732515</v>
       </c>
       <c r="D158" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E158">
         <v>2.183719283702006</v>
@@ -9408,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9422,7 +9362,7 @@
         <v>2.721632856402064</v>
       </c>
       <c r="D159" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E159">
         <v>2.127916568873808</v>
@@ -9458,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9472,7 +9412,7 @@
         <v>2.678525715783303</v>
       </c>
       <c r="D160" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E160">
         <v>2.09532033365037</v>
@@ -9508,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9522,7 +9462,7 @@
         <v>2.69110921416971</v>
       </c>
       <c r="D161" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E161">
         <v>2.09532033365037</v>
@@ -9558,7 +9498,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9658,7 +9598,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9708,7 +9648,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9758,7 +9698,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9908,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9958,7 +9898,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10008,7 +9948,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10058,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10108,7 +10048,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10158,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10208,7 +10148,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10222,7 +10162,7 @@
         <v>0.9328900239147986</v>
       </c>
       <c r="D175" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E175">
         <v>0.9481209772972727</v>
@@ -10258,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10272,7 +10212,7 @@
         <v>0.8361716558948933</v>
       </c>
       <c r="D176" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E176">
         <v>0.9453648051842674</v>
@@ -10322,7 +10262,7 @@
         <v>1.860133746163766</v>
       </c>
       <c r="D177" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E177">
         <v>1.319668494742769</v>
@@ -10358,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10372,7 +10312,7 @@
         <v>0.8121110647030001</v>
       </c>
       <c r="D178" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E178">
         <v>0.9618784389925015</v>
@@ -10408,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10422,7 +10362,7 @@
         <v>1.83652515616036</v>
       </c>
       <c r="D179" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E179">
         <v>1.296242563075947</v>
@@ -10458,7 +10398,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10472,7 +10412,7 @@
         <v>0.787726176769115</v>
       </c>
       <c r="D180" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E180">
         <v>1.126454507889258</v>
@@ -10508,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10522,7 +10462,7 @@
         <v>1.791439637530079</v>
       </c>
       <c r="D181" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E181">
         <v>1.27124240240025</v>
@@ -10558,7 +10498,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10572,7 +10512,7 @@
         <v>1.811330062457952</v>
       </c>
       <c r="D182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E182">
         <v>1.27124240240025</v>
@@ -10608,7 +10548,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10622,7 +10562,7 @@
         <v>1.791373892486802</v>
       </c>
       <c r="D183" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E183">
         <v>1.27124240240025</v>
@@ -10658,7 +10598,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10672,7 +10612,7 @@
         <v>0.7617026177031843</v>
       </c>
       <c r="D184" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E184">
         <v>1.161198572371399</v>
@@ -10708,7 +10648,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10722,7 +10662,7 @@
         <v>1.756679227858482</v>
       </c>
       <c r="D185" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E185">
         <v>1.246983702650287</v>
@@ -10758,7 +10698,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10772,7 +10712,7 @@
         <v>1.786882211053019</v>
       </c>
       <c r="D186" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E186">
         <v>1.246983702650287</v>
@@ -10808,7 +10748,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10822,7 +10762,7 @@
         <v>1.766831465254384</v>
       </c>
       <c r="D187" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E187">
         <v>1.246983702650287</v>
@@ -10858,7 +10798,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10872,7 +10812,7 @@
         <v>0.7364508717646272</v>
       </c>
       <c r="D188" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E188">
         <v>1.146806092355067</v>
@@ -10908,7 +10848,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10922,7 +10862,7 @@
         <v>1.727529637465925</v>
       </c>
       <c r="D189" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E189">
         <v>1.218500388609561</v>
@@ -10958,7 +10898,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10972,7 +10912,7 @@
         <v>1.758176804895015</v>
       </c>
       <c r="D190" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E190">
         <v>1.218500388609561</v>
@@ -11008,7 +10948,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11022,7 +10962,7 @@
         <v>1.738015013037742</v>
       </c>
       <c r="D191" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E191">
         <v>1.218500388609561</v>
@@ -11058,7 +10998,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11072,7 +11012,7 @@
         <v>0.735911718893199</v>
       </c>
       <c r="D192" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E192">
         <v>1.39631619853638</v>
@@ -11108,7 +11048,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11122,7 +11062,7 @@
         <v>0.7068015741081979</v>
       </c>
       <c r="D193" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E193">
         <v>1.39631619853638</v>
@@ -11158,7 +11098,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11172,7 +11112,7 @@
         <v>1.69440254301529</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E194">
         <v>1.186130484889226</v>
@@ -11208,7 +11148,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11222,7 +11162,7 @@
         <v>1.725554504264581</v>
       </c>
       <c r="D195" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E195">
         <v>1.186130484889226</v>
@@ -11258,7 +11198,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11272,7 +11212,7 @@
         <v>1.705266513952258</v>
       </c>
       <c r="D196" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E196">
         <v>1.186130484889226</v>
@@ -11308,7 +11248,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11322,7 +11262,7 @@
         <v>0.7015226398920635</v>
       </c>
       <c r="D197" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E197">
         <v>1.362242615672869</v>
@@ -11358,7 +11298,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11372,7 +11312,7 @@
         <v>0.6731065866098378</v>
       </c>
       <c r="D198" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E198">
         <v>1.362242615672869</v>
@@ -11408,7 +11348,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11422,7 +11362,7 @@
         <v>1.672556215816603</v>
       </c>
       <c r="D199" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E199">
         <v>1.164783502312224</v>
@@ -11458,7 +11398,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11472,7 +11412,7 @@
         <v>1.70404107348035</v>
       </c>
       <c r="D200" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E200">
         <v>1.164783502312224</v>
@@ -11508,7 +11448,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11522,7 +11462,7 @@
         <v>1.683669859064413</v>
       </c>
       <c r="D201" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E201">
         <v>1.164783502312224</v>
@@ -11558,7 +11498,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11572,7 +11512,7 @@
         <v>0.6788440716572364</v>
       </c>
       <c r="D202" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E202">
         <v>1.339772107697077</v>
@@ -11608,7 +11548,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11622,7 +11562,7 @@
         <v>0.6508857509448882</v>
       </c>
       <c r="D203" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E203">
         <v>1.339772107697077</v>
@@ -11658,7 +11598,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11672,7 +11612,7 @@
         <v>1.643503437868948</v>
       </c>
       <c r="D204" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E204">
         <v>1.136394787860515</v>
@@ -11708,7 +11648,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11722,7 +11662,7 @@
         <v>1.675431004529993</v>
       </c>
       <c r="D205" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E205">
         <v>1.136394787860515</v>
@@ -11758,7 +11698,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11772,7 +11712,7 @@
         <v>1.654949112864731</v>
       </c>
       <c r="D206" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E206">
         <v>1.136394787860515</v>
@@ -11808,7 +11748,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11822,7 +11762,7 @@
         <v>0.648684521216337</v>
       </c>
       <c r="D207" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E207">
         <v>1.309889250379489</v>
@@ -11858,7 +11798,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11872,7 +11812,7 @@
         <v>0.6213349253752734</v>
       </c>
       <c r="D208" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E208">
         <v>1.309889250379489</v>
@@ -11908,7 +11848,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11922,7 +11862,7 @@
         <v>1.629688879456757</v>
       </c>
       <c r="D209" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E209">
         <v>1.122895990783459</v>
@@ -11972,7 +11912,7 @@
         <v>1.661826953674558</v>
       </c>
       <c r="D210" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E210">
         <v>1.122895990783459</v>
@@ -12022,7 +11962,7 @@
         <v>1.623163250060685</v>
       </c>
       <c r="D211" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E211">
         <v>1.122895990783459</v>
@@ -12072,7 +12012,7 @@
         <v>0.6343436939122524</v>
       </c>
       <c r="D212" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E212">
         <v>1.295679990298378</v>
@@ -12122,7 +12062,7 @@
         <v>0.6072835459617298</v>
       </c>
       <c r="D213" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E213">
         <v>1.295679990298378</v>
@@ -12172,7 +12112,7 @@
         <v>1.607589133113905</v>
       </c>
       <c r="D214" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E214">
         <v>1.101301381499872</v>
@@ -12208,7 +12148,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12222,7 +12162,7 @@
         <v>1.640063965371216</v>
       </c>
       <c r="D215" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E215">
         <v>1.101301381499872</v>
@@ -12258,7 +12198,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12272,7 +12212,7 @@
         <v>1.619445257306888</v>
       </c>
       <c r="D216" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E216">
         <v>1.101301381499872</v>
@@ -12308,7 +12248,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12322,7 +12262,7 @@
         <v>0.6114020524706252</v>
       </c>
       <c r="D217" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E217">
         <v>1.272948822631444</v>
@@ -12358,7 +12298,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12372,7 +12312,7 @@
         <v>0.5848049468244287</v>
       </c>
       <c r="D218" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E218">
         <v>1.272948822631444</v>
@@ -12408,7 +12348,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12422,7 +12362,7 @@
         <v>1.581012843353852</v>
       </c>
       <c r="D219" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E219">
         <v>1.075332549791479</v>
@@ -12458,7 +12398,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12472,7 +12412,7 @@
         <v>1.613892647645603</v>
       </c>
       <c r="D220" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E220">
         <v>1.075332549791479</v>
@@ -12508,7 +12448,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12522,7 +12462,7 @@
         <v>1.593172696572664</v>
       </c>
       <c r="D221" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E221">
         <v>1.075332549791479</v>
@@ -12558,7 +12498,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12572,7 +12512,7 @@
         <v>0.5838133326244757</v>
       </c>
       <c r="D222" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E222">
         <v>1.245613210306819</v>
@@ -12608,7 +12548,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12622,7 +12562,7 @@
         <v>0.5577730635256328</v>
       </c>
       <c r="D223" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E223">
         <v>1.245613210306819</v>
@@ -12658,7 +12598,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12672,7 +12612,7 @@
         <v>1.084913495598071</v>
       </c>
       <c r="D224" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E224">
         <v>1.231364667854545</v>
@@ -12708,7 +12648,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12722,7 +12662,7 @@
         <v>1.091978143921128</v>
       </c>
       <c r="D225" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E225">
         <v>1.231364667854545</v>
@@ -12758,7 +12698,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12808,7 +12748,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12822,7 +12762,7 @@
         <v>1.21869175173632</v>
       </c>
       <c r="D227" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E227">
         <v>1.069755686141992</v>
@@ -12858,7 +12798,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12872,7 +12812,7 @@
         <v>1.184556198440929</v>
       </c>
       <c r="D228" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E228">
         <v>1.069755686141992</v>
@@ -12908,7 +12848,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12922,7 +12862,7 @@
         <v>1.060519812222489</v>
       </c>
       <c r="D229" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E229">
         <v>0.9907313015562922</v>
@@ -12958,7 +12898,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12972,7 +12912,7 @@
         <v>1.017939761129645</v>
       </c>
       <c r="D230" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E230">
         <v>0.9907313015562922</v>
@@ -13008,7 +12948,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13022,7 +12962,7 @@
         <v>1.755318635505916</v>
       </c>
       <c r="D231" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E231">
         <v>1.003833585600265</v>
@@ -13058,7 +12998,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13072,7 +13012,7 @@
         <v>1.894053096403</v>
       </c>
       <c r="D232" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E232">
         <v>1.003833585600265</v>
@@ -13108,7 +13048,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13122,7 +13062,7 @@
         <v>1.97376040323609</v>
       </c>
       <c r="D233" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E233">
         <v>1.250262419204153</v>
@@ -13158,7 +13098,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13172,7 +13112,7 @@
         <v>2.034815821986728</v>
       </c>
       <c r="D234" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E234">
         <v>1.357988243685597</v>
@@ -13208,7 +13148,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13222,7 +13162,7 @@
         <v>2.10245468159479</v>
       </c>
       <c r="D235" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E235">
         <v>1.356708020256039</v>
@@ -13258,7 +13198,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13272,7 +13212,7 @@
         <v>2.160736912923812</v>
       </c>
       <c r="D236" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E236">
         <v>1.515238926320149</v>
@@ -13308,7 +13248,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13322,7 +13262,7 @@
         <v>2.25315272423952</v>
       </c>
       <c r="D237" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E237">
         <v>1.696228284995405</v>
@@ -13358,7 +13298,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13372,7 +13312,7 @@
         <v>2.36943391560179</v>
       </c>
       <c r="D238" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E238">
         <v>1.892500425794016</v>
@@ -13408,7 +13348,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13422,7 +13362,7 @@
         <v>2.474058411102812</v>
       </c>
       <c r="D239" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E239">
         <v>1.89058438855279</v>
@@ -13458,7 +13398,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13472,7 +13412,7 @@
         <v>2.503056313450243</v>
       </c>
       <c r="D240" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E240">
         <v>1.996322171701399</v>
@@ -13508,7 +13448,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13522,7 +13462,7 @@
         <v>2.525264172262913</v>
       </c>
       <c r="D241" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E241">
         <v>1.973847066177296</v>
@@ -13558,7 +13498,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13572,7 +13512,7 @@
         <v>2.554243076596262</v>
       </c>
       <c r="D242" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E242">
         <v>1.938989294196617</v>
@@ -13608,7 +13548,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13622,7 +13562,7 @@
         <v>2.598334390223854</v>
       </c>
       <c r="D243" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E243">
         <v>2.028465786771591</v>
@@ -13658,7 +13598,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13672,7 +13612,7 @@
         <v>2.670586589154834</v>
       </c>
       <c r="D244" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E244">
         <v>1.994395774818371</v>
@@ -13722,7 +13662,7 @@
         <v>2.717624878766997</v>
       </c>
       <c r="D245" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E245">
         <v>2.20711354567414</v>
@@ -13772,7 +13712,7 @@
         <v>2.768201130893359</v>
       </c>
       <c r="D246" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E246">
         <v>2.294068506214541</v>
@@ -13808,7 +13748,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13822,7 +13762,7 @@
         <v>2.800856629280805</v>
       </c>
       <c r="D247" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E247">
         <v>2.225122088576691</v>
@@ -13858,7 +13798,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13872,7 +13812,7 @@
         <v>2.80951643088527</v>
       </c>
       <c r="D248" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E248">
         <v>2.242646460311337</v>
@@ -13908,7 +13848,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13922,7 +13862,7 @@
         <v>2.799569806125956</v>
       </c>
       <c r="D249" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E249">
         <v>2.14320981989216</v>
@@ -13972,7 +13912,7 @@
         <v>2.819828844666985</v>
       </c>
       <c r="D250" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E250">
         <v>2.18506309598321</v>
@@ -14008,7 +13948,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14022,7 +13962,7 @@
         <v>2.819851650007405</v>
       </c>
       <c r="D251" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E251">
         <v>2.072484872689354</v>
@@ -14072,7 +14012,7 @@
         <v>2.840423697083499</v>
       </c>
       <c r="D252" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E252">
         <v>2.262963564508703</v>
@@ -14122,7 +14062,7 @@
         <v>2.908629147129241</v>
       </c>
       <c r="D253" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E253">
         <v>2.216875943157096</v>
@@ -14158,7 +14098,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14172,7 +14112,7 @@
         <v>3.004384252257208</v>
       </c>
       <c r="D254" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E254">
         <v>2.339997391123474</v>
@@ -14208,7 +14148,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14222,7 +14162,7 @@
         <v>3.088901753172625</v>
       </c>
       <c r="D255" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E255">
         <v>2.06246025697973</v>
@@ -14258,7 +14198,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14272,7 +14212,7 @@
         <v>3.179054845713715</v>
       </c>
       <c r="D256" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E256">
         <v>2.414075593575115</v>
@@ -14308,7 +14248,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14322,7 +14262,7 @@
         <v>3.299462923221598</v>
       </c>
       <c r="D257" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E257">
         <v>2.237378699869055</v>
@@ -14358,7 +14298,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14372,7 +14312,7 @@
         <v>3.418692237363245</v>
       </c>
       <c r="D258" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E258">
         <v>2.342027703405609</v>
@@ -14408,7 +14348,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14422,7 +14362,7 @@
         <v>3.512759057977069</v>
       </c>
       <c r="D259" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E259">
         <v>2.424591283628788</v>
@@ -14458,7 +14398,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14472,7 +14412,7 @@
         <v>3.645345160280047</v>
       </c>
       <c r="D260" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E260">
         <v>2.540963700837517</v>
@@ -14508,7 +14448,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14522,7 +14462,7 @@
         <v>3.815771971902112</v>
       </c>
       <c r="D261" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E261">
         <v>2.690549363898303</v>
@@ -14558,7 +14498,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14572,7 +14512,7 @@
         <v>4.010037470388323</v>
       </c>
       <c r="D262" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E262">
         <v>2.861058529236299</v>
@@ -14608,7 +14548,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14622,7 +14562,7 @@
         <v>4.152500561307447</v>
       </c>
       <c r="D263" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E263">
         <v>2.986100098188981</v>
@@ -14658,7 +14598,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14672,7 +14612,7 @@
         <v>4.227000299262723</v>
       </c>
       <c r="D264" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E264">
         <v>3.05148941454026</v>
@@ -14708,7 +14648,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14722,7 +14662,7 @@
         <v>3.628868452425993</v>
       </c>
       <c r="D265" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E265">
         <v>3.018868452425993</v>
@@ -14758,7 +14698,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14772,7 +14712,7 @@
         <v>3.56416211054958</v>
       </c>
       <c r="D266" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E266">
         <v>2.954162110549579</v>
@@ -14808,7 +14748,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14822,7 +14762,7 @@
         <v>3.491997735810393</v>
       </c>
       <c r="D267" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E267">
         <v>2.881997735810393</v>
@@ -14858,7 +14798,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14872,7 +14812,7 @@
         <v>3.304014584160329</v>
       </c>
       <c r="D268" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E268">
         <v>2.694014584160328</v>
@@ -14908,7 +14848,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14922,7 +14862,7 @@
         <v>3.180251695694135</v>
       </c>
       <c r="D269" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E269">
         <v>2.570251695694135</v>
@@ -14958,7 +14898,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14972,7 +14912,7 @@
         <v>3.152401945865307</v>
       </c>
       <c r="D270" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E270">
         <v>2.542401945865306</v>
@@ -15008,7 +14948,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15022,7 +14962,7 @@
         <v>2.145825454055195</v>
       </c>
       <c r="D271" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E271">
         <v>2.567272076620798</v>
@@ -15058,7 +14998,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15072,7 +15012,7 @@
         <v>3.117834193471839</v>
       </c>
       <c r="D272" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E272">
         <v>2.507834193471838</v>
@@ -15108,7 +15048,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15122,7 +15062,7 @@
         <v>2.068689520733654</v>
       </c>
       <c r="D273" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E273">
         <v>2.489975777533515</v>
@@ -15158,7 +15098,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15172,7 +15112,7 @@
         <v>3.048235451140136</v>
       </c>
       <c r="D274" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E274">
         <v>2.438235451140136</v>
@@ -15208,7 +15148,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15222,7 +15162,7 @@
         <v>1.98934486068918</v>
       </c>
       <c r="D275" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E275">
         <v>2.539161477129087</v>
@@ -15258,7 +15198,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15272,7 +15212,7 @@
         <v>2.976643803615602</v>
       </c>
       <c r="D276" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E276">
         <v>2.366643803615601</v>
@@ -15308,7 +15248,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15322,7 +15262,7 @@
         <v>1.910228381091732</v>
       </c>
       <c r="D277" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E277">
         <v>2.463005697391833</v>
@@ -15358,7 +15298,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15372,7 +15312,7 @@
         <v>2.905258040319775</v>
       </c>
       <c r="D278" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E278">
         <v>2.295258040319774</v>
@@ -15408,7 +15348,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15422,7 +15362,7 @@
         <v>1.737565923958936</v>
       </c>
       <c r="D279" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E279">
         <v>2.268709795269682</v>
@@ -15458,7 +15398,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15472,7 +15412,7 @@
         <v>1.733986526635413</v>
       </c>
       <c r="D280" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E280">
         <v>2.293359172208309</v>
@@ -15508,7 +15448,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15522,7 +15462,7 @@
         <v>2.746237323409084</v>
       </c>
       <c r="D281" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E281">
         <v>2.136237323409084</v>
@@ -15558,7 +15498,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15572,7 +15512,7 @@
         <v>1.537618654463894</v>
       </c>
       <c r="D282" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E282">
         <v>2.074713337366754</v>
@@ -15608,7 +15548,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15622,7 +15562,7 @@
         <v>1.543163834914946</v>
       </c>
       <c r="D283" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E283">
         <v>2.109677454398378</v>
@@ -15658,7 +15598,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15672,7 +15612,7 @@
         <v>2.574060508010575</v>
       </c>
       <c r="D284" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E284">
         <v>1.964060508010575</v>
@@ -15708,7 +15648,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15722,7 +15662,7 @@
         <v>1.32861267508225</v>
       </c>
       <c r="D285" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E285">
         <v>1.871927774038136</v>
@@ -15758,7 +15698,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15772,7 +15712,7 @@
         <v>1.343695826814607</v>
       </c>
       <c r="D286" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E286">
         <v>1.91767394556167</v>
@@ -15808,7 +15748,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15822,7 +15762,7 @@
         <v>2.394083136876382</v>
       </c>
       <c r="D287" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E287">
         <v>1.784083136876382</v>
@@ -15858,7 +15798,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15872,7 +15812,7 @@
         <v>1.270355943810468</v>
       </c>
       <c r="D288" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E288">
         <v>1.815404874054204</v>
@@ -15908,7 +15848,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15922,7 +15862,7 @@
         <v>1.288097636850863</v>
       </c>
       <c r="D289" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E289">
         <v>1.864156353143347</v>
@@ -15958,7 +15898,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15972,7 +15912,7 @@
         <v>2.343917618281236</v>
       </c>
       <c r="D290" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E290">
         <v>1.733917618281236</v>
@@ -16008,7 +15948,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16022,7 +15962,7 @@
         <v>1.164376800206434</v>
       </c>
       <c r="D291" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E291">
         <v>1.712579871628862</v>
@@ -16058,7 +15998,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16072,7 +16012,7 @@
         <v>1.186954843054156</v>
       </c>
       <c r="D292" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E292">
         <v>1.76679852876107</v>
@@ -16108,7 +16048,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16122,7 +16062,7 @@
         <v>2.252657800177763</v>
       </c>
       <c r="D293" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E293">
         <v>1.642657800177763</v>
@@ -16158,7 +16098,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16172,7 +16112,7 @@
         <v>1.095337982971794</v>
       </c>
       <c r="D294" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E294">
         <v>1.645595781097634</v>
@@ -16208,7 +16148,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16222,7 +16162,7 @@
         <v>1.121066606764748</v>
       </c>
       <c r="D295" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E295">
         <v>1.703375964515756</v>
@@ -16258,7 +16198,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16272,7 +16212,7 @@
         <v>2.193207707559045</v>
       </c>
       <c r="D296" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E296">
         <v>1.583207707559045</v>
@@ -16308,7 +16248,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16322,7 +16262,7 @@
         <v>0.875155284260706</v>
       </c>
       <c r="D297" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E297">
         <v>1.489897717173242</v>
@@ -16358,7 +16298,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16372,7 +16312,7 @@
         <v>0.9109319280345227</v>
       </c>
       <c r="D298" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E298">
         <v>1.501104953596641</v>
@@ -16408,7 +16348,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16422,7 +16362,7 @@
         <v>2.003605939224497</v>
       </c>
       <c r="D299" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E299">
         <v>1.393605939224496</v>
@@ -16458,7 +16398,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16472,7 +16412,7 @@
         <v>0.7877632879655483</v>
       </c>
       <c r="D300" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E300">
         <v>1.407881022237508</v>
@@ -16508,7 +16448,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16522,7 +16462,7 @@
         <v>0.8275280585544227</v>
       </c>
       <c r="D301" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E301">
         <v>1.420822226841367</v>
@@ -16558,7 +16498,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16572,7 +16512,7 @@
         <v>1.928351720192556</v>
       </c>
       <c r="D302" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E302">
         <v>1.318351720192555</v>
@@ -16608,7 +16548,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16622,7 +16562,7 @@
         <v>0.6445889510900153</v>
       </c>
       <c r="D303" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E303">
         <v>1.273513043384081</v>
@@ -16658,7 +16598,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16672,7 +16612,7 @@
         <v>0.6908874711791615</v>
       </c>
       <c r="D304" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E304">
         <v>1.289295008640233</v>
@@ -16708,7 +16648,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16722,7 +16662,7 @@
         <v>1.805062707883069</v>
       </c>
       <c r="D305" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E305">
         <v>1.195062707883069</v>
@@ -16758,7 +16698,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16772,7 +16712,7 @@
         <v>0.5834745700515587</v>
       </c>
       <c r="D306" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E306">
         <v>1.216157681814259</v>
@@ -16808,7 +16748,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16822,7 +16762,7 @@
         <v>0.6325620400690468</v>
       </c>
       <c r="D307" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E307">
         <v>1.233152233995777</v>
@@ -16858,7 +16798,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16872,7 +16812,7 @@
         <v>1.752436435322175</v>
       </c>
       <c r="D308" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E308">
         <v>1.142436435322175</v>
@@ -16908,7 +16848,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16922,7 +16862,7 @@
         <v>0.6410588642705362</v>
       </c>
       <c r="D309" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E309">
         <v>1.24133108972403</v>
@@ -16958,7 +16898,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16972,7 +16912,7 @@
         <v>0.6556505260902954</v>
       </c>
       <c r="D310" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E310">
         <v>1.24133108972403</v>
@@ -17008,7 +16948,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17022,7 +16962,7 @@
         <v>1.760103008510213</v>
       </c>
       <c r="D311" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E311">
         <v>1.150103008510213</v>
@@ -17058,7 +16998,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17072,7 +17012,7 @@
         <v>0.6538601304024763</v>
       </c>
       <c r="D312" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E312">
         <v>1.253653306395731</v>
@@ -17108,7 +17048,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17122,7 +17062,7 @@
         <v>0.6691703664125939</v>
       </c>
       <c r="D313" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E313">
         <v>1.253653306395731</v>
@@ -17158,7 +17098,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17172,7 +17112,7 @@
         <v>1.771653423273752</v>
       </c>
       <c r="D314" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E314">
         <v>1.161653423273751</v>
@@ -17208,7 +17148,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17222,7 +17162,7 @@
         <v>0.5994681371241404</v>
       </c>
       <c r="D315" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E315">
         <v>1.201296772325317</v>
@@ -17258,7 +17198,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17272,7 +17212,7 @@
         <v>0.6117251843223768</v>
       </c>
       <c r="D316" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E316">
         <v>1.201296772325317</v>
@@ -17308,7 +17248,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17322,7 +17262,7 @@
         <v>1.722576240149433</v>
       </c>
       <c r="D317" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E317">
         <v>1.112576240149433</v>
@@ -17358,7 +17298,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17372,7 +17312,7 @@
         <v>0.6080222404361217</v>
       </c>
       <c r="D318" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E318">
         <v>1.209530763663045</v>
@@ -17408,7 +17348,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17422,7 +17362,7 @@
         <v>0.6207594555957376</v>
       </c>
       <c r="D319" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E319">
         <v>1.209530763663045</v>
@@ -17458,7 +17398,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17472,7 +17412,7 @@
         <v>1.730294495528642</v>
       </c>
       <c r="D320" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E320">
         <v>1.120294495528642</v>
@@ -17508,7 +17448,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17522,7 +17462,7 @@
         <v>0.5618859798618736</v>
       </c>
       <c r="D321" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E321">
         <v>1.165121015958519</v>
@@ -17558,7 +17498,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17572,7 +17512,7 @@
         <v>0.5720334257169055</v>
       </c>
       <c r="D322" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E322">
         <v>1.165121015958519</v>
@@ -17608,7 +17548,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17622,7 +17562,7 @@
         <v>1.688666351892003</v>
       </c>
       <c r="D323" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E323">
         <v>1.078666351892003</v>
@@ -17658,7 +17598,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17672,7 +17612,7 @@
         <v>0.508437810595022</v>
       </c>
       <c r="D324" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E324">
         <v>1.11367298608211</v>
@@ -17708,7 +17648,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17722,7 +17662,7 @@
         <v>0.5155850473643886</v>
       </c>
       <c r="D325" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E325">
         <v>1.11367298608211</v>
@@ -17758,7 +17698,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17772,7 +17712,7 @@
         <v>1.640440768811309</v>
       </c>
       <c r="D326" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E326">
         <v>1.030440768811308</v>
@@ -17808,7 +17748,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17822,7 +17762,7 @@
         <v>0.4164767378858123</v>
       </c>
       <c r="D327" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E327">
         <v>1.025153284077196</v>
@@ -17858,7 +17798,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17872,7 +17812,7 @@
         <v>0.4184619185987364</v>
       </c>
       <c r="D328" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E328">
         <v>1.025153284077196</v>
@@ -17908,7 +17848,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17922,7 +17862,7 @@
         <v>1.557465497385535</v>
       </c>
       <c r="D329" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E329">
         <v>0.9474654973855348</v>
@@ -17958,7 +17898,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17972,7 +17912,7 @@
         <v>0.3644704529510241</v>
       </c>
       <c r="D330" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E330">
         <v>0.9750931802834177</v>
@@ -18008,7 +17948,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18022,7 +17962,7 @@
         <v>0.3635363619524323</v>
       </c>
       <c r="D331" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E331">
         <v>0.9750931802834177</v>
@@ -18058,7 +17998,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18072,7 +18012,7 @@
         <v>1.565054544022541</v>
       </c>
       <c r="D332" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E332">
         <v>0.9005409076522746</v>
@@ -18108,7 +18048,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18122,7 +18062,7 @@
         <v>0.2866150347691372</v>
       </c>
       <c r="D333" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E333">
         <v>0.9143380680881883</v>
@@ -18158,7 +18098,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18172,7 +18112,7 @@
         <v>0.2813106812114787</v>
       </c>
       <c r="D334" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E334">
         <v>0.9143380680881883</v>
@@ -18208,7 +18148,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18222,7 +18162,7 @@
         <v>0.3483831526216896</v>
       </c>
       <c r="D335" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E335">
         <v>0.9143380680881883</v>
@@ -18258,7 +18198,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18272,7 +18212,7 @@
         <v>1.495130343077478</v>
       </c>
       <c r="D336" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E336">
         <v>0.8302929835546884</v>
@@ -18308,7 +18248,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18322,7 +18262,7 @@
         <v>0.2225831635998929</v>
       </c>
       <c r="D337" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E337">
         <v>0.8619688447062037</v>
@@ -18372,7 +18312,7 @@
         <v>0.2987488573747035</v>
       </c>
       <c r="D338" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E338">
         <v>0.8619688447062037</v>
@@ -18422,7 +18362,7 @@
         <v>0.2938174275967516</v>
       </c>
       <c r="D339" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E339">
         <v>0.8619688447062037</v>
@@ -18472,7 +18412,7 @@
         <v>1.445188832037704</v>
       </c>
       <c r="D340" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E340">
         <v>0.7801202618156564</v>
@@ -18522,7 +18462,7 @@
         <v>0.3281392211768228</v>
       </c>
       <c r="D341" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E341">
         <v>0.8803786785285439</v>
@@ -18558,7 +18498,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18572,7 +18512,7 @@
         <v>0.3180121272020529</v>
       </c>
       <c r="D342" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E342">
         <v>0.8803786785285439</v>
@@ -18608,7 +18548,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18622,7 +18562,7 @@
         <v>0.3129994178045763</v>
       </c>
       <c r="D343" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E343">
         <v>0.8803786785285439</v>
@@ -18658,7 +18598,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18672,7 +18612,7 @@
         <v>1.462745229855035</v>
       </c>
       <c r="D344" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E344">
         <v>0.7977579392525129</v>
@@ -18708,7 +18648,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18722,7 +18662,7 @@
         <v>0.3459316339300287</v>
       </c>
       <c r="D345" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E345">
         <v>0.8966943930572944</v>
@@ -18758,7 +18698,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18772,7 +18712,7 @@
         <v>0.3350841993579632</v>
       </c>
       <c r="D346" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E346">
         <v>0.8966943930572944</v>
@@ -18808,7 +18748,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18822,7 +18762,7 @@
         <v>0.3299994559007571</v>
       </c>
       <c r="D347" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E347">
         <v>0.8966943930572944</v>
@@ -18858,7 +18798,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18872,7 +18812,7 @@
         <v>1.478304586756625</v>
       </c>
       <c r="D348" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E348">
         <v>0.8133893302138313</v>
@@ -18908,7 +18848,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18922,7 +18862,7 @@
         <v>0.3746816311597856</v>
       </c>
       <c r="D349" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E349">
         <v>0.9230582569137313</v>
@@ -18958,7 +18898,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18972,7 +18912,7 @@
         <v>0.3626702290885397</v>
       </c>
       <c r="D350" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E350">
         <v>0.9230582569137313</v>
@@ -19008,7 +18948,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19022,7 +18962,7 @@
         <v>0.357469088881416</v>
       </c>
       <c r="D351" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E351">
         <v>0.9230582569137313</v>
@@ -19058,7 +18998,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19072,7 +19012,7 @@
         <v>1.503446284738923</v>
       </c>
       <c r="D352" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E352">
         <v>0.8386474249460472</v>
@@ -19108,7 +19048,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19122,7 +19062,7 @@
         <v>0.3609903029368784</v>
       </c>
       <c r="D353" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E353">
         <v>0.9727726579916833</v>
@@ -19172,7 +19112,7 @@
         <v>0.4278925267560636</v>
       </c>
       <c r="D354" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E354">
         <v>0.9853909591149721</v>
@@ -19222,7 +19162,7 @@
         <v>0.4224161869807217</v>
       </c>
       <c r="D355" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E355">
         <v>0.9853909591149721</v>
@@ -19272,7 +19212,7 @@
         <v>1.508365731249223</v>
       </c>
       <c r="D356" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E356">
         <v>0.898365731249223</v>
@@ -19322,7 +19262,7 @@
         <v>0.5369709001154694</v>
       </c>
       <c r="D357" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E357">
         <v>1.089636746312885</v>
@@ -19372,7 +19312,7 @@
         <v>0.531034314039033</v>
       </c>
       <c r="D358" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E358">
         <v>1.089636746312885</v>
@@ -19422,7 +19362,7 @@
         <v>1.608239178586738</v>
       </c>
       <c r="D359" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E359">
         <v>0.9982391785867382</v>
@@ -19472,7 +19412,7 @@
         <v>0.5385854937585846</v>
       </c>
       <c r="D360" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E360">
         <v>0.634839149452838</v>
@@ -19522,7 +19462,7 @@
         <v>2.009812451983092</v>
       </c>
       <c r="D361" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E361">
         <v>1.399812451983092</v>
@@ -19558,7 +19498,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19572,7 +19512,7 @@
         <v>0.9230051396340304</v>
       </c>
       <c r="D362" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E362">
         <v>0.9850070169538339</v>
@@ -19608,7 +19548,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19622,7 +19562,7 @@
         <v>0.8994749023453439</v>
       </c>
       <c r="D363" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E363">
         <v>0.9850070169538339</v>
@@ -19658,7 +19598,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19672,7 +19612,7 @@
         <v>2.109691017081675</v>
       </c>
       <c r="D364" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E364">
         <v>1.499691017081674</v>
@@ -19708,7 +19648,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19722,7 +19662,7 @@
         <v>1.015979656453909</v>
       </c>
       <c r="D365" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E365">
         <v>1.231185799135601</v>
@@ -19758,7 +19698,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19772,7 +19712,7 @@
         <v>0.9827837515750368</v>
       </c>
       <c r="D366" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E366">
         <v>1.231185799135601</v>
@@ -19808,7 +19748,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19822,7 +19762,7 @@
         <v>2.200993423621709</v>
       </c>
       <c r="D367" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E367">
         <v>1.590993423621708</v>
@@ -19858,7 +19798,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19872,7 +19812,7 @@
         <v>1.100970836735415</v>
       </c>
       <c r="D368" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E368">
         <v>1.303589318044656</v>
@@ -19908,7 +19848,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19922,7 +19862,7 @@
         <v>1.058939215094605</v>
       </c>
       <c r="D369" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E369">
         <v>1.303589318044656</v>
@@ -19958,7 +19898,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19972,7 +19912,7 @@
         <v>2.329644706282916</v>
       </c>
       <c r="D370" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E370">
         <v>1.719644706282915</v>
@@ -20008,7 +19948,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20022,7 +19962,7 @@
         <v>1.220729173590548</v>
       </c>
       <c r="D371" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E371">
         <v>1.321050696987874</v>
@@ -20058,7 +19998,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20072,7 +20012,7 @@
         <v>2.471463589779925</v>
       </c>
       <c r="D372" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E372">
         <v>1.861463589779925</v>
@@ -20108,7 +20048,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20158,7 +20098,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20172,7 +20112,7 @@
         <v>2.497443975683849</v>
       </c>
       <c r="D374" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E374">
         <v>1.887443975683849</v>
@@ -20208,7 +20148,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20258,7 +20198,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20308,7 +20248,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20322,7 +20262,7 @@
         <v>2.512308244184901</v>
       </c>
       <c r="D377" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E377">
         <v>1.9023082441849</v>
@@ -20358,7 +20298,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20372,7 +20312,7 @@
         <v>1.390766199655991</v>
       </c>
       <c r="D378" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E378">
         <v>1.47783631505106</v>
@@ -20408,7 +20348,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20422,7 +20362,7 @@
         <v>1.39783631505106</v>
       </c>
       <c r="D379" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E379">
         <v>1.47783631505106</v>
@@ -20458,7 +20398,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20472,7 +20412,7 @@
         <v>2.5135497431605</v>
       </c>
       <c r="D380" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E380">
         <v>1.903549743160499</v>
@@ -20508,7 +20448,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20522,7 +20462,7 @@
         <v>1.39192188073005</v>
       </c>
       <c r="D381" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E381">
         <v>1.488828942112197</v>
@@ -20558,7 +20498,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20572,7 +20512,7 @@
         <v>1.319642873327421</v>
       </c>
       <c r="D382" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E382">
         <v>1.488828942112197</v>
@@ -20608,7 +20548,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20622,7 +20562,7 @@
         <v>1.388828942112196</v>
       </c>
       <c r="D383" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E383">
         <v>1.488828942112197</v>
@@ -20658,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20672,7 +20612,7 @@
         <v>2.501566998394471</v>
       </c>
       <c r="D384" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E384">
         <v>1.891566998394471</v>
@@ -20708,7 +20648,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20722,7 +20662,7 @@
         <v>1.279594745212004</v>
       </c>
       <c r="D385" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E385">
         <v>1.519061703811337</v>
@@ -20758,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20772,7 +20712,7 @@
         <v>1.30964804935207</v>
       </c>
       <c r="D386" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E386">
         <v>1.519061703811337</v>
@@ -20808,7 +20748,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20822,7 +20762,7 @@
         <v>2.48573721583752</v>
       </c>
       <c r="D387" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E387">
         <v>1.875737215837519</v>
@@ -20858,7 +20798,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20872,7 +20812,7 @@
         <v>1.266464050003473</v>
       </c>
       <c r="D388" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E388">
         <v>1.59667031375327</v>
@@ -20908,7 +20848,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20922,7 +20862,7 @@
         <v>1.296444405836825</v>
       </c>
       <c r="D389" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E389">
         <v>1.59667031375327</v>
@@ -20958,7 +20898,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20972,7 +20912,7 @@
         <v>2.454303876936348</v>
       </c>
       <c r="D390" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E390">
         <v>1.844303876936348</v>
@@ -21008,7 +20948,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21022,7 +20962,7 @@
         <v>1.240390312666095</v>
       </c>
       <c r="D391" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E391">
         <v>1.592199793558723</v>
@@ -21058,7 +20998,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21072,7 +21012,7 @@
         <v>1.270225814403128</v>
       </c>
       <c r="D392" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E392">
         <v>1.592199793558723</v>
@@ -21108,7 +21048,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21122,7 +21062,7 @@
         <v>2.438801816749918</v>
       </c>
       <c r="D393" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E393">
         <v>1.828801816749918</v>
@@ -21158,7 +21098,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21172,7 +21112,7 @@
         <v>1.227531460898549</v>
       </c>
       <c r="D394" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E394">
         <v>1.611306442152011</v>
@@ -21208,7 +21148,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21222,7 +21162,7 @@
         <v>1.257295524570208</v>
       </c>
       <c r="D395" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E395">
         <v>1.611306442152011</v>
@@ -21258,7 +21198,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21272,7 +21212,7 @@
         <v>2.435888213210831</v>
       </c>
       <c r="D396" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E396">
         <v>1.825888213210831</v>
@@ -21308,7 +21248,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21322,7 +21262,7 @@
         <v>1.225114646902994</v>
       </c>
       <c r="D397" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E397">
         <v>1.589727863749075</v>
@@ -21358,7 +21298,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21372,7 +21312,7 @@
         <v>1.254865283830232</v>
       </c>
       <c r="D398" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E398">
         <v>1.589727863749075</v>
@@ -21408,7 +21348,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21422,7 +21362,7 @@
         <v>2.394557671241156</v>
       </c>
       <c r="D399" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E399">
         <v>1.784557671241155</v>
@@ -21458,7 +21398,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21472,7 +21412,7 @@
         <v>1.190831248034139</v>
       </c>
       <c r="D400" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E400">
         <v>1.609187949630535</v>
@@ -21508,7 +21448,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21522,7 +21462,7 @@
         <v>1.220391421634328</v>
       </c>
       <c r="D401" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E401">
         <v>1.609187949630535</v>
@@ -21558,7 +21498,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21572,7 +21512,7 @@
         <v>2.366135904185318</v>
       </c>
       <c r="D402" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E402">
         <v>1.756135904185318</v>
@@ -21608,7 +21548,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21622,7 +21562,7 @@
         <v>1.167255588725149</v>
       </c>
       <c r="D403" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E403">
         <v>1.578100832137494</v>
@@ -21658,7 +21598,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21672,7 +21612,7 @@
         <v>1.196684786440288</v>
       </c>
       <c r="D404" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E404">
         <v>1.578100832137494</v>
@@ -21708,7 +21648,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21722,7 +21662,7 @@
         <v>2.396096253709469</v>
       </c>
       <c r="D405" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E405">
         <v>1.786096253709469</v>
@@ -21758,7 +21698,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21772,7 +21712,7 @@
         <v>1.192107491556242</v>
       </c>
       <c r="D406" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E406">
         <v>1.492060423190722</v>
@@ -21808,7 +21748,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21822,7 +21762,7 @@
         <v>1.221674755398221</v>
       </c>
       <c r="D407" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E407">
         <v>1.492060423190722</v>
@@ -21858,7 +21798,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21872,7 +21812,7 @@
         <v>2.341003521520614</v>
       </c>
       <c r="D408" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E408">
         <v>1.731003521520614</v>
@@ -21908,7 +21848,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21922,7 +21862,7 @@
         <v>1.146408451030924</v>
       </c>
       <c r="D409" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E409">
         <v>1.603573943943295</v>
@@ -21958,7 +21898,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21972,7 +21912,7 @@
         <v>1.175721831314429</v>
       </c>
       <c r="D410" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E410">
         <v>1.603573943943295</v>
@@ -22008,7 +21948,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22022,7 +21962,7 @@
         <v>2.3387346635889</v>
       </c>
       <c r="D411" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E411">
         <v>1.7287346635889</v>
@@ -22058,7 +21998,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22072,7 +22012,7 @@
         <v>1.144526449059917</v>
       </c>
       <c r="D412" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E412">
         <v>1.601256255851928</v>
@@ -22108,7 +22048,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22122,7 +22062,7 @@
         <v>1.173829373776917</v>
       </c>
       <c r="D413" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E413">
         <v>1.601256255851928</v>
@@ -22158,7 +22098,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22172,7 +22112,7 @@
         <v>2.321864997704619</v>
       </c>
       <c r="D414" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E414">
         <v>1.711864997704619</v>
@@ -22208,7 +22148,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22222,7 +22162,7 @@
         <v>1.130533177819499</v>
       </c>
       <c r="D415" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E415">
         <v>1.628353938431452</v>
@@ -22258,7 +22198,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22272,7 +22212,7 @@
         <v>1.159758362140719</v>
       </c>
       <c r="D416" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E416">
         <v>1.628353938431452</v>
@@ -22308,7 +22248,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22322,7 +22262,7 @@
         <v>2.329307629672357</v>
       </c>
       <c r="D417" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E417">
         <v>1.719307629672357</v>
@@ -22358,7 +22298,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22372,7 +22312,7 @@
         <v>1.136706789589973</v>
       </c>
       <c r="D418" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E418">
         <v>1.641887405220004</v>
@@ -22408,7 +22348,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22422,7 +22362,7 @@
         <v>1.165966271754362</v>
       </c>
       <c r="D419" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E419">
         <v>1.641887405220004</v>
@@ -22458,7 +22398,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22472,7 +22412,7 @@
         <v>2.283832828965951</v>
       </c>
       <c r="D420" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E420">
         <v>1.673832828965951</v>
@@ -22522,7 +22462,7 @@
         <v>1.09898575674595</v>
       </c>
       <c r="D421" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E421">
         <v>1.611312616281895</v>
@@ -22572,7 +22512,7 @@
         <v>1.128035677616761</v>
       </c>
       <c r="D422" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E422">
         <v>1.611312616281895</v>
@@ -22622,7 +22562,7 @@
         <v>2.182831733767929</v>
       </c>
       <c r="D423" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E423">
         <v>1.572831733767929</v>
@@ -22658,7 +22598,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22672,7 +22612,7 @@
         <v>1.084064563230975</v>
       </c>
       <c r="D424" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E424">
         <v>1.514840661441129</v>
@@ -22708,7 +22648,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22722,7 +22662,7 @@
         <v>1.04379052447924</v>
       </c>
       <c r="D425" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E425">
         <v>1.514840661441129</v>
@@ -22758,7 +22698,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22772,7 +22712,7 @@
         <v>1.987186684521362</v>
       </c>
       <c r="D426" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E426">
         <v>1.377186684521361</v>
@@ -22808,7 +22748,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22822,7 +22762,7 @@
         <v>0.9019433653148159</v>
       </c>
       <c r="D427" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E427">
         <v>1.471274636039009</v>
@@ -22858,7 +22798,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22872,7 +22812,7 @@
         <v>0.8806027184256511</v>
       </c>
       <c r="D428" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E428">
         <v>1.471274636039009</v>
@@ -22908,7 +22848,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22922,7 +22862,7 @@
         <v>1.871503922012645</v>
       </c>
       <c r="D429" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E429">
         <v>1.261503922012645</v>
@@ -22972,7 +22912,7 @@
         <v>0.8271315762745894</v>
       </c>
       <c r="D430" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E430">
         <v>1.39104304268619</v>
@@ -23022,7 +22962,7 @@
         <v>0.784111566287045</v>
       </c>
       <c r="D431" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E431">
         <v>1.39104304268619</v>
@@ -23072,7 +23012,7 @@
         <v>1.725043908638261</v>
       </c>
       <c r="D432" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E432">
         <v>1.115043908638261</v>
@@ -23108,7 +23048,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23122,7 +23062,7 @@
         <v>0.6891081996153199</v>
       </c>
       <c r="D433" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E433">
         <v>1.208315076967225</v>
@@ -23158,7 +23098,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23172,7 +23112,7 @@
         <v>0.6619490666521894</v>
       </c>
       <c r="D434" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E434">
         <v>1.208315076967225</v>
@@ -23208,7 +23148,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23222,7 +23162,7 @@
         <v>1.603418511347999</v>
       </c>
       <c r="D435" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E435">
         <v>0.9934185113479987</v>
@@ -23258,7 +23198,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23272,7 +23212,7 @@
         <v>0.574488873597538</v>
       </c>
       <c r="D436" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E436">
         <v>1.108556250145786</v>
@@ -23308,7 +23248,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23322,7 +23262,7 @@
         <v>0.5605011546266709</v>
       </c>
       <c r="D437" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E437">
         <v>1.108556250145786</v>
@@ -23358,7 +23298,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23372,7 +23312,7 @@
         <v>1.504487777527864</v>
       </c>
       <c r="D438" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E438">
         <v>0.8944877775278632</v>
@@ -23408,7 +23348,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23422,7 +23362,7 @@
         <v>0.4812569147670418</v>
       </c>
       <c r="D439" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E439">
         <v>1.036979636275919</v>
@@ -23458,7 +23398,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23472,7 +23412,7 @@
         <v>0.4779828927766969</v>
       </c>
       <c r="D440" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E440">
         <v>1.036979636275919</v>
@@ -23508,7 +23448,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23522,7 +23462,7 @@
         <v>1.414501209603441</v>
       </c>
       <c r="D441" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E441">
         <v>0.9219355330393615</v>
@@ -23558,7 +23498,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23572,7 +23512,7 @@
         <v>0.3964539049027813</v>
       </c>
       <c r="D442" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E442">
         <v>0.9417865782881711</v>
@@ -23608,7 +23548,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23622,7 +23562,7 @@
         <v>0.4029249720655423</v>
       </c>
       <c r="D443" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E443">
         <v>0.9417865782881711</v>
@@ -23658,7 +23598,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23672,7 +23612,7 @@
         <v>1.374244075534095</v>
       </c>
       <c r="D444" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E444">
         <v>0.8269425846185072</v>
@@ -23708,7 +23648,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23722,7 +23662,7 @@
         <v>0.3063097844755669</v>
       </c>
       <c r="D445" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E445">
         <v>0.873462183832336</v>
@@ -23758,7 +23698,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23772,7 +23712,7 @@
         <v>0.3231397114429218</v>
       </c>
       <c r="D446" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E446">
         <v>0.873462183832336</v>
@@ -23808,7 +23748,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23822,7 +23762,7 @@
         <v>1.297276604707491</v>
       </c>
       <c r="D447" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E447">
         <v>0.7916599773381927</v>
@@ -23858,7 +23798,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23872,7 +23812,7 @@
         <v>0.233440118808713</v>
       </c>
       <c r="D448" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E448">
         <v>0.818230896896579</v>
@@ -23908,7 +23848,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23922,7 +23862,7 @@
         <v>0.2586438215372961</v>
       </c>
       <c r="D449" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E449">
         <v>0.818230896896579</v>
@@ -23958,7 +23898,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24008,7 +23948,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24022,7 +23962,7 @@
         <v>1.228322830557575</v>
       </c>
       <c r="D451" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E451">
         <v>0.7235042792779742</v>
@@ -24058,7 +23998,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24072,7 +24012,7 @@
         <v>0.1681574946714077</v>
       </c>
       <c r="D452" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E452">
         <v>0.7687501793352967</v>
@@ -24108,7 +24048,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24122,7 +24062,7 @@
         <v>0.2008631126431526</v>
       </c>
       <c r="D453" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E453">
         <v>0.7687501793352967</v>
@@ -24158,7 +24098,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24172,7 +24112,7 @@
         <v>1.23967353577152</v>
       </c>
       <c r="D454" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E454">
         <v>1.163072722956397</v>
@@ -24208,7 +24148,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24222,7 +24162,7 @@
         <v>1.225596128630588</v>
       </c>
       <c r="D455" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E455">
         <v>0.6905047055753135</v>
@@ -24258,7 +24198,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24272,7 +24212,7 @@
         <v>0.136549003700944</v>
       </c>
       <c r="D456" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E456">
         <v>0.7447926433919125</v>
@@ -24308,7 +24248,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24322,7 +24262,7 @@
         <v>0.172886893251202</v>
       </c>
       <c r="D457" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E457">
         <v>0.7447926433919125</v>
@@ -24358,7 +24298,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24408,7 +24348,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24422,7 +24362,7 @@
         <v>1.220200273962068</v>
       </c>
       <c r="D459" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E459">
         <v>0.6852080850156392</v>
@@ -24458,7 +24398,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24472,7 +24412,7 @@
         <v>0.1314756598861742</v>
       </c>
       <c r="D460" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E460">
         <v>0.7409473216741169</v>
@@ -24508,7 +24448,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24522,7 +24462,7 @@
         <v>0.1683965498259044</v>
       </c>
       <c r="D461" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E461">
         <v>0.7409473216741169</v>
@@ -24558,7 +24498,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24572,7 +24512,7 @@
         <v>1.216624069904026</v>
       </c>
       <c r="D462" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E462">
         <v>1.236624069904027</v>
@@ -24608,7 +24548,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24622,7 +24562,7 @@
         <v>1.283513715629472</v>
       </c>
       <c r="D463" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E463">
         <v>1.236624069904027</v>
@@ -24658,7 +24598,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24672,7 +24612,7 @@
         <v>1.245299916107382</v>
       </c>
       <c r="D464" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E464">
         <v>0.7098461245467869</v>
@@ -24708,7 +24648,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24722,7 +24662,7 @@
         <v>0.155075093535447</v>
       </c>
       <c r="D465" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E465">
         <v>0.7588344229730764</v>
@@ -24758,7 +24698,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24772,7 +24712,7 @@
         <v>0.1892840681169474</v>
       </c>
       <c r="D466" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E466">
         <v>0.7588344229730764</v>
@@ -24808,7 +24748,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24822,7 +24762,7 @@
         <v>1.346682022872791</v>
       </c>
       <c r="D467" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E467">
         <v>1.156906845444727</v>
@@ -24858,7 +24798,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24872,7 +24812,7 @@
         <v>1.297477194708015</v>
       </c>
       <c r="D468" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E468">
         <v>1.156906845444727</v>
@@ -24908,7 +24848,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24922,7 +24862,7 @@
         <v>1.297810076779093</v>
       </c>
       <c r="D469" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E469">
         <v>0.761390581114191</v>
@@ -24958,7 +24898,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24972,7 +24912,7 @@
         <v>0.2044467158681593</v>
       </c>
       <c r="D470" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E470">
         <v>0.7962554570149853</v>
@@ -25008,7 +24948,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25022,7 +24962,7 @@
         <v>0.2329821788368545</v>
       </c>
       <c r="D471" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E471">
         <v>0.7962554570149853</v>
@@ -25058,7 +24998,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25072,7 +25012,7 @@
         <v>1.375532432988972</v>
       </c>
       <c r="D472" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E472">
         <v>1.038262852606697</v>
@@ -25108,7 +25048,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25122,7 +25062,7 @@
         <v>1.326689743863311</v>
       </c>
       <c r="D473" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E473">
         <v>1.038262852606697</v>
@@ -25158,7 +25098,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25172,7 +25112,7 @@
         <v>1.316058735434172</v>
       </c>
       <c r="D474" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E474">
         <v>0.7793036322537743</v>
@@ -25208,7 +25148,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25222,7 +25162,7 @@
         <v>0.221604650097877</v>
       </c>
       <c r="D475" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E475">
         <v>0.8092602482404443</v>
@@ -25258,7 +25198,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25272,7 +25212,7 @@
         <v>0.2481684189130346</v>
       </c>
       <c r="D476" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E476">
         <v>0.8092602482404443</v>
@@ -25308,7 +25248,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25322,7 +25262,7 @@
         <v>1.385558707514407</v>
       </c>
       <c r="D477" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E477">
         <v>1.0151454476213</v>
@@ -25358,7 +25298,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25372,7 +25312,7 @@
         <v>1.336841871207057</v>
       </c>
       <c r="D478" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E478">
         <v>1.0151454476213</v>
@@ -25408,7 +25348,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25422,7 +25362,7 @@
         <v>1.357255810174356</v>
       </c>
       <c r="D479" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E479">
         <v>0.8197430596424145</v>
@@ -25458,7 +25398,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25472,7 +25412,7 @@
         <v>0.2603393709455446</v>
       </c>
       <c r="D480" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E480">
         <v>0.8673754583787305</v>
@@ -25508,7 +25448,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25522,7 +25462,7 @@
         <v>0.2824519615703833</v>
       </c>
       <c r="D481" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E481">
         <v>0.8673754583787305</v>
@@ -25558,7 +25498,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25572,7 +25512,7 @@
         <v>1.408193422141772</v>
       </c>
       <c r="D482" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E482">
         <v>1.092946268617976</v>
@@ -25608,7 +25548,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25622,7 +25562,7 @@
         <v>1.359760703591251</v>
       </c>
       <c r="D483" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E483">
         <v>1.092946268617976</v>
@@ -25658,7 +25598,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25672,7 +25612,7 @@
         <v>1.400693800028334</v>
       </c>
       <c r="D484" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E484">
         <v>0.8623821899128705</v>
@@ -25708,7 +25648,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25722,7 +25662,7 @@
         <v>0.3011810671530766</v>
       </c>
       <c r="D485" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E485">
         <v>0.898730697031946</v>
@@ -25758,7 +25698,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25772,7 +25712,7 @@
         <v>0.3186003577247281</v>
       </c>
       <c r="D486" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E486">
         <v>0.898730697031946</v>
@@ -25808,7 +25748,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25822,7 +25762,7 @@
         <v>1.432059352199475</v>
       </c>
       <c r="D487" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E487">
         <v>0.9910848179499889</v>
@@ -25858,7 +25798,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25872,7 +25812,7 @@
         <v>1.383926205992774</v>
       </c>
       <c r="D488" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E488">
         <v>0.9910848179499889</v>
@@ -25908,7 +25848,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25922,7 +25862,7 @@
         <v>1.389878787820437</v>
       </c>
       <c r="D489" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E489">
         <v>0.851766074481211</v>
@@ -25958,7 +25898,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25972,7 +25912,7 @@
         <v>0.291012469467951</v>
       </c>
       <c r="D490" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E490">
         <v>0.8909239985646367</v>
@@ -26008,7 +25948,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26022,7 +25962,7 @@
         <v>0.3096002785999952</v>
       </c>
       <c r="D491" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E491">
         <v>0.8909239985646367</v>
@@ -26058,7 +25998,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26072,7 +26012,7 @@
         <v>1.426117311009389</v>
       </c>
       <c r="D492" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E492">
         <v>1.145927272692262</v>
@@ -26108,7 +26048,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26122,7 +26062,7 @@
         <v>1.377909578511599</v>
       </c>
       <c r="D493" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E493">
         <v>1.145927272692262</v>
@@ -26158,7 +26098,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26172,7 +26112,7 @@
         <v>1.390470377742177</v>
       </c>
       <c r="D494" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E494">
         <v>0.8523467845882973</v>
@@ -26208,7 +26148,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26222,7 +26162,7 @@
         <v>0.2915686999920695</v>
       </c>
       <c r="D495" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E495">
         <v>0.8913510312897541</v>
@@ -26258,7 +26198,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26272,7 +26212,7 @@
         <v>0.3100925902130296</v>
       </c>
       <c r="D496" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E496">
         <v>0.8913510312897541</v>
@@ -26308,7 +26248,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26322,7 +26262,7 @@
         <v>1.426442345472138</v>
       </c>
       <c r="D497" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E497">
         <v>1.04260947236648</v>
@@ -26358,7 +26298,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26372,7 +26312,7 @@
         <v>1.4090266167915</v>
       </c>
       <c r="D498" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E498">
         <v>0.8705617594711974</v>
@@ -26408,7 +26348,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26422,7 +26362,7 @@
         <v>0.3090158305005142</v>
       </c>
       <c r="D499" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E499">
         <v>0.9047456498219102</v>
@@ -26458,7 +26398,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26472,7 +26412,7 @@
         <v>0.3255347937437314</v>
       </c>
       <c r="D500" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E500">
         <v>0.9047456498219102</v>
@@ -26508,7 +26448,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26522,7 +26462,7 @@
         <v>1.436637612444065</v>
       </c>
       <c r="D501" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E501">
         <v>1.0174159700749</v>
@@ -26558,7 +26498,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26572,7 +26512,7 @@
         <v>1.481023111428944</v>
       </c>
       <c r="D502" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E502">
         <v>0.9412341806440443</v>
@@ -26608,7 +26548,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26622,7 +26562,7 @@
         <v>0.3767090863780185</v>
       </c>
       <c r="D503" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E503">
         <v>0.9692419169592172</v>
@@ -26658,7 +26598,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26672,7 +26612,7 @@
         <v>0.3854491180167301</v>
       </c>
       <c r="D504" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E504">
         <v>0.9692419169592172</v>
@@ -26708,7 +26648,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26722,7 +26662,7 @@
         <v>1.476194307198891</v>
       </c>
       <c r="D505" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E505">
         <v>1.037981948597929</v>
@@ -26758,7 +26698,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26772,7 +26712,7 @@
         <v>1.566896676462016</v>
       </c>
       <c r="D506" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E506">
         <v>1.019149230451688</v>
@@ -26808,7 +26748,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26822,7 +26762,7 @@
         <v>0.4887054182244546</v>
       </c>
       <c r="D507" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E507">
         <v>1.141981249108951</v>
@@ -26858,7 +26798,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26872,7 +26812,7 @@
         <v>0.4845754557390034</v>
       </c>
       <c r="D508" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E508">
         <v>1.141981249108951</v>
@@ -26908,7 +26848,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26922,7 +26862,7 @@
         <v>1.575427906313638</v>
       </c>
       <c r="D509" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E509">
         <v>0.9905476528404038</v>
@@ -26958,7 +26898,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26972,7 +26912,7 @@
         <v>1.651922146792429</v>
       </c>
       <c r="D510" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E510">
         <v>1.103977882563743</v>
@@ -27008,7 +26948,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27022,7 +26962,7 @@
         <v>0.5692040695326464</v>
       </c>
       <c r="D511" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E511">
         <v>1.20122353283454</v>
@@ -27058,7 +26998,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27072,7 +27012,7 @@
         <v>0.5558236507843963</v>
       </c>
       <c r="D512" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E512">
         <v>1.20122353283454</v>
@@ -27108,7 +27048,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27122,7 +27062,7 @@
         <v>1.619515187225704</v>
       </c>
       <c r="D513" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E513">
         <v>1.044672662888699</v>
@@ -27158,7 +27098,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27172,7 +27112,7 @@
         <v>1.713538754440068</v>
       </c>
       <c r="D514" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E514">
         <v>1.21890599807297</v>
@@ -27208,7 +27148,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27222,7 +27162,7 @@
         <v>0.6782657847142568</v>
       </c>
       <c r="D515" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E515">
         <v>1.281486555498756</v>
@@ -27258,7 +27198,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27272,7 +27212,7 @@
         <v>0.6523526016297332</v>
       </c>
       <c r="D516" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E516">
         <v>1.281486555498756</v>
@@ -27308,7 +27248,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27322,7 +27262,7 @@
         <v>1.849941600908833</v>
       </c>
       <c r="D517" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E517">
         <v>1.239941600908833</v>
@@ -27358,7 +27298,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27372,7 +27312,7 @@
         <v>0.8068113243587849</v>
       </c>
       <c r="D518" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E518">
         <v>1.376088529662578</v>
@@ -27408,7 +27348,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27422,7 +27362,7 @@
         <v>0.7661264044446945</v>
       </c>
       <c r="D519" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E519">
         <v>1.376088529662578</v>
@@ -27458,7 +27398,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27472,7 +27412,7 @@
         <v>2.41237924775196</v>
       </c>
       <c r="D520" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E520">
         <v>1.720876564407629</v>
@@ -27508,7 +27448,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27522,7 +27462,7 @@
         <v>1.615923807921956</v>
       </c>
       <c r="D521" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E521">
         <v>1.035548815721295</v>
@@ -27558,7 +27498,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27569,46 +27509,46 @@
         <v>69</v>
       </c>
       <c r="C522">
-        <v>-1.152815314629065</v>
+        <v>-1.484070927407007</v>
       </c>
       <c r="D522" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E522">
-        <v>-0.79399315370196</v>
+        <v>-1.906588603387449</v>
       </c>
       <c r="F522">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G522">
-        <v>0.009592815314629063</v>
+        <v>0.009364070927407006</v>
       </c>
       <c r="H522">
-        <v>0.009173993153701961</v>
+        <v>0.009866588603387448</v>
       </c>
       <c r="I522">
-        <v>0.3588221609271045</v>
+        <v>0.4225176759804423</v>
       </c>
       <c r="J522">
-        <v>1.767373458759561</v>
+        <v>2.102353072638375</v>
       </c>
       <c r="K522">
-        <v>3.04</v>
+        <v>2.58</v>
       </c>
       <c r="L522">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
       <c r="M522">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N522">
-        <v>4.19</v>
+        <v>3.98</v>
       </c>
       <c r="O522">
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27619,946 +27559,46 @@
         <v>69</v>
       </c>
       <c r="C523">
-        <v>-1.228488383499212</v>
+        <v>-1.073545579884814</v>
       </c>
       <c r="D523" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E523">
-        <v>-0.8641898820617673</v>
+        <v>-1.461057218479642</v>
       </c>
       <c r="F523">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.009668488383499211</v>
+        <v>0.008953545579884814</v>
       </c>
       <c r="H523">
-        <v>0.009244189882061769</v>
+        <v>0.009421057218479642</v>
       </c>
       <c r="I523">
-        <v>0.3642985014374442</v>
+        <v>0.3875116385948285</v>
       </c>
       <c r="J523">
-        <v>1.79226591562474</v>
+        <v>1.943234720885587</v>
       </c>
       <c r="K523">
-        <v>3.04</v>
+        <v>2.58</v>
       </c>
       <c r="L523">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
       <c r="M523">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N523">
-        <v>4.19</v>
+        <v>3.98</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="524" spans="1:16">
-      <c r="A524" s="1">
-        <v>0</v>
-      </c>
-      <c r="B524" t="s">
-        <v>69</v>
-      </c>
-      <c r="C524">
-        <v>-1.29306060430628</v>
-      </c>
-      <c r="D524" t="s">
-        <v>160</v>
-      </c>
-      <c r="E524">
-        <v>-0.9240891132051665</v>
-      </c>
-      <c r="F524">
-        <v>1</v>
-      </c>
-      <c r="G524">
-        <v>0.00973306060430628</v>
-      </c>
-      <c r="H524">
-        <v>0.009304089113205167</v>
-      </c>
-      <c r="I524">
-        <v>0.3689714911011137</v>
-      </c>
-      <c r="J524">
-        <v>1.813506777732329</v>
-      </c>
-      <c r="K524">
-        <v>3.04</v>
-      </c>
-      <c r="L524">
-        <v>4.22</v>
-      </c>
-      <c r="M524">
-        <v>2.82</v>
-      </c>
-      <c r="N524">
-        <v>4.19</v>
-      </c>
-      <c r="O524">
-        <v>1</v>
-      </c>
-      <c r="P524" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="525" spans="1:16">
-      <c r="A525" s="1">
-        <v>0</v>
-      </c>
-      <c r="B525" t="s">
-        <v>69</v>
-      </c>
-      <c r="C525">
-        <v>-1.362823987486787</v>
-      </c>
-      <c r="D525" t="s">
-        <v>160</v>
-      </c>
-      <c r="E525">
-        <v>-0.988803830497611</v>
-      </c>
-      <c r="F525">
-        <v>1</v>
-      </c>
-      <c r="G525">
-        <v>0.009802823987486785</v>
-      </c>
-      <c r="H525">
-        <v>0.009368803830497612</v>
-      </c>
-      <c r="I525">
-        <v>0.3740201569891761</v>
-      </c>
-      <c r="J525">
-        <v>1.836455259041706</v>
-      </c>
-      <c r="K525">
-        <v>3.04</v>
-      </c>
-      <c r="L525">
-        <v>4.22</v>
-      </c>
-      <c r="M525">
-        <v>2.82</v>
-      </c>
-      <c r="N525">
-        <v>4.19</v>
-      </c>
-      <c r="O525">
-        <v>1</v>
-      </c>
-      <c r="P525" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="526" spans="1:16">
-      <c r="A526" s="1">
-        <v>0</v>
-      </c>
-      <c r="B526" t="s">
-        <v>69</v>
-      </c>
-      <c r="C526">
-        <v>-1.446771238461646</v>
-      </c>
-      <c r="D526" t="s">
-        <v>160</v>
-      </c>
-      <c r="E526">
-        <v>-1.06667595146771</v>
-      </c>
-      <c r="F526">
-        <v>1</v>
-      </c>
-      <c r="G526">
-        <v>0.009886771238461645</v>
-      </c>
-      <c r="H526">
-        <v>0.009446675951467712</v>
-      </c>
-      <c r="I526">
-        <v>0.380095286993936</v>
-      </c>
-      <c r="J526">
-        <v>1.864069486336068</v>
-      </c>
-      <c r="K526">
-        <v>3.04</v>
-      </c>
-      <c r="L526">
-        <v>4.22</v>
-      </c>
-      <c r="M526">
-        <v>2.82</v>
-      </c>
-      <c r="N526">
-        <v>4.19</v>
-      </c>
-      <c r="O526">
-        <v>1</v>
-      </c>
-      <c r="P526" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="527" spans="1:16">
-      <c r="A527" s="1">
-        <v>0</v>
-      </c>
-      <c r="B527" t="s">
-        <v>69</v>
-      </c>
-      <c r="C527">
-        <v>-1.55778001938641</v>
-      </c>
-      <c r="D527" t="s">
-        <v>160</v>
-      </c>
-      <c r="E527">
-        <v>-1.169651202193972</v>
-      </c>
-      <c r="F527">
-        <v>1</v>
-      </c>
-      <c r="G527">
-        <v>0.00999778001938641</v>
-      </c>
-      <c r="H527">
-        <v>0.009549651202193973</v>
-      </c>
-      <c r="I527">
-        <v>0.3881288171924382</v>
-      </c>
-      <c r="J527">
-        <v>1.900585532692898</v>
-      </c>
-      <c r="K527">
-        <v>3.04</v>
-      </c>
-      <c r="L527">
-        <v>4.22</v>
-      </c>
-      <c r="M527">
-        <v>2.82</v>
-      </c>
-      <c r="N527">
-        <v>4.19</v>
-      </c>
-      <c r="O527">
-        <v>1</v>
-      </c>
-      <c r="P527" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="528" spans="1:16">
-      <c r="A528" s="1">
-        <v>0</v>
-      </c>
-      <c r="B528" t="s">
-        <v>69</v>
-      </c>
-      <c r="C528">
-        <v>-1.675411230839367</v>
-      </c>
-      <c r="D528" t="s">
-        <v>160</v>
-      </c>
-      <c r="E528">
-        <v>-1.278769628607569</v>
-      </c>
-      <c r="F528">
-        <v>1</v>
-      </c>
-      <c r="G528">
-        <v>0.01011541123083937</v>
-      </c>
-      <c r="H528">
-        <v>0.00965876962860757</v>
-      </c>
-      <c r="I528">
-        <v>0.3966416022317976</v>
-      </c>
-      <c r="J528">
-        <v>1.939280010144528</v>
-      </c>
-      <c r="K528">
-        <v>3.04</v>
-      </c>
-      <c r="L528">
-        <v>4.22</v>
-      </c>
-      <c r="M528">
-        <v>2.82</v>
-      </c>
-      <c r="N528">
-        <v>4.19</v>
-      </c>
-      <c r="O528">
-        <v>1</v>
-      </c>
-      <c r="P528" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="529" spans="1:16">
-      <c r="A529" s="1">
-        <v>0</v>
-      </c>
-      <c r="B529" t="s">
-        <v>69</v>
-      </c>
-      <c r="C529">
-        <v>-1.976515141630071</v>
-      </c>
-      <c r="D529" t="s">
-        <v>160</v>
-      </c>
-      <c r="E529">
-        <v>-1.558083124801579</v>
-      </c>
-      <c r="F529">
-        <v>1</v>
-      </c>
-      <c r="G529">
-        <v>0.01041651514163007</v>
-      </c>
-      <c r="H529">
-        <v>0.009938083124801579</v>
-      </c>
-      <c r="I529">
-        <v>0.4184320168284925</v>
-      </c>
-      <c r="J529">
-        <v>2.038327349220418</v>
-      </c>
-      <c r="K529">
-        <v>3.04</v>
-      </c>
-      <c r="L529">
-        <v>4.22</v>
-      </c>
-      <c r="M529">
-        <v>2.82</v>
-      </c>
-      <c r="N529">
-        <v>4.19</v>
-      </c>
-      <c r="O529">
-        <v>1</v>
-      </c>
-      <c r="P529" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="530" spans="1:16">
-      <c r="A530" s="1">
-        <v>0</v>
-      </c>
-      <c r="B530" t="s">
-        <v>69</v>
-      </c>
-      <c r="C530">
-        <v>-2.248289351143409</v>
-      </c>
-      <c r="D530" t="s">
-        <v>160</v>
-      </c>
-      <c r="E530">
-        <v>-1.810189463889609</v>
-      </c>
-      <c r="F530">
-        <v>1</v>
-      </c>
-      <c r="G530">
-        <v>0.01068828935114341</v>
-      </c>
-      <c r="H530">
-        <v>0.01019018946388961</v>
-      </c>
-      <c r="I530">
-        <v>0.4380998872538004</v>
-      </c>
-      <c r="J530">
-        <v>2.127726760244542</v>
-      </c>
-      <c r="K530">
-        <v>3.04</v>
-      </c>
-      <c r="L530">
-        <v>4.22</v>
-      </c>
-      <c r="M530">
-        <v>2.82</v>
-      </c>
-      <c r="N530">
-        <v>4.19</v>
-      </c>
-      <c r="O530">
-        <v>1</v>
-      </c>
-      <c r="P530" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="531" spans="1:16">
-      <c r="A531" s="1">
-        <v>0</v>
-      </c>
-      <c r="B531" t="s">
-        <v>69</v>
-      </c>
-      <c r="C531">
-        <v>-2.353293759761697</v>
-      </c>
-      <c r="D531" t="s">
-        <v>160</v>
-      </c>
-      <c r="E531">
-        <v>-1.907594869252626</v>
-      </c>
-      <c r="F531">
-        <v>1</v>
-      </c>
-      <c r="G531">
-        <v>0.0107932937597617</v>
-      </c>
-      <c r="H531">
-        <v>0.01028759486925263</v>
-      </c>
-      <c r="I531">
-        <v>0.4456988905090711</v>
-      </c>
-      <c r="J531">
-        <v>2.162267684132137</v>
-      </c>
-      <c r="K531">
-        <v>3.04</v>
-      </c>
-      <c r="L531">
-        <v>4.22</v>
-      </c>
-      <c r="M531">
-        <v>2.82</v>
-      </c>
-      <c r="N531">
-        <v>4.19</v>
-      </c>
-      <c r="O531">
-        <v>1</v>
-      </c>
-      <c r="P531" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="532" spans="1:16">
-      <c r="A532" s="1">
-        <v>0</v>
-      </c>
-      <c r="B532" t="s">
-        <v>69</v>
-      </c>
-      <c r="C532">
-        <v>-2.526299327422145</v>
-      </c>
-      <c r="D532" t="s">
-        <v>160</v>
-      </c>
-      <c r="E532">
-        <v>-2.068080297148173</v>
-      </c>
-      <c r="F532">
-        <v>1</v>
-      </c>
-      <c r="G532">
-        <v>0.01096629932742215</v>
-      </c>
-      <c r="H532">
-        <v>0.01044808029714817</v>
-      </c>
-      <c r="I532">
-        <v>0.4582190302739724</v>
-      </c>
-      <c r="J532">
-        <v>2.219177410336232</v>
-      </c>
-      <c r="K532">
-        <v>3.04</v>
-      </c>
-      <c r="L532">
-        <v>4.22</v>
-      </c>
-      <c r="M532">
-        <v>2.82</v>
-      </c>
-      <c r="N532">
-        <v>4.19</v>
-      </c>
-      <c r="O532">
-        <v>1</v>
-      </c>
-      <c r="P532" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="533" spans="1:16">
-      <c r="A533" s="1">
-        <v>0</v>
-      </c>
-      <c r="B533" t="s">
-        <v>69</v>
-      </c>
-      <c r="C533">
-        <v>-2.743107768168906</v>
-      </c>
-      <c r="D533" t="s">
-        <v>160</v>
-      </c>
-      <c r="E533">
-        <v>-2.269198653367208</v>
-      </c>
-      <c r="F533">
-        <v>1</v>
-      </c>
-      <c r="G533">
-        <v>0.01118310776816891</v>
-      </c>
-      <c r="H533">
-        <v>0.01064919865336721</v>
-      </c>
-      <c r="I533">
-        <v>0.4739091148016978</v>
-      </c>
-      <c r="J533">
-        <v>2.29049597637135</v>
-      </c>
-      <c r="K533">
-        <v>3.04</v>
-      </c>
-      <c r="L533">
-        <v>4.22</v>
-      </c>
-      <c r="M533">
-        <v>2.82</v>
-      </c>
-      <c r="N533">
-        <v>4.19</v>
-      </c>
-      <c r="O533">
-        <v>1</v>
-      </c>
-      <c r="P533" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="534" spans="1:16">
-      <c r="A534" s="1">
-        <v>0</v>
-      </c>
-      <c r="B534" t="s">
-        <v>69</v>
-      </c>
-      <c r="C534">
-        <v>-2.900537245558254</v>
-      </c>
-      <c r="D534" t="s">
-        <v>160</v>
-      </c>
-      <c r="E534">
-        <v>-2.415235208050748</v>
-      </c>
-      <c r="F534">
-        <v>1</v>
-      </c>
-      <c r="G534">
-        <v>0.01134053724555825</v>
-      </c>
-      <c r="H534">
-        <v>0.01079523520805075</v>
-      </c>
-      <c r="I534">
-        <v>0.4853020375075054</v>
-      </c>
-      <c r="J534">
-        <v>2.342281988670478</v>
-      </c>
-      <c r="K534">
-        <v>3.04</v>
-      </c>
-      <c r="L534">
-        <v>4.22</v>
-      </c>
-      <c r="M534">
-        <v>2.82</v>
-      </c>
-      <c r="N534">
-        <v>4.19</v>
-      </c>
-      <c r="O534">
-        <v>1</v>
-      </c>
-      <c r="P534" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="535" spans="1:16">
-      <c r="A535" s="1">
-        <v>0</v>
-      </c>
-      <c r="B535" t="s">
-        <v>69</v>
-      </c>
-      <c r="C535">
-        <v>-3.035837006849226</v>
-      </c>
-      <c r="D535" t="s">
-        <v>160</v>
-      </c>
-      <c r="E535">
-        <v>-2.540743539248294</v>
-      </c>
-      <c r="F535">
-        <v>1</v>
-      </c>
-      <c r="G535">
-        <v>0.01147583700684923</v>
-      </c>
-      <c r="H535">
-        <v>0.0109207435392483</v>
-      </c>
-      <c r="I535">
-        <v>0.495093467600932</v>
-      </c>
-      <c r="J535">
-        <v>2.38678848909514</v>
-      </c>
-      <c r="K535">
-        <v>3.04</v>
-      </c>
-      <c r="L535">
-        <v>4.22</v>
-      </c>
-      <c r="M535">
-        <v>2.82</v>
-      </c>
-      <c r="N535">
-        <v>4.19</v>
-      </c>
-      <c r="O535">
-        <v>1</v>
-      </c>
-      <c r="P535" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="536" spans="1:16">
-      <c r="A536" s="1">
-        <v>0</v>
-      </c>
-      <c r="B536" t="s">
-        <v>69</v>
-      </c>
-      <c r="C536">
-        <v>-3.067435364143786</v>
-      </c>
-      <c r="D536" t="s">
-        <v>160</v>
-      </c>
-      <c r="E536">
-        <v>-2.57005517331759</v>
-      </c>
-      <c r="F536">
-        <v>1</v>
-      </c>
-      <c r="G536">
-        <v>0.01150743536414378</v>
-      </c>
-      <c r="H536">
-        <v>0.01095005517331759</v>
-      </c>
-      <c r="I536">
-        <v>0.4973801908261954</v>
-      </c>
-      <c r="J536">
-        <v>2.397182685573614</v>
-      </c>
-      <c r="K536">
-        <v>3.04</v>
-      </c>
-      <c r="L536">
-        <v>4.22</v>
-      </c>
-      <c r="M536">
-        <v>2.82</v>
-      </c>
-      <c r="N536">
-        <v>4.19</v>
-      </c>
-      <c r="O536">
-        <v>1</v>
-      </c>
-      <c r="P536" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="537" spans="1:16">
-      <c r="A537" s="1">
-        <v>0</v>
-      </c>
-      <c r="B537" t="s">
-        <v>69</v>
-      </c>
-      <c r="C537">
-        <v>-3.089535962632947</v>
-      </c>
-      <c r="D537" t="s">
-        <v>160</v>
-      </c>
-      <c r="E537">
-        <v>-2.590556386389772</v>
-      </c>
-      <c r="F537">
-        <v>1</v>
-      </c>
-      <c r="G537">
-        <v>0.01152953596263295</v>
-      </c>
-      <c r="H537">
-        <v>0.01097055638638977</v>
-      </c>
-      <c r="I537">
-        <v>0.4989795762431752</v>
-      </c>
-      <c r="J537">
-        <v>2.404452619287154</v>
-      </c>
-      <c r="K537">
-        <v>3.04</v>
-      </c>
-      <c r="L537">
-        <v>4.22</v>
-      </c>
-      <c r="M537">
-        <v>2.82</v>
-      </c>
-      <c r="N537">
-        <v>4.19</v>
-      </c>
-      <c r="O537">
-        <v>1</v>
-      </c>
-      <c r="P537" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="538" spans="1:16">
-      <c r="A538" s="1">
-        <v>0</v>
-      </c>
-      <c r="B538" t="s">
-        <v>69</v>
-      </c>
-      <c r="C538">
-        <v>-3.034510811938273</v>
-      </c>
-      <c r="D538" t="s">
-        <v>160</v>
-      </c>
-      <c r="E538">
-        <v>-2.539513318969055</v>
-      </c>
-      <c r="F538">
-        <v>1</v>
-      </c>
-      <c r="G538">
-        <v>0.01147451081193827</v>
-      </c>
-      <c r="H538">
-        <v>0.01091951331896906</v>
-      </c>
-      <c r="I538">
-        <v>0.494997492969218</v>
-      </c>
-      <c r="J538">
-        <v>2.386352240769169</v>
-      </c>
-      <c r="K538">
-        <v>3.04</v>
-      </c>
-      <c r="L538">
-        <v>4.22</v>
-      </c>
-      <c r="M538">
-        <v>2.82</v>
-      </c>
-      <c r="N538">
-        <v>4.19</v>
-      </c>
-      <c r="O538">
-        <v>1</v>
-      </c>
-      <c r="P538" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="539" spans="1:16">
-      <c r="A539" s="1">
-        <v>0</v>
-      </c>
-      <c r="B539" t="s">
-        <v>69</v>
-      </c>
-      <c r="C539">
-        <v>-2.988299063792063</v>
-      </c>
-      <c r="D539" t="s">
-        <v>160</v>
-      </c>
-      <c r="E539">
-        <v>-2.496645842070268</v>
-      </c>
-      <c r="F539">
-        <v>1</v>
-      </c>
-      <c r="G539">
-        <v>0.01142829906379206</v>
-      </c>
-      <c r="H539">
-        <v>0.01087664584207027</v>
-      </c>
-      <c r="I539">
-        <v>0.491653221721795</v>
-      </c>
-      <c r="J539">
-        <v>2.371151007826336</v>
-      </c>
-      <c r="K539">
-        <v>3.04</v>
-      </c>
-      <c r="L539">
-        <v>4.22</v>
-      </c>
-      <c r="M539">
-        <v>2.82</v>
-      </c>
-      <c r="N539">
-        <v>4.19</v>
-      </c>
-      <c r="O539">
-        <v>1</v>
-      </c>
-      <c r="P539" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="540" spans="1:16">
-      <c r="A540" s="1">
-        <v>0</v>
-      </c>
-      <c r="B540" t="s">
-        <v>70</v>
-      </c>
-      <c r="C540">
-        <v>-1.484070927407007</v>
-      </c>
-      <c r="D540" t="s">
-        <v>161</v>
-      </c>
-      <c r="E540">
-        <v>-1.906588603387449</v>
-      </c>
-      <c r="F540">
-        <v>-1</v>
-      </c>
-      <c r="G540">
-        <v>0.009364070927407006</v>
-      </c>
-      <c r="H540">
-        <v>0.009866588603387448</v>
-      </c>
-      <c r="I540">
-        <v>0.4225176759804423</v>
-      </c>
-      <c r="J540">
-        <v>2.102353072638375</v>
-      </c>
-      <c r="K540">
-        <v>2.58</v>
-      </c>
-      <c r="L540">
-        <v>3.94</v>
-      </c>
-      <c r="M540">
-        <v>2.8</v>
-      </c>
-      <c r="N540">
-        <v>3.98</v>
-      </c>
-      <c r="O540">
-        <v>1</v>
-      </c>
-      <c r="P540" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="541" spans="1:16">
-      <c r="A541" s="1">
-        <v>0</v>
-      </c>
-      <c r="B541" t="s">
-        <v>70</v>
-      </c>
-      <c r="C541">
-        <v>-1.073545579884814</v>
-      </c>
-      <c r="D541" t="s">
-        <v>161</v>
-      </c>
-      <c r="E541">
-        <v>-1.461057218479642</v>
-      </c>
-      <c r="F541">
-        <v>-1</v>
-      </c>
-      <c r="G541">
-        <v>0.008953545579884814</v>
-      </c>
-      <c r="H541">
-        <v>0.009421057218479642</v>
-      </c>
-      <c r="I541">
-        <v>0.3875116385948285</v>
-      </c>
-      <c r="J541">
-        <v>1.943234720885587</v>
-      </c>
-      <c r="K541">
-        <v>2.58</v>
-      </c>
-      <c r="L541">
-        <v>3.94</v>
-      </c>
-      <c r="M541">
-        <v>2.8</v>
-      </c>
-      <c r="N541">
-        <v>3.98</v>
-      </c>
-      <c r="O541">
-        <v>1</v>
-      </c>
-      <c r="P541" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="373">
   <si>
     <t>trade_time</t>
   </si>
@@ -223,6 +223,12 @@
     <t>2020-11-26</t>
   </si>
   <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
     <t>2021-07-27</t>
   </si>
   <si>
@@ -493,6 +499,9 @@
     <t>2021-01-05</t>
   </si>
   <si>
+    <t>2021-08-11</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
@@ -1088,6 +1097,36 @@
   </si>
   <si>
     <t>2020-11-23</t>
+  </si>
+  <si>
+    <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
   </si>
   <si>
     <t>2021-06-02</t>
@@ -1451,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P523"/>
+  <dimension ref="A1:P533"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1512,7 +1551,7 @@
         <v>6.869727715272395</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2">
         <v>6.050137140894572</v>
@@ -1548,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1562,7 +1601,7 @@
         <v>6.844463593057311</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>6.050137140894572</v>
@@ -1598,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1612,7 +1651,7 @@
         <v>6.857637482930865</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E4">
         <v>6.039233803242143</v>
@@ -1648,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1662,7 +1701,7 @@
         <v>6.83283604847594</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E5">
         <v>6.039233803242143</v>
@@ -1698,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1712,7 +1751,7 @@
         <v>6.826153414303063</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E6">
         <v>6.01084051672589</v>
@@ -1748,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1762,7 +1801,7 @@
         <v>6.802556861010267</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E7">
         <v>6.01084051672589</v>
@@ -1798,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1812,7 +1851,7 @@
         <v>6.794839943414579</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E8">
         <v>5.98260108041714</v>
@@ -1848,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1862,7 +1901,7 @@
         <v>6.77244174258507</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9">
         <v>5.98260108041714</v>
@@ -1898,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1912,7 +1951,7 @@
         <v>6.763675289556306</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E10">
         <v>5.95449585181284</v>
@@ -1948,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1962,7 +2001,7 @@
         <v>6.742469746029192</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E11">
         <v>5.95449585181284</v>
@@ -1998,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2012,7 +2051,7 @@
         <v>6.730117010025435</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E12">
         <v>5.924231979091157</v>
@@ -2048,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2062,7 +2101,7 @@
         <v>6.710195726779869</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13">
         <v>5.924231979091157</v>
@@ -2098,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2112,7 +2151,7 @@
         <v>6.693046966006446</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E14">
         <v>5.890801090807809</v>
@@ -2148,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2162,7 +2201,7 @@
         <v>6.674544336691723</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E15">
         <v>5.890801090807809</v>
@@ -2198,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2212,7 +2251,7 @@
         <v>6.644553392998862</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E16">
         <v>5.847068118145396</v>
@@ -2248,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2262,7 +2301,7 @@
         <v>6.627906590937341</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E17">
         <v>5.847068118145396</v>
@@ -2298,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2312,7 +2351,7 @@
         <v>6.617128166636995</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E18">
         <v>5.822335218497922</v>
@@ -2348,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2362,7 +2401,7 @@
         <v>6.601530915667526</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E19">
         <v>5.822335218497922</v>
@@ -2398,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2412,7 +2451,7 @@
         <v>6.581803978417834</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E20">
         <v>5.790478795844368</v>
@@ -2448,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2462,7 +2501,7 @@
         <v>6.567558568262076</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E21">
         <v>5.790478795844368</v>
@@ -2498,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2512,7 +2551,7 @@
         <v>6.554001439910648</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E22">
         <v>5.765405624678154</v>
@@ -2548,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2562,7 +2601,7 @@
         <v>6.540820020413236</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E23">
         <v>5.765405624678154</v>
@@ -2598,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2612,7 +2651,7 @@
         <v>6.529894038726229</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E24">
         <v>5.743664840248944</v>
@@ -2648,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2662,7 +2701,7 @@
         <v>6.517635198641864</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E25">
         <v>5.743664840248944</v>
@@ -2698,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2712,7 +2751,7 @@
         <v>6.493137342079</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E26">
         <v>5.710516538114505</v>
@@ -2748,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2762,7 +2801,7 @@
         <v>6.482285164262333</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E27">
         <v>5.710516538114505</v>
@@ -2798,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2812,7 +2851,7 @@
         <v>6.444477546138163</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E28">
         <v>5.666633660577178</v>
@@ -2848,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2862,7 +2901,7 @@
         <v>6.435487556851677</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E29">
         <v>5.666633660577178</v>
@@ -2898,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2912,7 +2951,7 @@
         <v>6.395287017911711</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E30">
         <v>5.62227215259259</v>
@@ -2948,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2962,7 +3001,7 @@
         <v>6.388179528041545</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E31">
         <v>5.62227215259259</v>
@@ -2998,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3012,7 +3051,7 @@
         <v>6.391868530229962</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E32">
         <v>5.619189256879599</v>
@@ -3048,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3062,7 +3101,7 @@
         <v>6.384891864347617</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E33">
         <v>5.619189256879599</v>
@@ -3098,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3112,7 +3151,7 @@
         <v>6.396520135507044</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E34">
         <v>5.623384215382392</v>
@@ -3148,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3162,7 +3201,7 @@
         <v>6.389365454780485</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E35">
         <v>5.623384215382392</v>
@@ -3198,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3212,7 +3251,7 @@
         <v>6.403506732043612</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E36">
         <v>5.629684939713206</v>
@@ -3248,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3262,7 +3301,7 @@
         <v>6.396084677406335</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E37">
         <v>5.629684939713206</v>
@@ -3298,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3312,7 +3351,7 @@
         <v>6.390454186369448</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E38">
         <v>5.617913758755807</v>
@@ -3348,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3362,7 +3401,7 @@
         <v>6.38353164679125</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E39">
         <v>5.617913758755807</v>
@@ -3398,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3412,7 +3451,7 @@
         <v>6.385694652927858</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E40">
         <v>5.613621467365888</v>
@@ -3448,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3462,7 +3501,7 @@
         <v>6.378954258556243</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E41">
         <v>5.613621467365888</v>
@@ -3498,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3512,7 +3551,7 @@
         <v>6.398324700271503</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E42">
         <v>5.625011626534365</v>
@@ -3548,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3562,7 +3601,7 @@
         <v>6.39110095966211</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E43">
         <v>5.625011626534365</v>
@@ -3598,7 +3637,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3612,7 +3651,7 @@
         <v>6.406965992917668</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E44">
         <v>5.63280460592575</v>
@@ -3648,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3662,7 +3701,7 @@
         <v>6.399411553920818</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E45">
         <v>5.63280460592575</v>
@@ -3698,7 +3737,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3712,7 +3751,7 @@
         <v>6.400651203652978</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E46">
         <v>5.627109737736961</v>
@@ -3748,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3762,7 +3801,7 @@
         <v>6.393338428804362</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E47">
         <v>5.627109737736961</v>
@@ -3798,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3812,7 +3851,7 @@
         <v>6.421264387742685</v>
       </c>
       <c r="D48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E48">
         <v>5.645699331375265</v>
@@ -3848,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3862,7 +3901,7 @@
         <v>6.413162755599453</v>
       </c>
       <c r="D49" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E49">
         <v>5.645699331375265</v>
@@ -3898,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3912,7 +3951,7 @@
         <v>6.463467063219744</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E50">
         <v>5.68375898213827</v>
@@ -3948,7 +3987,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3962,7 +4001,7 @@
         <v>6.45375035364561</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E51">
         <v>5.68375898213827</v>
@@ -3998,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4012,7 +4051,7 @@
         <v>6.488418927255035</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E52">
         <v>5.706261328739149</v>
@@ -4048,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4062,7 +4101,7 @@
         <v>6.477747321053927</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E53">
         <v>5.706261328739149</v>
@@ -4098,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4112,7 +4151,7 @@
         <v>6.583255790923473</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E54">
         <v>5.791788084326992</v>
@@ -4148,7 +4187,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4162,7 +4201,7 @@
         <v>6.440394668218746</v>
       </c>
       <c r="D55" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E55">
         <v>5.791788084326992</v>
@@ -4198,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4212,7 +4251,7 @@
         <v>6.568954820555353</v>
       </c>
       <c r="D56" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E56">
         <v>5.791788084326992</v>
@@ -4248,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4262,7 +4301,7 @@
         <v>6.628230185262845</v>
       </c>
       <c r="D57" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E57">
         <v>5.83234735509561</v>
@@ -4298,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4312,7 +4351,7 @@
         <v>6.484920066940753</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E58">
         <v>5.83234735509561</v>
@@ -4348,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4362,7 +4401,7 @@
         <v>6.61220806502816</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E59">
         <v>5.83234735509561</v>
@@ -4398,7 +4437,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4412,7 +4451,7 @@
         <v>6.646411890511949</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E60">
         <v>5.84874416748332</v>
@@ -4448,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4462,7 +4501,7 @@
         <v>6.50292025766158</v>
       </c>
       <c r="D61" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E61">
         <v>5.84874416748332</v>
@@ -4498,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4512,7 +4551,7 @@
         <v>6.629693964585535</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E62">
         <v>5.84874416748332</v>
@@ -4548,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4562,7 +4601,7 @@
         <v>6.642559529608892</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E63">
         <v>5.84526999176043</v>
@@ -4598,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4612,7 +4651,7 @@
         <v>6.499106356268371</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E64">
         <v>5.84526999176043</v>
@@ -4648,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4662,7 +4701,7 @@
         <v>6.625989031803559</v>
       </c>
       <c r="D65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E65">
         <v>5.84526999176043</v>
@@ -4698,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4712,7 +4751,7 @@
         <v>6.645390633912061</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E66">
         <v>5.847823167354969</v>
@@ -4748,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4762,7 +4801,7 @@
         <v>6.501909196635068</v>
       </c>
       <c r="D67" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E67">
         <v>5.847823167354969</v>
@@ -4798,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4812,7 +4851,7 @@
         <v>6.628711791016923</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E68">
         <v>5.847823167354969</v>
@@ -4848,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4862,7 +4901,7 @@
         <v>6.628009372010197</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E69">
         <v>5.832148219017515</v>
@@ -4898,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4912,7 +4951,7 @@
         <v>6.611995702199492</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E70">
         <v>5.832148219017515</v>
@@ -4948,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4962,7 +5001,7 @@
         <v>6.616738911804213</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E71">
         <v>5.821984176701968</v>
@@ -4998,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5012,7 +5051,7 @@
         <v>6.601156557442321</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E72">
         <v>5.821984176701968</v>
@@ -5048,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5062,7 +5101,7 @@
         <v>6.626158243616882</v>
       </c>
       <c r="D73" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E73">
         <v>5.830478815374958</v>
@@ -5098,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5112,7 +5151,7 @@
         <v>6.610215415658166</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E74">
         <v>5.830478815374958</v>
@@ -5148,7 +5187,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5162,7 +5201,7 @@
         <v>6.650940043106316</v>
       </c>
       <c r="D75" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E75">
         <v>5.85282779261834</v>
@@ -5198,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5212,7 +5251,7 @@
         <v>6.634048826814393</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E76">
         <v>5.85282779261834</v>
@@ -5248,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5262,7 +5301,7 @@
         <v>6.655761178830648</v>
       </c>
       <c r="D77" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E77">
         <v>5.857175638812331</v>
@@ -5298,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5312,7 +5351,7 @@
         <v>6.638685459840457</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E78">
         <v>5.857175638812331</v>
@@ -5348,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5362,7 +5401,7 @@
         <v>6.682065765134389</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E79">
         <v>5.880897911319199</v>
@@ -5398,7 +5437,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5412,7 +5451,7 @@
         <v>6.663983381443721</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E80">
         <v>5.880897911319199</v>
@@ -5448,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5462,7 +5501,7 @@
         <v>6.734829447046008</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E81">
         <v>5.928481797502389</v>
@@ -5498,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5512,7 +5551,7 @@
         <v>6.714727820952732</v>
       </c>
       <c r="D82" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E82">
         <v>5.928481797502389</v>
@@ -5548,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5562,7 +5601,7 @@
         <v>6.744601630625527</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E83">
         <v>5.937294648584086</v>
@@ -5598,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5612,7 +5651,7 @@
         <v>6.72412602745683</v>
       </c>
       <c r="D84" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E84">
         <v>5.937294648584086</v>
@@ -5648,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5662,7 +5701,7 @@
         <v>6.868996803282632</v>
       </c>
       <c r="D85" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E85">
         <v>6.049477982328097</v>
@@ -5698,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5712,7 +5751,7 @@
         <v>6.723283024880476</v>
       </c>
       <c r="D86" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E86">
         <v>6.049477982328097</v>
@@ -5748,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5762,7 +5801,7 @@
         <v>6.843760652741033</v>
       </c>
       <c r="D87" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E87">
         <v>6.049477982328097</v>
@@ -5798,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5812,7 +5851,7 @@
         <v>7.461980748234559</v>
       </c>
       <c r="D88" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E88">
         <v>6.584248861136657</v>
@@ -5848,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5862,7 +5901,7 @@
         <v>7.310346997004264</v>
       </c>
       <c r="D89" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E89">
         <v>6.584248861136657</v>
@@ -5898,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5912,7 +5951,7 @@
         <v>7.414051368518428</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E90">
         <v>6.584248861136657</v>
@@ -5948,7 +5987,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5962,7 +6001,7 @@
         <v>7.503790226406835</v>
       </c>
       <c r="D91" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E91">
         <v>6.621953914663068</v>
@@ -5998,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6012,7 +6051,7 @@
         <v>7.351739076060011</v>
       </c>
       <c r="D92" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E92">
         <v>6.621953914663068</v>
@@ -6048,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6062,7 +6101,7 @@
         <v>7.454260816744011</v>
       </c>
       <c r="D93" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E93">
         <v>6.621953914663068</v>
@@ -6098,7 +6137,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6112,7 +6151,7 @@
         <v>7.442891522635139</v>
       </c>
       <c r="D94" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E94">
         <v>6.567033619414717</v>
@@ -6148,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6162,7 +6201,7 @@
         <v>7.291448346036452</v>
       </c>
       <c r="D95" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E95">
         <v>6.567033619414717</v>
@@ -6198,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6212,7 +6251,7 @@
         <v>7.39569267900684</v>
       </c>
       <c r="D96" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E96">
         <v>6.567033619414717</v>
@@ -6248,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6262,7 +6301,7 @@
         <v>7.440682840908001</v>
       </c>
       <c r="D97" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E97">
         <v>6.56504176334798</v>
@@ -6298,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6312,7 +6351,7 @@
         <v>7.289261714376473</v>
       </c>
       <c r="D98" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E98">
         <v>6.56504176334798</v>
@@ -6348,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6362,7 +6401,7 @@
         <v>7.393568522537145</v>
       </c>
       <c r="D99" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E99">
         <v>6.56504176334798</v>
@@ -6398,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6412,7 +6451,7 @@
         <v>7.424306444365878</v>
       </c>
       <c r="D100" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E100">
         <v>6.550273033022139</v>
@@ -6448,7 +6487,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6462,7 +6501,7 @@
         <v>7.377818843333573</v>
       </c>
       <c r="D101" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E101">
         <v>6.550273033022139</v>
@@ -6498,7 +6537,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6512,7 +6551,7 @@
         <v>7.534499875331724</v>
       </c>
       <c r="D102" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E102">
         <v>6.649648806039591</v>
@@ -6548,7 +6587,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6562,7 +6601,7 @@
         <v>7.483795221200893</v>
       </c>
       <c r="D103" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E103">
         <v>6.649648806039591</v>
@@ -6598,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6612,7 +6651,7 @@
         <v>7.561436426814521</v>
       </c>
       <c r="D104" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E104">
         <v>6.673941003882645</v>
@@ -6648,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6662,7 +6701,7 @@
         <v>7.509700922959722</v>
       </c>
       <c r="D105" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E105">
         <v>6.673941003882645</v>
@@ -6698,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6712,7 +6751,7 @@
         <v>7.578789061755105</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E106">
         <v>6.689590135559512</v>
@@ -6748,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6762,7 +6801,7 @@
         <v>7.526389480356823</v>
       </c>
       <c r="D107" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E107">
         <v>6.689590135559512</v>
@@ -6798,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6812,7 +6851,7 @@
         <v>6.876779630058808</v>
       </c>
       <c r="D108" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E108">
         <v>6.056496771201121</v>
@@ -6848,7 +6887,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6862,7 +6901,7 @@
         <v>6.85124563423293</v>
       </c>
       <c r="D109" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E109">
         <v>6.056496771201121</v>
@@ -6898,7 +6937,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6912,7 +6951,7 @@
         <v>6.803309666682317</v>
       </c>
       <c r="D110" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E110">
         <v>5.990239333347446</v>
@@ -6948,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6962,7 +7001,7 @@
         <v>6.780587333348385</v>
       </c>
       <c r="D111" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E111">
         <v>5.990239333347446</v>
@@ -6998,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7012,7 +7051,7 @@
         <v>6.690125588143431</v>
       </c>
       <c r="D112" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E112">
         <v>5.88816650378326</v>
@@ -7048,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7062,7 +7101,7 @@
         <v>6.671734758647093</v>
       </c>
       <c r="D113" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E113">
         <v>5.88816650378326</v>
@@ -7098,7 +7137,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7112,7 +7151,7 @@
         <v>6.546850371675455</v>
       </c>
       <c r="D114" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E114">
         <v>5.758956574788845</v>
@@ -7148,7 +7187,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7162,7 +7201,7 @@
         <v>6.533942620346777</v>
       </c>
       <c r="D115" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E115">
         <v>5.758956574788845</v>
@@ -7198,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7212,7 +7251,7 @@
         <v>6.36581543133911</v>
       </c>
       <c r="D116" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E116">
         <v>5.595693783337433</v>
@@ -7248,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7262,7 +7301,7 @@
         <v>6.359835805846931</v>
       </c>
       <c r="D117" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E117">
         <v>5.595693783337433</v>
@@ -7298,7 +7337,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7312,7 +7351,7 @@
         <v>5.655118426801266</v>
       </c>
       <c r="D118" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E118">
         <v>4.954765702705966</v>
@@ -7348,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7362,7 +7401,7 @@
         <v>5.676336856391234</v>
       </c>
       <c r="D119" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E119">
         <v>4.954765702705966</v>
@@ -7398,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7412,7 +7451,7 @@
         <v>4.385984132295935</v>
       </c>
       <c r="D120" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E120">
         <v>4.515964100132926</v>
@@ -7448,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7462,7 +7501,7 @@
         <v>5.520410496630564</v>
       </c>
       <c r="D121" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E121">
         <v>4.833282011936382</v>
@@ -7498,7 +7537,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7512,7 +7551,7 @@
         <v>5.54678413819046</v>
       </c>
       <c r="D122" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E122">
         <v>4.833282011936382</v>
@@ -7548,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7598,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7612,7 +7651,7 @@
         <v>5.300818351460203</v>
       </c>
       <c r="D124" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E124">
         <v>4.635247165543143</v>
@@ -7648,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7662,7 +7701,7 @@
         <v>5.335595685763722</v>
       </c>
       <c r="D125" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E125">
         <v>4.635247165543143</v>
@@ -7698,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7748,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7798,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7812,7 +7851,7 @@
         <v>5.067644558031954</v>
       </c>
       <c r="D128" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E128">
         <v>4.254963977459765</v>
@@ -7848,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7862,7 +7901,7 @@
         <v>5.111345348656355</v>
       </c>
       <c r="D129" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E129">
         <v>4.254963977459765</v>
@@ -7898,7 +7937,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7912,7 +7951,7 @@
         <v>3.765802729769834</v>
       </c>
       <c r="D130" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E130">
         <v>3.674881815638774</v>
@@ -7948,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7962,7 +8001,7 @@
         <v>4.618291357603566</v>
       </c>
       <c r="D131" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E131">
         <v>3.650865136965114</v>
@@ -7998,7 +8037,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8012,7 +8051,7 @@
         <v>4.268167177296843</v>
       </c>
       <c r="D132" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E132">
         <v>3.514053115333852</v>
@@ -8048,7 +8087,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8062,7 +8101,7 @@
         <v>4.254037078744074</v>
       </c>
       <c r="D133" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E133">
         <v>3.510852837781765</v>
@@ -8098,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8112,7 +8151,7 @@
         <v>4.264789106547418</v>
       </c>
       <c r="D134" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E134">
         <v>3.510852837781765</v>
@@ -8148,7 +8187,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8162,7 +8201,7 @@
         <v>4.267776501761822</v>
       </c>
       <c r="D135" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E135">
         <v>3.523940390364364</v>
@@ -8198,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8212,7 +8251,7 @@
         <v>4.278603745384606</v>
       </c>
       <c r="D136" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E136">
         <v>3.523940390364364</v>
@@ -8248,7 +8287,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8262,7 +8301,7 @@
         <v>4.280771326539147</v>
       </c>
       <c r="D137" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E137">
         <v>3.485420289185799</v>
@@ -8298,7 +8337,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8312,7 +8351,7 @@
         <v>4.291669709713632</v>
       </c>
       <c r="D138" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E138">
         <v>3.485420289185799</v>
@@ -8348,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8362,7 +8401,7 @@
         <v>4.295828187834458</v>
       </c>
       <c r="D139" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E139">
         <v>3.499680345777525</v>
@@ -8398,7 +8437,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8412,7 +8451,7 @@
         <v>4.306808999081727</v>
       </c>
       <c r="D140" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E140">
         <v>3.499680345777525</v>
@@ -8448,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8462,7 +8501,7 @@
         <v>4.311022789612967</v>
       </c>
       <c r="D141" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E141">
         <v>3.503649415261579</v>
@@ -8512,7 +8551,7 @@
         <v>4.306094254478001</v>
       </c>
       <c r="D142" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E142">
         <v>3.499007110842255</v>
@@ -8548,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8562,7 +8601,7 @@
         <v>4.306502251029037</v>
       </c>
       <c r="D143" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E143">
         <v>3.499391412493775</v>
@@ -8598,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8612,7 +8651,7 @@
         <v>4.318153845587818</v>
       </c>
       <c r="D144" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E144">
         <v>3.510366326424823</v>
@@ -8648,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8698,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8748,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8798,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8812,7 +8851,7 @@
         <v>2.959973514323903</v>
       </c>
       <c r="D148" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E148">
         <v>2.331565797970563</v>
@@ -8848,7 +8887,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8862,7 +8901,7 @@
         <v>2.954681081546583</v>
       </c>
       <c r="D149" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E149">
         <v>2.325889855571697</v>
@@ -8898,7 +8937,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8912,7 +8951,7 @@
         <v>2.952436806561317</v>
       </c>
       <c r="D150" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E150">
         <v>2.323482951964311</v>
@@ -8948,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8962,7 +9001,7 @@
         <v>2.939220179650368</v>
       </c>
       <c r="D151" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E151">
         <v>2.309308598465612</v>
@@ -8998,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9012,7 +9051,7 @@
         <v>2.885800805603528</v>
       </c>
       <c r="D152" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E152">
         <v>2.285985098138231</v>
@@ -9048,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9062,7 +9101,7 @@
         <v>2.882518664640946</v>
       </c>
       <c r="D153" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E153">
         <v>2.285985098138231</v>
@@ -9098,7 +9137,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9112,7 +9151,7 @@
         <v>2.871759791100637</v>
       </c>
       <c r="D154" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E154">
         <v>2.270895377157946</v>
@@ -9148,7 +9187,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9162,7 +9201,7 @@
         <v>2.868186342783224</v>
       </c>
       <c r="D155" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E155">
         <v>2.270895377157946</v>
@@ -9198,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9212,7 +9251,7 @@
         <v>2.851373977249472</v>
       </c>
       <c r="D156" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E156">
         <v>2.248986971400885</v>
@@ -9248,7 +9287,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9262,7 +9301,7 @@
         <v>2.813597099989564</v>
       </c>
       <c r="D157" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E157">
         <v>2.215446285791325</v>
@@ -9298,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9312,7 +9351,7 @@
         <v>2.783887421732515</v>
       </c>
       <c r="D158" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E158">
         <v>2.183719283702006</v>
@@ -9348,7 +9387,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9362,7 +9401,7 @@
         <v>2.721632856402064</v>
       </c>
       <c r="D159" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E159">
         <v>2.127916568873808</v>
@@ -9398,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9412,7 +9451,7 @@
         <v>2.678525715783303</v>
       </c>
       <c r="D160" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E160">
         <v>2.09532033365037</v>
@@ -9448,7 +9487,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9462,7 +9501,7 @@
         <v>2.69110921416971</v>
       </c>
       <c r="D161" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E161">
         <v>2.09532033365037</v>
@@ -9498,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9598,7 +9637,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9648,7 +9687,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9698,7 +9737,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9848,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9898,7 +9937,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9948,7 +9987,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9998,7 +10037,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10048,7 +10087,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10098,7 +10137,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10148,7 +10187,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10162,7 +10201,7 @@
         <v>0.9328900239147986</v>
       </c>
       <c r="D175" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E175">
         <v>0.9481209772972727</v>
@@ -10198,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10212,7 +10251,7 @@
         <v>0.8361716558948933</v>
       </c>
       <c r="D176" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E176">
         <v>0.9453648051842674</v>
@@ -10262,7 +10301,7 @@
         <v>1.860133746163766</v>
       </c>
       <c r="D177" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E177">
         <v>1.319668494742769</v>
@@ -10298,7 +10337,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10312,7 +10351,7 @@
         <v>0.8121110647030001</v>
       </c>
       <c r="D178" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E178">
         <v>0.9618784389925015</v>
@@ -10348,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10362,7 +10401,7 @@
         <v>1.83652515616036</v>
       </c>
       <c r="D179" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E179">
         <v>1.296242563075947</v>
@@ -10398,7 +10437,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10412,7 +10451,7 @@
         <v>0.787726176769115</v>
       </c>
       <c r="D180" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E180">
         <v>1.126454507889258</v>
@@ -10448,7 +10487,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10462,7 +10501,7 @@
         <v>1.791439637530079</v>
       </c>
       <c r="D181" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E181">
         <v>1.27124240240025</v>
@@ -10498,7 +10537,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10512,7 +10551,7 @@
         <v>1.811330062457952</v>
       </c>
       <c r="D182" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E182">
         <v>1.27124240240025</v>
@@ -10548,7 +10587,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10562,7 +10601,7 @@
         <v>1.791373892486802</v>
       </c>
       <c r="D183" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E183">
         <v>1.27124240240025</v>
@@ -10598,7 +10637,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10612,7 +10651,7 @@
         <v>0.7617026177031843</v>
       </c>
       <c r="D184" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E184">
         <v>1.161198572371399</v>
@@ -10648,7 +10687,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10662,7 +10701,7 @@
         <v>1.756679227858482</v>
       </c>
       <c r="D185" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E185">
         <v>1.246983702650287</v>
@@ -10698,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10712,7 +10751,7 @@
         <v>1.786882211053019</v>
       </c>
       <c r="D186" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E186">
         <v>1.246983702650287</v>
@@ -10748,7 +10787,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10762,7 +10801,7 @@
         <v>1.766831465254384</v>
       </c>
       <c r="D187" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E187">
         <v>1.246983702650287</v>
@@ -10798,7 +10837,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10812,7 +10851,7 @@
         <v>0.7364508717646272</v>
       </c>
       <c r="D188" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E188">
         <v>1.146806092355067</v>
@@ -10848,7 +10887,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10862,7 +10901,7 @@
         <v>1.727529637465925</v>
       </c>
       <c r="D189" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E189">
         <v>1.218500388609561</v>
@@ -10898,7 +10937,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10912,7 +10951,7 @@
         <v>1.758176804895015</v>
       </c>
       <c r="D190" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E190">
         <v>1.218500388609561</v>
@@ -10948,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10962,7 +11001,7 @@
         <v>1.738015013037742</v>
       </c>
       <c r="D191" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E191">
         <v>1.218500388609561</v>
@@ -10998,7 +11037,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11012,7 +11051,7 @@
         <v>0.735911718893199</v>
       </c>
       <c r="D192" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E192">
         <v>1.39631619853638</v>
@@ -11048,7 +11087,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11062,7 +11101,7 @@
         <v>0.7068015741081979</v>
       </c>
       <c r="D193" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E193">
         <v>1.39631619853638</v>
@@ -11098,7 +11137,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11112,7 +11151,7 @@
         <v>1.69440254301529</v>
       </c>
       <c r="D194" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E194">
         <v>1.186130484889226</v>
@@ -11148,7 +11187,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11162,7 +11201,7 @@
         <v>1.725554504264581</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E195">
         <v>1.186130484889226</v>
@@ -11198,7 +11237,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11212,7 +11251,7 @@
         <v>1.705266513952258</v>
       </c>
       <c r="D196" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E196">
         <v>1.186130484889226</v>
@@ -11248,7 +11287,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11262,7 +11301,7 @@
         <v>0.7015226398920635</v>
       </c>
       <c r="D197" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E197">
         <v>1.362242615672869</v>
@@ -11298,7 +11337,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11312,7 +11351,7 @@
         <v>0.6731065866098378</v>
       </c>
       <c r="D198" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E198">
         <v>1.362242615672869</v>
@@ -11348,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11362,7 +11401,7 @@
         <v>1.672556215816603</v>
       </c>
       <c r="D199" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E199">
         <v>1.164783502312224</v>
@@ -11398,7 +11437,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11412,7 +11451,7 @@
         <v>1.70404107348035</v>
       </c>
       <c r="D200" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E200">
         <v>1.164783502312224</v>
@@ -11448,7 +11487,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11462,7 +11501,7 @@
         <v>1.683669859064413</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E201">
         <v>1.164783502312224</v>
@@ -11498,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11512,7 +11551,7 @@
         <v>0.6788440716572364</v>
       </c>
       <c r="D202" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E202">
         <v>1.339772107697077</v>
@@ -11548,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11562,7 +11601,7 @@
         <v>0.6508857509448882</v>
       </c>
       <c r="D203" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E203">
         <v>1.339772107697077</v>
@@ -11598,7 +11637,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11612,7 +11651,7 @@
         <v>1.643503437868948</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E204">
         <v>1.136394787860515</v>
@@ -11648,7 +11687,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11662,7 +11701,7 @@
         <v>1.675431004529993</v>
       </c>
       <c r="D205" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E205">
         <v>1.136394787860515</v>
@@ -11698,7 +11737,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11712,7 +11751,7 @@
         <v>1.654949112864731</v>
       </c>
       <c r="D206" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E206">
         <v>1.136394787860515</v>
@@ -11748,7 +11787,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11762,7 +11801,7 @@
         <v>0.648684521216337</v>
       </c>
       <c r="D207" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E207">
         <v>1.309889250379489</v>
@@ -11798,7 +11837,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11812,7 +11851,7 @@
         <v>0.6213349253752734</v>
       </c>
       <c r="D208" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E208">
         <v>1.309889250379489</v>
@@ -11848,7 +11887,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11862,7 +11901,7 @@
         <v>1.629688879456757</v>
       </c>
       <c r="D209" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E209">
         <v>1.122895990783459</v>
@@ -11912,7 +11951,7 @@
         <v>1.661826953674558</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E210">
         <v>1.122895990783459</v>
@@ -11962,7 +12001,7 @@
         <v>1.623163250060685</v>
       </c>
       <c r="D211" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E211">
         <v>1.122895990783459</v>
@@ -12012,7 +12051,7 @@
         <v>0.6343436939122524</v>
       </c>
       <c r="D212" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E212">
         <v>1.295679990298378</v>
@@ -12062,7 +12101,7 @@
         <v>0.6072835459617298</v>
       </c>
       <c r="D213" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E213">
         <v>1.295679990298378</v>
@@ -12112,7 +12151,7 @@
         <v>1.607589133113905</v>
       </c>
       <c r="D214" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E214">
         <v>1.101301381499872</v>
@@ -12148,7 +12187,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12162,7 +12201,7 @@
         <v>1.640063965371216</v>
       </c>
       <c r="D215" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E215">
         <v>1.101301381499872</v>
@@ -12198,7 +12237,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12212,7 +12251,7 @@
         <v>1.619445257306888</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E216">
         <v>1.101301381499872</v>
@@ -12248,7 +12287,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12262,7 +12301,7 @@
         <v>0.6114020524706252</v>
       </c>
       <c r="D217" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E217">
         <v>1.272948822631444</v>
@@ -12298,7 +12337,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12312,7 +12351,7 @@
         <v>0.5848049468244287</v>
       </c>
       <c r="D218" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E218">
         <v>1.272948822631444</v>
@@ -12348,7 +12387,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12362,7 +12401,7 @@
         <v>1.581012843353852</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E219">
         <v>1.075332549791479</v>
@@ -12398,7 +12437,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12412,7 +12451,7 @@
         <v>1.613892647645603</v>
       </c>
       <c r="D220" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E220">
         <v>1.075332549791479</v>
@@ -12448,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12462,7 +12501,7 @@
         <v>1.593172696572664</v>
       </c>
       <c r="D221" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E221">
         <v>1.075332549791479</v>
@@ -12498,7 +12537,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12512,7 +12551,7 @@
         <v>0.5838133326244757</v>
       </c>
       <c r="D222" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E222">
         <v>1.245613210306819</v>
@@ -12548,7 +12587,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12562,7 +12601,7 @@
         <v>0.5577730635256328</v>
       </c>
       <c r="D223" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E223">
         <v>1.245613210306819</v>
@@ -12598,7 +12637,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12612,7 +12651,7 @@
         <v>1.084913495598071</v>
       </c>
       <c r="D224" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E224">
         <v>1.231364667854545</v>
@@ -12648,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12662,7 +12701,7 @@
         <v>1.091978143921128</v>
       </c>
       <c r="D225" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E225">
         <v>1.231364667854545</v>
@@ -12698,7 +12737,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12748,7 +12787,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12762,7 +12801,7 @@
         <v>1.21869175173632</v>
       </c>
       <c r="D227" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E227">
         <v>1.069755686141992</v>
@@ -12798,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12812,7 +12851,7 @@
         <v>1.184556198440929</v>
       </c>
       <c r="D228" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E228">
         <v>1.069755686141992</v>
@@ -12848,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12862,7 +12901,7 @@
         <v>1.060519812222489</v>
       </c>
       <c r="D229" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E229">
         <v>0.9907313015562922</v>
@@ -12898,7 +12937,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12912,7 +12951,7 @@
         <v>1.017939761129645</v>
       </c>
       <c r="D230" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E230">
         <v>0.9907313015562922</v>
@@ -12948,7 +12987,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12962,7 +13001,7 @@
         <v>1.755318635505916</v>
       </c>
       <c r="D231" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E231">
         <v>1.003833585600265</v>
@@ -12998,7 +13037,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13012,7 +13051,7 @@
         <v>1.894053096403</v>
       </c>
       <c r="D232" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E232">
         <v>1.003833585600265</v>
@@ -13048,7 +13087,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13062,7 +13101,7 @@
         <v>1.97376040323609</v>
       </c>
       <c r="D233" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E233">
         <v>1.250262419204153</v>
@@ -13098,7 +13137,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13112,7 +13151,7 @@
         <v>2.034815821986728</v>
       </c>
       <c r="D234" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E234">
         <v>1.357988243685597</v>
@@ -13148,7 +13187,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13162,7 +13201,7 @@
         <v>2.10245468159479</v>
       </c>
       <c r="D235" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E235">
         <v>1.356708020256039</v>
@@ -13198,7 +13237,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13212,7 +13251,7 @@
         <v>2.160736912923812</v>
       </c>
       <c r="D236" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E236">
         <v>1.515238926320149</v>
@@ -13248,7 +13287,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13262,7 +13301,7 @@
         <v>2.25315272423952</v>
       </c>
       <c r="D237" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E237">
         <v>1.696228284995405</v>
@@ -13298,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13312,7 +13351,7 @@
         <v>2.36943391560179</v>
       </c>
       <c r="D238" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E238">
         <v>1.892500425794016</v>
@@ -13348,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13362,7 +13401,7 @@
         <v>2.474058411102812</v>
       </c>
       <c r="D239" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E239">
         <v>1.89058438855279</v>
@@ -13398,7 +13437,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13412,7 +13451,7 @@
         <v>2.503056313450243</v>
       </c>
       <c r="D240" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E240">
         <v>1.996322171701399</v>
@@ -13448,7 +13487,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13462,7 +13501,7 @@
         <v>2.525264172262913</v>
       </c>
       <c r="D241" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E241">
         <v>1.973847066177296</v>
@@ -13498,7 +13537,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13512,7 +13551,7 @@
         <v>2.554243076596262</v>
       </c>
       <c r="D242" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E242">
         <v>1.938989294196617</v>
@@ -13548,7 +13587,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13562,7 +13601,7 @@
         <v>2.598334390223854</v>
       </c>
       <c r="D243" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E243">
         <v>2.028465786771591</v>
@@ -13598,7 +13637,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13612,7 +13651,7 @@
         <v>2.670586589154834</v>
       </c>
       <c r="D244" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E244">
         <v>1.994395774818371</v>
@@ -13662,7 +13701,7 @@
         <v>2.717624878766997</v>
       </c>
       <c r="D245" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E245">
         <v>2.20711354567414</v>
@@ -13712,7 +13751,7 @@
         <v>2.768201130893359</v>
       </c>
       <c r="D246" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E246">
         <v>2.294068506214541</v>
@@ -13748,7 +13787,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13762,7 +13801,7 @@
         <v>2.800856629280805</v>
       </c>
       <c r="D247" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E247">
         <v>2.225122088576691</v>
@@ -13798,7 +13837,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13812,7 +13851,7 @@
         <v>2.80951643088527</v>
       </c>
       <c r="D248" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E248">
         <v>2.242646460311337</v>
@@ -13848,7 +13887,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13862,7 +13901,7 @@
         <v>2.799569806125956</v>
       </c>
       <c r="D249" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E249">
         <v>2.14320981989216</v>
@@ -13912,7 +13951,7 @@
         <v>2.819828844666985</v>
       </c>
       <c r="D250" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E250">
         <v>2.18506309598321</v>
@@ -13948,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13962,7 +14001,7 @@
         <v>2.819851650007405</v>
       </c>
       <c r="D251" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E251">
         <v>2.072484872689354</v>
@@ -14012,7 +14051,7 @@
         <v>2.840423697083499</v>
       </c>
       <c r="D252" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E252">
         <v>2.262963564508703</v>
@@ -14062,7 +14101,7 @@
         <v>2.908629147129241</v>
       </c>
       <c r="D253" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E253">
         <v>2.216875943157096</v>
@@ -14098,7 +14137,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14112,7 +14151,7 @@
         <v>3.004384252257208</v>
       </c>
       <c r="D254" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E254">
         <v>2.339997391123474</v>
@@ -14148,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14162,7 +14201,7 @@
         <v>3.088901753172625</v>
       </c>
       <c r="D255" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E255">
         <v>2.06246025697973</v>
@@ -14198,7 +14237,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14212,7 +14251,7 @@
         <v>3.179054845713715</v>
       </c>
       <c r="D256" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E256">
         <v>2.414075593575115</v>
@@ -14248,7 +14287,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14262,7 +14301,7 @@
         <v>3.299462923221598</v>
       </c>
       <c r="D257" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E257">
         <v>2.237378699869055</v>
@@ -14298,7 +14337,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14312,7 +14351,7 @@
         <v>3.418692237363245</v>
       </c>
       <c r="D258" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E258">
         <v>2.342027703405609</v>
@@ -14348,7 +14387,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14362,7 +14401,7 @@
         <v>3.512759057977069</v>
       </c>
       <c r="D259" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E259">
         <v>2.424591283628788</v>
@@ -14398,7 +14437,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14412,7 +14451,7 @@
         <v>3.645345160280047</v>
       </c>
       <c r="D260" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E260">
         <v>2.540963700837517</v>
@@ -14448,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14462,7 +14501,7 @@
         <v>3.815771971902112</v>
       </c>
       <c r="D261" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E261">
         <v>2.690549363898303</v>
@@ -14498,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14512,7 +14551,7 @@
         <v>4.010037470388323</v>
       </c>
       <c r="D262" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E262">
         <v>2.861058529236299</v>
@@ -14548,7 +14587,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14562,7 +14601,7 @@
         <v>4.152500561307447</v>
       </c>
       <c r="D263" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E263">
         <v>2.986100098188981</v>
@@ -14598,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14612,7 +14651,7 @@
         <v>4.227000299262723</v>
       </c>
       <c r="D264" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E264">
         <v>3.05148941454026</v>
@@ -14648,7 +14687,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14662,7 +14701,7 @@
         <v>3.628868452425993</v>
       </c>
       <c r="D265" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E265">
         <v>3.018868452425993</v>
@@ -14698,7 +14737,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14712,7 +14751,7 @@
         <v>3.56416211054958</v>
       </c>
       <c r="D266" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E266">
         <v>2.954162110549579</v>
@@ -14748,7 +14787,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14762,7 +14801,7 @@
         <v>3.491997735810393</v>
       </c>
       <c r="D267" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E267">
         <v>2.881997735810393</v>
@@ -14798,7 +14837,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14812,7 +14851,7 @@
         <v>3.304014584160329</v>
       </c>
       <c r="D268" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E268">
         <v>2.694014584160328</v>
@@ -14848,7 +14887,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14862,7 +14901,7 @@
         <v>3.180251695694135</v>
       </c>
       <c r="D269" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E269">
         <v>2.570251695694135</v>
@@ -14898,7 +14937,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14912,7 +14951,7 @@
         <v>3.152401945865307</v>
       </c>
       <c r="D270" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E270">
         <v>2.542401945865306</v>
@@ -14948,7 +14987,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14962,7 +15001,7 @@
         <v>2.145825454055195</v>
       </c>
       <c r="D271" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E271">
         <v>2.567272076620798</v>
@@ -14998,7 +15037,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15012,7 +15051,7 @@
         <v>3.117834193471839</v>
       </c>
       <c r="D272" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E272">
         <v>2.507834193471838</v>
@@ -15048,7 +15087,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15062,7 +15101,7 @@
         <v>2.068689520733654</v>
       </c>
       <c r="D273" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E273">
         <v>2.489975777533515</v>
@@ -15098,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15112,7 +15151,7 @@
         <v>3.048235451140136</v>
       </c>
       <c r="D274" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E274">
         <v>2.438235451140136</v>
@@ -15148,7 +15187,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15162,7 +15201,7 @@
         <v>1.98934486068918</v>
       </c>
       <c r="D275" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E275">
         <v>2.539161477129087</v>
@@ -15198,7 +15237,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15212,7 +15251,7 @@
         <v>2.976643803615602</v>
       </c>
       <c r="D276" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E276">
         <v>2.366643803615601</v>
@@ -15248,7 +15287,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15262,7 +15301,7 @@
         <v>1.910228381091732</v>
       </c>
       <c r="D277" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E277">
         <v>2.463005697391833</v>
@@ -15298,7 +15337,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15312,7 +15351,7 @@
         <v>2.905258040319775</v>
       </c>
       <c r="D278" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E278">
         <v>2.295258040319774</v>
@@ -15348,7 +15387,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15362,7 +15401,7 @@
         <v>1.737565923958936</v>
       </c>
       <c r="D279" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E279">
         <v>2.268709795269682</v>
@@ -15398,7 +15437,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15412,7 +15451,7 @@
         <v>1.733986526635413</v>
       </c>
       <c r="D280" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E280">
         <v>2.293359172208309</v>
@@ -15448,7 +15487,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15462,7 +15501,7 @@
         <v>2.746237323409084</v>
       </c>
       <c r="D281" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E281">
         <v>2.136237323409084</v>
@@ -15498,7 +15537,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15512,7 +15551,7 @@
         <v>1.537618654463894</v>
       </c>
       <c r="D282" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E282">
         <v>2.074713337366754</v>
@@ -15548,7 +15587,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15562,7 +15601,7 @@
         <v>1.543163834914946</v>
       </c>
       <c r="D283" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E283">
         <v>2.109677454398378</v>
@@ -15598,7 +15637,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15612,7 +15651,7 @@
         <v>2.574060508010575</v>
       </c>
       <c r="D284" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E284">
         <v>1.964060508010575</v>
@@ -15648,7 +15687,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15662,7 +15701,7 @@
         <v>1.32861267508225</v>
       </c>
       <c r="D285" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E285">
         <v>1.871927774038136</v>
@@ -15698,7 +15737,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15712,7 +15751,7 @@
         <v>1.343695826814607</v>
       </c>
       <c r="D286" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E286">
         <v>1.91767394556167</v>
@@ -15748,7 +15787,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15762,7 +15801,7 @@
         <v>2.394083136876382</v>
       </c>
       <c r="D287" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E287">
         <v>1.784083136876382</v>
@@ -15798,7 +15837,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15812,7 +15851,7 @@
         <v>1.270355943810468</v>
       </c>
       <c r="D288" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E288">
         <v>1.815404874054204</v>
@@ -15848,7 +15887,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15862,7 +15901,7 @@
         <v>1.288097636850863</v>
       </c>
       <c r="D289" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E289">
         <v>1.864156353143347</v>
@@ -15898,7 +15937,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15912,7 +15951,7 @@
         <v>2.343917618281236</v>
       </c>
       <c r="D290" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E290">
         <v>1.733917618281236</v>
@@ -15948,7 +15987,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15962,7 +16001,7 @@
         <v>1.164376800206434</v>
       </c>
       <c r="D291" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E291">
         <v>1.712579871628862</v>
@@ -15998,7 +16037,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16012,7 +16051,7 @@
         <v>1.186954843054156</v>
       </c>
       <c r="D292" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E292">
         <v>1.76679852876107</v>
@@ -16048,7 +16087,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16062,7 +16101,7 @@
         <v>2.252657800177763</v>
       </c>
       <c r="D293" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E293">
         <v>1.642657800177763</v>
@@ -16098,7 +16137,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16112,7 +16151,7 @@
         <v>1.095337982971794</v>
       </c>
       <c r="D294" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E294">
         <v>1.645595781097634</v>
@@ -16148,7 +16187,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16162,7 +16201,7 @@
         <v>1.121066606764748</v>
       </c>
       <c r="D295" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E295">
         <v>1.703375964515756</v>
@@ -16198,7 +16237,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16212,7 +16251,7 @@
         <v>2.193207707559045</v>
       </c>
       <c r="D296" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E296">
         <v>1.583207707559045</v>
@@ -16248,7 +16287,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16262,7 +16301,7 @@
         <v>0.875155284260706</v>
       </c>
       <c r="D297" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E297">
         <v>1.489897717173242</v>
@@ -16298,7 +16337,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16312,7 +16351,7 @@
         <v>0.9109319280345227</v>
       </c>
       <c r="D298" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E298">
         <v>1.501104953596641</v>
@@ -16348,7 +16387,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16362,7 +16401,7 @@
         <v>2.003605939224497</v>
       </c>
       <c r="D299" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E299">
         <v>1.393605939224496</v>
@@ -16398,7 +16437,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16412,7 +16451,7 @@
         <v>0.7877632879655483</v>
       </c>
       <c r="D300" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E300">
         <v>1.407881022237508</v>
@@ -16448,7 +16487,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16462,7 +16501,7 @@
         <v>0.8275280585544227</v>
       </c>
       <c r="D301" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E301">
         <v>1.420822226841367</v>
@@ -16498,7 +16537,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16512,7 +16551,7 @@
         <v>1.928351720192556</v>
       </c>
       <c r="D302" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E302">
         <v>1.318351720192555</v>
@@ -16548,7 +16587,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16562,7 +16601,7 @@
         <v>0.6445889510900153</v>
       </c>
       <c r="D303" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E303">
         <v>1.273513043384081</v>
@@ -16598,7 +16637,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16612,7 +16651,7 @@
         <v>0.6908874711791615</v>
       </c>
       <c r="D304" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E304">
         <v>1.289295008640233</v>
@@ -16648,7 +16687,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16662,7 +16701,7 @@
         <v>1.805062707883069</v>
       </c>
       <c r="D305" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E305">
         <v>1.195062707883069</v>
@@ -16698,7 +16737,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16712,7 +16751,7 @@
         <v>0.5834745700515587</v>
       </c>
       <c r="D306" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E306">
         <v>1.216157681814259</v>
@@ -16748,7 +16787,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16762,7 +16801,7 @@
         <v>0.6325620400690468</v>
       </c>
       <c r="D307" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E307">
         <v>1.233152233995777</v>
@@ -16798,7 +16837,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16812,7 +16851,7 @@
         <v>1.752436435322175</v>
       </c>
       <c r="D308" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E308">
         <v>1.142436435322175</v>
@@ -16848,7 +16887,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16862,7 +16901,7 @@
         <v>0.6410588642705362</v>
       </c>
       <c r="D309" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E309">
         <v>1.24133108972403</v>
@@ -16898,7 +16937,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16912,7 +16951,7 @@
         <v>0.6556505260902954</v>
       </c>
       <c r="D310" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E310">
         <v>1.24133108972403</v>
@@ -16948,7 +16987,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16962,7 +17001,7 @@
         <v>1.760103008510213</v>
       </c>
       <c r="D311" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E311">
         <v>1.150103008510213</v>
@@ -16998,7 +17037,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17012,7 +17051,7 @@
         <v>0.6538601304024763</v>
       </c>
       <c r="D312" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E312">
         <v>1.253653306395731</v>
@@ -17048,7 +17087,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17062,7 +17101,7 @@
         <v>0.6691703664125939</v>
       </c>
       <c r="D313" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E313">
         <v>1.253653306395731</v>
@@ -17098,7 +17137,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17112,7 +17151,7 @@
         <v>1.771653423273752</v>
       </c>
       <c r="D314" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E314">
         <v>1.161653423273751</v>
@@ -17148,7 +17187,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17162,7 +17201,7 @@
         <v>0.5994681371241404</v>
       </c>
       <c r="D315" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E315">
         <v>1.201296772325317</v>
@@ -17198,7 +17237,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17212,7 +17251,7 @@
         <v>0.6117251843223768</v>
       </c>
       <c r="D316" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E316">
         <v>1.201296772325317</v>
@@ -17248,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17262,7 +17301,7 @@
         <v>1.722576240149433</v>
       </c>
       <c r="D317" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E317">
         <v>1.112576240149433</v>
@@ -17298,7 +17337,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17312,7 +17351,7 @@
         <v>0.6080222404361217</v>
       </c>
       <c r="D318" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E318">
         <v>1.209530763663045</v>
@@ -17348,7 +17387,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17362,7 +17401,7 @@
         <v>0.6207594555957376</v>
       </c>
       <c r="D319" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E319">
         <v>1.209530763663045</v>
@@ -17398,7 +17437,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17412,7 +17451,7 @@
         <v>1.730294495528642</v>
       </c>
       <c r="D320" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E320">
         <v>1.120294495528642</v>
@@ -17448,7 +17487,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17462,7 +17501,7 @@
         <v>0.5618859798618736</v>
       </c>
       <c r="D321" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E321">
         <v>1.165121015958519</v>
@@ -17498,7 +17537,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17512,7 +17551,7 @@
         <v>0.5720334257169055</v>
       </c>
       <c r="D322" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E322">
         <v>1.165121015958519</v>
@@ -17548,7 +17587,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17562,7 +17601,7 @@
         <v>1.688666351892003</v>
       </c>
       <c r="D323" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E323">
         <v>1.078666351892003</v>
@@ -17598,7 +17637,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17612,7 +17651,7 @@
         <v>0.508437810595022</v>
       </c>
       <c r="D324" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E324">
         <v>1.11367298608211</v>
@@ -17648,7 +17687,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17662,7 +17701,7 @@
         <v>0.5155850473643886</v>
       </c>
       <c r="D325" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E325">
         <v>1.11367298608211</v>
@@ -17698,7 +17737,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17712,7 +17751,7 @@
         <v>1.640440768811309</v>
       </c>
       <c r="D326" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E326">
         <v>1.030440768811308</v>
@@ -17748,7 +17787,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17762,7 +17801,7 @@
         <v>0.4164767378858123</v>
       </c>
       <c r="D327" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E327">
         <v>1.025153284077196</v>
@@ -17798,7 +17837,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17812,7 +17851,7 @@
         <v>0.4184619185987364</v>
       </c>
       <c r="D328" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E328">
         <v>1.025153284077196</v>
@@ -17848,7 +17887,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17862,7 +17901,7 @@
         <v>1.557465497385535</v>
       </c>
       <c r="D329" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E329">
         <v>0.9474654973855348</v>
@@ -17898,7 +17937,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17912,7 +17951,7 @@
         <v>0.3644704529510241</v>
       </c>
       <c r="D330" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E330">
         <v>0.9750931802834177</v>
@@ -17948,7 +17987,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17962,7 +18001,7 @@
         <v>0.3635363619524323</v>
       </c>
       <c r="D331" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E331">
         <v>0.9750931802834177</v>
@@ -17998,7 +18037,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18012,7 +18051,7 @@
         <v>1.565054544022541</v>
       </c>
       <c r="D332" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E332">
         <v>0.9005409076522746</v>
@@ -18048,7 +18087,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18062,7 +18101,7 @@
         <v>0.2866150347691372</v>
       </c>
       <c r="D333" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E333">
         <v>0.9143380680881883</v>
@@ -18098,7 +18137,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18112,7 +18151,7 @@
         <v>0.2813106812114787</v>
       </c>
       <c r="D334" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E334">
         <v>0.9143380680881883</v>
@@ -18148,7 +18187,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18162,7 +18201,7 @@
         <v>0.3483831526216896</v>
       </c>
       <c r="D335" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E335">
         <v>0.9143380680881883</v>
@@ -18198,7 +18237,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18212,7 +18251,7 @@
         <v>1.495130343077478</v>
       </c>
       <c r="D336" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E336">
         <v>0.8302929835546884</v>
@@ -18248,7 +18287,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18262,7 +18301,7 @@
         <v>0.2225831635998929</v>
       </c>
       <c r="D337" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E337">
         <v>0.8619688447062037</v>
@@ -18312,7 +18351,7 @@
         <v>0.2987488573747035</v>
       </c>
       <c r="D338" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E338">
         <v>0.8619688447062037</v>
@@ -18362,7 +18401,7 @@
         <v>0.2938174275967516</v>
       </c>
       <c r="D339" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E339">
         <v>0.8619688447062037</v>
@@ -18412,7 +18451,7 @@
         <v>1.445188832037704</v>
       </c>
       <c r="D340" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E340">
         <v>0.7801202618156564</v>
@@ -18462,7 +18501,7 @@
         <v>0.3281392211768228</v>
       </c>
       <c r="D341" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E341">
         <v>0.8803786785285439</v>
@@ -18498,7 +18537,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18512,7 +18551,7 @@
         <v>0.3180121272020529</v>
       </c>
       <c r="D342" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E342">
         <v>0.8803786785285439</v>
@@ -18548,7 +18587,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18562,7 +18601,7 @@
         <v>0.3129994178045763</v>
       </c>
       <c r="D343" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E343">
         <v>0.8803786785285439</v>
@@ -18598,7 +18637,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18612,7 +18651,7 @@
         <v>1.462745229855035</v>
       </c>
       <c r="D344" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E344">
         <v>0.7977579392525129</v>
@@ -18648,7 +18687,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18662,7 +18701,7 @@
         <v>0.3459316339300287</v>
       </c>
       <c r="D345" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E345">
         <v>0.8966943930572944</v>
@@ -18698,7 +18737,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18712,7 +18751,7 @@
         <v>0.3350841993579632</v>
       </c>
       <c r="D346" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E346">
         <v>0.8966943930572944</v>
@@ -18748,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18762,7 +18801,7 @@
         <v>0.3299994559007571</v>
       </c>
       <c r="D347" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E347">
         <v>0.8966943930572944</v>
@@ -18798,7 +18837,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18812,7 +18851,7 @@
         <v>1.478304586756625</v>
       </c>
       <c r="D348" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E348">
         <v>0.8133893302138313</v>
@@ -18848,7 +18887,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18862,7 +18901,7 @@
         <v>0.3746816311597856</v>
       </c>
       <c r="D349" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E349">
         <v>0.9230582569137313</v>
@@ -18898,7 +18937,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18912,7 +18951,7 @@
         <v>0.3626702290885397</v>
       </c>
       <c r="D350" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E350">
         <v>0.9230582569137313</v>
@@ -18948,7 +18987,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18962,7 +19001,7 @@
         <v>0.357469088881416</v>
       </c>
       <c r="D351" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E351">
         <v>0.9230582569137313</v>
@@ -18998,7 +19037,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19012,7 +19051,7 @@
         <v>1.503446284738923</v>
       </c>
       <c r="D352" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E352">
         <v>0.8386474249460472</v>
@@ -19048,7 +19087,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19062,7 +19101,7 @@
         <v>0.3609903029368784</v>
       </c>
       <c r="D353" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E353">
         <v>0.9727726579916833</v>
@@ -19112,7 +19151,7 @@
         <v>0.4278925267560636</v>
       </c>
       <c r="D354" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E354">
         <v>0.9853909591149721</v>
@@ -19162,7 +19201,7 @@
         <v>0.4224161869807217</v>
       </c>
       <c r="D355" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E355">
         <v>0.9853909591149721</v>
@@ -19212,7 +19251,7 @@
         <v>1.508365731249223</v>
       </c>
       <c r="D356" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E356">
         <v>0.898365731249223</v>
@@ -19262,7 +19301,7 @@
         <v>0.5369709001154694</v>
       </c>
       <c r="D357" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E357">
         <v>1.089636746312885</v>
@@ -19312,7 +19351,7 @@
         <v>0.531034314039033</v>
       </c>
       <c r="D358" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E358">
         <v>1.089636746312885</v>
@@ -19362,7 +19401,7 @@
         <v>1.608239178586738</v>
       </c>
       <c r="D359" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E359">
         <v>0.9982391785867382</v>
@@ -19412,7 +19451,7 @@
         <v>0.5385854937585846</v>
       </c>
       <c r="D360" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E360">
         <v>0.634839149452838</v>
@@ -19462,7 +19501,7 @@
         <v>2.009812451983092</v>
       </c>
       <c r="D361" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E361">
         <v>1.399812451983092</v>
@@ -19498,7 +19537,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19512,7 +19551,7 @@
         <v>0.9230051396340304</v>
       </c>
       <c r="D362" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E362">
         <v>0.9850070169538339</v>
@@ -19548,7 +19587,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19562,7 +19601,7 @@
         <v>0.8994749023453439</v>
       </c>
       <c r="D363" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E363">
         <v>0.9850070169538339</v>
@@ -19598,7 +19637,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19612,7 +19651,7 @@
         <v>2.109691017081675</v>
       </c>
       <c r="D364" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E364">
         <v>1.499691017081674</v>
@@ -19648,7 +19687,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19662,7 +19701,7 @@
         <v>1.015979656453909</v>
       </c>
       <c r="D365" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E365">
         <v>1.231185799135601</v>
@@ -19698,7 +19737,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19712,7 +19751,7 @@
         <v>0.9827837515750368</v>
       </c>
       <c r="D366" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E366">
         <v>1.231185799135601</v>
@@ -19748,7 +19787,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19762,7 +19801,7 @@
         <v>2.200993423621709</v>
       </c>
       <c r="D367" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E367">
         <v>1.590993423621708</v>
@@ -19798,7 +19837,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19812,7 +19851,7 @@
         <v>1.100970836735415</v>
       </c>
       <c r="D368" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E368">
         <v>1.303589318044656</v>
@@ -19848,7 +19887,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19862,7 +19901,7 @@
         <v>1.058939215094605</v>
       </c>
       <c r="D369" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E369">
         <v>1.303589318044656</v>
@@ -19898,7 +19937,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19912,7 +19951,7 @@
         <v>2.329644706282916</v>
       </c>
       <c r="D370" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E370">
         <v>1.719644706282915</v>
@@ -19948,7 +19987,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19962,7 +20001,7 @@
         <v>1.220729173590548</v>
       </c>
       <c r="D371" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E371">
         <v>1.321050696987874</v>
@@ -19998,7 +20037,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20012,7 +20051,7 @@
         <v>2.471463589779925</v>
       </c>
       <c r="D372" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E372">
         <v>1.861463589779925</v>
@@ -20048,7 +20087,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20098,7 +20137,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20112,7 +20151,7 @@
         <v>2.497443975683849</v>
       </c>
       <c r="D374" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E374">
         <v>1.887443975683849</v>
@@ -20148,7 +20187,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20198,7 +20237,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20248,7 +20287,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20262,7 +20301,7 @@
         <v>2.512308244184901</v>
       </c>
       <c r="D377" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E377">
         <v>1.9023082441849</v>
@@ -20298,7 +20337,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20312,7 +20351,7 @@
         <v>1.390766199655991</v>
       </c>
       <c r="D378" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E378">
         <v>1.47783631505106</v>
@@ -20348,7 +20387,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20362,7 +20401,7 @@
         <v>1.39783631505106</v>
       </c>
       <c r="D379" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E379">
         <v>1.47783631505106</v>
@@ -20398,7 +20437,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20412,7 +20451,7 @@
         <v>2.5135497431605</v>
       </c>
       <c r="D380" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E380">
         <v>1.903549743160499</v>
@@ -20448,7 +20487,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20462,7 +20501,7 @@
         <v>1.39192188073005</v>
       </c>
       <c r="D381" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E381">
         <v>1.488828942112197</v>
@@ -20498,7 +20537,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20512,7 +20551,7 @@
         <v>1.319642873327421</v>
       </c>
       <c r="D382" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E382">
         <v>1.488828942112197</v>
@@ -20548,7 +20587,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20562,7 +20601,7 @@
         <v>1.388828942112196</v>
       </c>
       <c r="D383" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E383">
         <v>1.488828942112197</v>
@@ -20598,7 +20637,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20612,7 +20651,7 @@
         <v>2.501566998394471</v>
       </c>
       <c r="D384" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E384">
         <v>1.891566998394471</v>
@@ -20648,7 +20687,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20662,7 +20701,7 @@
         <v>1.279594745212004</v>
       </c>
       <c r="D385" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E385">
         <v>1.519061703811337</v>
@@ -20698,7 +20737,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20712,7 +20751,7 @@
         <v>1.30964804935207</v>
       </c>
       <c r="D386" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E386">
         <v>1.519061703811337</v>
@@ -20748,7 +20787,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20762,7 +20801,7 @@
         <v>2.48573721583752</v>
       </c>
       <c r="D387" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E387">
         <v>1.875737215837519</v>
@@ -20798,7 +20837,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20812,7 +20851,7 @@
         <v>1.266464050003473</v>
       </c>
       <c r="D388" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E388">
         <v>1.59667031375327</v>
@@ -20848,7 +20887,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20862,7 +20901,7 @@
         <v>1.296444405836825</v>
       </c>
       <c r="D389" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E389">
         <v>1.59667031375327</v>
@@ -20898,7 +20937,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20912,7 +20951,7 @@
         <v>2.454303876936348</v>
       </c>
       <c r="D390" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E390">
         <v>1.844303876936348</v>
@@ -20948,7 +20987,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20962,7 +21001,7 @@
         <v>1.240390312666095</v>
       </c>
       <c r="D391" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E391">
         <v>1.592199793558723</v>
@@ -20998,7 +21037,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21012,7 +21051,7 @@
         <v>1.270225814403128</v>
       </c>
       <c r="D392" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E392">
         <v>1.592199793558723</v>
@@ -21048,7 +21087,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21062,7 +21101,7 @@
         <v>2.438801816749918</v>
       </c>
       <c r="D393" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E393">
         <v>1.828801816749918</v>
@@ -21098,7 +21137,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21112,7 +21151,7 @@
         <v>1.227531460898549</v>
       </c>
       <c r="D394" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E394">
         <v>1.611306442152011</v>
@@ -21148,7 +21187,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21162,7 +21201,7 @@
         <v>1.257295524570208</v>
       </c>
       <c r="D395" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E395">
         <v>1.611306442152011</v>
@@ -21198,7 +21237,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21212,7 +21251,7 @@
         <v>2.435888213210831</v>
       </c>
       <c r="D396" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E396">
         <v>1.825888213210831</v>
@@ -21248,7 +21287,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21262,7 +21301,7 @@
         <v>1.225114646902994</v>
       </c>
       <c r="D397" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E397">
         <v>1.589727863749075</v>
@@ -21298,7 +21337,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21312,7 +21351,7 @@
         <v>1.254865283830232</v>
       </c>
       <c r="D398" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E398">
         <v>1.589727863749075</v>
@@ -21348,7 +21387,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21362,7 +21401,7 @@
         <v>2.394557671241156</v>
       </c>
       <c r="D399" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E399">
         <v>1.784557671241155</v>
@@ -21398,7 +21437,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21412,7 +21451,7 @@
         <v>1.190831248034139</v>
       </c>
       <c r="D400" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E400">
         <v>1.609187949630535</v>
@@ -21448,7 +21487,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21462,7 +21501,7 @@
         <v>1.220391421634328</v>
       </c>
       <c r="D401" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E401">
         <v>1.609187949630535</v>
@@ -21498,7 +21537,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21512,7 +21551,7 @@
         <v>2.366135904185318</v>
       </c>
       <c r="D402" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E402">
         <v>1.756135904185318</v>
@@ -21548,7 +21587,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21562,7 +21601,7 @@
         <v>1.167255588725149</v>
       </c>
       <c r="D403" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E403">
         <v>1.578100832137494</v>
@@ -21598,7 +21637,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21612,7 +21651,7 @@
         <v>1.196684786440288</v>
       </c>
       <c r="D404" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E404">
         <v>1.578100832137494</v>
@@ -21648,7 +21687,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21662,7 +21701,7 @@
         <v>2.396096253709469</v>
       </c>
       <c r="D405" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E405">
         <v>1.786096253709469</v>
@@ -21698,7 +21737,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21712,7 +21751,7 @@
         <v>1.192107491556242</v>
       </c>
       <c r="D406" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E406">
         <v>1.492060423190722</v>
@@ -21748,7 +21787,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21762,7 +21801,7 @@
         <v>1.221674755398221</v>
       </c>
       <c r="D407" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E407">
         <v>1.492060423190722</v>
@@ -21798,7 +21837,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21812,7 +21851,7 @@
         <v>2.341003521520614</v>
       </c>
       <c r="D408" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E408">
         <v>1.731003521520614</v>
@@ -21848,7 +21887,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21862,7 +21901,7 @@
         <v>1.146408451030924</v>
       </c>
       <c r="D409" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E409">
         <v>1.603573943943295</v>
@@ -21898,7 +21937,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21912,7 +21951,7 @@
         <v>1.175721831314429</v>
       </c>
       <c r="D410" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E410">
         <v>1.603573943943295</v>
@@ -21948,7 +21987,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21962,7 +22001,7 @@
         <v>2.3387346635889</v>
       </c>
       <c r="D411" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E411">
         <v>1.7287346635889</v>
@@ -21998,7 +22037,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22012,7 +22051,7 @@
         <v>1.144526449059917</v>
       </c>
       <c r="D412" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E412">
         <v>1.601256255851928</v>
@@ -22048,7 +22087,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22062,7 +22101,7 @@
         <v>1.173829373776917</v>
       </c>
       <c r="D413" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E413">
         <v>1.601256255851928</v>
@@ -22098,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22112,7 +22151,7 @@
         <v>2.321864997704619</v>
       </c>
       <c r="D414" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E414">
         <v>1.711864997704619</v>
@@ -22148,7 +22187,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22162,7 +22201,7 @@
         <v>1.130533177819499</v>
       </c>
       <c r="D415" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E415">
         <v>1.628353938431452</v>
@@ -22198,7 +22237,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22212,7 +22251,7 @@
         <v>1.159758362140719</v>
       </c>
       <c r="D416" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E416">
         <v>1.628353938431452</v>
@@ -22248,7 +22287,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22262,7 +22301,7 @@
         <v>2.329307629672357</v>
       </c>
       <c r="D417" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E417">
         <v>1.719307629672357</v>
@@ -22298,7 +22337,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22312,7 +22351,7 @@
         <v>1.136706789589973</v>
       </c>
       <c r="D418" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E418">
         <v>1.641887405220004</v>
@@ -22348,7 +22387,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22362,7 +22401,7 @@
         <v>1.165966271754362</v>
       </c>
       <c r="D419" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E419">
         <v>1.641887405220004</v>
@@ -22398,7 +22437,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22412,7 +22451,7 @@
         <v>2.283832828965951</v>
       </c>
       <c r="D420" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E420">
         <v>1.673832828965951</v>
@@ -22462,7 +22501,7 @@
         <v>1.09898575674595</v>
       </c>
       <c r="D421" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E421">
         <v>1.611312616281895</v>
@@ -22512,7 +22551,7 @@
         <v>1.128035677616761</v>
       </c>
       <c r="D422" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E422">
         <v>1.611312616281895</v>
@@ -22562,7 +22601,7 @@
         <v>2.182831733767929</v>
       </c>
       <c r="D423" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E423">
         <v>1.572831733767929</v>
@@ -22598,7 +22637,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22612,7 +22651,7 @@
         <v>1.084064563230975</v>
       </c>
       <c r="D424" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E424">
         <v>1.514840661441129</v>
@@ -22648,7 +22687,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22662,7 +22701,7 @@
         <v>1.04379052447924</v>
       </c>
       <c r="D425" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E425">
         <v>1.514840661441129</v>
@@ -22698,7 +22737,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22712,7 +22751,7 @@
         <v>1.987186684521362</v>
       </c>
       <c r="D426" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E426">
         <v>1.377186684521361</v>
@@ -22748,7 +22787,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22762,7 +22801,7 @@
         <v>0.9019433653148159</v>
       </c>
       <c r="D427" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E427">
         <v>1.471274636039009</v>
@@ -22798,7 +22837,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22812,7 +22851,7 @@
         <v>0.8806027184256511</v>
       </c>
       <c r="D428" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E428">
         <v>1.471274636039009</v>
@@ -22848,7 +22887,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22862,7 +22901,7 @@
         <v>1.871503922012645</v>
       </c>
       <c r="D429" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E429">
         <v>1.261503922012645</v>
@@ -22912,7 +22951,7 @@
         <v>0.8271315762745894</v>
       </c>
       <c r="D430" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E430">
         <v>1.39104304268619</v>
@@ -22962,7 +23001,7 @@
         <v>0.784111566287045</v>
       </c>
       <c r="D431" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E431">
         <v>1.39104304268619</v>
@@ -23012,7 +23051,7 @@
         <v>1.725043908638261</v>
       </c>
       <c r="D432" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E432">
         <v>1.115043908638261</v>
@@ -23048,7 +23087,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23062,7 +23101,7 @@
         <v>0.6891081996153199</v>
       </c>
       <c r="D433" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E433">
         <v>1.208315076967225</v>
@@ -23098,7 +23137,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23112,7 +23151,7 @@
         <v>0.6619490666521894</v>
       </c>
       <c r="D434" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E434">
         <v>1.208315076967225</v>
@@ -23148,7 +23187,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23162,7 +23201,7 @@
         <v>1.603418511347999</v>
       </c>
       <c r="D435" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E435">
         <v>0.9934185113479987</v>
@@ -23198,7 +23237,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23212,7 +23251,7 @@
         <v>0.574488873597538</v>
       </c>
       <c r="D436" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E436">
         <v>1.108556250145786</v>
@@ -23248,7 +23287,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23262,7 +23301,7 @@
         <v>0.5605011546266709</v>
       </c>
       <c r="D437" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E437">
         <v>1.108556250145786</v>
@@ -23298,7 +23337,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23312,7 +23351,7 @@
         <v>1.504487777527864</v>
       </c>
       <c r="D438" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E438">
         <v>0.8944877775278632</v>
@@ -23348,7 +23387,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23362,7 +23401,7 @@
         <v>0.4812569147670418</v>
       </c>
       <c r="D439" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E439">
         <v>1.036979636275919</v>
@@ -23398,7 +23437,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23412,7 +23451,7 @@
         <v>0.4779828927766969</v>
       </c>
       <c r="D440" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E440">
         <v>1.036979636275919</v>
@@ -23448,7 +23487,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23462,7 +23501,7 @@
         <v>1.414501209603441</v>
       </c>
       <c r="D441" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E441">
         <v>0.9219355330393615</v>
@@ -23498,7 +23537,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23512,7 +23551,7 @@
         <v>0.3964539049027813</v>
       </c>
       <c r="D442" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E442">
         <v>0.9417865782881711</v>
@@ -23548,7 +23587,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23562,7 +23601,7 @@
         <v>0.4029249720655423</v>
       </c>
       <c r="D443" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E443">
         <v>0.9417865782881711</v>
@@ -23598,7 +23637,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23612,7 +23651,7 @@
         <v>1.374244075534095</v>
       </c>
       <c r="D444" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E444">
         <v>0.8269425846185072</v>
@@ -23648,7 +23687,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23662,7 +23701,7 @@
         <v>0.3063097844755669</v>
       </c>
       <c r="D445" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E445">
         <v>0.873462183832336</v>
@@ -23698,7 +23737,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23712,7 +23751,7 @@
         <v>0.3231397114429218</v>
       </c>
       <c r="D446" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E446">
         <v>0.873462183832336</v>
@@ -23748,7 +23787,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23762,7 +23801,7 @@
         <v>1.297276604707491</v>
       </c>
       <c r="D447" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E447">
         <v>0.7916599773381927</v>
@@ -23798,7 +23837,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23812,7 +23851,7 @@
         <v>0.233440118808713</v>
       </c>
       <c r="D448" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E448">
         <v>0.818230896896579</v>
@@ -23848,7 +23887,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23862,7 +23901,7 @@
         <v>0.2586438215372961</v>
       </c>
       <c r="D449" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E449">
         <v>0.818230896896579</v>
@@ -23898,7 +23937,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23948,7 +23987,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23962,7 +24001,7 @@
         <v>1.228322830557575</v>
       </c>
       <c r="D451" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E451">
         <v>0.7235042792779742</v>
@@ -23998,7 +24037,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24012,7 +24051,7 @@
         <v>0.1681574946714077</v>
       </c>
       <c r="D452" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E452">
         <v>0.7687501793352967</v>
@@ -24048,7 +24087,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24062,7 +24101,7 @@
         <v>0.2008631126431526</v>
       </c>
       <c r="D453" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E453">
         <v>0.7687501793352967</v>
@@ -24098,7 +24137,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24112,7 +24151,7 @@
         <v>1.23967353577152</v>
       </c>
       <c r="D454" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E454">
         <v>1.163072722956397</v>
@@ -24148,7 +24187,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24162,7 +24201,7 @@
         <v>1.225596128630588</v>
       </c>
       <c r="D455" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E455">
         <v>0.6905047055753135</v>
@@ -24198,7 +24237,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24212,7 +24251,7 @@
         <v>0.136549003700944</v>
       </c>
       <c r="D456" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E456">
         <v>0.7447926433919125</v>
@@ -24248,7 +24287,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24262,7 +24301,7 @@
         <v>0.172886893251202</v>
       </c>
       <c r="D457" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E457">
         <v>0.7447926433919125</v>
@@ -24298,7 +24337,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24348,7 +24387,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24362,7 +24401,7 @@
         <v>1.220200273962068</v>
       </c>
       <c r="D459" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E459">
         <v>0.6852080850156392</v>
@@ -24398,7 +24437,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24412,7 +24451,7 @@
         <v>0.1314756598861742</v>
       </c>
       <c r="D460" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E460">
         <v>0.7409473216741169</v>
@@ -24448,7 +24487,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24462,7 +24501,7 @@
         <v>0.1683965498259044</v>
       </c>
       <c r="D461" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E461">
         <v>0.7409473216741169</v>
@@ -24498,7 +24537,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24512,7 +24551,7 @@
         <v>1.216624069904026</v>
       </c>
       <c r="D462" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E462">
         <v>1.236624069904027</v>
@@ -24548,7 +24587,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24562,7 +24601,7 @@
         <v>1.283513715629472</v>
       </c>
       <c r="D463" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E463">
         <v>1.236624069904027</v>
@@ -24598,7 +24637,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24612,7 +24651,7 @@
         <v>1.245299916107382</v>
       </c>
       <c r="D464" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E464">
         <v>0.7098461245467869</v>
@@ -24648,7 +24687,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24662,7 +24701,7 @@
         <v>0.155075093535447</v>
       </c>
       <c r="D465" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E465">
         <v>0.7588344229730764</v>
@@ -24698,7 +24737,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24712,7 +24751,7 @@
         <v>0.1892840681169474</v>
       </c>
       <c r="D466" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E466">
         <v>0.7588344229730764</v>
@@ -24748,7 +24787,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24762,7 +24801,7 @@
         <v>1.346682022872791</v>
       </c>
       <c r="D467" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E467">
         <v>1.156906845444727</v>
@@ -24798,7 +24837,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24812,7 +24851,7 @@
         <v>1.297477194708015</v>
       </c>
       <c r="D468" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E468">
         <v>1.156906845444727</v>
@@ -24848,7 +24887,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24862,7 +24901,7 @@
         <v>1.297810076779093</v>
       </c>
       <c r="D469" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E469">
         <v>0.761390581114191</v>
@@ -24898,7 +24937,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24912,7 +24951,7 @@
         <v>0.2044467158681593</v>
       </c>
       <c r="D470" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E470">
         <v>0.7962554570149853</v>
@@ -24948,7 +24987,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24962,7 +25001,7 @@
         <v>0.2329821788368545</v>
       </c>
       <c r="D471" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E471">
         <v>0.7962554570149853</v>
@@ -24998,7 +25037,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25012,7 +25051,7 @@
         <v>1.375532432988972</v>
       </c>
       <c r="D472" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E472">
         <v>1.038262852606697</v>
@@ -25048,7 +25087,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25062,7 +25101,7 @@
         <v>1.326689743863311</v>
       </c>
       <c r="D473" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E473">
         <v>1.038262852606697</v>
@@ -25098,7 +25137,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25112,7 +25151,7 @@
         <v>1.316058735434172</v>
       </c>
       <c r="D474" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E474">
         <v>0.7793036322537743</v>
@@ -25148,7 +25187,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25162,7 +25201,7 @@
         <v>0.221604650097877</v>
       </c>
       <c r="D475" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E475">
         <v>0.8092602482404443</v>
@@ -25198,7 +25237,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25212,7 +25251,7 @@
         <v>0.2481684189130346</v>
       </c>
       <c r="D476" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E476">
         <v>0.8092602482404443</v>
@@ -25248,7 +25287,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25262,7 +25301,7 @@
         <v>1.385558707514407</v>
       </c>
       <c r="D477" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E477">
         <v>1.0151454476213</v>
@@ -25298,7 +25337,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25312,7 +25351,7 @@
         <v>1.336841871207057</v>
       </c>
       <c r="D478" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E478">
         <v>1.0151454476213</v>
@@ -25348,7 +25387,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25362,7 +25401,7 @@
         <v>1.357255810174356</v>
       </c>
       <c r="D479" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E479">
         <v>0.8197430596424145</v>
@@ -25398,7 +25437,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25412,7 +25451,7 @@
         <v>0.2603393709455446</v>
       </c>
       <c r="D480" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E480">
         <v>0.8673754583787305</v>
@@ -25448,7 +25487,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25462,7 +25501,7 @@
         <v>0.2824519615703833</v>
       </c>
       <c r="D481" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E481">
         <v>0.8673754583787305</v>
@@ -25498,7 +25537,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25512,7 +25551,7 @@
         <v>1.408193422141772</v>
       </c>
       <c r="D482" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E482">
         <v>1.092946268617976</v>
@@ -25548,7 +25587,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25562,7 +25601,7 @@
         <v>1.359760703591251</v>
       </c>
       <c r="D483" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E483">
         <v>1.092946268617976</v>
@@ -25598,7 +25637,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25612,7 +25651,7 @@
         <v>1.400693800028334</v>
       </c>
       <c r="D484" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E484">
         <v>0.8623821899128705</v>
@@ -25648,7 +25687,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25662,7 +25701,7 @@
         <v>0.3011810671530766</v>
       </c>
       <c r="D485" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E485">
         <v>0.898730697031946</v>
@@ -25698,7 +25737,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25712,7 +25751,7 @@
         <v>0.3186003577247281</v>
       </c>
       <c r="D486" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E486">
         <v>0.898730697031946</v>
@@ -25748,7 +25787,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25762,7 +25801,7 @@
         <v>1.432059352199475</v>
       </c>
       <c r="D487" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E487">
         <v>0.9910848179499889</v>
@@ -25798,7 +25837,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25812,7 +25851,7 @@
         <v>1.383926205992774</v>
       </c>
       <c r="D488" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E488">
         <v>0.9910848179499889</v>
@@ -25848,7 +25887,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25862,7 +25901,7 @@
         <v>1.389878787820437</v>
       </c>
       <c r="D489" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E489">
         <v>0.851766074481211</v>
@@ -25898,7 +25937,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25912,7 +25951,7 @@
         <v>0.291012469467951</v>
       </c>
       <c r="D490" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E490">
         <v>0.8909239985646367</v>
@@ -25948,7 +25987,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25962,7 +26001,7 @@
         <v>0.3096002785999952</v>
       </c>
       <c r="D491" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E491">
         <v>0.8909239985646367</v>
@@ -25998,7 +26037,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26012,7 +26051,7 @@
         <v>1.426117311009389</v>
       </c>
       <c r="D492" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E492">
         <v>1.145927272692262</v>
@@ -26048,7 +26087,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26062,7 +26101,7 @@
         <v>1.377909578511599</v>
       </c>
       <c r="D493" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E493">
         <v>1.145927272692262</v>
@@ -26098,7 +26137,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26112,7 +26151,7 @@
         <v>1.390470377742177</v>
       </c>
       <c r="D494" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E494">
         <v>0.8523467845882973</v>
@@ -26148,7 +26187,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26162,7 +26201,7 @@
         <v>0.2915686999920695</v>
       </c>
       <c r="D495" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E495">
         <v>0.8913510312897541</v>
@@ -26198,7 +26237,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26212,7 +26251,7 @@
         <v>0.3100925902130296</v>
       </c>
       <c r="D496" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E496">
         <v>0.8913510312897541</v>
@@ -26248,7 +26287,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26262,7 +26301,7 @@
         <v>1.426442345472138</v>
       </c>
       <c r="D497" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E497">
         <v>1.04260947236648</v>
@@ -26298,7 +26337,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26312,7 +26351,7 @@
         <v>1.4090266167915</v>
       </c>
       <c r="D498" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E498">
         <v>0.8705617594711974</v>
@@ -26348,7 +26387,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26362,7 +26401,7 @@
         <v>0.3090158305005142</v>
       </c>
       <c r="D499" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E499">
         <v>0.9047456498219102</v>
@@ -26398,7 +26437,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26412,7 +26451,7 @@
         <v>0.3255347937437314</v>
       </c>
       <c r="D500" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E500">
         <v>0.9047456498219102</v>
@@ -26448,7 +26487,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26462,7 +26501,7 @@
         <v>1.436637612444065</v>
       </c>
       <c r="D501" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E501">
         <v>1.0174159700749</v>
@@ -26498,7 +26537,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26512,7 +26551,7 @@
         <v>1.481023111428944</v>
       </c>
       <c r="D502" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E502">
         <v>0.9412341806440443</v>
@@ -26548,7 +26587,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26562,7 +26601,7 @@
         <v>0.3767090863780185</v>
       </c>
       <c r="D503" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E503">
         <v>0.9692419169592172</v>
@@ -26598,7 +26637,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26612,7 +26651,7 @@
         <v>0.3854491180167301</v>
       </c>
       <c r="D504" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E504">
         <v>0.9692419169592172</v>
@@ -26648,7 +26687,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26662,7 +26701,7 @@
         <v>1.476194307198891</v>
       </c>
       <c r="D505" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E505">
         <v>1.037981948597929</v>
@@ -26698,7 +26737,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26712,7 +26751,7 @@
         <v>1.566896676462016</v>
       </c>
       <c r="D506" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E506">
         <v>1.019149230451688</v>
@@ -26748,7 +26787,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26762,7 +26801,7 @@
         <v>0.4887054182244546</v>
       </c>
       <c r="D507" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E507">
         <v>1.141981249108951</v>
@@ -26798,7 +26837,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26812,7 +26851,7 @@
         <v>0.4845754557390034</v>
       </c>
       <c r="D508" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E508">
         <v>1.141981249108951</v>
@@ -26848,7 +26887,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26862,7 +26901,7 @@
         <v>1.575427906313638</v>
       </c>
       <c r="D509" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E509">
         <v>0.9905476528404038</v>
@@ -26898,7 +26937,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26912,7 +26951,7 @@
         <v>1.651922146792429</v>
       </c>
       <c r="D510" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E510">
         <v>1.103977882563743</v>
@@ -26948,7 +26987,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26962,7 +27001,7 @@
         <v>0.5692040695326464</v>
       </c>
       <c r="D511" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E511">
         <v>1.20122353283454</v>
@@ -26998,7 +27037,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27012,7 +27051,7 @@
         <v>0.5558236507843963</v>
       </c>
       <c r="D512" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E512">
         <v>1.20122353283454</v>
@@ -27048,7 +27087,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27062,7 +27101,7 @@
         <v>1.619515187225704</v>
       </c>
       <c r="D513" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E513">
         <v>1.044672662888699</v>
@@ -27098,7 +27137,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27112,7 +27151,7 @@
         <v>1.713538754440068</v>
       </c>
       <c r="D514" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E514">
         <v>1.21890599807297</v>
@@ -27148,7 +27187,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27162,7 +27201,7 @@
         <v>0.6782657847142568</v>
       </c>
       <c r="D515" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E515">
         <v>1.281486555498756</v>
@@ -27198,7 +27237,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27212,7 +27251,7 @@
         <v>0.6523526016297332</v>
       </c>
       <c r="D516" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E516">
         <v>1.281486555498756</v>
@@ -27248,7 +27287,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27262,7 +27301,7 @@
         <v>1.849941600908833</v>
       </c>
       <c r="D517" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E517">
         <v>1.239941600908833</v>
@@ -27298,7 +27337,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27312,7 +27351,7 @@
         <v>0.8068113243587849</v>
       </c>
       <c r="D518" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E518">
         <v>1.376088529662578</v>
@@ -27348,7 +27387,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27362,7 +27401,7 @@
         <v>0.7661264044446945</v>
       </c>
       <c r="D519" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E519">
         <v>1.376088529662578</v>
@@ -27398,7 +27437,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27412,7 +27451,7 @@
         <v>2.41237924775196</v>
       </c>
       <c r="D520" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E520">
         <v>1.720876564407629</v>
@@ -27448,7 +27487,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27462,7 +27501,7 @@
         <v>1.615923807921956</v>
       </c>
       <c r="D521" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E521">
         <v>1.035548815721295</v>
@@ -27498,7 +27537,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27509,46 +27548,46 @@
         <v>69</v>
       </c>
       <c r="C522">
-        <v>-1.484070927407007</v>
+        <v>-0.7483951014025427</v>
       </c>
       <c r="D522" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E522">
-        <v>-1.906588603387449</v>
+        <v>-0.8335168682265941</v>
       </c>
       <c r="F522">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G522">
-        <v>0.009364070927407006</v>
+        <v>0.008668395101402541</v>
       </c>
       <c r="H522">
-        <v>0.009866588603387448</v>
+        <v>0.008873516868226593</v>
       </c>
       <c r="I522">
-        <v>0.4225176759804423</v>
+        <v>-0.08512176682405137</v>
       </c>
       <c r="J522">
-        <v>2.102353072638375</v>
+        <v>1.612464075822789</v>
       </c>
       <c r="K522">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="L522">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="M522">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="N522">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="O522">
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27559,46 +27598,546 @@
         <v>69</v>
       </c>
       <c r="C523">
+        <v>-1.200730499577917</v>
+      </c>
+      <c r="D523" t="s">
+        <v>161</v>
+      </c>
+      <c r="E523">
+        <v>-1.299794110866277</v>
+      </c>
+      <c r="F523">
+        <v>1</v>
+      </c>
+      <c r="G523">
+        <v>0.009120730499577918</v>
+      </c>
+      <c r="H523">
+        <v>0.009339794110866276</v>
+      </c>
+      <c r="I523">
+        <v>-0.0990636112883605</v>
+      </c>
+      <c r="J523">
+        <v>1.767373458759561</v>
+      </c>
+      <c r="K523">
+        <v>2.92</v>
+      </c>
+      <c r="L523">
+        <v>3.96</v>
+      </c>
+      <c r="M523">
+        <v>3.01</v>
+      </c>
+      <c r="N523">
+        <v>4.02</v>
+      </c>
+      <c r="O523">
+        <v>1</v>
+      </c>
+      <c r="P523" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="524" spans="1:16">
+      <c r="A524" s="1">
+        <v>0</v>
+      </c>
+      <c r="B524" t="s">
+        <v>70</v>
+      </c>
+      <c r="C524">
+        <v>-1.31133913278049</v>
+      </c>
+      <c r="D524" t="s">
+        <v>161</v>
+      </c>
+      <c r="E524">
+        <v>-1.374720406030469</v>
+      </c>
+      <c r="F524">
+        <v>1</v>
+      </c>
+      <c r="G524">
+        <v>0.009191339132780489</v>
+      </c>
+      <c r="H524">
+        <v>0.009414720406030469</v>
+      </c>
+      <c r="I524">
+        <v>-0.06338127324997922</v>
+      </c>
+      <c r="J524">
+        <v>1.79226591562474</v>
+      </c>
+      <c r="K524">
+        <v>2.93</v>
+      </c>
+      <c r="L524">
+        <v>3.94</v>
+      </c>
+      <c r="M524">
+        <v>3.01</v>
+      </c>
+      <c r="N524">
+        <v>4.02</v>
+      </c>
+      <c r="O524">
+        <v>1</v>
+      </c>
+      <c r="P524" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="525" spans="1:16">
+      <c r="A525" s="1">
+        <v>0</v>
+      </c>
+      <c r="B525" t="s">
+        <v>70</v>
+      </c>
+      <c r="C525">
+        <v>-1.373574858755723</v>
+      </c>
+      <c r="D525" t="s">
+        <v>161</v>
+      </c>
+      <c r="E525">
+        <v>-1.43865540097431</v>
+      </c>
+      <c r="F525">
+        <v>1</v>
+      </c>
+      <c r="G525">
+        <v>0.009253574858755723</v>
+      </c>
+      <c r="H525">
+        <v>0.009478655400974308</v>
+      </c>
+      <c r="I525">
+        <v>-0.06508054221858606</v>
+      </c>
+      <c r="J525">
+        <v>1.813506777732329</v>
+      </c>
+      <c r="K525">
+        <v>2.93</v>
+      </c>
+      <c r="L525">
+        <v>3.94</v>
+      </c>
+      <c r="M525">
+        <v>3.01</v>
+      </c>
+      <c r="N525">
+        <v>4.02</v>
+      </c>
+      <c r="O525">
+        <v>1</v>
+      </c>
+      <c r="P525" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="526" spans="1:16">
+      <c r="A526" s="1">
+        <v>0</v>
+      </c>
+      <c r="B526" t="s">
+        <v>70</v>
+      </c>
+      <c r="C526">
+        <v>-1.4408139089922</v>
+      </c>
+      <c r="D526" t="s">
+        <v>161</v>
+      </c>
+      <c r="E526">
+        <v>-1.507730329715536</v>
+      </c>
+      <c r="F526">
+        <v>1</v>
+      </c>
+      <c r="G526">
+        <v>0.0093208139089922</v>
+      </c>
+      <c r="H526">
+        <v>0.009547730329715535</v>
+      </c>
+      <c r="I526">
+        <v>-0.06691642072333659</v>
+      </c>
+      <c r="J526">
+        <v>1.836455259041706</v>
+      </c>
+      <c r="K526">
+        <v>2.93</v>
+      </c>
+      <c r="L526">
+        <v>3.94</v>
+      </c>
+      <c r="M526">
+        <v>3.01</v>
+      </c>
+      <c r="N526">
+        <v>4.02</v>
+      </c>
+      <c r="O526">
+        <v>1</v>
+      </c>
+      <c r="P526" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="527" spans="1:16">
+      <c r="A527" s="1">
+        <v>0</v>
+      </c>
+      <c r="B527" t="s">
+        <v>70</v>
+      </c>
+      <c r="C527">
+        <v>-1.521723594964679</v>
+      </c>
+      <c r="D527" t="s">
+        <v>161</v>
+      </c>
+      <c r="E527">
+        <v>-1.590849153871564</v>
+      </c>
+      <c r="F527">
+        <v>1</v>
+      </c>
+      <c r="G527">
+        <v>0.009401723594964679</v>
+      </c>
+      <c r="H527">
+        <v>0.009630849153871562</v>
+      </c>
+      <c r="I527">
+        <v>-0.06912555890688532</v>
+      </c>
+      <c r="J527">
+        <v>1.864069486336068</v>
+      </c>
+      <c r="K527">
+        <v>2.93</v>
+      </c>
+      <c r="L527">
+        <v>3.94</v>
+      </c>
+      <c r="M527">
+        <v>3.01</v>
+      </c>
+      <c r="N527">
+        <v>4.02</v>
+      </c>
+      <c r="O527">
+        <v>1</v>
+      </c>
+      <c r="P527" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="528" spans="1:16">
+      <c r="A528" s="1">
+        <v>0</v>
+      </c>
+      <c r="B528" t="s">
+        <v>70</v>
+      </c>
+      <c r="C528">
+        <v>-1.628715610790191</v>
+      </c>
+      <c r="D528" t="s">
+        <v>161</v>
+      </c>
+      <c r="E528">
+        <v>-1.700762453405623</v>
+      </c>
+      <c r="F528">
+        <v>1</v>
+      </c>
+      <c r="G528">
+        <v>0.00950871561079019</v>
+      </c>
+      <c r="H528">
+        <v>0.009740762453405622</v>
+      </c>
+      <c r="I528">
+        <v>-0.07204684261543237</v>
+      </c>
+      <c r="J528">
+        <v>1.900585532692898</v>
+      </c>
+      <c r="K528">
+        <v>2.93</v>
+      </c>
+      <c r="L528">
+        <v>3.94</v>
+      </c>
+      <c r="M528">
+        <v>3.01</v>
+      </c>
+      <c r="N528">
+        <v>4.02</v>
+      </c>
+      <c r="O528">
+        <v>1</v>
+      </c>
+      <c r="P528" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="529" spans="1:16">
+      <c r="A529" s="1">
+        <v>0</v>
+      </c>
+      <c r="B529" t="s">
+        <v>70</v>
+      </c>
+      <c r="C529">
+        <v>-1.742090429723469</v>
+      </c>
+      <c r="D529" t="s">
+        <v>161</v>
+      </c>
+      <c r="E529">
+        <v>-1.817232830535031</v>
+      </c>
+      <c r="F529">
+        <v>1</v>
+      </c>
+      <c r="G529">
+        <v>0.00962209042972347</v>
+      </c>
+      <c r="H529">
+        <v>0.009857232830535028</v>
+      </c>
+      <c r="I529">
+        <v>-0.07514240081156176</v>
+      </c>
+      <c r="J529">
+        <v>1.939280010144528</v>
+      </c>
+      <c r="K529">
+        <v>2.93</v>
+      </c>
+      <c r="L529">
+        <v>3.94</v>
+      </c>
+      <c r="M529">
+        <v>3.01</v>
+      </c>
+      <c r="N529">
+        <v>4.02</v>
+      </c>
+      <c r="O529">
+        <v>1</v>
+      </c>
+      <c r="P529" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="530" spans="1:16">
+      <c r="A530" s="1">
+        <v>0</v>
+      </c>
+      <c r="B530" t="s">
+        <v>70</v>
+      </c>
+      <c r="C530">
+        <v>-2.032299133215826</v>
+      </c>
+      <c r="D530" t="s">
+        <v>161</v>
+      </c>
+      <c r="E530">
+        <v>-2.115365321153458</v>
+      </c>
+      <c r="F530">
+        <v>1</v>
+      </c>
+      <c r="G530">
+        <v>0.009912299133215825</v>
+      </c>
+      <c r="H530">
+        <v>0.01015536532115346</v>
+      </c>
+      <c r="I530">
+        <v>-0.08306618793763265</v>
+      </c>
+      <c r="J530">
+        <v>2.038327349220418</v>
+      </c>
+      <c r="K530">
+        <v>2.93</v>
+      </c>
+      <c r="L530">
+        <v>3.94</v>
+      </c>
+      <c r="M530">
+        <v>3.01</v>
+      </c>
+      <c r="N530">
+        <v>4.02</v>
+      </c>
+      <c r="O530">
+        <v>1</v>
+      </c>
+      <c r="P530" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="531" spans="1:16">
+      <c r="A531" s="1">
+        <v>0</v>
+      </c>
+      <c r="B531" t="s">
+        <v>70</v>
+      </c>
+      <c r="C531">
+        <v>-2.29423940751651</v>
+      </c>
+      <c r="D531" t="s">
+        <v>161</v>
+      </c>
+      <c r="E531">
+        <v>-2.384457548336073</v>
+      </c>
+      <c r="F531">
+        <v>1</v>
+      </c>
+      <c r="G531">
+        <v>0.01017423940751651</v>
+      </c>
+      <c r="H531">
+        <v>0.01042445754833607</v>
+      </c>
+      <c r="I531">
+        <v>-0.09021814081956281</v>
+      </c>
+      <c r="J531">
+        <v>2.127726760244542</v>
+      </c>
+      <c r="K531">
+        <v>2.93</v>
+      </c>
+      <c r="L531">
+        <v>3.94</v>
+      </c>
+      <c r="M531">
+        <v>3.01</v>
+      </c>
+      <c r="N531">
+        <v>4.02</v>
+      </c>
+      <c r="O531">
+        <v>1</v>
+      </c>
+      <c r="P531" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="532" spans="1:16">
+      <c r="A532" s="1">
+        <v>0</v>
+      </c>
+      <c r="B532" t="s">
+        <v>71</v>
+      </c>
+      <c r="C532">
+        <v>-1.484070927407007</v>
+      </c>
+      <c r="D532" t="s">
+        <v>162</v>
+      </c>
+      <c r="E532">
+        <v>-1.906588603387449</v>
+      </c>
+      <c r="F532">
+        <v>-1</v>
+      </c>
+      <c r="G532">
+        <v>0.009364070927407006</v>
+      </c>
+      <c r="H532">
+        <v>0.009866588603387448</v>
+      </c>
+      <c r="I532">
+        <v>0.4225176759804423</v>
+      </c>
+      <c r="J532">
+        <v>2.102353072638375</v>
+      </c>
+      <c r="K532">
+        <v>2.58</v>
+      </c>
+      <c r="L532">
+        <v>3.94</v>
+      </c>
+      <c r="M532">
+        <v>2.8</v>
+      </c>
+      <c r="N532">
+        <v>3.98</v>
+      </c>
+      <c r="O532">
+        <v>1</v>
+      </c>
+      <c r="P532" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="533" spans="1:16">
+      <c r="A533" s="1">
+        <v>0</v>
+      </c>
+      <c r="B533" t="s">
+        <v>71</v>
+      </c>
+      <c r="C533">
         <v>-1.073545579884814</v>
       </c>
-      <c r="D523" t="s">
-        <v>159</v>
-      </c>
-      <c r="E523">
+      <c r="D533" t="s">
+        <v>162</v>
+      </c>
+      <c r="E533">
         <v>-1.461057218479642</v>
       </c>
-      <c r="F523">
-        <v>-1</v>
-      </c>
-      <c r="G523">
+      <c r="F533">
+        <v>-1</v>
+      </c>
+      <c r="G533">
         <v>0.008953545579884814</v>
       </c>
-      <c r="H523">
+      <c r="H533">
         <v>0.009421057218479642</v>
       </c>
-      <c r="I523">
+      <c r="I533">
         <v>0.3875116385948285</v>
       </c>
-      <c r="J523">
+      <c r="J533">
         <v>1.943234720885587</v>
       </c>
-      <c r="K523">
+      <c r="K533">
         <v>2.58</v>
       </c>
-      <c r="L523">
+      <c r="L533">
         <v>3.94</v>
       </c>
-      <c r="M523">
+      <c r="M533">
         <v>2.8</v>
       </c>
-      <c r="N523">
+      <c r="N533">
         <v>3.98</v>
       </c>
-      <c r="O523">
-        <v>1</v>
-      </c>
-      <c r="P523" t="s">
-        <v>359</v>
+      <c r="O533">
+        <v>1</v>
+      </c>
+      <c r="P533" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="388">
   <si>
     <t>trade_time</t>
   </si>
@@ -223,12 +223,12 @@
     <t>2020-11-26</t>
   </si>
   <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
     <t>2021-08-10</t>
   </si>
   <si>
+    <t>2021-08-11</t>
+  </si>
+  <si>
     <t>2021-07-27</t>
   </si>
   <si>
@@ -499,7 +499,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-11</t>
+    <t>2021-08-12</t>
   </si>
   <si>
     <t>2021-08-03</t>
@@ -1127,6 +1127,51 @@
   </si>
   <si>
     <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>2021-05-10</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>2021-05-12</t>
+  </si>
+  <si>
+    <t>2021-05-13</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-05-18</t>
+  </si>
+  <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
+    <t>2021-05-24</t>
+  </si>
+  <si>
+    <t>2021-05-25</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
   </si>
   <si>
     <t>2021-06-02</t>
@@ -1490,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P533"/>
+  <dimension ref="A1:P549"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -27548,40 +27593,40 @@
         <v>69</v>
       </c>
       <c r="C522">
-        <v>-0.7483951014025427</v>
+        <v>-0.784519742160771</v>
       </c>
       <c r="D522" t="s">
         <v>161</v>
       </c>
       <c r="E522">
-        <v>-0.8335168682265941</v>
+        <v>-0.8857661497430493</v>
       </c>
       <c r="F522">
         <v>1</v>
       </c>
       <c r="G522">
-        <v>0.008668395101402541</v>
+        <v>0.008664519742160771</v>
       </c>
       <c r="H522">
-        <v>0.008873516868226593</v>
+        <v>0.008885766149743049</v>
       </c>
       <c r="I522">
-        <v>-0.08512176682405137</v>
+        <v>-0.1012464075822783</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
       </c>
       <c r="K522">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="L522">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="M522">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N522">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27598,40 +27643,40 @@
         <v>69</v>
       </c>
       <c r="C523">
-        <v>-1.200730499577917</v>
+        <v>-1.238404234165513</v>
       </c>
       <c r="D523" t="s">
         <v>161</v>
       </c>
       <c r="E523">
-        <v>-1.299794110866277</v>
+        <v>-1.355141580041469</v>
       </c>
       <c r="F523">
         <v>1</v>
       </c>
       <c r="G523">
-        <v>0.009120730499577918</v>
+        <v>0.009118404234165513</v>
       </c>
       <c r="H523">
-        <v>0.009339794110866276</v>
+        <v>0.009355141580041469</v>
       </c>
       <c r="I523">
-        <v>-0.0990636112883605</v>
+        <v>-0.1167373458759555</v>
       </c>
       <c r="J523">
         <v>1.767373458759561</v>
       </c>
       <c r="K523">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="L523">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="M523">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N523">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27645,7 +27690,7 @@
         <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C524">
         <v>-1.31133913278049</v>
@@ -27654,7 +27699,7 @@
         <v>161</v>
       </c>
       <c r="E524">
-        <v>-1.374720406030469</v>
+        <v>-1.430565724342963</v>
       </c>
       <c r="F524">
         <v>1</v>
@@ -27663,10 +27708,10 @@
         <v>0.009191339132780489</v>
       </c>
       <c r="H524">
-        <v>0.009414720406030469</v>
+        <v>0.009430565724342962</v>
       </c>
       <c r="I524">
-        <v>-0.06338127324997922</v>
+        <v>-0.1192265915624735</v>
       </c>
       <c r="J524">
         <v>1.79226591562474</v>
@@ -27678,10 +27723,10 @@
         <v>3.94</v>
       </c>
       <c r="M524">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N524">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27695,7 +27740,7 @@
         <v>0</v>
       </c>
       <c r="B525" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C525">
         <v>-1.373574858755723</v>
@@ -27704,7 +27749,7 @@
         <v>161</v>
       </c>
       <c r="E525">
-        <v>-1.43865540097431</v>
+        <v>-1.494925536528956</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27713,10 +27758,10 @@
         <v>0.009253574858755723</v>
       </c>
       <c r="H525">
-        <v>0.009478655400974308</v>
+        <v>0.009494925536528956</v>
       </c>
       <c r="I525">
-        <v>-0.06508054221858606</v>
+        <v>-0.1213506777732323</v>
       </c>
       <c r="J525">
         <v>1.813506777732329</v>
@@ -27728,10 +27773,10 @@
         <v>3.94</v>
       </c>
       <c r="M525">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N525">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27745,7 +27790,7 @@
         <v>0</v>
       </c>
       <c r="B526" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C526">
         <v>-1.4408139089922</v>
@@ -27754,7 +27799,7 @@
         <v>161</v>
       </c>
       <c r="E526">
-        <v>-1.507730329715536</v>
+        <v>-1.56445943489637</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27763,10 +27808,10 @@
         <v>0.0093208139089922</v>
       </c>
       <c r="H526">
-        <v>0.009547730329715535</v>
+        <v>0.009564459434896372</v>
       </c>
       <c r="I526">
-        <v>-0.06691642072333659</v>
+        <v>-0.1236455259041702</v>
       </c>
       <c r="J526">
         <v>1.836455259041706</v>
@@ -27778,10 +27823,10 @@
         <v>3.94</v>
       </c>
       <c r="M526">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N526">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27795,7 +27840,7 @@
         <v>0</v>
       </c>
       <c r="B527" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C527">
         <v>-1.521723594964679</v>
@@ -27804,7 +27849,7 @@
         <v>161</v>
       </c>
       <c r="E527">
-        <v>-1.590849153871564</v>
+        <v>-1.648130543598285</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27813,10 +27858,10 @@
         <v>0.009401723594964679</v>
       </c>
       <c r="H527">
-        <v>0.009630849153871562</v>
+        <v>0.009648130543598286</v>
       </c>
       <c r="I527">
-        <v>-0.06912555890688532</v>
+        <v>-0.1264069486336061</v>
       </c>
       <c r="J527">
         <v>1.864069486336068</v>
@@ -27828,10 +27873,10 @@
         <v>3.94</v>
       </c>
       <c r="M527">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N527">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27848,40 +27893,40 @@
         <v>70</v>
       </c>
       <c r="C528">
-        <v>-1.628715610790191</v>
+        <v>-1.700762453405623</v>
       </c>
       <c r="D528" t="s">
         <v>161</v>
       </c>
       <c r="E528">
-        <v>-1.700762453405623</v>
+        <v>-1.758774164059481</v>
       </c>
       <c r="F528">
         <v>1</v>
       </c>
       <c r="G528">
-        <v>0.00950871561079019</v>
+        <v>0.009740762453405622</v>
       </c>
       <c r="H528">
-        <v>0.009740762453405622</v>
+        <v>0.009758774164059481</v>
       </c>
       <c r="I528">
-        <v>-0.07204684261543237</v>
+        <v>-0.05801171065385713</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
       </c>
       <c r="K528">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L528">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M528">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N528">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27898,40 +27943,40 @@
         <v>70</v>
       </c>
       <c r="C529">
-        <v>-1.742090429723469</v>
+        <v>-1.817232830535031</v>
       </c>
       <c r="D529" t="s">
         <v>161</v>
       </c>
       <c r="E529">
-        <v>-1.817232830535031</v>
+        <v>-1.876018430737921</v>
       </c>
       <c r="F529">
         <v>1</v>
       </c>
       <c r="G529">
-        <v>0.00962209042972347</v>
+        <v>0.009857232830535028</v>
       </c>
       <c r="H529">
-        <v>0.009857232830535028</v>
+        <v>0.009876018430737921</v>
       </c>
       <c r="I529">
-        <v>-0.07514240081156176</v>
+        <v>-0.05878560020289036</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
       </c>
       <c r="K529">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L529">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M529">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N529">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27948,40 +27993,40 @@
         <v>70</v>
       </c>
       <c r="C530">
-        <v>-2.032299133215826</v>
+        <v>-2.115365321153458</v>
       </c>
       <c r="D530" t="s">
         <v>161</v>
       </c>
       <c r="E530">
-        <v>-2.115365321153458</v>
+        <v>-2.176131868137866</v>
       </c>
       <c r="F530">
         <v>1</v>
       </c>
       <c r="G530">
-        <v>0.009912299133215825</v>
+        <v>0.01015536532115346</v>
       </c>
       <c r="H530">
-        <v>0.01015536532115346</v>
+        <v>0.01017613186813787</v>
       </c>
       <c r="I530">
-        <v>-0.08306618793763265</v>
+        <v>-0.06076654698440809</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
       </c>
       <c r="K530">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L530">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M530">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N530">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -27998,40 +28043,40 @@
         <v>70</v>
       </c>
       <c r="C531">
-        <v>-2.29423940751651</v>
+        <v>-2.384457548336073</v>
       </c>
       <c r="D531" t="s">
         <v>161</v>
       </c>
       <c r="E531">
-        <v>-2.384457548336073</v>
+        <v>-2.447012083540963</v>
       </c>
       <c r="F531">
         <v>1</v>
       </c>
       <c r="G531">
-        <v>0.01017423940751651</v>
+        <v>0.01042445754833607</v>
       </c>
       <c r="H531">
-        <v>0.01042445754833607</v>
+        <v>0.01044701208354096</v>
       </c>
       <c r="I531">
-        <v>-0.09021814081956281</v>
+        <v>-0.06255453520489063</v>
       </c>
       <c r="J531">
         <v>2.127726760244542</v>
       </c>
       <c r="K531">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L531">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M531">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="N531">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28045,43 +28090,43 @@
         <v>0</v>
       </c>
       <c r="B532" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C532">
-        <v>-1.484070927407007</v>
+        <v>-2.488425729237733</v>
       </c>
       <c r="D532" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E532">
-        <v>-1.906588603387449</v>
+        <v>-2.551671082920375</v>
       </c>
       <c r="F532">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G532">
-        <v>0.009364070927407006</v>
+        <v>0.01052842572923773</v>
       </c>
       <c r="H532">
-        <v>0.009866588603387448</v>
+        <v>0.01055167108292038</v>
       </c>
       <c r="I532">
-        <v>0.4225176759804423</v>
+        <v>-0.0632453536826425</v>
       </c>
       <c r="J532">
-        <v>2.102353072638375</v>
+        <v>2.162267684132137</v>
       </c>
       <c r="K532">
-        <v>2.58</v>
+        <v>3.01</v>
       </c>
       <c r="L532">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M532">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="N532">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28095,49 +28140,849 @@
         <v>0</v>
       </c>
       <c r="B533" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C533">
-        <v>-1.073545579884814</v>
+        <v>-2.659724005112058</v>
       </c>
       <c r="D533" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E533">
-        <v>-1.461057218479642</v>
+        <v>-2.724107553318782</v>
       </c>
       <c r="F533">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G533">
-        <v>0.008953545579884814</v>
+        <v>0.01069972400511206</v>
       </c>
       <c r="H533">
-        <v>0.009421057218479642</v>
+        <v>0.01072410755331878</v>
       </c>
       <c r="I533">
-        <v>0.3875116385948285</v>
+        <v>-0.06438354820672387</v>
       </c>
       <c r="J533">
-        <v>1.943234720885587</v>
+        <v>2.219177410336232</v>
       </c>
       <c r="K533">
-        <v>2.58</v>
+        <v>3.01</v>
       </c>
       <c r="L533">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M533">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="N533">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="534" spans="1:16">
+      <c r="A534" s="1">
+        <v>0</v>
+      </c>
+      <c r="B534" t="s">
+        <v>70</v>
+      </c>
+      <c r="C534">
+        <v>-2.874392888877765</v>
+      </c>
+      <c r="D534" t="s">
+        <v>161</v>
+      </c>
+      <c r="E534">
+        <v>-2.940202808405191</v>
+      </c>
+      <c r="F534">
+        <v>1</v>
+      </c>
+      <c r="G534">
+        <v>0.01091439288887776</v>
+      </c>
+      <c r="H534">
+        <v>0.01094020280840519</v>
+      </c>
+      <c r="I534">
+        <v>-0.06580991952742643</v>
+      </c>
+      <c r="J534">
+        <v>2.29049597637135</v>
+      </c>
+      <c r="K534">
+        <v>3.01</v>
+      </c>
+      <c r="L534">
+        <v>4.02</v>
+      </c>
+      <c r="M534">
+        <v>3.03</v>
+      </c>
+      <c r="N534">
+        <v>4</v>
+      </c>
+      <c r="O534">
+        <v>1</v>
+      </c>
+      <c r="P534" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="535" spans="1:16">
+      <c r="A535" s="1">
+        <v>0</v>
+      </c>
+      <c r="B535" t="s">
+        <v>70</v>
+      </c>
+      <c r="C535">
+        <v>-3.030268785898139</v>
+      </c>
+      <c r="D535" t="s">
+        <v>161</v>
+      </c>
+      <c r="E535">
+        <v>-3.097114425671548</v>
+      </c>
+      <c r="F535">
+        <v>1</v>
+      </c>
+      <c r="G535">
+        <v>0.01107026878589814</v>
+      </c>
+      <c r="H535">
+        <v>0.01109711442567155</v>
+      </c>
+      <c r="I535">
+        <v>-0.06684563977340918</v>
+      </c>
+      <c r="J535">
+        <v>2.342281988670478</v>
+      </c>
+      <c r="K535">
+        <v>3.01</v>
+      </c>
+      <c r="L535">
+        <v>4.02</v>
+      </c>
+      <c r="M535">
+        <v>3.03</v>
+      </c>
+      <c r="N535">
+        <v>4</v>
+      </c>
+      <c r="O535">
+        <v>1</v>
+      </c>
+      <c r="P535" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="536" spans="1:16">
+      <c r="A536" s="1">
+        <v>0</v>
+      </c>
+      <c r="B536" t="s">
+        <v>70</v>
+      </c>
+      <c r="C536">
+        <v>-3.164233352176372</v>
+      </c>
+      <c r="D536" t="s">
+        <v>161</v>
+      </c>
+      <c r="E536">
+        <v>-3.231969121958274</v>
+      </c>
+      <c r="F536">
+        <v>1</v>
+      </c>
+      <c r="G536">
+        <v>0.01120423335217637</v>
+      </c>
+      <c r="H536">
+        <v>0.01123196912195827</v>
+      </c>
+      <c r="I536">
+        <v>-0.0677357697819021</v>
+      </c>
+      <c r="J536">
+        <v>2.38678848909514</v>
+      </c>
+      <c r="K536">
+        <v>3.01</v>
+      </c>
+      <c r="L536">
+        <v>4.02</v>
+      </c>
+      <c r="M536">
+        <v>3.03</v>
+      </c>
+      <c r="N536">
+        <v>4</v>
+      </c>
+      <c r="O536">
+        <v>1</v>
+      </c>
+      <c r="P536" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="537" spans="1:16">
+      <c r="A537" s="1">
+        <v>0</v>
+      </c>
+      <c r="B537" t="s">
+        <v>70</v>
+      </c>
+      <c r="C537">
+        <v>-3.195519883576577</v>
+      </c>
+      <c r="D537" t="s">
+        <v>161</v>
+      </c>
+      <c r="E537">
+        <v>-3.263463537288049</v>
+      </c>
+      <c r="F537">
+        <v>1</v>
+      </c>
+      <c r="G537">
+        <v>0.01123551988357658</v>
+      </c>
+      <c r="H537">
+        <v>0.01126346353728805</v>
+      </c>
+      <c r="I537">
+        <v>-0.06794365371147215</v>
+      </c>
+      <c r="J537">
+        <v>2.397182685573614</v>
+      </c>
+      <c r="K537">
+        <v>3.01</v>
+      </c>
+      <c r="L537">
+        <v>4.02</v>
+      </c>
+      <c r="M537">
+        <v>3.03</v>
+      </c>
+      <c r="N537">
+        <v>4</v>
+      </c>
+      <c r="O537">
+        <v>1</v>
+      </c>
+      <c r="P537" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="538" spans="1:16">
+      <c r="A538" s="1">
+        <v>0</v>
+      </c>
+      <c r="B538" t="s">
+        <v>70</v>
+      </c>
+      <c r="C538">
+        <v>-3.217402384054332</v>
+      </c>
+      <c r="D538" t="s">
+        <v>161</v>
+      </c>
+      <c r="E538">
+        <v>-3.285491436440075</v>
+      </c>
+      <c r="F538">
+        <v>1</v>
+      </c>
+      <c r="G538">
+        <v>0.01125740238405433</v>
+      </c>
+      <c r="H538">
+        <v>0.01128549143644007</v>
+      </c>
+      <c r="I538">
+        <v>-0.06808905238574248</v>
+      </c>
+      <c r="J538">
+        <v>2.404452619287154</v>
+      </c>
+      <c r="K538">
+        <v>3.01</v>
+      </c>
+      <c r="L538">
+        <v>4.02</v>
+      </c>
+      <c r="M538">
+        <v>3.03</v>
+      </c>
+      <c r="N538">
+        <v>4</v>
+      </c>
+      <c r="O538">
+        <v>1</v>
+      </c>
+      <c r="P538" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="539" spans="1:16">
+      <c r="A539" s="1">
+        <v>0</v>
+      </c>
+      <c r="B539" t="s">
+        <v>70</v>
+      </c>
+      <c r="C539">
+        <v>-3.162920244715197</v>
+      </c>
+      <c r="D539" t="s">
+        <v>161</v>
+      </c>
+      <c r="E539">
+        <v>-3.23064728953058</v>
+      </c>
+      <c r="F539">
+        <v>1</v>
+      </c>
+      <c r="G539">
+        <v>0.0112029202447152</v>
+      </c>
+      <c r="H539">
+        <v>0.01123064728953058</v>
+      </c>
+      <c r="I539">
+        <v>-0.06772704481538305</v>
+      </c>
+      <c r="J539">
+        <v>2.386352240769169</v>
+      </c>
+      <c r="K539">
+        <v>3.01</v>
+      </c>
+      <c r="L539">
+        <v>4.02</v>
+      </c>
+      <c r="M539">
+        <v>3.03</v>
+      </c>
+      <c r="N539">
+        <v>4</v>
+      </c>
+      <c r="O539">
+        <v>1</v>
+      </c>
+      <c r="P539" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="540" spans="1:16">
+      <c r="A540" s="1">
+        <v>0</v>
+      </c>
+      <c r="B540" t="s">
+        <v>70</v>
+      </c>
+      <c r="C540">
+        <v>-3.117164533557272</v>
+      </c>
+      <c r="D540" t="s">
+        <v>161</v>
+      </c>
+      <c r="E540">
+        <v>-3.184587553713798</v>
+      </c>
+      <c r="F540">
+        <v>1</v>
+      </c>
+      <c r="G540">
+        <v>0.01115716453355727</v>
+      </c>
+      <c r="H540">
+        <v>0.0111845875537138</v>
+      </c>
+      <c r="I540">
+        <v>-0.06742302015652601</v>
+      </c>
+      <c r="J540">
+        <v>2.371151007826336</v>
+      </c>
+      <c r="K540">
+        <v>3.01</v>
+      </c>
+      <c r="L540">
+        <v>4.02</v>
+      </c>
+      <c r="M540">
+        <v>3.03</v>
+      </c>
+      <c r="N540">
+        <v>4</v>
+      </c>
+      <c r="O540">
+        <v>1</v>
+      </c>
+      <c r="P540" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="541" spans="1:16">
+      <c r="A541" s="1">
+        <v>0</v>
+      </c>
+      <c r="B541" t="s">
+        <v>70</v>
+      </c>
+      <c r="C541">
+        <v>-3.07014367427936</v>
+      </c>
+      <c r="D541" t="s">
+        <v>161</v>
+      </c>
+      <c r="E541">
+        <v>-3.137254263477229</v>
+      </c>
+      <c r="F541">
+        <v>1</v>
+      </c>
+      <c r="G541">
+        <v>0.01111014367427936</v>
+      </c>
+      <c r="H541">
+        <v>0.01113725426347723</v>
+      </c>
+      <c r="I541">
+        <v>-0.06711058919786872</v>
+      </c>
+      <c r="J541">
+        <v>2.355529459893475</v>
+      </c>
+      <c r="K541">
+        <v>3.01</v>
+      </c>
+      <c r="L541">
+        <v>4.02</v>
+      </c>
+      <c r="M541">
+        <v>3.03</v>
+      </c>
+      <c r="N541">
+        <v>4</v>
+      </c>
+      <c r="O541">
+        <v>1</v>
+      </c>
+      <c r="P541" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="542" spans="1:16">
+      <c r="A542" s="1">
+        <v>0</v>
+      </c>
+      <c r="B542" t="s">
+        <v>70</v>
+      </c>
+      <c r="C542">
+        <v>-3.050749658757123</v>
+      </c>
+      <c r="D542" t="s">
+        <v>161</v>
+      </c>
+      <c r="E542">
+        <v>-3.117731384064479</v>
+      </c>
+      <c r="F542">
+        <v>1</v>
+      </c>
+      <c r="G542">
+        <v>0.01109074965875712</v>
+      </c>
+      <c r="H542">
+        <v>0.01111773138406448</v>
+      </c>
+      <c r="I542">
+        <v>-0.06698172530735569</v>
+      </c>
+      <c r="J542">
+        <v>2.349086265367815</v>
+      </c>
+      <c r="K542">
+        <v>3.01</v>
+      </c>
+      <c r="L542">
+        <v>4.02</v>
+      </c>
+      <c r="M542">
+        <v>3.03</v>
+      </c>
+      <c r="N542">
+        <v>4</v>
+      </c>
+      <c r="O542">
+        <v>1</v>
+      </c>
+      <c r="P542" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="543" spans="1:16">
+      <c r="A543" s="1">
+        <v>0</v>
+      </c>
+      <c r="B543" t="s">
+        <v>70</v>
+      </c>
+      <c r="C543">
+        <v>-2.975413246666379</v>
+      </c>
+      <c r="D543" t="s">
+        <v>161</v>
+      </c>
+      <c r="E543">
+        <v>-3.041894397807019</v>
+      </c>
+      <c r="F543">
+        <v>1</v>
+      </c>
+      <c r="G543">
+        <v>0.01101541324666638</v>
+      </c>
+      <c r="H543">
+        <v>0.01104189439780702</v>
+      </c>
+      <c r="I543">
+        <v>-0.06648115114064002</v>
+      </c>
+      <c r="J543">
+        <v>2.324057557032019</v>
+      </c>
+      <c r="K543">
+        <v>3.01</v>
+      </c>
+      <c r="L543">
+        <v>4.02</v>
+      </c>
+      <c r="M543">
+        <v>3.03</v>
+      </c>
+      <c r="N543">
+        <v>4</v>
+      </c>
+      <c r="O543">
+        <v>1</v>
+      </c>
+      <c r="P543" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="544" spans="1:16">
+      <c r="A544" s="1">
+        <v>0</v>
+      </c>
+      <c r="B544" t="s">
+        <v>70</v>
+      </c>
+      <c r="C544">
+        <v>-2.912247903214602</v>
+      </c>
+      <c r="D544" t="s">
+        <v>161</v>
+      </c>
+      <c r="E544">
+        <v>-2.978309351076493</v>
+      </c>
+      <c r="F544">
+        <v>1</v>
+      </c>
+      <c r="G544">
+        <v>0.0109522479032146</v>
+      </c>
+      <c r="H544">
+        <v>0.01097830935107649</v>
+      </c>
+      <c r="I544">
+        <v>-0.06606144786189017</v>
+      </c>
+      <c r="J544">
+        <v>2.303072393094552</v>
+      </c>
+      <c r="K544">
+        <v>3.01</v>
+      </c>
+      <c r="L544">
+        <v>4.02</v>
+      </c>
+      <c r="M544">
+        <v>3.03</v>
+      </c>
+      <c r="N544">
+        <v>4</v>
+      </c>
+      <c r="O544">
+        <v>1</v>
+      </c>
+      <c r="P544" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="545" spans="1:16">
+      <c r="A545" s="1">
+        <v>0</v>
+      </c>
+      <c r="B545" t="s">
+        <v>70</v>
+      </c>
+      <c r="C545">
+        <v>-2.818195860753343</v>
+      </c>
+      <c r="D545" t="s">
+        <v>161</v>
+      </c>
+      <c r="E545">
+        <v>-2.883632378100542</v>
+      </c>
+      <c r="F545">
+        <v>1</v>
+      </c>
+      <c r="G545">
+        <v>0.01085819586075334</v>
+      </c>
+      <c r="H545">
+        <v>0.01088363237810054</v>
+      </c>
+      <c r="I545">
+        <v>-0.06543651734719802</v>
+      </c>
+      <c r="J545">
+        <v>2.271825867359915</v>
+      </c>
+      <c r="K545">
+        <v>3.01</v>
+      </c>
+      <c r="L545">
+        <v>4.02</v>
+      </c>
+      <c r="M545">
+        <v>3.03</v>
+      </c>
+      <c r="N545">
+        <v>4</v>
+      </c>
+      <c r="O545">
+        <v>1</v>
+      </c>
+      <c r="P545" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="546" spans="1:16">
+      <c r="A546" s="1">
+        <v>0</v>
+      </c>
+      <c r="B546" t="s">
+        <v>70</v>
+      </c>
+      <c r="C546">
+        <v>-2.732508902923009</v>
+      </c>
+      <c r="D546" t="s">
+        <v>161</v>
+      </c>
+      <c r="E546">
+        <v>-2.797376071713194</v>
+      </c>
+      <c r="F546">
+        <v>1</v>
+      </c>
+      <c r="G546">
+        <v>0.01077250890292301</v>
+      </c>
+      <c r="H546">
+        <v>0.0107973760717132</v>
+      </c>
+      <c r="I546">
+        <v>-0.06486716879018584</v>
+      </c>
+      <c r="J546">
+        <v>2.243358439509305</v>
+      </c>
+      <c r="K546">
+        <v>3.01</v>
+      </c>
+      <c r="L546">
+        <v>4.02</v>
+      </c>
+      <c r="M546">
+        <v>3.03</v>
+      </c>
+      <c r="N546">
+        <v>4</v>
+      </c>
+      <c r="O546">
+        <v>1</v>
+      </c>
+      <c r="P546" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="547" spans="1:16">
+      <c r="A547" s="1">
+        <v>0</v>
+      </c>
+      <c r="B547" t="s">
+        <v>71</v>
+      </c>
+      <c r="C547">
+        <v>-1.484070927407007</v>
+      </c>
+      <c r="D547" t="s">
+        <v>162</v>
+      </c>
+      <c r="E547">
+        <v>-1.906588603387449</v>
+      </c>
+      <c r="F547">
+        <v>-1</v>
+      </c>
+      <c r="G547">
+        <v>0.009364070927407006</v>
+      </c>
+      <c r="H547">
+        <v>0.009866588603387448</v>
+      </c>
+      <c r="I547">
+        <v>0.4225176759804423</v>
+      </c>
+      <c r="J547">
+        <v>2.102353072638375</v>
+      </c>
+      <c r="K547">
+        <v>2.58</v>
+      </c>
+      <c r="L547">
+        <v>3.94</v>
+      </c>
+      <c r="M547">
+        <v>2.8</v>
+      </c>
+      <c r="N547">
+        <v>3.98</v>
+      </c>
+      <c r="O547">
+        <v>1</v>
+      </c>
+      <c r="P547" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="548" spans="1:16">
+      <c r="A548" s="1">
+        <v>1</v>
+      </c>
+      <c r="B548" t="s">
+        <v>70</v>
+      </c>
+      <c r="C548">
+        <v>-2.308082748641509</v>
+      </c>
+      <c r="D548" t="s">
+        <v>161</v>
+      </c>
+      <c r="E548">
+        <v>-2.370129810094276</v>
+      </c>
+      <c r="F548">
+        <v>1</v>
+      </c>
+      <c r="G548">
+        <v>0.01034808274864151</v>
+      </c>
+      <c r="H548">
+        <v>0.01037012981009428</v>
+      </c>
+      <c r="I548">
+        <v>-0.06204706145276706</v>
+      </c>
+      <c r="J548">
+        <v>2.102353072638375</v>
+      </c>
+      <c r="K548">
+        <v>3.01</v>
+      </c>
+      <c r="L548">
+        <v>4.02</v>
+      </c>
+      <c r="M548">
+        <v>3.03</v>
+      </c>
+      <c r="N548">
+        <v>4</v>
+      </c>
+      <c r="O548">
+        <v>1</v>
+      </c>
+      <c r="P548" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="549" spans="1:16">
+      <c r="A549" s="1">
+        <v>0</v>
+      </c>
+      <c r="B549" t="s">
+        <v>71</v>
+      </c>
+      <c r="C549">
+        <v>-1.073545579884814</v>
+      </c>
+      <c r="D549" t="s">
+        <v>162</v>
+      </c>
+      <c r="E549">
+        <v>-1.461057218479642</v>
+      </c>
+      <c r="F549">
+        <v>-1</v>
+      </c>
+      <c r="G549">
+        <v>0.008953545579884814</v>
+      </c>
+      <c r="H549">
+        <v>0.009421057218479642</v>
+      </c>
+      <c r="I549">
+        <v>0.3875116385948285</v>
+      </c>
+      <c r="J549">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K549">
+        <v>2.58</v>
+      </c>
+      <c r="L549">
+        <v>3.94</v>
+      </c>
+      <c r="M549">
+        <v>2.8</v>
+      </c>
+      <c r="N549">
+        <v>3.98</v>
+      </c>
+      <c r="O549">
+        <v>1</v>
+      </c>
+      <c r="P549" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -223,12 +223,12 @@
     <t>2020-11-26</t>
   </si>
   <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
     <t>2021-08-11</t>
   </si>
   <si>
+    <t>2021-08-12</t>
+  </si>
+  <si>
     <t>2021-07-27</t>
   </si>
   <si>
@@ -499,10 +499,10 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-12</t>
-  </si>
-  <si>
-    <t>2021-08-03</t>
+    <t>2021-08-16</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -27593,40 +27593,40 @@
         <v>69</v>
       </c>
       <c r="C522">
-        <v>-0.784519742160771</v>
+        <v>-0.8335168682265941</v>
       </c>
       <c r="D522" t="s">
         <v>161</v>
       </c>
       <c r="E522">
-        <v>-0.8857661497430493</v>
+        <v>-0.8263893535341893</v>
       </c>
       <c r="F522">
         <v>1</v>
       </c>
       <c r="G522">
-        <v>0.008664519742160771</v>
+        <v>0.008873516868226593</v>
       </c>
       <c r="H522">
-        <v>0.008885766149743049</v>
+        <v>0.009106389353534189</v>
       </c>
       <c r="I522">
-        <v>-0.1012464075822783</v>
+        <v>0.007127514692404802</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
       </c>
       <c r="K522">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L522">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M522">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N522">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27643,40 +27643,40 @@
         <v>69</v>
       </c>
       <c r="C523">
-        <v>-1.238404234165513</v>
+        <v>-1.299794110866277</v>
       </c>
       <c r="D523" t="s">
         <v>161</v>
       </c>
       <c r="E523">
-        <v>-1.355141580041469</v>
+        <v>-1.303510252979447</v>
       </c>
       <c r="F523">
         <v>1</v>
       </c>
       <c r="G523">
-        <v>0.009118404234165513</v>
+        <v>0.009339794110866276</v>
       </c>
       <c r="H523">
-        <v>0.009355141580041469</v>
+        <v>0.009583510252979448</v>
       </c>
       <c r="I523">
-        <v>-0.1167373458759555</v>
+        <v>-0.003716142113169951</v>
       </c>
       <c r="J523">
         <v>1.767373458759561</v>
       </c>
       <c r="K523">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L523">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M523">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N523">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27693,40 +27693,40 @@
         <v>69</v>
       </c>
       <c r="C524">
-        <v>-1.31133913278049</v>
+        <v>-1.374720406030469</v>
       </c>
       <c r="D524" t="s">
         <v>161</v>
       </c>
       <c r="E524">
-        <v>-1.430565724342963</v>
+        <v>-1.380179020124201</v>
       </c>
       <c r="F524">
         <v>1</v>
       </c>
       <c r="G524">
-        <v>0.009191339132780489</v>
+        <v>0.009414720406030469</v>
       </c>
       <c r="H524">
-        <v>0.009430565724342962</v>
+        <v>0.009660179020124201</v>
       </c>
       <c r="I524">
-        <v>-0.1192265915624735</v>
+        <v>-0.005458614093732272</v>
       </c>
       <c r="J524">
         <v>1.79226591562474</v>
       </c>
       <c r="K524">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L524">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M524">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N524">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27743,40 +27743,40 @@
         <v>69</v>
       </c>
       <c r="C525">
-        <v>-1.373574858755723</v>
+        <v>-1.43865540097431</v>
       </c>
       <c r="D525" t="s">
         <v>161</v>
       </c>
       <c r="E525">
-        <v>-1.494925536528956</v>
+        <v>-1.445600875415574</v>
       </c>
       <c r="F525">
         <v>1</v>
       </c>
       <c r="G525">
-        <v>0.009253574858755723</v>
+        <v>0.009478655400974308</v>
       </c>
       <c r="H525">
-        <v>0.009494925536528956</v>
+        <v>0.009725600875415573</v>
       </c>
       <c r="I525">
-        <v>-0.1213506777732323</v>
+        <v>-0.006945474441264032</v>
       </c>
       <c r="J525">
         <v>1.813506777732329</v>
       </c>
       <c r="K525">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L525">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M525">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N525">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27793,40 +27793,40 @@
         <v>69</v>
       </c>
       <c r="C526">
-        <v>-1.4408139089922</v>
+        <v>-1.507730329715536</v>
       </c>
       <c r="D526" t="s">
         <v>161</v>
       </c>
       <c r="E526">
-        <v>-1.56445943489637</v>
+        <v>-1.516282197848455</v>
       </c>
       <c r="F526">
         <v>1</v>
       </c>
       <c r="G526">
-        <v>0.0093208139089922</v>
+        <v>0.009547730329715535</v>
       </c>
       <c r="H526">
-        <v>0.009564459434896372</v>
+        <v>0.009796282197848456</v>
       </c>
       <c r="I526">
-        <v>-0.1236455259041702</v>
+        <v>-0.008551868132919083</v>
       </c>
       <c r="J526">
         <v>1.836455259041706</v>
       </c>
       <c r="K526">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L526">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M526">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N526">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27843,40 +27843,40 @@
         <v>69</v>
       </c>
       <c r="C527">
-        <v>-1.521723594964679</v>
+        <v>-1.590849153871564</v>
       </c>
       <c r="D527" t="s">
         <v>161</v>
       </c>
       <c r="E527">
-        <v>-1.648130543598285</v>
+        <v>-1.601334017915089</v>
       </c>
       <c r="F527">
         <v>1</v>
       </c>
       <c r="G527">
-        <v>0.009401723594964679</v>
+        <v>0.009630849153871562</v>
       </c>
       <c r="H527">
-        <v>0.009648130543598286</v>
+        <v>0.009881334017915086</v>
       </c>
       <c r="I527">
-        <v>-0.1264069486336061</v>
+        <v>-0.01048486404352467</v>
       </c>
       <c r="J527">
         <v>1.864069486336068</v>
       </c>
       <c r="K527">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="L527">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="M527">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N527">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27890,7 +27890,7 @@
         <v>0</v>
       </c>
       <c r="B528" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C528">
         <v>-1.700762453405623</v>
@@ -27899,7 +27899,7 @@
         <v>161</v>
       </c>
       <c r="E528">
-        <v>-1.758774164059481</v>
+        <v>-1.713803440694126</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27908,10 +27908,10 @@
         <v>0.009740762453405622</v>
       </c>
       <c r="H528">
-        <v>0.009758774164059481</v>
+        <v>0.009993803440694126</v>
       </c>
       <c r="I528">
-        <v>-0.05801171065385713</v>
+        <v>-0.01304098728850267</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27923,10 +27923,10 @@
         <v>4.02</v>
       </c>
       <c r="M528">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N528">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27940,7 +27940,7 @@
         <v>0</v>
       </c>
       <c r="B529" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C529">
         <v>-1.817232830535031</v>
@@ -27949,7 +27949,7 @@
         <v>161</v>
       </c>
       <c r="E529">
-        <v>-1.876018430737921</v>
+        <v>-1.832982431245148</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27958,10 +27958,10 @@
         <v>0.009857232830535028</v>
       </c>
       <c r="H529">
-        <v>0.009876018430737921</v>
+        <v>0.01011298243124515</v>
       </c>
       <c r="I529">
-        <v>-0.05878560020289036</v>
+        <v>-0.01574960071011766</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27973,10 +27973,10 @@
         <v>4.02</v>
       </c>
       <c r="M529">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N529">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27990,7 +27990,7 @@
         <v>0</v>
       </c>
       <c r="B530" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C530">
         <v>-2.115365321153458</v>
@@ -27999,7 +27999,7 @@
         <v>161</v>
       </c>
       <c r="E530">
-        <v>-2.176131868137866</v>
+        <v>-2.138048235598888</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28008,10 +28008,10 @@
         <v>0.01015536532115346</v>
       </c>
       <c r="H530">
-        <v>0.01017613186813787</v>
+        <v>0.01041804823559889</v>
       </c>
       <c r="I530">
-        <v>-0.06076654698440809</v>
+        <v>-0.02268291444543014</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28023,10 +28023,10 @@
         <v>4.02</v>
       </c>
       <c r="M530">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N530">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28040,7 +28040,7 @@
         <v>0</v>
       </c>
       <c r="B531" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C531">
         <v>-2.384457548336073</v>
@@ -28049,7 +28049,7 @@
         <v>161</v>
       </c>
       <c r="E531">
-        <v>-2.447012083540963</v>
+        <v>-2.413398421553191</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28058,10 +28058,10 @@
         <v>0.01042445754833607</v>
       </c>
       <c r="H531">
-        <v>0.01044701208354096</v>
+        <v>0.01069339842155319</v>
       </c>
       <c r="I531">
-        <v>-0.06255453520489063</v>
+        <v>-0.02894087321711858</v>
       </c>
       <c r="J531">
         <v>2.127726760244542</v>
@@ -28073,10 +28073,10 @@
         <v>4.02</v>
       </c>
       <c r="M531">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N531">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28090,7 +28090,7 @@
         <v>0</v>
       </c>
       <c r="B532" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C532">
         <v>-2.488425729237733</v>
@@ -28099,7 +28099,7 @@
         <v>161</v>
       </c>
       <c r="E532">
-        <v>-2.551671082920375</v>
+        <v>-2.519784467126983</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28108,10 +28108,10 @@
         <v>0.01052842572923773</v>
       </c>
       <c r="H532">
-        <v>0.01055167108292038</v>
+        <v>0.01079978446712698</v>
       </c>
       <c r="I532">
-        <v>-0.0632453536826425</v>
+        <v>-0.03135873788925014</v>
       </c>
       <c r="J532">
         <v>2.162267684132137</v>
@@ -28123,10 +28123,10 @@
         <v>4.02</v>
       </c>
       <c r="M532">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N532">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28140,7 +28140,7 @@
         <v>0</v>
       </c>
       <c r="B533" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C533">
         <v>-2.659724005112058</v>
@@ -28149,7 +28149,7 @@
         <v>161</v>
       </c>
       <c r="E533">
-        <v>-2.724107553318782</v>
+        <v>-2.695066423835595</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28158,10 +28158,10 @@
         <v>0.01069972400511206</v>
       </c>
       <c r="H533">
-        <v>0.01072410755331878</v>
+        <v>0.01097506642383559</v>
       </c>
       <c r="I533">
-        <v>-0.06438354820672387</v>
+        <v>-0.03534241872353672</v>
       </c>
       <c r="J533">
         <v>2.219177410336232</v>
@@ -28173,10 +28173,10 @@
         <v>4.02</v>
       </c>
       <c r="M533">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N533">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28190,7 +28190,7 @@
         <v>0</v>
       </c>
       <c r="B534" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C534">
         <v>-2.874392888877765</v>
@@ -28199,7 +28199,7 @@
         <v>161</v>
       </c>
       <c r="E534">
-        <v>-2.940202808405191</v>
+        <v>-2.914727607223759</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28208,10 +28208,10 @@
         <v>0.01091439288887776</v>
       </c>
       <c r="H534">
-        <v>0.01094020280840519</v>
+        <v>0.01119472760722376</v>
       </c>
       <c r="I534">
-        <v>-0.06580991952742643</v>
+        <v>-0.04033471834599478</v>
       </c>
       <c r="J534">
         <v>2.29049597637135</v>
@@ -28223,10 +28223,10 @@
         <v>4.02</v>
       </c>
       <c r="M534">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N534">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28240,7 +28240,7 @@
         <v>0</v>
       </c>
       <c r="B535" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C535">
         <v>-3.030268785898139</v>
@@ -28249,7 +28249,7 @@
         <v>161</v>
       </c>
       <c r="E535">
-        <v>-3.097114425671548</v>
+        <v>-3.074228525105073</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28258,10 +28258,10 @@
         <v>0.01107026878589814</v>
       </c>
       <c r="H535">
-        <v>0.01109711442567155</v>
+        <v>0.01135422852510507</v>
       </c>
       <c r="I535">
-        <v>-0.06684563977340918</v>
+        <v>-0.04395973920693397</v>
       </c>
       <c r="J535">
         <v>2.342281988670478</v>
@@ -28273,10 +28273,10 @@
         <v>4.02</v>
       </c>
       <c r="M535">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N535">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28293,40 +28293,40 @@
         <v>70</v>
       </c>
       <c r="C536">
-        <v>-3.164233352176372</v>
+        <v>-3.231969121958274</v>
       </c>
       <c r="D536" t="s">
         <v>161</v>
       </c>
       <c r="E536">
-        <v>-3.231969121958274</v>
+        <v>-3.211308546413032</v>
       </c>
       <c r="F536">
         <v>1</v>
       </c>
       <c r="G536">
-        <v>0.01120423335217637</v>
+        <v>0.01123196912195827</v>
       </c>
       <c r="H536">
-        <v>0.01123196912195827</v>
+        <v>0.01149130854641303</v>
       </c>
       <c r="I536">
-        <v>-0.0677357697819021</v>
+        <v>0.02066057554524203</v>
       </c>
       <c r="J536">
         <v>2.38678848909514</v>
       </c>
       <c r="K536">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L536">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M536">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N536">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28343,40 +28343,40 @@
         <v>70</v>
       </c>
       <c r="C537">
-        <v>-3.195519883576577</v>
+        <v>-3.263463537288049</v>
       </c>
       <c r="D537" t="s">
         <v>161</v>
       </c>
       <c r="E537">
-        <v>-3.263463537288049</v>
+        <v>-3.243322671566731</v>
       </c>
       <c r="F537">
         <v>1</v>
       </c>
       <c r="G537">
-        <v>0.01123551988357658</v>
+        <v>0.01126346353728805</v>
       </c>
       <c r="H537">
-        <v>0.01126346353728805</v>
+        <v>0.01152332267156673</v>
       </c>
       <c r="I537">
-        <v>-0.06794365371147215</v>
+        <v>0.02014086572131824</v>
       </c>
       <c r="J537">
         <v>2.397182685573614</v>
       </c>
       <c r="K537">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L537">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M537">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N537">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28393,40 +28393,40 @@
         <v>70</v>
       </c>
       <c r="C538">
-        <v>-3.217402384054332</v>
+        <v>-3.285491436440075</v>
       </c>
       <c r="D538" t="s">
         <v>161</v>
       </c>
       <c r="E538">
-        <v>-3.285491436440075</v>
+        <v>-3.265714067404433</v>
       </c>
       <c r="F538">
         <v>1</v>
       </c>
       <c r="G538">
-        <v>0.01125740238405433</v>
+        <v>0.01128549143644007</v>
       </c>
       <c r="H538">
-        <v>0.01128549143644007</v>
+        <v>0.01154571406740443</v>
       </c>
       <c r="I538">
-        <v>-0.06808905238574248</v>
+        <v>0.01977736903564153</v>
       </c>
       <c r="J538">
         <v>2.404452619287154</v>
       </c>
       <c r="K538">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L538">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M538">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N538">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28443,40 +28443,40 @@
         <v>70</v>
       </c>
       <c r="C539">
-        <v>-3.162920244715197</v>
+        <v>-3.23064728953058</v>
       </c>
       <c r="D539" t="s">
         <v>161</v>
       </c>
       <c r="E539">
-        <v>-3.23064728953058</v>
+        <v>-3.20996490156904</v>
       </c>
       <c r="F539">
         <v>1</v>
       </c>
       <c r="G539">
-        <v>0.0112029202447152</v>
+        <v>0.01123064728953058</v>
       </c>
       <c r="H539">
-        <v>0.01123064728953058</v>
+        <v>0.01148996490156904</v>
       </c>
       <c r="I539">
-        <v>-0.06772704481538305</v>
+        <v>0.02068238796154009</v>
       </c>
       <c r="J539">
         <v>2.386352240769169</v>
       </c>
       <c r="K539">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L539">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M539">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N539">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28493,40 +28493,40 @@
         <v>70</v>
       </c>
       <c r="C540">
-        <v>-3.117164533557272</v>
+        <v>-3.184587553713798</v>
       </c>
       <c r="D540" t="s">
         <v>161</v>
       </c>
       <c r="E540">
-        <v>-3.184587553713798</v>
+        <v>-3.163145104105116</v>
       </c>
       <c r="F540">
         <v>1</v>
       </c>
       <c r="G540">
-        <v>0.01115716453355727</v>
+        <v>0.0111845875537138</v>
       </c>
       <c r="H540">
-        <v>0.0111845875537138</v>
+        <v>0.01144314510410512</v>
       </c>
       <c r="I540">
-        <v>-0.06742302015652601</v>
+        <v>0.02144244960868225</v>
       </c>
       <c r="J540">
         <v>2.371151007826336</v>
       </c>
       <c r="K540">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L540">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M540">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N540">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28543,40 +28543,40 @@
         <v>70</v>
       </c>
       <c r="C541">
-        <v>-3.07014367427936</v>
+        <v>-3.137254263477229</v>
       </c>
       <c r="D541" t="s">
         <v>161</v>
       </c>
       <c r="E541">
-        <v>-3.137254263477229</v>
+        <v>-3.115030736471904</v>
       </c>
       <c r="F541">
         <v>1</v>
       </c>
       <c r="G541">
-        <v>0.01111014367427936</v>
+        <v>0.01113725426347723</v>
       </c>
       <c r="H541">
-        <v>0.01113725426347723</v>
+        <v>0.0113950307364719</v>
       </c>
       <c r="I541">
-        <v>-0.06711058919786872</v>
+        <v>0.02222352700532504</v>
       </c>
       <c r="J541">
         <v>2.355529459893475</v>
       </c>
       <c r="K541">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L541">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M541">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N541">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28593,40 +28593,40 @@
         <v>70</v>
       </c>
       <c r="C542">
-        <v>-3.050749658757123</v>
+        <v>-3.117731384064479</v>
       </c>
       <c r="D542" t="s">
         <v>161</v>
       </c>
       <c r="E542">
-        <v>-3.117731384064479</v>
+        <v>-3.095185697332871</v>
       </c>
       <c r="F542">
         <v>1</v>
       </c>
       <c r="G542">
-        <v>0.01109074965875712</v>
+        <v>0.01111773138406448</v>
       </c>
       <c r="H542">
-        <v>0.01111773138406448</v>
+        <v>0.01137518569733287</v>
       </c>
       <c r="I542">
-        <v>-0.06698172530735569</v>
+        <v>0.02254568673160762</v>
       </c>
       <c r="J542">
         <v>2.349086265367815</v>
       </c>
       <c r="K542">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L542">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M542">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N542">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28643,40 +28643,40 @@
         <v>70</v>
       </c>
       <c r="C543">
-        <v>-2.975413246666379</v>
+        <v>-3.041894397807019</v>
       </c>
       <c r="D543" t="s">
         <v>161</v>
       </c>
       <c r="E543">
-        <v>-3.041894397807019</v>
+        <v>-3.01809727565862</v>
       </c>
       <c r="F543">
         <v>1</v>
       </c>
       <c r="G543">
-        <v>0.01101541324666638</v>
+        <v>0.01104189439780702</v>
       </c>
       <c r="H543">
-        <v>0.01104189439780702</v>
+        <v>0.01129809727565862</v>
       </c>
       <c r="I543">
-        <v>-0.06648115114064002</v>
+        <v>0.02379712214839813</v>
       </c>
       <c r="J543">
         <v>2.324057557032019</v>
       </c>
       <c r="K543">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L543">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M543">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N543">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28693,40 +28693,40 @@
         <v>70</v>
       </c>
       <c r="C544">
-        <v>-2.912247903214602</v>
+        <v>-2.978309351076493</v>
       </c>
       <c r="D544" t="s">
         <v>161</v>
       </c>
       <c r="E544">
-        <v>-2.978309351076493</v>
+        <v>-2.953462970731222</v>
       </c>
       <c r="F544">
         <v>1</v>
       </c>
       <c r="G544">
-        <v>0.0109522479032146</v>
+        <v>0.01097830935107649</v>
       </c>
       <c r="H544">
-        <v>0.01097830935107649</v>
+        <v>0.01123346297073122</v>
       </c>
       <c r="I544">
-        <v>-0.06606144786189017</v>
+        <v>0.02484638034527098</v>
       </c>
       <c r="J544">
         <v>2.303072393094552</v>
       </c>
       <c r="K544">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L544">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M544">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N544">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28743,40 +28743,40 @@
         <v>70</v>
       </c>
       <c r="C545">
-        <v>-2.818195860753343</v>
+        <v>-2.883632378100542</v>
       </c>
       <c r="D545" t="s">
         <v>161</v>
       </c>
       <c r="E545">
-        <v>-2.883632378100542</v>
+        <v>-2.857223671468538</v>
       </c>
       <c r="F545">
         <v>1</v>
       </c>
       <c r="G545">
-        <v>0.01085819586075334</v>
+        <v>0.01088363237810054</v>
       </c>
       <c r="H545">
-        <v>0.01088363237810054</v>
+        <v>0.01113722367146854</v>
       </c>
       <c r="I545">
-        <v>-0.06543651734719802</v>
+        <v>0.02640870663200356</v>
       </c>
       <c r="J545">
         <v>2.271825867359915</v>
       </c>
       <c r="K545">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L545">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M545">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N545">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28793,40 +28793,40 @@
         <v>70</v>
       </c>
       <c r="C546">
-        <v>-2.732508902923009</v>
+        <v>-2.797376071713194</v>
       </c>
       <c r="D546" t="s">
         <v>161</v>
       </c>
       <c r="E546">
-        <v>-2.797376071713194</v>
+        <v>-2.76954399368866</v>
       </c>
       <c r="F546">
         <v>1</v>
       </c>
       <c r="G546">
-        <v>0.01077250890292301</v>
+        <v>0.0107973760717132</v>
       </c>
       <c r="H546">
-        <v>0.0107973760717132</v>
+        <v>0.01104954399368866</v>
       </c>
       <c r="I546">
-        <v>-0.06486716879018584</v>
+        <v>0.02783207802453447</v>
       </c>
       <c r="J546">
         <v>2.243358439509305</v>
       </c>
       <c r="K546">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L546">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M546">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N546">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28849,7 +28849,7 @@
         <v>162</v>
       </c>
       <c r="E547">
-        <v>-1.906588603387449</v>
+        <v>-2.021706257019368</v>
       </c>
       <c r="F547">
         <v>-1</v>
@@ -28858,10 +28858,10 @@
         <v>0.009364070927407006</v>
       </c>
       <c r="H547">
-        <v>0.009866588603387448</v>
+        <v>0.009961706257019368</v>
       </c>
       <c r="I547">
-        <v>0.4225176759804423</v>
+        <v>0.5376353296123613</v>
       </c>
       <c r="J547">
         <v>2.102353072638375</v>
@@ -28873,10 +28873,10 @@
         <v>3.94</v>
       </c>
       <c r="M547">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N547">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -28893,40 +28893,40 @@
         <v>70</v>
       </c>
       <c r="C548">
-        <v>-2.308082748641509</v>
+        <v>-2.370129810094276</v>
       </c>
       <c r="D548" t="s">
         <v>161</v>
       </c>
       <c r="E548">
-        <v>-2.370129810094276</v>
+        <v>-2.335247463726195</v>
       </c>
       <c r="F548">
         <v>1</v>
       </c>
       <c r="G548">
-        <v>0.01034808274864151</v>
+        <v>0.01037012981009428</v>
       </c>
       <c r="H548">
-        <v>0.01037012981009428</v>
+        <v>0.0106152474637262</v>
       </c>
       <c r="I548">
-        <v>-0.06204706145276706</v>
+        <v>0.03488234636808052</v>
       </c>
       <c r="J548">
         <v>2.102353072638375</v>
       </c>
       <c r="K548">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L548">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M548">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="N548">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -28940,43 +28940,43 @@
         <v>0</v>
       </c>
       <c r="B549" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C549">
-        <v>-1.073545579884814</v>
+        <v>-1.888001204283327</v>
       </c>
       <c r="D549" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E549">
-        <v>-1.461057218479642</v>
+        <v>-1.845162940327607</v>
       </c>
       <c r="F549">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G549">
-        <v>0.008953545579884814</v>
+        <v>0.009888001204283327</v>
       </c>
       <c r="H549">
-        <v>0.009421057218479642</v>
+        <v>0.01012516294032761</v>
       </c>
       <c r="I549">
-        <v>0.3875116385948285</v>
+        <v>0.0428382639557201</v>
       </c>
       <c r="J549">
         <v>1.943234720885587</v>
       </c>
       <c r="K549">
-        <v>2.58</v>
+        <v>3.03</v>
       </c>
       <c r="L549">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="M549">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="N549">
-        <v>3.98</v>
+        <v>4.14</v>
       </c>
       <c r="O549">
         <v>1</v>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="387">
   <si>
     <t>trade_time</t>
   </si>
@@ -499,7 +499,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-16</t>
+    <t>2021-08-17</t>
   </si>
   <si>
     <t>2021-08-04</t>
@@ -1175,9 +1175,6 @@
   </si>
   <si>
     <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P549"/>
+  <dimension ref="A1:P548"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -27599,7 +27596,7 @@
         <v>161</v>
       </c>
       <c r="E522">
-        <v>-0.8263893535341893</v>
+        <v>-0.7228936644354542</v>
       </c>
       <c r="F522">
         <v>1</v>
@@ -27608,10 +27605,10 @@
         <v>0.008873516868226593</v>
       </c>
       <c r="H522">
-        <v>0.009106389353534189</v>
+        <v>0.008822893664435455</v>
       </c>
       <c r="I522">
-        <v>0.007127514692404802</v>
+        <v>0.1106232037911399</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
@@ -27623,10 +27620,10 @@
         <v>4.02</v>
       </c>
       <c r="M522">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N522">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27649,7 +27646,7 @@
         <v>161</v>
       </c>
       <c r="E523">
-        <v>-1.303510252979447</v>
+        <v>-1.1814254379283</v>
       </c>
       <c r="F523">
         <v>1</v>
@@ -27658,10 +27655,10 @@
         <v>0.009339794110866276</v>
       </c>
       <c r="H523">
-        <v>0.009583510252979448</v>
+        <v>0.009281425437928299</v>
       </c>
       <c r="I523">
-        <v>-0.003716142113169951</v>
+        <v>0.1183686729379776</v>
       </c>
       <c r="J523">
         <v>1.767373458759561</v>
@@ -27673,10 +27670,10 @@
         <v>4.02</v>
       </c>
       <c r="M523">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N523">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27699,7 +27696,7 @@
         <v>161</v>
       </c>
       <c r="E524">
-        <v>-1.380179020124201</v>
+        <v>-1.255107110249232</v>
       </c>
       <c r="F524">
         <v>1</v>
@@ -27708,10 +27705,10 @@
         <v>0.009414720406030469</v>
       </c>
       <c r="H524">
-        <v>0.009660179020124201</v>
+        <v>0.009355107110249233</v>
       </c>
       <c r="I524">
-        <v>-0.005458614093732272</v>
+        <v>0.119613295781237</v>
       </c>
       <c r="J524">
         <v>1.79226591562474</v>
@@ -27723,10 +27720,10 @@
         <v>4.02</v>
       </c>
       <c r="M524">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N524">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27749,7 +27746,7 @@
         <v>161</v>
       </c>
       <c r="E525">
-        <v>-1.445600875415574</v>
+        <v>-1.317980062087694</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27758,10 +27755,10 @@
         <v>0.009478655400974308</v>
       </c>
       <c r="H525">
-        <v>0.009725600875415573</v>
+        <v>0.009417980062087694</v>
       </c>
       <c r="I525">
-        <v>-0.006945474441264032</v>
+        <v>0.120675338886616</v>
       </c>
       <c r="J525">
         <v>1.813506777732329</v>
@@ -27773,10 +27770,10 @@
         <v>4.02</v>
       </c>
       <c r="M525">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N525">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27799,7 +27796,7 @@
         <v>161</v>
       </c>
       <c r="E526">
-        <v>-1.516282197848455</v>
+        <v>-1.385907566763451</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27808,10 +27805,10 @@
         <v>0.009547730329715535</v>
       </c>
       <c r="H526">
-        <v>0.009796282197848456</v>
+        <v>0.009485907566763452</v>
       </c>
       <c r="I526">
-        <v>-0.008551868132919083</v>
+        <v>0.1218227629520854</v>
       </c>
       <c r="J526">
         <v>1.836455259041706</v>
@@ -27823,10 +27820,10 @@
         <v>4.02</v>
       </c>
       <c r="M526">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N526">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27849,7 +27846,7 @@
         <v>161</v>
       </c>
       <c r="E527">
-        <v>-1.601334017915089</v>
+        <v>-1.46764567955476</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27858,10 +27855,10 @@
         <v>0.009630849153871562</v>
       </c>
       <c r="H527">
-        <v>0.009881334017915086</v>
+        <v>0.009567645679554759</v>
       </c>
       <c r="I527">
-        <v>-0.01048486404352467</v>
+        <v>0.1232034743168038</v>
       </c>
       <c r="J527">
         <v>1.864069486336068</v>
@@ -27873,10 +27870,10 @@
         <v>4.02</v>
       </c>
       <c r="M527">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N527">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27899,7 +27896,7 @@
         <v>161</v>
       </c>
       <c r="E528">
-        <v>-1.713803440694126</v>
+        <v>-1.575733176770978</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27908,10 +27905,10 @@
         <v>0.009740762453405622</v>
       </c>
       <c r="H528">
-        <v>0.009993803440694126</v>
+        <v>0.009675733176770977</v>
       </c>
       <c r="I528">
-        <v>-0.01304098728850267</v>
+        <v>0.1250292766346455</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27923,10 +27920,10 @@
         <v>4.02</v>
       </c>
       <c r="M528">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N528">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27949,7 +27946,7 @@
         <v>161</v>
       </c>
       <c r="E529">
-        <v>-1.832982431245148</v>
+        <v>-1.690268830027804</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27958,10 +27955,10 @@
         <v>0.009857232830535028</v>
       </c>
       <c r="H529">
-        <v>0.01011298243124515</v>
+        <v>0.009790268830027805</v>
       </c>
       <c r="I529">
-        <v>-0.01574960071011766</v>
+        <v>0.1269640005072263</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27973,10 +27970,10 @@
         <v>4.02</v>
       </c>
       <c r="M529">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N529">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27999,7 +27996,7 @@
         <v>161</v>
       </c>
       <c r="E530">
-        <v>-2.138048235598888</v>
+        <v>-1.983448953692438</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28008,10 +28005,10 @@
         <v>0.01015536532115346</v>
       </c>
       <c r="H530">
-        <v>0.01041804823559889</v>
+        <v>0.01008344895369244</v>
       </c>
       <c r="I530">
-        <v>-0.02268291444543014</v>
+        <v>0.1319163674610202</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28023,10 +28020,10 @@
         <v>4.02</v>
       </c>
       <c r="M530">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N530">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28049,7 +28046,7 @@
         <v>161</v>
       </c>
       <c r="E531">
-        <v>-2.413398421553191</v>
+        <v>-2.248071210323846</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28058,10 +28055,10 @@
         <v>0.01042445754833607</v>
       </c>
       <c r="H531">
-        <v>0.01069339842155319</v>
+        <v>0.01034807121032385</v>
       </c>
       <c r="I531">
-        <v>-0.02894087321711858</v>
+        <v>0.136386338012227</v>
       </c>
       <c r="J531">
         <v>2.127726760244542</v>
@@ -28073,10 +28070,10 @@
         <v>4.02</v>
       </c>
       <c r="M531">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N531">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28099,7 +28096,7 @@
         <v>161</v>
       </c>
       <c r="E532">
-        <v>-2.519784467126983</v>
+        <v>-2.350312345031126</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28108,10 +28105,10 @@
         <v>0.01052842572923773</v>
       </c>
       <c r="H532">
-        <v>0.01079978446712698</v>
+        <v>0.01045031234503113</v>
       </c>
       <c r="I532">
-        <v>-0.03135873788925014</v>
+        <v>0.1381133842066067</v>
       </c>
       <c r="J532">
         <v>2.162267684132137</v>
@@ -28123,10 +28120,10 @@
         <v>4.02</v>
       </c>
       <c r="M532">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N532">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28149,7 +28146,7 @@
         <v>161</v>
       </c>
       <c r="E533">
-        <v>-2.695066423835595</v>
+        <v>-2.518765134595246</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28158,10 +28155,10 @@
         <v>0.01069972400511206</v>
       </c>
       <c r="H533">
-        <v>0.01097506642383559</v>
+        <v>0.01061876513459525</v>
       </c>
       <c r="I533">
-        <v>-0.03534241872353672</v>
+        <v>0.1409588705168119</v>
       </c>
       <c r="J533">
         <v>2.219177410336232</v>
@@ -28173,10 +28170,10 @@
         <v>4.02</v>
       </c>
       <c r="M533">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N533">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28190,43 +28187,43 @@
         <v>0</v>
       </c>
       <c r="B534" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C534">
-        <v>-2.874392888877765</v>
+        <v>-2.940202808405191</v>
       </c>
       <c r="D534" t="s">
         <v>161</v>
       </c>
       <c r="E534">
-        <v>-2.914727607223759</v>
+        <v>-2.729868090059197</v>
       </c>
       <c r="F534">
         <v>1</v>
       </c>
       <c r="G534">
-        <v>0.01091439288887776</v>
+        <v>0.01094020280840519</v>
       </c>
       <c r="H534">
-        <v>0.01119472760722376</v>
+        <v>0.0108298680900592</v>
       </c>
       <c r="I534">
-        <v>-0.04033471834599478</v>
+        <v>0.2103347183459938</v>
       </c>
       <c r="J534">
         <v>2.29049597637135</v>
       </c>
       <c r="K534">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L534">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M534">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N534">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28240,43 +28237,43 @@
         <v>0</v>
       </c>
       <c r="B535" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C535">
-        <v>-3.030268785898139</v>
+        <v>-3.097114425671548</v>
       </c>
       <c r="D535" t="s">
         <v>161</v>
       </c>
       <c r="E535">
-        <v>-3.074228525105073</v>
+        <v>-2.883154686464616</v>
       </c>
       <c r="F535">
         <v>1</v>
       </c>
       <c r="G535">
-        <v>0.01107026878589814</v>
+        <v>0.01109711442567155</v>
       </c>
       <c r="H535">
-        <v>0.01135422852510507</v>
+        <v>0.01098315468646462</v>
       </c>
       <c r="I535">
-        <v>-0.04395973920693397</v>
+        <v>0.2139597392069321</v>
       </c>
       <c r="J535">
         <v>2.342281988670478</v>
       </c>
       <c r="K535">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L535">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M535">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N535">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28299,7 +28296,7 @@
         <v>161</v>
       </c>
       <c r="E536">
-        <v>-3.211308546413032</v>
+        <v>-3.014893927721615</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28308,10 +28305,10 @@
         <v>0.01123196912195827</v>
       </c>
       <c r="H536">
-        <v>0.01149130854641303</v>
+        <v>0.01111489392772161</v>
       </c>
       <c r="I536">
-        <v>0.02066057554524203</v>
+        <v>0.2170751942366591</v>
       </c>
       <c r="J536">
         <v>2.38678848909514</v>
@@ -28323,10 +28320,10 @@
         <v>4</v>
       </c>
       <c r="M536">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N536">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28349,7 +28346,7 @@
         <v>161</v>
       </c>
       <c r="E537">
-        <v>-3.243322671566731</v>
+        <v>-3.045660749297897</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28358,10 +28355,10 @@
         <v>0.01126346353728805</v>
       </c>
       <c r="H537">
-        <v>0.01152332267156673</v>
+        <v>0.0111456607492979</v>
       </c>
       <c r="I537">
-        <v>0.02014086572131824</v>
+        <v>0.2178027879901521</v>
       </c>
       <c r="J537">
         <v>2.397182685573614</v>
@@ -28373,10 +28370,10 @@
         <v>4</v>
       </c>
       <c r="M537">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N537">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28399,7 +28396,7 @@
         <v>161</v>
       </c>
       <c r="E538">
-        <v>-3.265714067404433</v>
+        <v>-3.067179753089975</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28408,10 +28405,10 @@
         <v>0.01128549143644007</v>
       </c>
       <c r="H538">
-        <v>0.01154571406740443</v>
+        <v>0.01116717975308998</v>
       </c>
       <c r="I538">
-        <v>0.01977736903564153</v>
+        <v>0.2183116833501</v>
       </c>
       <c r="J538">
         <v>2.404452619287154</v>
@@ -28423,10 +28420,10 @@
         <v>4</v>
       </c>
       <c r="M538">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N538">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28449,7 +28446,7 @@
         <v>161</v>
       </c>
       <c r="E539">
-        <v>-3.20996490156904</v>
+        <v>-3.013602632676739</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28458,10 +28455,10 @@
         <v>0.01123064728953058</v>
       </c>
       <c r="H539">
-        <v>0.01148996490156904</v>
+        <v>0.01111360263267674</v>
       </c>
       <c r="I539">
-        <v>0.02068238796154009</v>
+        <v>0.2170446568538411</v>
       </c>
       <c r="J539">
         <v>2.386352240769169</v>
@@ -28473,10 +28470,10 @@
         <v>4</v>
       </c>
       <c r="M539">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N539">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28499,7 +28496,7 @@
         <v>161</v>
       </c>
       <c r="E540">
-        <v>-3.163145104105116</v>
+        <v>-2.968606983165955</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28508,10 +28505,10 @@
         <v>0.0111845875537138</v>
       </c>
       <c r="H540">
-        <v>0.01144314510410512</v>
+        <v>0.01106860698316595</v>
       </c>
       <c r="I540">
-        <v>0.02144244960868225</v>
+        <v>0.2159805705478428</v>
       </c>
       <c r="J540">
         <v>2.371151007826336</v>
@@ -28523,10 +28520,10 @@
         <v>4</v>
       </c>
       <c r="M540">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N540">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28549,7 +28546,7 @@
         <v>161</v>
       </c>
       <c r="E541">
-        <v>-3.115030736471904</v>
+        <v>-2.922367201284686</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28558,10 +28555,10 @@
         <v>0.01113725426347723</v>
       </c>
       <c r="H541">
-        <v>0.0113950307364719</v>
+        <v>0.01102236720128469</v>
       </c>
       <c r="I541">
-        <v>0.02222352700532504</v>
+        <v>0.2148870621925427</v>
       </c>
       <c r="J541">
         <v>2.355529459893475</v>
@@ -28573,10 +28570,10 @@
         <v>4</v>
       </c>
       <c r="M541">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N541">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28599,7 +28596,7 @@
         <v>161</v>
       </c>
       <c r="E542">
-        <v>-3.095185697332871</v>
+        <v>-2.903295345488733</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28608,10 +28605,10 @@
         <v>0.01111773138406448</v>
       </c>
       <c r="H542">
-        <v>0.01137518569733287</v>
+        <v>0.01100329534548873</v>
       </c>
       <c r="I542">
-        <v>0.02254568673160762</v>
+        <v>0.2144360385757462</v>
       </c>
       <c r="J542">
         <v>2.349086265367815</v>
@@ -28623,10 +28620,10 @@
         <v>4</v>
       </c>
       <c r="M542">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N542">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28649,7 +28646,7 @@
         <v>161</v>
       </c>
       <c r="E543">
-        <v>-3.01809727565862</v>
+        <v>-2.829210368814778</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28658,10 +28655,10 @@
         <v>0.01104189439780702</v>
       </c>
       <c r="H543">
-        <v>0.01129809727565862</v>
+        <v>0.01092921036881478</v>
       </c>
       <c r="I543">
-        <v>0.02379712214839813</v>
+        <v>0.2126840289922409</v>
       </c>
       <c r="J543">
         <v>2.324057557032019</v>
@@ -28673,10 +28670,10 @@
         <v>4</v>
       </c>
       <c r="M543">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N543">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28699,7 +28696,7 @@
         <v>161</v>
       </c>
       <c r="E544">
-        <v>-2.953462970731222</v>
+        <v>-2.767094283559874</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28708,10 +28705,10 @@
         <v>0.01097830935107649</v>
       </c>
       <c r="H544">
-        <v>0.01123346297073122</v>
+        <v>0.01086709428355987</v>
       </c>
       <c r="I544">
-        <v>0.02484638034527098</v>
+        <v>0.2112150675166182</v>
       </c>
       <c r="J544">
         <v>2.303072393094552</v>
@@ -28723,10 +28720,10 @@
         <v>4</v>
       </c>
       <c r="M544">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N544">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28749,7 +28746,7 @@
         <v>161</v>
       </c>
       <c r="E545">
-        <v>-2.857223671468538</v>
+        <v>-2.674604567385348</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28758,10 +28755,10 @@
         <v>0.01088363237810054</v>
       </c>
       <c r="H545">
-        <v>0.01113722367146854</v>
+        <v>0.01077460456738535</v>
       </c>
       <c r="I545">
-        <v>0.02640870663200356</v>
+        <v>0.2090278107151935</v>
       </c>
       <c r="J545">
         <v>2.271825867359915</v>
@@ -28773,10 +28770,10 @@
         <v>4</v>
       </c>
       <c r="M545">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N545">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28799,7 +28796,7 @@
         <v>161</v>
       </c>
       <c r="E546">
-        <v>-2.76954399368866</v>
+        <v>-2.590340980947543</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28808,10 +28805,10 @@
         <v>0.0107973760717132</v>
       </c>
       <c r="H546">
-        <v>0.01104954399368866</v>
+        <v>0.01069034098094754</v>
       </c>
       <c r="I546">
-        <v>0.02783207802453447</v>
+        <v>0.2070350907656513</v>
       </c>
       <c r="J546">
         <v>2.243358439509305</v>
@@ -28823,10 +28820,10 @@
         <v>4</v>
       </c>
       <c r="M546">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N546">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28899,7 +28896,7 @@
         <v>161</v>
       </c>
       <c r="E548">
-        <v>-2.335247463726195</v>
+        <v>-2.172965095009589</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28908,10 +28905,10 @@
         <v>0.01037012981009428</v>
       </c>
       <c r="H548">
-        <v>0.0106152474637262</v>
+        <v>0.01027296509500959</v>
       </c>
       <c r="I548">
-        <v>0.03488234636808052</v>
+        <v>0.1971647150846865</v>
       </c>
       <c r="J548">
         <v>2.102353072638375</v>
@@ -28923,66 +28920,16 @@
         <v>4</v>
       </c>
       <c r="M548">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N548">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
         <v>386</v>
-      </c>
-    </row>
-    <row r="549" spans="1:16">
-      <c r="A549" s="1">
-        <v>0</v>
-      </c>
-      <c r="B549" t="s">
-        <v>70</v>
-      </c>
-      <c r="C549">
-        <v>-1.888001204283327</v>
-      </c>
-      <c r="D549" t="s">
-        <v>161</v>
-      </c>
-      <c r="E549">
-        <v>-1.845162940327607</v>
-      </c>
-      <c r="F549">
-        <v>1</v>
-      </c>
-      <c r="G549">
-        <v>0.009888001204283327</v>
-      </c>
-      <c r="H549">
-        <v>0.01012516294032761</v>
-      </c>
-      <c r="I549">
-        <v>0.0428382639557201</v>
-      </c>
-      <c r="J549">
-        <v>1.943234720885587</v>
-      </c>
-      <c r="K549">
-        <v>3.03</v>
-      </c>
-      <c r="L549">
-        <v>4</v>
-      </c>
-      <c r="M549">
-        <v>3.08</v>
-      </c>
-      <c r="N549">
-        <v>4.14</v>
-      </c>
-      <c r="O549">
-        <v>1</v>
-      </c>
-      <c r="P549" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="388">
   <si>
     <t>trade_time</t>
   </si>
@@ -499,7 +499,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-17</t>
+    <t>2021-08-18</t>
   </si>
   <si>
     <t>2021-08-04</t>
@@ -1175,6 +1175,9 @@
   </si>
   <si>
     <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>2021-06-10</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P548"/>
+  <dimension ref="A1:P550"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -27596,7 +27599,7 @@
         <v>161</v>
       </c>
       <c r="E522">
-        <v>-0.7228936644354542</v>
+        <v>-0.5590183051936819</v>
       </c>
       <c r="F522">
         <v>1</v>
@@ -27605,10 +27608,10 @@
         <v>0.008873516868226593</v>
       </c>
       <c r="H522">
-        <v>0.008822893664435455</v>
+        <v>0.009019018305193683</v>
       </c>
       <c r="I522">
-        <v>0.1106232037911399</v>
+        <v>0.2744985630329122</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
@@ -27620,10 +27623,10 @@
         <v>4.02</v>
       </c>
       <c r="M522">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N522">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27646,7 +27649,7 @@
         <v>161</v>
       </c>
       <c r="E523">
-        <v>-1.1814254379283</v>
+        <v>-1.019099172515895</v>
       </c>
       <c r="F523">
         <v>1</v>
@@ -27655,10 +27658,10 @@
         <v>0.009339794110866276</v>
       </c>
       <c r="H523">
-        <v>0.009281425437928299</v>
+        <v>0.009479099172515895</v>
       </c>
       <c r="I523">
-        <v>0.1183686729379776</v>
+        <v>0.2806949383503827</v>
       </c>
       <c r="J523">
         <v>1.767373458759561</v>
@@ -27670,10 +27673,10 @@
         <v>4.02</v>
       </c>
       <c r="M523">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N523">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27696,7 +27699,7 @@
         <v>161</v>
       </c>
       <c r="E524">
-        <v>-1.255107110249232</v>
+        <v>-1.093029769405479</v>
       </c>
       <c r="F524">
         <v>1</v>
@@ -27705,10 +27708,10 @@
         <v>0.009414720406030469</v>
       </c>
       <c r="H524">
-        <v>0.009355107110249233</v>
+        <v>0.00955302976940548</v>
       </c>
       <c r="I524">
-        <v>0.119613295781237</v>
+        <v>0.2816906366249894</v>
       </c>
       <c r="J524">
         <v>1.79226591562474</v>
@@ -27720,10 +27723,10 @@
         <v>4.02</v>
       </c>
       <c r="M524">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N524">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27746,7 +27749,7 @@
         <v>161</v>
       </c>
       <c r="E525">
-        <v>-1.317980062087694</v>
+        <v>-1.156115129865016</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27755,10 +27758,10 @@
         <v>0.009478655400974308</v>
       </c>
       <c r="H525">
-        <v>0.009417980062087694</v>
+        <v>0.009616115129865018</v>
       </c>
       <c r="I525">
-        <v>0.120675338886616</v>
+        <v>0.2825402711092933</v>
       </c>
       <c r="J525">
         <v>1.813506777732329</v>
@@ -27770,10 +27773,10 @@
         <v>4.02</v>
       </c>
       <c r="M525">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N525">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27796,7 +27799,7 @@
         <v>161</v>
       </c>
       <c r="E526">
-        <v>-1.385907566763451</v>
+        <v>-1.224272119353867</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27805,10 +27808,10 @@
         <v>0.009547730329715535</v>
       </c>
       <c r="H526">
-        <v>0.009485907566763452</v>
+        <v>0.009684272119353868</v>
       </c>
       <c r="I526">
-        <v>0.1218227629520854</v>
+        <v>0.283458210361669</v>
       </c>
       <c r="J526">
         <v>1.836455259041706</v>
@@ -27820,10 +27823,10 @@
         <v>4.02</v>
       </c>
       <c r="M526">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N526">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27846,7 +27849,7 @@
         <v>161</v>
       </c>
       <c r="E527">
-        <v>-1.46764567955476</v>
+        <v>-1.306286374418121</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27855,10 +27858,10 @@
         <v>0.009630849153871562</v>
       </c>
       <c r="H527">
-        <v>0.009567645679554759</v>
+        <v>0.009766286374418122</v>
       </c>
       <c r="I527">
-        <v>0.1232034743168038</v>
+        <v>0.2845627794534433</v>
       </c>
       <c r="J527">
         <v>1.864069486336068</v>
@@ -27870,10 +27873,10 @@
         <v>4.02</v>
       </c>
       <c r="M527">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N527">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27896,7 +27899,7 @@
         <v>161</v>
       </c>
       <c r="E528">
-        <v>-1.575733176770978</v>
+        <v>-1.414739032097907</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27905,10 +27908,10 @@
         <v>0.009740762453405622</v>
       </c>
       <c r="H528">
-        <v>0.009675733176770977</v>
+        <v>0.009874739032097906</v>
       </c>
       <c r="I528">
-        <v>0.1250292766346455</v>
+        <v>0.2860234213077169</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27920,10 +27923,10 @@
         <v>4.02</v>
       </c>
       <c r="M528">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N528">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27946,7 +27949,7 @@
         <v>161</v>
       </c>
       <c r="E529">
-        <v>-1.690268830027804</v>
+        <v>-1.529661630129249</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27955,10 +27958,10 @@
         <v>0.009857232830535028</v>
       </c>
       <c r="H529">
-        <v>0.009790268830027805</v>
+        <v>0.00998966163012925</v>
       </c>
       <c r="I529">
-        <v>0.1269640005072263</v>
+        <v>0.2875712004057815</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27970,10 +27973,10 @@
         <v>4.02</v>
       </c>
       <c r="M529">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N529">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27996,7 +27999,7 @@
         <v>161</v>
       </c>
       <c r="E530">
-        <v>-1.983448953692438</v>
+        <v>-1.823832227184642</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28005,10 +28008,10 @@
         <v>0.01015536532115346</v>
       </c>
       <c r="H530">
-        <v>0.01008344895369244</v>
+        <v>0.01028383222718464</v>
       </c>
       <c r="I530">
-        <v>0.1319163674610202</v>
+        <v>0.2915330939688161</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28020,10 +28023,10 @@
         <v>4.02</v>
       </c>
       <c r="M530">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N530">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28046,7 +28049,7 @@
         <v>161</v>
       </c>
       <c r="E531">
-        <v>-2.248071210323846</v>
+        <v>-2.089348477926291</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28055,10 +28058,10 @@
         <v>0.01042445754833607</v>
       </c>
       <c r="H531">
-        <v>0.01034807121032385</v>
+        <v>0.01054934847792629</v>
       </c>
       <c r="I531">
-        <v>0.136386338012227</v>
+        <v>0.2951090704097821</v>
       </c>
       <c r="J531">
         <v>2.127726760244542</v>
@@ -28070,10 +28073,10 @@
         <v>4.02</v>
       </c>
       <c r="M531">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N531">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28096,7 +28099,7 @@
         <v>161</v>
       </c>
       <c r="E532">
-        <v>-2.350312345031126</v>
+        <v>-2.191935021872447</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28105,10 +28108,10 @@
         <v>0.01052842572923773</v>
       </c>
       <c r="H532">
-        <v>0.01045031234503113</v>
+        <v>0.01065193502187245</v>
       </c>
       <c r="I532">
-        <v>0.1381133842066067</v>
+        <v>0.2964907073652858</v>
       </c>
       <c r="J532">
         <v>2.162267684132137</v>
@@ -28120,10 +28123,10 @@
         <v>4.02</v>
       </c>
       <c r="M532">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N532">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28146,7 +28149,7 @@
         <v>161</v>
       </c>
       <c r="E533">
-        <v>-2.518765134595246</v>
+        <v>-2.360956908698609</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28155,10 +28158,10 @@
         <v>0.01069972400511206</v>
       </c>
       <c r="H533">
-        <v>0.01061876513459525</v>
+        <v>0.01082095690869861</v>
       </c>
       <c r="I533">
-        <v>0.1409588705168119</v>
+        <v>0.2987670964134495</v>
       </c>
       <c r="J533">
         <v>2.219177410336232</v>
@@ -28170,10 +28173,10 @@
         <v>4.02</v>
       </c>
       <c r="M533">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N533">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28196,7 +28199,7 @@
         <v>161</v>
       </c>
       <c r="E534">
-        <v>-2.729868090059197</v>
+        <v>-2.572773049822911</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28205,10 +28208,10 @@
         <v>0.01094020280840519</v>
       </c>
       <c r="H534">
-        <v>0.0108298680900592</v>
+        <v>0.01103277304982291</v>
       </c>
       <c r="I534">
-        <v>0.2103347183459938</v>
+        <v>0.3674297585822801</v>
       </c>
       <c r="J534">
         <v>2.29049597637135</v>
@@ -28220,10 +28223,10 @@
         <v>4</v>
       </c>
       <c r="M534">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N534">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28246,7 +28249,7 @@
         <v>161</v>
       </c>
       <c r="E535">
-        <v>-2.883154686464616</v>
+        <v>-2.726577506351321</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28255,10 +28258,10 @@
         <v>0.01109711442567155</v>
       </c>
       <c r="H535">
-        <v>0.01098315468646462</v>
+        <v>0.01118657750635132</v>
       </c>
       <c r="I535">
-        <v>0.2139597392069321</v>
+        <v>0.3705369193202275</v>
       </c>
       <c r="J535">
         <v>2.342281988670478</v>
@@ -28270,10 +28273,10 @@
         <v>4</v>
       </c>
       <c r="M535">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N535">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28296,7 +28299,7 @@
         <v>161</v>
       </c>
       <c r="E536">
-        <v>-3.014893927721615</v>
+        <v>-2.858761812612566</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28305,10 +28308,10 @@
         <v>0.01123196912195827</v>
       </c>
       <c r="H536">
-        <v>0.01111489392772161</v>
+        <v>0.01131876181261257</v>
       </c>
       <c r="I536">
-        <v>0.2170751942366591</v>
+        <v>0.373207309345708</v>
       </c>
       <c r="J536">
         <v>2.38678848909514</v>
@@ -28320,10 +28323,10 @@
         <v>4</v>
       </c>
       <c r="M536">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N536">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28346,7 +28349,7 @@
         <v>161</v>
       </c>
       <c r="E537">
-        <v>-3.045660749297897</v>
+        <v>-2.889632576153633</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28355,10 +28358,10 @@
         <v>0.01126346353728805</v>
       </c>
       <c r="H537">
-        <v>0.0111456607492979</v>
+        <v>0.01134963257615364</v>
       </c>
       <c r="I537">
-        <v>0.2178027879901521</v>
+        <v>0.3738309611344164</v>
       </c>
       <c r="J537">
         <v>2.397182685573614</v>
@@ -28370,10 +28373,10 @@
         <v>4</v>
       </c>
       <c r="M537">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N537">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28396,7 +28399,7 @@
         <v>161</v>
       </c>
       <c r="E538">
-        <v>-3.067179753089975</v>
+        <v>-2.911224279282846</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28405,10 +28408,10 @@
         <v>0.01128549143644007</v>
       </c>
       <c r="H538">
-        <v>0.01116717975308998</v>
+        <v>0.01137122427928285</v>
       </c>
       <c r="I538">
-        <v>0.2183116833501</v>
+        <v>0.3742671571572282</v>
       </c>
       <c r="J538">
         <v>2.404452619287154</v>
@@ -28420,10 +28423,10 @@
         <v>4</v>
       </c>
       <c r="M538">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N538">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28446,7 +28449,7 @@
         <v>161</v>
       </c>
       <c r="E539">
-        <v>-3.013602632676739</v>
+        <v>-2.857466155084431</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28455,10 +28458,10 @@
         <v>0.01123064728953058</v>
       </c>
       <c r="H539">
-        <v>0.01111360263267674</v>
+        <v>0.01131746615508443</v>
       </c>
       <c r="I539">
-        <v>0.2170446568538411</v>
+        <v>0.3731811344461491</v>
       </c>
       <c r="J539">
         <v>2.386352240769169</v>
@@ -28470,10 +28473,10 @@
         <v>4</v>
       </c>
       <c r="M539">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N539">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28496,7 +28499,7 @@
         <v>161</v>
       </c>
       <c r="E540">
-        <v>-2.968606983165955</v>
+        <v>-2.812318493244219</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28505,10 +28508,10 @@
         <v>0.0111845875537138</v>
       </c>
       <c r="H540">
-        <v>0.01106860698316595</v>
+        <v>0.01127231849324422</v>
       </c>
       <c r="I540">
-        <v>0.2159805705478428</v>
+        <v>0.3722690604695789</v>
       </c>
       <c r="J540">
         <v>2.371151007826336</v>
@@ -28520,10 +28523,10 @@
         <v>4</v>
       </c>
       <c r="M540">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N540">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28546,7 +28549,7 @@
         <v>161</v>
       </c>
       <c r="E541">
-        <v>-2.922367201284686</v>
+        <v>-2.765922495883621</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28555,10 +28558,10 @@
         <v>0.01113725426347723</v>
       </c>
       <c r="H541">
-        <v>0.01102236720128469</v>
+        <v>0.01122592249588362</v>
       </c>
       <c r="I541">
-        <v>0.2148870621925427</v>
+        <v>0.3713317675936079</v>
       </c>
       <c r="J541">
         <v>2.355529459893475</v>
@@ -28570,10 +28573,10 @@
         <v>4</v>
       </c>
       <c r="M541">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N541">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28596,7 +28599,7 @@
         <v>161</v>
       </c>
       <c r="E542">
-        <v>-2.903295345488733</v>
+        <v>-2.746786208142411</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28605,10 +28608,10 @@
         <v>0.01111773138406448</v>
       </c>
       <c r="H542">
-        <v>0.01100329534548873</v>
+        <v>0.01120678620814241</v>
       </c>
       <c r="I542">
-        <v>0.2144360385757462</v>
+        <v>0.3709451759220679</v>
       </c>
       <c r="J542">
         <v>2.349086265367815</v>
@@ -28620,10 +28623,10 @@
         <v>4</v>
       </c>
       <c r="M542">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N542">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28646,7 +28649,7 @@
         <v>161</v>
       </c>
       <c r="E543">
-        <v>-2.829210368814778</v>
+        <v>-2.672450944385098</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28655,10 +28658,10 @@
         <v>0.01104189439780702</v>
       </c>
       <c r="H543">
-        <v>0.01092921036881478</v>
+        <v>0.0111324509443851</v>
       </c>
       <c r="I543">
-        <v>0.2126840289922409</v>
+        <v>0.3694434534219209</v>
       </c>
       <c r="J543">
         <v>2.324057557032019</v>
@@ -28670,10 +28673,10 @@
         <v>4</v>
       </c>
       <c r="M543">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N543">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28696,7 +28699,7 @@
         <v>161</v>
       </c>
       <c r="E544">
-        <v>-2.767094283559874</v>
+        <v>-2.61012500749082</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28705,10 +28708,10 @@
         <v>0.01097830935107649</v>
       </c>
       <c r="H544">
-        <v>0.01086709428355987</v>
+        <v>0.01107012500749082</v>
       </c>
       <c r="I544">
-        <v>0.2112150675166182</v>
+        <v>0.3681843435856722</v>
       </c>
       <c r="J544">
         <v>2.303072393094552</v>
@@ -28720,10 +28723,10 @@
         <v>4</v>
       </c>
       <c r="M544">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N544">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28746,7 +28749,7 @@
         <v>161</v>
       </c>
       <c r="E545">
-        <v>-2.674604567385348</v>
+        <v>-2.517322826058947</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28755,10 +28758,10 @@
         <v>0.01088363237810054</v>
       </c>
       <c r="H545">
-        <v>0.01077460456738535</v>
+        <v>0.01097732282605895</v>
       </c>
       <c r="I545">
-        <v>0.2090278107151935</v>
+        <v>0.3663095520415949</v>
       </c>
       <c r="J545">
         <v>2.271825867359915</v>
@@ -28770,10 +28773,10 @@
         <v>4</v>
       </c>
       <c r="M545">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N545">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28796,7 +28799,7 @@
         <v>161</v>
       </c>
       <c r="E546">
-        <v>-2.590340980947543</v>
+        <v>-2.432774565342636</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28805,10 +28808,10 @@
         <v>0.0107973760717132</v>
       </c>
       <c r="H546">
-        <v>0.01069034098094754</v>
+        <v>0.01089277456534264</v>
       </c>
       <c r="I546">
-        <v>0.2070350907656513</v>
+        <v>0.3646015063705583</v>
       </c>
       <c r="J546">
         <v>2.243358439509305</v>
@@ -28820,10 +28823,10 @@
         <v>4</v>
       </c>
       <c r="M546">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N546">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28896,7 +28899,7 @@
         <v>161</v>
       </c>
       <c r="E548">
-        <v>-2.172965095009589</v>
+        <v>-2.013988625735973</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28905,10 +28908,10 @@
         <v>0.01037012981009428</v>
       </c>
       <c r="H548">
-        <v>0.01027296509500959</v>
+        <v>0.01047398862573597</v>
       </c>
       <c r="I548">
-        <v>0.1971647150846865</v>
+        <v>0.3561411843583029</v>
       </c>
       <c r="J548">
         <v>2.102353072638375</v>
@@ -28920,16 +28923,116 @@
         <v>4</v>
       </c>
       <c r="M548">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="N548">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
         <v>386</v>
+      </c>
+    </row>
+    <row r="549" spans="1:16">
+      <c r="A549" s="1">
+        <v>0</v>
+      </c>
+      <c r="B549" t="s">
+        <v>71</v>
+      </c>
+      <c r="C549">
+        <v>-1.073545579884814</v>
+      </c>
+      <c r="D549" t="s">
+        <v>162</v>
+      </c>
+      <c r="E549">
+        <v>-1.568218954523922</v>
+      </c>
+      <c r="F549">
+        <v>-1</v>
+      </c>
+      <c r="G549">
+        <v>0.008953545579884814</v>
+      </c>
+      <c r="H549">
+        <v>0.009508218954523922</v>
+      </c>
+      <c r="I549">
+        <v>0.4946733746391088</v>
+      </c>
+      <c r="J549">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K549">
+        <v>2.58</v>
+      </c>
+      <c r="L549">
+        <v>3.94</v>
+      </c>
+      <c r="M549">
+        <v>2.85</v>
+      </c>
+      <c r="N549">
+        <v>3.97</v>
+      </c>
+      <c r="O549">
+        <v>1</v>
+      </c>
+      <c r="P549" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="550" spans="1:16">
+      <c r="A550" s="1">
+        <v>1</v>
+      </c>
+      <c r="B550" t="s">
+        <v>70</v>
+      </c>
+      <c r="C550">
+        <v>-1.888001204283327</v>
+      </c>
+      <c r="D550" t="s">
+        <v>161</v>
+      </c>
+      <c r="E550">
+        <v>-1.541407121030193</v>
+      </c>
+      <c r="F550">
+        <v>1</v>
+      </c>
+      <c r="G550">
+        <v>0.009888001204283327</v>
+      </c>
+      <c r="H550">
+        <v>0.01000140712103019</v>
+      </c>
+      <c r="I550">
+        <v>0.3465940832531347</v>
+      </c>
+      <c r="J550">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K550">
+        <v>3.03</v>
+      </c>
+      <c r="L550">
+        <v>4</v>
+      </c>
+      <c r="M550">
+        <v>2.97</v>
+      </c>
+      <c r="N550">
+        <v>4.23</v>
+      </c>
+      <c r="O550">
+        <v>1</v>
+      </c>
+      <c r="P550" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="388">
   <si>
     <t>trade_time</t>
   </si>
@@ -499,7 +499,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-18</t>
+    <t>2021-08-19</t>
   </si>
   <si>
     <t>2021-08-04</t>
@@ -1535,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P550"/>
+  <dimension ref="A1:P549"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -27599,7 +27599,7 @@
         <v>161</v>
       </c>
       <c r="E522">
-        <v>-0.5590183051936819</v>
+        <v>-0.5582589649076066</v>
       </c>
       <c r="F522">
         <v>1</v>
@@ -27608,10 +27608,10 @@
         <v>0.008873516868226593</v>
       </c>
       <c r="H522">
-        <v>0.009019018305193683</v>
+        <v>0.009858258964907607</v>
       </c>
       <c r="I522">
-        <v>0.2744985630329122</v>
+        <v>0.2752579033189875</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
@@ -27623,10 +27623,10 @@
         <v>4.02</v>
       </c>
       <c r="M522">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N522">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27649,7 +27649,7 @@
         <v>161</v>
       </c>
       <c r="E523">
-        <v>-1.019099172515895</v>
+        <v>-1.05861627179338</v>
       </c>
       <c r="F523">
         <v>1</v>
@@ -27658,10 +27658,10 @@
         <v>0.009339794110866276</v>
       </c>
       <c r="H523">
-        <v>0.009479099172515895</v>
+        <v>0.01035861627179338</v>
       </c>
       <c r="I523">
-        <v>0.2806949383503827</v>
+        <v>0.2411778390728969</v>
       </c>
       <c r="J523">
         <v>1.767373458759561</v>
@@ -27673,10 +27673,10 @@
         <v>4.02</v>
       </c>
       <c r="M523">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N523">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27699,7 +27699,7 @@
         <v>161</v>
       </c>
       <c r="E524">
-        <v>-1.093029769405479</v>
+        <v>-1.139018907467912</v>
       </c>
       <c r="F524">
         <v>1</v>
@@ -27708,10 +27708,10 @@
         <v>0.009414720406030469</v>
       </c>
       <c r="H524">
-        <v>0.00955302976940548</v>
+        <v>0.01043901890746791</v>
       </c>
       <c r="I524">
-        <v>0.2816906366249894</v>
+        <v>0.2357014985625572</v>
       </c>
       <c r="J524">
         <v>1.79226591562474</v>
@@ -27723,10 +27723,10 @@
         <v>4.02</v>
       </c>
       <c r="M524">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N524">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27749,7 +27749,7 @@
         <v>161</v>
       </c>
       <c r="E525">
-        <v>-1.156115129865016</v>
+        <v>-1.207626892075422</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27758,10 +27758,10 @@
         <v>0.009478655400974308</v>
       </c>
       <c r="H525">
-        <v>0.009616115129865018</v>
+        <v>0.01050762689207542</v>
       </c>
       <c r="I525">
-        <v>0.2825402711092933</v>
+        <v>0.2310285088988877</v>
       </c>
       <c r="J525">
         <v>1.813506777732329</v>
@@ -27773,10 +27773,10 @@
         <v>4.02</v>
       </c>
       <c r="M525">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N525">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27799,7 +27799,7 @@
         <v>161</v>
       </c>
       <c r="E526">
-        <v>-1.224272119353867</v>
+        <v>-1.281750486704711</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27808,10 +27808,10 @@
         <v>0.009547730329715535</v>
       </c>
       <c r="H526">
-        <v>0.009684272119353868</v>
+        <v>0.01058175048670471</v>
       </c>
       <c r="I526">
-        <v>0.283458210361669</v>
+        <v>0.2259798430108253</v>
       </c>
       <c r="J526">
         <v>1.836455259041706</v>
@@ -27823,10 +27823,10 @@
         <v>4.02</v>
       </c>
       <c r="M526">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N526">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27849,7 +27849,7 @@
         <v>161</v>
       </c>
       <c r="E527">
-        <v>-1.306286374418121</v>
+        <v>-1.370944440865498</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27858,10 +27858,10 @@
         <v>0.009630849153871562</v>
       </c>
       <c r="H527">
-        <v>0.009766286374418122</v>
+        <v>0.0106709444408655</v>
       </c>
       <c r="I527">
-        <v>0.2845627794534433</v>
+        <v>0.2199047130060663</v>
       </c>
       <c r="J527">
         <v>1.864069486336068</v>
@@ -27873,10 +27873,10 @@
         <v>4.02</v>
       </c>
       <c r="M527">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N527">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27899,7 +27899,7 @@
         <v>161</v>
       </c>
       <c r="E528">
-        <v>-1.414739032097907</v>
+        <v>-1.48889127059806</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27908,10 +27908,10 @@
         <v>0.009740762453405622</v>
       </c>
       <c r="H528">
-        <v>0.009874739032097906</v>
+        <v>0.01078889127059806</v>
       </c>
       <c r="I528">
-        <v>0.2860234213077169</v>
+        <v>0.2118711828075632</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27923,10 +27923,10 @@
         <v>4.02</v>
       </c>
       <c r="M528">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N528">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27949,7 +27949,7 @@
         <v>161</v>
       </c>
       <c r="E529">
-        <v>-1.529661630129249</v>
+        <v>-1.613874432766827</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27958,10 +27958,10 @@
         <v>0.009857232830535028</v>
       </c>
       <c r="H529">
-        <v>0.00998966163012925</v>
+        <v>0.01091387443276683</v>
       </c>
       <c r="I529">
-        <v>0.2875712004057815</v>
+        <v>0.2033583977682039</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27973,10 +27973,10 @@
         <v>4.02</v>
       </c>
       <c r="M529">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N529">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27999,7 +27999,7 @@
         <v>161</v>
       </c>
       <c r="E530">
-        <v>-1.823832227184642</v>
+        <v>-1.93379733798195</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28008,10 +28008,10 @@
         <v>0.01015536532115346</v>
       </c>
       <c r="H530">
-        <v>0.01028383222718464</v>
+        <v>0.01123379733798195</v>
       </c>
       <c r="I530">
-        <v>0.2915330939688161</v>
+        <v>0.181567983171508</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28023,10 +28023,10 @@
         <v>4.02</v>
       </c>
       <c r="M530">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N530">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28049,7 +28049,7 @@
         <v>161</v>
       </c>
       <c r="E531">
-        <v>-2.089348477926291</v>
+        <v>-2.222557435589872</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28058,10 +28058,10 @@
         <v>0.01042445754833607</v>
       </c>
       <c r="H531">
-        <v>0.01054934847792629</v>
+        <v>0.01152255743558987</v>
       </c>
       <c r="I531">
-        <v>0.2951090704097821</v>
+        <v>0.161900112746201</v>
       </c>
       <c r="J531">
         <v>2.127726760244542</v>
@@ -28073,10 +28073,10 @@
         <v>4.02</v>
       </c>
       <c r="M531">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N531">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28090,43 +28090,43 @@
         <v>0</v>
       </c>
       <c r="B532" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C532">
-        <v>-2.488425729237733</v>
+        <v>-2.551671082920375</v>
       </c>
       <c r="D532" t="s">
         <v>161</v>
       </c>
       <c r="E532">
-        <v>-2.191935021872447</v>
+        <v>-2.334124619746802</v>
       </c>
       <c r="F532">
         <v>1</v>
       </c>
       <c r="G532">
-        <v>0.01052842572923773</v>
+        <v>0.01055167108292038</v>
       </c>
       <c r="H532">
-        <v>0.01065193502187245</v>
+        <v>0.0116341246197468</v>
       </c>
       <c r="I532">
-        <v>0.2964907073652858</v>
+        <v>0.2175464631735728</v>
       </c>
       <c r="J532">
         <v>2.162267684132137</v>
       </c>
       <c r="K532">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L532">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M532">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N532">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28140,43 +28140,43 @@
         <v>0</v>
       </c>
       <c r="B533" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C533">
-        <v>-2.659724005112058</v>
+        <v>-2.724107553318782</v>
       </c>
       <c r="D533" t="s">
         <v>161</v>
       </c>
       <c r="E533">
-        <v>-2.360956908698609</v>
+        <v>-2.517943035386028</v>
       </c>
       <c r="F533">
         <v>1</v>
       </c>
       <c r="G533">
-        <v>0.01069972400511206</v>
+        <v>0.01072410755331878</v>
       </c>
       <c r="H533">
-        <v>0.01082095690869861</v>
+        <v>0.01181794303538603</v>
       </c>
       <c r="I533">
-        <v>0.2987670964134495</v>
+        <v>0.2061645179327538</v>
       </c>
       <c r="J533">
         <v>2.219177410336232</v>
       </c>
       <c r="K533">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="L533">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="M533">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N533">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28199,7 +28199,7 @@
         <v>161</v>
       </c>
       <c r="E534">
-        <v>-2.572773049822911</v>
+        <v>-2.748302003679461</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28208,10 +28208,10 @@
         <v>0.01094020280840519</v>
       </c>
       <c r="H534">
-        <v>0.01103277304982291</v>
+        <v>0.01204830200367946</v>
       </c>
       <c r="I534">
-        <v>0.3674297585822801</v>
+        <v>0.19190080472573</v>
       </c>
       <c r="J534">
         <v>2.29049597637135</v>
@@ -28223,10 +28223,10 @@
         <v>4</v>
       </c>
       <c r="M534">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N534">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28249,7 +28249,7 @@
         <v>161</v>
       </c>
       <c r="E535">
-        <v>-2.726577506351321</v>
+        <v>-2.915570823405644</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28258,10 +28258,10 @@
         <v>0.01109711442567155</v>
       </c>
       <c r="H535">
-        <v>0.01118657750635132</v>
+        <v>0.01221557082340565</v>
       </c>
       <c r="I535">
-        <v>0.3705369193202275</v>
+        <v>0.1815436022659043</v>
       </c>
       <c r="J535">
         <v>2.342281988670478</v>
@@ -28273,10 +28273,10 @@
         <v>4</v>
       </c>
       <c r="M535">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N535">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28299,7 +28299,7 @@
         <v>161</v>
       </c>
       <c r="E536">
-        <v>-2.858761812612566</v>
+        <v>-3.059326819777302</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28308,10 +28308,10 @@
         <v>0.01123196912195827</v>
       </c>
       <c r="H536">
-        <v>0.01131876181261257</v>
+        <v>0.0123593268197773</v>
       </c>
       <c r="I536">
-        <v>0.373207309345708</v>
+        <v>0.1726423021809715</v>
       </c>
       <c r="J536">
         <v>2.38678848909514</v>
@@ -28323,10 +28323,10 @@
         <v>4</v>
       </c>
       <c r="M536">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N536">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28349,7 +28349,7 @@
         <v>161</v>
       </c>
       <c r="E537">
-        <v>-2.889632576153633</v>
+        <v>-3.092900074402772</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28358,10 +28358,10 @@
         <v>0.01126346353728805</v>
       </c>
       <c r="H537">
-        <v>0.01134963257615364</v>
+        <v>0.01239290007440277</v>
       </c>
       <c r="I537">
-        <v>0.3738309611344164</v>
+        <v>0.1705634628852772</v>
       </c>
       <c r="J537">
         <v>2.397182685573614</v>
@@ -28373,10 +28373,10 @@
         <v>4</v>
       </c>
       <c r="M537">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N537">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28399,7 +28399,7 @@
         <v>161</v>
       </c>
       <c r="E538">
-        <v>-2.911224279282846</v>
+        <v>-3.116381960297506</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28408,10 +28408,10 @@
         <v>0.01128549143644007</v>
       </c>
       <c r="H538">
-        <v>0.01137122427928285</v>
+        <v>0.01241638196029751</v>
       </c>
       <c r="I538">
-        <v>0.3742671571572282</v>
+        <v>0.1691094761425687</v>
       </c>
       <c r="J538">
         <v>2.404452619287154</v>
@@ -28423,10 +28423,10 @@
         <v>4</v>
       </c>
       <c r="M538">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N538">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28449,7 +28449,7 @@
         <v>161</v>
       </c>
       <c r="E539">
-        <v>-2.857466155084431</v>
+        <v>-3.057917737684415</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28458,10 +28458,10 @@
         <v>0.01123064728953058</v>
       </c>
       <c r="H539">
-        <v>0.01131746615508443</v>
+        <v>0.01235791773768441</v>
       </c>
       <c r="I539">
-        <v>0.3731811344461491</v>
+        <v>0.1727295518461656</v>
       </c>
       <c r="J539">
         <v>2.386352240769169</v>
@@ -28473,10 +28473,10 @@
         <v>4</v>
       </c>
       <c r="M539">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N539">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28499,7 +28499,7 @@
         <v>161</v>
       </c>
       <c r="E540">
-        <v>-2.812318493244219</v>
+        <v>-3.008817755279066</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28508,10 +28508,10 @@
         <v>0.0111845875537138</v>
       </c>
       <c r="H540">
-        <v>0.01127231849324422</v>
+        <v>0.01230881775527907</v>
       </c>
       <c r="I540">
-        <v>0.3722690604695789</v>
+        <v>0.1757697984347324</v>
       </c>
       <c r="J540">
         <v>2.371151007826336</v>
@@ -28523,10 +28523,10 @@
         <v>4</v>
       </c>
       <c r="M540">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N540">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28549,7 +28549,7 @@
         <v>161</v>
       </c>
       <c r="E541">
-        <v>-2.765922495883621</v>
+        <v>-2.958360155455924</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28558,10 +28558,10 @@
         <v>0.01113725426347723</v>
       </c>
       <c r="H541">
-        <v>0.01122592249588362</v>
+        <v>0.01225836015545593</v>
       </c>
       <c r="I541">
-        <v>0.3713317675936079</v>
+        <v>0.1788941080213045</v>
       </c>
       <c r="J541">
         <v>2.355529459893475</v>
@@ -28573,10 +28573,10 @@
         <v>4</v>
       </c>
       <c r="M541">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N541">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28599,7 +28599,7 @@
         <v>161</v>
       </c>
       <c r="E542">
-        <v>-2.746786208142411</v>
+        <v>-2.937548637138042</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28608,10 +28608,10 @@
         <v>0.01111773138406448</v>
       </c>
       <c r="H542">
-        <v>0.01120678620814241</v>
+        <v>0.01223754863713804</v>
       </c>
       <c r="I542">
-        <v>0.3709451759220679</v>
+        <v>0.1801827469264365</v>
       </c>
       <c r="J542">
         <v>2.349086265367815</v>
@@ -28623,10 +28623,10 @@
         <v>4</v>
       </c>
       <c r="M542">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N542">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28649,7 +28649,7 @@
         <v>161</v>
       </c>
       <c r="E543">
-        <v>-2.672450944385098</v>
+        <v>-2.856705909213423</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28658,10 +28658,10 @@
         <v>0.01104189439780702</v>
       </c>
       <c r="H543">
-        <v>0.0111324509443851</v>
+        <v>0.01215670590921342</v>
       </c>
       <c r="I543">
-        <v>0.3694434534219209</v>
+        <v>0.1851884885935959</v>
       </c>
       <c r="J543">
         <v>2.324057557032019</v>
@@ -28673,10 +28673,10 @@
         <v>4</v>
       </c>
       <c r="M543">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N543">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28699,7 +28699,7 @@
         <v>161</v>
       </c>
       <c r="E544">
-        <v>-2.61012500749082</v>
+        <v>-2.788923829695404</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28708,10 +28708,10 @@
         <v>0.01097830935107649</v>
       </c>
       <c r="H544">
-        <v>0.01107012500749082</v>
+        <v>0.0120889238296954</v>
       </c>
       <c r="I544">
-        <v>0.3681843435856722</v>
+        <v>0.1893855213810891</v>
       </c>
       <c r="J544">
         <v>2.303072393094552</v>
@@ -28723,10 +28723,10 @@
         <v>4</v>
       </c>
       <c r="M544">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N544">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28749,7 +28749,7 @@
         <v>161</v>
       </c>
       <c r="E545">
-        <v>-2.517322826058947</v>
+        <v>-2.687997551572524</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28758,10 +28758,10 @@
         <v>0.01088363237810054</v>
       </c>
       <c r="H545">
-        <v>0.01097732282605895</v>
+        <v>0.01198799755157252</v>
       </c>
       <c r="I545">
-        <v>0.3663095520415949</v>
+        <v>0.1956348265280177</v>
       </c>
       <c r="J545">
         <v>2.271825867359915</v>
@@ -28773,10 +28773,10 @@
         <v>4</v>
       </c>
       <c r="M545">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N545">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28799,7 +28799,7 @@
         <v>161</v>
       </c>
       <c r="E546">
-        <v>-2.432774565342636</v>
+        <v>-2.596047759615055</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28808,10 +28808,10 @@
         <v>0.0107973760717132</v>
       </c>
       <c r="H546">
-        <v>0.01089277456534264</v>
+        <v>0.01189604775961505</v>
       </c>
       <c r="I546">
-        <v>0.3646015063705583</v>
+        <v>0.2013283120981395</v>
       </c>
       <c r="J546">
         <v>2.243358439509305</v>
@@ -28823,10 +28823,10 @@
         <v>4</v>
       </c>
       <c r="M546">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N546">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28899,7 +28899,7 @@
         <v>161</v>
       </c>
       <c r="E548">
-        <v>-2.013988625735973</v>
+        <v>-2.14060042462195</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28908,10 +28908,10 @@
         <v>0.01037012981009428</v>
       </c>
       <c r="H548">
-        <v>0.01047398862573597</v>
+        <v>0.01144060042462195</v>
       </c>
       <c r="I548">
-        <v>0.3561411843583029</v>
+        <v>0.2295293854723255</v>
       </c>
       <c r="J548">
         <v>2.102353072638375</v>
@@ -28923,10 +28923,10 @@
         <v>4</v>
       </c>
       <c r="M548">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="N548">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -28982,56 +28982,6 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="550" spans="1:16">
-      <c r="A550" s="1">
-        <v>1</v>
-      </c>
-      <c r="B550" t="s">
-        <v>70</v>
-      </c>
-      <c r="C550">
-        <v>-1.888001204283327</v>
-      </c>
-      <c r="D550" t="s">
-        <v>161</v>
-      </c>
-      <c r="E550">
-        <v>-1.541407121030193</v>
-      </c>
-      <c r="F550">
-        <v>1</v>
-      </c>
-      <c r="G550">
-        <v>0.009888001204283327</v>
-      </c>
-      <c r="H550">
-        <v>0.01000140712103019</v>
-      </c>
-      <c r="I550">
-        <v>0.3465940832531347</v>
-      </c>
-      <c r="J550">
-        <v>1.943234720885587</v>
-      </c>
-      <c r="K550">
-        <v>3.03</v>
-      </c>
-      <c r="L550">
-        <v>4</v>
-      </c>
-      <c r="M550">
-        <v>2.97</v>
-      </c>
-      <c r="N550">
-        <v>4.23</v>
-      </c>
-      <c r="O550">
-        <v>1</v>
-      </c>
-      <c r="P550" t="s">
         <v>387</v>
       </c>
     </row>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="361">
   <si>
     <t>trade_time</t>
   </si>
@@ -226,6 +226,9 @@
     <t>2021-08-12</t>
   </si>
   <si>
+    <t>2021-08-23</t>
+  </si>
+  <si>
     <t>2017-06-30</t>
   </si>
   <si>
@@ -493,7 +496,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-08-24</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -1093,19 +1096,7 @@
     <t>2021-04-08</t>
   </si>
   <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
+    <t>2021-06-10</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P527"/>
+  <dimension ref="A1:P524"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1524,7 +1515,7 @@
         <v>6.869727715272395</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>6.050137140894572</v>
@@ -1560,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1574,7 +1565,7 @@
         <v>6.844463593057311</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3">
         <v>6.050137140894572</v>
@@ -1610,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1624,7 +1615,7 @@
         <v>6.857637482930865</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>6.039233803242143</v>
@@ -1660,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1674,7 +1665,7 @@
         <v>6.83283604847594</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E5">
         <v>6.039233803242143</v>
@@ -1710,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1724,7 +1715,7 @@
         <v>6.826153414303063</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6">
         <v>6.01084051672589</v>
@@ -1760,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1774,7 +1765,7 @@
         <v>6.802556861010267</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7">
         <v>6.01084051672589</v>
@@ -1810,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1824,7 +1815,7 @@
         <v>6.794839943414579</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8">
         <v>5.98260108041714</v>
@@ -1860,7 +1851,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1874,7 +1865,7 @@
         <v>6.77244174258507</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E9">
         <v>5.98260108041714</v>
@@ -1910,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1924,7 +1915,7 @@
         <v>6.763675289556306</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10">
         <v>5.95449585181284</v>
@@ -1960,7 +1951,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1974,7 +1965,7 @@
         <v>6.742469746029192</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11">
         <v>5.95449585181284</v>
@@ -2010,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2024,7 +2015,7 @@
         <v>6.730117010025435</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>5.924231979091157</v>
@@ -2060,7 +2051,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2074,7 +2065,7 @@
         <v>6.710195726779869</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13">
         <v>5.924231979091157</v>
@@ -2110,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2124,7 +2115,7 @@
         <v>6.693046966006446</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14">
         <v>5.890801090807809</v>
@@ -2160,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2174,7 +2165,7 @@
         <v>6.674544336691723</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15">
         <v>5.890801090807809</v>
@@ -2210,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2224,7 +2215,7 @@
         <v>6.644553392998862</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16">
         <v>5.847068118145396</v>
@@ -2260,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2274,7 +2265,7 @@
         <v>6.627906590937341</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17">
         <v>5.847068118145396</v>
@@ -2310,7 +2301,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2324,7 +2315,7 @@
         <v>6.617128166636995</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18">
         <v>5.822335218497922</v>
@@ -2360,7 +2351,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2374,7 +2365,7 @@
         <v>6.601530915667526</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19">
         <v>5.822335218497922</v>
@@ -2410,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2424,7 +2415,7 @@
         <v>6.581803978417834</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20">
         <v>5.790478795844368</v>
@@ -2460,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2474,7 +2465,7 @@
         <v>6.567558568262076</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21">
         <v>5.790478795844368</v>
@@ -2510,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2524,7 +2515,7 @@
         <v>6.554001439910648</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>5.765405624678154</v>
@@ -2560,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2574,7 +2565,7 @@
         <v>6.540820020413236</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E23">
         <v>5.765405624678154</v>
@@ -2610,7 +2601,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2624,7 +2615,7 @@
         <v>6.529894038726229</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E24">
         <v>5.743664840248944</v>
@@ -2660,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2674,7 +2665,7 @@
         <v>6.517635198641864</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E25">
         <v>5.743664840248944</v>
@@ -2710,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2724,7 +2715,7 @@
         <v>6.493137342079</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E26">
         <v>5.710516538114505</v>
@@ -2760,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2774,7 +2765,7 @@
         <v>6.482285164262333</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E27">
         <v>5.710516538114505</v>
@@ -2810,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2824,7 +2815,7 @@
         <v>6.444477546138163</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28">
         <v>5.666633660577178</v>
@@ -2860,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2874,7 +2865,7 @@
         <v>6.435487556851677</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E29">
         <v>5.666633660577178</v>
@@ -2910,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2924,7 +2915,7 @@
         <v>6.395287017911711</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E30">
         <v>5.62227215259259</v>
@@ -2960,7 +2951,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2974,7 +2965,7 @@
         <v>6.388179528041545</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E31">
         <v>5.62227215259259</v>
@@ -3010,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3024,7 +3015,7 @@
         <v>6.391868530229962</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E32">
         <v>5.619189256879599</v>
@@ -3060,7 +3051,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3074,7 +3065,7 @@
         <v>6.384891864347617</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E33">
         <v>5.619189256879599</v>
@@ -3110,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3124,7 +3115,7 @@
         <v>6.396520135507044</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E34">
         <v>5.623384215382392</v>
@@ -3160,7 +3151,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3174,7 +3165,7 @@
         <v>6.389365454780485</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E35">
         <v>5.623384215382392</v>
@@ -3210,7 +3201,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3224,7 +3215,7 @@
         <v>6.403506732043612</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E36">
         <v>5.629684939713206</v>
@@ -3260,7 +3251,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3274,7 +3265,7 @@
         <v>6.396084677406335</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E37">
         <v>5.629684939713206</v>
@@ -3310,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3324,7 +3315,7 @@
         <v>6.390454186369448</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E38">
         <v>5.617913758755807</v>
@@ -3360,7 +3351,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3374,7 +3365,7 @@
         <v>6.38353164679125</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E39">
         <v>5.617913758755807</v>
@@ -3410,7 +3401,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3424,7 +3415,7 @@
         <v>6.385694652927858</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E40">
         <v>5.613621467365888</v>
@@ -3460,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3474,7 +3465,7 @@
         <v>6.378954258556243</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E41">
         <v>5.613621467365888</v>
@@ -3510,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3524,7 +3515,7 @@
         <v>6.398324700271503</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E42">
         <v>5.625011626534365</v>
@@ -3560,7 +3551,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3574,7 +3565,7 @@
         <v>6.39110095966211</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E43">
         <v>5.625011626534365</v>
@@ -3610,7 +3601,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3624,7 +3615,7 @@
         <v>6.406965992917668</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E44">
         <v>5.63280460592575</v>
@@ -3660,7 +3651,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3674,7 +3665,7 @@
         <v>6.399411553920818</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E45">
         <v>5.63280460592575</v>
@@ -3710,7 +3701,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3724,7 +3715,7 @@
         <v>6.400651203652978</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E46">
         <v>5.627109737736961</v>
@@ -3760,7 +3751,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3774,7 +3765,7 @@
         <v>6.393338428804362</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E47">
         <v>5.627109737736961</v>
@@ -3810,7 +3801,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3824,7 +3815,7 @@
         <v>6.421264387742685</v>
       </c>
       <c r="D48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E48">
         <v>5.645699331375265</v>
@@ -3860,7 +3851,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3874,7 +3865,7 @@
         <v>6.413162755599453</v>
       </c>
       <c r="D49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E49">
         <v>5.645699331375265</v>
@@ -3910,7 +3901,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3924,7 +3915,7 @@
         <v>6.463467063219744</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E50">
         <v>5.68375898213827</v>
@@ -3960,7 +3951,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3974,7 +3965,7 @@
         <v>6.45375035364561</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E51">
         <v>5.68375898213827</v>
@@ -4010,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4024,7 +4015,7 @@
         <v>6.488418927255035</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E52">
         <v>5.706261328739149</v>
@@ -4060,7 +4051,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4074,7 +4065,7 @@
         <v>6.477747321053927</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E53">
         <v>5.706261328739149</v>
@@ -4110,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4124,7 +4115,7 @@
         <v>6.583255790923473</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E54">
         <v>5.791788084326992</v>
@@ -4160,7 +4151,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4174,7 +4165,7 @@
         <v>6.440394668218746</v>
       </c>
       <c r="D55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E55">
         <v>5.791788084326992</v>
@@ -4210,7 +4201,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4224,7 +4215,7 @@
         <v>6.568954820555353</v>
       </c>
       <c r="D56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E56">
         <v>5.791788084326992</v>
@@ -4260,7 +4251,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4274,7 +4265,7 @@
         <v>6.628230185262845</v>
       </c>
       <c r="D57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E57">
         <v>5.83234735509561</v>
@@ -4310,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4324,7 +4315,7 @@
         <v>6.484920066940753</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E58">
         <v>5.83234735509561</v>
@@ -4360,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4374,7 +4365,7 @@
         <v>6.61220806502816</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E59">
         <v>5.83234735509561</v>
@@ -4410,7 +4401,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4424,7 +4415,7 @@
         <v>6.646411890511949</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E60">
         <v>5.84874416748332</v>
@@ -4460,7 +4451,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4474,7 +4465,7 @@
         <v>6.50292025766158</v>
       </c>
       <c r="D61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E61">
         <v>5.84874416748332</v>
@@ -4510,7 +4501,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4524,7 +4515,7 @@
         <v>6.629693964585535</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E62">
         <v>5.84874416748332</v>
@@ -4560,7 +4551,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4574,7 +4565,7 @@
         <v>6.642559529608892</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E63">
         <v>5.84526999176043</v>
@@ -4610,7 +4601,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4624,7 +4615,7 @@
         <v>6.499106356268371</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>5.84526999176043</v>
@@ -4660,7 +4651,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4674,7 +4665,7 @@
         <v>6.625989031803559</v>
       </c>
       <c r="D65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E65">
         <v>5.84526999176043</v>
@@ -4710,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4724,7 +4715,7 @@
         <v>6.645390633912061</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E66">
         <v>5.847823167354969</v>
@@ -4760,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4774,7 +4765,7 @@
         <v>6.501909196635068</v>
       </c>
       <c r="D67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E67">
         <v>5.847823167354969</v>
@@ -4810,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4824,7 +4815,7 @@
         <v>6.628711791016923</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E68">
         <v>5.847823167354969</v>
@@ -4860,7 +4851,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4874,7 +4865,7 @@
         <v>6.628009372010197</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E69">
         <v>5.832148219017515</v>
@@ -4910,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4924,7 +4915,7 @@
         <v>6.611995702199492</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E70">
         <v>5.832148219017515</v>
@@ -4960,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4974,7 +4965,7 @@
         <v>6.616738911804213</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E71">
         <v>5.821984176701968</v>
@@ -5010,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5024,7 +5015,7 @@
         <v>6.601156557442321</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E72">
         <v>5.821984176701968</v>
@@ -5060,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5074,7 +5065,7 @@
         <v>6.626158243616882</v>
       </c>
       <c r="D73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E73">
         <v>5.830478815374958</v>
@@ -5110,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5124,7 +5115,7 @@
         <v>6.610215415658166</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E74">
         <v>5.830478815374958</v>
@@ -5160,7 +5151,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5174,7 +5165,7 @@
         <v>6.650940043106316</v>
       </c>
       <c r="D75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E75">
         <v>5.85282779261834</v>
@@ -5210,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5224,7 +5215,7 @@
         <v>6.634048826814393</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E76">
         <v>5.85282779261834</v>
@@ -5260,7 +5251,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5274,7 +5265,7 @@
         <v>6.655761178830648</v>
       </c>
       <c r="D77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E77">
         <v>5.857175638812331</v>
@@ -5310,7 +5301,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5324,7 +5315,7 @@
         <v>6.638685459840457</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E78">
         <v>5.857175638812331</v>
@@ -5360,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5374,7 +5365,7 @@
         <v>6.682065765134389</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E79">
         <v>5.880897911319199</v>
@@ -5410,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5424,7 +5415,7 @@
         <v>6.663983381443721</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E80">
         <v>5.880897911319199</v>
@@ -5460,7 +5451,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5474,7 +5465,7 @@
         <v>6.734829447046008</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E81">
         <v>5.928481797502389</v>
@@ -5510,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5524,7 +5515,7 @@
         <v>6.714727820952732</v>
       </c>
       <c r="D82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E82">
         <v>5.928481797502389</v>
@@ -5560,7 +5551,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5574,7 +5565,7 @@
         <v>6.744601630625527</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E83">
         <v>5.937294648584086</v>
@@ -5610,7 +5601,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5624,7 +5615,7 @@
         <v>6.72412602745683</v>
       </c>
       <c r="D84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E84">
         <v>5.937294648584086</v>
@@ -5660,7 +5651,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5674,7 +5665,7 @@
         <v>6.868996803282632</v>
       </c>
       <c r="D85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E85">
         <v>6.049477982328097</v>
@@ -5710,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5724,7 +5715,7 @@
         <v>6.723283024880476</v>
       </c>
       <c r="D86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E86">
         <v>6.049477982328097</v>
@@ -5760,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5774,7 +5765,7 @@
         <v>6.843760652741033</v>
       </c>
       <c r="D87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E87">
         <v>6.049477982328097</v>
@@ -5810,7 +5801,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5824,7 +5815,7 @@
         <v>7.461980748234559</v>
       </c>
       <c r="D88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E88">
         <v>6.584248861136657</v>
@@ -5860,7 +5851,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5874,7 +5865,7 @@
         <v>7.310346997004264</v>
       </c>
       <c r="D89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E89">
         <v>6.584248861136657</v>
@@ -5910,7 +5901,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5924,7 +5915,7 @@
         <v>7.414051368518428</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E90">
         <v>6.584248861136657</v>
@@ -5960,7 +5951,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5974,7 +5965,7 @@
         <v>7.503790226406835</v>
       </c>
       <c r="D91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E91">
         <v>6.621953914663068</v>
@@ -6010,7 +6001,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6024,7 +6015,7 @@
         <v>7.351739076060011</v>
       </c>
       <c r="D92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E92">
         <v>6.621953914663068</v>
@@ -6060,7 +6051,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6074,7 +6065,7 @@
         <v>7.454260816744011</v>
       </c>
       <c r="D93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E93">
         <v>6.621953914663068</v>
@@ -6110,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6124,7 +6115,7 @@
         <v>7.442891522635139</v>
       </c>
       <c r="D94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E94">
         <v>6.567033619414717</v>
@@ -6160,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6174,7 +6165,7 @@
         <v>7.291448346036452</v>
       </c>
       <c r="D95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E95">
         <v>6.567033619414717</v>
@@ -6210,7 +6201,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6224,7 +6215,7 @@
         <v>7.39569267900684</v>
       </c>
       <c r="D96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E96">
         <v>6.567033619414717</v>
@@ -6260,7 +6251,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6274,7 +6265,7 @@
         <v>7.440682840908001</v>
       </c>
       <c r="D97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E97">
         <v>6.56504176334798</v>
@@ -6310,7 +6301,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6324,7 +6315,7 @@
         <v>7.289261714376473</v>
       </c>
       <c r="D98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E98">
         <v>6.56504176334798</v>
@@ -6360,7 +6351,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6374,7 +6365,7 @@
         <v>7.393568522537145</v>
       </c>
       <c r="D99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E99">
         <v>6.56504176334798</v>
@@ -6410,7 +6401,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6424,7 +6415,7 @@
         <v>7.424306444365878</v>
       </c>
       <c r="D100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E100">
         <v>6.550273033022139</v>
@@ -6460,7 +6451,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6474,7 +6465,7 @@
         <v>7.377818843333573</v>
       </c>
       <c r="D101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E101">
         <v>6.550273033022139</v>
@@ -6510,7 +6501,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6524,7 +6515,7 @@
         <v>7.534499875331724</v>
       </c>
       <c r="D102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E102">
         <v>6.649648806039591</v>
@@ -6560,7 +6551,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6574,7 +6565,7 @@
         <v>7.483795221200893</v>
       </c>
       <c r="D103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E103">
         <v>6.649648806039591</v>
@@ -6610,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6624,7 +6615,7 @@
         <v>7.561436426814521</v>
       </c>
       <c r="D104" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E104">
         <v>6.673941003882645</v>
@@ -6660,7 +6651,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6674,7 +6665,7 @@
         <v>7.509700922959722</v>
       </c>
       <c r="D105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E105">
         <v>6.673941003882645</v>
@@ -6710,7 +6701,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6724,7 +6715,7 @@
         <v>7.578789061755105</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E106">
         <v>6.689590135559512</v>
@@ -6760,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6774,7 +6765,7 @@
         <v>7.526389480356823</v>
       </c>
       <c r="D107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E107">
         <v>6.689590135559512</v>
@@ -6810,7 +6801,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6824,7 +6815,7 @@
         <v>6.876779630058808</v>
       </c>
       <c r="D108" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E108">
         <v>6.056496771201121</v>
@@ -6860,7 +6851,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6874,7 +6865,7 @@
         <v>6.85124563423293</v>
       </c>
       <c r="D109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E109">
         <v>6.056496771201121</v>
@@ -6910,7 +6901,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6924,7 +6915,7 @@
         <v>6.803309666682317</v>
       </c>
       <c r="D110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E110">
         <v>5.990239333347446</v>
@@ -6960,7 +6951,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6974,7 +6965,7 @@
         <v>6.780587333348385</v>
       </c>
       <c r="D111" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E111">
         <v>5.990239333347446</v>
@@ -7010,7 +7001,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7024,7 +7015,7 @@
         <v>6.690125588143431</v>
       </c>
       <c r="D112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E112">
         <v>5.88816650378326</v>
@@ -7060,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7074,7 +7065,7 @@
         <v>6.671734758647093</v>
       </c>
       <c r="D113" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E113">
         <v>5.88816650378326</v>
@@ -7110,7 +7101,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7124,7 +7115,7 @@
         <v>6.546850371675455</v>
       </c>
       <c r="D114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E114">
         <v>5.758956574788845</v>
@@ -7160,7 +7151,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7174,7 +7165,7 @@
         <v>6.533942620346777</v>
       </c>
       <c r="D115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E115">
         <v>5.758956574788845</v>
@@ -7210,7 +7201,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7224,7 +7215,7 @@
         <v>6.36581543133911</v>
       </c>
       <c r="D116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E116">
         <v>5.595693783337433</v>
@@ -7260,7 +7251,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7274,7 +7265,7 @@
         <v>6.359835805846931</v>
       </c>
       <c r="D117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E117">
         <v>5.595693783337433</v>
@@ -7310,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7324,7 +7315,7 @@
         <v>5.655118426801266</v>
       </c>
       <c r="D118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E118">
         <v>4.954765702705966</v>
@@ -7360,7 +7351,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7374,7 +7365,7 @@
         <v>5.676336856391234</v>
       </c>
       <c r="D119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E119">
         <v>4.954765702705966</v>
@@ -7410,7 +7401,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7424,7 +7415,7 @@
         <v>4.385984132295935</v>
       </c>
       <c r="D120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E120">
         <v>4.515964100132926</v>
@@ -7460,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7474,7 +7465,7 @@
         <v>5.520410496630564</v>
       </c>
       <c r="D121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E121">
         <v>4.833282011936382</v>
@@ -7510,7 +7501,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7524,7 +7515,7 @@
         <v>5.54678413819046</v>
       </c>
       <c r="D122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E122">
         <v>4.833282011936382</v>
@@ -7560,7 +7551,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7610,7 +7601,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7624,7 +7615,7 @@
         <v>5.300818351460203</v>
       </c>
       <c r="D124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E124">
         <v>4.635247165543143</v>
@@ -7660,7 +7651,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7674,7 +7665,7 @@
         <v>5.335595685763722</v>
       </c>
       <c r="D125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E125">
         <v>4.635247165543143</v>
@@ -7710,7 +7701,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7760,7 +7751,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7810,7 +7801,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7824,7 +7815,7 @@
         <v>5.067644558031954</v>
       </c>
       <c r="D128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E128">
         <v>4.254963977459765</v>
@@ -7860,7 +7851,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7874,7 +7865,7 @@
         <v>5.111345348656355</v>
       </c>
       <c r="D129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E129">
         <v>4.254963977459765</v>
@@ -7910,7 +7901,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7924,7 +7915,7 @@
         <v>3.765802729769834</v>
       </c>
       <c r="D130" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E130">
         <v>3.674881815638774</v>
@@ -7960,7 +7951,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7974,7 +7965,7 @@
         <v>4.618291357603566</v>
       </c>
       <c r="D131" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E131">
         <v>3.650865136965114</v>
@@ -8010,7 +8001,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8024,7 +8015,7 @@
         <v>4.268167177296843</v>
       </c>
       <c r="D132" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E132">
         <v>3.514053115333852</v>
@@ -8060,7 +8051,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8074,7 +8065,7 @@
         <v>4.254037078744074</v>
       </c>
       <c r="D133" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E133">
         <v>3.510852837781765</v>
@@ -8110,7 +8101,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8124,7 +8115,7 @@
         <v>4.264789106547418</v>
       </c>
       <c r="D134" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E134">
         <v>3.510852837781765</v>
@@ -8160,7 +8151,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8174,7 +8165,7 @@
         <v>4.267776501761822</v>
       </c>
       <c r="D135" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E135">
         <v>3.523940390364364</v>
@@ -8210,7 +8201,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8224,7 +8215,7 @@
         <v>4.278603745384606</v>
       </c>
       <c r="D136" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E136">
         <v>3.523940390364364</v>
@@ -8260,7 +8251,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8274,7 +8265,7 @@
         <v>4.280771326539147</v>
       </c>
       <c r="D137" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E137">
         <v>3.485420289185799</v>
@@ -8310,7 +8301,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8324,7 +8315,7 @@
         <v>4.291669709713632</v>
       </c>
       <c r="D138" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E138">
         <v>3.485420289185799</v>
@@ -8360,7 +8351,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8374,7 +8365,7 @@
         <v>4.295828187834458</v>
       </c>
       <c r="D139" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E139">
         <v>3.499680345777525</v>
@@ -8410,7 +8401,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8424,7 +8415,7 @@
         <v>4.306808999081727</v>
       </c>
       <c r="D140" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E140">
         <v>3.499680345777525</v>
@@ -8460,7 +8451,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8474,7 +8465,7 @@
         <v>4.311022789612967</v>
       </c>
       <c r="D141" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E141">
         <v>3.503649415261579</v>
@@ -8524,7 +8515,7 @@
         <v>4.306094254478001</v>
       </c>
       <c r="D142" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E142">
         <v>3.499007110842255</v>
@@ -8560,7 +8551,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8574,7 +8565,7 @@
         <v>4.306502251029037</v>
       </c>
       <c r="D143" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E143">
         <v>3.499391412493775</v>
@@ -8610,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8624,7 +8615,7 @@
         <v>4.318153845587818</v>
       </c>
       <c r="D144" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E144">
         <v>3.510366326424823</v>
@@ -8660,7 +8651,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8710,7 +8701,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8760,7 +8751,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8810,7 +8801,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8824,7 +8815,7 @@
         <v>2.959973514323903</v>
       </c>
       <c r="D148" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E148">
         <v>2.331565797970563</v>
@@ -8860,7 +8851,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8874,7 +8865,7 @@
         <v>2.954681081546583</v>
       </c>
       <c r="D149" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E149">
         <v>2.325889855571697</v>
@@ -8910,7 +8901,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8924,7 +8915,7 @@
         <v>2.952436806561317</v>
       </c>
       <c r="D150" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E150">
         <v>2.323482951964311</v>
@@ -8960,7 +8951,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8974,7 +8965,7 @@
         <v>2.939220179650368</v>
       </c>
       <c r="D151" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E151">
         <v>2.309308598465612</v>
@@ -9010,7 +9001,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9024,7 +9015,7 @@
         <v>2.885800805603528</v>
       </c>
       <c r="D152" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E152">
         <v>2.285985098138231</v>
@@ -9060,7 +9051,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9074,7 +9065,7 @@
         <v>2.882518664640946</v>
       </c>
       <c r="D153" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E153">
         <v>2.285985098138231</v>
@@ -9110,7 +9101,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9124,7 +9115,7 @@
         <v>2.871759791100637</v>
       </c>
       <c r="D154" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E154">
         <v>2.270895377157946</v>
@@ -9160,7 +9151,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9174,7 +9165,7 @@
         <v>2.868186342783224</v>
       </c>
       <c r="D155" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E155">
         <v>2.270895377157946</v>
@@ -9210,7 +9201,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9224,7 +9215,7 @@
         <v>2.851373977249472</v>
       </c>
       <c r="D156" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E156">
         <v>2.248986971400885</v>
@@ -9260,7 +9251,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9274,7 +9265,7 @@
         <v>2.813597099989564</v>
       </c>
       <c r="D157" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E157">
         <v>2.215446285791325</v>
@@ -9310,7 +9301,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9324,7 +9315,7 @@
         <v>2.783887421732515</v>
       </c>
       <c r="D158" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E158">
         <v>2.183719283702006</v>
@@ -9360,7 +9351,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9374,7 +9365,7 @@
         <v>2.721632856402064</v>
       </c>
       <c r="D159" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E159">
         <v>2.127916568873808</v>
@@ -9410,7 +9401,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9424,7 +9415,7 @@
         <v>2.678525715783303</v>
       </c>
       <c r="D160" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E160">
         <v>2.09532033365037</v>
@@ -9460,7 +9451,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9474,7 +9465,7 @@
         <v>2.69110921416971</v>
       </c>
       <c r="D161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E161">
         <v>2.09532033365037</v>
@@ -9510,7 +9501,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9610,7 +9601,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9660,7 +9651,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9710,7 +9701,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9860,7 +9851,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9910,7 +9901,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9960,7 +9951,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10010,7 +10001,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10060,7 +10051,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10110,7 +10101,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10160,7 +10151,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10174,7 +10165,7 @@
         <v>0.9328900239147986</v>
       </c>
       <c r="D175" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E175">
         <v>0.9481209772972727</v>
@@ -10210,7 +10201,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10224,7 +10215,7 @@
         <v>0.8361716558948933</v>
       </c>
       <c r="D176" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E176">
         <v>0.9453648051842674</v>
@@ -10274,7 +10265,7 @@
         <v>1.860133746163766</v>
       </c>
       <c r="D177" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E177">
         <v>1.319668494742769</v>
@@ -10310,7 +10301,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10324,7 +10315,7 @@
         <v>0.8121110647030001</v>
       </c>
       <c r="D178" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E178">
         <v>0.9618784389925015</v>
@@ -10360,7 +10351,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10374,7 +10365,7 @@
         <v>1.83652515616036</v>
       </c>
       <c r="D179" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E179">
         <v>1.296242563075947</v>
@@ -10410,7 +10401,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10424,7 +10415,7 @@
         <v>0.787726176769115</v>
       </c>
       <c r="D180" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E180">
         <v>1.126454507889258</v>
@@ -10460,7 +10451,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10474,7 +10465,7 @@
         <v>1.791439637530079</v>
       </c>
       <c r="D181" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E181">
         <v>1.27124240240025</v>
@@ -10510,7 +10501,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10524,7 +10515,7 @@
         <v>1.811330062457952</v>
       </c>
       <c r="D182" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E182">
         <v>1.27124240240025</v>
@@ -10560,7 +10551,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10574,7 +10565,7 @@
         <v>1.791373892486802</v>
       </c>
       <c r="D183" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E183">
         <v>1.27124240240025</v>
@@ -10610,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10624,7 +10615,7 @@
         <v>0.7617026177031843</v>
       </c>
       <c r="D184" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E184">
         <v>1.161198572371399</v>
@@ -10660,7 +10651,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10674,7 +10665,7 @@
         <v>1.756679227858482</v>
       </c>
       <c r="D185" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E185">
         <v>1.246983702650287</v>
@@ -10710,7 +10701,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10724,7 +10715,7 @@
         <v>1.786882211053019</v>
       </c>
       <c r="D186" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E186">
         <v>1.246983702650287</v>
@@ -10760,7 +10751,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10774,7 +10765,7 @@
         <v>1.766831465254384</v>
       </c>
       <c r="D187" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E187">
         <v>1.246983702650287</v>
@@ -10810,7 +10801,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10824,7 +10815,7 @@
         <v>0.7364508717646272</v>
       </c>
       <c r="D188" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E188">
         <v>1.146806092355067</v>
@@ -10860,7 +10851,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10874,7 +10865,7 @@
         <v>1.727529637465925</v>
       </c>
       <c r="D189" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E189">
         <v>1.218500388609561</v>
@@ -10910,7 +10901,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10924,7 +10915,7 @@
         <v>1.758176804895015</v>
       </c>
       <c r="D190" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E190">
         <v>1.218500388609561</v>
@@ -10960,7 +10951,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10974,7 +10965,7 @@
         <v>1.738015013037742</v>
       </c>
       <c r="D191" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E191">
         <v>1.218500388609561</v>
@@ -11010,7 +11001,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11024,7 +11015,7 @@
         <v>0.735911718893199</v>
       </c>
       <c r="D192" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E192">
         <v>1.39631619853638</v>
@@ -11060,7 +11051,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11074,7 +11065,7 @@
         <v>0.7068015741081979</v>
       </c>
       <c r="D193" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E193">
         <v>1.39631619853638</v>
@@ -11110,7 +11101,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11124,7 +11115,7 @@
         <v>1.69440254301529</v>
       </c>
       <c r="D194" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E194">
         <v>1.186130484889226</v>
@@ -11160,7 +11151,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11174,7 +11165,7 @@
         <v>1.725554504264581</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E195">
         <v>1.186130484889226</v>
@@ -11210,7 +11201,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11224,7 +11215,7 @@
         <v>1.705266513952258</v>
       </c>
       <c r="D196" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E196">
         <v>1.186130484889226</v>
@@ -11260,7 +11251,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11274,7 +11265,7 @@
         <v>0.7015226398920635</v>
       </c>
       <c r="D197" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E197">
         <v>1.362242615672869</v>
@@ -11310,7 +11301,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11324,7 +11315,7 @@
         <v>0.6731065866098378</v>
       </c>
       <c r="D198" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E198">
         <v>1.362242615672869</v>
@@ -11360,7 +11351,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11374,7 +11365,7 @@
         <v>1.672556215816603</v>
       </c>
       <c r="D199" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E199">
         <v>1.164783502312224</v>
@@ -11410,7 +11401,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11424,7 +11415,7 @@
         <v>1.70404107348035</v>
       </c>
       <c r="D200" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E200">
         <v>1.164783502312224</v>
@@ -11460,7 +11451,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11474,7 +11465,7 @@
         <v>1.683669859064413</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E201">
         <v>1.164783502312224</v>
@@ -11510,7 +11501,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11524,7 +11515,7 @@
         <v>0.6788440716572364</v>
       </c>
       <c r="D202" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E202">
         <v>1.339772107697077</v>
@@ -11560,7 +11551,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11574,7 +11565,7 @@
         <v>0.6508857509448882</v>
       </c>
       <c r="D203" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E203">
         <v>1.339772107697077</v>
@@ -11610,7 +11601,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11624,7 +11615,7 @@
         <v>1.643503437868948</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E204">
         <v>1.136394787860515</v>
@@ -11660,7 +11651,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11674,7 +11665,7 @@
         <v>1.675431004529993</v>
       </c>
       <c r="D205" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E205">
         <v>1.136394787860515</v>
@@ -11710,7 +11701,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11724,7 +11715,7 @@
         <v>1.654949112864731</v>
       </c>
       <c r="D206" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E206">
         <v>1.136394787860515</v>
@@ -11760,7 +11751,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11774,7 +11765,7 @@
         <v>0.648684521216337</v>
       </c>
       <c r="D207" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E207">
         <v>1.309889250379489</v>
@@ -11810,7 +11801,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11824,7 +11815,7 @@
         <v>0.6213349253752734</v>
       </c>
       <c r="D208" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E208">
         <v>1.309889250379489</v>
@@ -11860,7 +11851,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11874,7 +11865,7 @@
         <v>1.629688879456757</v>
       </c>
       <c r="D209" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E209">
         <v>1.122895990783459</v>
@@ -11924,7 +11915,7 @@
         <v>1.661826953674558</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E210">
         <v>1.122895990783459</v>
@@ -11974,7 +11965,7 @@
         <v>1.623163250060685</v>
       </c>
       <c r="D211" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E211">
         <v>1.122895990783459</v>
@@ -12024,7 +12015,7 @@
         <v>0.6343436939122524</v>
       </c>
       <c r="D212" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E212">
         <v>1.295679990298378</v>
@@ -12074,7 +12065,7 @@
         <v>0.6072835459617298</v>
       </c>
       <c r="D213" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E213">
         <v>1.295679990298378</v>
@@ -12124,7 +12115,7 @@
         <v>1.607589133113905</v>
       </c>
       <c r="D214" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E214">
         <v>1.101301381499872</v>
@@ -12160,7 +12151,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12174,7 +12165,7 @@
         <v>1.640063965371216</v>
       </c>
       <c r="D215" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E215">
         <v>1.101301381499872</v>
@@ -12210,7 +12201,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12224,7 +12215,7 @@
         <v>1.619445257306888</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E216">
         <v>1.101301381499872</v>
@@ -12260,7 +12251,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12274,7 +12265,7 @@
         <v>0.6114020524706252</v>
       </c>
       <c r="D217" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E217">
         <v>1.272948822631444</v>
@@ -12310,7 +12301,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12324,7 +12315,7 @@
         <v>0.5848049468244287</v>
       </c>
       <c r="D218" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E218">
         <v>1.272948822631444</v>
@@ -12360,7 +12351,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12374,7 +12365,7 @@
         <v>1.581012843353852</v>
       </c>
       <c r="D219" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E219">
         <v>1.075332549791479</v>
@@ -12410,7 +12401,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12424,7 +12415,7 @@
         <v>1.613892647645603</v>
       </c>
       <c r="D220" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E220">
         <v>1.075332549791479</v>
@@ -12460,7 +12451,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12474,7 +12465,7 @@
         <v>1.593172696572664</v>
       </c>
       <c r="D221" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E221">
         <v>1.075332549791479</v>
@@ -12510,7 +12501,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12524,7 +12515,7 @@
         <v>0.5838133326244757</v>
       </c>
       <c r="D222" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E222">
         <v>1.245613210306819</v>
@@ -12560,7 +12551,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12574,7 +12565,7 @@
         <v>0.5577730635256328</v>
       </c>
       <c r="D223" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E223">
         <v>1.245613210306819</v>
@@ -12610,7 +12601,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12624,7 +12615,7 @@
         <v>1.084913495598071</v>
       </c>
       <c r="D224" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E224">
         <v>1.231364667854545</v>
@@ -12660,7 +12651,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12674,7 +12665,7 @@
         <v>1.091978143921128</v>
       </c>
       <c r="D225" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E225">
         <v>1.231364667854545</v>
@@ -12710,7 +12701,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12760,7 +12751,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12774,7 +12765,7 @@
         <v>1.21869175173632</v>
       </c>
       <c r="D227" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E227">
         <v>1.069755686141992</v>
@@ -12810,7 +12801,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12824,7 +12815,7 @@
         <v>1.184556198440929</v>
       </c>
       <c r="D228" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E228">
         <v>1.069755686141992</v>
@@ -12860,7 +12851,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12874,7 +12865,7 @@
         <v>1.060519812222489</v>
       </c>
       <c r="D229" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E229">
         <v>0.9907313015562922</v>
@@ -12910,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12924,7 +12915,7 @@
         <v>1.017939761129645</v>
       </c>
       <c r="D230" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E230">
         <v>0.9907313015562922</v>
@@ -12960,7 +12951,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12974,7 +12965,7 @@
         <v>1.755318635505916</v>
       </c>
       <c r="D231" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E231">
         <v>1.003833585600265</v>
@@ -13010,7 +13001,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13024,7 +13015,7 @@
         <v>1.894053096403</v>
       </c>
       <c r="D232" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E232">
         <v>1.003833585600265</v>
@@ -13060,7 +13051,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13074,7 +13065,7 @@
         <v>1.97376040323609</v>
       </c>
       <c r="D233" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E233">
         <v>1.250262419204153</v>
@@ -13110,7 +13101,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13124,7 +13115,7 @@
         <v>2.034815821986728</v>
       </c>
       <c r="D234" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E234">
         <v>1.357988243685597</v>
@@ -13160,7 +13151,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13174,7 +13165,7 @@
         <v>2.10245468159479</v>
       </c>
       <c r="D235" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E235">
         <v>1.356708020256039</v>
@@ -13210,7 +13201,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13224,7 +13215,7 @@
         <v>2.160736912923812</v>
       </c>
       <c r="D236" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E236">
         <v>1.515238926320149</v>
@@ -13260,7 +13251,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13274,7 +13265,7 @@
         <v>2.25315272423952</v>
       </c>
       <c r="D237" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E237">
         <v>1.696228284995405</v>
@@ -13310,7 +13301,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13324,7 +13315,7 @@
         <v>2.36943391560179</v>
       </c>
       <c r="D238" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E238">
         <v>1.892500425794016</v>
@@ -13360,7 +13351,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13374,7 +13365,7 @@
         <v>2.474058411102812</v>
       </c>
       <c r="D239" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E239">
         <v>1.89058438855279</v>
@@ -13410,7 +13401,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13424,7 +13415,7 @@
         <v>2.503056313450243</v>
       </c>
       <c r="D240" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E240">
         <v>1.996322171701399</v>
@@ -13460,7 +13451,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13474,7 +13465,7 @@
         <v>2.525264172262913</v>
       </c>
       <c r="D241" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E241">
         <v>1.973847066177296</v>
@@ -13510,7 +13501,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13524,7 +13515,7 @@
         <v>2.554243076596262</v>
       </c>
       <c r="D242" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E242">
         <v>1.938989294196617</v>
@@ -13560,7 +13551,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13574,7 +13565,7 @@
         <v>2.598334390223854</v>
       </c>
       <c r="D243" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E243">
         <v>2.028465786771591</v>
@@ -13610,7 +13601,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13624,7 +13615,7 @@
         <v>2.670586589154834</v>
       </c>
       <c r="D244" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E244">
         <v>1.994395774818371</v>
@@ -13674,7 +13665,7 @@
         <v>2.717624878766997</v>
       </c>
       <c r="D245" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E245">
         <v>2.20711354567414</v>
@@ -13724,7 +13715,7 @@
         <v>2.768201130893359</v>
       </c>
       <c r="D246" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E246">
         <v>2.294068506214541</v>
@@ -13760,7 +13751,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13774,7 +13765,7 @@
         <v>2.800856629280805</v>
       </c>
       <c r="D247" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E247">
         <v>2.225122088576691</v>
@@ -13810,7 +13801,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13824,7 +13815,7 @@
         <v>2.80951643088527</v>
       </c>
       <c r="D248" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E248">
         <v>2.242646460311337</v>
@@ -13860,7 +13851,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13874,7 +13865,7 @@
         <v>2.799569806125956</v>
       </c>
       <c r="D249" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E249">
         <v>2.14320981989216</v>
@@ -13924,7 +13915,7 @@
         <v>2.819828844666985</v>
       </c>
       <c r="D250" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E250">
         <v>2.18506309598321</v>
@@ -13960,7 +13951,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13974,7 +13965,7 @@
         <v>2.819851650007405</v>
       </c>
       <c r="D251" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E251">
         <v>2.072484872689354</v>
@@ -14024,7 +14015,7 @@
         <v>2.840423697083499</v>
       </c>
       <c r="D252" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E252">
         <v>2.262963564508703</v>
@@ -14074,7 +14065,7 @@
         <v>2.908629147129241</v>
       </c>
       <c r="D253" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E253">
         <v>2.216875943157096</v>
@@ -14110,7 +14101,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14124,7 +14115,7 @@
         <v>3.004384252257208</v>
       </c>
       <c r="D254" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E254">
         <v>2.339997391123474</v>
@@ -14160,7 +14151,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14174,7 +14165,7 @@
         <v>3.088901753172625</v>
       </c>
       <c r="D255" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E255">
         <v>2.06246025697973</v>
@@ -14210,7 +14201,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14224,7 +14215,7 @@
         <v>3.179054845713715</v>
       </c>
       <c r="D256" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E256">
         <v>2.414075593575115</v>
@@ -14260,7 +14251,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14274,7 +14265,7 @@
         <v>3.299462923221598</v>
       </c>
       <c r="D257" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E257">
         <v>2.237378699869055</v>
@@ -14310,7 +14301,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14324,7 +14315,7 @@
         <v>3.418692237363245</v>
       </c>
       <c r="D258" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E258">
         <v>2.342027703405609</v>
@@ -14360,7 +14351,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14374,7 +14365,7 @@
         <v>3.512759057977069</v>
       </c>
       <c r="D259" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E259">
         <v>2.424591283628788</v>
@@ -14410,7 +14401,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14424,7 +14415,7 @@
         <v>3.645345160280047</v>
       </c>
       <c r="D260" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E260">
         <v>2.540963700837517</v>
@@ -14460,7 +14451,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14474,7 +14465,7 @@
         <v>3.815771971902112</v>
       </c>
       <c r="D261" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E261">
         <v>2.690549363898303</v>
@@ -14510,7 +14501,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14524,7 +14515,7 @@
         <v>4.010037470388323</v>
       </c>
       <c r="D262" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E262">
         <v>2.861058529236299</v>
@@ -14560,7 +14551,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14574,7 +14565,7 @@
         <v>4.152500561307447</v>
       </c>
       <c r="D263" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E263">
         <v>2.986100098188981</v>
@@ -14610,7 +14601,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14624,7 +14615,7 @@
         <v>4.227000299262723</v>
       </c>
       <c r="D264" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E264">
         <v>3.05148941454026</v>
@@ -14660,7 +14651,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14674,7 +14665,7 @@
         <v>3.628868452425993</v>
       </c>
       <c r="D265" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E265">
         <v>3.018868452425993</v>
@@ -14710,7 +14701,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14724,7 +14715,7 @@
         <v>3.56416211054958</v>
       </c>
       <c r="D266" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E266">
         <v>2.954162110549579</v>
@@ -14760,7 +14751,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14774,7 +14765,7 @@
         <v>3.491997735810393</v>
       </c>
       <c r="D267" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E267">
         <v>2.881997735810393</v>
@@ -14810,7 +14801,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14824,7 +14815,7 @@
         <v>3.304014584160329</v>
       </c>
       <c r="D268" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E268">
         <v>2.694014584160328</v>
@@ -14860,7 +14851,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14874,7 +14865,7 @@
         <v>3.180251695694135</v>
       </c>
       <c r="D269" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E269">
         <v>2.570251695694135</v>
@@ -14910,7 +14901,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14924,7 +14915,7 @@
         <v>3.152401945865307</v>
       </c>
       <c r="D270" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E270">
         <v>2.542401945865306</v>
@@ -14960,7 +14951,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14974,7 +14965,7 @@
         <v>2.145825454055195</v>
       </c>
       <c r="D271" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E271">
         <v>2.567272076620798</v>
@@ -15010,7 +15001,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15024,7 +15015,7 @@
         <v>3.117834193471839</v>
       </c>
       <c r="D272" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E272">
         <v>2.507834193471838</v>
@@ -15060,7 +15051,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15074,7 +15065,7 @@
         <v>2.068689520733654</v>
       </c>
       <c r="D273" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E273">
         <v>2.489975777533515</v>
@@ -15110,7 +15101,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15124,7 +15115,7 @@
         <v>3.048235451140136</v>
       </c>
       <c r="D274" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E274">
         <v>2.438235451140136</v>
@@ -15160,7 +15151,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15174,7 +15165,7 @@
         <v>1.98934486068918</v>
       </c>
       <c r="D275" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E275">
         <v>2.539161477129087</v>
@@ -15210,7 +15201,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15224,7 +15215,7 @@
         <v>2.976643803615602</v>
       </c>
       <c r="D276" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E276">
         <v>2.366643803615601</v>
@@ -15260,7 +15251,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15274,7 +15265,7 @@
         <v>1.910228381091732</v>
       </c>
       <c r="D277" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E277">
         <v>2.463005697391833</v>
@@ -15310,7 +15301,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15324,7 +15315,7 @@
         <v>2.905258040319775</v>
       </c>
       <c r="D278" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E278">
         <v>2.295258040319774</v>
@@ -15360,7 +15351,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15374,7 +15365,7 @@
         <v>1.737565923958936</v>
       </c>
       <c r="D279" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E279">
         <v>2.268709795269682</v>
@@ -15410,7 +15401,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15424,7 +15415,7 @@
         <v>1.733986526635413</v>
       </c>
       <c r="D280" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E280">
         <v>2.293359172208309</v>
@@ -15460,7 +15451,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15474,7 +15465,7 @@
         <v>2.746237323409084</v>
       </c>
       <c r="D281" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E281">
         <v>2.136237323409084</v>
@@ -15510,7 +15501,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15524,7 +15515,7 @@
         <v>1.537618654463894</v>
       </c>
       <c r="D282" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E282">
         <v>2.074713337366754</v>
@@ -15560,7 +15551,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15574,7 +15565,7 @@
         <v>1.543163834914946</v>
       </c>
       <c r="D283" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E283">
         <v>2.109677454398378</v>
@@ -15610,7 +15601,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15624,7 +15615,7 @@
         <v>2.574060508010575</v>
       </c>
       <c r="D284" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E284">
         <v>1.964060508010575</v>
@@ -15660,7 +15651,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15674,7 +15665,7 @@
         <v>1.32861267508225</v>
       </c>
       <c r="D285" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E285">
         <v>1.871927774038136</v>
@@ -15710,7 +15701,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15724,7 +15715,7 @@
         <v>1.343695826814607</v>
       </c>
       <c r="D286" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E286">
         <v>1.91767394556167</v>
@@ -15760,7 +15751,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15774,7 +15765,7 @@
         <v>2.394083136876382</v>
       </c>
       <c r="D287" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E287">
         <v>1.784083136876382</v>
@@ -15810,7 +15801,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15824,7 +15815,7 @@
         <v>1.270355943810468</v>
       </c>
       <c r="D288" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E288">
         <v>1.815404874054204</v>
@@ -15860,7 +15851,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15874,7 +15865,7 @@
         <v>1.288097636850863</v>
       </c>
       <c r="D289" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E289">
         <v>1.864156353143347</v>
@@ -15910,7 +15901,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15924,7 +15915,7 @@
         <v>2.343917618281236</v>
       </c>
       <c r="D290" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E290">
         <v>1.733917618281236</v>
@@ -15960,7 +15951,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15974,7 +15965,7 @@
         <v>1.164376800206434</v>
       </c>
       <c r="D291" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E291">
         <v>1.712579871628862</v>
@@ -16010,7 +16001,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16024,7 +16015,7 @@
         <v>1.186954843054156</v>
       </c>
       <c r="D292" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E292">
         <v>1.76679852876107</v>
@@ -16060,7 +16051,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16074,7 +16065,7 @@
         <v>2.252657800177763</v>
       </c>
       <c r="D293" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E293">
         <v>1.642657800177763</v>
@@ -16110,7 +16101,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16124,7 +16115,7 @@
         <v>1.095337982971794</v>
       </c>
       <c r="D294" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E294">
         <v>1.645595781097634</v>
@@ -16160,7 +16151,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16174,7 +16165,7 @@
         <v>1.121066606764748</v>
       </c>
       <c r="D295" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E295">
         <v>1.703375964515756</v>
@@ -16210,7 +16201,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16224,7 +16215,7 @@
         <v>2.193207707559045</v>
       </c>
       <c r="D296" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E296">
         <v>1.583207707559045</v>
@@ -16260,7 +16251,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16274,7 +16265,7 @@
         <v>0.875155284260706</v>
       </c>
       <c r="D297" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E297">
         <v>1.489897717173242</v>
@@ -16310,7 +16301,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16324,7 +16315,7 @@
         <v>0.9109319280345227</v>
       </c>
       <c r="D298" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E298">
         <v>1.501104953596641</v>
@@ -16360,7 +16351,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16374,7 +16365,7 @@
         <v>2.003605939224497</v>
       </c>
       <c r="D299" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E299">
         <v>1.393605939224496</v>
@@ -16410,7 +16401,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16424,7 +16415,7 @@
         <v>0.7877632879655483</v>
       </c>
       <c r="D300" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E300">
         <v>1.407881022237508</v>
@@ -16460,7 +16451,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16474,7 +16465,7 @@
         <v>0.8275280585544227</v>
       </c>
       <c r="D301" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E301">
         <v>1.420822226841367</v>
@@ -16510,7 +16501,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16524,7 +16515,7 @@
         <v>1.928351720192556</v>
       </c>
       <c r="D302" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E302">
         <v>1.318351720192555</v>
@@ -16560,7 +16551,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16574,7 +16565,7 @@
         <v>0.6445889510900153</v>
       </c>
       <c r="D303" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E303">
         <v>1.273513043384081</v>
@@ -16610,7 +16601,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16624,7 +16615,7 @@
         <v>0.6908874711791615</v>
       </c>
       <c r="D304" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E304">
         <v>1.289295008640233</v>
@@ -16660,7 +16651,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16674,7 +16665,7 @@
         <v>1.805062707883069</v>
       </c>
       <c r="D305" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E305">
         <v>1.195062707883069</v>
@@ -16710,7 +16701,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16724,7 +16715,7 @@
         <v>0.5834745700515587</v>
       </c>
       <c r="D306" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E306">
         <v>1.216157681814259</v>
@@ -16760,7 +16751,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16774,7 +16765,7 @@
         <v>0.6325620400690468</v>
       </c>
       <c r="D307" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E307">
         <v>1.233152233995777</v>
@@ -16810,7 +16801,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16824,7 +16815,7 @@
         <v>1.752436435322175</v>
       </c>
       <c r="D308" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E308">
         <v>1.142436435322175</v>
@@ -16860,7 +16851,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16874,7 +16865,7 @@
         <v>0.6410588642705362</v>
       </c>
       <c r="D309" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E309">
         <v>1.24133108972403</v>
@@ -16910,7 +16901,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16924,7 +16915,7 @@
         <v>0.6556505260902954</v>
       </c>
       <c r="D310" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E310">
         <v>1.24133108972403</v>
@@ -16960,7 +16951,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16974,7 +16965,7 @@
         <v>1.760103008510213</v>
       </c>
       <c r="D311" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E311">
         <v>1.150103008510213</v>
@@ -17010,7 +17001,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17024,7 +17015,7 @@
         <v>0.6538601304024763</v>
       </c>
       <c r="D312" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E312">
         <v>1.253653306395731</v>
@@ -17060,7 +17051,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17074,7 +17065,7 @@
         <v>0.6691703664125939</v>
       </c>
       <c r="D313" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E313">
         <v>1.253653306395731</v>
@@ -17110,7 +17101,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17124,7 +17115,7 @@
         <v>1.771653423273752</v>
       </c>
       <c r="D314" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E314">
         <v>1.161653423273751</v>
@@ -17160,7 +17151,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17174,7 +17165,7 @@
         <v>0.5994681371241404</v>
       </c>
       <c r="D315" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E315">
         <v>1.201296772325317</v>
@@ -17210,7 +17201,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17224,7 +17215,7 @@
         <v>0.6117251843223768</v>
       </c>
       <c r="D316" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E316">
         <v>1.201296772325317</v>
@@ -17260,7 +17251,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17274,7 +17265,7 @@
         <v>1.722576240149433</v>
       </c>
       <c r="D317" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E317">
         <v>1.112576240149433</v>
@@ -17310,7 +17301,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17324,7 +17315,7 @@
         <v>0.6080222404361217</v>
       </c>
       <c r="D318" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E318">
         <v>1.209530763663045</v>
@@ -17360,7 +17351,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17374,7 +17365,7 @@
         <v>0.6207594555957376</v>
       </c>
       <c r="D319" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E319">
         <v>1.209530763663045</v>
@@ -17410,7 +17401,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17424,7 +17415,7 @@
         <v>1.730294495528642</v>
       </c>
       <c r="D320" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E320">
         <v>1.120294495528642</v>
@@ -17460,7 +17451,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17474,7 +17465,7 @@
         <v>0.5618859798618736</v>
       </c>
       <c r="D321" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E321">
         <v>1.165121015958519</v>
@@ -17510,7 +17501,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17524,7 +17515,7 @@
         <v>0.5720334257169055</v>
       </c>
       <c r="D322" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E322">
         <v>1.165121015958519</v>
@@ -17560,7 +17551,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17574,7 +17565,7 @@
         <v>1.688666351892003</v>
       </c>
       <c r="D323" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E323">
         <v>1.078666351892003</v>
@@ -17610,7 +17601,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17624,7 +17615,7 @@
         <v>0.508437810595022</v>
       </c>
       <c r="D324" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E324">
         <v>1.11367298608211</v>
@@ -17660,7 +17651,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17674,7 +17665,7 @@
         <v>0.5155850473643886</v>
       </c>
       <c r="D325" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E325">
         <v>1.11367298608211</v>
@@ -17710,7 +17701,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17724,7 +17715,7 @@
         <v>1.640440768811309</v>
       </c>
       <c r="D326" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E326">
         <v>1.030440768811308</v>
@@ -17760,7 +17751,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17774,7 +17765,7 @@
         <v>0.4164767378858123</v>
       </c>
       <c r="D327" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E327">
         <v>1.025153284077196</v>
@@ -17810,7 +17801,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17824,7 +17815,7 @@
         <v>0.4184619185987364</v>
       </c>
       <c r="D328" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E328">
         <v>1.025153284077196</v>
@@ -17860,7 +17851,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17874,7 +17865,7 @@
         <v>1.557465497385535</v>
       </c>
       <c r="D329" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E329">
         <v>0.9474654973855348</v>
@@ -17910,7 +17901,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17924,7 +17915,7 @@
         <v>0.3644704529510241</v>
       </c>
       <c r="D330" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E330">
         <v>0.9750931802834177</v>
@@ -17960,7 +17951,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17974,7 +17965,7 @@
         <v>0.3635363619524323</v>
       </c>
       <c r="D331" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E331">
         <v>0.9750931802834177</v>
@@ -18010,7 +18001,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18024,7 +18015,7 @@
         <v>1.565054544022541</v>
       </c>
       <c r="D332" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E332">
         <v>0.9005409076522746</v>
@@ -18060,7 +18051,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18074,7 +18065,7 @@
         <v>0.2866150347691372</v>
       </c>
       <c r="D333" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E333">
         <v>0.9143380680881883</v>
@@ -18110,7 +18101,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18124,7 +18115,7 @@
         <v>0.2813106812114787</v>
       </c>
       <c r="D334" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E334">
         <v>0.9143380680881883</v>
@@ -18160,7 +18151,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18174,7 +18165,7 @@
         <v>0.3483831526216896</v>
       </c>
       <c r="D335" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E335">
         <v>0.9143380680881883</v>
@@ -18210,7 +18201,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18224,7 +18215,7 @@
         <v>1.495130343077478</v>
       </c>
       <c r="D336" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E336">
         <v>0.8302929835546884</v>
@@ -18260,7 +18251,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18274,7 +18265,7 @@
         <v>0.2225831635998929</v>
       </c>
       <c r="D337" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E337">
         <v>0.8619688447062037</v>
@@ -18324,7 +18315,7 @@
         <v>0.2987488573747035</v>
       </c>
       <c r="D338" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E338">
         <v>0.8619688447062037</v>
@@ -18374,7 +18365,7 @@
         <v>0.2938174275967516</v>
       </c>
       <c r="D339" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E339">
         <v>0.8619688447062037</v>
@@ -18424,7 +18415,7 @@
         <v>1.445188832037704</v>
       </c>
       <c r="D340" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E340">
         <v>0.7801202618156564</v>
@@ -18474,7 +18465,7 @@
         <v>0.3281392211768228</v>
       </c>
       <c r="D341" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E341">
         <v>0.8803786785285439</v>
@@ -18510,7 +18501,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18524,7 +18515,7 @@
         <v>0.3180121272020529</v>
       </c>
       <c r="D342" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E342">
         <v>0.8803786785285439</v>
@@ -18560,7 +18551,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18574,7 +18565,7 @@
         <v>0.3129994178045763</v>
       </c>
       <c r="D343" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E343">
         <v>0.8803786785285439</v>
@@ -18610,7 +18601,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18624,7 +18615,7 @@
         <v>1.462745229855035</v>
       </c>
       <c r="D344" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E344">
         <v>0.7977579392525129</v>
@@ -18660,7 +18651,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18674,7 +18665,7 @@
         <v>0.3459316339300287</v>
       </c>
       <c r="D345" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E345">
         <v>0.8966943930572944</v>
@@ -18710,7 +18701,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18724,7 +18715,7 @@
         <v>0.3350841993579632</v>
       </c>
       <c r="D346" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E346">
         <v>0.8966943930572944</v>
@@ -18760,7 +18751,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18774,7 +18765,7 @@
         <v>0.3299994559007571</v>
       </c>
       <c r="D347" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E347">
         <v>0.8966943930572944</v>
@@ -18810,7 +18801,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18824,7 +18815,7 @@
         <v>1.478304586756625</v>
       </c>
       <c r="D348" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E348">
         <v>0.8133893302138313</v>
@@ -18860,7 +18851,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18874,7 +18865,7 @@
         <v>0.3746816311597856</v>
       </c>
       <c r="D349" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E349">
         <v>0.9230582569137313</v>
@@ -18910,7 +18901,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18924,7 +18915,7 @@
         <v>0.3626702290885397</v>
       </c>
       <c r="D350" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E350">
         <v>0.9230582569137313</v>
@@ -18960,7 +18951,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18974,7 +18965,7 @@
         <v>0.357469088881416</v>
       </c>
       <c r="D351" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E351">
         <v>0.9230582569137313</v>
@@ -19010,7 +19001,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19024,7 +19015,7 @@
         <v>1.503446284738923</v>
       </c>
       <c r="D352" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E352">
         <v>0.8386474249460472</v>
@@ -19060,7 +19051,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19074,7 +19065,7 @@
         <v>0.3609903029368784</v>
       </c>
       <c r="D353" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E353">
         <v>0.9727726579916833</v>
@@ -19124,7 +19115,7 @@
         <v>0.4278925267560636</v>
       </c>
       <c r="D354" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E354">
         <v>0.9853909591149721</v>
@@ -19174,7 +19165,7 @@
         <v>0.4224161869807217</v>
       </c>
       <c r="D355" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E355">
         <v>0.9853909591149721</v>
@@ -19224,7 +19215,7 @@
         <v>1.508365731249223</v>
       </c>
       <c r="D356" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E356">
         <v>0.898365731249223</v>
@@ -19274,7 +19265,7 @@
         <v>0.5369709001154694</v>
       </c>
       <c r="D357" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E357">
         <v>1.089636746312885</v>
@@ -19324,7 +19315,7 @@
         <v>0.531034314039033</v>
       </c>
       <c r="D358" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E358">
         <v>1.089636746312885</v>
@@ -19374,7 +19365,7 @@
         <v>1.608239178586738</v>
       </c>
       <c r="D359" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E359">
         <v>0.9982391785867382</v>
@@ -19424,7 +19415,7 @@
         <v>0.5385854937585846</v>
       </c>
       <c r="D360" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E360">
         <v>0.634839149452838</v>
@@ -19474,7 +19465,7 @@
         <v>2.009812451983092</v>
       </c>
       <c r="D361" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E361">
         <v>1.399812451983092</v>
@@ -19510,7 +19501,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19524,7 +19515,7 @@
         <v>0.9230051396340304</v>
       </c>
       <c r="D362" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E362">
         <v>0.9850070169538339</v>
@@ -19560,7 +19551,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19574,7 +19565,7 @@
         <v>0.8994749023453439</v>
       </c>
       <c r="D363" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E363">
         <v>0.9850070169538339</v>
@@ -19610,7 +19601,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19624,7 +19615,7 @@
         <v>2.109691017081675</v>
       </c>
       <c r="D364" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E364">
         <v>1.499691017081674</v>
@@ -19660,7 +19651,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19674,7 +19665,7 @@
         <v>1.015979656453909</v>
       </c>
       <c r="D365" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E365">
         <v>1.231185799135601</v>
@@ -19710,7 +19701,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19724,7 +19715,7 @@
         <v>0.9827837515750368</v>
       </c>
       <c r="D366" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E366">
         <v>1.231185799135601</v>
@@ -19760,7 +19751,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19774,7 +19765,7 @@
         <v>2.200993423621709</v>
       </c>
       <c r="D367" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E367">
         <v>1.590993423621708</v>
@@ -19810,7 +19801,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19824,7 +19815,7 @@
         <v>1.100970836735415</v>
       </c>
       <c r="D368" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E368">
         <v>1.303589318044656</v>
@@ -19860,7 +19851,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19874,7 +19865,7 @@
         <v>1.058939215094605</v>
       </c>
       <c r="D369" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E369">
         <v>1.303589318044656</v>
@@ -19910,7 +19901,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19924,7 +19915,7 @@
         <v>2.329644706282916</v>
       </c>
       <c r="D370" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E370">
         <v>1.719644706282915</v>
@@ -19960,7 +19951,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19974,7 +19965,7 @@
         <v>1.220729173590548</v>
       </c>
       <c r="D371" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E371">
         <v>1.321050696987874</v>
@@ -20010,7 +20001,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20024,7 +20015,7 @@
         <v>2.471463589779925</v>
       </c>
       <c r="D372" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E372">
         <v>1.861463589779925</v>
@@ -20060,7 +20051,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20110,7 +20101,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20124,7 +20115,7 @@
         <v>2.497443975683849</v>
       </c>
       <c r="D374" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E374">
         <v>1.887443975683849</v>
@@ -20160,7 +20151,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20210,7 +20201,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20260,7 +20251,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20274,7 +20265,7 @@
         <v>2.512308244184901</v>
       </c>
       <c r="D377" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E377">
         <v>1.9023082441849</v>
@@ -20310,7 +20301,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20324,7 +20315,7 @@
         <v>1.390766199655991</v>
       </c>
       <c r="D378" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E378">
         <v>1.47783631505106</v>
@@ -20360,7 +20351,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20374,7 +20365,7 @@
         <v>1.39783631505106</v>
       </c>
       <c r="D379" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E379">
         <v>1.47783631505106</v>
@@ -20410,7 +20401,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20424,7 +20415,7 @@
         <v>2.5135497431605</v>
       </c>
       <c r="D380" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E380">
         <v>1.903549743160499</v>
@@ -20460,7 +20451,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20474,7 +20465,7 @@
         <v>1.39192188073005</v>
       </c>
       <c r="D381" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E381">
         <v>1.488828942112197</v>
@@ -20510,7 +20501,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20524,7 +20515,7 @@
         <v>1.319642873327421</v>
       </c>
       <c r="D382" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E382">
         <v>1.488828942112197</v>
@@ -20560,7 +20551,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20574,7 +20565,7 @@
         <v>1.388828942112196</v>
       </c>
       <c r="D383" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E383">
         <v>1.488828942112197</v>
@@ -20610,7 +20601,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20624,7 +20615,7 @@
         <v>2.501566998394471</v>
       </c>
       <c r="D384" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E384">
         <v>1.891566998394471</v>
@@ -20660,7 +20651,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20674,7 +20665,7 @@
         <v>1.279594745212004</v>
       </c>
       <c r="D385" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E385">
         <v>1.519061703811337</v>
@@ -20710,7 +20701,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20724,7 +20715,7 @@
         <v>1.30964804935207</v>
       </c>
       <c r="D386" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E386">
         <v>1.519061703811337</v>
@@ -20760,7 +20751,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20774,7 +20765,7 @@
         <v>2.48573721583752</v>
       </c>
       <c r="D387" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E387">
         <v>1.875737215837519</v>
@@ -20810,7 +20801,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20824,7 +20815,7 @@
         <v>1.266464050003473</v>
       </c>
       <c r="D388" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E388">
         <v>1.59667031375327</v>
@@ -20860,7 +20851,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20874,7 +20865,7 @@
         <v>1.296444405836825</v>
       </c>
       <c r="D389" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E389">
         <v>1.59667031375327</v>
@@ -20910,7 +20901,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20924,7 +20915,7 @@
         <v>2.454303876936348</v>
       </c>
       <c r="D390" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E390">
         <v>1.844303876936348</v>
@@ -20960,7 +20951,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20974,7 +20965,7 @@
         <v>1.240390312666095</v>
       </c>
       <c r="D391" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E391">
         <v>1.592199793558723</v>
@@ -21010,7 +21001,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21024,7 +21015,7 @@
         <v>1.270225814403128</v>
       </c>
       <c r="D392" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E392">
         <v>1.592199793558723</v>
@@ -21060,7 +21051,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21074,7 +21065,7 @@
         <v>2.438801816749918</v>
       </c>
       <c r="D393" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E393">
         <v>1.828801816749918</v>
@@ -21110,7 +21101,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21124,7 +21115,7 @@
         <v>1.227531460898549</v>
       </c>
       <c r="D394" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E394">
         <v>1.611306442152011</v>
@@ -21160,7 +21151,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21174,7 +21165,7 @@
         <v>1.257295524570208</v>
       </c>
       <c r="D395" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E395">
         <v>1.611306442152011</v>
@@ -21210,7 +21201,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21224,7 +21215,7 @@
         <v>2.435888213210831</v>
       </c>
       <c r="D396" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E396">
         <v>1.825888213210831</v>
@@ -21260,7 +21251,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21274,7 +21265,7 @@
         <v>1.225114646902994</v>
       </c>
       <c r="D397" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E397">
         <v>1.589727863749075</v>
@@ -21310,7 +21301,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21324,7 +21315,7 @@
         <v>1.254865283830232</v>
       </c>
       <c r="D398" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E398">
         <v>1.589727863749075</v>
@@ -21360,7 +21351,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21374,7 +21365,7 @@
         <v>2.394557671241156</v>
       </c>
       <c r="D399" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E399">
         <v>1.784557671241155</v>
@@ -21410,7 +21401,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21424,7 +21415,7 @@
         <v>1.190831248034139</v>
       </c>
       <c r="D400" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E400">
         <v>1.609187949630535</v>
@@ -21460,7 +21451,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21474,7 +21465,7 @@
         <v>1.220391421634328</v>
       </c>
       <c r="D401" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E401">
         <v>1.609187949630535</v>
@@ -21510,7 +21501,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21524,7 +21515,7 @@
         <v>2.366135904185318</v>
       </c>
       <c r="D402" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E402">
         <v>1.756135904185318</v>
@@ -21560,7 +21551,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21574,7 +21565,7 @@
         <v>1.167255588725149</v>
       </c>
       <c r="D403" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E403">
         <v>1.578100832137494</v>
@@ -21610,7 +21601,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21624,7 +21615,7 @@
         <v>1.196684786440288</v>
       </c>
       <c r="D404" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E404">
         <v>1.578100832137494</v>
@@ -21660,7 +21651,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21674,7 +21665,7 @@
         <v>2.396096253709469</v>
       </c>
       <c r="D405" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E405">
         <v>1.786096253709469</v>
@@ -21710,7 +21701,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21724,7 +21715,7 @@
         <v>1.192107491556242</v>
       </c>
       <c r="D406" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E406">
         <v>1.492060423190722</v>
@@ -21760,7 +21751,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21774,7 +21765,7 @@
         <v>1.221674755398221</v>
       </c>
       <c r="D407" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E407">
         <v>1.492060423190722</v>
@@ -21810,7 +21801,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21824,7 +21815,7 @@
         <v>2.341003521520614</v>
       </c>
       <c r="D408" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E408">
         <v>1.731003521520614</v>
@@ -21860,7 +21851,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21874,7 +21865,7 @@
         <v>1.146408451030924</v>
       </c>
       <c r="D409" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E409">
         <v>1.603573943943295</v>
@@ -21910,7 +21901,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21924,7 +21915,7 @@
         <v>1.175721831314429</v>
       </c>
       <c r="D410" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E410">
         <v>1.603573943943295</v>
@@ -21960,7 +21951,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21974,7 +21965,7 @@
         <v>2.3387346635889</v>
       </c>
       <c r="D411" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E411">
         <v>1.7287346635889</v>
@@ -22010,7 +22001,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22024,7 +22015,7 @@
         <v>1.144526449059917</v>
       </c>
       <c r="D412" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E412">
         <v>1.601256255851928</v>
@@ -22060,7 +22051,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22074,7 +22065,7 @@
         <v>1.173829373776917</v>
       </c>
       <c r="D413" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E413">
         <v>1.601256255851928</v>
@@ -22110,7 +22101,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22124,7 +22115,7 @@
         <v>2.321864997704619</v>
       </c>
       <c r="D414" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E414">
         <v>1.711864997704619</v>
@@ -22160,7 +22151,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22174,7 +22165,7 @@
         <v>1.130533177819499</v>
       </c>
       <c r="D415" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E415">
         <v>1.628353938431452</v>
@@ -22210,7 +22201,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22224,7 +22215,7 @@
         <v>1.159758362140719</v>
       </c>
       <c r="D416" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E416">
         <v>1.628353938431452</v>
@@ -22260,7 +22251,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22274,7 +22265,7 @@
         <v>2.329307629672357</v>
       </c>
       <c r="D417" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E417">
         <v>1.719307629672357</v>
@@ -22310,7 +22301,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22324,7 +22315,7 @@
         <v>1.136706789589973</v>
       </c>
       <c r="D418" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E418">
         <v>1.641887405220004</v>
@@ -22360,7 +22351,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22374,7 +22365,7 @@
         <v>1.165966271754362</v>
       </c>
       <c r="D419" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E419">
         <v>1.641887405220004</v>
@@ -22410,7 +22401,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22424,7 +22415,7 @@
         <v>2.283832828965951</v>
       </c>
       <c r="D420" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E420">
         <v>1.673832828965951</v>
@@ -22474,7 +22465,7 @@
         <v>1.09898575674595</v>
       </c>
       <c r="D421" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E421">
         <v>1.611312616281895</v>
@@ -22524,7 +22515,7 @@
         <v>1.128035677616761</v>
       </c>
       <c r="D422" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E422">
         <v>1.611312616281895</v>
@@ -22574,7 +22565,7 @@
         <v>2.182831733767929</v>
       </c>
       <c r="D423" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E423">
         <v>1.572831733767929</v>
@@ -22610,7 +22601,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22624,7 +22615,7 @@
         <v>1.084064563230975</v>
       </c>
       <c r="D424" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E424">
         <v>1.514840661441129</v>
@@ -22660,7 +22651,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22674,7 +22665,7 @@
         <v>1.04379052447924</v>
       </c>
       <c r="D425" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E425">
         <v>1.514840661441129</v>
@@ -22710,7 +22701,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22724,7 +22715,7 @@
         <v>1.987186684521362</v>
       </c>
       <c r="D426" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E426">
         <v>1.377186684521361</v>
@@ -22760,7 +22751,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22774,7 +22765,7 @@
         <v>0.9019433653148159</v>
       </c>
       <c r="D427" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E427">
         <v>1.471274636039009</v>
@@ -22810,7 +22801,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22824,7 +22815,7 @@
         <v>0.8806027184256511</v>
       </c>
       <c r="D428" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E428">
         <v>1.471274636039009</v>
@@ -22860,7 +22851,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22874,7 +22865,7 @@
         <v>1.871503922012645</v>
       </c>
       <c r="D429" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E429">
         <v>1.261503922012645</v>
@@ -22924,7 +22915,7 @@
         <v>0.8271315762745894</v>
       </c>
       <c r="D430" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E430">
         <v>1.39104304268619</v>
@@ -22974,7 +22965,7 @@
         <v>0.784111566287045</v>
       </c>
       <c r="D431" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E431">
         <v>1.39104304268619</v>
@@ -23024,7 +23015,7 @@
         <v>1.725043908638261</v>
       </c>
       <c r="D432" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E432">
         <v>1.115043908638261</v>
@@ -23060,7 +23051,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23074,7 +23065,7 @@
         <v>0.6891081996153199</v>
       </c>
       <c r="D433" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E433">
         <v>1.208315076967225</v>
@@ -23110,7 +23101,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23124,7 +23115,7 @@
         <v>0.6619490666521894</v>
       </c>
       <c r="D434" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E434">
         <v>1.208315076967225</v>
@@ -23160,7 +23151,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23174,7 +23165,7 @@
         <v>1.603418511347999</v>
       </c>
       <c r="D435" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E435">
         <v>0.9934185113479987</v>
@@ -23210,7 +23201,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23224,7 +23215,7 @@
         <v>0.574488873597538</v>
       </c>
       <c r="D436" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E436">
         <v>1.108556250145786</v>
@@ -23260,7 +23251,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23274,7 +23265,7 @@
         <v>0.5605011546266709</v>
       </c>
       <c r="D437" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E437">
         <v>1.108556250145786</v>
@@ -23310,7 +23301,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23324,7 +23315,7 @@
         <v>1.504487777527864</v>
       </c>
       <c r="D438" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E438">
         <v>0.8944877775278632</v>
@@ -23360,7 +23351,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23374,7 +23365,7 @@
         <v>0.4812569147670418</v>
       </c>
       <c r="D439" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E439">
         <v>1.036979636275919</v>
@@ -23410,7 +23401,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23424,7 +23415,7 @@
         <v>0.4779828927766969</v>
       </c>
       <c r="D440" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E440">
         <v>1.036979636275919</v>
@@ -23460,7 +23451,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23474,7 +23465,7 @@
         <v>1.414501209603441</v>
       </c>
       <c r="D441" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E441">
         <v>0.9219355330393615</v>
@@ -23510,7 +23501,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23524,7 +23515,7 @@
         <v>0.3964539049027813</v>
       </c>
       <c r="D442" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E442">
         <v>0.9417865782881711</v>
@@ -23560,7 +23551,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23574,7 +23565,7 @@
         <v>0.4029249720655423</v>
       </c>
       <c r="D443" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E443">
         <v>0.9417865782881711</v>
@@ -23610,7 +23601,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23624,7 +23615,7 @@
         <v>1.374244075534095</v>
       </c>
       <c r="D444" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E444">
         <v>0.8269425846185072</v>
@@ -23660,7 +23651,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23674,7 +23665,7 @@
         <v>0.3063097844755669</v>
       </c>
       <c r="D445" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E445">
         <v>0.873462183832336</v>
@@ -23710,7 +23701,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23724,7 +23715,7 @@
         <v>0.3231397114429218</v>
       </c>
       <c r="D446" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E446">
         <v>0.873462183832336</v>
@@ -23760,7 +23751,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23774,7 +23765,7 @@
         <v>1.297276604707491</v>
       </c>
       <c r="D447" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E447">
         <v>0.7916599773381927</v>
@@ -23810,7 +23801,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23824,7 +23815,7 @@
         <v>0.233440118808713</v>
       </c>
       <c r="D448" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E448">
         <v>0.818230896896579</v>
@@ -23860,7 +23851,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23874,7 +23865,7 @@
         <v>0.2586438215372961</v>
       </c>
       <c r="D449" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E449">
         <v>0.818230896896579</v>
@@ -23910,7 +23901,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23960,7 +23951,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23974,7 +23965,7 @@
         <v>1.228322830557575</v>
       </c>
       <c r="D451" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E451">
         <v>0.7235042792779742</v>
@@ -24010,7 +24001,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24024,7 +24015,7 @@
         <v>0.1681574946714077</v>
       </c>
       <c r="D452" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E452">
         <v>0.7687501793352967</v>
@@ -24060,7 +24051,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24074,7 +24065,7 @@
         <v>0.2008631126431526</v>
       </c>
       <c r="D453" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E453">
         <v>0.7687501793352967</v>
@@ -24110,7 +24101,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24124,7 +24115,7 @@
         <v>1.23967353577152</v>
       </c>
       <c r="D454" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E454">
         <v>1.163072722956397</v>
@@ -24160,7 +24151,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24174,7 +24165,7 @@
         <v>1.225596128630588</v>
       </c>
       <c r="D455" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E455">
         <v>0.6905047055753135</v>
@@ -24210,7 +24201,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24224,7 +24215,7 @@
         <v>0.136549003700944</v>
       </c>
       <c r="D456" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E456">
         <v>0.7447926433919125</v>
@@ -24260,7 +24251,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24274,7 +24265,7 @@
         <v>0.172886893251202</v>
       </c>
       <c r="D457" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E457">
         <v>0.7447926433919125</v>
@@ -24310,7 +24301,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24360,7 +24351,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24374,7 +24365,7 @@
         <v>1.220200273962068</v>
       </c>
       <c r="D459" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E459">
         <v>0.6852080850156392</v>
@@ -24410,7 +24401,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24424,7 +24415,7 @@
         <v>0.1314756598861742</v>
       </c>
       <c r="D460" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E460">
         <v>0.7409473216741169</v>
@@ -24460,7 +24451,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24474,7 +24465,7 @@
         <v>0.1683965498259044</v>
       </c>
       <c r="D461" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E461">
         <v>0.7409473216741169</v>
@@ -24510,7 +24501,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24524,7 +24515,7 @@
         <v>1.216624069904026</v>
       </c>
       <c r="D462" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E462">
         <v>1.236624069904027</v>
@@ -24560,7 +24551,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24574,7 +24565,7 @@
         <v>1.283513715629472</v>
       </c>
       <c r="D463" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E463">
         <v>1.236624069904027</v>
@@ -24610,7 +24601,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24624,7 +24615,7 @@
         <v>1.245299916107382</v>
       </c>
       <c r="D464" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E464">
         <v>0.7098461245467869</v>
@@ -24660,7 +24651,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24674,7 +24665,7 @@
         <v>0.155075093535447</v>
       </c>
       <c r="D465" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E465">
         <v>0.7588344229730764</v>
@@ -24710,7 +24701,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24724,7 +24715,7 @@
         <v>0.1892840681169474</v>
       </c>
       <c r="D466" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E466">
         <v>0.7588344229730764</v>
@@ -24760,7 +24751,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24774,7 +24765,7 @@
         <v>1.346682022872791</v>
       </c>
       <c r="D467" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E467">
         <v>1.156906845444727</v>
@@ -24810,7 +24801,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24824,7 +24815,7 @@
         <v>1.297477194708015</v>
       </c>
       <c r="D468" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E468">
         <v>1.156906845444727</v>
@@ -24860,7 +24851,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24874,7 +24865,7 @@
         <v>1.297810076779093</v>
       </c>
       <c r="D469" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E469">
         <v>0.761390581114191</v>
@@ -24910,7 +24901,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24924,7 +24915,7 @@
         <v>0.2044467158681593</v>
       </c>
       <c r="D470" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E470">
         <v>0.7962554570149853</v>
@@ -24960,7 +24951,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24974,7 +24965,7 @@
         <v>0.2329821788368545</v>
       </c>
       <c r="D471" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E471">
         <v>0.7962554570149853</v>
@@ -25010,7 +25001,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25024,7 +25015,7 @@
         <v>1.375532432988972</v>
       </c>
       <c r="D472" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E472">
         <v>1.038262852606697</v>
@@ -25060,7 +25051,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25074,7 +25065,7 @@
         <v>1.326689743863311</v>
       </c>
       <c r="D473" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E473">
         <v>1.038262852606697</v>
@@ -25110,7 +25101,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25124,7 +25115,7 @@
         <v>1.316058735434172</v>
       </c>
       <c r="D474" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E474">
         <v>0.7793036322537743</v>
@@ -25160,7 +25151,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25174,7 +25165,7 @@
         <v>0.221604650097877</v>
       </c>
       <c r="D475" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E475">
         <v>0.8092602482404443</v>
@@ -25210,7 +25201,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25224,7 +25215,7 @@
         <v>0.2481684189130346</v>
       </c>
       <c r="D476" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E476">
         <v>0.8092602482404443</v>
@@ -25260,7 +25251,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25274,7 +25265,7 @@
         <v>1.385558707514407</v>
       </c>
       <c r="D477" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E477">
         <v>1.0151454476213</v>
@@ -25310,7 +25301,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25324,7 +25315,7 @@
         <v>1.336841871207057</v>
       </c>
       <c r="D478" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E478">
         <v>1.0151454476213</v>
@@ -25360,7 +25351,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25374,7 +25365,7 @@
         <v>1.357255810174356</v>
       </c>
       <c r="D479" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E479">
         <v>0.8197430596424145</v>
@@ -25410,7 +25401,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25424,7 +25415,7 @@
         <v>0.2603393709455446</v>
       </c>
       <c r="D480" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E480">
         <v>0.8673754583787305</v>
@@ -25460,7 +25451,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25474,7 +25465,7 @@
         <v>0.2824519615703833</v>
       </c>
       <c r="D481" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E481">
         <v>0.8673754583787305</v>
@@ -25510,7 +25501,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25524,7 +25515,7 @@
         <v>1.408193422141772</v>
       </c>
       <c r="D482" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E482">
         <v>1.092946268617976</v>
@@ -25560,7 +25551,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25574,7 +25565,7 @@
         <v>1.359760703591251</v>
       </c>
       <c r="D483" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E483">
         <v>1.092946268617976</v>
@@ -25610,7 +25601,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25624,7 +25615,7 @@
         <v>1.400693800028334</v>
       </c>
       <c r="D484" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E484">
         <v>0.8623821899128705</v>
@@ -25660,7 +25651,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25674,7 +25665,7 @@
         <v>0.3011810671530766</v>
       </c>
       <c r="D485" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E485">
         <v>0.898730697031946</v>
@@ -25710,7 +25701,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25724,7 +25715,7 @@
         <v>0.3186003577247281</v>
       </c>
       <c r="D486" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E486">
         <v>0.898730697031946</v>
@@ -25760,7 +25751,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25774,7 +25765,7 @@
         <v>1.432059352199475</v>
       </c>
       <c r="D487" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E487">
         <v>0.9910848179499889</v>
@@ -25810,7 +25801,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25824,7 +25815,7 @@
         <v>1.383926205992774</v>
       </c>
       <c r="D488" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E488">
         <v>0.9910848179499889</v>
@@ -25860,7 +25851,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25874,7 +25865,7 @@
         <v>1.389878787820437</v>
       </c>
       <c r="D489" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E489">
         <v>0.851766074481211</v>
@@ -25910,7 +25901,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25924,7 +25915,7 @@
         <v>0.291012469467951</v>
       </c>
       <c r="D490" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E490">
         <v>0.8909239985646367</v>
@@ -25960,7 +25951,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25974,7 +25965,7 @@
         <v>0.3096002785999952</v>
       </c>
       <c r="D491" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E491">
         <v>0.8909239985646367</v>
@@ -26010,7 +26001,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26024,7 +26015,7 @@
         <v>1.426117311009389</v>
       </c>
       <c r="D492" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E492">
         <v>1.145927272692262</v>
@@ -26060,7 +26051,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26074,7 +26065,7 @@
         <v>1.377909578511599</v>
       </c>
       <c r="D493" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E493">
         <v>1.145927272692262</v>
@@ -26110,7 +26101,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26124,7 +26115,7 @@
         <v>1.390470377742177</v>
       </c>
       <c r="D494" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E494">
         <v>0.8523467845882973</v>
@@ -26160,7 +26151,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26174,7 +26165,7 @@
         <v>0.2915686999920695</v>
       </c>
       <c r="D495" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E495">
         <v>0.8913510312897541</v>
@@ -26210,7 +26201,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26224,7 +26215,7 @@
         <v>0.3100925902130296</v>
       </c>
       <c r="D496" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E496">
         <v>0.8913510312897541</v>
@@ -26260,7 +26251,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26274,7 +26265,7 @@
         <v>1.426442345472138</v>
       </c>
       <c r="D497" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E497">
         <v>1.04260947236648</v>
@@ -26310,7 +26301,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26324,7 +26315,7 @@
         <v>1.4090266167915</v>
       </c>
       <c r="D498" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E498">
         <v>0.8705617594711974</v>
@@ -26360,7 +26351,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26374,7 +26365,7 @@
         <v>0.3090158305005142</v>
       </c>
       <c r="D499" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E499">
         <v>0.9047456498219102</v>
@@ -26410,7 +26401,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26424,7 +26415,7 @@
         <v>0.3255347937437314</v>
       </c>
       <c r="D500" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E500">
         <v>0.9047456498219102</v>
@@ -26460,7 +26451,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26474,7 +26465,7 @@
         <v>1.436637612444065</v>
       </c>
       <c r="D501" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E501">
         <v>1.0174159700749</v>
@@ -26510,7 +26501,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26524,7 +26515,7 @@
         <v>1.481023111428944</v>
       </c>
       <c r="D502" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E502">
         <v>0.9412341806440443</v>
@@ -26560,7 +26551,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26574,7 +26565,7 @@
         <v>0.3767090863780185</v>
       </c>
       <c r="D503" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E503">
         <v>0.9692419169592172</v>
@@ -26610,7 +26601,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26624,7 +26615,7 @@
         <v>0.3854491180167301</v>
       </c>
       <c r="D504" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E504">
         <v>0.9692419169592172</v>
@@ -26660,7 +26651,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26674,7 +26665,7 @@
         <v>1.476194307198891</v>
       </c>
       <c r="D505" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E505">
         <v>1.037981948597929</v>
@@ -26710,7 +26701,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26724,7 +26715,7 @@
         <v>1.566896676462016</v>
       </c>
       <c r="D506" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E506">
         <v>1.019149230451688</v>
@@ -26760,7 +26751,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26774,7 +26765,7 @@
         <v>0.4887054182244546</v>
       </c>
       <c r="D507" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E507">
         <v>1.141981249108951</v>
@@ -26810,7 +26801,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26824,7 +26815,7 @@
         <v>0.4845754557390034</v>
       </c>
       <c r="D508" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E508">
         <v>1.141981249108951</v>
@@ -26860,7 +26851,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26874,7 +26865,7 @@
         <v>1.575427906313638</v>
       </c>
       <c r="D509" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E509">
         <v>0.9905476528404038</v>
@@ -26910,7 +26901,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26924,7 +26915,7 @@
         <v>1.651922146792429</v>
       </c>
       <c r="D510" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E510">
         <v>1.103977882563743</v>
@@ -26960,7 +26951,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26974,7 +26965,7 @@
         <v>0.5692040695326464</v>
       </c>
       <c r="D511" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E511">
         <v>1.20122353283454</v>
@@ -27010,7 +27001,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27024,7 +27015,7 @@
         <v>0.5558236507843963</v>
       </c>
       <c r="D512" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E512">
         <v>1.20122353283454</v>
@@ -27060,7 +27051,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27074,7 +27065,7 @@
         <v>1.619515187225704</v>
       </c>
       <c r="D513" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E513">
         <v>1.044672662888699</v>
@@ -27110,7 +27101,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27124,7 +27115,7 @@
         <v>1.713538754440068</v>
       </c>
       <c r="D514" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E514">
         <v>1.21890599807297</v>
@@ -27160,7 +27151,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27174,7 +27165,7 @@
         <v>0.6782657847142568</v>
       </c>
       <c r="D515" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E515">
         <v>1.281486555498756</v>
@@ -27210,7 +27201,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27224,7 +27215,7 @@
         <v>0.6523526016297332</v>
       </c>
       <c r="D516" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E516">
         <v>1.281486555498756</v>
@@ -27260,7 +27251,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27274,7 +27265,7 @@
         <v>1.849941600908833</v>
       </c>
       <c r="D517" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E517">
         <v>1.239941600908833</v>
@@ -27310,7 +27301,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27324,7 +27315,7 @@
         <v>0.8068113243587849</v>
       </c>
       <c r="D518" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E518">
         <v>1.376088529662578</v>
@@ -27360,7 +27351,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27374,7 +27365,7 @@
         <v>0.7661264044446945</v>
       </c>
       <c r="D519" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E519">
         <v>1.376088529662578</v>
@@ -27410,7 +27401,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27424,7 +27415,7 @@
         <v>2.41237924775196</v>
       </c>
       <c r="D520" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E520">
         <v>1.720876564407629</v>
@@ -27460,7 +27451,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27474,7 +27465,7 @@
         <v>1.615923807921956</v>
       </c>
       <c r="D521" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E521">
         <v>1.035548815721295</v>
@@ -27510,7 +27501,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27524,10 +27515,10 @@
         <v>-0.8857661497430493</v>
       </c>
       <c r="D522" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E522">
-        <v>-1.235980944049381</v>
+        <v>-1.169233099500016</v>
       </c>
       <c r="F522">
         <v>1</v>
@@ -27536,10 +27527,10 @@
         <v>0.008885766149743049</v>
       </c>
       <c r="H522">
-        <v>0.01169598094404938</v>
+        <v>0.01156923309950002</v>
       </c>
       <c r="I522">
-        <v>-0.3502147943063321</v>
+        <v>-0.2834669497569662</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
@@ -27551,60 +27542,60 @@
         <v>4</v>
       </c>
       <c r="M522">
-        <v>4.01</v>
+        <v>3.95</v>
       </c>
       <c r="N522">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="O522">
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B523" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C523">
-        <v>-1.355141580041469</v>
+        <v>-1.235980944049381</v>
       </c>
       <c r="D523" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E523">
-        <v>-1.857167569625838</v>
+        <v>-1.169233099500016</v>
       </c>
       <c r="F523">
         <v>1</v>
       </c>
       <c r="G523">
-        <v>0.009355141580041469</v>
+        <v>0.01169598094404938</v>
       </c>
       <c r="H523">
-        <v>0.01231716756962584</v>
+        <v>0.01156923309950002</v>
       </c>
       <c r="I523">
-        <v>-0.5020259895843688</v>
+        <v>0.06674784454936589</v>
       </c>
       <c r="J523">
-        <v>1.767373458759561</v>
+        <v>1.612464075822789</v>
       </c>
       <c r="K523">
-        <v>3.03</v>
+        <v>4.01</v>
       </c>
       <c r="L523">
-        <v>4</v>
+        <v>5.23</v>
       </c>
       <c r="M523">
-        <v>4.01</v>
+        <v>3.95</v>
       </c>
       <c r="N523">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27618,199 +27609,49 @@
         <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C524">
-        <v>-1.430565724342963</v>
+        <v>-2.562371230751202</v>
       </c>
       <c r="D524" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E524">
-        <v>-1.956986321655209</v>
+        <v>-2.475777147498068</v>
       </c>
       <c r="F524">
         <v>1</v>
       </c>
       <c r="G524">
-        <v>0.009430565724342962</v>
+        <v>0.0130223712307512</v>
       </c>
       <c r="H524">
-        <v>0.01241698632165521</v>
+        <v>0.01287577714749807</v>
       </c>
       <c r="I524">
-        <v>-0.5264205973122458</v>
+        <v>0.086594083253134</v>
       </c>
       <c r="J524">
-        <v>1.79226591562474</v>
+        <v>1.943234720885587</v>
       </c>
       <c r="K524">
-        <v>3.03</v>
+        <v>4.01</v>
       </c>
       <c r="L524">
-        <v>4</v>
+        <v>5.23</v>
       </c>
       <c r="M524">
-        <v>4.01</v>
+        <v>3.95</v>
       </c>
       <c r="N524">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="O524">
         <v>1</v>
       </c>
       <c r="P524" t="s">
         <v>360</v>
-      </c>
-    </row>
-    <row r="525" spans="1:16">
-      <c r="A525" s="1">
-        <v>0</v>
-      </c>
-      <c r="B525" t="s">
-        <v>69</v>
-      </c>
-      <c r="C525">
-        <v>-1.494925536528956</v>
-      </c>
-      <c r="D525" t="s">
-        <v>159</v>
-      </c>
-      <c r="E525">
-        <v>-2.042162178706638</v>
-      </c>
-      <c r="F525">
-        <v>1</v>
-      </c>
-      <c r="G525">
-        <v>0.009494925536528956</v>
-      </c>
-      <c r="H525">
-        <v>0.01250216217870664</v>
-      </c>
-      <c r="I525">
-        <v>-0.5472366421776824</v>
-      </c>
-      <c r="J525">
-        <v>1.813506777732329</v>
-      </c>
-      <c r="K525">
-        <v>3.03</v>
-      </c>
-      <c r="L525">
-        <v>4</v>
-      </c>
-      <c r="M525">
-        <v>4.01</v>
-      </c>
-      <c r="N525">
-        <v>5.23</v>
-      </c>
-      <c r="O525">
-        <v>1</v>
-      </c>
-      <c r="P525" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="526" spans="1:16">
-      <c r="A526" s="1">
-        <v>0</v>
-      </c>
-      <c r="B526" t="s">
-        <v>69</v>
-      </c>
-      <c r="C526">
-        <v>-1.56445943489637</v>
-      </c>
-      <c r="D526" t="s">
-        <v>159</v>
-      </c>
-      <c r="E526">
-        <v>-2.134185588757242</v>
-      </c>
-      <c r="F526">
-        <v>1</v>
-      </c>
-      <c r="G526">
-        <v>0.009564459434896372</v>
-      </c>
-      <c r="H526">
-        <v>0.01259418558875724</v>
-      </c>
-      <c r="I526">
-        <v>-0.5697261538608718</v>
-      </c>
-      <c r="J526">
-        <v>1.836455259041706</v>
-      </c>
-      <c r="K526">
-        <v>3.03</v>
-      </c>
-      <c r="L526">
-        <v>4</v>
-      </c>
-      <c r="M526">
-        <v>4.01</v>
-      </c>
-      <c r="N526">
-        <v>5.23</v>
-      </c>
-      <c r="O526">
-        <v>1</v>
-      </c>
-      <c r="P526" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="527" spans="1:16">
-      <c r="A527" s="1">
-        <v>0</v>
-      </c>
-      <c r="B527" t="s">
-        <v>69</v>
-      </c>
-      <c r="C527">
-        <v>-1.648130543598285</v>
-      </c>
-      <c r="D527" t="s">
-        <v>159</v>
-      </c>
-      <c r="E527">
-        <v>-2.24491864020763</v>
-      </c>
-      <c r="F527">
-        <v>1</v>
-      </c>
-      <c r="G527">
-        <v>0.009648130543598286</v>
-      </c>
-      <c r="H527">
-        <v>0.01270491864020763</v>
-      </c>
-      <c r="I527">
-        <v>-0.5967880966093455</v>
-      </c>
-      <c r="J527">
-        <v>1.864069486336068</v>
-      </c>
-      <c r="K527">
-        <v>3.03</v>
-      </c>
-      <c r="L527">
-        <v>4</v>
-      </c>
-      <c r="M527">
-        <v>4.01</v>
-      </c>
-      <c r="N527">
-        <v>5.23</v>
-      </c>
-      <c r="O527">
-        <v>1</v>
-      </c>
-      <c r="P527" t="s">
-        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -493,7 +493,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-25</t>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -27590,7 +27590,7 @@
         <v>159</v>
       </c>
       <c r="E522">
-        <v>-1.164354866324066</v>
+        <v>-1.217607021774699</v>
       </c>
       <c r="F522">
         <v>1</v>
@@ -27599,10 +27599,10 @@
         <v>0.01169598094404938</v>
       </c>
       <c r="H522">
-        <v>0.01186435486632407</v>
+        <v>0.0116176070217747</v>
       </c>
       <c r="I522">
-        <v>0.07162607772531526</v>
+        <v>0.01837392227468282</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
@@ -27614,10 +27614,10 @@
         <v>5.23</v>
       </c>
       <c r="M522">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N522">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27640,7 +27640,7 @@
         <v>159</v>
       </c>
       <c r="E523">
-        <v>-1.790188773388626</v>
+        <v>-1.834146365863051</v>
       </c>
       <c r="F523">
         <v>1</v>
@@ -27649,10 +27649,10 @@
         <v>0.01231716756962584</v>
       </c>
       <c r="H523">
-        <v>0.01249018877338863</v>
+        <v>0.01223414636586305</v>
       </c>
       <c r="I523">
-        <v>0.06697879623721192</v>
+        <v>0.02302120376278616</v>
       </c>
       <c r="J523">
         <v>1.767373458759561</v>
@@ -27664,10 +27664,10 @@
         <v>5.23</v>
       </c>
       <c r="M523">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N523">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27690,7 +27690,7 @@
         <v>159</v>
       </c>
       <c r="E524">
-        <v>-1.890754299123952</v>
+        <v>-1.933218344186467</v>
       </c>
       <c r="F524">
         <v>1</v>
@@ -27699,10 +27699,10 @@
         <v>0.01241698632165521</v>
       </c>
       <c r="H524">
-        <v>0.01259075429912395</v>
+        <v>0.01233321834418647</v>
       </c>
       <c r="I524">
-        <v>0.06623202253125715</v>
+        <v>0.02376797746874182</v>
       </c>
       <c r="J524">
         <v>1.79226591562474</v>
@@ -27714,10 +27714,10 @@
         <v>5.23</v>
       </c>
       <c r="M524">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N524">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27740,7 +27740,7 @@
         <v>159</v>
       </c>
       <c r="E525">
-        <v>-1.976567382038609</v>
+        <v>-2.017756975374668</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27749,10 +27749,10 @@
         <v>0.01250216217870664</v>
       </c>
       <c r="H525">
-        <v>0.01267656738203861</v>
+        <v>0.01241775697537467</v>
       </c>
       <c r="I525">
-        <v>0.06559479666802925</v>
+        <v>0.02440520333196972</v>
       </c>
       <c r="J525">
         <v>1.813506777732329</v>
@@ -27764,10 +27764,10 @@
         <v>5.23</v>
       </c>
       <c r="M525">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N525">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27790,7 +27790,7 @@
         <v>159</v>
       </c>
       <c r="E526">
-        <v>-2.069279246528493</v>
+        <v>-2.109091930985991</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27799,10 +27799,10 @@
         <v>0.01259418558875724</v>
       </c>
       <c r="H526">
-        <v>0.01276927924652849</v>
+        <v>0.01250909193098599</v>
       </c>
       <c r="I526">
-        <v>0.06490634222874814</v>
+        <v>0.02509365777125083</v>
       </c>
       <c r="J526">
         <v>1.836455259041706</v>
@@ -27814,10 +27814,10 @@
         <v>5.23</v>
       </c>
       <c r="M526">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N526">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27840,7 +27840,7 @@
         <v>159</v>
       </c>
       <c r="E527">
-        <v>-2.180840724797713</v>
+        <v>-2.218996555617549</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27849,10 +27849,10 @@
         <v>0.01270491864020763</v>
       </c>
       <c r="H527">
-        <v>0.01288084072479771</v>
+        <v>0.01261899655561755</v>
       </c>
       <c r="I527">
-        <v>0.06407791540991692</v>
+        <v>0.02592208459008116</v>
       </c>
       <c r="J527">
         <v>1.864069486336068</v>
@@ -27864,10 +27864,10 @@
         <v>5.23</v>
       </c>
       <c r="M527">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N527">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27890,7 +27890,7 @@
         <v>159</v>
       </c>
       <c r="E528">
-        <v>-2.328365552079308</v>
+        <v>-2.364330420117734</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27899,10 +27899,10 @@
         <v>0.01285134798609852</v>
       </c>
       <c r="H528">
-        <v>0.01302836555207931</v>
+        <v>0.01276433042011773</v>
       </c>
       <c r="I528">
-        <v>0.06298243401921155</v>
+        <v>0.02701756598078564</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27914,10 +27914,10 @@
         <v>5.23</v>
       </c>
       <c r="M528">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N528">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27940,7 +27940,7 @@
         <v>159</v>
       </c>
       <c r="E529">
-        <v>-2.484691240983896</v>
+        <v>-2.518334440375223</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27949,10 +27949,10 @@
         <v>0.01300651284067956</v>
       </c>
       <c r="H529">
-        <v>0.01318469124098389</v>
+        <v>0.01291833444037522</v>
       </c>
       <c r="I529">
-        <v>0.06182159969566214</v>
+        <v>0.02817840030433505</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27964,10 +27964,10 @@
         <v>5.23</v>
       </c>
       <c r="M529">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N529">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27990,7 +27990,7 @@
         <v>159</v>
       </c>
       <c r="E530">
-        <v>-2.88484249085049</v>
+        <v>-2.912542849897265</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -27999,10 +27999,10 @@
         <v>0.01340369267037388</v>
       </c>
       <c r="H530">
-        <v>0.01358484249085049</v>
+        <v>0.01331254284989727</v>
       </c>
       <c r="I530">
-        <v>0.058850179523386</v>
+        <v>0.03114982047661119</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28014,10 +28014,10 @@
         <v>5.23</v>
       </c>
       <c r="M530">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N530">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28040,7 +28040,7 @@
         <v>159</v>
       </c>
       <c r="E531">
-        <v>-3.246016111387952</v>
+        <v>-3.268352505773279</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28049,10 +28049,10 @@
         <v>0.01376218430858061</v>
       </c>
       <c r="H531">
-        <v>0.01394601611138795</v>
+        <v>0.01366835250577328</v>
       </c>
       <c r="I531">
-        <v>0.05616819719266175</v>
+        <v>0.03383180280733544</v>
       </c>
       <c r="J531">
         <v>2.127726760244542</v>
@@ -28064,10 +28064,10 @@
         <v>5.23</v>
       </c>
       <c r="M531">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N531">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28090,7 +28090,7 @@
         <v>159</v>
       </c>
       <c r="E532">
-        <v>-3.385561443893835</v>
+        <v>-3.405825382845905</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28099,10 +28099,10 @@
         <v>0.01390069341336987</v>
       </c>
       <c r="H532">
-        <v>0.01408556144389383</v>
+        <v>0.01380582538284591</v>
       </c>
       <c r="I532">
-        <v>0.05513196947603483</v>
+        <v>0.03486803052396414</v>
       </c>
       <c r="J532">
         <v>2.162267684132137</v>
@@ -28114,10 +28114,10 @@
         <v>5.23</v>
       </c>
       <c r="M532">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N532">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28140,7 +28140,7 @@
         <v>159</v>
       </c>
       <c r="E533">
-        <v>-3.615476737758376</v>
+        <v>-3.632326093138203</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28149,10 +28149,10 @@
         <v>0.01412890141544829</v>
       </c>
       <c r="H533">
-        <v>0.01431547673775838</v>
+        <v>0.0140323260931382</v>
       </c>
       <c r="I533">
-        <v>0.05342467768991277</v>
+        <v>0.0365753223100862</v>
       </c>
       <c r="J533">
         <v>2.219177410336232</v>
@@ -28164,10 +28164,10 @@
         <v>5.23</v>
       </c>
       <c r="M533">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N533">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28190,7 +28190,7 @@
         <v>159</v>
       </c>
       <c r="E534">
-        <v>-3.903603744540256</v>
+        <v>-3.916173985957975</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28199,10 +28199,10 @@
         <v>0.01441488886524911</v>
       </c>
       <c r="H534">
-        <v>0.01460360374454026</v>
+        <v>0.01431617398595797</v>
       </c>
       <c r="I534">
-        <v>0.05128512070885805</v>
+        <v>0.03871487929113915</v>
       </c>
       <c r="J534">
         <v>2.29049597637135</v>
@@ -28214,10 +28214,10 @@
         <v>5.23</v>
       </c>
       <c r="M534">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N534">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28240,7 +28240,7 @@
         <v>159</v>
       </c>
       <c r="E535">
-        <v>-4.112819234228732</v>
+        <v>-4.122282314908504</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28249,10 +28249,10 @@
         <v>0.01462255077456862</v>
       </c>
       <c r="H535">
-        <v>0.01481281923422873</v>
+        <v>0.0145222823149085</v>
       </c>
       <c r="I535">
-        <v>0.04973154033988436</v>
+        <v>0.04026845966011283</v>
       </c>
       <c r="J535">
         <v>2.342281988670478</v>
@@ -28264,10 +28264,10 @@
         <v>5.23</v>
       </c>
       <c r="M535">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N535">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28290,7 +28290,7 @@
         <v>159</v>
       </c>
       <c r="E536">
-        <v>-4.292625495944366</v>
+        <v>-4.299418186598657</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28299,10 +28299,10 @@
         <v>0.01480102184127151</v>
       </c>
       <c r="H536">
-        <v>0.01499262549594436</v>
+        <v>0.01469941818659866</v>
       </c>
       <c r="I536">
-        <v>0.04839634532714499</v>
+        <v>0.04160365467285398</v>
       </c>
       <c r="J536">
         <v>2.38678848909514</v>
@@ -28314,10 +28314,10 @@
         <v>5.23</v>
       </c>
       <c r="M536">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N536">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28340,7 +28340,7 @@
         <v>159</v>
       </c>
       <c r="E537">
-        <v>-4.334618049717401</v>
+        <v>-4.340787088582982</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28349,10 +28349,10 @@
         <v>0.01484270256915019</v>
       </c>
       <c r="H537">
-        <v>0.0150346180497174</v>
+        <v>0.01474078708858298</v>
       </c>
       <c r="I537">
-        <v>0.04808451943278946</v>
+        <v>0.04191548056720773</v>
       </c>
       <c r="J537">
         <v>2.397182685573614</v>
@@ -28364,10 +28364,10 @@
         <v>5.23</v>
       </c>
       <c r="M537">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N537">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28390,7 +28390,7 @@
         <v>159</v>
       </c>
       <c r="E538">
-        <v>-4.363988581920101</v>
+        <v>-4.369721424762871</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28399,10 +28399,10 @@
         <v>0.01487185500334148</v>
       </c>
       <c r="H538">
-        <v>0.0150639885819201</v>
+        <v>0.01476972142476287</v>
       </c>
       <c r="I538">
-        <v>0.04786642142138398</v>
+        <v>0.04213357857861322</v>
       </c>
       <c r="J538">
         <v>2.404452619287154</v>
@@ -28414,10 +28414,10 @@
         <v>5.23</v>
       </c>
       <c r="M538">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N538">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28440,7 +28440,7 @@
         <v>159</v>
       </c>
       <c r="E539">
-        <v>-4.290863052707442</v>
+        <v>-4.297681918261291</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28449,10 +28449,10 @@
         <v>0.01479927248548437</v>
       </c>
       <c r="H539">
-        <v>0.01499086305270744</v>
+        <v>0.01469768191826129</v>
       </c>
       <c r="I539">
-        <v>0.04840943277692311</v>
+        <v>0.04159056722307408</v>
       </c>
       <c r="J539">
         <v>2.386352240769169</v>
@@ -28464,10 +28464,10 @@
         <v>5.23</v>
       </c>
       <c r="M539">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N539">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28490,7 +28490,7 @@
         <v>159</v>
       </c>
       <c r="E540">
-        <v>-4.229450071618398</v>
+        <v>-4.237181011148818</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28499,10 +28499,10 @@
         <v>0.01473831554138361</v>
       </c>
       <c r="H540">
-        <v>0.0149294500716184</v>
+        <v>0.01463718101114882</v>
       </c>
       <c r="I540">
-        <v>0.04886546976520911</v>
+        <v>0.04113453023478986</v>
       </c>
       <c r="J540">
         <v>2.371151007826336</v>
@@ -28514,10 +28514,10 @@
         <v>5.23</v>
       </c>
       <c r="M540">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N540">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28540,7 +28540,7 @@
         <v>159</v>
       </c>
       <c r="E541">
-        <v>-4.166339017969639</v>
+        <v>-4.175007250376031</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28549,10 +28549,10 @@
         <v>0.01467567313417283</v>
       </c>
       <c r="H541">
-        <v>0.01486633901796964</v>
+        <v>0.01457500725037603</v>
       </c>
       <c r="I541">
-        <v>0.04933411620319461</v>
+        <v>0.04066588379680258</v>
       </c>
       <c r="J541">
         <v>2.355529459893475</v>
@@ -28564,10 +28564,10 @@
         <v>5.23</v>
       </c>
       <c r="M541">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N541">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28590,7 +28590,7 @@
         <v>159</v>
       </c>
       <c r="E542">
-        <v>-4.140308512085973</v>
+        <v>-4.149363336163904</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28599,10 +28599,10 @@
         <v>0.01464983592412494</v>
       </c>
       <c r="H542">
-        <v>0.01484030851208597</v>
+        <v>0.0145493633361639</v>
       </c>
       <c r="I542">
-        <v>0.04952741203896416</v>
+        <v>0.04047258796103304</v>
       </c>
       <c r="J542">
         <v>2.349086265367815</v>
@@ -28614,10 +28614,10 @@
         <v>5.23</v>
       </c>
       <c r="M542">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N542">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28640,7 +28640,7 @@
         <v>159</v>
       </c>
       <c r="E543">
-        <v>-4.039192530409359</v>
+        <v>-4.049749076987438</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28649,10 +28649,10 @@
         <v>0.0145494708036984</v>
       </c>
       <c r="H543">
-        <v>0.01473919253040936</v>
+        <v>0.01444974907698744</v>
       </c>
       <c r="I543">
-        <v>0.05027827328903811</v>
+        <v>0.03972172671095908</v>
       </c>
       <c r="J543">
         <v>2.324057557032019</v>
@@ -28664,10 +28664,10 @@
         <v>5.23</v>
       </c>
       <c r="M543">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N543">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28690,7 +28690,7 @@
         <v>159</v>
       </c>
       <c r="E544">
-        <v>-3.954412468101992</v>
+        <v>-3.966228124516317</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28699,10 +28699,10 @@
         <v>0.01446532029630916</v>
       </c>
       <c r="H544">
-        <v>0.01465441246810199</v>
+        <v>0.01436622812451632</v>
       </c>
       <c r="I544">
-        <v>0.050907828207162</v>
+        <v>0.03909217179283697</v>
       </c>
       <c r="J544">
         <v>2.303072393094552</v>
@@ -28714,10 +28714,10 @@
         <v>5.23</v>
       </c>
       <c r="M544">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N544">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28740,7 +28740,7 @@
         <v>159</v>
       </c>
       <c r="E545">
-        <v>-3.828176504134056</v>
+        <v>-3.84186695209246</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28749,10 +28749,10 @@
         <v>0.01434002172811326</v>
       </c>
       <c r="H545">
-        <v>0.01452817650413406</v>
+        <v>0.01424186695209246</v>
       </c>
       <c r="I545">
-        <v>0.05184522397920155</v>
+        <v>0.03815477602079742</v>
       </c>
       <c r="J545">
         <v>2.271825867359915</v>
@@ -28764,10 +28764,10 @@
         <v>5.23</v>
       </c>
       <c r="M545">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N545">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28790,7 +28790,7 @@
         <v>159</v>
       </c>
       <c r="E546">
-        <v>-3.713168095617593</v>
+        <v>-3.728566589247035</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28799,10 +28799,10 @@
         <v>0.01422586734243231</v>
       </c>
       <c r="H546">
-        <v>0.01441316809561759</v>
+        <v>0.01412856658924704</v>
       </c>
       <c r="I546">
-        <v>0.05269924681471849</v>
+        <v>0.03730075318527692</v>
       </c>
       <c r="J546">
         <v>2.243358439509305</v>
@@ -28814,10 +28814,10 @@
         <v>5.23</v>
       </c>
       <c r="M546">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N546">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28840,7 +28840,7 @@
         <v>159</v>
       </c>
       <c r="E547">
-        <v>-3.143506413459034</v>
+        <v>-3.167365229100731</v>
       </c>
       <c r="F547">
         <v>1</v>
@@ -28849,10 +28849,10 @@
         <v>0.01366043582127988</v>
       </c>
       <c r="H547">
-        <v>0.01384350641345903</v>
+        <v>0.01356736522910073</v>
       </c>
       <c r="I547">
-        <v>0.05692940782084754</v>
+        <v>0.03307059217915143</v>
       </c>
       <c r="J547">
         <v>2.102353072638375</v>
@@ -28864,10 +28864,10 @@
         <v>5.23</v>
       </c>
       <c r="M547">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N547">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -28890,7 +28890,7 @@
         <v>159</v>
       </c>
       <c r="E548">
-        <v>-2.50066827237777</v>
+        <v>-2.534074189124635</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28899,10 +28899,10 @@
         <v>0.0130223712307512</v>
       </c>
       <c r="H548">
-        <v>0.01320066827237777</v>
+        <v>0.01293407418912463</v>
       </c>
       <c r="I548">
-        <v>0.06170295837343165</v>
+        <v>0.02829704162656732</v>
       </c>
       <c r="J548">
         <v>1.943234720885587</v>
@@ -28914,10 +28914,10 @@
         <v>5.23</v>
       </c>
       <c r="M548">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="N548">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="O548">
         <v>1</v>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -493,7 +493,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-26</t>
+    <t>2021-08-30</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -27590,7 +27590,7 @@
         <v>159</v>
       </c>
       <c r="E522">
-        <v>-1.217607021774699</v>
+        <v>-0.8396127696430522</v>
       </c>
       <c r="F522">
         <v>1</v>
@@ -27599,10 +27599,10 @@
         <v>0.01169598094404938</v>
       </c>
       <c r="H522">
-        <v>0.0116176070217747</v>
+        <v>0.01147961276964305</v>
       </c>
       <c r="I522">
-        <v>0.01837392227468282</v>
+        <v>0.3963681744063292</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
@@ -27614,10 +27614,10 @@
         <v>5.23</v>
       </c>
       <c r="M522">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N522">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27640,7 +27640,7 @@
         <v>159</v>
       </c>
       <c r="E523">
-        <v>-1.834146365863051</v>
+        <v>-1.431366612461521</v>
       </c>
       <c r="F523">
         <v>1</v>
@@ -27649,10 +27649,10 @@
         <v>0.01231716756962584</v>
       </c>
       <c r="H523">
-        <v>0.01223414636586305</v>
+        <v>0.01207136661246152</v>
       </c>
       <c r="I523">
-        <v>0.02302120376278616</v>
+        <v>0.4258009571643164</v>
       </c>
       <c r="J523">
         <v>1.767373458759561</v>
@@ -27664,10 +27664,10 @@
         <v>5.23</v>
       </c>
       <c r="M523">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N523">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27690,7 +27690,7 @@
         <v>159</v>
       </c>
       <c r="E524">
-        <v>-1.933218344186467</v>
+        <v>-1.526455797686508</v>
       </c>
       <c r="F524">
         <v>1</v>
@@ -27699,10 +27699,10 @@
         <v>0.01241698632165521</v>
       </c>
       <c r="H524">
-        <v>0.01233321834418647</v>
+        <v>0.01216645579768651</v>
       </c>
       <c r="I524">
-        <v>0.02376797746874182</v>
+        <v>0.4305305239687005</v>
       </c>
       <c r="J524">
         <v>1.79226591562474</v>
@@ -27714,10 +27714,10 @@
         <v>5.23</v>
       </c>
       <c r="M524">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N524">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27740,7 +27740,7 @@
         <v>159</v>
       </c>
       <c r="E525">
-        <v>-2.017756975374668</v>
+        <v>-1.607595890937495</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27749,10 +27749,10 @@
         <v>0.01250216217870664</v>
       </c>
       <c r="H525">
-        <v>0.01241775697537467</v>
+        <v>0.0122475958909375</v>
       </c>
       <c r="I525">
-        <v>0.02440520333196972</v>
+        <v>0.434566287769143</v>
       </c>
       <c r="J525">
         <v>1.813506777732329</v>
@@ -27764,10 +27764,10 @@
         <v>5.23</v>
       </c>
       <c r="M525">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N525">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27790,7 +27790,7 @@
         <v>159</v>
       </c>
       <c r="E526">
-        <v>-2.109091930985991</v>
+        <v>-1.695259089539317</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27799,10 +27799,10 @@
         <v>0.01259418558875724</v>
       </c>
       <c r="H526">
-        <v>0.01250909193098599</v>
+        <v>0.01233525908953932</v>
       </c>
       <c r="I526">
-        <v>0.02509365777125083</v>
+        <v>0.4389264992179243</v>
       </c>
       <c r="J526">
         <v>1.836455259041706</v>
@@ -27814,10 +27814,10 @@
         <v>5.23</v>
       </c>
       <c r="M526">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N526">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27840,7 +27840,7 @@
         <v>159</v>
       </c>
       <c r="E527">
-        <v>-2.218996555617549</v>
+        <v>-1.800745437803777</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27849,10 +27849,10 @@
         <v>0.01270491864020763</v>
       </c>
       <c r="H527">
-        <v>0.01261899655561755</v>
+        <v>0.01244074543780378</v>
       </c>
       <c r="I527">
-        <v>0.02592208459008116</v>
+        <v>0.4441732024038529</v>
       </c>
       <c r="J527">
         <v>1.864069486336068</v>
@@ -27864,10 +27864,10 @@
         <v>5.23</v>
       </c>
       <c r="M527">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N527">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27890,7 +27890,7 @@
         <v>159</v>
       </c>
       <c r="E528">
-        <v>-2.364330420117734</v>
+        <v>-1.94023673488687</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27899,10 +27899,10 @@
         <v>0.01285134798609852</v>
       </c>
       <c r="H528">
-        <v>0.01276433042011773</v>
+        <v>0.01258023673488687</v>
       </c>
       <c r="I528">
-        <v>0.02701756598078564</v>
+        <v>0.4511112512116497</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27914,10 +27914,10 @@
         <v>5.23</v>
       </c>
       <c r="M528">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N528">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27940,7 +27940,7 @@
         <v>159</v>
       </c>
       <c r="E529">
-        <v>-2.518334440375223</v>
+        <v>-2.088049638752098</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27949,10 +27949,10 @@
         <v>0.01300651284067956</v>
       </c>
       <c r="H529">
-        <v>0.01291833444037522</v>
+        <v>0.0127280496387521</v>
       </c>
       <c r="I529">
-        <v>0.02817840030433505</v>
+        <v>0.4584632019274597</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27964,10 +27964,10 @@
         <v>5.23</v>
       </c>
       <c r="M529">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N529">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27990,7 +27990,7 @@
         <v>159</v>
       </c>
       <c r="E530">
-        <v>-2.912542849897265</v>
+        <v>-2.466410474021997</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -27999,10 +27999,10 @@
         <v>0.01340369267037388</v>
       </c>
       <c r="H530">
-        <v>0.01331254284989727</v>
+        <v>0.013106410474022</v>
       </c>
       <c r="I530">
-        <v>0.03114982047661119</v>
+        <v>0.4772821963518794</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28014,10 +28014,10 @@
         <v>5.23</v>
       </c>
       <c r="M530">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N530">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28040,7 +28040,7 @@
         <v>159</v>
       </c>
       <c r="E531">
-        <v>-3.268352505773279</v>
+        <v>-2.807916224134152</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28049,10 +28049,10 @@
         <v>0.01376218430858061</v>
       </c>
       <c r="H531">
-        <v>0.01366835250577328</v>
+        <v>0.01344791622413415</v>
       </c>
       <c r="I531">
-        <v>0.03383180280733544</v>
+        <v>0.4942680844464622</v>
       </c>
       <c r="J531">
         <v>2.127726760244542</v>
@@ -28064,10 +28064,10 @@
         <v>5.23</v>
       </c>
       <c r="M531">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N531">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28090,7 +28090,7 @@
         <v>159</v>
       </c>
       <c r="E532">
-        <v>-3.405825382845905</v>
+        <v>-2.939862553384764</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28099,10 +28099,10 @@
         <v>0.01390069341336987</v>
       </c>
       <c r="H532">
-        <v>0.01380582538284591</v>
+        <v>0.01357986255338476</v>
       </c>
       <c r="I532">
-        <v>0.03486803052396414</v>
+        <v>0.5008308599851059</v>
       </c>
       <c r="J532">
         <v>2.162267684132137</v>
@@ -28114,10 +28114,10 @@
         <v>5.23</v>
       </c>
       <c r="M532">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N532">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28140,7 +28140,7 @@
         <v>159</v>
       </c>
       <c r="E533">
-        <v>-3.632326093138203</v>
+        <v>-3.157257707484405</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28149,10 +28149,10 @@
         <v>0.01412890141544829</v>
       </c>
       <c r="H533">
-        <v>0.0140323260931382</v>
+        <v>0.01379725770748441</v>
       </c>
       <c r="I533">
-        <v>0.0365753223100862</v>
+        <v>0.5116437079638843</v>
       </c>
       <c r="J533">
         <v>2.219177410336232</v>
@@ -28164,10 +28164,10 @@
         <v>5.23</v>
       </c>
       <c r="M533">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N533">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28190,7 +28190,7 @@
         <v>159</v>
       </c>
       <c r="E534">
-        <v>-3.916173985957975</v>
+        <v>-3.429694629738558</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28199,10 +28199,10 @@
         <v>0.01441488886524911</v>
       </c>
       <c r="H534">
-        <v>0.01431617398595797</v>
+        <v>0.01406969462973856</v>
       </c>
       <c r="I534">
-        <v>0.03871487929113915</v>
+        <v>0.5251942355105559</v>
       </c>
       <c r="J534">
         <v>2.29049597637135</v>
@@ -28214,10 +28214,10 @@
         <v>5.23</v>
       </c>
       <c r="M534">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N534">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28240,7 +28240,7 @@
         <v>159</v>
       </c>
       <c r="E535">
-        <v>-4.122282314908504</v>
+        <v>-3.627517196721227</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28249,10 +28249,10 @@
         <v>0.01462255077456862</v>
       </c>
       <c r="H535">
-        <v>0.0145222823149085</v>
+        <v>0.01426751719672123</v>
       </c>
       <c r="I535">
-        <v>0.04026845966011283</v>
+        <v>0.5350335778473898</v>
       </c>
       <c r="J535">
         <v>2.342281988670478</v>
@@ -28264,10 +28264,10 @@
         <v>5.23</v>
       </c>
       <c r="M535">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N535">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28290,7 +28290,7 @@
         <v>159</v>
       </c>
       <c r="E536">
-        <v>-4.299418186598657</v>
+        <v>-3.797532028343435</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28299,10 +28299,10 @@
         <v>0.01480102184127151</v>
       </c>
       <c r="H536">
-        <v>0.01469941818659866</v>
+        <v>0.01443753202834343</v>
       </c>
       <c r="I536">
-        <v>0.04160365467285398</v>
+        <v>0.5434898129280761</v>
       </c>
       <c r="J536">
         <v>2.38678848909514</v>
@@ -28314,10 +28314,10 @@
         <v>5.23</v>
       </c>
       <c r="M536">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N536">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28340,7 +28340,7 @@
         <v>159</v>
       </c>
       <c r="E537">
-        <v>-4.340787088582982</v>
+        <v>-3.837237858891204</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28349,10 +28349,10 @@
         <v>0.01484270256915019</v>
       </c>
       <c r="H537">
-        <v>0.01474078708858298</v>
+        <v>0.01447723785889121</v>
       </c>
       <c r="I537">
-        <v>0.04191548056720773</v>
+        <v>0.5454647102589867</v>
       </c>
       <c r="J537">
         <v>2.397182685573614</v>
@@ -28364,10 +28364,10 @@
         <v>5.23</v>
       </c>
       <c r="M537">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N537">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28390,7 +28390,7 @@
         <v>159</v>
       </c>
       <c r="E538">
-        <v>-4.369721424762871</v>
+        <v>-3.865009005676926</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28399,10 +28399,10 @@
         <v>0.01487185500334148</v>
       </c>
       <c r="H538">
-        <v>0.01476972142476287</v>
+        <v>0.01450500900567693</v>
       </c>
       <c r="I538">
-        <v>0.04213357857861322</v>
+        <v>0.5468459976645583</v>
       </c>
       <c r="J538">
         <v>2.404452619287154</v>
@@ -28414,10 +28414,10 @@
         <v>5.23</v>
       </c>
       <c r="M538">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N538">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28440,7 +28440,7 @@
         <v>159</v>
       </c>
       <c r="E539">
-        <v>-4.297681918261291</v>
+        <v>-3.795865559738223</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28449,10 +28449,10 @@
         <v>0.01479927248548437</v>
       </c>
       <c r="H539">
-        <v>0.01469768191826129</v>
+        <v>0.01443586555973822</v>
       </c>
       <c r="I539">
-        <v>0.04159056722307408</v>
+        <v>0.543406925746142</v>
       </c>
       <c r="J539">
         <v>2.386352240769169</v>
@@ -28464,10 +28464,10 @@
         <v>5.23</v>
       </c>
       <c r="M539">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N539">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28490,7 +28490,7 @@
         <v>159</v>
       </c>
       <c r="E540">
-        <v>-4.237181011148818</v>
+        <v>-3.737796849896604</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28499,10 +28499,10 @@
         <v>0.01473831554138361</v>
       </c>
       <c r="H540">
-        <v>0.01463718101114882</v>
+        <v>0.0143777968498966</v>
       </c>
       <c r="I540">
-        <v>0.04113453023478986</v>
+        <v>0.5405186914870033</v>
       </c>
       <c r="J540">
         <v>2.371151007826336</v>
@@ -28514,10 +28514,10 @@
         <v>5.23</v>
       </c>
       <c r="M540">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N540">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28540,7 +28540,7 @@
         <v>159</v>
       </c>
       <c r="E541">
-        <v>-4.175007250376031</v>
+        <v>-3.678122536793074</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28549,10 +28549,10 @@
         <v>0.01467567313417283</v>
       </c>
       <c r="H541">
-        <v>0.01457500725037603</v>
+        <v>0.01431812253679307</v>
       </c>
       <c r="I541">
-        <v>0.04066588379680258</v>
+        <v>0.5375505973797594</v>
       </c>
       <c r="J541">
         <v>2.355529459893475</v>
@@ -28564,10 +28564,10 @@
         <v>5.23</v>
       </c>
       <c r="M541">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N541">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28590,7 +28590,7 @@
         <v>159</v>
       </c>
       <c r="E542">
-        <v>-4.149363336163904</v>
+        <v>-3.653509533705053</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28599,10 +28599,10 @@
         <v>0.01464983592412494</v>
       </c>
       <c r="H542">
-        <v>0.0145493633361639</v>
+        <v>0.01429350953370505</v>
       </c>
       <c r="I542">
-        <v>0.04047258796103304</v>
+        <v>0.5363263904198838</v>
       </c>
       <c r="J542">
         <v>2.349086265367815</v>
@@ -28614,10 +28614,10 @@
         <v>5.23</v>
       </c>
       <c r="M542">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N542">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28640,7 +28640,7 @@
         <v>159</v>
       </c>
       <c r="E543">
-        <v>-4.049749076987438</v>
+        <v>-3.557899867862314</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28649,10 +28649,10 @@
         <v>0.0145494708036984</v>
       </c>
       <c r="H543">
-        <v>0.01444974907698744</v>
+        <v>0.01419789986786231</v>
       </c>
       <c r="I543">
-        <v>0.03972172671095908</v>
+        <v>0.5315709358360827</v>
       </c>
       <c r="J543">
         <v>2.324057557032019</v>
@@ -28664,10 +28664,10 @@
         <v>5.23</v>
       </c>
       <c r="M543">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N543">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28690,7 +28690,7 @@
         <v>159</v>
       </c>
       <c r="E544">
-        <v>-3.966228124516317</v>
+        <v>-3.477736541621189</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28699,10 +28699,10 @@
         <v>0.01446532029630916</v>
       </c>
       <c r="H544">
-        <v>0.01436622812451632</v>
+        <v>0.01411773654162119</v>
       </c>
       <c r="I544">
-        <v>0.03909217179283697</v>
+        <v>0.5275837546879654</v>
       </c>
       <c r="J544">
         <v>2.303072393094552</v>
@@ -28714,10 +28714,10 @@
         <v>5.23</v>
       </c>
       <c r="M544">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N544">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28740,7 +28740,7 @@
         <v>159</v>
       </c>
       <c r="E545">
-        <v>-3.84186695209246</v>
+        <v>-3.358374813314875</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28749,10 +28749,10 @@
         <v>0.01434002172811326</v>
       </c>
       <c r="H545">
-        <v>0.01424186695209246</v>
+        <v>0.01399837481331487</v>
       </c>
       <c r="I545">
-        <v>0.03815477602079742</v>
+        <v>0.5216469147983833</v>
       </c>
       <c r="J545">
         <v>2.271825867359915</v>
@@ -28764,10 +28764,10 @@
         <v>5.23</v>
       </c>
       <c r="M545">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N545">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28790,7 +28790,7 @@
         <v>159</v>
       </c>
       <c r="E546">
-        <v>-3.728566589247035</v>
+        <v>-3.249629238925545</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28799,10 +28799,10 @@
         <v>0.01422586734243231</v>
       </c>
       <c r="H546">
-        <v>0.01412856658924704</v>
+        <v>0.01388962923892554</v>
       </c>
       <c r="I546">
-        <v>0.03730075318527692</v>
+        <v>0.5162381035067671</v>
       </c>
       <c r="J546">
         <v>2.243358439509305</v>
@@ -28814,10 +28814,10 @@
         <v>5.23</v>
       </c>
       <c r="M546">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N546">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28840,7 +28840,7 @@
         <v>159</v>
       </c>
       <c r="E547">
-        <v>-3.167365229100731</v>
+        <v>-2.710988737478591</v>
       </c>
       <c r="F547">
         <v>1</v>
@@ -28849,10 +28849,10 @@
         <v>0.01366043582127988</v>
       </c>
       <c r="H547">
-        <v>0.01356736522910073</v>
+        <v>0.01335098873747859</v>
       </c>
       <c r="I547">
-        <v>0.03307059217915143</v>
+        <v>0.4894470838012914</v>
       </c>
       <c r="J547">
         <v>2.102353072638375</v>
@@ -28864,10 +28864,10 @@
         <v>5.23</v>
       </c>
       <c r="M547">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N547">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -28890,7 +28890,7 @@
         <v>159</v>
       </c>
       <c r="E548">
-        <v>-2.534074189124635</v>
+        <v>-2.10315663378294</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28899,10 +28899,10 @@
         <v>0.0130223712307512</v>
       </c>
       <c r="H548">
-        <v>0.01293407418912463</v>
+        <v>0.01274315663378294</v>
       </c>
       <c r="I548">
-        <v>0.02829704162656732</v>
+        <v>0.4592145969682617</v>
       </c>
       <c r="J548">
         <v>1.943234720885587</v>
@@ -28914,10 +28914,10 @@
         <v>5.23</v>
       </c>
       <c r="M548">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="N548">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O548">
         <v>1</v>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -496,7 +496,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-08-31</t>
+    <t>2021-09-01</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -27593,7 +27593,7 @@
         <v>160</v>
       </c>
       <c r="E522">
-        <v>-0.4967402843354574</v>
+        <v>-0.2551142066101404</v>
       </c>
       <c r="F522">
         <v>1</v>
@@ -27602,10 +27602,10 @@
         <v>0.01169598094404938</v>
       </c>
       <c r="H522">
-        <v>0.01159674028433546</v>
+        <v>0.01193511420661014</v>
       </c>
       <c r="I522">
-        <v>0.7392406597139241</v>
+        <v>0.980866737439241</v>
       </c>
       <c r="J522">
         <v>1.612464075822789</v>
@@ -27617,10 +27617,10 @@
         <v>5.23</v>
       </c>
       <c r="M522">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N522">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27643,7 +27643,7 @@
         <v>160</v>
       </c>
       <c r="E523">
-        <v>-1.077650470348352</v>
+        <v>-0.8406716741111389</v>
       </c>
       <c r="F523">
         <v>1</v>
@@ -27652,10 +27652,10 @@
         <v>0.01231716756962584</v>
       </c>
       <c r="H523">
-        <v>0.01217765047034835</v>
+        <v>0.01252067167411114</v>
       </c>
       <c r="I523">
-        <v>0.7795170992774851</v>
+        <v>1.016495895514699</v>
       </c>
       <c r="J523">
         <v>1.767373458759561</v>
@@ -27667,10 +27667,10 @@
         <v>5.23</v>
       </c>
       <c r="M523">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N523">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27693,7 +27693,7 @@
         <v>160</v>
       </c>
       <c r="E524">
-        <v>-1.170997183592777</v>
+        <v>-0.9347651610615184</v>
       </c>
       <c r="F524">
         <v>1</v>
@@ -27702,10 +27702,10 @@
         <v>0.01241698632165521</v>
       </c>
       <c r="H524">
-        <v>0.01227099718359278</v>
+        <v>0.01261476516106152</v>
       </c>
       <c r="I524">
-        <v>0.7859891380624315</v>
+        <v>1.02222116059369</v>
       </c>
       <c r="J524">
         <v>1.79226591562474</v>
@@ -27717,10 +27717,10 @@
         <v>5.23</v>
       </c>
       <c r="M524">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N524">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27743,7 +27743,7 @@
         <v>160</v>
       </c>
       <c r="E525">
-        <v>-1.250650416496233</v>
+        <v>-1.015055619828202</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27752,10 +27752,10 @@
         <v>0.01250216217870664</v>
       </c>
       <c r="H525">
-        <v>0.01235065041649623</v>
+        <v>0.0126950556198282</v>
       </c>
       <c r="I525">
-        <v>0.7915117622104049</v>
+        <v>1.027106558878436</v>
       </c>
       <c r="J525">
         <v>1.813506777732329</v>
@@ -27767,10 +27767,10 @@
         <v>5.23</v>
       </c>
       <c r="M525">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N525">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27793,7 +27793,7 @@
         <v>160</v>
       </c>
       <c r="E526">
-        <v>-1.336707221406399</v>
+        <v>-1.10180087917765</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27802,10 +27802,10 @@
         <v>0.01259418558875724</v>
       </c>
       <c r="H526">
-        <v>0.0124367072214064</v>
+        <v>0.01278180087917765</v>
       </c>
       <c r="I526">
-        <v>0.797478367350843</v>
+        <v>1.032384709579592</v>
       </c>
       <c r="J526">
         <v>1.836455259041706</v>
@@ -27817,10 +27817,10 @@
         <v>5.23</v>
       </c>
       <c r="M526">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N526">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27843,7 +27843,7 @@
         <v>160</v>
       </c>
       <c r="E527">
-        <v>-1.440260573760254</v>
+        <v>-1.206182658350335</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27852,10 +27852,10 @@
         <v>0.01270491864020763</v>
       </c>
       <c r="H527">
-        <v>0.01254026057376025</v>
+        <v>0.01288618265835034</v>
       </c>
       <c r="I527">
-        <v>0.8046580664473764</v>
+        <v>1.038735981857295</v>
       </c>
       <c r="J527">
         <v>1.864069486336068</v>
@@ -27867,10 +27867,10 @@
         <v>5.23</v>
       </c>
       <c r="M527">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N527">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27893,7 +27893,7 @@
         <v>160</v>
       </c>
       <c r="E528">
-        <v>-1.577195747598368</v>
+        <v>-1.344213313579155</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27902,10 +27902,10 @@
         <v>0.01285134798609852</v>
       </c>
       <c r="H528">
-        <v>0.01267719574759837</v>
+        <v>0.01302421331357915</v>
       </c>
       <c r="I528">
-        <v>0.8141522385001521</v>
+        <v>1.047134672519365</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27917,10 +27917,10 @@
         <v>5.23</v>
       </c>
       <c r="M528">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N528">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27943,7 +27943,7 @@
         <v>160</v>
       </c>
       <c r="E529">
-        <v>-1.722300038041982</v>
+        <v>-1.490478438346317</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27952,10 +27952,10 @@
         <v>0.01300651284067956</v>
       </c>
       <c r="H529">
-        <v>0.01282230003804198</v>
+        <v>0.01317047843834632</v>
       </c>
       <c r="I529">
-        <v>0.8242128026375761</v>
+        <v>1.056034402333241</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27967,10 +27967,10 @@
         <v>5.23</v>
       </c>
       <c r="M529">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N529">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27993,7 +27993,7 @@
         <v>160</v>
       </c>
       <c r="E530">
-        <v>-2.093727559576569</v>
+        <v>-1.86487738005318</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28002,10 +28002,10 @@
         <v>0.01340369267037388</v>
       </c>
       <c r="H530">
-        <v>0.01319372755957657</v>
+        <v>0.01354487738005318</v>
       </c>
       <c r="I530">
-        <v>0.8499651107973074</v>
+        <v>1.078815290320696</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28017,10 +28017,10 @@
         <v>5.23</v>
       </c>
       <c r="M530">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N530">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28043,7 +28043,7 @@
         <v>160</v>
       </c>
       <c r="E531">
-        <v>-2.093727559576569</v>
+        <v>-1.86487738005318</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28052,10 +28052,10 @@
         <v>0.013106410474022</v>
       </c>
       <c r="H531">
-        <v>0.01319372755957657</v>
+        <v>0.01354487738005318</v>
       </c>
       <c r="I531">
-        <v>0.372682914445428</v>
+        <v>0.6015330939688166</v>
       </c>
       <c r="J531">
         <v>2.038327349220418</v>
@@ -28067,10 +28067,10 @@
         <v>5.32</v>
       </c>
       <c r="M531">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N531">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28093,7 +28093,7 @@
         <v>160</v>
       </c>
       <c r="E532">
-        <v>-2.428975350917034</v>
+        <v>-2.20280715372437</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28102,10 +28102,10 @@
         <v>0.01376218430858061</v>
       </c>
       <c r="H532">
-        <v>0.01352897535091703</v>
+        <v>0.01388280715372437</v>
       </c>
       <c r="I532">
-        <v>0.8732089576635795</v>
+        <v>1.099377154856244</v>
       </c>
       <c r="J532">
         <v>2.127726760244542</v>
@@ -28117,10 +28117,10 @@
         <v>5.23</v>
       </c>
       <c r="M532">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N532">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28143,7 +28143,7 @@
         <v>160</v>
       </c>
       <c r="E533">
-        <v>-2.428975350917034</v>
+        <v>-2.20280715372437</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28152,10 +28152,10 @@
         <v>0.01344791622413415</v>
       </c>
       <c r="H533">
-        <v>0.01352897535091703</v>
+        <v>0.01388280715372437</v>
       </c>
       <c r="I533">
-        <v>0.3789408732171173</v>
+        <v>0.6051090704097817</v>
       </c>
       <c r="J533">
         <v>2.127726760244542</v>
@@ -28167,10 +28167,10 @@
         <v>5.32</v>
       </c>
       <c r="M533">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N533">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28193,7 +28193,7 @@
         <v>160</v>
       </c>
       <c r="E534">
-        <v>-2.558503815495514</v>
+        <v>-2.333371846019478</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28202,10 +28202,10 @@
         <v>0.01390069341336987</v>
       </c>
       <c r="H534">
-        <v>0.01365850381549551</v>
+        <v>0.01401337184601948</v>
       </c>
       <c r="I534">
-        <v>0.8821895978743557</v>
+        <v>1.107321567350391</v>
       </c>
       <c r="J534">
         <v>2.162267684132137</v>
@@ -28217,10 +28217,10 @@
         <v>5.23</v>
       </c>
       <c r="M534">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N534">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28243,7 +28243,7 @@
         <v>160</v>
       </c>
       <c r="E535">
-        <v>-2.558503815495514</v>
+        <v>-2.333371846019478</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28252,10 +28252,10 @@
         <v>0.01357986255338476</v>
       </c>
       <c r="H535">
-        <v>0.01365850381549551</v>
+        <v>0.01401337184601948</v>
       </c>
       <c r="I535">
-        <v>0.3813587378892498</v>
+        <v>0.6064907073652854</v>
       </c>
       <c r="J535">
         <v>2.162267684132137</v>
@@ -28267,10 +28267,10 @@
         <v>5.32</v>
       </c>
       <c r="M535">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N535">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28293,7 +28293,7 @@
         <v>160</v>
       </c>
       <c r="E536">
-        <v>-2.77191528876087</v>
+        <v>-2.548490611070957</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28302,10 +28302,10 @@
         <v>0.01412890141544829</v>
       </c>
       <c r="H536">
-        <v>0.01387191528876087</v>
+        <v>0.01422849061107096</v>
       </c>
       <c r="I536">
-        <v>0.8969861266874188</v>
+        <v>1.120410804377332</v>
       </c>
       <c r="J536">
         <v>2.219177410336232</v>
@@ -28317,10 +28317,10 @@
         <v>5.23</v>
       </c>
       <c r="M536">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N536">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28343,7 +28343,7 @@
         <v>160</v>
       </c>
       <c r="E537">
-        <v>-2.77191528876087</v>
+        <v>-2.548490611070957</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28352,10 +28352,10 @@
         <v>0.01379725770748441</v>
       </c>
       <c r="H537">
-        <v>0.01387191528876087</v>
+        <v>0.01422849061107096</v>
       </c>
       <c r="I537">
-        <v>0.3853424187235346</v>
+        <v>0.6087670964134482</v>
       </c>
       <c r="J537">
         <v>2.219177410336232</v>
@@ -28367,10 +28367,10 @@
         <v>5.32</v>
       </c>
       <c r="M537">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N537">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28393,7 +28393,7 @@
         <v>160</v>
       </c>
       <c r="E538">
-        <v>-3.039359911392563</v>
+        <v>-2.818074790683704</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28402,10 +28402,10 @@
         <v>0.01441488886524911</v>
       </c>
       <c r="H538">
-        <v>0.01413935991139256</v>
+        <v>0.0144980747906837</v>
       </c>
       <c r="I538">
-        <v>0.9155289538565503</v>
+        <v>1.136814074565409</v>
       </c>
       <c r="J538">
         <v>2.29049597637135</v>
@@ -28417,10 +28417,10 @@
         <v>5.23</v>
       </c>
       <c r="M538">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N538">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28443,7 +28443,7 @@
         <v>160</v>
       </c>
       <c r="E539">
-        <v>-3.039359911392563</v>
+        <v>-2.818074790683704</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28452,10 +28452,10 @@
         <v>0.01406969462973856</v>
       </c>
       <c r="H539">
-        <v>0.01413935991139256</v>
+        <v>0.0144980747906837</v>
       </c>
       <c r="I539">
-        <v>0.3903347183459944</v>
+        <v>0.6116198390548533</v>
       </c>
       <c r="J539">
         <v>2.29049597637135</v>
@@ -28467,10 +28467,10 @@
         <v>5.32</v>
       </c>
       <c r="M539">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N539">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28493,7 +28493,7 @@
         <v>160</v>
       </c>
       <c r="E540">
-        <v>-3.233557457514293</v>
+        <v>-3.013825917174408</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28502,10 +28502,10 @@
         <v>0.01462255077456862</v>
       </c>
       <c r="H540">
-        <v>0.01433355745751429</v>
+        <v>0.01469382591717441</v>
       </c>
       <c r="I540">
-        <v>0.9289933170543234</v>
+        <v>1.148724857394209</v>
       </c>
       <c r="J540">
         <v>2.342281988670478</v>
@@ -28517,10 +28517,10 @@
         <v>5.23</v>
       </c>
       <c r="M540">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N540">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28543,7 +28543,7 @@
         <v>160</v>
       </c>
       <c r="E541">
-        <v>-3.233557457514293</v>
+        <v>-3.013825917174408</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28552,10 +28552,10 @@
         <v>0.01426751719672123</v>
       </c>
       <c r="H541">
-        <v>0.01433355745751429</v>
+        <v>0.01469382591717441</v>
       </c>
       <c r="I541">
-        <v>0.3939597392069336</v>
+        <v>0.6136912795468188</v>
       </c>
       <c r="J541">
         <v>2.342281988670478</v>
@@ -28567,10 +28567,10 @@
         <v>5.32</v>
       </c>
       <c r="M541">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N541">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28593,7 +28593,7 @@
         <v>160</v>
       </c>
       <c r="E542">
-        <v>-3.400456834106776</v>
+        <v>-3.18206048877963</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28602,10 +28602,10 @@
         <v>0.01480102184127151</v>
       </c>
       <c r="H542">
-        <v>0.01450045683410678</v>
+        <v>0.01486206048877963</v>
       </c>
       <c r="I542">
-        <v>0.9405650071647349</v>
+        <v>1.158961352491881</v>
       </c>
       <c r="J542">
         <v>2.38678848909514</v>
@@ -28617,10 +28617,10 @@
         <v>5.23</v>
       </c>
       <c r="M542">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N542">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28643,7 +28643,7 @@
         <v>160</v>
       </c>
       <c r="E543">
-        <v>-3.400456834106776</v>
+        <v>-3.18206048877963</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28652,10 +28652,10 @@
         <v>0.01443753202834343</v>
       </c>
       <c r="H543">
-        <v>0.01450045683410678</v>
+        <v>0.01486206048877963</v>
       </c>
       <c r="I543">
-        <v>0.3970751942366588</v>
+        <v>0.6154715395638046</v>
       </c>
       <c r="J543">
         <v>2.38678848909514</v>
@@ -28667,10 +28667,10 @@
         <v>5.32</v>
       </c>
       <c r="M543">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N543">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28693,7 +28693,7 @@
         <v>160</v>
       </c>
       <c r="E544">
-        <v>-3.439435070901053</v>
+        <v>-3.221350551468261</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28702,10 +28702,10 @@
         <v>0.01484270256915019</v>
       </c>
       <c r="H544">
-        <v>0.01453943507090105</v>
+        <v>0.01490135055146826</v>
       </c>
       <c r="I544">
-        <v>0.9432674982491376</v>
+        <v>1.16135201768193</v>
       </c>
       <c r="J544">
         <v>2.397182685573614</v>
@@ -28717,10 +28717,10 @@
         <v>5.23</v>
       </c>
       <c r="M544">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N544">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28743,7 +28743,7 @@
         <v>160</v>
       </c>
       <c r="E545">
-        <v>-3.439435070901053</v>
+        <v>-3.221350551468261</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28752,10 +28752,10 @@
         <v>0.01447723785889121</v>
       </c>
       <c r="H545">
-        <v>0.01453943507090105</v>
+        <v>0.01490135055146826</v>
       </c>
       <c r="I545">
-        <v>0.3978027879901509</v>
+        <v>0.615887307422943</v>
       </c>
       <c r="J545">
         <v>2.397182685573614</v>
@@ -28767,10 +28767,10 @@
         <v>5.32</v>
       </c>
       <c r="M545">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N545">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28793,7 +28793,7 @@
         <v>160</v>
       </c>
       <c r="E546">
-        <v>-3.466697322326826</v>
+        <v>-3.248830900905441</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28802,10 +28802,10 @@
         <v>0.01487185500334148</v>
       </c>
       <c r="H546">
-        <v>0.01456669732232682</v>
+        <v>0.01492883090090544</v>
       </c>
       <c r="I546">
-        <v>0.9451576810146589</v>
+        <v>1.163024102436044</v>
       </c>
       <c r="J546">
         <v>2.404452619287154</v>
@@ -28817,10 +28817,10 @@
         <v>5.23</v>
       </c>
       <c r="M546">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N546">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28843,7 +28843,7 @@
         <v>160</v>
       </c>
       <c r="E547">
-        <v>-3.466697322326826</v>
+        <v>-3.248830900905441</v>
       </c>
       <c r="F547">
         <v>1</v>
@@ -28852,10 +28852,10 @@
         <v>0.01450500900567693</v>
       </c>
       <c r="H547">
-        <v>0.01456669732232682</v>
+        <v>0.01492883090090544</v>
       </c>
       <c r="I547">
-        <v>0.3983116833501006</v>
+        <v>0.6161781047714854</v>
       </c>
       <c r="J547">
         <v>2.404452619287154</v>
@@ -28867,10 +28867,10 @@
         <v>5.32</v>
       </c>
       <c r="M547">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N547">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -28893,7 +28893,7 @@
         <v>160</v>
       </c>
       <c r="E548">
-        <v>-3.398820902884382</v>
+        <v>-3.180411470107456</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28902,10 +28902,10 @@
         <v>0.01479927248548437</v>
       </c>
       <c r="H548">
-        <v>0.01449882090288438</v>
+        <v>0.01486041147010746</v>
       </c>
       <c r="I548">
-        <v>0.9404515825999828</v>
+        <v>1.158861015376909</v>
       </c>
       <c r="J548">
         <v>2.386352240769169</v>
@@ -28917,10 +28917,10 @@
         <v>5.23</v>
       </c>
       <c r="M548">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N548">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -28943,7 +28943,7 @@
         <v>160</v>
       </c>
       <c r="E549">
-        <v>-3.398820902884382</v>
+        <v>-3.180411470107456</v>
       </c>
       <c r="F549">
         <v>1</v>
@@ -28952,10 +28952,10 @@
         <v>0.01443586555973822</v>
       </c>
       <c r="H549">
-        <v>0.01449882090288438</v>
+        <v>0.01486041147010746</v>
       </c>
       <c r="I549">
-        <v>0.3970446568538408</v>
+        <v>0.6154540896307665</v>
       </c>
       <c r="J549">
         <v>2.386352240769169</v>
@@ -28967,10 +28967,10 @@
         <v>5.32</v>
       </c>
       <c r="M549">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N549">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -28993,7 +28993,7 @@
         <v>160</v>
       </c>
       <c r="E550">
-        <v>-3.341816279348762</v>
+        <v>-3.12295080958355</v>
       </c>
       <c r="F550">
         <v>1</v>
@@ -29002,10 +29002,10 @@
         <v>0.01473831554138361</v>
       </c>
       <c r="H550">
-        <v>0.01444181627934876</v>
+        <v>0.01480295080958355</v>
       </c>
       <c r="I550">
-        <v>0.9364992620348458</v>
+        <v>1.155364731800057</v>
       </c>
       <c r="J550">
         <v>2.371151007826336</v>
@@ -29017,10 +29017,10 @@
         <v>5.23</v>
       </c>
       <c r="M550">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N550">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O550">
         <v>1</v>
@@ -29043,7 +29043,7 @@
         <v>160</v>
       </c>
       <c r="E551">
-        <v>-3.341816279348762</v>
+        <v>-3.12295080958355</v>
       </c>
       <c r="F551">
         <v>1</v>
@@ -29052,10 +29052,10 @@
         <v>0.0143777968498966</v>
       </c>
       <c r="H551">
-        <v>0.01444181627934876</v>
+        <v>0.01480295080958355</v>
       </c>
       <c r="I551">
-        <v>0.3959805705478425</v>
+        <v>0.6148460403130542</v>
       </c>
       <c r="J551">
         <v>2.371151007826336</v>
@@ -29067,10 +29067,10 @@
         <v>5.32</v>
       </c>
       <c r="M551">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N551">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O551">
         <v>1</v>
@@ -29093,7 +29093,7 @@
         <v>160</v>
       </c>
       <c r="E552">
-        <v>-3.283235474600532</v>
+        <v>-3.063901358397336</v>
       </c>
       <c r="F552">
         <v>1</v>
@@ -29102,10 +29102,10 @@
         <v>0.01467567313417283</v>
       </c>
       <c r="H552">
-        <v>0.01438323547460053</v>
+        <v>0.01474390135839734</v>
       </c>
       <c r="I552">
-        <v>0.9324376595723018</v>
+        <v>1.151771775775497</v>
       </c>
       <c r="J552">
         <v>2.355529459893475</v>
@@ -29117,10 +29117,10 @@
         <v>5.23</v>
       </c>
       <c r="M552">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N552">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -29143,7 +29143,7 @@
         <v>160</v>
       </c>
       <c r="E553">
-        <v>-3.283235474600532</v>
+        <v>-3.063901358397336</v>
       </c>
       <c r="F553">
         <v>1</v>
@@ -29152,10 +29152,10 @@
         <v>0.01431812253679307</v>
       </c>
       <c r="H553">
-        <v>0.01438323547460053</v>
+        <v>0.01474390135839734</v>
       </c>
       <c r="I553">
-        <v>0.3948870621925424</v>
+        <v>0.6142211783957379</v>
       </c>
       <c r="J553">
         <v>2.355529459893475</v>
@@ -29167,10 +29167,10 @@
         <v>5.32</v>
       </c>
       <c r="M553">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N553">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O553">
         <v>1</v>
@@ -29193,7 +29193,7 @@
         <v>160</v>
       </c>
       <c r="E554">
-        <v>-3.259073495129306</v>
+        <v>-3.039546083090341</v>
       </c>
       <c r="F554">
         <v>1</v>
@@ -29202,10 +29202,10 @@
         <v>0.01464983592412494</v>
       </c>
       <c r="H554">
-        <v>0.01435907349512931</v>
+        <v>0.01471954608309034</v>
       </c>
       <c r="I554">
-        <v>0.9307624289956307</v>
+        <v>1.150289841034596</v>
       </c>
       <c r="J554">
         <v>2.349086265367815</v>
@@ -29217,10 +29217,10 @@
         <v>5.23</v>
       </c>
       <c r="M554">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N554">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O554">
         <v>1</v>
@@ -29243,7 +29243,7 @@
         <v>160</v>
       </c>
       <c r="E555">
-        <v>-3.259073495129306</v>
+        <v>-3.039546083090341</v>
       </c>
       <c r="F555">
         <v>1</v>
@@ -29252,10 +29252,10 @@
         <v>0.01429350953370505</v>
       </c>
       <c r="H555">
-        <v>0.01435907349512931</v>
+        <v>0.01471954608309034</v>
       </c>
       <c r="I555">
-        <v>0.3944360385757468</v>
+        <v>0.6139634506147118</v>
       </c>
       <c r="J555">
         <v>2.349086265367815</v>
@@ -29267,10 +29267,10 @@
         <v>5.32</v>
       </c>
       <c r="M555">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N555">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O555">
         <v>1</v>
@@ -29293,7 +29293,7 @@
         <v>160</v>
       </c>
       <c r="E556">
-        <v>-3.165215838870073</v>
+        <v>-2.944937565581034</v>
       </c>
       <c r="F556">
         <v>1</v>
@@ -29302,10 +29302,10 @@
         <v>0.0145494708036984</v>
       </c>
       <c r="H556">
-        <v>0.01426521583887007</v>
+        <v>0.01462493756558103</v>
       </c>
       <c r="I556">
-        <v>0.9242549648283243</v>
+        <v>1.144533238117363</v>
       </c>
       <c r="J556">
         <v>2.324057557032019</v>
@@ -29317,10 +29317,10 @@
         <v>5.23</v>
       </c>
       <c r="M556">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N556">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O556">
         <v>1</v>
@@ -29343,7 +29343,7 @@
         <v>160</v>
       </c>
       <c r="E557">
-        <v>-3.086521474104571</v>
+        <v>-2.865613645897406</v>
       </c>
       <c r="F557">
         <v>1</v>
@@ -29352,10 +29352,10 @@
         <v>0.01446532029630916</v>
       </c>
       <c r="H557">
-        <v>0.01418652147410457</v>
+        <v>0.01454561364589741</v>
       </c>
       <c r="I557">
-        <v>0.9187988222045833</v>
+        <v>1.139706650411748</v>
       </c>
       <c r="J557">
         <v>2.303072393094552</v>
@@ -29367,10 +29367,10 @@
         <v>5.23</v>
       </c>
       <c r="M557">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N557">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O557">
         <v>1</v>
@@ -29393,7 +29393,7 @@
         <v>160</v>
       </c>
       <c r="E558">
-        <v>-2.96934700259968</v>
+        <v>-2.747501778620478</v>
       </c>
       <c r="F558">
         <v>1</v>
@@ -29402,10 +29402,10 @@
         <v>0.01434002172811326</v>
       </c>
       <c r="H558">
-        <v>0.01406934700259968</v>
+        <v>0.01442750177862048</v>
       </c>
       <c r="I558">
-        <v>0.9106747255135774</v>
+        <v>1.13251994949278</v>
       </c>
       <c r="J558">
         <v>2.271825867359915</v>
@@ -29417,10 +29417,10 @@
         <v>5.23</v>
       </c>
       <c r="M558">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N558">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O558">
         <v>1</v>
@@ -29443,7 +29443,7 @@
         <v>160</v>
       </c>
       <c r="E559">
-        <v>-2.862594148159894</v>
+        <v>-2.639894901345173</v>
       </c>
       <c r="F559">
         <v>1</v>
@@ -29452,10 +29452,10 @@
         <v>0.01422586734243231</v>
       </c>
       <c r="H559">
-        <v>0.01396259414815989</v>
+        <v>0.01431989490134517</v>
       </c>
       <c r="I559">
-        <v>0.9032731942724181</v>
+        <v>1.125972441087139</v>
       </c>
       <c r="J559">
         <v>2.243358439509305</v>
@@ -29467,10 +29467,10 @@
         <v>5.23</v>
       </c>
       <c r="M559">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N559">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O559">
         <v>1</v>
@@ -29493,7 +29493,7 @@
         <v>160</v>
       </c>
       <c r="E560">
-        <v>-2.333824022393905</v>
+        <v>-2.106894614573056</v>
       </c>
       <c r="F560">
         <v>1</v>
@@ -29502,10 +29502,10 @@
         <v>0.01366043582127988</v>
       </c>
       <c r="H560">
-        <v>0.0134338240223939</v>
+        <v>0.01378689461457306</v>
       </c>
       <c r="I560">
-        <v>0.8666117988859767</v>
+        <v>1.093541206706826</v>
       </c>
       <c r="J560">
         <v>2.102353072638375</v>
@@ -29517,10 +29517,10 @@
         <v>5.23</v>
       </c>
       <c r="M560">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N560">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O560">
         <v>1</v>
@@ -29543,7 +29543,7 @@
         <v>160</v>
       </c>
       <c r="E561">
-        <v>-1.73713020332095</v>
+        <v>-1.505427244947517</v>
       </c>
       <c r="F561">
         <v>1</v>
@@ -29552,10 +29552,10 @@
         <v>0.0130223712307512</v>
       </c>
       <c r="H561">
-        <v>0.01283713020332095</v>
+        <v>0.01318542724494752</v>
       </c>
       <c r="I561">
-        <v>0.825241027430252</v>
+        <v>1.056943985803684</v>
       </c>
       <c r="J561">
         <v>1.943234720885587</v>
@@ -29567,10 +29567,10 @@
         <v>5.23</v>
       </c>
       <c r="M561">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N561">
-        <v>5.55</v>
+        <v>5.84</v>
       </c>
       <c r="O561">
         <v>1</v>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="387">
   <si>
     <t>trade_time</t>
   </si>
@@ -497,6 +497,9 @@
   </si>
   <si>
     <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-02</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -1626,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1676,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1726,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1776,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1826,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1876,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1926,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1976,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2026,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2076,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2126,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2176,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2226,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2276,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2326,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2376,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2426,7 +2429,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2476,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2526,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2576,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2626,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2676,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2726,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2776,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2826,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2876,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2926,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2976,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3026,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3076,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3126,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3176,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3226,7 +3229,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3276,7 +3279,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3326,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3376,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3426,7 +3429,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3476,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3526,7 +3529,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3576,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3626,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3676,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3726,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3776,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3826,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3876,7 +3879,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3926,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3976,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4026,7 +4029,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4076,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4126,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4176,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4226,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4276,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4326,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4376,7 +4379,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4426,7 +4429,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4476,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4526,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4576,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4626,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4676,7 +4679,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4726,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4776,7 +4779,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4826,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4876,7 +4879,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4926,7 +4929,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4976,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5026,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5076,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5126,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5176,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5226,7 +5229,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5276,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5326,7 +5329,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5376,7 +5379,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5426,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5476,7 +5479,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5526,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5576,7 +5579,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5626,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5676,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5726,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5776,7 +5779,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5826,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5876,7 +5879,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5926,7 +5929,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5976,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6026,7 +6029,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6076,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6126,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6176,7 +6179,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6226,7 +6229,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6276,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6326,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6376,7 +6379,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6426,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6476,7 +6479,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6526,7 +6529,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6576,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6626,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6676,7 +6679,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6726,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6776,7 +6779,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6826,7 +6829,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6876,7 +6879,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6926,7 +6929,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6976,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7026,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7076,7 +7079,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7126,7 +7129,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7176,7 +7179,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7226,7 +7229,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7276,7 +7279,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7326,7 +7329,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7376,7 +7379,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7426,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7476,7 +7479,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7526,7 +7529,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7576,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7626,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7676,7 +7679,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7726,7 +7729,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7776,7 +7779,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7826,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7876,7 +7879,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7926,7 +7929,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7976,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8026,7 +8029,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8076,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8126,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8176,7 +8179,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8226,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8276,7 +8279,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8326,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8376,7 +8379,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8426,7 +8429,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8476,7 +8479,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8526,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8626,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8676,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8726,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8776,7 +8779,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8826,7 +8829,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8876,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8926,7 +8929,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8976,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9026,7 +9029,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9076,7 +9079,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9126,7 +9129,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9176,7 +9179,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9226,7 +9229,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9276,7 +9279,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9326,7 +9329,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9376,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9426,7 +9429,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9476,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9526,7 +9529,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9576,7 +9579,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9676,7 +9679,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9726,7 +9729,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9776,7 +9779,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9926,7 +9929,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9976,7 +9979,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10026,7 +10029,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10076,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10126,7 +10129,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10176,7 +10179,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10226,7 +10229,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10276,7 +10279,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10376,7 +10379,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10426,7 +10429,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10576,7 +10579,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10626,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10676,7 +10679,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10726,7 +10729,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11226,7 +11229,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11276,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11326,7 +11329,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11376,7 +11379,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11426,7 +11429,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11476,7 +11479,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11526,7 +11529,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11576,7 +11579,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11626,7 +11629,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11676,7 +11679,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11726,7 +11729,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11776,7 +11779,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11826,7 +11829,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11876,7 +11879,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11926,7 +11929,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12726,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12776,7 +12779,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12826,7 +12829,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12876,7 +12879,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12926,7 +12929,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12976,7 +12979,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13026,7 +13029,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13076,7 +13079,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13126,7 +13129,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13176,7 +13179,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13226,7 +13229,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13276,7 +13279,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13326,7 +13329,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13376,7 +13379,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13426,7 +13429,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13476,7 +13479,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13526,7 +13529,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13576,7 +13579,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13626,7 +13629,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13676,7 +13679,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13826,7 +13829,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13876,7 +13879,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13926,7 +13929,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14026,7 +14029,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14176,7 +14179,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14226,7 +14229,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14276,7 +14279,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14326,7 +14329,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14376,7 +14379,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14426,7 +14429,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14476,7 +14479,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14576,7 +14579,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14626,7 +14629,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14676,7 +14679,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14726,7 +14729,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14776,7 +14779,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14826,7 +14829,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14876,7 +14879,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14926,7 +14929,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14976,7 +14979,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15026,7 +15029,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15076,7 +15079,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15126,7 +15129,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15176,7 +15179,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15226,7 +15229,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15276,7 +15279,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15326,7 +15329,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15376,7 +15379,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15426,7 +15429,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15476,7 +15479,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15526,7 +15529,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15576,7 +15579,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15626,7 +15629,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15676,7 +15679,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15726,7 +15729,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15776,7 +15779,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15826,7 +15829,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15876,7 +15879,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15926,7 +15929,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15976,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16026,7 +16029,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16076,7 +16079,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16126,7 +16129,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16176,7 +16179,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16226,7 +16229,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16276,7 +16279,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16326,7 +16329,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16376,7 +16379,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16426,7 +16429,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16476,7 +16479,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16526,7 +16529,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16576,7 +16579,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16626,7 +16629,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16676,7 +16679,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16726,7 +16729,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16776,7 +16779,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16826,7 +16829,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16876,7 +16879,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16926,7 +16929,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17126,7 +17129,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17176,7 +17179,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17226,7 +17229,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17276,7 +17279,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17326,7 +17329,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17376,7 +17379,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17426,7 +17429,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17476,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17526,7 +17529,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17576,7 +17579,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17626,7 +17629,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17676,7 +17679,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17726,7 +17729,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17776,7 +17779,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17826,7 +17829,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17876,7 +17879,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17926,7 +17929,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17976,7 +17979,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18026,7 +18029,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18076,7 +18079,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18126,7 +18129,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18176,7 +18179,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18226,7 +18229,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18276,7 +18279,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18326,7 +18329,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18576,7 +18579,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18626,7 +18629,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18676,7 +18679,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18726,7 +18729,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18776,7 +18779,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18826,7 +18829,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18876,7 +18879,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18926,7 +18929,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18976,7 +18979,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19026,7 +19029,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19076,7 +19079,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19126,7 +19129,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19576,7 +19579,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19626,7 +19629,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19676,7 +19679,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19726,7 +19729,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19776,7 +19779,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19826,7 +19829,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19876,7 +19879,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19926,7 +19929,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19976,7 +19979,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20026,7 +20029,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20076,7 +20079,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20126,7 +20129,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20176,7 +20179,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20226,7 +20229,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20276,7 +20279,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20326,7 +20329,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20526,7 +20529,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20576,7 +20579,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20626,7 +20629,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20676,7 +20679,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20876,7 +20879,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20926,7 +20929,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20976,7 +20979,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21026,7 +21029,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21076,7 +21079,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21126,7 +21129,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21176,7 +21179,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21226,7 +21229,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21276,7 +21279,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21326,7 +21329,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21376,7 +21379,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21426,7 +21429,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21476,7 +21479,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21526,7 +21529,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21576,7 +21579,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21626,7 +21629,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21676,7 +21679,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21726,7 +21729,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21776,7 +21779,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21826,7 +21829,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21876,7 +21879,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21926,7 +21929,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21976,7 +21979,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22026,7 +22029,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22076,7 +22079,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22126,7 +22129,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22176,7 +22179,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22226,7 +22229,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22276,7 +22279,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22326,7 +22329,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22376,7 +22379,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22426,7 +22429,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22476,7 +22479,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22676,7 +22679,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22726,7 +22729,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22776,7 +22779,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22826,7 +22829,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22876,7 +22879,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22926,7 +22929,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23126,7 +23129,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23176,7 +23179,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23226,7 +23229,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23276,7 +23279,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23326,7 +23329,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23376,7 +23379,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23426,7 +23429,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23476,7 +23479,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23526,7 +23529,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23576,7 +23579,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23626,7 +23629,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23676,7 +23679,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23726,7 +23729,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23776,7 +23779,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23826,7 +23829,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23876,7 +23879,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23926,7 +23929,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23976,7 +23979,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24026,7 +24029,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24076,7 +24079,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24126,7 +24129,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24176,7 +24179,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24226,7 +24229,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24276,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24326,7 +24329,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24376,7 +24379,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24426,7 +24429,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24476,7 +24479,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24526,7 +24529,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24576,7 +24579,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24626,7 +24629,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24676,7 +24679,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24726,7 +24729,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24776,7 +24779,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24826,7 +24829,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24876,7 +24879,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24926,7 +24929,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24976,7 +24979,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25026,7 +25029,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25076,7 +25079,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25126,7 +25129,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25176,7 +25179,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25476,7 +25479,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25526,7 +25529,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25576,7 +25579,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25626,7 +25629,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25676,7 +25679,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25726,7 +25729,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25776,7 +25779,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25826,7 +25829,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25876,7 +25879,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25926,7 +25929,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25976,7 +25979,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26026,7 +26029,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26076,7 +26079,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26126,7 +26129,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26176,7 +26179,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26226,7 +26229,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26276,7 +26279,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26326,7 +26329,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26376,7 +26379,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26426,7 +26429,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26476,7 +26479,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26526,7 +26529,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26576,7 +26579,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26626,7 +26629,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26676,7 +26679,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26726,7 +26729,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26776,7 +26779,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26826,7 +26829,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26876,7 +26879,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26926,7 +26929,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26976,7 +26979,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27026,7 +27029,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27076,7 +27079,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27126,7 +27129,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27176,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27226,7 +27229,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27276,7 +27279,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27326,7 +27329,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27376,7 +27379,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27426,7 +27429,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27476,7 +27479,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27526,7 +27529,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27576,7 +27579,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27626,7 +27629,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27676,7 +27679,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27726,7 +27729,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27776,7 +27779,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27826,7 +27829,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27876,7 +27879,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27890,10 +27893,10 @@
         <v>-2.39134798609852</v>
       </c>
       <c r="D528" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E528">
-        <v>-1.344213313579155</v>
+        <v>-1.41041239469474</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27902,10 +27905,10 @@
         <v>0.01285134798609852</v>
       </c>
       <c r="H528">
-        <v>0.01302421331357915</v>
+        <v>0.01425041239469474</v>
       </c>
       <c r="I528">
-        <v>1.047134672519365</v>
+        <v>0.9809355914037798</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27917,16 +27920,16 @@
         <v>5.23</v>
       </c>
       <c r="M528">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N528">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O528">
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27940,10 +27943,10 @@
         <v>-2.546512840679558</v>
       </c>
       <c r="D529" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E529">
-        <v>-1.490478438346317</v>
+        <v>-1.569833641795458</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27952,10 +27955,10 @@
         <v>0.01300651284067956</v>
       </c>
       <c r="H529">
-        <v>0.01317047843834632</v>
+        <v>0.01440983364179546</v>
       </c>
       <c r="I529">
-        <v>1.056034402333241</v>
+        <v>0.9766791988841002</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27967,16 +27970,16 @@
         <v>5.23</v>
       </c>
       <c r="M529">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N529">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O529">
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27990,10 +27993,10 @@
         <v>-2.943692670373876</v>
       </c>
       <c r="D530" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E530">
-        <v>-1.86487738005318</v>
+        <v>-1.977908678788124</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28002,10 +28005,10 @@
         <v>0.01340369267037388</v>
       </c>
       <c r="H530">
-        <v>0.01354487738005318</v>
+        <v>0.01481790867878812</v>
       </c>
       <c r="I530">
-        <v>1.078815290320696</v>
+        <v>0.9657839915857522</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28017,16 +28020,16 @@
         <v>5.23</v>
       </c>
       <c r="M530">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N530">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O530">
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28040,10 +28043,10 @@
         <v>-2.466410474021997</v>
       </c>
       <c r="D531" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E531">
-        <v>-1.86487738005318</v>
+        <v>-1.977908678788124</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28052,10 +28055,10 @@
         <v>0.013106410474022</v>
       </c>
       <c r="H531">
-        <v>0.01354487738005318</v>
+        <v>0.01481790867878812</v>
       </c>
       <c r="I531">
-        <v>0.6015330939688166</v>
+        <v>0.4885017952338728</v>
       </c>
       <c r="J531">
         <v>2.038327349220418</v>
@@ -28067,16 +28070,16 @@
         <v>5.32</v>
       </c>
       <c r="M531">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N531">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O531">
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28090,10 +28093,10 @@
         <v>-3.302184308580614</v>
       </c>
       <c r="D532" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E532">
-        <v>-2.20280715372437</v>
+        <v>-2.346234252207514</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28102,10 +28105,10 @@
         <v>0.01376218430858061</v>
       </c>
       <c r="H532">
-        <v>0.01388280715372437</v>
+        <v>0.01518623425220752</v>
       </c>
       <c r="I532">
-        <v>1.099377154856244</v>
+        <v>0.9559500563730996</v>
       </c>
       <c r="J532">
         <v>2.127726760244542</v>
@@ -28117,16 +28120,16 @@
         <v>5.23</v>
       </c>
       <c r="M532">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N532">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O532">
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28140,10 +28143,10 @@
         <v>-2.807916224134152</v>
       </c>
       <c r="D533" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E533">
-        <v>-2.20280715372437</v>
+        <v>-2.346234252207514</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28152,10 +28155,10 @@
         <v>0.01344791622413415</v>
       </c>
       <c r="H533">
-        <v>0.01388280715372437</v>
+        <v>0.01518623425220752</v>
       </c>
       <c r="I533">
-        <v>0.6051090704097817</v>
+        <v>0.4616819719266374</v>
       </c>
       <c r="J533">
         <v>2.127726760244542</v>
@@ -28167,16 +28170,16 @@
         <v>5.32</v>
       </c>
       <c r="M533">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N533">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28190,10 +28193,10 @@
         <v>-3.440693413369869</v>
       </c>
       <c r="D534" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E534">
-        <v>-2.333371846019478</v>
+        <v>-2.488542858624404</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28202,10 +28205,10 @@
         <v>0.01390069341336987</v>
       </c>
       <c r="H534">
-        <v>0.01401337184601948</v>
+        <v>0.0153285428586244</v>
       </c>
       <c r="I534">
-        <v>1.107321567350391</v>
+        <v>0.9521505547454652</v>
       </c>
       <c r="J534">
         <v>2.162267684132137</v>
@@ -28217,16 +28220,16 @@
         <v>5.23</v>
       </c>
       <c r="M534">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N534">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O534">
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28240,10 +28243,10 @@
         <v>-2.939862553384764</v>
       </c>
       <c r="D535" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E535">
-        <v>-2.333371846019478</v>
+        <v>-2.488542858624404</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28252,10 +28255,10 @@
         <v>0.01357986255338476</v>
       </c>
       <c r="H535">
-        <v>0.01401337184601948</v>
+        <v>0.0153285428586244</v>
       </c>
       <c r="I535">
-        <v>0.6064907073652854</v>
+        <v>0.4513196947603593</v>
       </c>
       <c r="J535">
         <v>2.162267684132137</v>
@@ -28267,16 +28270,16 @@
         <v>5.32</v>
       </c>
       <c r="M535">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N535">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28290,10 +28293,10 @@
         <v>-3.668901415448289</v>
       </c>
       <c r="D536" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E536">
-        <v>-2.548490611070957</v>
+        <v>-2.723010930585275</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28302,10 +28305,10 @@
         <v>0.01412890141544829</v>
       </c>
       <c r="H536">
-        <v>0.01422849061107096</v>
+        <v>0.01556301093058528</v>
       </c>
       <c r="I536">
-        <v>1.120410804377332</v>
+        <v>0.9458904848630141</v>
       </c>
       <c r="J536">
         <v>2.219177410336232</v>
@@ -28317,16 +28320,16 @@
         <v>5.23</v>
       </c>
       <c r="M536">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N536">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O536">
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28340,10 +28343,10 @@
         <v>-3.157257707484405</v>
       </c>
       <c r="D537" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E537">
-        <v>-2.548490611070957</v>
+        <v>-2.723010930585275</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28352,10 +28355,10 @@
         <v>0.01379725770748441</v>
       </c>
       <c r="H537">
-        <v>0.01422849061107096</v>
+        <v>0.01556301093058528</v>
       </c>
       <c r="I537">
-        <v>0.6087670964134482</v>
+        <v>0.4342467768991298</v>
       </c>
       <c r="J537">
         <v>2.219177410336232</v>
@@ -28367,16 +28370,16 @@
         <v>5.32</v>
       </c>
       <c r="M537">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N537">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O537">
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28390,10 +28393,10 @@
         <v>-3.954888865249114</v>
       </c>
       <c r="D538" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E538">
-        <v>-2.818074790683704</v>
+        <v>-3.016843422649965</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28402,10 +28405,10 @@
         <v>0.01441488886524911</v>
       </c>
       <c r="H538">
-        <v>0.0144980747906837</v>
+        <v>0.01585684342264997</v>
       </c>
       <c r="I538">
-        <v>1.136814074565409</v>
+        <v>0.9380454425991491</v>
       </c>
       <c r="J538">
         <v>2.29049597637135</v>
@@ -28417,16 +28420,16 @@
         <v>5.23</v>
       </c>
       <c r="M538">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N538">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28440,10 +28443,10 @@
         <v>-3.429694629738558</v>
       </c>
       <c r="D539" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E539">
-        <v>-2.818074790683704</v>
+        <v>-3.016843422649965</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28452,10 +28455,10 @@
         <v>0.01406969462973856</v>
       </c>
       <c r="H539">
-        <v>0.0144980747906837</v>
+        <v>0.01585684342264997</v>
       </c>
       <c r="I539">
-        <v>0.6116198390548533</v>
+        <v>0.4128512070885932</v>
       </c>
       <c r="J539">
         <v>2.29049597637135</v>
@@ -28467,16 +28470,16 @@
         <v>5.32</v>
       </c>
       <c r="M539">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N539">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28490,10 +28493,10 @@
         <v>-4.162550774568617</v>
       </c>
       <c r="D540" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E540">
-        <v>-3.013825917174408</v>
+        <v>-3.230201793322371</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28502,10 +28505,10 @@
         <v>0.01462255077456862</v>
       </c>
       <c r="H540">
-        <v>0.01469382591717441</v>
+        <v>0.01607020179332237</v>
       </c>
       <c r="I540">
-        <v>1.148724857394209</v>
+        <v>0.9323489812462462</v>
       </c>
       <c r="J540">
         <v>2.342281988670478</v>
@@ -28517,16 +28520,16 @@
         <v>5.23</v>
       </c>
       <c r="M540">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N540">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O540">
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28540,10 +28543,10 @@
         <v>-3.627517196721227</v>
       </c>
       <c r="D541" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E541">
-        <v>-3.013825917174408</v>
+        <v>-3.230201793322371</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28552,10 +28555,10 @@
         <v>0.01426751719672123</v>
       </c>
       <c r="H541">
-        <v>0.01469382591717441</v>
+        <v>0.01607020179332237</v>
       </c>
       <c r="I541">
-        <v>0.6136912795468188</v>
+        <v>0.3973154033988564</v>
       </c>
       <c r="J541">
         <v>2.342281988670478</v>
@@ -28567,16 +28570,16 @@
         <v>5.32</v>
       </c>
       <c r="M541">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N541">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28590,10 +28593,10 @@
         <v>-4.341021841271511</v>
       </c>
       <c r="D542" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E542">
-        <v>-3.18206048877963</v>
+        <v>-3.413568575071977</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28602,10 +28605,10 @@
         <v>0.01480102184127151</v>
       </c>
       <c r="H542">
-        <v>0.01486206048877963</v>
+        <v>0.01625356857507198</v>
       </c>
       <c r="I542">
-        <v>1.158961352491881</v>
+        <v>0.9274532661995334</v>
       </c>
       <c r="J542">
         <v>2.38678848909514</v>
@@ -28617,16 +28620,16 @@
         <v>5.23</v>
       </c>
       <c r="M542">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N542">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28640,10 +28643,10 @@
         <v>-3.797532028343435</v>
       </c>
       <c r="D543" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E543">
-        <v>-3.18206048877963</v>
+        <v>-3.413568575071977</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28652,10 +28655,10 @@
         <v>0.01443753202834343</v>
       </c>
       <c r="H543">
-        <v>0.01486206048877963</v>
+        <v>0.01625356857507198</v>
       </c>
       <c r="I543">
-        <v>0.6154715395638046</v>
+        <v>0.3839634532714573</v>
       </c>
       <c r="J543">
         <v>2.38678848909514</v>
@@ -28667,16 +28670,16 @@
         <v>5.32</v>
       </c>
       <c r="M543">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N543">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28690,10 +28693,10 @@
         <v>-4.38270256915019</v>
       </c>
       <c r="D544" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E544">
-        <v>-3.221350551468261</v>
+        <v>-3.456392664563289</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28702,10 +28705,10 @@
         <v>0.01484270256915019</v>
       </c>
       <c r="H544">
-        <v>0.01490135055146826</v>
+        <v>0.01629639266456329</v>
       </c>
       <c r="I544">
-        <v>1.16135201768193</v>
+        <v>0.9263099045869012</v>
       </c>
       <c r="J544">
         <v>2.397182685573614</v>
@@ -28717,16 +28720,16 @@
         <v>5.23</v>
       </c>
       <c r="M544">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N544">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28740,10 +28743,10 @@
         <v>-3.837237858891204</v>
       </c>
       <c r="D545" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E545">
-        <v>-3.221350551468261</v>
+        <v>-3.456392664563289</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28752,10 +28755,10 @@
         <v>0.01447723785889121</v>
       </c>
       <c r="H545">
-        <v>0.01490135055146826</v>
+        <v>0.01629639266456329</v>
       </c>
       <c r="I545">
-        <v>0.615887307422943</v>
+        <v>0.3808451943279145</v>
       </c>
       <c r="J545">
         <v>2.397182685573614</v>
@@ -28767,16 +28770,16 @@
         <v>5.32</v>
       </c>
       <c r="M545">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N545">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28790,10 +28793,10 @@
         <v>-4.411855003341485</v>
       </c>
       <c r="D546" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E546">
-        <v>-3.248830900905441</v>
+        <v>-3.486344791463074</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28802,10 +28805,10 @@
         <v>0.01487185500334148</v>
       </c>
       <c r="H546">
-        <v>0.01492883090090544</v>
+        <v>0.01632634479146307</v>
       </c>
       <c r="I546">
-        <v>1.163024102436044</v>
+        <v>0.9255102118784109</v>
       </c>
       <c r="J546">
         <v>2.404452619287154</v>
@@ -28817,16 +28820,16 @@
         <v>5.23</v>
       </c>
       <c r="M546">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N546">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28840,10 +28843,10 @@
         <v>-3.865009005676926</v>
       </c>
       <c r="D547" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E547">
-        <v>-3.248830900905441</v>
+        <v>-3.486344791463074</v>
       </c>
       <c r="F547">
         <v>1</v>
@@ -28852,10 +28855,10 @@
         <v>0.01450500900567693</v>
       </c>
       <c r="H547">
-        <v>0.01492883090090544</v>
+        <v>0.01632634479146307</v>
       </c>
       <c r="I547">
-        <v>0.6161781047714854</v>
+        <v>0.3786642142138525</v>
       </c>
       <c r="J547">
         <v>2.404452619287154</v>
@@ -28867,16 +28870,16 @@
         <v>5.32</v>
       </c>
       <c r="M547">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N547">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28890,10 +28893,10 @@
         <v>-4.339272485484365</v>
       </c>
       <c r="D548" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E548">
-        <v>-3.180411470107456</v>
+        <v>-3.411771231968975</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28902,10 +28905,10 @@
         <v>0.01479927248548437</v>
       </c>
       <c r="H548">
-        <v>0.01486041147010746</v>
+        <v>0.01625177123196897</v>
       </c>
       <c r="I548">
-        <v>1.158861015376909</v>
+        <v>0.9275012535153895</v>
       </c>
       <c r="J548">
         <v>2.386352240769169</v>
@@ -28917,16 +28920,16 @@
         <v>5.23</v>
       </c>
       <c r="M548">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N548">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28940,10 +28943,10 @@
         <v>-3.795865559738223</v>
       </c>
       <c r="D549" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E549">
-        <v>-3.180411470107456</v>
+        <v>-3.411771231968975</v>
       </c>
       <c r="F549">
         <v>1</v>
@@ -28952,10 +28955,10 @@
         <v>0.01443586555973822</v>
       </c>
       <c r="H549">
-        <v>0.01486041147010746</v>
+        <v>0.01625177123196897</v>
       </c>
       <c r="I549">
-        <v>0.6154540896307665</v>
+        <v>0.3840943277692475</v>
       </c>
       <c r="J549">
         <v>2.386352240769169</v>
@@ -28967,16 +28970,16 @@
         <v>5.32</v>
       </c>
       <c r="M549">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N549">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O549">
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28990,10 +28993,10 @@
         <v>-4.278315541383607</v>
       </c>
       <c r="D550" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E550">
-        <v>-3.12295080958355</v>
+        <v>-3.349142152244506</v>
       </c>
       <c r="F550">
         <v>1</v>
@@ -29002,10 +29005,10 @@
         <v>0.01473831554138361</v>
       </c>
       <c r="H550">
-        <v>0.01480295080958355</v>
+        <v>0.01618914215224451</v>
       </c>
       <c r="I550">
-        <v>1.155364731800057</v>
+        <v>0.9291733891391019</v>
       </c>
       <c r="J550">
         <v>2.371151007826336</v>
@@ -29017,16 +29020,16 @@
         <v>5.23</v>
       </c>
       <c r="M550">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N550">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29040,10 +29043,10 @@
         <v>-3.737796849896604</v>
       </c>
       <c r="D551" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E551">
-        <v>-3.12295080958355</v>
+        <v>-3.349142152244506</v>
       </c>
       <c r="F551">
         <v>1</v>
@@ -29052,10 +29055,10 @@
         <v>0.0143777968498966</v>
       </c>
       <c r="H551">
-        <v>0.01480295080958355</v>
+        <v>0.01618914215224451</v>
       </c>
       <c r="I551">
-        <v>0.6148460403130542</v>
+        <v>0.3886546976520986</v>
       </c>
       <c r="J551">
         <v>2.371151007826336</v>
@@ -29067,16 +29070,16 @@
         <v>5.32</v>
       </c>
       <c r="M551">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N551">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29090,10 +29093,10 @@
         <v>-4.215673134172834</v>
       </c>
       <c r="D552" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E552">
-        <v>-3.063901358397336</v>
+        <v>-3.284781374761117</v>
       </c>
       <c r="F552">
         <v>1</v>
@@ -29102,10 +29105,10 @@
         <v>0.01467567313417283</v>
       </c>
       <c r="H552">
-        <v>0.01474390135839734</v>
+        <v>0.01612478137476112</v>
       </c>
       <c r="I552">
-        <v>1.151771775775497</v>
+        <v>0.9308917594117165</v>
       </c>
       <c r="J552">
         <v>2.355529459893475</v>
@@ -29117,16 +29120,16 @@
         <v>5.23</v>
       </c>
       <c r="M552">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N552">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O552">
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29140,10 +29143,10 @@
         <v>-3.678122536793074</v>
       </c>
       <c r="D553" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E553">
-        <v>-3.063901358397336</v>
+        <v>-3.284781374761117</v>
       </c>
       <c r="F553">
         <v>1</v>
@@ -29152,10 +29155,10 @@
         <v>0.01431812253679307</v>
       </c>
       <c r="H553">
-        <v>0.01474390135839734</v>
+        <v>0.01612478137476112</v>
       </c>
       <c r="I553">
-        <v>0.6142211783957379</v>
+        <v>0.3933411620319571</v>
       </c>
       <c r="J553">
         <v>2.355529459893475</v>
@@ -29167,16 +29170,16 @@
         <v>5.32</v>
       </c>
       <c r="M553">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N553">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O553">
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29190,10 +29193,10 @@
         <v>-4.189835924124937</v>
       </c>
       <c r="D554" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E554">
-        <v>-3.039546083090341</v>
+        <v>-3.258235413315399</v>
       </c>
       <c r="F554">
         <v>1</v>
@@ -29202,10 +29205,10 @@
         <v>0.01464983592412494</v>
       </c>
       <c r="H554">
-        <v>0.01471954608309034</v>
+        <v>0.0160982354133154</v>
       </c>
       <c r="I554">
-        <v>1.150289841034596</v>
+        <v>0.9316005108095382</v>
       </c>
       <c r="J554">
         <v>2.349086265367815</v>
@@ -29217,16 +29220,16 @@
         <v>5.23</v>
       </c>
       <c r="M554">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N554">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O554">
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29240,10 +29243,10 @@
         <v>-3.653509533705053</v>
       </c>
       <c r="D555" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E555">
-        <v>-3.039546083090341</v>
+        <v>-3.258235413315399</v>
       </c>
       <c r="F555">
         <v>1</v>
@@ -29252,10 +29255,10 @@
         <v>0.01429350953370505</v>
       </c>
       <c r="H555">
-        <v>0.01471954608309034</v>
+        <v>0.0160982354133154</v>
       </c>
       <c r="I555">
-        <v>0.6139634506147118</v>
+        <v>0.3952741203896544</v>
       </c>
       <c r="J555">
         <v>2.349086265367815</v>
@@ -29267,16 +29270,16 @@
         <v>5.32</v>
       </c>
       <c r="M555">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N555">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O555">
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29290,10 +29293,10 @@
         <v>-4.089470803698397</v>
       </c>
       <c r="D556" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E556">
-        <v>-2.944937565581034</v>
+        <v>-3.15511713497192</v>
       </c>
       <c r="F556">
         <v>1</v>
@@ -29302,10 +29305,10 @@
         <v>0.0145494708036984</v>
       </c>
       <c r="H556">
-        <v>0.01462493756558103</v>
+        <v>0.01599511713497192</v>
       </c>
       <c r="I556">
-        <v>1.144533238117363</v>
+        <v>0.9343536687264766</v>
       </c>
       <c r="J556">
         <v>2.324057557032019</v>
@@ -29317,16 +29320,16 @@
         <v>5.23</v>
       </c>
       <c r="M556">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N556">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O556">
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29340,10 +29343,10 @@
         <v>-4.005320296309154</v>
       </c>
       <c r="D557" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E557">
-        <v>-2.865613645897406</v>
+        <v>-3.068658259549556</v>
       </c>
       <c r="F557">
         <v>1</v>
@@ -29352,10 +29355,10 @@
         <v>0.01446532029630916</v>
       </c>
       <c r="H557">
-        <v>0.01454561364589741</v>
+        <v>0.01590865825954956</v>
       </c>
       <c r="I557">
-        <v>1.139706650411748</v>
+        <v>0.9366620367595981</v>
       </c>
       <c r="J557">
         <v>2.303072393094552</v>
@@ -29367,16 +29370,16 @@
         <v>5.23</v>
       </c>
       <c r="M557">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N557">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O557">
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29390,10 +29393,10 @@
         <v>-3.880021728113258</v>
       </c>
       <c r="D558" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E558">
-        <v>-2.747501778620478</v>
+        <v>-2.93992257352285</v>
       </c>
       <c r="F558">
         <v>1</v>
@@ -29402,10 +29405,10 @@
         <v>0.01434002172811326</v>
       </c>
       <c r="H558">
-        <v>0.01442750177862048</v>
+        <v>0.01577992257352285</v>
       </c>
       <c r="I558">
-        <v>1.13251994949278</v>
+        <v>0.940099154590408</v>
       </c>
       <c r="J558">
         <v>2.271825867359915</v>
@@ -29417,16 +29420,16 @@
         <v>5.23</v>
       </c>
       <c r="M558">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N558">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O558">
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29440,10 +29443,10 @@
         <v>-3.765867342432312</v>
       </c>
       <c r="D559" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E559">
-        <v>-2.639894901345173</v>
+        <v>-2.822636770778338</v>
       </c>
       <c r="F559">
         <v>1</v>
@@ -29452,10 +29455,10 @@
         <v>0.01422586734243231</v>
       </c>
       <c r="H559">
-        <v>0.01431989490134517</v>
+        <v>0.01566263677077834</v>
       </c>
       <c r="I559">
-        <v>1.125972441087139</v>
+        <v>0.9432305716539737</v>
       </c>
       <c r="J559">
         <v>2.243358439509305</v>
@@ -29467,16 +29470,16 @@
         <v>5.23</v>
       </c>
       <c r="M559">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N559">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O559">
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29490,10 +29493,10 @@
         <v>-3.200435821279882</v>
       </c>
       <c r="D560" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E560">
-        <v>-2.106894614573056</v>
+        <v>-2.241694659270104</v>
       </c>
       <c r="F560">
         <v>1</v>
@@ -29502,10 +29505,10 @@
         <v>0.01366043582127988</v>
       </c>
       <c r="H560">
-        <v>0.01378689461457306</v>
+        <v>0.01508169465927011</v>
       </c>
       <c r="I560">
-        <v>1.093541206706826</v>
+        <v>0.9587411620097779</v>
       </c>
       <c r="J560">
         <v>2.102353072638375</v>
@@ -29517,16 +29520,16 @@
         <v>5.23</v>
       </c>
       <c r="M560">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N560">
-        <v>5.84</v>
+        <v>6.42</v>
       </c>
       <c r="O560">
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29576,7 +29579,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="387">
   <si>
     <t>trade_time</t>
   </si>
@@ -499,7 +499,7 @@
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-09-02</t>
+    <t>2021-09-06</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -1532,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P561"/>
+  <dimension ref="A1:P557"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -27896,7 +27896,7 @@
         <v>161</v>
       </c>
       <c r="E528">
-        <v>-1.41041239469474</v>
+        <v>-1.165617331137254</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27905,10 +27905,10 @@
         <v>0.01285134798609852</v>
       </c>
       <c r="H528">
-        <v>0.01425041239469474</v>
+        <v>0.01582561733113725</v>
       </c>
       <c r="I528">
-        <v>0.9809355914037798</v>
+        <v>1.225730654961266</v>
       </c>
       <c r="J528">
         <v>1.900585532692898</v>
@@ -27920,10 +27920,10 @@
         <v>5.23</v>
       </c>
       <c r="M528">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N528">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27946,7 +27946,7 @@
         <v>161</v>
       </c>
       <c r="E529">
-        <v>-1.569833641795458</v>
+        <v>-1.338581645346041</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27955,10 +27955,10 @@
         <v>0.01300651284067956</v>
       </c>
       <c r="H529">
-        <v>0.01440983364179546</v>
+        <v>0.01599858164534604</v>
       </c>
       <c r="I529">
-        <v>0.9766791988841002</v>
+        <v>1.207931195333517</v>
       </c>
       <c r="J529">
         <v>1.939280010144528</v>
@@ -27970,10 +27970,10 @@
         <v>5.23</v>
       </c>
       <c r="M529">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N529">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -27996,7 +27996,7 @@
         <v>161</v>
       </c>
       <c r="E530">
-        <v>-1.977908678788124</v>
+        <v>-1.781323251015268</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28005,10 +28005,10 @@
         <v>0.01340369267037388</v>
       </c>
       <c r="H530">
-        <v>0.01481790867878812</v>
+        <v>0.01644132325101527</v>
       </c>
       <c r="I530">
-        <v>0.9657839915857522</v>
+        <v>1.162369419358608</v>
       </c>
       <c r="J530">
         <v>2.038327349220418</v>
@@ -28020,10 +28020,10 @@
         <v>5.23</v>
       </c>
       <c r="M530">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N530">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28046,7 +28046,7 @@
         <v>161</v>
       </c>
       <c r="E531">
-        <v>-1.977908678788124</v>
+        <v>-1.781323251015268</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28055,10 +28055,10 @@
         <v>0.013106410474022</v>
       </c>
       <c r="H531">
-        <v>0.01481790867878812</v>
+        <v>0.01644132325101527</v>
       </c>
       <c r="I531">
-        <v>0.4885017952338728</v>
+        <v>0.6850872230067289</v>
       </c>
       <c r="J531">
         <v>2.038327349220418</v>
@@ -28070,10 +28070,10 @@
         <v>5.32</v>
       </c>
       <c r="M531">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N531">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28096,7 +28096,7 @@
         <v>161</v>
       </c>
       <c r="E532">
-        <v>-2.346234252207514</v>
+        <v>-2.180938618293103</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28105,10 +28105,10 @@
         <v>0.01376218430858061</v>
       </c>
       <c r="H532">
-        <v>0.01518623425220752</v>
+        <v>0.0168409386182931</v>
       </c>
       <c r="I532">
-        <v>0.9559500563730996</v>
+        <v>1.121245690287511</v>
       </c>
       <c r="J532">
         <v>2.127726760244542</v>
@@ -28120,10 +28120,10 @@
         <v>5.23</v>
       </c>
       <c r="M532">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N532">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O532">
         <v>1</v>
@@ -28146,7 +28146,7 @@
         <v>161</v>
       </c>
       <c r="E533">
-        <v>-2.346234252207514</v>
+        <v>-2.180938618293103</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28155,10 +28155,10 @@
         <v>0.01344791622413415</v>
       </c>
       <c r="H533">
-        <v>0.01518623425220752</v>
+        <v>0.0168409386182931</v>
       </c>
       <c r="I533">
-        <v>0.4616819719266374</v>
+        <v>0.6269776058410486</v>
       </c>
       <c r="J533">
         <v>2.127726760244542</v>
@@ -28170,10 +28170,10 @@
         <v>5.32</v>
       </c>
       <c r="M533">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N533">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28196,7 +28196,7 @@
         <v>161</v>
       </c>
       <c r="E534">
-        <v>-2.488542858624404</v>
+        <v>-2.335336548070652</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28205,10 +28205,10 @@
         <v>0.01390069341336987</v>
       </c>
       <c r="H534">
-        <v>0.0153285428586244</v>
+        <v>0.01699533654807065</v>
       </c>
       <c r="I534">
-        <v>0.9521505547454652</v>
+        <v>1.105356865299218</v>
       </c>
       <c r="J534">
         <v>2.162267684132137</v>
@@ -28220,10 +28220,10 @@
         <v>5.23</v>
       </c>
       <c r="M534">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N534">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28246,7 +28246,7 @@
         <v>161</v>
       </c>
       <c r="E535">
-        <v>-2.488542858624404</v>
+        <v>-2.335336548070652</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28255,10 +28255,10 @@
         <v>0.01357986255338476</v>
       </c>
       <c r="H535">
-        <v>0.0153285428586244</v>
+        <v>0.01699533654807065</v>
       </c>
       <c r="I535">
-        <v>0.4513196947603593</v>
+        <v>0.6045260053141117</v>
       </c>
       <c r="J535">
         <v>2.162267684132137</v>
@@ -28270,10 +28270,10 @@
         <v>5.32</v>
       </c>
       <c r="M535">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N535">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28296,7 +28296,7 @@
         <v>161</v>
       </c>
       <c r="E536">
-        <v>-2.723010930585275</v>
+        <v>-2.589723024202955</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28305,10 +28305,10 @@
         <v>0.01412890141544829</v>
       </c>
       <c r="H536">
-        <v>0.01556301093058528</v>
+        <v>0.01724972302420296</v>
       </c>
       <c r="I536">
-        <v>0.9458904848630141</v>
+        <v>1.079178391245334</v>
       </c>
       <c r="J536">
         <v>2.219177410336232</v>
@@ -28320,10 +28320,10 @@
         <v>5.23</v>
       </c>
       <c r="M536">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N536">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28346,7 +28346,7 @@
         <v>161</v>
       </c>
       <c r="E537">
-        <v>-2.723010930585275</v>
+        <v>-2.589723024202955</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28355,10 +28355,10 @@
         <v>0.01379725770748441</v>
       </c>
       <c r="H537">
-        <v>0.01556301093058528</v>
+        <v>0.01724972302420296</v>
       </c>
       <c r="I537">
-        <v>0.4342467768991298</v>
+        <v>0.5675346832814494</v>
       </c>
       <c r="J537">
         <v>2.219177410336232</v>
@@ -28370,10 +28370,10 @@
         <v>5.32</v>
       </c>
       <c r="M537">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N537">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28396,7 +28396,7 @@
         <v>161</v>
       </c>
       <c r="E538">
-        <v>-3.016843422649965</v>
+        <v>-2.908517014379935</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28405,10 +28405,10 @@
         <v>0.01441488886524911</v>
       </c>
       <c r="H538">
-        <v>0.01585684342264997</v>
+        <v>0.01756851701437994</v>
       </c>
       <c r="I538">
-        <v>0.9380454425991491</v>
+        <v>1.046371850869178</v>
       </c>
       <c r="J538">
         <v>2.29049597637135</v>
@@ -28420,10 +28420,10 @@
         <v>5.23</v>
       </c>
       <c r="M538">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N538">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>161</v>
       </c>
       <c r="E539">
-        <v>-3.016843422649965</v>
+        <v>-2.908517014379935</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28455,10 +28455,10 @@
         <v>0.01406969462973856</v>
       </c>
       <c r="H539">
-        <v>0.01585684342264997</v>
+        <v>0.01756851701437994</v>
       </c>
       <c r="I539">
-        <v>0.4128512070885932</v>
+        <v>0.5211776153586225</v>
       </c>
       <c r="J539">
         <v>2.29049597637135</v>
@@ -28470,10 +28470,10 @@
         <v>5.32</v>
       </c>
       <c r="M539">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N539">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28496,7 +28496,7 @@
         <v>161</v>
       </c>
       <c r="E540">
-        <v>-3.230201793322371</v>
+        <v>-3.140000489357037</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28505,10 +28505,10 @@
         <v>0.01462255077456862</v>
       </c>
       <c r="H540">
-        <v>0.01607020179332237</v>
+        <v>0.01780000048935704</v>
       </c>
       <c r="I540">
-        <v>0.9323489812462462</v>
+        <v>1.02255028521158</v>
       </c>
       <c r="J540">
         <v>2.342281988670478</v>
@@ -28520,10 +28520,10 @@
         <v>5.23</v>
       </c>
       <c r="M540">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N540">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28546,7 +28546,7 @@
         <v>161</v>
       </c>
       <c r="E541">
-        <v>-3.230201793322371</v>
+        <v>-3.140000489357037</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28555,10 +28555,10 @@
         <v>0.01426751719672123</v>
       </c>
       <c r="H541">
-        <v>0.01607020179332237</v>
+        <v>0.01780000048935704</v>
       </c>
       <c r="I541">
-        <v>0.3973154033988564</v>
+        <v>0.4875167073641897</v>
       </c>
       <c r="J541">
         <v>2.342281988670478</v>
@@ -28570,10 +28570,10 @@
         <v>5.32</v>
       </c>
       <c r="M541">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N541">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28596,7 +28596,7 @@
         <v>161</v>
       </c>
       <c r="E542">
-        <v>-3.413568575071977</v>
+        <v>-3.338944546255275</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28605,10 +28605,10 @@
         <v>0.01480102184127151</v>
       </c>
       <c r="H542">
-        <v>0.01625356857507198</v>
+        <v>0.01799894454625527</v>
       </c>
       <c r="I542">
-        <v>0.9274532661995334</v>
+        <v>1.002077295016235</v>
       </c>
       <c r="J542">
         <v>2.38678848909514</v>
@@ -28620,10 +28620,10 @@
         <v>5.23</v>
       </c>
       <c r="M542">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N542">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28646,7 +28646,7 @@
         <v>161</v>
       </c>
       <c r="E543">
-        <v>-3.413568575071977</v>
+        <v>-3.338944546255275</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28655,10 +28655,10 @@
         <v>0.01443753202834343</v>
       </c>
       <c r="H543">
-        <v>0.01625356857507198</v>
+        <v>0.01799894454625527</v>
       </c>
       <c r="I543">
-        <v>0.3839634532714573</v>
+        <v>0.4585874820881592</v>
       </c>
       <c r="J543">
         <v>2.38678848909514</v>
@@ -28670,10 +28670,10 @@
         <v>5.32</v>
       </c>
       <c r="M543">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N543">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28696,7 +28696,7 @@
         <v>161</v>
       </c>
       <c r="E544">
-        <v>-3.456392664563289</v>
+        <v>-3.385406604514053</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28705,10 +28705,10 @@
         <v>0.01484270256915019</v>
       </c>
       <c r="H544">
-        <v>0.01629639266456329</v>
+        <v>0.01804540660451405</v>
       </c>
       <c r="I544">
-        <v>0.9263099045869012</v>
+        <v>0.9972959646361375</v>
       </c>
       <c r="J544">
         <v>2.397182685573614</v>
@@ -28720,10 +28720,10 @@
         <v>5.23</v>
       </c>
       <c r="M544">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N544">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28746,7 +28746,7 @@
         <v>161</v>
       </c>
       <c r="E545">
-        <v>-3.456392664563289</v>
+        <v>-3.385406604514053</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28755,10 +28755,10 @@
         <v>0.01447723785889121</v>
       </c>
       <c r="H545">
-        <v>0.01629639266456329</v>
+        <v>0.01804540660451405</v>
       </c>
       <c r="I545">
-        <v>0.3808451943279145</v>
+        <v>0.4518312543771508</v>
       </c>
       <c r="J545">
         <v>2.397182685573614</v>
@@ -28770,10 +28770,10 @@
         <v>5.32</v>
       </c>
       <c r="M545">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N545">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28796,7 +28796,7 @@
         <v>161</v>
       </c>
       <c r="E546">
-        <v>-3.486344791463074</v>
+        <v>-3.417903208213575</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28805,10 +28805,10 @@
         <v>0.01487185500334148</v>
       </c>
       <c r="H546">
-        <v>0.01632634479146307</v>
+        <v>0.01807790320821358</v>
       </c>
       <c r="I546">
-        <v>0.9255102118784109</v>
+        <v>0.9939517951279093</v>
       </c>
       <c r="J546">
         <v>2.404452619287154</v>
@@ -28820,10 +28820,10 @@
         <v>5.23</v>
       </c>
       <c r="M546">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N546">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28846,7 +28846,7 @@
         <v>161</v>
       </c>
       <c r="E547">
-        <v>-3.486344791463074</v>
+        <v>-3.417903208213575</v>
       </c>
       <c r="F547">
         <v>1</v>
@@ -28855,10 +28855,10 @@
         <v>0.01450500900567693</v>
       </c>
       <c r="H547">
-        <v>0.01632634479146307</v>
+        <v>0.01807790320821358</v>
       </c>
       <c r="I547">
-        <v>0.3786642142138525</v>
+        <v>0.447105797463351</v>
       </c>
       <c r="J547">
         <v>2.404452619287154</v>
@@ -28870,10 +28870,10 @@
         <v>5.32</v>
       </c>
       <c r="M547">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N547">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -28896,7 +28896,7 @@
         <v>161</v>
       </c>
       <c r="E548">
-        <v>-3.411771231968975</v>
+        <v>-3.336994516238184</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28905,10 +28905,10 @@
         <v>0.01479927248548437</v>
       </c>
       <c r="H548">
-        <v>0.01625177123196897</v>
+        <v>0.01799699451623818</v>
       </c>
       <c r="I548">
-        <v>0.9275012535153895</v>
+        <v>1.002277969246181</v>
       </c>
       <c r="J548">
         <v>2.386352240769169</v>
@@ -28920,10 +28920,10 @@
         <v>5.23</v>
       </c>
       <c r="M548">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N548">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -28934,52 +28934,52 @@
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B549" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C549">
-        <v>-3.795865559738223</v>
+        <v>-4.278315541383607</v>
       </c>
       <c r="D549" t="s">
         <v>161</v>
       </c>
       <c r="E549">
-        <v>-3.411771231968975</v>
+        <v>-3.269045004983722</v>
       </c>
       <c r="F549">
         <v>1</v>
       </c>
       <c r="G549">
-        <v>0.01443586555973822</v>
+        <v>0.01473831554138361</v>
       </c>
       <c r="H549">
-        <v>0.01625177123196897</v>
+        <v>0.01792904500498372</v>
       </c>
       <c r="I549">
-        <v>0.3840943277692475</v>
+        <v>1.009270536399885</v>
       </c>
       <c r="J549">
-        <v>2.386352240769169</v>
+        <v>2.371151007826336</v>
       </c>
       <c r="K549">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L549">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M549">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N549">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O549">
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28990,28 +28990,28 @@
         <v>69</v>
       </c>
       <c r="C550">
-        <v>-4.278315541383607</v>
+        <v>-4.215673134172834</v>
       </c>
       <c r="D550" t="s">
         <v>161</v>
       </c>
       <c r="E550">
-        <v>-3.349142152244506</v>
+        <v>-3.199216685723833</v>
       </c>
       <c r="F550">
         <v>1</v>
       </c>
       <c r="G550">
-        <v>0.01473831554138361</v>
+        <v>0.01467567313417283</v>
       </c>
       <c r="H550">
-        <v>0.01618914215224451</v>
+        <v>0.01785921668572383</v>
       </c>
       <c r="I550">
-        <v>0.9291733891391019</v>
+        <v>1.016456448449</v>
       </c>
       <c r="J550">
-        <v>2.371151007826336</v>
+        <v>2.355529459893475</v>
       </c>
       <c r="K550">
         <v>4.01</v>
@@ -29020,66 +29020,66 @@
         <v>5.23</v>
       </c>
       <c r="M550">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N550">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="551" spans="1:16">
       <c r="A551" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B551" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C551">
-        <v>-3.737796849896604</v>
+        <v>-4.189835924124937</v>
       </c>
       <c r="D551" t="s">
         <v>161</v>
       </c>
       <c r="E551">
-        <v>-3.349142152244506</v>
+        <v>-3.170415606194133</v>
       </c>
       <c r="F551">
         <v>1</v>
       </c>
       <c r="G551">
-        <v>0.0143777968498966</v>
+        <v>0.01464983592412494</v>
       </c>
       <c r="H551">
-        <v>0.01618914215224451</v>
+        <v>0.01783041560619414</v>
       </c>
       <c r="I551">
-        <v>0.3886546976520986</v>
+        <v>1.019420317930804</v>
       </c>
       <c r="J551">
-        <v>2.371151007826336</v>
+        <v>2.349086265367815</v>
       </c>
       <c r="K551">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L551">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M551">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N551">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29090,28 +29090,28 @@
         <v>69</v>
       </c>
       <c r="C552">
-        <v>-4.215673134172834</v>
+        <v>-4.089470803698397</v>
       </c>
       <c r="D552" t="s">
         <v>161</v>
       </c>
       <c r="E552">
-        <v>-3.284781374761117</v>
+        <v>-3.058537279933127</v>
       </c>
       <c r="F552">
         <v>1</v>
       </c>
       <c r="G552">
-        <v>0.01467567313417283</v>
+        <v>0.0145494708036984</v>
       </c>
       <c r="H552">
-        <v>0.01612478137476112</v>
+        <v>0.01771853727993313</v>
       </c>
       <c r="I552">
-        <v>0.9308917594117165</v>
+        <v>1.03093352376527</v>
       </c>
       <c r="J552">
-        <v>2.355529459893475</v>
+        <v>2.324057557032019</v>
       </c>
       <c r="K552">
         <v>4.01</v>
@@ -29120,66 +29120,66 @@
         <v>5.23</v>
       </c>
       <c r="M552">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N552">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O552">
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="553" spans="1:16">
       <c r="A553" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B553" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C553">
-        <v>-3.678122536793074</v>
+        <v>-4.005320296309154</v>
       </c>
       <c r="D553" t="s">
         <v>161</v>
       </c>
       <c r="E553">
-        <v>-3.284781374761117</v>
+        <v>-2.964733597132648</v>
       </c>
       <c r="F553">
         <v>1</v>
       </c>
       <c r="G553">
-        <v>0.01431812253679307</v>
+        <v>0.01446532029630916</v>
       </c>
       <c r="H553">
-        <v>0.01612478137476112</v>
+        <v>0.01762473359713265</v>
       </c>
       <c r="I553">
-        <v>0.3933411620319571</v>
+        <v>1.040586699176506</v>
       </c>
       <c r="J553">
-        <v>2.355529459893475</v>
+        <v>2.303072393094552</v>
       </c>
       <c r="K553">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L553">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M553">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N553">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O553">
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29190,28 +29190,28 @@
         <v>69</v>
       </c>
       <c r="C554">
-        <v>-4.189835924124937</v>
+        <v>-3.880021728113258</v>
       </c>
       <c r="D554" t="s">
         <v>161</v>
       </c>
       <c r="E554">
-        <v>-3.258235413315399</v>
+        <v>-2.825061627098819</v>
       </c>
       <c r="F554">
         <v>1</v>
       </c>
       <c r="G554">
-        <v>0.01464983592412494</v>
+        <v>0.01434002172811326</v>
       </c>
       <c r="H554">
-        <v>0.0160982354133154</v>
+        <v>0.01748506162709882</v>
       </c>
       <c r="I554">
-        <v>0.9316005108095382</v>
+        <v>1.054960101014439</v>
       </c>
       <c r="J554">
-        <v>2.349086265367815</v>
+        <v>2.271825867359915</v>
       </c>
       <c r="K554">
         <v>4.01</v>
@@ -29220,66 +29220,66 @@
         <v>5.23</v>
       </c>
       <c r="M554">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N554">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O554">
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="555" spans="1:16">
       <c r="A555" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B555" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C555">
-        <v>-3.653509533705053</v>
+        <v>-3.765867342432312</v>
       </c>
       <c r="D555" t="s">
         <v>161</v>
       </c>
       <c r="E555">
-        <v>-3.258235413315399</v>
+        <v>-2.697812224606594</v>
       </c>
       <c r="F555">
         <v>1</v>
       </c>
       <c r="G555">
-        <v>0.01429350953370505</v>
+        <v>0.01422586734243231</v>
       </c>
       <c r="H555">
-        <v>0.0160982354133154</v>
+        <v>0.01735781222460659</v>
       </c>
       <c r="I555">
-        <v>0.3952741203896544</v>
+        <v>1.068055117825718</v>
       </c>
       <c r="J555">
-        <v>2.349086265367815</v>
+        <v>2.243358439509305</v>
       </c>
       <c r="K555">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L555">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M555">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N555">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O555">
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29290,28 +29290,28 @@
         <v>69</v>
       </c>
       <c r="C556">
-        <v>-4.089470803698397</v>
+        <v>-3.200435821279882</v>
       </c>
       <c r="D556" t="s">
         <v>161</v>
       </c>
       <c r="E556">
-        <v>-3.15511713497192</v>
+        <v>-2.067518234693535</v>
       </c>
       <c r="F556">
         <v>1</v>
       </c>
       <c r="G556">
-        <v>0.0145494708036984</v>
+        <v>0.01366043582127988</v>
       </c>
       <c r="H556">
-        <v>0.01599511713497192</v>
+        <v>0.01672751823469354</v>
       </c>
       <c r="I556">
-        <v>0.9343536687264766</v>
+        <v>1.132917586586347</v>
       </c>
       <c r="J556">
-        <v>2.324057557032019</v>
+        <v>2.102353072638375</v>
       </c>
       <c r="K556">
         <v>4.01</v>
@@ -29320,16 +29320,16 @@
         <v>5.23</v>
       </c>
       <c r="M556">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N556">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="O556">
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29340,28 +29340,28 @@
         <v>69</v>
       </c>
       <c r="C557">
-        <v>-4.005320296309154</v>
+        <v>-2.562371230751202</v>
       </c>
       <c r="D557" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E557">
-        <v>-3.068658259549556</v>
+        <v>-1.505427244947517</v>
       </c>
       <c r="F557">
         <v>1</v>
       </c>
       <c r="G557">
-        <v>0.01446532029630916</v>
+        <v>0.0130223712307512</v>
       </c>
       <c r="H557">
-        <v>0.01590865825954956</v>
+        <v>0.01318542724494752</v>
       </c>
       <c r="I557">
-        <v>0.9366620367595981</v>
+        <v>1.056943985803684</v>
       </c>
       <c r="J557">
-        <v>2.303072393094552</v>
+        <v>1.943234720885587</v>
       </c>
       <c r="K557">
         <v>4.01</v>
@@ -29370,215 +29370,15 @@
         <v>5.23</v>
       </c>
       <c r="M557">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="N557">
-        <v>6.42</v>
+        <v>5.84</v>
       </c>
       <c r="O557">
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="558" spans="1:16">
-      <c r="A558" s="1">
-        <v>0</v>
-      </c>
-      <c r="B558" t="s">
-        <v>69</v>
-      </c>
-      <c r="C558">
-        <v>-3.880021728113258</v>
-      </c>
-      <c r="D558" t="s">
-        <v>161</v>
-      </c>
-      <c r="E558">
-        <v>-2.93992257352285</v>
-      </c>
-      <c r="F558">
-        <v>1</v>
-      </c>
-      <c r="G558">
-        <v>0.01434002172811326</v>
-      </c>
-      <c r="H558">
-        <v>0.01577992257352285</v>
-      </c>
-      <c r="I558">
-        <v>0.940099154590408</v>
-      </c>
-      <c r="J558">
-        <v>2.271825867359915</v>
-      </c>
-      <c r="K558">
-        <v>4.01</v>
-      </c>
-      <c r="L558">
-        <v>5.23</v>
-      </c>
-      <c r="M558">
-        <v>4.12</v>
-      </c>
-      <c r="N558">
-        <v>6.42</v>
-      </c>
-      <c r="O558">
-        <v>1</v>
-      </c>
-      <c r="P558" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="559" spans="1:16">
-      <c r="A559" s="1">
-        <v>0</v>
-      </c>
-      <c r="B559" t="s">
-        <v>69</v>
-      </c>
-      <c r="C559">
-        <v>-3.765867342432312</v>
-      </c>
-      <c r="D559" t="s">
-        <v>161</v>
-      </c>
-      <c r="E559">
-        <v>-2.822636770778338</v>
-      </c>
-      <c r="F559">
-        <v>1</v>
-      </c>
-      <c r="G559">
-        <v>0.01422586734243231</v>
-      </c>
-      <c r="H559">
-        <v>0.01566263677077834</v>
-      </c>
-      <c r="I559">
-        <v>0.9432305716539737</v>
-      </c>
-      <c r="J559">
-        <v>2.243358439509305</v>
-      </c>
-      <c r="K559">
-        <v>4.01</v>
-      </c>
-      <c r="L559">
-        <v>5.23</v>
-      </c>
-      <c r="M559">
-        <v>4.12</v>
-      </c>
-      <c r="N559">
-        <v>6.42</v>
-      </c>
-      <c r="O559">
-        <v>1</v>
-      </c>
-      <c r="P559" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="560" spans="1:16">
-      <c r="A560" s="1">
-        <v>0</v>
-      </c>
-      <c r="B560" t="s">
-        <v>69</v>
-      </c>
-      <c r="C560">
-        <v>-3.200435821279882</v>
-      </c>
-      <c r="D560" t="s">
-        <v>161</v>
-      </c>
-      <c r="E560">
-        <v>-2.241694659270104</v>
-      </c>
-      <c r="F560">
-        <v>1</v>
-      </c>
-      <c r="G560">
-        <v>0.01366043582127988</v>
-      </c>
-      <c r="H560">
-        <v>0.01508169465927011</v>
-      </c>
-      <c r="I560">
-        <v>0.9587411620097779</v>
-      </c>
-      <c r="J560">
-        <v>2.102353072638375</v>
-      </c>
-      <c r="K560">
-        <v>4.01</v>
-      </c>
-      <c r="L560">
-        <v>5.23</v>
-      </c>
-      <c r="M560">
-        <v>4.12</v>
-      </c>
-      <c r="N560">
-        <v>6.42</v>
-      </c>
-      <c r="O560">
-        <v>1</v>
-      </c>
-      <c r="P560" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="561" spans="1:16">
-      <c r="A561" s="1">
-        <v>0</v>
-      </c>
-      <c r="B561" t="s">
-        <v>69</v>
-      </c>
-      <c r="C561">
-        <v>-2.562371230751202</v>
-      </c>
-      <c r="D561" t="s">
-        <v>160</v>
-      </c>
-      <c r="E561">
-        <v>-1.505427244947517</v>
-      </c>
-      <c r="F561">
-        <v>1</v>
-      </c>
-      <c r="G561">
-        <v>0.0130223712307512</v>
-      </c>
-      <c r="H561">
-        <v>0.01318542724494752</v>
-      </c>
-      <c r="I561">
-        <v>1.056943985803684</v>
-      </c>
-      <c r="J561">
-        <v>1.943234720885587</v>
-      </c>
-      <c r="K561">
-        <v>4.01</v>
-      </c>
-      <c r="L561">
-        <v>5.23</v>
-      </c>
-      <c r="M561">
-        <v>3.78</v>
-      </c>
-      <c r="N561">
-        <v>5.84</v>
-      </c>
-      <c r="O561">
-        <v>1</v>
-      </c>
-      <c r="P561" t="s">
         <v>386</v>
       </c>
     </row>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="389">
   <si>
     <t>trade_time</t>
   </si>
@@ -500,6 +500,9 @@
   </si>
   <si>
     <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -1632,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1682,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1732,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1782,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1832,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1882,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1932,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1982,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2032,7 +2035,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2082,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2132,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2182,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2232,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2282,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2332,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2382,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2432,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2482,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2532,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2582,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2632,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2682,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2732,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2782,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2832,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2882,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2932,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2982,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3032,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3082,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3132,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3182,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3232,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3282,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3332,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3382,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3432,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3482,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3532,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3582,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3632,7 +3635,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3682,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3732,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3782,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3832,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3882,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3932,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3982,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4032,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4082,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4132,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4182,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4232,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4282,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4332,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4382,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4432,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4482,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4532,7 +4535,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4582,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4632,7 +4635,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4682,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4732,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4782,7 +4785,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4832,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4882,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4932,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4982,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5032,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5082,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5132,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5182,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5232,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5282,7 +5285,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5332,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5382,7 +5385,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5432,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5482,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5532,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5582,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5632,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5682,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5732,7 +5735,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5782,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5832,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5882,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5932,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5982,7 +5985,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6032,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6082,7 +6085,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6132,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6182,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6232,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6282,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6332,7 +6335,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6382,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6432,7 +6435,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6482,7 +6485,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6532,7 +6535,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6582,7 +6585,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6632,7 +6635,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6682,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6732,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6782,7 +6785,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6832,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6882,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6932,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6982,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7032,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7082,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7132,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7182,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7232,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7282,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7332,7 +7335,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7382,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7432,7 +7435,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7482,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7532,7 +7535,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7582,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7632,7 +7635,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7682,7 +7685,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7732,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7782,7 +7785,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7832,7 +7835,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7882,7 +7885,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7932,7 +7935,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7982,7 +7985,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8032,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8082,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8132,7 +8135,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8182,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8232,7 +8235,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8282,7 +8285,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8332,7 +8335,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8382,7 +8385,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8432,7 +8435,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8482,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8532,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8632,7 +8635,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8682,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8732,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8782,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8832,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8882,7 +8885,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8932,7 +8935,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8982,7 +8985,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9032,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9082,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9132,7 +9135,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9182,7 +9185,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9232,7 +9235,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9282,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9332,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9382,7 +9385,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9432,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9482,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9532,7 +9535,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9582,7 +9585,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9682,7 +9685,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9732,7 +9735,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9782,7 +9785,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9932,7 +9935,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9982,7 +9985,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10032,7 +10035,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10082,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10132,7 +10135,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10182,7 +10185,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10232,7 +10235,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10282,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10382,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10432,7 +10435,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10582,7 +10585,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10632,7 +10635,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10682,7 +10685,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10732,7 +10735,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11232,7 +11235,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11282,7 +11285,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11332,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11382,7 +11385,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11432,7 +11435,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11482,7 +11485,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11532,7 +11535,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11582,7 +11585,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11632,7 +11635,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11682,7 +11685,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11732,7 +11735,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11782,7 +11785,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11832,7 +11835,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11882,7 +11885,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11932,7 +11935,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12732,7 +12735,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12782,7 +12785,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12832,7 +12835,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12882,7 +12885,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12932,7 +12935,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12982,7 +12985,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13032,7 +13035,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13082,7 +13085,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13132,7 +13135,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13182,7 +13185,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13232,7 +13235,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13282,7 +13285,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13332,7 +13335,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13382,7 +13385,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13432,7 +13435,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13482,7 +13485,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13532,7 +13535,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13582,7 +13585,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13632,7 +13635,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13682,7 +13685,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13832,7 +13835,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13882,7 +13885,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13932,7 +13935,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14032,7 +14035,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14182,7 +14185,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14232,7 +14235,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14282,7 +14285,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14332,7 +14335,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14382,7 +14385,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14432,7 +14435,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14482,7 +14485,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14582,7 +14585,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14632,7 +14635,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14682,7 +14685,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14732,7 +14735,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14782,7 +14785,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14832,7 +14835,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14882,7 +14885,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14932,7 +14935,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14982,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15032,7 +15035,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15082,7 +15085,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15132,7 +15135,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15182,7 +15185,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15232,7 +15235,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15282,7 +15285,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15332,7 +15335,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15382,7 +15385,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15432,7 +15435,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15482,7 +15485,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15532,7 +15535,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15582,7 +15585,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15632,7 +15635,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15682,7 +15685,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15732,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15782,7 +15785,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15832,7 +15835,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15882,7 +15885,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15932,7 +15935,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15982,7 +15985,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16032,7 +16035,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16082,7 +16085,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16132,7 +16135,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16182,7 +16185,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16232,7 +16235,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16282,7 +16285,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16332,7 +16335,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16382,7 +16385,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16432,7 +16435,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16482,7 +16485,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16532,7 +16535,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16582,7 +16585,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16632,7 +16635,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16682,7 +16685,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16732,7 +16735,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16782,7 +16785,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16832,7 +16835,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16882,7 +16885,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16932,7 +16935,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17132,7 +17135,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17182,7 +17185,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17232,7 +17235,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17282,7 +17285,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17332,7 +17335,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17382,7 +17385,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17432,7 +17435,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17482,7 +17485,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17532,7 +17535,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17582,7 +17585,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17632,7 +17635,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17682,7 +17685,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17732,7 +17735,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17782,7 +17785,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17832,7 +17835,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17882,7 +17885,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17932,7 +17935,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17982,7 +17985,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18032,7 +18035,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18082,7 +18085,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18132,7 +18135,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18182,7 +18185,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18232,7 +18235,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18282,7 +18285,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18332,7 +18335,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18582,7 +18585,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18632,7 +18635,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18682,7 +18685,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18732,7 +18735,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18782,7 +18785,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18832,7 +18835,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18882,7 +18885,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18932,7 +18935,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18982,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19032,7 +19035,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19082,7 +19085,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19132,7 +19135,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19582,7 +19585,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19632,7 +19635,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19682,7 +19685,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19732,7 +19735,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19782,7 +19785,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19832,7 +19835,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19882,7 +19885,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19932,7 +19935,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19982,7 +19985,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20032,7 +20035,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20082,7 +20085,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20132,7 +20135,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20182,7 +20185,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20232,7 +20235,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20282,7 +20285,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20332,7 +20335,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20532,7 +20535,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20582,7 +20585,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20632,7 +20635,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20682,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20882,7 +20885,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20932,7 +20935,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20982,7 +20985,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21032,7 +21035,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21082,7 +21085,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21132,7 +21135,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21182,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21232,7 +21235,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21282,7 +21285,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21332,7 +21335,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21382,7 +21385,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21432,7 +21435,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21482,7 +21485,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21532,7 +21535,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21582,7 +21585,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21632,7 +21635,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21682,7 +21685,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21732,7 +21735,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21782,7 +21785,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21832,7 +21835,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21882,7 +21885,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21932,7 +21935,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21982,7 +21985,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22032,7 +22035,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22082,7 +22085,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22132,7 +22135,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22182,7 +22185,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22232,7 +22235,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22282,7 +22285,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22332,7 +22335,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22382,7 +22385,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22432,7 +22435,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22482,7 +22485,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22682,7 +22685,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22732,7 +22735,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22782,7 +22785,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22832,7 +22835,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22882,7 +22885,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22932,7 +22935,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23132,7 +23135,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23182,7 +23185,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23232,7 +23235,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23282,7 +23285,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23332,7 +23335,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23382,7 +23385,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23432,7 +23435,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23482,7 +23485,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23532,7 +23535,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23582,7 +23585,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23632,7 +23635,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23682,7 +23685,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23732,7 +23735,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23782,7 +23785,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23832,7 +23835,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23882,7 +23885,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23932,7 +23935,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23982,7 +23985,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24032,7 +24035,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24082,7 +24085,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24132,7 +24135,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24182,7 +24185,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24232,7 +24235,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24282,7 +24285,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24332,7 +24335,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24382,7 +24385,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24432,7 +24435,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24482,7 +24485,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24532,7 +24535,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24582,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24632,7 +24635,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24682,7 +24685,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24732,7 +24735,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24782,7 +24785,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24832,7 +24835,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24882,7 +24885,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24932,7 +24935,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24982,7 +24985,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25032,7 +25035,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25082,7 +25085,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25132,7 +25135,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25182,7 +25185,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25482,7 +25485,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25532,7 +25535,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25582,7 +25585,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25632,7 +25635,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25682,7 +25685,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25732,7 +25735,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25782,7 +25785,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25832,7 +25835,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25882,7 +25885,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25932,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25982,7 +25985,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26032,7 +26035,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26082,7 +26085,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26132,7 +26135,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26182,7 +26185,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26232,7 +26235,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26282,7 +26285,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26332,7 +26335,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26382,7 +26385,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26432,7 +26435,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26482,7 +26485,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26532,7 +26535,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26582,7 +26585,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26632,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26682,7 +26685,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26732,7 +26735,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26782,7 +26785,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26832,7 +26835,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26882,7 +26885,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26932,7 +26935,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26982,7 +26985,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27032,7 +27035,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27082,7 +27085,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27132,7 +27135,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27182,7 +27185,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27232,7 +27235,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27282,7 +27285,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27332,7 +27335,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27382,7 +27385,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27432,7 +27435,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27482,7 +27485,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27532,7 +27535,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27582,7 +27585,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27632,7 +27635,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27649,7 +27652,7 @@
         <v>162</v>
       </c>
       <c r="E523">
-        <v>0.1441551924455533</v>
+        <v>0.1180305516873252</v>
       </c>
       <c r="F523">
         <v>-1</v>
@@ -27658,10 +27661,10 @@
         <v>0.01453771441892787</v>
       </c>
       <c r="H523">
-        <v>0.01407584480755445</v>
+        <v>0.01408196944831267</v>
       </c>
       <c r="I523">
-        <v>-0.02186961137341825</v>
+        <v>0.004255029384809816</v>
       </c>
       <c r="J523">
         <v>1.612464075822789</v>
@@ -27673,16 +27676,16 @@
         <v>7.33</v>
       </c>
       <c r="M523">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N523">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27732,7 +27735,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27782,7 +27785,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27832,7 +27835,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27882,7 +27885,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27932,7 +27935,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27982,7 +27985,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28032,7 +28035,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28046,7 +28049,7 @@
         <v>-2.943692670373876</v>
       </c>
       <c r="D531" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E531">
         <v>-1.695574148632207</v>
@@ -28082,7 +28085,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28096,7 +28099,7 @@
         <v>-2.466410474021997</v>
       </c>
       <c r="D532" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E532">
         <v>-1.695574148632207</v>
@@ -28132,7 +28135,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28149,7 +28152,7 @@
         <v>162</v>
       </c>
       <c r="E533">
-        <v>-2.081779604256424</v>
+        <v>-2.11305687185887</v>
       </c>
       <c r="F533">
         <v>1</v>
@@ -28158,10 +28161,10 @@
         <v>0.01376218430858061</v>
       </c>
       <c r="H533">
-        <v>0.01630177960425643</v>
+        <v>0.01631305687185887</v>
       </c>
       <c r="I533">
-        <v>1.220404704324189</v>
+        <v>1.189127436721744</v>
       </c>
       <c r="J533">
         <v>2.127726760244542</v>
@@ -28173,16 +28176,16 @@
         <v>5.23</v>
       </c>
       <c r="M533">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N533">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28199,7 +28202,7 @@
         <v>162</v>
       </c>
       <c r="E534">
-        <v>-2.081779604256424</v>
+        <v>-2.11305687185887</v>
       </c>
       <c r="F534">
         <v>1</v>
@@ -28208,10 +28211,10 @@
         <v>0.01344791622413415</v>
       </c>
       <c r="H534">
-        <v>0.01630177960425643</v>
+        <v>0.01631305687185887</v>
       </c>
       <c r="I534">
-        <v>0.7261366198777273</v>
+        <v>0.6948593522752819</v>
       </c>
       <c r="J534">
         <v>2.127726760244542</v>
@@ -28223,16 +28226,16 @@
         <v>5.32</v>
       </c>
       <c r="M534">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N534">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O534">
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28249,7 +28252,7 @@
         <v>162</v>
       </c>
       <c r="E535">
-        <v>-2.230996395450833</v>
+        <v>-2.262619072292154</v>
       </c>
       <c r="F535">
         <v>1</v>
@@ -28258,10 +28261,10 @@
         <v>0.01390069341336987</v>
       </c>
       <c r="H535">
-        <v>0.01645099639545083</v>
+        <v>0.01646261907229215</v>
       </c>
       <c r="I535">
-        <v>1.209697017919036</v>
+        <v>1.178074341077716</v>
       </c>
       <c r="J535">
         <v>2.162267684132137</v>
@@ -28273,16 +28276,16 @@
         <v>5.23</v>
       </c>
       <c r="M535">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N535">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28299,7 +28302,7 @@
         <v>162</v>
       </c>
       <c r="E536">
-        <v>-2.230996395450833</v>
+        <v>-2.262619072292154</v>
       </c>
       <c r="F536">
         <v>1</v>
@@ -28308,10 +28311,10 @@
         <v>0.01357986255338476</v>
       </c>
       <c r="H536">
-        <v>0.01645099639545083</v>
+        <v>0.01646261907229215</v>
       </c>
       <c r="I536">
-        <v>0.7088661579339304</v>
+        <v>0.67724348109261</v>
       </c>
       <c r="J536">
         <v>2.162267684132137</v>
@@ -28323,16 +28326,16 @@
         <v>5.32</v>
       </c>
       <c r="M536">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N536">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O536">
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28349,7 +28352,7 @@
         <v>162</v>
       </c>
       <c r="E537">
-        <v>-2.476846412652521</v>
+        <v>-2.509038186755884</v>
       </c>
       <c r="F537">
         <v>1</v>
@@ -28358,10 +28361,10 @@
         <v>0.01412890141544829</v>
       </c>
       <c r="H537">
-        <v>0.01669684641265252</v>
+        <v>0.01670903818675588</v>
       </c>
       <c r="I537">
-        <v>1.192055002795768</v>
+        <v>1.159863228692405</v>
       </c>
       <c r="J537">
         <v>2.219177410336232</v>
@@ -28373,16 +28376,16 @@
         <v>5.23</v>
       </c>
       <c r="M537">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N537">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O537">
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28399,7 +28402,7 @@
         <v>162</v>
       </c>
       <c r="E538">
-        <v>-2.476846412652521</v>
+        <v>-2.509038186755884</v>
       </c>
       <c r="F538">
         <v>1</v>
@@ -28408,10 +28411,10 @@
         <v>0.01379725770748441</v>
       </c>
       <c r="H538">
-        <v>0.01669684641265252</v>
+        <v>0.01670903818675588</v>
       </c>
       <c r="I538">
-        <v>0.6804112948318837</v>
+        <v>0.6482195207285208</v>
       </c>
       <c r="J538">
         <v>2.219177410336232</v>
@@ -28423,16 +28426,16 @@
         <v>5.32</v>
       </c>
       <c r="M538">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N538">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28449,7 +28452,7 @@
         <v>162</v>
       </c>
       <c r="E539">
-        <v>-2.784942617924234</v>
+        <v>-2.817847577687948</v>
       </c>
       <c r="F539">
         <v>1</v>
@@ -28458,10 +28461,10 @@
         <v>0.01441488886524911</v>
       </c>
       <c r="H539">
-        <v>0.01700494261792423</v>
+        <v>0.01701784757768795</v>
       </c>
       <c r="I539">
-        <v>1.169946247324879</v>
+        <v>1.137041287561166</v>
       </c>
       <c r="J539">
         <v>2.29049597637135</v>
@@ -28473,16 +28476,16 @@
         <v>5.23</v>
       </c>
       <c r="M539">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N539">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28499,7 +28502,7 @@
         <v>162</v>
       </c>
       <c r="E540">
-        <v>-2.784942617924234</v>
+        <v>-2.817847577687948</v>
       </c>
       <c r="F540">
         <v>1</v>
@@ -28508,10 +28511,10 @@
         <v>0.01406969462973856</v>
       </c>
       <c r="H540">
-        <v>0.01700494261792423</v>
+        <v>0.01701784757768795</v>
       </c>
       <c r="I540">
-        <v>0.6447520118143233</v>
+        <v>0.6118470520506101</v>
       </c>
       <c r="J540">
         <v>2.29049597637135</v>
@@ -28523,16 +28526,16 @@
         <v>5.32</v>
       </c>
       <c r="M540">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N540">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O540">
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28549,7 +28552,7 @@
         <v>162</v>
       </c>
       <c r="E541">
-        <v>-3.008658191056466</v>
+        <v>-3.042081010943171</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28558,10 +28561,10 @@
         <v>0.01462255077456862</v>
       </c>
       <c r="H541">
-        <v>0.01722865819105647</v>
+        <v>0.01724208101094317</v>
       </c>
       <c r="I541">
-        <v>1.153892583512151</v>
+        <v>1.120469763625445</v>
       </c>
       <c r="J541">
         <v>2.342281988670478</v>
@@ -28573,16 +28576,16 @@
         <v>5.23</v>
       </c>
       <c r="M541">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N541">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28599,7 +28602,7 @@
         <v>162</v>
       </c>
       <c r="E542">
-        <v>-3.008658191056466</v>
+        <v>-3.042081010943171</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28608,10 +28611,10 @@
         <v>0.01426751719672123</v>
       </c>
       <c r="H542">
-        <v>0.01722865819105647</v>
+        <v>0.01724208101094317</v>
       </c>
       <c r="I542">
-        <v>0.6188590056647607</v>
+        <v>0.5854361857780557</v>
       </c>
       <c r="J542">
         <v>2.342281988670478</v>
@@ -28623,16 +28626,16 @@
         <v>5.32</v>
       </c>
       <c r="M542">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N542">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28649,7 +28652,7 @@
         <v>162</v>
       </c>
       <c r="E543">
-        <v>-3.200926272891006</v>
+        <v>-3.234794157781957</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28658,10 +28661,10 @@
         <v>0.01480102184127151</v>
       </c>
       <c r="H543">
-        <v>0.017420926272891</v>
+        <v>0.01743479415778196</v>
       </c>
       <c r="I543">
-        <v>1.140095568380505</v>
+        <v>1.106227683489553</v>
       </c>
       <c r="J543">
         <v>2.38678848909514</v>
@@ -28673,16 +28676,16 @@
         <v>5.23</v>
       </c>
       <c r="M543">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N543">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28699,7 +28702,7 @@
         <v>162</v>
       </c>
       <c r="E544">
-        <v>-3.200926272891006</v>
+        <v>-3.234794157781957</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28708,10 +28711,10 @@
         <v>0.01443753202834343</v>
       </c>
       <c r="H544">
-        <v>0.017420926272891</v>
+        <v>0.01743479415778196</v>
       </c>
       <c r="I544">
-        <v>0.5966057554524289</v>
+        <v>0.5627378705614774</v>
       </c>
       <c r="J544">
         <v>2.38678848909514</v>
@@ -28723,16 +28726,16 @@
         <v>5.32</v>
       </c>
       <c r="M544">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N544">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28749,7 +28752,7 @@
         <v>162</v>
       </c>
       <c r="E545">
-        <v>-3.245829201678013</v>
+        <v>-3.279801028533749</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28758,10 +28761,10 @@
         <v>0.01484270256915019</v>
       </c>
       <c r="H545">
-        <v>0.01746582920167801</v>
+        <v>0.01747980102853375</v>
       </c>
       <c r="I545">
-        <v>1.136873367472178</v>
+        <v>1.102901540616442</v>
       </c>
       <c r="J545">
         <v>2.397182685573614</v>
@@ -28773,16 +28776,16 @@
         <v>5.23</v>
       </c>
       <c r="M545">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N545">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28799,7 +28802,7 @@
         <v>162</v>
       </c>
       <c r="E546">
-        <v>-3.245829201678013</v>
+        <v>-3.279801028533749</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28808,10 +28811,10 @@
         <v>0.01447723785889121</v>
       </c>
       <c r="H546">
-        <v>0.01746582920167801</v>
+        <v>0.01747980102853375</v>
       </c>
       <c r="I546">
-        <v>0.5914086572131909</v>
+        <v>0.5574368303574548</v>
       </c>
       <c r="J546">
         <v>2.397182685573614</v>
@@ -28823,16 +28826,16 @@
         <v>5.32</v>
       </c>
       <c r="M546">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N546">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28849,7 +28852,7 @@
         <v>162</v>
       </c>
       <c r="E547">
-        <v>-3.277235315320504</v>
+        <v>-3.311279841513375</v>
       </c>
       <c r="F547">
         <v>1</v>
@@ -28858,10 +28861,10 @@
         <v>0.01487185500334148</v>
       </c>
       <c r="H547">
-        <v>0.01749723531532051</v>
+        <v>0.01751127984151337</v>
       </c>
       <c r="I547">
-        <v>1.13461968802098</v>
+        <v>1.100575161828109</v>
       </c>
       <c r="J547">
         <v>2.404452619287154</v>
@@ -28873,16 +28876,16 @@
         <v>5.23</v>
       </c>
       <c r="M547">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N547">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28899,7 +28902,7 @@
         <v>162</v>
       </c>
       <c r="E548">
-        <v>-3.277235315320504</v>
+        <v>-3.311279841513375</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28908,10 +28911,10 @@
         <v>0.01450500900567693</v>
       </c>
       <c r="H548">
-        <v>0.01749723531532051</v>
+        <v>0.01751127984151337</v>
       </c>
       <c r="I548">
-        <v>0.5877736903564221</v>
+        <v>0.5537291641635509</v>
       </c>
       <c r="J548">
         <v>2.404452619287154</v>
@@ -28923,16 +28926,16 @@
         <v>5.32</v>
       </c>
       <c r="M548">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N548">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28949,7 +28952,7 @@
         <v>162</v>
       </c>
       <c r="E549">
-        <v>-3.199041680122808</v>
+        <v>-3.232905202530501</v>
       </c>
       <c r="F549">
         <v>1</v>
@@ -28958,10 +28961,10 @@
         <v>0.01479927248548437</v>
       </c>
       <c r="H549">
-        <v>0.01741904168012281</v>
+        <v>0.0174329052025305</v>
       </c>
       <c r="I549">
-        <v>1.140230805361557</v>
+        <v>1.106367282953864</v>
       </c>
       <c r="J549">
         <v>2.386352240769169</v>
@@ -28973,16 +28976,16 @@
         <v>5.23</v>
       </c>
       <c r="M549">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N549">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O549">
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28999,7 +29002,7 @@
         <v>162</v>
       </c>
       <c r="E550">
-        <v>-3.133372353809773</v>
+        <v>-3.167083863888037</v>
       </c>
       <c r="F550">
         <v>1</v>
@@ -29008,10 +29011,10 @@
         <v>0.01473831554138361</v>
       </c>
       <c r="H550">
-        <v>0.01735337235380978</v>
+        <v>0.01736708386388804</v>
       </c>
       <c r="I550">
-        <v>1.144943187573834</v>
+        <v>1.111231677495571</v>
       </c>
       <c r="J550">
         <v>2.371151007826336</v>
@@ -29023,16 +29026,16 @@
         <v>5.23</v>
       </c>
       <c r="M550">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N550">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29049,7 +29052,7 @@
         <v>162</v>
       </c>
       <c r="E551">
-        <v>-3.065887266739813</v>
+        <v>-3.099442561338748</v>
       </c>
       <c r="F551">
         <v>1</v>
@@ -29058,10 +29061,10 @@
         <v>0.01467567313417283</v>
       </c>
       <c r="H551">
-        <v>0.01728588726673981</v>
+        <v>0.01729944256133875</v>
       </c>
       <c r="I551">
-        <v>1.14978586743302</v>
+        <v>1.116230572834086</v>
       </c>
       <c r="J551">
         <v>2.355529459893475</v>
@@ -29073,16 +29076,16 @@
         <v>5.23</v>
       </c>
       <c r="M551">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N551">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29099,7 +29102,7 @@
         <v>162</v>
       </c>
       <c r="E552">
-        <v>-3.038052666388961</v>
+        <v>-3.071543529042639</v>
       </c>
       <c r="F552">
         <v>1</v>
@@ -29108,10 +29111,10 @@
         <v>0.01464983592412494</v>
       </c>
       <c r="H552">
-        <v>0.01725805266638896</v>
+        <v>0.01727154352904264</v>
       </c>
       <c r="I552">
-        <v>1.151783257735976</v>
+        <v>1.118292395082298</v>
       </c>
       <c r="J552">
         <v>2.349086265367815</v>
@@ -29123,16 +29126,16 @@
         <v>5.23</v>
       </c>
       <c r="M552">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N552">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O552">
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29149,7 +29152,7 @@
         <v>162</v>
       </c>
       <c r="E553">
-        <v>-2.929928646378325</v>
+        <v>-2.963169221948645</v>
       </c>
       <c r="F553">
         <v>1</v>
@@ -29158,10 +29161,10 @@
         <v>0.0145494708036984</v>
       </c>
       <c r="H553">
-        <v>0.01714992864637832</v>
+        <v>0.01716316922194864</v>
       </c>
       <c r="I553">
-        <v>1.159542157320073</v>
+        <v>1.126301581749752</v>
       </c>
       <c r="J553">
         <v>2.324057557032019</v>
@@ -29173,16 +29176,16 @@
         <v>5.23</v>
       </c>
       <c r="M553">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N553">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O553">
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29199,7 +29202,7 @@
         <v>162</v>
       </c>
       <c r="E554">
-        <v>-2.839272738168465</v>
+        <v>-2.872303462099412</v>
       </c>
       <c r="F554">
         <v>1</v>
@@ -29208,10 +29211,10 @@
         <v>0.01446532029630916</v>
       </c>
       <c r="H554">
-        <v>0.01705927273816847</v>
+        <v>0.01707230346209941</v>
       </c>
       <c r="I554">
-        <v>1.166047558140689</v>
+        <v>1.133016834209743</v>
       </c>
       <c r="J554">
         <v>2.303072393094552</v>
@@ -29223,16 +29226,16 @@
         <v>5.23</v>
       </c>
       <c r="M554">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N554">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O554">
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29249,7 +29252,7 @@
         <v>162</v>
       </c>
       <c r="E555">
-        <v>-2.704287746994832</v>
+        <v>-2.737006005668432</v>
       </c>
       <c r="F555">
         <v>1</v>
@@ -29258,10 +29261,10 @@
         <v>0.01434002172811326</v>
       </c>
       <c r="H555">
-        <v>0.01692428774699483</v>
+        <v>0.01693700600566843</v>
       </c>
       <c r="I555">
-        <v>1.175733981118426</v>
+        <v>1.143015722444826</v>
       </c>
       <c r="J555">
         <v>2.271825867359915</v>
@@ -29273,16 +29276,16 @@
         <v>5.23</v>
       </c>
       <c r="M555">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N555">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O555">
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29299,7 +29302,7 @@
         <v>162</v>
       </c>
       <c r="E556">
-        <v>-2.581308458680199</v>
+        <v>-2.613742043075291</v>
       </c>
       <c r="F556">
         <v>1</v>
@@ -29308,10 +29311,10 @@
         <v>0.01422586734243231</v>
       </c>
       <c r="H556">
-        <v>0.0168013084586802</v>
+        <v>0.01681374204307529</v>
       </c>
       <c r="I556">
-        <v>1.184558883752113</v>
+        <v>1.152125299357021</v>
       </c>
       <c r="J556">
         <v>2.243358439509305</v>
@@ -29323,16 +29326,16 @@
         <v>5.23</v>
       </c>
       <c r="M556">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="N556">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="O556">
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29346,7 +29349,7 @@
         <v>-3.200435821279882</v>
       </c>
       <c r="D557" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E557">
         <v>-1.972165273797779</v>
@@ -29382,7 +29385,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29432,7 +29435,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -502,7 +502,7 @@
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-09-08</t>
+    <t>2021-09-09</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -27652,7 +27652,7 @@
         <v>162</v>
       </c>
       <c r="E523">
-        <v>0.1180305516873252</v>
+        <v>0.04640447396200997</v>
       </c>
       <c r="F523">
         <v>-1</v>
@@ -27661,10 +27661,10 @@
         <v>0.01453771441892787</v>
       </c>
       <c r="H523">
-        <v>0.01408196944831267</v>
+        <v>0.01391359552603799</v>
       </c>
       <c r="I523">
-        <v>0.004255029384809816</v>
+        <v>0.07588110711012508</v>
       </c>
       <c r="J523">
         <v>1.612464075822789</v>
@@ -27676,10 +27676,10 @@
         <v>7.33</v>
       </c>
       <c r="M523">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N523">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -28040,63 +28040,63 @@
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B531" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C531">
-        <v>-2.943692670373876</v>
+        <v>-2.088049638752098</v>
       </c>
       <c r="D531" t="s">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="E531">
-        <v>-1.695574148632207</v>
+        <v>-1.338581645346041</v>
       </c>
       <c r="F531">
         <v>1</v>
       </c>
       <c r="G531">
-        <v>0.01340369267037388</v>
+        <v>0.0127280496387521</v>
       </c>
       <c r="H531">
-        <v>0.01591557414863221</v>
+        <v>0.01599858164534604</v>
       </c>
       <c r="I531">
-        <v>1.248118521741669</v>
+        <v>0.7494679934060571</v>
       </c>
       <c r="J531">
-        <v>2.038327349220418</v>
+        <v>1.939280010144528</v>
       </c>
       <c r="K531">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L531">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M531">
-        <v>4.32</v>
+        <v>4.47</v>
       </c>
       <c r="N531">
-        <v>7.11</v>
+        <v>7.33</v>
       </c>
       <c r="O531">
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B532" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C532">
-        <v>-2.466410474021997</v>
+        <v>-2.943692670373876</v>
       </c>
       <c r="D532" t="s">
         <v>163</v>
@@ -28108,22 +28108,22 @@
         <v>1</v>
       </c>
       <c r="G532">
-        <v>0.013106410474022</v>
+        <v>0.01340369267037388</v>
       </c>
       <c r="H532">
         <v>0.01591557414863221</v>
       </c>
       <c r="I532">
-        <v>0.7708363253897899</v>
+        <v>1.248118521741669</v>
       </c>
       <c r="J532">
         <v>2.038327349220418</v>
       </c>
       <c r="K532">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L532">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M532">
         <v>4.32</v>
@@ -28140,96 +28140,96 @@
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B533" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C533">
-        <v>-3.302184308580614</v>
+        <v>-2.466410474021997</v>
       </c>
       <c r="D533" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E533">
-        <v>-2.11305687185887</v>
+        <v>-1.695574148632207</v>
       </c>
       <c r="F533">
         <v>1</v>
       </c>
       <c r="G533">
-        <v>0.01376218430858061</v>
+        <v>0.013106410474022</v>
       </c>
       <c r="H533">
-        <v>0.01631305687185887</v>
+        <v>0.01591557414863221</v>
       </c>
       <c r="I533">
-        <v>1.189127436721744</v>
+        <v>0.7708363253897899</v>
       </c>
       <c r="J533">
-        <v>2.127726760244542</v>
+        <v>2.038327349220418</v>
       </c>
       <c r="K533">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L533">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M533">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="N533">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B534" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C534">
-        <v>-2.807916224134152</v>
+        <v>-3.302184308580614</v>
       </c>
       <c r="D534" t="s">
         <v>162</v>
       </c>
       <c r="E534">
-        <v>-2.11305687185887</v>
+        <v>-2.169225069051532</v>
       </c>
       <c r="F534">
         <v>1</v>
       </c>
       <c r="G534">
-        <v>0.01344791622413415</v>
+        <v>0.01376218430858061</v>
       </c>
       <c r="H534">
-        <v>0.01631305687185887</v>
+        <v>0.01612922506905153</v>
       </c>
       <c r="I534">
-        <v>0.6948593522752819</v>
+        <v>1.132959239529082</v>
       </c>
       <c r="J534">
         <v>2.127726760244542</v>
       </c>
       <c r="K534">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L534">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M534">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N534">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O534">
         <v>1</v>
@@ -28240,96 +28240,96 @@
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B535" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C535">
-        <v>-3.440693413369869</v>
+        <v>-2.807916224134152</v>
       </c>
       <c r="D535" t="s">
         <v>162</v>
       </c>
       <c r="E535">
-        <v>-2.262619072292154</v>
+        <v>-2.169225069051532</v>
       </c>
       <c r="F535">
         <v>1</v>
       </c>
       <c r="G535">
-        <v>0.01390069341336987</v>
+        <v>0.01344791622413415</v>
       </c>
       <c r="H535">
-        <v>0.01646261907229215</v>
+        <v>0.01612922506905153</v>
       </c>
       <c r="I535">
-        <v>1.178074341077716</v>
+        <v>0.6386911550826202</v>
       </c>
       <c r="J535">
-        <v>2.162267684132137</v>
+        <v>2.127726760244542</v>
       </c>
       <c r="K535">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L535">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M535">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N535">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B536" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C536">
-        <v>-2.939862553384764</v>
+        <v>-3.440693413369869</v>
       </c>
       <c r="D536" t="s">
         <v>162</v>
       </c>
       <c r="E536">
-        <v>-2.262619072292154</v>
+        <v>-2.317751041768188</v>
       </c>
       <c r="F536">
         <v>1</v>
       </c>
       <c r="G536">
-        <v>0.01357986255338476</v>
+        <v>0.01390069341336987</v>
       </c>
       <c r="H536">
-        <v>0.01646261907229215</v>
+        <v>0.01627775104176819</v>
       </c>
       <c r="I536">
-        <v>0.67724348109261</v>
+        <v>1.122942371601681</v>
       </c>
       <c r="J536">
         <v>2.162267684132137</v>
       </c>
       <c r="K536">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L536">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M536">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N536">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O536">
         <v>1</v>
@@ -28340,96 +28340,96 @@
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B537" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C537">
-        <v>-3.668901415448289</v>
+        <v>-2.939862553384764</v>
       </c>
       <c r="D537" t="s">
         <v>162</v>
       </c>
       <c r="E537">
-        <v>-2.509038186755884</v>
+        <v>-2.317751041768188</v>
       </c>
       <c r="F537">
         <v>1</v>
       </c>
       <c r="G537">
-        <v>0.01412890141544829</v>
+        <v>0.01357986255338476</v>
       </c>
       <c r="H537">
-        <v>0.01670903818675588</v>
+        <v>0.01627775104176819</v>
       </c>
       <c r="I537">
-        <v>1.159863228692405</v>
+        <v>0.6221115116165752</v>
       </c>
       <c r="J537">
-        <v>2.219177410336232</v>
+        <v>2.162267684132137</v>
       </c>
       <c r="K537">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L537">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M537">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N537">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O537">
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B538" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C538">
-        <v>-3.157257707484405</v>
+        <v>-3.668901415448289</v>
       </c>
       <c r="D538" t="s">
         <v>162</v>
       </c>
       <c r="E538">
-        <v>-2.509038186755884</v>
+        <v>-2.562462864445797</v>
       </c>
       <c r="F538">
         <v>1</v>
       </c>
       <c r="G538">
-        <v>0.01379725770748441</v>
+        <v>0.01412890141544829</v>
       </c>
       <c r="H538">
-        <v>0.01670903818675588</v>
+        <v>0.0165224628644458</v>
       </c>
       <c r="I538">
-        <v>0.6482195207285208</v>
+        <v>1.106438551002492</v>
       </c>
       <c r="J538">
         <v>2.219177410336232</v>
       </c>
       <c r="K538">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L538">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M538">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N538">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28440,96 +28440,96 @@
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B539" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C539">
-        <v>-3.954888865249114</v>
+        <v>-3.157257707484405</v>
       </c>
       <c r="D539" t="s">
         <v>162</v>
       </c>
       <c r="E539">
-        <v>-2.817847577687948</v>
+        <v>-2.562462864445797</v>
       </c>
       <c r="F539">
         <v>1</v>
       </c>
       <c r="G539">
-        <v>0.01441488886524911</v>
+        <v>0.01379725770748441</v>
       </c>
       <c r="H539">
-        <v>0.01701784757768795</v>
+        <v>0.0165224628644458</v>
       </c>
       <c r="I539">
-        <v>1.137041287561166</v>
+        <v>0.5947948430386081</v>
       </c>
       <c r="J539">
-        <v>2.29049597637135</v>
+        <v>2.219177410336232</v>
       </c>
       <c r="K539">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L539">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M539">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N539">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B540" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C540">
-        <v>-3.429694629738558</v>
+        <v>-3.954888865249114</v>
       </c>
       <c r="D540" t="s">
         <v>162</v>
       </c>
       <c r="E540">
-        <v>-2.817847577687948</v>
+        <v>-2.869132698396806</v>
       </c>
       <c r="F540">
         <v>1</v>
       </c>
       <c r="G540">
-        <v>0.01406969462973856</v>
+        <v>0.01441488886524911</v>
       </c>
       <c r="H540">
-        <v>0.01701784757768795</v>
+        <v>0.01682913269839681</v>
       </c>
       <c r="I540">
-        <v>0.6118470520506101</v>
+        <v>1.085756166852308</v>
       </c>
       <c r="J540">
         <v>2.29049597637135</v>
       </c>
       <c r="K540">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L540">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M540">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N540">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28540,96 +28540,96 @@
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B541" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C541">
-        <v>-4.162550774568617</v>
+        <v>-3.429694629738558</v>
       </c>
       <c r="D541" t="s">
         <v>162</v>
       </c>
       <c r="E541">
-        <v>-3.042081010943171</v>
+        <v>-2.869132698396806</v>
       </c>
       <c r="F541">
         <v>1</v>
       </c>
       <c r="G541">
-        <v>0.01462255077456862</v>
+        <v>0.01406969462973856</v>
       </c>
       <c r="H541">
-        <v>0.01724208101094317</v>
+        <v>0.01682913269839681</v>
       </c>
       <c r="I541">
-        <v>1.120469763625445</v>
+        <v>0.560561931341752</v>
       </c>
       <c r="J541">
-        <v>2.342281988670478</v>
+        <v>2.29049597637135</v>
       </c>
       <c r="K541">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L541">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M541">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N541">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C542">
-        <v>-3.627517196721227</v>
+        <v>-4.162550774568617</v>
       </c>
       <c r="D542" t="s">
         <v>162</v>
       </c>
       <c r="E542">
-        <v>-3.042081010943171</v>
+        <v>-3.091812551283056</v>
       </c>
       <c r="F542">
         <v>1</v>
       </c>
       <c r="G542">
-        <v>0.01426751719672123</v>
+        <v>0.01462255077456862</v>
       </c>
       <c r="H542">
-        <v>0.01724208101094317</v>
+        <v>0.01705181255128306</v>
       </c>
       <c r="I542">
-        <v>0.5854361857780557</v>
+        <v>1.070738223285561</v>
       </c>
       <c r="J542">
         <v>2.342281988670478</v>
       </c>
       <c r="K542">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L542">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M542">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N542">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28640,96 +28640,96 @@
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B543" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C543">
-        <v>-4.341021841271511</v>
+        <v>-3.627517196721227</v>
       </c>
       <c r="D543" t="s">
         <v>162</v>
       </c>
       <c r="E543">
-        <v>-3.234794157781957</v>
+        <v>-3.091812551283056</v>
       </c>
       <c r="F543">
         <v>1</v>
       </c>
       <c r="G543">
-        <v>0.01480102184127151</v>
+        <v>0.01426751719672123</v>
       </c>
       <c r="H543">
-        <v>0.01743479415778196</v>
+        <v>0.01705181255128306</v>
       </c>
       <c r="I543">
-        <v>1.106227683489553</v>
+        <v>0.5357046454381713</v>
       </c>
       <c r="J543">
-        <v>2.38678848909514</v>
+        <v>2.342281988670478</v>
       </c>
       <c r="K543">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L543">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M543">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N543">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B544" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C544">
-        <v>-3.797532028343435</v>
+        <v>-4.341021841271511</v>
       </c>
       <c r="D544" t="s">
         <v>162</v>
       </c>
       <c r="E544">
-        <v>-3.234794157781957</v>
+        <v>-3.283190503109102</v>
       </c>
       <c r="F544">
         <v>1</v>
       </c>
       <c r="G544">
-        <v>0.01443753202834343</v>
+        <v>0.01480102184127151</v>
       </c>
       <c r="H544">
-        <v>0.01743479415778196</v>
+        <v>0.0172431905031091</v>
       </c>
       <c r="I544">
-        <v>0.5627378705614774</v>
+        <v>1.057831338162408</v>
       </c>
       <c r="J544">
         <v>2.38678848909514</v>
       </c>
       <c r="K544">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L544">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M544">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N544">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28740,96 +28740,96 @@
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B545" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C545">
-        <v>-4.38270256915019</v>
+        <v>-3.797532028343435</v>
       </c>
       <c r="D545" t="s">
         <v>162</v>
       </c>
       <c r="E545">
-        <v>-3.279801028533749</v>
+        <v>-3.283190503109102</v>
       </c>
       <c r="F545">
         <v>1</v>
       </c>
       <c r="G545">
-        <v>0.01484270256915019</v>
+        <v>0.01443753202834343</v>
       </c>
       <c r="H545">
-        <v>0.01747980102853375</v>
+        <v>0.0172431905031091</v>
       </c>
       <c r="I545">
-        <v>1.102901540616442</v>
+        <v>0.5143415252343324</v>
       </c>
       <c r="J545">
-        <v>2.397182685573614</v>
+        <v>2.38678848909514</v>
       </c>
       <c r="K545">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L545">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M545">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N545">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B546" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C546">
-        <v>-3.837237858891204</v>
+        <v>-4.38270256915019</v>
       </c>
       <c r="D546" t="s">
         <v>162</v>
       </c>
       <c r="E546">
-        <v>-3.279801028533749</v>
+        <v>-3.327885547966538</v>
       </c>
       <c r="F546">
         <v>1</v>
       </c>
       <c r="G546">
-        <v>0.01447723785889121</v>
+        <v>0.01484270256915019</v>
       </c>
       <c r="H546">
-        <v>0.01747980102853375</v>
+        <v>0.01728788554796654</v>
       </c>
       <c r="I546">
-        <v>0.5574368303574548</v>
+        <v>1.054817021183652</v>
       </c>
       <c r="J546">
         <v>2.397182685573614</v>
       </c>
       <c r="K546">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L546">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M546">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N546">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28840,96 +28840,96 @@
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B547" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C547">
-        <v>-4.411855003341485</v>
+        <v>-3.837237858891204</v>
       </c>
       <c r="D547" t="s">
         <v>162</v>
       </c>
       <c r="E547">
-        <v>-3.311279841513375</v>
+        <v>-3.327885547966538</v>
       </c>
       <c r="F547">
         <v>1</v>
       </c>
       <c r="G547">
-        <v>0.01487185500334148</v>
+        <v>0.01447723785889121</v>
       </c>
       <c r="H547">
-        <v>0.01751127984151337</v>
+        <v>0.01728788554796654</v>
       </c>
       <c r="I547">
-        <v>1.100575161828109</v>
+        <v>0.5093523109246654</v>
       </c>
       <c r="J547">
-        <v>2.404452619287154</v>
+        <v>2.397182685573614</v>
       </c>
       <c r="K547">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L547">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M547">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N547">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B548" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C548">
-        <v>-3.865009005676926</v>
+        <v>-4.411855003341485</v>
       </c>
       <c r="D548" t="s">
         <v>162</v>
       </c>
       <c r="E548">
-        <v>-3.311279841513375</v>
+        <v>-3.359146262934759</v>
       </c>
       <c r="F548">
         <v>1</v>
       </c>
       <c r="G548">
-        <v>0.01450500900567693</v>
+        <v>0.01487185500334148</v>
       </c>
       <c r="H548">
-        <v>0.01751127984151337</v>
+        <v>0.01731914626293476</v>
       </c>
       <c r="I548">
-        <v>0.5537291641635509</v>
+        <v>1.052708740406725</v>
       </c>
       <c r="J548">
         <v>2.404452619287154</v>
       </c>
       <c r="K548">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L548">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M548">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N548">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -28952,7 +28952,7 @@
         <v>162</v>
       </c>
       <c r="E549">
-        <v>-3.232905202530501</v>
+        <v>-3.281314635307425</v>
       </c>
       <c r="F549">
         <v>1</v>
@@ -28961,10 +28961,10 @@
         <v>0.01479927248548437</v>
       </c>
       <c r="H549">
-        <v>0.0174329052025305</v>
+        <v>0.01724131463530743</v>
       </c>
       <c r="I549">
-        <v>1.106367282953864</v>
+        <v>1.05795785017694</v>
       </c>
       <c r="J549">
         <v>2.386352240769169</v>
@@ -28976,10 +28976,10 @@
         <v>5.23</v>
       </c>
       <c r="M549">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N549">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -29002,7 +29002,7 @@
         <v>162</v>
       </c>
       <c r="E550">
-        <v>-3.167083863888037</v>
+        <v>-3.215949333653246</v>
       </c>
       <c r="F550">
         <v>1</v>
@@ -29011,10 +29011,10 @@
         <v>0.01473831554138361</v>
       </c>
       <c r="H550">
-        <v>0.01736708386388804</v>
+        <v>0.01717594933365325</v>
       </c>
       <c r="I550">
-        <v>1.111231677495571</v>
+        <v>1.062366207730362</v>
       </c>
       <c r="J550">
         <v>2.371151007826336</v>
@@ -29026,10 +29026,10 @@
         <v>5.23</v>
       </c>
       <c r="M550">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N550">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O550">
         <v>1</v>
@@ -29052,7 +29052,7 @@
         <v>162</v>
       </c>
       <c r="E551">
-        <v>-3.099442561338748</v>
+        <v>-3.148776677541942</v>
       </c>
       <c r="F551">
         <v>1</v>
@@ -29061,10 +29061,10 @@
         <v>0.01467567313417283</v>
       </c>
       <c r="H551">
-        <v>0.01729944256133875</v>
+        <v>0.01710877667754194</v>
       </c>
       <c r="I551">
-        <v>1.116230572834086</v>
+        <v>1.066896456630891</v>
       </c>
       <c r="J551">
         <v>2.355529459893475</v>
@@ -29076,10 +29076,10 @@
         <v>5.23</v>
       </c>
       <c r="M551">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N551">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O551">
         <v>1</v>
@@ -29102,7 +29102,7 @@
         <v>162</v>
       </c>
       <c r="E552">
-        <v>-3.071543529042639</v>
+        <v>-3.121070941081603</v>
       </c>
       <c r="F552">
         <v>1</v>
@@ -29111,10 +29111,10 @@
         <v>0.01464983592412494</v>
       </c>
       <c r="H552">
-        <v>0.01727154352904264</v>
+        <v>0.01708107094108161</v>
       </c>
       <c r="I552">
-        <v>1.118292395082298</v>
+        <v>1.068764983043334</v>
       </c>
       <c r="J552">
         <v>2.349086265367815</v>
@@ -29126,10 +29126,10 @@
         <v>5.23</v>
       </c>
       <c r="M552">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N552">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -29152,7 +29152,7 @@
         <v>162</v>
       </c>
       <c r="E553">
-        <v>-2.963169221948645</v>
+        <v>-3.013447495237683</v>
       </c>
       <c r="F553">
         <v>1</v>
@@ -29161,10 +29161,10 @@
         <v>0.0145494708036984</v>
       </c>
       <c r="H553">
-        <v>0.01716316922194864</v>
+        <v>0.01697344749523769</v>
       </c>
       <c r="I553">
-        <v>1.126301581749752</v>
+        <v>1.076023308460714</v>
       </c>
       <c r="J553">
         <v>2.324057557032019</v>
@@ -29176,10 +29176,10 @@
         <v>5.23</v>
       </c>
       <c r="M553">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N553">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O553">
         <v>1</v>
@@ -29202,7 +29202,7 @@
         <v>162</v>
       </c>
       <c r="E554">
-        <v>-2.872303462099412</v>
+        <v>-2.923211290306574</v>
       </c>
       <c r="F554">
         <v>1</v>
@@ -29211,10 +29211,10 @@
         <v>0.01446532029630916</v>
       </c>
       <c r="H554">
-        <v>0.01707230346209941</v>
+        <v>0.01688321129030658</v>
       </c>
       <c r="I554">
-        <v>1.133016834209743</v>
+        <v>1.082109006002581</v>
       </c>
       <c r="J554">
         <v>2.303072393094552</v>
@@ -29226,10 +29226,10 @@
         <v>5.23</v>
       </c>
       <c r="M554">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N554">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O554">
         <v>1</v>
@@ -29252,7 +29252,7 @@
         <v>162</v>
       </c>
       <c r="E555">
-        <v>-2.737006005668432</v>
+        <v>-2.788851229647632</v>
       </c>
       <c r="F555">
         <v>1</v>
@@ -29261,10 +29261,10 @@
         <v>0.01434002172811326</v>
       </c>
       <c r="H555">
-        <v>0.01693700600566843</v>
+        <v>0.01674885122964764</v>
       </c>
       <c r="I555">
-        <v>1.143015722444826</v>
+        <v>1.091170498465626</v>
       </c>
       <c r="J555">
         <v>2.271825867359915</v>
@@ -29276,10 +29276,10 @@
         <v>5.23</v>
       </c>
       <c r="M555">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N555">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O555">
         <v>1</v>
@@ -29302,7 +29302,7 @@
         <v>162</v>
       </c>
       <c r="E556">
-        <v>-2.613742043075291</v>
+        <v>-2.666441289890011</v>
       </c>
       <c r="F556">
         <v>1</v>
@@ -29311,10 +29311,10 @@
         <v>0.01422586734243231</v>
       </c>
       <c r="H556">
-        <v>0.01681374204307529</v>
+        <v>0.01662644128989001</v>
       </c>
       <c r="I556">
-        <v>1.152125299357021</v>
+        <v>1.099426052542301</v>
       </c>
       <c r="J556">
         <v>2.243358439509305</v>
@@ -29326,10 +29326,10 @@
         <v>5.23</v>
       </c>
       <c r="M556">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="N556">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="O556">
         <v>1</v>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="391">
   <si>
     <t>trade_time</t>
   </si>
@@ -226,289 +226,292 @@
     <t>2021-08-23</t>
   </si>
   <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-09-13</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-11-08</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-11-21</t>
+  </si>
+  <si>
+    <t>2017-10-25</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>2017-11-07</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2018-06-26</t>
+  </si>
+  <si>
+    <t>2018-06-27</t>
+  </si>
+  <si>
+    <t>2018-06-28</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-03</t>
+  </si>
+  <si>
+    <t>2018-09-14</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-09-26</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-25</t>
+  </si>
+  <si>
+    <t>2018-10-26</t>
+  </si>
+  <si>
+    <t>2018-10-29</t>
+  </si>
+  <si>
+    <t>2018-10-30</t>
+  </si>
+  <si>
+    <t>2018-10-31</t>
+  </si>
+  <si>
+    <t>2018-11-01</t>
+  </si>
+  <si>
+    <t>2018-11-02</t>
+  </si>
+  <si>
+    <t>2018-11-05</t>
+  </si>
+  <si>
+    <t>2018-11-06</t>
+  </si>
+  <si>
+    <t>2018-11-07</t>
+  </si>
+  <si>
+    <t>2018-11-08</t>
+  </si>
+  <si>
+    <t>2018-11-09</t>
+  </si>
+  <si>
+    <t>2018-11-12</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>2018-11-14</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2018-11-21</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-23</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-11-27</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-06-17</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-07-29</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-07</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-11</t>
+  </si>
+  <si>
+    <t>2020-02-12</t>
+  </si>
+  <si>
+    <t>2020-02-17</t>
+  </si>
+  <si>
+    <t>2020-02-18</t>
+  </si>
+  <si>
+    <t>2020-02-19</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-10</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-24</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-03-27</t>
+  </si>
+  <si>
+    <t>2020-03-30</t>
+  </si>
+  <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-04-02</t>
+  </si>
+  <si>
+    <t>2020-04-03</t>
+  </si>
+  <si>
+    <t>2020-04-07</t>
+  </si>
+  <si>
+    <t>2020-04-08</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-14</t>
+  </si>
+  <si>
     <t>2021-09-06</t>
   </si>
   <si>
     <t>2021-09-10</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-11-08</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-11-21</t>
-  </si>
-  <si>
-    <t>2017-10-25</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-11-06</t>
-  </si>
-  <si>
-    <t>2017-11-07</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2018-06-26</t>
-  </si>
-  <si>
-    <t>2018-06-27</t>
-  </si>
-  <si>
-    <t>2018-06-28</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-03</t>
-  </si>
-  <si>
-    <t>2018-09-14</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-09-26</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-25</t>
-  </si>
-  <si>
-    <t>2018-10-26</t>
-  </si>
-  <si>
-    <t>2018-10-29</t>
-  </si>
-  <si>
-    <t>2018-10-30</t>
-  </si>
-  <si>
-    <t>2018-10-31</t>
-  </si>
-  <si>
-    <t>2018-11-01</t>
-  </si>
-  <si>
-    <t>2018-11-02</t>
-  </si>
-  <si>
-    <t>2018-11-05</t>
-  </si>
-  <si>
-    <t>2018-11-06</t>
-  </si>
-  <si>
-    <t>2018-11-07</t>
-  </si>
-  <si>
-    <t>2018-11-08</t>
-  </si>
-  <si>
-    <t>2018-11-09</t>
-  </si>
-  <si>
-    <t>2018-11-12</t>
-  </si>
-  <si>
-    <t>2018-11-13</t>
-  </si>
-  <si>
-    <t>2018-11-14</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-20</t>
-  </si>
-  <si>
-    <t>2018-11-21</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-23</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-11-27</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-06-17</t>
-  </si>
-  <si>
-    <t>2019-06-19</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-07-29</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-07</t>
-  </si>
-  <si>
-    <t>2020-02-10</t>
-  </si>
-  <si>
-    <t>2020-02-11</t>
-  </si>
-  <si>
-    <t>2020-02-12</t>
-  </si>
-  <si>
-    <t>2020-02-17</t>
-  </si>
-  <si>
-    <t>2020-02-18</t>
-  </si>
-  <si>
-    <t>2020-02-19</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-10</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-24</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-03-27</t>
-  </si>
-  <si>
-    <t>2020-03-30</t>
-  </si>
-  <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-04-02</t>
-  </si>
-  <si>
-    <t>2020-04-03</t>
-  </si>
-  <si>
-    <t>2020-04-07</t>
-  </si>
-  <si>
-    <t>2020-04-08</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-09-13</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -1541,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P560"/>
+  <dimension ref="A1:P562"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1638,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1688,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1738,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1788,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1838,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1888,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1938,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1988,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2038,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2088,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2138,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2188,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2238,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2288,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2338,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2388,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2438,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2488,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2538,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2588,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2638,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2688,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2738,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2788,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2838,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2888,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2938,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2988,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3038,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3088,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3138,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3188,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3238,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3288,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3338,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3388,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3438,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3488,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3538,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3588,7 +3591,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3638,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3688,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3738,7 +3741,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3788,7 +3791,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3838,7 +3841,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3888,7 +3891,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3938,7 +3941,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3988,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4038,7 +4041,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4088,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4138,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4188,7 +4191,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4238,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4288,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4338,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4388,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4438,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4488,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4538,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4588,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4638,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4688,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4738,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4788,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4838,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4888,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4938,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4988,7 +4991,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5038,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5088,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5138,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5188,7 +5191,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5238,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5288,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5338,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5388,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5438,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5488,7 +5491,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5538,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5588,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5638,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5688,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5738,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5788,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5838,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5888,7 +5891,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5938,7 +5941,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5988,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6038,7 +6041,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6088,7 +6091,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6138,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6188,7 +6191,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6238,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6288,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6338,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6388,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6438,7 +6441,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6488,7 +6491,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6538,7 +6541,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6588,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6638,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6688,7 +6691,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6738,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6788,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6838,7 +6841,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6888,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6938,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6988,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7038,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7088,7 +7091,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7138,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7188,7 +7191,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7238,7 +7241,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7288,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7338,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7388,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7438,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7488,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7538,7 +7541,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7588,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7638,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7688,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7738,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7788,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7838,7 +7841,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7888,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7938,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7988,7 +7991,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8038,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8088,7 +8091,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8138,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8188,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8238,7 +8241,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8288,7 +8291,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8338,7 +8341,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8388,7 +8391,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8438,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8488,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8538,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8638,7 +8641,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8688,7 +8691,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8738,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8788,7 +8791,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8838,7 +8841,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8888,7 +8891,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8938,7 +8941,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8988,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9038,7 +9041,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9088,7 +9091,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9138,7 +9141,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9188,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9238,7 +9241,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9288,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9338,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9388,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9438,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9488,7 +9491,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9538,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9588,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9688,7 +9691,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9738,7 +9741,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9788,7 +9791,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9938,7 +9941,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9988,7 +9991,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10038,7 +10041,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10088,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10138,7 +10141,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10188,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10238,7 +10241,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10288,7 +10291,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10388,7 +10391,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10438,7 +10441,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10588,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10638,7 +10641,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10688,7 +10691,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10738,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11238,7 +11241,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11288,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11338,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11388,7 +11391,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11438,7 +11441,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11488,7 +11491,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11538,7 +11541,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11588,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11638,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11688,7 +11691,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11738,7 +11741,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11788,7 +11791,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11838,7 +11841,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11888,7 +11891,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11938,7 +11941,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12738,7 +12741,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12788,7 +12791,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12838,7 +12841,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12888,7 +12891,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12938,7 +12941,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12988,7 +12991,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13038,7 +13041,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13088,7 +13091,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13138,7 +13141,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13188,7 +13191,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13238,7 +13241,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13288,7 +13291,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13338,7 +13341,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13388,7 +13391,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13438,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13488,7 +13491,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13538,7 +13541,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13588,7 +13591,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13638,7 +13641,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13688,7 +13691,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13838,7 +13841,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13888,7 +13891,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13938,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14038,7 +14041,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14188,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14238,7 +14241,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14288,7 +14291,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14338,7 +14341,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14388,7 +14391,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14438,7 +14441,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14488,7 +14491,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14588,7 +14591,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14638,7 +14641,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14688,7 +14691,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14738,7 +14741,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14788,7 +14791,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14838,7 +14841,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14888,7 +14891,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14938,7 +14941,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14988,7 +14991,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15038,7 +15041,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15088,7 +15091,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15138,7 +15141,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15188,7 +15191,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15238,7 +15241,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15288,7 +15291,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15338,7 +15341,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15388,7 +15391,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15438,7 +15441,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15488,7 +15491,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15538,7 +15541,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15588,7 +15591,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15638,7 +15641,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15688,7 +15691,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15738,7 +15741,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15788,7 +15791,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15838,7 +15841,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15888,7 +15891,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15938,7 +15941,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15988,7 +15991,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16038,7 +16041,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16088,7 +16091,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16138,7 +16141,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16188,7 +16191,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16238,7 +16241,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16288,7 +16291,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16338,7 +16341,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16388,7 +16391,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16438,7 +16441,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16488,7 +16491,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16538,7 +16541,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16588,7 +16591,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16638,7 +16641,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16688,7 +16691,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16738,7 +16741,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16788,7 +16791,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16838,7 +16841,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16888,7 +16891,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16938,7 +16941,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17138,7 +17141,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17188,7 +17191,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17238,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17288,7 +17291,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17338,7 +17341,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17388,7 +17391,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17438,7 +17441,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17488,7 +17491,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17538,7 +17541,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17588,7 +17591,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17638,7 +17641,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17688,7 +17691,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17738,7 +17741,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17788,7 +17791,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17838,7 +17841,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17888,7 +17891,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17938,7 +17941,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17988,7 +17991,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18038,7 +18041,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18088,7 +18091,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18138,7 +18141,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18188,7 +18191,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18238,7 +18241,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18288,7 +18291,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18338,7 +18341,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18588,7 +18591,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18638,7 +18641,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18688,7 +18691,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18738,7 +18741,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18788,7 +18791,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18838,7 +18841,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18888,7 +18891,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18938,7 +18941,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18988,7 +18991,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19038,7 +19041,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19088,7 +19091,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19138,7 +19141,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19588,7 +19591,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19638,7 +19641,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19688,7 +19691,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19738,7 +19741,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19788,7 +19791,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19838,7 +19841,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19888,7 +19891,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19938,7 +19941,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19988,7 +19991,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20038,7 +20041,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20088,7 +20091,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20138,7 +20141,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20188,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20238,7 +20241,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20288,7 +20291,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20338,7 +20341,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20538,7 +20541,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20588,7 +20591,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20638,7 +20641,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20688,7 +20691,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20888,7 +20891,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20938,7 +20941,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20988,7 +20991,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21038,7 +21041,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21088,7 +21091,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21138,7 +21141,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21188,7 +21191,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21238,7 +21241,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21288,7 +21291,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21338,7 +21341,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21388,7 +21391,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21438,7 +21441,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21488,7 +21491,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21538,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21588,7 +21591,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21638,7 +21641,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21688,7 +21691,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21738,7 +21741,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21788,7 +21791,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21838,7 +21841,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21888,7 +21891,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21938,7 +21941,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21988,7 +21991,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22038,7 +22041,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22088,7 +22091,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22138,7 +22141,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22188,7 +22191,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22238,7 +22241,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22288,7 +22291,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22338,7 +22341,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22388,7 +22391,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22438,7 +22441,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22488,7 +22491,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22688,7 +22691,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22738,7 +22741,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22788,7 +22791,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22838,7 +22841,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22888,7 +22891,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22938,7 +22941,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23138,7 +23141,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23188,7 +23191,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23238,7 +23241,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23288,7 +23291,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23338,7 +23341,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23388,7 +23391,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23438,7 +23441,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23488,7 +23491,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23538,7 +23541,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23588,7 +23591,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23638,7 +23641,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23688,7 +23691,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23738,7 +23741,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23788,7 +23791,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23838,7 +23841,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23888,7 +23891,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23938,7 +23941,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23988,7 +23991,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24038,7 +24041,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24088,7 +24091,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24138,7 +24141,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24188,7 +24191,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24238,7 +24241,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24288,7 +24291,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24338,7 +24341,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24388,7 +24391,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24438,7 +24441,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24488,7 +24491,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24538,7 +24541,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24588,7 +24591,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24638,7 +24641,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24688,7 +24691,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24738,7 +24741,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24788,7 +24791,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24838,7 +24841,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24888,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24938,7 +24941,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24988,7 +24991,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25038,7 +25041,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25088,7 +25091,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25138,7 +25141,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25188,7 +25191,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25488,7 +25491,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25538,7 +25541,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25588,7 +25591,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25638,7 +25641,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25688,7 +25691,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25738,7 +25741,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25788,7 +25791,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25838,7 +25841,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25888,7 +25891,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25938,7 +25941,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25988,7 +25991,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26038,7 +26041,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26088,7 +26091,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26138,7 +26141,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26188,7 +26191,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26238,7 +26241,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26288,7 +26291,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26338,7 +26341,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26388,7 +26391,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26438,7 +26441,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26488,7 +26491,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26538,7 +26541,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26588,7 +26591,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26638,7 +26641,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26688,7 +26691,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26738,7 +26741,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26788,7 +26791,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26838,7 +26841,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26888,7 +26891,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26938,7 +26941,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26988,7 +26991,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27038,7 +27041,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27088,7 +27091,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27138,7 +27141,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27188,7 +27191,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27238,7 +27241,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27288,7 +27291,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27338,7 +27341,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27388,7 +27391,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27438,7 +27441,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27488,7 +27491,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27538,7 +27541,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27588,7 +27591,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27638,7 +27641,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27649,46 +27652,46 @@
         <v>70</v>
       </c>
       <c r="C523">
-        <v>0.1222855810721351</v>
+        <v>0.1441551924455533</v>
       </c>
       <c r="D523" t="s">
         <v>163</v>
       </c>
       <c r="E523">
-        <v>0.296648007610111</v>
+        <v>0.3168915412582125</v>
       </c>
       <c r="F523">
         <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.01453771441892787</v>
+        <v>0.01407584480755445</v>
       </c>
       <c r="H523">
-        <v>0.01358335199238989</v>
+        <v>0.01302310845874179</v>
       </c>
       <c r="I523">
-        <v>-0.174362426537976</v>
+        <v>-0.1727363488126592</v>
       </c>
       <c r="J523">
         <v>1.612464075822789</v>
       </c>
       <c r="K523">
-        <v>4.47</v>
+        <v>4.32</v>
       </c>
       <c r="L523">
-        <v>7.33</v>
+        <v>7.11</v>
       </c>
       <c r="M523">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N523">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27699,46 +27702,46 @@
         <v>71</v>
       </c>
       <c r="C524">
-        <v>0.1205233668518835</v>
+        <v>0.296648007610111</v>
       </c>
       <c r="D524" t="s">
         <v>163</v>
       </c>
       <c r="E524">
-        <v>0.296648007610111</v>
+        <v>0.3168915412582125</v>
       </c>
       <c r="F524">
         <v>-1</v>
       </c>
       <c r="G524">
-        <v>0.01343947663314812</v>
+        <v>0.01358335199238989</v>
       </c>
       <c r="H524">
-        <v>0.01358335199238989</v>
+        <v>0.01302310845874179</v>
       </c>
       <c r="I524">
-        <v>-0.1761246407582275</v>
+        <v>-0.0202435336481015</v>
       </c>
       <c r="J524">
         <v>1.612464075822789</v>
       </c>
       <c r="K524">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="L524">
-        <v>6.78</v>
+        <v>6.94</v>
       </c>
       <c r="M524">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N524">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O524">
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27788,7 +27791,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27838,7 +27841,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27888,7 +27891,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27938,7 +27941,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27952,10 +27955,10 @@
         <v>-2.24491864020763</v>
       </c>
       <c r="D529" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E529">
-        <v>-1.206182658350335</v>
+        <v>-1.002390603922223</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -27964,10 +27967,10 @@
         <v>0.01270491864020763</v>
       </c>
       <c r="H529">
-        <v>0.01288618265835034</v>
+        <v>0.01566239060392222</v>
       </c>
       <c r="I529">
-        <v>1.038735981857295</v>
+        <v>1.242528036285408</v>
       </c>
       <c r="J529">
         <v>1.864069486336068</v>
@@ -27979,16 +27982,16 @@
         <v>5.23</v>
       </c>
       <c r="M529">
-        <v>3.78</v>
+        <v>4.47</v>
       </c>
       <c r="N529">
-        <v>5.84</v>
+        <v>7.33</v>
       </c>
       <c r="O529">
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28002,7 +28005,7 @@
         <v>-2.39134798609852</v>
       </c>
       <c r="D530" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E530">
         <v>-1.165617331137254</v>
@@ -28038,7 +28041,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28052,7 +28055,7 @@
         <v>-2.546512840679558</v>
       </c>
       <c r="D531" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E531">
         <v>-1.338581645346041</v>
@@ -28088,7 +28091,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28102,7 +28105,7 @@
         <v>-2.088049638752098</v>
       </c>
       <c r="D532" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E532">
         <v>-1.338581645346041</v>
@@ -28138,7 +28141,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28152,7 +28155,7 @@
         <v>-2.943692670373876</v>
       </c>
       <c r="D533" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="E533">
         <v>-1.695574148632207</v>
@@ -28188,7 +28191,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28202,7 +28205,7 @@
         <v>-2.466410474021997</v>
       </c>
       <c r="D534" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="E534">
         <v>-1.695574148632207</v>
@@ -28238,7 +28241,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28252,7 +28255,7 @@
         <v>-3.302184308580614</v>
       </c>
       <c r="D535" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="E535">
         <v>-2.00751151980996</v>
@@ -28288,7 +28291,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28302,7 +28305,7 @@
         <v>-2.807916224134152</v>
       </c>
       <c r="D536" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="E536">
         <v>-2.00751151980996</v>
@@ -28338,7 +28341,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28352,7 +28355,7 @@
         <v>-3.440693413369869</v>
       </c>
       <c r="D537" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E537">
         <v>-1.968542858624404</v>
@@ -28388,7 +28391,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28402,7 +28405,7 @@
         <v>-2.939862553384764</v>
       </c>
       <c r="D538" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E538">
         <v>-1.968542858624404</v>
@@ -28438,7 +28441,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28452,7 +28455,7 @@
         <v>-3.668901415448289</v>
       </c>
       <c r="D539" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E539">
         <v>-2.203010930585275</v>
@@ -28488,7 +28491,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28502,7 +28505,7 @@
         <v>-3.157257707484405</v>
       </c>
       <c r="D540" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E540">
         <v>-2.203010930585275</v>
@@ -28538,7 +28541,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28552,7 +28555,7 @@
         <v>-3.954888865249114</v>
       </c>
       <c r="D541" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E541">
         <v>-2.496843422649964</v>
@@ -28588,7 +28591,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28602,7 +28605,7 @@
         <v>-3.429694629738558</v>
       </c>
       <c r="D542" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E542">
         <v>-2.496843422649964</v>
@@ -28638,7 +28641,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28655,7 +28658,7 @@
         <v>163</v>
       </c>
       <c r="E543">
-        <v>-2.71020179332237</v>
+        <v>-2.558591035361685</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28664,10 +28667,10 @@
         <v>0.01462255077456862</v>
       </c>
       <c r="H543">
-        <v>0.01659020179332237</v>
+        <v>0.01589859103536169</v>
       </c>
       <c r="I543">
-        <v>1.452348981246247</v>
+        <v>1.603959739206932</v>
       </c>
       <c r="J543">
         <v>2.342281988670478</v>
@@ -28679,16 +28682,16 @@
         <v>5.23</v>
       </c>
       <c r="M543">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N543">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28705,7 +28708,7 @@
         <v>163</v>
       </c>
       <c r="E544">
-        <v>-2.71020179332237</v>
+        <v>-2.558591035361685</v>
       </c>
       <c r="F544">
         <v>1</v>
@@ -28714,10 +28717,10 @@
         <v>0.01426751719672123</v>
       </c>
       <c r="H544">
-        <v>0.01659020179332237</v>
+        <v>0.01589859103536169</v>
       </c>
       <c r="I544">
-        <v>0.9173154033988569</v>
+        <v>1.068926161359542</v>
       </c>
       <c r="J544">
         <v>2.342281988670478</v>
@@ -28729,16 +28732,16 @@
         <v>5.32</v>
       </c>
       <c r="M544">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N544">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28755,7 +28758,7 @@
         <v>163</v>
       </c>
       <c r="E545">
-        <v>-2.893568575071977</v>
+        <v>-2.733946647034852</v>
       </c>
       <c r="F545">
         <v>1</v>
@@ -28764,10 +28767,10 @@
         <v>0.01480102184127151</v>
       </c>
       <c r="H545">
-        <v>0.01677356857507198</v>
+        <v>0.01607394664703485</v>
       </c>
       <c r="I545">
-        <v>1.447453266199534</v>
+        <v>1.607075194236659</v>
       </c>
       <c r="J545">
         <v>2.38678848909514</v>
@@ -28779,16 +28782,16 @@
         <v>5.23</v>
       </c>
       <c r="M545">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N545">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28805,7 +28808,7 @@
         <v>163</v>
       </c>
       <c r="E546">
-        <v>-2.893568575071977</v>
+        <v>-2.733946647034852</v>
       </c>
       <c r="F546">
         <v>1</v>
@@ -28814,10 +28817,10 @@
         <v>0.01443753202834343</v>
       </c>
       <c r="H546">
-        <v>0.01677356857507198</v>
+        <v>0.01607394664703485</v>
       </c>
       <c r="I546">
-        <v>0.9039634532714578</v>
+        <v>1.063585381308583</v>
       </c>
       <c r="J546">
         <v>2.38678848909514</v>
@@ -28829,16 +28832,16 @@
         <v>5.32</v>
       </c>
       <c r="M546">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N546">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28855,7 +28858,7 @@
         <v>163</v>
       </c>
       <c r="E547">
-        <v>-2.936392664563289</v>
+        <v>-2.774899781160038</v>
       </c>
       <c r="F547">
         <v>1</v>
@@ -28864,10 +28867,10 @@
         <v>0.01484270256915019</v>
       </c>
       <c r="H547">
-        <v>0.01681639266456329</v>
+        <v>0.01611489978116004</v>
       </c>
       <c r="I547">
-        <v>1.446309904586902</v>
+        <v>1.607802787990153</v>
       </c>
       <c r="J547">
         <v>2.397182685573614</v>
@@ -28879,16 +28882,16 @@
         <v>5.23</v>
       </c>
       <c r="M547">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N547">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28905,7 +28908,7 @@
         <v>163</v>
       </c>
       <c r="E548">
-        <v>-2.936392664563289</v>
+        <v>-2.774899781160038</v>
       </c>
       <c r="F548">
         <v>1</v>
@@ -28914,10 +28917,10 @@
         <v>0.01447723785889121</v>
       </c>
       <c r="H548">
-        <v>0.01681639266456329</v>
+        <v>0.01611489978116004</v>
       </c>
       <c r="I548">
-        <v>0.900845194327915</v>
+        <v>1.062338077731166</v>
       </c>
       <c r="J548">
         <v>2.397182685573614</v>
@@ -28929,16 +28932,16 @@
         <v>5.32</v>
       </c>
       <c r="M548">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N548">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28955,7 +28958,7 @@
         <v>163</v>
       </c>
       <c r="E549">
-        <v>-2.966344791463073</v>
+        <v>-2.803543319991386</v>
       </c>
       <c r="F549">
         <v>1</v>
@@ -28964,10 +28967,10 @@
         <v>0.01487185500334148</v>
       </c>
       <c r="H549">
-        <v>0.01684634479146307</v>
+        <v>0.01614354331999139</v>
       </c>
       <c r="I549">
-        <v>1.445510211878411</v>
+        <v>1.608311683350099</v>
       </c>
       <c r="J549">
         <v>2.404452619287154</v>
@@ -28979,16 +28982,16 @@
         <v>5.23</v>
       </c>
       <c r="M549">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N549">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O549">
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29005,7 +29008,7 @@
         <v>163</v>
       </c>
       <c r="E550">
-        <v>-2.966344791463073</v>
+        <v>-2.803543319991386</v>
       </c>
       <c r="F550">
         <v>1</v>
@@ -29014,10 +29017,10 @@
         <v>0.01450500900567693</v>
       </c>
       <c r="H550">
-        <v>0.01684634479146307</v>
+        <v>0.01614354331999139</v>
       </c>
       <c r="I550">
-        <v>0.898664214213853</v>
+        <v>1.06146568568554</v>
       </c>
       <c r="J550">
         <v>2.404452619287154</v>
@@ -29029,16 +29032,16 @@
         <v>5.32</v>
       </c>
       <c r="M550">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N550">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29055,7 +29058,7 @@
         <v>163</v>
       </c>
       <c r="E551">
-        <v>-2.891771231968975</v>
+        <v>-2.732227828630524</v>
       </c>
       <c r="F551">
         <v>1</v>
@@ -29064,10 +29067,10 @@
         <v>0.01479927248548437</v>
       </c>
       <c r="H551">
-        <v>0.01677177123196898</v>
+        <v>0.01607222782863052</v>
       </c>
       <c r="I551">
-        <v>1.44750125351539</v>
+        <v>1.607044656853841</v>
       </c>
       <c r="J551">
         <v>2.386352240769169</v>
@@ -29079,60 +29082,60 @@
         <v>5.23</v>
       </c>
       <c r="M551">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N551">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="552" spans="1:16">
       <c r="A552" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B552" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C552">
-        <v>-4.278315541383607</v>
+        <v>-3.795865559738223</v>
       </c>
       <c r="D552" t="s">
         <v>163</v>
       </c>
       <c r="E552">
-        <v>-2.829142152244505</v>
+        <v>-2.732227828630524</v>
       </c>
       <c r="F552">
         <v>1</v>
       </c>
       <c r="G552">
-        <v>0.01473831554138361</v>
+        <v>0.01443586555973822</v>
       </c>
       <c r="H552">
-        <v>0.01670914215224451</v>
+        <v>0.01607222782863052</v>
       </c>
       <c r="I552">
-        <v>1.449173389139102</v>
+        <v>1.063637731107699</v>
       </c>
       <c r="J552">
-        <v>2.371151007826336</v>
+        <v>2.386352240769169</v>
       </c>
       <c r="K552">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L552">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M552">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N552">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -29149,28 +29152,28 @@
         <v>69</v>
       </c>
       <c r="C553">
-        <v>-4.215673134172834</v>
+        <v>-4.278315541383607</v>
       </c>
       <c r="D553" t="s">
         <v>163</v>
       </c>
       <c r="E553">
-        <v>-2.764781374761117</v>
+        <v>-2.672334970835765</v>
       </c>
       <c r="F553">
         <v>1</v>
       </c>
       <c r="G553">
-        <v>0.01467567313417283</v>
+        <v>0.01473831554138361</v>
       </c>
       <c r="H553">
-        <v>0.01664478137476112</v>
+        <v>0.01601233497083577</v>
       </c>
       <c r="I553">
-        <v>1.450891759411717</v>
+        <v>1.605980570547842</v>
       </c>
       <c r="J553">
-        <v>2.355529459893475</v>
+        <v>2.371151007826336</v>
       </c>
       <c r="K553">
         <v>4.01</v>
@@ -29179,10 +29182,10 @@
         <v>5.23</v>
       </c>
       <c r="M553">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N553">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O553">
         <v>1</v>
@@ -29193,52 +29196,52 @@
     </row>
     <row r="554" spans="1:16">
       <c r="A554" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B554" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C554">
-        <v>-4.189835924124937</v>
+        <v>-3.737796849896604</v>
       </c>
       <c r="D554" t="s">
         <v>163</v>
       </c>
       <c r="E554">
-        <v>-2.738235413315398</v>
+        <v>-2.672334970835765</v>
       </c>
       <c r="F554">
         <v>1</v>
       </c>
       <c r="G554">
-        <v>0.01464983592412494</v>
+        <v>0.0143777968498966</v>
       </c>
       <c r="H554">
-        <v>0.0166182354133154</v>
+        <v>0.01601233497083577</v>
       </c>
       <c r="I554">
-        <v>1.451600510809539</v>
+        <v>1.065461879060839</v>
       </c>
       <c r="J554">
-        <v>2.349086265367815</v>
+        <v>2.371151007826336</v>
       </c>
       <c r="K554">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L554">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M554">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N554">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O554">
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29249,28 +29252,28 @@
         <v>69</v>
       </c>
       <c r="C555">
-        <v>-4.089470803698397</v>
+        <v>-4.215673134172834</v>
       </c>
       <c r="D555" t="s">
         <v>163</v>
       </c>
       <c r="E555">
-        <v>-2.63511713497192</v>
+        <v>-2.610786071980291</v>
       </c>
       <c r="F555">
         <v>1</v>
       </c>
       <c r="G555">
-        <v>0.0145494708036984</v>
+        <v>0.01467567313417283</v>
       </c>
       <c r="H555">
-        <v>0.01651511713497192</v>
+        <v>0.01595078607198029</v>
       </c>
       <c r="I555">
-        <v>1.454353668726477</v>
+        <v>1.604887062192542</v>
       </c>
       <c r="J555">
-        <v>2.324057557032019</v>
+        <v>2.355529459893475</v>
       </c>
       <c r="K555">
         <v>4.01</v>
@@ -29279,16 +29282,16 @@
         <v>5.23</v>
       </c>
       <c r="M555">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N555">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O555">
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29299,28 +29302,28 @@
         <v>69</v>
       </c>
       <c r="C556">
-        <v>-4.005320296309154</v>
+        <v>-4.189835924124937</v>
       </c>
       <c r="D556" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E556">
-        <v>-2.548658259549556</v>
+        <v>-2.738235413315398</v>
       </c>
       <c r="F556">
         <v>1</v>
       </c>
       <c r="G556">
-        <v>0.01446532029630916</v>
+        <v>0.01464983592412494</v>
       </c>
       <c r="H556">
-        <v>0.01642865825954956</v>
+        <v>0.0166182354133154</v>
       </c>
       <c r="I556">
-        <v>1.456662036759599</v>
+        <v>1.451600510809539</v>
       </c>
       <c r="J556">
-        <v>2.303072393094552</v>
+        <v>2.349086265367815</v>
       </c>
       <c r="K556">
         <v>4.01</v>
@@ -29338,7 +29341,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29349,28 +29352,28 @@
         <v>69</v>
       </c>
       <c r="C557">
-        <v>-3.880021728113258</v>
+        <v>-4.089470803698397</v>
       </c>
       <c r="D557" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E557">
-        <v>-2.419922573522849</v>
+        <v>-2.63511713497192</v>
       </c>
       <c r="F557">
         <v>1</v>
       </c>
       <c r="G557">
-        <v>0.01434002172811326</v>
+        <v>0.0145494708036984</v>
       </c>
       <c r="H557">
-        <v>0.01629992257352285</v>
+        <v>0.01651511713497192</v>
       </c>
       <c r="I557">
-        <v>1.460099154590409</v>
+        <v>1.454353668726477</v>
       </c>
       <c r="J557">
-        <v>2.271825867359915</v>
+        <v>2.324057557032019</v>
       </c>
       <c r="K557">
         <v>4.01</v>
@@ -29388,7 +29391,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29399,28 +29402,28 @@
         <v>69</v>
       </c>
       <c r="C558">
-        <v>-3.765867342432312</v>
+        <v>-4.005320296309154</v>
       </c>
       <c r="D558" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E558">
-        <v>-2.302636770778338</v>
+        <v>-2.548658259549556</v>
       </c>
       <c r="F558">
         <v>1</v>
       </c>
       <c r="G558">
-        <v>0.01422586734243231</v>
+        <v>0.01446532029630916</v>
       </c>
       <c r="H558">
-        <v>0.01618263677077834</v>
+        <v>0.01642865825954956</v>
       </c>
       <c r="I558">
-        <v>1.463230571653974</v>
+        <v>1.456662036759599</v>
       </c>
       <c r="J558">
-        <v>2.243358439509305</v>
+        <v>2.303072393094552</v>
       </c>
       <c r="K558">
         <v>4.01</v>
@@ -29438,7 +29441,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29449,28 +29452,28 @@
         <v>69</v>
       </c>
       <c r="C559">
-        <v>-3.200435821279882</v>
+        <v>-3.880021728113258</v>
       </c>
       <c r="D559" t="s">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="E559">
-        <v>-1.972165273797779</v>
+        <v>-2.419922573522849</v>
       </c>
       <c r="F559">
         <v>1</v>
       </c>
       <c r="G559">
-        <v>0.01366043582127988</v>
+        <v>0.01434002172811326</v>
       </c>
       <c r="H559">
-        <v>0.01619216527379778</v>
+        <v>0.01629992257352285</v>
       </c>
       <c r="I559">
-        <v>1.228270547482103</v>
+        <v>1.460099154590409</v>
       </c>
       <c r="J559">
-        <v>2.102353072638375</v>
+        <v>2.271825867359915</v>
       </c>
       <c r="K559">
         <v>4.01</v>
@@ -29479,16 +29482,16 @@
         <v>5.23</v>
       </c>
       <c r="M559">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="N559">
-        <v>7.11</v>
+        <v>6.94</v>
       </c>
       <c r="O559">
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29499,28 +29502,28 @@
         <v>69</v>
       </c>
       <c r="C560">
-        <v>-2.562371230751202</v>
+        <v>-3.765867342432312</v>
       </c>
       <c r="D560" t="s">
-        <v>162</v>
+        <v>71</v>
       </c>
       <c r="E560">
-        <v>-1.505427244947517</v>
+        <v>-2.302636770778338</v>
       </c>
       <c r="F560">
         <v>1</v>
       </c>
       <c r="G560">
-        <v>0.0130223712307512</v>
+        <v>0.01422586734243231</v>
       </c>
       <c r="H560">
-        <v>0.01318542724494752</v>
+        <v>0.01618263677077834</v>
       </c>
       <c r="I560">
-        <v>1.056943985803684</v>
+        <v>1.463230571653974</v>
       </c>
       <c r="J560">
-        <v>1.943234720885587</v>
+        <v>2.243358439509305</v>
       </c>
       <c r="K560">
         <v>4.01</v>
@@ -29529,16 +29532,116 @@
         <v>5.23</v>
       </c>
       <c r="M560">
+        <v>4.12</v>
+      </c>
+      <c r="N560">
+        <v>6.94</v>
+      </c>
+      <c r="O560">
+        <v>1</v>
+      </c>
+      <c r="P560" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="561" spans="1:16">
+      <c r="A561" s="1">
+        <v>0</v>
+      </c>
+      <c r="B561" t="s">
+        <v>69</v>
+      </c>
+      <c r="C561">
+        <v>-3.200435821279882</v>
+      </c>
+      <c r="D561" t="s">
+        <v>70</v>
+      </c>
+      <c r="E561">
+        <v>-1.972165273797779</v>
+      </c>
+      <c r="F561">
+        <v>1</v>
+      </c>
+      <c r="G561">
+        <v>0.01366043582127988</v>
+      </c>
+      <c r="H561">
+        <v>0.01619216527379778</v>
+      </c>
+      <c r="I561">
+        <v>1.228270547482103</v>
+      </c>
+      <c r="J561">
+        <v>2.102353072638375</v>
+      </c>
+      <c r="K561">
+        <v>4.01</v>
+      </c>
+      <c r="L561">
+        <v>5.23</v>
+      </c>
+      <c r="M561">
+        <v>4.32</v>
+      </c>
+      <c r="N561">
+        <v>7.11</v>
+      </c>
+      <c r="O561">
+        <v>1</v>
+      </c>
+      <c r="P561" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="562" spans="1:16">
+      <c r="A562" s="1">
+        <v>0</v>
+      </c>
+      <c r="B562" t="s">
+        <v>69</v>
+      </c>
+      <c r="C562">
+        <v>-2.562371230751202</v>
+      </c>
+      <c r="D562" t="s">
+        <v>162</v>
+      </c>
+      <c r="E562">
+        <v>-1.505427244947517</v>
+      </c>
+      <c r="F562">
+        <v>1</v>
+      </c>
+      <c r="G562">
+        <v>0.0130223712307512</v>
+      </c>
+      <c r="H562">
+        <v>0.01318542724494752</v>
+      </c>
+      <c r="I562">
+        <v>1.056943985803684</v>
+      </c>
+      <c r="J562">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K562">
+        <v>4.01</v>
+      </c>
+      <c r="L562">
+        <v>5.23</v>
+      </c>
+      <c r="M562">
         <v>3.78</v>
       </c>
-      <c r="N560">
+      <c r="N562">
         <v>5.84</v>
       </c>
-      <c r="O560">
-        <v>1</v>
-      </c>
-      <c r="P560" t="s">
-        <v>389</v>
+      <c r="O562">
+        <v>1</v>
+      </c>
+      <c r="P562" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="392">
   <si>
     <t>trade_time</t>
   </si>
@@ -226,289 +226,292 @@
     <t>2021-08-23</t>
   </si>
   <si>
+    <t>2021-09-13</t>
+  </si>
+  <si>
+    <t>2021-09-14</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-11-08</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-11-21</t>
+  </si>
+  <si>
+    <t>2017-10-25</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>2017-11-07</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2018-06-26</t>
+  </si>
+  <si>
+    <t>2018-06-27</t>
+  </si>
+  <si>
+    <t>2018-06-28</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-03</t>
+  </si>
+  <si>
+    <t>2018-09-14</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-09-26</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-25</t>
+  </si>
+  <si>
+    <t>2018-10-26</t>
+  </si>
+  <si>
+    <t>2018-10-29</t>
+  </si>
+  <si>
+    <t>2018-10-30</t>
+  </si>
+  <si>
+    <t>2018-10-31</t>
+  </si>
+  <si>
+    <t>2018-11-01</t>
+  </si>
+  <si>
+    <t>2018-11-02</t>
+  </si>
+  <si>
+    <t>2018-11-05</t>
+  </si>
+  <si>
+    <t>2018-11-06</t>
+  </si>
+  <si>
+    <t>2018-11-07</t>
+  </si>
+  <si>
+    <t>2018-11-08</t>
+  </si>
+  <si>
+    <t>2018-11-09</t>
+  </si>
+  <si>
+    <t>2018-11-12</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>2018-11-14</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2018-11-21</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-23</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-11-27</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-06-17</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-07-29</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-07</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-11</t>
+  </si>
+  <si>
+    <t>2020-02-12</t>
+  </si>
+  <si>
+    <t>2020-02-17</t>
+  </si>
+  <si>
+    <t>2020-02-18</t>
+  </si>
+  <si>
+    <t>2020-02-19</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-10</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-24</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-03-27</t>
+  </si>
+  <si>
+    <t>2020-03-30</t>
+  </si>
+  <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-04-02</t>
+  </si>
+  <si>
+    <t>2020-04-03</t>
+  </si>
+  <si>
+    <t>2020-04-07</t>
+  </si>
+  <si>
+    <t>2020-04-08</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
     <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-09-13</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-11-08</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-11-21</t>
-  </si>
-  <si>
-    <t>2017-10-25</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-11-06</t>
-  </si>
-  <si>
-    <t>2017-11-07</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2018-06-26</t>
-  </si>
-  <si>
-    <t>2018-06-27</t>
-  </si>
-  <si>
-    <t>2018-06-28</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-03</t>
-  </si>
-  <si>
-    <t>2018-09-14</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-09-26</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-25</t>
-  </si>
-  <si>
-    <t>2018-10-26</t>
-  </si>
-  <si>
-    <t>2018-10-29</t>
-  </si>
-  <si>
-    <t>2018-10-30</t>
-  </si>
-  <si>
-    <t>2018-10-31</t>
-  </si>
-  <si>
-    <t>2018-11-01</t>
-  </si>
-  <si>
-    <t>2018-11-02</t>
-  </si>
-  <si>
-    <t>2018-11-05</t>
-  </si>
-  <si>
-    <t>2018-11-06</t>
-  </si>
-  <si>
-    <t>2018-11-07</t>
-  </si>
-  <si>
-    <t>2018-11-08</t>
-  </si>
-  <si>
-    <t>2018-11-09</t>
-  </si>
-  <si>
-    <t>2018-11-12</t>
-  </si>
-  <si>
-    <t>2018-11-13</t>
-  </si>
-  <si>
-    <t>2018-11-14</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-20</t>
-  </si>
-  <si>
-    <t>2018-11-21</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-23</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-11-27</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-06-17</t>
-  </si>
-  <si>
-    <t>2019-06-19</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-07-29</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-07</t>
-  </si>
-  <si>
-    <t>2020-02-10</t>
-  </si>
-  <si>
-    <t>2020-02-11</t>
-  </si>
-  <si>
-    <t>2020-02-12</t>
-  </si>
-  <si>
-    <t>2020-02-17</t>
-  </si>
-  <si>
-    <t>2020-02-18</t>
-  </si>
-  <si>
-    <t>2020-02-19</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-10</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-24</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-03-27</t>
-  </si>
-  <si>
-    <t>2020-03-30</t>
-  </si>
-  <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-04-02</t>
-  </si>
-  <si>
-    <t>2020-04-03</t>
-  </si>
-  <si>
-    <t>2020-04-07</t>
-  </si>
-  <si>
-    <t>2020-04-08</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-09-14</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
   </si>
   <si>
     <t>2021-09-10</t>
@@ -1544,7 +1547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P562"/>
+  <dimension ref="A1:P563"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1641,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1691,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1741,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1791,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1841,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1891,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1941,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1991,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2041,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2091,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2141,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2191,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2241,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2291,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2341,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2391,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2441,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2491,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2541,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2591,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2641,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2691,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2741,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2791,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2841,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2891,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2941,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2991,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3041,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3091,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3141,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3191,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3241,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3291,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3341,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3391,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3441,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3491,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3541,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3591,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3641,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3691,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3741,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3791,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3841,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3891,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3941,7 +3944,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3991,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4041,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4091,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4141,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4191,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4241,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4291,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4341,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4391,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4441,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4491,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4541,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4591,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4641,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4691,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4741,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4791,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4841,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4891,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4941,7 +4944,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4991,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5041,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5091,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5141,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5191,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5241,7 +5244,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5291,7 +5294,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5341,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5391,7 +5394,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5441,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5491,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5541,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5591,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5641,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5691,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5741,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5791,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5841,7 +5844,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5891,7 +5894,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5941,7 +5944,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5991,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6041,7 +6044,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6091,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6141,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6191,7 +6194,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6241,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6291,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6341,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6391,7 +6394,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6441,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6491,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6541,7 +6544,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6591,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6641,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6691,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6741,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6791,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6841,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6891,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6941,7 +6944,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6991,7 +6994,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7041,7 +7044,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7091,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7141,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7191,7 +7194,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7241,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7291,7 +7294,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7341,7 +7344,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7391,7 +7394,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7441,7 +7444,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7491,7 +7494,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7541,7 +7544,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7591,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7641,7 +7644,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7691,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7741,7 +7744,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7791,7 +7794,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7841,7 +7844,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7891,7 +7894,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7941,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7991,7 +7994,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8041,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8091,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8141,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8191,7 +8194,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8241,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8291,7 +8294,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8341,7 +8344,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8391,7 +8394,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8441,7 +8444,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8491,7 +8494,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8541,7 +8544,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8641,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8691,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8741,7 +8744,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8791,7 +8794,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8841,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8891,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8941,7 +8944,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8991,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9041,7 +9044,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9091,7 +9094,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9141,7 +9144,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9191,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9241,7 +9244,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9291,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9341,7 +9344,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9391,7 +9394,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9441,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9491,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9541,7 +9544,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9591,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9691,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9741,7 +9744,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9791,7 +9794,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9941,7 +9944,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9991,7 +9994,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10041,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10091,7 +10094,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10141,7 +10144,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10191,7 +10194,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10241,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10291,7 +10294,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10391,7 +10394,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10441,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10591,7 +10594,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10641,7 +10644,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10691,7 +10694,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10741,7 +10744,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11241,7 +11244,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11291,7 +11294,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11341,7 +11344,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11391,7 +11394,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11441,7 +11444,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11491,7 +11494,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11541,7 +11544,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11591,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11641,7 +11644,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11691,7 +11694,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11741,7 +11744,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11791,7 +11794,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11841,7 +11844,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11891,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11941,7 +11944,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12741,7 +12744,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12791,7 +12794,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12841,7 +12844,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12891,7 +12894,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12941,7 +12944,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12991,7 +12994,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13041,7 +13044,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13091,7 +13094,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13141,7 +13144,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13191,7 +13194,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13241,7 +13244,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13291,7 +13294,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13341,7 +13344,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13391,7 +13394,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13441,7 +13444,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13491,7 +13494,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13541,7 +13544,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13591,7 +13594,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13641,7 +13644,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13691,7 +13694,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13841,7 +13844,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13891,7 +13894,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13941,7 +13944,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14041,7 +14044,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14191,7 +14194,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14241,7 +14244,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14291,7 +14294,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14341,7 +14344,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14391,7 +14394,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14441,7 +14444,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14491,7 +14494,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14591,7 +14594,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14641,7 +14644,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14691,7 +14694,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14741,7 +14744,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14791,7 +14794,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14841,7 +14844,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14891,7 +14894,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14941,7 +14944,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14991,7 +14994,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15041,7 +15044,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15091,7 +15094,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15141,7 +15144,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15191,7 +15194,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15241,7 +15244,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15291,7 +15294,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15341,7 +15344,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15391,7 +15394,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15441,7 +15444,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15491,7 +15494,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15541,7 +15544,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15591,7 +15594,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15641,7 +15644,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15691,7 +15694,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15741,7 +15744,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15791,7 +15794,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15841,7 +15844,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15891,7 +15894,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15941,7 +15944,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15991,7 +15994,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16041,7 +16044,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16091,7 +16094,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16141,7 +16144,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16191,7 +16194,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16241,7 +16244,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16291,7 +16294,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16341,7 +16344,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16391,7 +16394,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16441,7 +16444,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16491,7 +16494,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16541,7 +16544,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16591,7 +16594,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16641,7 +16644,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16691,7 +16694,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16741,7 +16744,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16791,7 +16794,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16841,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16891,7 +16894,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16941,7 +16944,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17141,7 +17144,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17191,7 +17194,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17241,7 +17244,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17291,7 +17294,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17341,7 +17344,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17391,7 +17394,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17441,7 +17444,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17491,7 +17494,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17541,7 +17544,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17591,7 +17594,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17641,7 +17644,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17691,7 +17694,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17741,7 +17744,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17791,7 +17794,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17841,7 +17844,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17891,7 +17894,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17941,7 +17944,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17991,7 +17994,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18041,7 +18044,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18091,7 +18094,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18141,7 +18144,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18191,7 +18194,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18241,7 +18244,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18291,7 +18294,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18341,7 +18344,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18591,7 +18594,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18641,7 +18644,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18691,7 +18694,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18741,7 +18744,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18791,7 +18794,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18841,7 +18844,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18891,7 +18894,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18941,7 +18944,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18991,7 +18994,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19041,7 +19044,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19091,7 +19094,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19141,7 +19144,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19591,7 +19594,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19641,7 +19644,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19691,7 +19694,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19741,7 +19744,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19791,7 +19794,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19841,7 +19844,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19891,7 +19894,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19941,7 +19944,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19991,7 +19994,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20041,7 +20044,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20091,7 +20094,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20141,7 +20144,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20191,7 +20194,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20241,7 +20244,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20291,7 +20294,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20341,7 +20344,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20541,7 +20544,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20591,7 +20594,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20641,7 +20644,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20691,7 +20694,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20891,7 +20894,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20941,7 +20944,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20991,7 +20994,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21041,7 +21044,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21091,7 +21094,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21141,7 +21144,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21191,7 +21194,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21241,7 +21244,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21291,7 +21294,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21341,7 +21344,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21391,7 +21394,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21441,7 +21444,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21491,7 +21494,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21541,7 +21544,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21591,7 +21594,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21641,7 +21644,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21691,7 +21694,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21741,7 +21744,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21791,7 +21794,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21841,7 +21844,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21891,7 +21894,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21941,7 +21944,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21991,7 +21994,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22041,7 +22044,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22091,7 +22094,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22141,7 +22144,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22191,7 +22194,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22241,7 +22244,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22291,7 +22294,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22341,7 +22344,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22391,7 +22394,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22441,7 +22444,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22491,7 +22494,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22691,7 +22694,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22741,7 +22744,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22791,7 +22794,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22841,7 +22844,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22891,7 +22894,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22941,7 +22944,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23141,7 +23144,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23191,7 +23194,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23241,7 +23244,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23291,7 +23294,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23341,7 +23344,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23391,7 +23394,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23441,7 +23444,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23491,7 +23494,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23541,7 +23544,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23591,7 +23594,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23641,7 +23644,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23691,7 +23694,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23741,7 +23744,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23791,7 +23794,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23841,7 +23844,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23891,7 +23894,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23941,7 +23944,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23991,7 +23994,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24041,7 +24044,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24091,7 +24094,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24141,7 +24144,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24191,7 +24194,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24241,7 +24244,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24291,7 +24294,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24341,7 +24344,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24391,7 +24394,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24441,7 +24444,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24491,7 +24494,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24541,7 +24544,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24591,7 +24594,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24641,7 +24644,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24691,7 +24694,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24741,7 +24744,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24791,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24841,7 +24844,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24891,7 +24894,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24941,7 +24944,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24991,7 +24994,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25041,7 +25044,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25091,7 +25094,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25141,7 +25144,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25191,7 +25194,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25491,7 +25494,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25541,7 +25544,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25591,7 +25594,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25641,7 +25644,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25691,7 +25694,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25741,7 +25744,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25791,7 +25794,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25841,7 +25844,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25891,7 +25894,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25941,7 +25944,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25991,7 +25994,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26041,7 +26044,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26091,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26141,7 +26144,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26191,7 +26194,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26241,7 +26244,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26291,7 +26294,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26341,7 +26344,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26391,7 +26394,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26441,7 +26444,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26491,7 +26494,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26541,7 +26544,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26591,7 +26594,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26641,7 +26644,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26691,7 +26694,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26741,7 +26744,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26791,7 +26794,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26841,7 +26844,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26891,7 +26894,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26941,7 +26944,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26991,7 +26994,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27041,7 +27044,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27091,7 +27094,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27141,7 +27144,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27191,7 +27194,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27241,7 +27244,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27291,7 +27294,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27341,7 +27344,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27391,7 +27394,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27441,7 +27444,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27491,7 +27494,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27541,7 +27544,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27591,7 +27594,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27641,7 +27644,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27652,146 +27655,146 @@
         <v>70</v>
       </c>
       <c r="C523">
-        <v>0.1441551924455533</v>
+        <v>0.296648007610111</v>
       </c>
       <c r="D523" t="s">
         <v>163</v>
       </c>
       <c r="E523">
-        <v>0.3168915412582125</v>
+        <v>0.5181379488404918</v>
       </c>
       <c r="F523">
         <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.01407584480755445</v>
+        <v>0.01358335199238989</v>
       </c>
       <c r="H523">
-        <v>0.01302310845874179</v>
+        <v>0.01290186205115951</v>
       </c>
       <c r="I523">
-        <v>-0.1727363488126592</v>
+        <v>-0.2214899412303808</v>
       </c>
       <c r="J523">
         <v>1.612464075822789</v>
       </c>
       <c r="K523">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="L523">
-        <v>7.11</v>
+        <v>6.94</v>
       </c>
       <c r="M523">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="N523">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C524">
-        <v>0.296648007610111</v>
+        <v>-1.857167569625838</v>
       </c>
       <c r="D524" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E524">
-        <v>0.3168915412582125</v>
+        <v>-0.8406716741111389</v>
       </c>
       <c r="F524">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G524">
-        <v>0.01358335199238989</v>
+        <v>0.01231716756962584</v>
       </c>
       <c r="H524">
-        <v>0.01302310845874179</v>
+        <v>0.01252067167411114</v>
       </c>
       <c r="I524">
-        <v>-0.0202435336481015</v>
+        <v>1.016495895514699</v>
       </c>
       <c r="J524">
-        <v>1.612464075822789</v>
+        <v>1.767373458759561</v>
       </c>
       <c r="K524">
-        <v>4.12</v>
+        <v>4.01</v>
       </c>
       <c r="L524">
-        <v>6.94</v>
+        <v>5.23</v>
       </c>
       <c r="M524">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="N524">
-        <v>6.67</v>
+        <v>5.84</v>
       </c>
       <c r="O524">
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B525" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C525">
-        <v>-1.857167569625838</v>
+        <v>-0.2934514275126689</v>
       </c>
       <c r="D525" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E525">
-        <v>-0.8406716741111389</v>
+        <v>-0.07671408163671245</v>
       </c>
       <c r="F525">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G525">
-        <v>0.01231716756962584</v>
+        <v>0.01363345142751267</v>
       </c>
       <c r="H525">
-        <v>0.01252067167411114</v>
+        <v>0.01349671408163671</v>
       </c>
       <c r="I525">
-        <v>1.016495895514699</v>
+        <v>-0.2167373458759565</v>
       </c>
       <c r="J525">
         <v>1.767373458759561</v>
       </c>
       <c r="K525">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="L525">
-        <v>5.23</v>
+        <v>6.67</v>
       </c>
       <c r="M525">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="N525">
-        <v>5.84</v>
+        <v>6.71</v>
       </c>
       <c r="O525">
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27841,7 +27844,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27891,7 +27894,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27941,7 +27944,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27991,7 +27994,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28041,7 +28044,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28091,7 +28094,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28141,7 +28144,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28155,7 +28158,7 @@
         <v>-2.943692670373876</v>
       </c>
       <c r="D533" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="E533">
         <v>-1.695574148632207</v>
@@ -28191,7 +28194,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28205,7 +28208,7 @@
         <v>-2.466410474021997</v>
       </c>
       <c r="D534" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="E534">
         <v>-1.695574148632207</v>
@@ -28241,7 +28244,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28255,7 +28258,7 @@
         <v>-3.302184308580614</v>
       </c>
       <c r="D535" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E535">
         <v>-2.00751151980996</v>
@@ -28291,7 +28294,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28305,7 +28308,7 @@
         <v>-2.807916224134152</v>
       </c>
       <c r="D536" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E536">
         <v>-2.00751151980996</v>
@@ -28341,7 +28344,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28355,7 +28358,7 @@
         <v>-3.440693413369869</v>
       </c>
       <c r="D537" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E537">
         <v>-1.968542858624404</v>
@@ -28391,7 +28394,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28405,7 +28408,7 @@
         <v>-2.939862553384764</v>
       </c>
       <c r="D538" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E538">
         <v>-1.968542858624404</v>
@@ -28441,7 +28444,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28455,7 +28458,7 @@
         <v>-3.668901415448289</v>
       </c>
       <c r="D539" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E539">
         <v>-2.203010930585275</v>
@@ -28491,7 +28494,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28505,7 +28508,7 @@
         <v>-3.157257707484405</v>
       </c>
       <c r="D540" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E540">
         <v>-2.203010930585275</v>
@@ -28541,7 +28544,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28555,7 +28558,7 @@
         <v>-3.954888865249114</v>
       </c>
       <c r="D541" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E541">
         <v>-2.496843422649964</v>
@@ -28591,7 +28594,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28605,7 +28608,7 @@
         <v>-3.429694629738558</v>
       </c>
       <c r="D542" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E542">
         <v>-2.496843422649964</v>
@@ -28641,7 +28644,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28655,7 +28658,7 @@
         <v>-4.162550774568617</v>
       </c>
       <c r="D543" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E543">
         <v>-2.558591035361685</v>
@@ -28691,7 +28694,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28705,7 +28708,7 @@
         <v>-3.627517196721227</v>
       </c>
       <c r="D544" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E544">
         <v>-2.558591035361685</v>
@@ -28741,7 +28744,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28755,7 +28758,7 @@
         <v>-4.341021841271511</v>
       </c>
       <c r="D545" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E545">
         <v>-2.733946647034852</v>
@@ -28791,7 +28794,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28805,7 +28808,7 @@
         <v>-3.797532028343435</v>
       </c>
       <c r="D546" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E546">
         <v>-2.733946647034852</v>
@@ -28841,7 +28844,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28855,7 +28858,7 @@
         <v>-4.38270256915019</v>
       </c>
       <c r="D547" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E547">
         <v>-2.774899781160038</v>
@@ -28891,7 +28894,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28905,7 +28908,7 @@
         <v>-3.837237858891204</v>
       </c>
       <c r="D548" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E548">
         <v>-2.774899781160038</v>
@@ -28941,7 +28944,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28955,7 +28958,7 @@
         <v>-4.411855003341485</v>
       </c>
       <c r="D549" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E549">
         <v>-2.803543319991386</v>
@@ -28991,7 +28994,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29005,7 +29008,7 @@
         <v>-3.865009005676926</v>
       </c>
       <c r="D550" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E550">
         <v>-2.803543319991386</v>
@@ -29041,7 +29044,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29055,7 +29058,7 @@
         <v>-4.339272485484365</v>
       </c>
       <c r="D551" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E551">
         <v>-2.732227828630524</v>
@@ -29091,7 +29094,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29105,7 +29108,7 @@
         <v>-3.795865559738223</v>
       </c>
       <c r="D552" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E552">
         <v>-2.732227828630524</v>
@@ -29141,7 +29144,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29155,7 +29158,7 @@
         <v>-4.278315541383607</v>
       </c>
       <c r="D553" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E553">
         <v>-2.672334970835765</v>
@@ -29191,7 +29194,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29205,7 +29208,7 @@
         <v>-3.737796849896604</v>
       </c>
       <c r="D554" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E554">
         <v>-2.672334970835765</v>
@@ -29241,7 +29244,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29255,7 +29258,7 @@
         <v>-4.215673134172834</v>
       </c>
       <c r="D555" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="E555">
         <v>-2.610786071980291</v>
@@ -29291,51 +29294,51 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="556" spans="1:16">
       <c r="A556" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B556" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C556">
-        <v>-4.189835924124937</v>
+        <v>-3.678122536793074</v>
       </c>
       <c r="D556" t="s">
         <v>71</v>
       </c>
       <c r="E556">
-        <v>-2.738235413315398</v>
+        <v>-2.610786071980291</v>
       </c>
       <c r="F556">
         <v>1</v>
       </c>
       <c r="G556">
-        <v>0.01464983592412494</v>
+        <v>0.01431812253679307</v>
       </c>
       <c r="H556">
-        <v>0.0166182354133154</v>
+        <v>0.01595078607198029</v>
       </c>
       <c r="I556">
-        <v>1.451600510809539</v>
+        <v>1.067336464812783</v>
       </c>
       <c r="J556">
-        <v>2.349086265367815</v>
+        <v>2.355529459893475</v>
       </c>
       <c r="K556">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L556">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M556">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N556">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O556">
         <v>1</v>
@@ -29352,28 +29355,28 @@
         <v>69</v>
       </c>
       <c r="C557">
-        <v>-4.089470803698397</v>
+        <v>-4.189835924124937</v>
       </c>
       <c r="D557" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E557">
-        <v>-2.63511713497192</v>
+        <v>-2.738235413315398</v>
       </c>
       <c r="F557">
         <v>1</v>
       </c>
       <c r="G557">
-        <v>0.0145494708036984</v>
+        <v>0.01464983592412494</v>
       </c>
       <c r="H557">
-        <v>0.01651511713497192</v>
+        <v>0.0166182354133154</v>
       </c>
       <c r="I557">
-        <v>1.454353668726477</v>
+        <v>1.451600510809539</v>
       </c>
       <c r="J557">
-        <v>2.324057557032019</v>
+        <v>2.349086265367815</v>
       </c>
       <c r="K557">
         <v>4.01</v>
@@ -29402,28 +29405,28 @@
         <v>69</v>
       </c>
       <c r="C558">
-        <v>-4.005320296309154</v>
+        <v>-4.089470803698397</v>
       </c>
       <c r="D558" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E558">
-        <v>-2.548658259549556</v>
+        <v>-2.63511713497192</v>
       </c>
       <c r="F558">
         <v>1</v>
       </c>
       <c r="G558">
-        <v>0.01446532029630916</v>
+        <v>0.0145494708036984</v>
       </c>
       <c r="H558">
-        <v>0.01642865825954956</v>
+        <v>0.01651511713497192</v>
       </c>
       <c r="I558">
-        <v>1.456662036759599</v>
+        <v>1.454353668726477</v>
       </c>
       <c r="J558">
-        <v>2.303072393094552</v>
+        <v>2.324057557032019</v>
       </c>
       <c r="K558">
         <v>4.01</v>
@@ -29452,28 +29455,28 @@
         <v>69</v>
       </c>
       <c r="C559">
-        <v>-3.880021728113258</v>
+        <v>-4.005320296309154</v>
       </c>
       <c r="D559" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E559">
-        <v>-2.419922573522849</v>
+        <v>-2.548658259549556</v>
       </c>
       <c r="F559">
         <v>1</v>
       </c>
       <c r="G559">
-        <v>0.01434002172811326</v>
+        <v>0.01446532029630916</v>
       </c>
       <c r="H559">
-        <v>0.01629992257352285</v>
+        <v>0.01642865825954956</v>
       </c>
       <c r="I559">
-        <v>1.460099154590409</v>
+        <v>1.456662036759599</v>
       </c>
       <c r="J559">
-        <v>2.271825867359915</v>
+        <v>2.303072393094552</v>
       </c>
       <c r="K559">
         <v>4.01</v>
@@ -29502,28 +29505,28 @@
         <v>69</v>
       </c>
       <c r="C560">
-        <v>-3.765867342432312</v>
+        <v>-3.880021728113258</v>
       </c>
       <c r="D560" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E560">
-        <v>-2.302636770778338</v>
+        <v>-2.419922573522849</v>
       </c>
       <c r="F560">
         <v>1</v>
       </c>
       <c r="G560">
-        <v>0.01422586734243231</v>
+        <v>0.01434002172811326</v>
       </c>
       <c r="H560">
-        <v>0.01618263677077834</v>
+        <v>0.01629992257352285</v>
       </c>
       <c r="I560">
-        <v>1.463230571653974</v>
+        <v>1.460099154590409</v>
       </c>
       <c r="J560">
-        <v>2.243358439509305</v>
+        <v>2.271825867359915</v>
       </c>
       <c r="K560">
         <v>4.01</v>
@@ -29552,28 +29555,28 @@
         <v>69</v>
       </c>
       <c r="C561">
-        <v>-3.200435821279882</v>
+        <v>-3.765867342432312</v>
       </c>
       <c r="D561" t="s">
         <v>70</v>
       </c>
       <c r="E561">
-        <v>-1.972165273797779</v>
+        <v>-2.302636770778338</v>
       </c>
       <c r="F561">
         <v>1</v>
       </c>
       <c r="G561">
-        <v>0.01366043582127988</v>
+        <v>0.01422586734243231</v>
       </c>
       <c r="H561">
-        <v>0.01619216527379778</v>
+        <v>0.01618263677077834</v>
       </c>
       <c r="I561">
-        <v>1.228270547482103</v>
+        <v>1.463230571653974</v>
       </c>
       <c r="J561">
-        <v>2.102353072638375</v>
+        <v>2.243358439509305</v>
       </c>
       <c r="K561">
         <v>4.01</v>
@@ -29582,10 +29585,10 @@
         <v>5.23</v>
       </c>
       <c r="M561">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="N561">
-        <v>7.11</v>
+        <v>6.94</v>
       </c>
       <c r="O561">
         <v>1</v>
@@ -29602,28 +29605,28 @@
         <v>69</v>
       </c>
       <c r="C562">
-        <v>-2.562371230751202</v>
+        <v>-3.200435821279882</v>
       </c>
       <c r="D562" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E562">
-        <v>-1.505427244947517</v>
+        <v>-1.972165273797779</v>
       </c>
       <c r="F562">
         <v>1</v>
       </c>
       <c r="G562">
-        <v>0.0130223712307512</v>
+        <v>0.01366043582127988</v>
       </c>
       <c r="H562">
-        <v>0.01318542724494752</v>
+        <v>0.01619216527379778</v>
       </c>
       <c r="I562">
-        <v>1.056943985803684</v>
+        <v>1.228270547482103</v>
       </c>
       <c r="J562">
-        <v>1.943234720885587</v>
+        <v>2.102353072638375</v>
       </c>
       <c r="K562">
         <v>4.01</v>
@@ -29632,16 +29635,66 @@
         <v>5.23</v>
       </c>
       <c r="M562">
-        <v>3.78</v>
+        <v>4.32</v>
       </c>
       <c r="N562">
-        <v>5.84</v>
+        <v>7.11</v>
       </c>
       <c r="O562">
         <v>1</v>
       </c>
       <c r="P562" t="s">
         <v>390</v>
+      </c>
+    </row>
+    <row r="563" spans="1:16">
+      <c r="A563" s="1">
+        <v>0</v>
+      </c>
+      <c r="B563" t="s">
+        <v>69</v>
+      </c>
+      <c r="C563">
+        <v>-2.562371230751202</v>
+      </c>
+      <c r="D563" t="s">
+        <v>162</v>
+      </c>
+      <c r="E563">
+        <v>-1.505427244947517</v>
+      </c>
+      <c r="F563">
+        <v>1</v>
+      </c>
+      <c r="G563">
+        <v>0.0130223712307512</v>
+      </c>
+      <c r="H563">
+        <v>0.01318542724494752</v>
+      </c>
+      <c r="I563">
+        <v>1.056943985803684</v>
+      </c>
+      <c r="J563">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K563">
+        <v>4.01</v>
+      </c>
+      <c r="L563">
+        <v>5.23</v>
+      </c>
+      <c r="M563">
+        <v>3.78</v>
+      </c>
+      <c r="N563">
+        <v>5.84</v>
+      </c>
+      <c r="O563">
+        <v>1</v>
+      </c>
+      <c r="P563" t="s">
+        <v>391</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="393">
   <si>
     <t>trade_time</t>
   </si>
@@ -229,292 +229,295 @@
     <t>2021-09-13</t>
   </si>
   <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-11-08</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-11-21</t>
+  </si>
+  <si>
+    <t>2017-10-25</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>2017-11-07</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2018-06-26</t>
+  </si>
+  <si>
+    <t>2018-06-27</t>
+  </si>
+  <si>
+    <t>2018-06-28</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-03</t>
+  </si>
+  <si>
+    <t>2018-09-14</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-09-26</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-25</t>
+  </si>
+  <si>
+    <t>2018-10-26</t>
+  </si>
+  <si>
+    <t>2018-10-29</t>
+  </si>
+  <si>
+    <t>2018-10-30</t>
+  </si>
+  <si>
+    <t>2018-10-31</t>
+  </si>
+  <si>
+    <t>2018-11-01</t>
+  </si>
+  <si>
+    <t>2018-11-02</t>
+  </si>
+  <si>
+    <t>2018-11-05</t>
+  </si>
+  <si>
+    <t>2018-11-06</t>
+  </si>
+  <si>
+    <t>2018-11-07</t>
+  </si>
+  <si>
+    <t>2018-11-08</t>
+  </si>
+  <si>
+    <t>2018-11-09</t>
+  </si>
+  <si>
+    <t>2018-11-12</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>2018-11-14</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2018-11-21</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-23</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-11-27</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-06-17</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-07-29</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-07</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-11</t>
+  </si>
+  <si>
+    <t>2020-02-12</t>
+  </si>
+  <si>
+    <t>2020-02-17</t>
+  </si>
+  <si>
+    <t>2020-02-18</t>
+  </si>
+  <si>
+    <t>2020-02-19</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-10</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-24</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-03-27</t>
+  </si>
+  <si>
+    <t>2020-03-30</t>
+  </si>
+  <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-04-02</t>
+  </si>
+  <si>
+    <t>2020-04-03</t>
+  </si>
+  <si>
+    <t>2020-04-07</t>
+  </si>
+  <si>
+    <t>2020-04-08</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-16</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
+  </si>
+  <si>
     <t>2021-09-14</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-11-08</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-11-21</t>
-  </si>
-  <si>
-    <t>2017-10-25</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-11-06</t>
-  </si>
-  <si>
-    <t>2017-11-07</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2018-06-26</t>
-  </si>
-  <si>
-    <t>2018-06-27</t>
-  </si>
-  <si>
-    <t>2018-06-28</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-03</t>
-  </si>
-  <si>
-    <t>2018-09-14</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-09-26</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-25</t>
-  </si>
-  <si>
-    <t>2018-10-26</t>
-  </si>
-  <si>
-    <t>2018-10-29</t>
-  </si>
-  <si>
-    <t>2018-10-30</t>
-  </si>
-  <si>
-    <t>2018-10-31</t>
-  </si>
-  <si>
-    <t>2018-11-01</t>
-  </si>
-  <si>
-    <t>2018-11-02</t>
-  </si>
-  <si>
-    <t>2018-11-05</t>
-  </si>
-  <si>
-    <t>2018-11-06</t>
-  </si>
-  <si>
-    <t>2018-11-07</t>
-  </si>
-  <si>
-    <t>2018-11-08</t>
-  </si>
-  <si>
-    <t>2018-11-09</t>
-  </si>
-  <si>
-    <t>2018-11-12</t>
-  </si>
-  <si>
-    <t>2018-11-13</t>
-  </si>
-  <si>
-    <t>2018-11-14</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-20</t>
-  </si>
-  <si>
-    <t>2018-11-21</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-23</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-11-27</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-06-17</t>
-  </si>
-  <si>
-    <t>2019-06-19</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-07-29</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-07</t>
-  </si>
-  <si>
-    <t>2020-02-10</t>
-  </si>
-  <si>
-    <t>2020-02-11</t>
-  </si>
-  <si>
-    <t>2020-02-12</t>
-  </si>
-  <si>
-    <t>2020-02-17</t>
-  </si>
-  <si>
-    <t>2020-02-18</t>
-  </si>
-  <si>
-    <t>2020-02-19</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-10</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-24</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-03-27</t>
-  </si>
-  <si>
-    <t>2020-03-30</t>
-  </si>
-  <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-04-02</t>
-  </si>
-  <si>
-    <t>2020-04-03</t>
-  </si>
-  <si>
-    <t>2020-04-07</t>
-  </si>
-  <si>
-    <t>2020-04-08</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-09-10</t>
   </si>
   <si>
     <t>2016-10-28</t>
@@ -1547,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P563"/>
+  <dimension ref="A1:P571"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1644,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1694,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1744,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1794,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1844,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1894,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1944,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1994,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2044,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2094,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2144,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2194,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2244,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2294,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2344,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2394,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2444,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2494,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2544,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2594,7 +2597,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2644,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2694,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2744,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2794,7 +2797,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2844,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2894,7 +2897,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2944,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2994,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3044,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3094,7 +3097,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3144,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3194,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3244,7 +3247,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3294,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3344,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3394,7 +3397,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3444,7 +3447,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3494,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3544,7 +3547,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3594,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3644,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3694,7 +3697,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3744,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3794,7 +3797,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3844,7 +3847,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3894,7 +3897,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3944,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3994,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4044,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4094,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4144,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4194,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4244,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4294,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4344,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4394,7 +4397,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4444,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4494,7 +4497,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4544,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4594,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4644,7 +4647,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4694,7 +4697,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4744,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4794,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4844,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4894,7 +4897,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4944,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4994,7 +4997,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5044,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5094,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5144,7 +5147,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5194,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5244,7 +5247,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5294,7 +5297,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5344,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5394,7 +5397,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5444,7 +5447,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5494,7 +5497,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5544,7 +5547,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5594,7 +5597,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5644,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5694,7 +5697,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5744,7 +5747,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5794,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5844,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5894,7 +5897,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5944,7 +5947,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5994,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6044,7 +6047,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6094,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6144,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6194,7 +6197,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6244,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6294,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6344,7 +6347,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6394,7 +6397,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6444,7 +6447,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6494,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6544,7 +6547,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6594,7 +6597,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6644,7 +6647,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6694,7 +6697,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6744,7 +6747,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6794,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6844,7 +6847,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6894,7 +6897,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6944,7 +6947,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6994,7 +6997,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7044,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7094,7 +7097,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7144,7 +7147,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7194,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7244,7 +7247,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7294,7 +7297,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7344,7 +7347,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7394,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7444,7 +7447,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7494,7 +7497,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7544,7 +7547,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7594,7 +7597,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7644,7 +7647,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7694,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7744,7 +7747,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7794,7 +7797,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7844,7 +7847,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7894,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7944,7 +7947,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7994,7 +7997,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8044,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8094,7 +8097,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8144,7 +8147,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8194,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8244,7 +8247,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8294,7 +8297,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8344,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8394,7 +8397,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8444,7 +8447,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8494,7 +8497,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8544,7 +8547,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8644,7 +8647,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8694,7 +8697,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8744,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8794,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8844,7 +8847,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8894,7 +8897,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8944,7 +8947,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8994,7 +8997,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9044,7 +9047,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9094,7 +9097,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9144,7 +9147,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9194,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9244,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9294,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9344,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9394,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9444,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9494,7 +9497,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9544,7 +9547,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9594,7 +9597,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9694,7 +9697,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9744,7 +9747,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9794,7 +9797,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9944,7 +9947,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9994,7 +9997,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10044,7 +10047,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10094,7 +10097,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10144,7 +10147,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10194,7 +10197,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10244,7 +10247,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10294,7 +10297,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10394,7 +10397,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10444,7 +10447,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10594,7 +10597,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10644,7 +10647,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10694,7 +10697,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10744,7 +10747,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11244,7 +11247,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11294,7 +11297,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11344,7 +11347,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11394,7 +11397,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11444,7 +11447,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11494,7 +11497,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11544,7 +11547,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11594,7 +11597,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11644,7 +11647,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11694,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11744,7 +11747,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11794,7 +11797,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11844,7 +11847,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11894,7 +11897,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11944,7 +11947,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12744,7 +12747,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12794,7 +12797,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12844,7 +12847,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12894,7 +12897,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12944,7 +12947,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12994,7 +12997,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13044,7 +13047,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13094,7 +13097,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13144,7 +13147,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13194,7 +13197,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13244,7 +13247,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13294,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13344,7 +13347,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13394,7 +13397,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13444,7 +13447,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13494,7 +13497,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13544,7 +13547,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13594,7 +13597,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13644,7 +13647,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13694,7 +13697,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13844,7 +13847,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13894,7 +13897,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13944,7 +13947,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14044,7 +14047,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14194,7 +14197,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14244,7 +14247,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14294,7 +14297,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14344,7 +14347,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14394,7 +14397,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14444,7 +14447,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14494,7 +14497,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14594,7 +14597,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14644,7 +14647,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14694,7 +14697,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14744,7 +14747,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14794,7 +14797,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14844,7 +14847,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14894,7 +14897,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14944,7 +14947,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14994,7 +14997,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15044,7 +15047,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15094,7 +15097,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15144,7 +15147,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15194,7 +15197,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15244,7 +15247,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15294,7 +15297,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15344,7 +15347,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15394,7 +15397,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15444,7 +15447,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15494,7 +15497,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15544,7 +15547,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15594,7 +15597,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15644,7 +15647,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15694,7 +15697,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15744,7 +15747,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15794,7 +15797,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15844,7 +15847,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15894,7 +15897,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15944,7 +15947,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15994,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16044,7 +16047,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16094,7 +16097,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16144,7 +16147,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16194,7 +16197,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16244,7 +16247,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16294,7 +16297,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16344,7 +16347,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16394,7 +16397,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16444,7 +16447,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16494,7 +16497,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16544,7 +16547,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16594,7 +16597,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16644,7 +16647,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16694,7 +16697,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16744,7 +16747,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16794,7 +16797,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16844,7 +16847,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16894,7 +16897,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16944,7 +16947,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17144,7 +17147,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17194,7 +17197,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17244,7 +17247,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17294,7 +17297,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17344,7 +17347,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17394,7 +17397,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17444,7 +17447,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17494,7 +17497,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17544,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17594,7 +17597,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17644,7 +17647,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17694,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17744,7 +17747,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17794,7 +17797,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17844,7 +17847,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17894,7 +17897,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17944,7 +17947,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17994,7 +17997,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18044,7 +18047,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18094,7 +18097,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18144,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18194,7 +18197,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18244,7 +18247,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18294,7 +18297,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18344,7 +18347,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18594,7 +18597,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18644,7 +18647,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18694,7 +18697,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18744,7 +18747,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18794,7 +18797,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18844,7 +18847,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18894,7 +18897,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18944,7 +18947,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18994,7 +18997,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19044,7 +19047,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19094,7 +19097,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19144,7 +19147,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19594,7 +19597,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19644,7 +19647,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19694,7 +19697,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19744,7 +19747,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19794,7 +19797,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19844,7 +19847,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19894,7 +19897,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19944,7 +19947,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19994,7 +19997,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20044,7 +20047,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20094,7 +20097,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20144,7 +20147,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20194,7 +20197,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20244,7 +20247,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20294,7 +20297,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20344,7 +20347,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20544,7 +20547,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20594,7 +20597,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20644,7 +20647,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20694,7 +20697,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20894,7 +20897,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20944,7 +20947,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20994,7 +20997,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21044,7 +21047,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21094,7 +21097,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21144,7 +21147,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21194,7 +21197,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21244,7 +21247,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21294,7 +21297,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21344,7 +21347,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21394,7 +21397,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21444,7 +21447,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21494,7 +21497,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21544,7 +21547,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21594,7 +21597,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21644,7 +21647,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21694,7 +21697,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21744,7 +21747,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21794,7 +21797,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21844,7 +21847,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21894,7 +21897,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21944,7 +21947,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21994,7 +21997,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22044,7 +22047,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22094,7 +22097,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22144,7 +22147,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22194,7 +22197,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22244,7 +22247,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22294,7 +22297,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22344,7 +22347,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22394,7 +22397,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22444,7 +22447,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22494,7 +22497,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22694,7 +22697,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22744,7 +22747,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22794,7 +22797,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22844,7 +22847,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22894,7 +22897,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22944,7 +22947,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23144,7 +23147,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23194,7 +23197,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23244,7 +23247,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23294,7 +23297,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23344,7 +23347,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23394,7 +23397,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23444,7 +23447,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23494,7 +23497,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23544,7 +23547,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23594,7 +23597,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23644,7 +23647,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23694,7 +23697,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23744,7 +23747,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23794,7 +23797,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23844,7 +23847,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23894,7 +23897,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23944,7 +23947,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23994,7 +23997,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24044,7 +24047,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24094,7 +24097,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24144,7 +24147,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24194,7 +24197,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24244,7 +24247,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24294,7 +24297,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24344,7 +24347,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24394,7 +24397,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24444,7 +24447,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24494,7 +24497,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24544,7 +24547,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24594,7 +24597,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24644,7 +24647,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24694,7 +24697,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24744,7 +24747,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24794,7 +24797,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24844,7 +24847,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24894,7 +24897,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24944,7 +24947,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24994,7 +24997,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25044,7 +25047,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25094,7 +25097,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25144,7 +25147,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25194,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25494,7 +25497,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25544,7 +25547,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25594,7 +25597,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25644,7 +25647,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25694,7 +25697,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25744,7 +25747,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25794,7 +25797,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25844,7 +25847,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25894,7 +25897,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25944,7 +25947,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25994,7 +25997,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26044,7 +26047,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26094,7 +26097,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26144,7 +26147,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26194,7 +26197,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26244,7 +26247,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26294,7 +26297,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26344,7 +26347,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26394,7 +26397,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26444,7 +26447,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26494,7 +26497,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26544,7 +26547,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26594,7 +26597,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26644,7 +26647,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26694,7 +26697,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26744,7 +26747,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26794,7 +26797,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26844,7 +26847,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26894,7 +26897,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26944,7 +26947,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26994,7 +26997,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27044,7 +27047,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27094,7 +27097,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27144,7 +27147,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27194,7 +27197,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27244,7 +27247,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27294,7 +27297,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27344,7 +27347,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27394,7 +27397,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27444,7 +27447,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27494,7 +27497,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27544,7 +27547,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27594,7 +27597,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27644,7 +27647,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27661,7 +27664,7 @@
         <v>163</v>
       </c>
       <c r="E523">
-        <v>0.5181379488404918</v>
+        <v>0.2816336379392261</v>
       </c>
       <c r="F523">
         <v>-1</v>
@@ -27670,10 +27673,10 @@
         <v>0.01358335199238989</v>
       </c>
       <c r="H523">
-        <v>0.01290186205115951</v>
+        <v>0.01227836636206077</v>
       </c>
       <c r="I523">
-        <v>-0.2214899412303808</v>
+        <v>0.01501436967088488</v>
       </c>
       <c r="J523">
         <v>1.612464075822789</v>
@@ -27685,16 +27688,16 @@
         <v>6.94</v>
       </c>
       <c r="M523">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="N523">
-        <v>6.71</v>
+        <v>6.28</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27744,7 +27747,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27755,46 +27758,46 @@
         <v>71</v>
       </c>
       <c r="C525">
-        <v>-0.2934514275126689</v>
+        <v>-0.07671408163671245</v>
       </c>
       <c r="D525" t="s">
         <v>163</v>
       </c>
       <c r="E525">
-        <v>-0.07671408163671245</v>
+        <v>-0.2946292665855657</v>
       </c>
       <c r="F525">
         <v>-1</v>
       </c>
       <c r="G525">
-        <v>0.01363345142751267</v>
+        <v>0.01349671408163671</v>
       </c>
       <c r="H525">
-        <v>0.01349671408163671</v>
+        <v>0.01285462926658557</v>
       </c>
       <c r="I525">
-        <v>-0.2167373458759565</v>
+        <v>0.2179151849488532</v>
       </c>
       <c r="J525">
         <v>1.767373458759561</v>
       </c>
       <c r="K525">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="L525">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="M525">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="N525">
-        <v>6.71</v>
+        <v>6.28</v>
       </c>
       <c r="O525">
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27844,51 +27847,51 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B527" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C527">
-        <v>-2.042162178706638</v>
+        <v>-0.1723011159990033</v>
       </c>
       <c r="D527" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E527">
-        <v>-1.015055619828202</v>
+        <v>-0.3872292061240348</v>
       </c>
       <c r="F527">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G527">
-        <v>0.01250216217870664</v>
+        <v>0.013592301115999</v>
       </c>
       <c r="H527">
-        <v>0.0126950556198282</v>
+        <v>0.01294722920612404</v>
       </c>
       <c r="I527">
-        <v>1.027106558878436</v>
+        <v>0.2149280901250314</v>
       </c>
       <c r="J527">
-        <v>1.813506777732329</v>
+        <v>1.79226591562474</v>
       </c>
       <c r="K527">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="L527">
-        <v>5.23</v>
+        <v>6.71</v>
       </c>
       <c r="M527">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="N527">
-        <v>5.84</v>
+        <v>6.28</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27905,28 +27908,28 @@
         <v>69</v>
       </c>
       <c r="C528">
-        <v>-2.134185588757242</v>
+        <v>-2.042162178706638</v>
       </c>
       <c r="D528" t="s">
         <v>162</v>
       </c>
       <c r="E528">
-        <v>-1.10180087917765</v>
+        <v>-1.015055619828202</v>
       </c>
       <c r="F528">
         <v>1</v>
       </c>
       <c r="G528">
-        <v>0.01259418558875724</v>
+        <v>0.01250216217870664</v>
       </c>
       <c r="H528">
-        <v>0.01278180087917765</v>
+        <v>0.0126950556198282</v>
       </c>
       <c r="I528">
-        <v>1.032384709579592</v>
+        <v>1.027106558878436</v>
       </c>
       <c r="J528">
-        <v>1.836455259041706</v>
+        <v>1.813506777732329</v>
       </c>
       <c r="K528">
         <v>4.01</v>
@@ -27949,52 +27952,52 @@
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B529" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C529">
-        <v>-2.24491864020763</v>
+        <v>-0.2538660264921422</v>
       </c>
       <c r="D529" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E529">
-        <v>-1.002390603922223</v>
+        <v>-0.4662452131642629</v>
       </c>
       <c r="F529">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G529">
-        <v>0.01270491864020763</v>
+        <v>0.01367386602649214</v>
       </c>
       <c r="H529">
-        <v>0.01566239060392222</v>
+        <v>0.01302624521316426</v>
       </c>
       <c r="I529">
-        <v>1.242528036285408</v>
+        <v>0.2123791866721207</v>
       </c>
       <c r="J529">
-        <v>1.864069486336068</v>
+        <v>1.813506777732329</v>
       </c>
       <c r="K529">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="L529">
-        <v>5.23</v>
+        <v>6.71</v>
       </c>
       <c r="M529">
-        <v>4.47</v>
+        <v>3.72</v>
       </c>
       <c r="N529">
-        <v>7.33</v>
+        <v>6.28</v>
       </c>
       <c r="O529">
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28005,28 +28008,28 @@
         <v>69</v>
       </c>
       <c r="C530">
-        <v>-2.39134798609852</v>
+        <v>-2.134185588757242</v>
       </c>
       <c r="D530" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E530">
-        <v>-1.165617331137254</v>
+        <v>-1.10180087917765</v>
       </c>
       <c r="F530">
         <v>1</v>
       </c>
       <c r="G530">
-        <v>0.01285134798609852</v>
+        <v>0.01259418558875724</v>
       </c>
       <c r="H530">
-        <v>0.01582561733113725</v>
+        <v>0.01278180087917765</v>
       </c>
       <c r="I530">
-        <v>1.225730654961266</v>
+        <v>1.032384709579592</v>
       </c>
       <c r="J530">
-        <v>1.900585532692898</v>
+        <v>1.836455259041706</v>
       </c>
       <c r="K530">
         <v>4.01</v>
@@ -28035,104 +28038,104 @@
         <v>5.23</v>
       </c>
       <c r="M530">
-        <v>4.47</v>
+        <v>3.78</v>
       </c>
       <c r="N530">
-        <v>7.33</v>
+        <v>5.84</v>
       </c>
       <c r="O530">
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B531" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C531">
-        <v>-2.546512840679558</v>
+        <v>-0.3419881947201517</v>
       </c>
       <c r="D531" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E531">
-        <v>-1.338581645346041</v>
+        <v>-0.5516135636351471</v>
       </c>
       <c r="F531">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G531">
-        <v>0.01300651284067956</v>
+        <v>0.01376198819472015</v>
       </c>
       <c r="H531">
-        <v>0.01599858164534604</v>
+        <v>0.01311161356363515</v>
       </c>
       <c r="I531">
-        <v>1.207931195333517</v>
+        <v>0.2096253689149954</v>
       </c>
       <c r="J531">
-        <v>1.939280010144528</v>
+        <v>1.836455259041706</v>
       </c>
       <c r="K531">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="L531">
-        <v>5.23</v>
+        <v>6.71</v>
       </c>
       <c r="M531">
-        <v>4.47</v>
+        <v>3.72</v>
       </c>
       <c r="N531">
-        <v>7.33</v>
+        <v>6.28</v>
       </c>
       <c r="O531">
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B532" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C532">
-        <v>-2.088049638752098</v>
+        <v>-2.24491864020763</v>
       </c>
       <c r="D532" t="s">
         <v>164</v>
       </c>
       <c r="E532">
-        <v>-1.338581645346041</v>
+        <v>-1.002390603922223</v>
       </c>
       <c r="F532">
         <v>1</v>
       </c>
       <c r="G532">
-        <v>0.0127280496387521</v>
+        <v>0.01270491864020763</v>
       </c>
       <c r="H532">
-        <v>0.01599858164534604</v>
+        <v>0.01566239060392222</v>
       </c>
       <c r="I532">
-        <v>0.7494679934060571</v>
+        <v>1.242528036285408</v>
       </c>
       <c r="J532">
-        <v>1.939280010144528</v>
+        <v>1.864069486336068</v>
       </c>
       <c r="K532">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L532">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M532">
         <v>4.47</v>
@@ -28144,307 +28147,307 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B533" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C533">
-        <v>-2.943692670373876</v>
+        <v>-0.4480268275304997</v>
       </c>
       <c r="D533" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E533">
-        <v>-1.695574148632207</v>
+        <v>-0.654338489170172</v>
       </c>
       <c r="F533">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G533">
-        <v>0.01340369267037388</v>
+        <v>0.0138680268275305</v>
       </c>
       <c r="H533">
-        <v>0.01591557414863221</v>
+        <v>0.01321433848917017</v>
       </c>
       <c r="I533">
-        <v>1.248118521741669</v>
+        <v>0.2063116616396723</v>
       </c>
       <c r="J533">
-        <v>2.038327349220418</v>
+        <v>1.864069486336068</v>
       </c>
       <c r="K533">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="L533">
-        <v>5.23</v>
+        <v>6.71</v>
       </c>
       <c r="M533">
-        <v>4.32</v>
+        <v>3.72</v>
       </c>
       <c r="N533">
-        <v>7.11</v>
+        <v>6.28</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B534" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C534">
-        <v>-2.466410474021997</v>
+        <v>-2.39134798609852</v>
       </c>
       <c r="D534" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E534">
-        <v>-1.695574148632207</v>
+        <v>-1.165617331137254</v>
       </c>
       <c r="F534">
         <v>1</v>
       </c>
       <c r="G534">
-        <v>0.013106410474022</v>
+        <v>0.01285134798609852</v>
       </c>
       <c r="H534">
-        <v>0.01591557414863221</v>
+        <v>0.01582561733113725</v>
       </c>
       <c r="I534">
-        <v>0.7708363253897899</v>
+        <v>1.225730654961266</v>
       </c>
       <c r="J534">
-        <v>2.038327349220418</v>
+        <v>1.900585532692898</v>
       </c>
       <c r="K534">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L534">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M534">
-        <v>4.32</v>
+        <v>4.47</v>
       </c>
       <c r="N534">
-        <v>7.11</v>
+        <v>7.33</v>
       </c>
       <c r="O534">
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B535" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C535">
-        <v>-3.302184308580614</v>
+        <v>-0.588248445540728</v>
       </c>
       <c r="D535" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E535">
-        <v>-2.00751151980996</v>
+        <v>-0.7901781816175806</v>
       </c>
       <c r="F535">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G535">
-        <v>0.01376218430858061</v>
+        <v>0.01400824844554073</v>
       </c>
       <c r="H535">
-        <v>0.01556751151980996</v>
+        <v>0.01335017818161758</v>
       </c>
       <c r="I535">
-        <v>1.294672788770654</v>
+        <v>0.2019297360768526</v>
       </c>
       <c r="J535">
-        <v>2.127726760244542</v>
+        <v>1.900585532692898</v>
       </c>
       <c r="K535">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="L535">
-        <v>5.23</v>
+        <v>6.71</v>
       </c>
       <c r="M535">
-        <v>4.13</v>
+        <v>3.72</v>
       </c>
       <c r="N535">
-        <v>6.78</v>
+        <v>6.28</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B536" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C536">
-        <v>-2.807916224134152</v>
+        <v>-2.546512840679558</v>
       </c>
       <c r="D536" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E536">
-        <v>-2.00751151980996</v>
+        <v>-1.338581645346041</v>
       </c>
       <c r="F536">
         <v>1</v>
       </c>
       <c r="G536">
-        <v>0.01344791622413415</v>
+        <v>0.01300651284067956</v>
       </c>
       <c r="H536">
-        <v>0.01556751151980996</v>
+        <v>0.01599858164534604</v>
       </c>
       <c r="I536">
-        <v>0.8004047043241913</v>
+        <v>1.207931195333517</v>
       </c>
       <c r="J536">
-        <v>2.127726760244542</v>
+        <v>1.939280010144528</v>
       </c>
       <c r="K536">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L536">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M536">
-        <v>4.13</v>
+        <v>4.47</v>
       </c>
       <c r="N536">
-        <v>6.78</v>
+        <v>7.33</v>
       </c>
       <c r="O536">
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B537" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C537">
-        <v>-3.440693413369869</v>
+        <v>-2.088049638752098</v>
       </c>
       <c r="D537" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="E537">
-        <v>-1.968542858624404</v>
+        <v>-1.338581645346041</v>
       </c>
       <c r="F537">
         <v>1</v>
       </c>
       <c r="G537">
-        <v>0.01390069341336987</v>
+        <v>0.0127280496387521</v>
       </c>
       <c r="H537">
-        <v>0.0158485428586244</v>
+        <v>0.01599858164534604</v>
       </c>
       <c r="I537">
-        <v>1.472150554745466</v>
+        <v>0.7494679934060571</v>
       </c>
       <c r="J537">
-        <v>2.162267684132137</v>
+        <v>1.939280010144528</v>
       </c>
       <c r="K537">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L537">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M537">
-        <v>4.12</v>
+        <v>4.47</v>
       </c>
       <c r="N537">
-        <v>6.94</v>
+        <v>7.33</v>
       </c>
       <c r="O537">
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B538" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C538">
-        <v>-2.939862553384764</v>
+        <v>-0.7368352389549893</v>
       </c>
       <c r="D538" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="E538">
-        <v>-1.968542858624404</v>
+        <v>-0.934121637737646</v>
       </c>
       <c r="F538">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G538">
-        <v>0.01357986255338476</v>
+        <v>0.01415683523895499</v>
       </c>
       <c r="H538">
-        <v>0.0158485428586244</v>
+        <v>0.01349412163773765</v>
       </c>
       <c r="I538">
-        <v>0.9713196947603597</v>
+        <v>0.1972863987826567</v>
       </c>
       <c r="J538">
-        <v>2.162267684132137</v>
+        <v>1.939280010144528</v>
       </c>
       <c r="K538">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="L538">
-        <v>5.32</v>
+        <v>6.71</v>
       </c>
       <c r="M538">
-        <v>4.12</v>
+        <v>3.72</v>
       </c>
       <c r="N538">
-        <v>6.94</v>
+        <v>6.28</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28455,28 +28458,28 @@
         <v>69</v>
       </c>
       <c r="C539">
-        <v>-3.668901415448289</v>
+        <v>-2.943692670373876</v>
       </c>
       <c r="D539" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="E539">
-        <v>-2.203010930585275</v>
+        <v>-1.695574148632207</v>
       </c>
       <c r="F539">
         <v>1</v>
       </c>
       <c r="G539">
-        <v>0.01412890141544829</v>
+        <v>0.01340369267037388</v>
       </c>
       <c r="H539">
-        <v>0.01608301093058527</v>
+        <v>0.01591557414863221</v>
       </c>
       <c r="I539">
-        <v>1.465890484863015</v>
+        <v>1.248118521741669</v>
       </c>
       <c r="J539">
-        <v>2.219177410336232</v>
+        <v>2.038327349220418</v>
       </c>
       <c r="K539">
         <v>4.01</v>
@@ -28485,16 +28488,16 @@
         <v>5.23</v>
       </c>
       <c r="M539">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="N539">
-        <v>6.94</v>
+        <v>7.11</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28505,28 +28508,28 @@
         <v>72</v>
       </c>
       <c r="C540">
-        <v>-3.157257707484405</v>
+        <v>-2.466410474021997</v>
       </c>
       <c r="D540" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="E540">
-        <v>-2.203010930585275</v>
+        <v>-1.695574148632207</v>
       </c>
       <c r="F540">
         <v>1</v>
       </c>
       <c r="G540">
-        <v>0.01379725770748441</v>
+        <v>0.013106410474022</v>
       </c>
       <c r="H540">
-        <v>0.01608301093058527</v>
+        <v>0.01591557414863221</v>
       </c>
       <c r="I540">
-        <v>0.9542467768991303</v>
+        <v>0.7708363253897899</v>
       </c>
       <c r="J540">
-        <v>2.219177410336232</v>
+        <v>2.038327349220418</v>
       </c>
       <c r="K540">
         <v>3.82</v>
@@ -28535,16 +28538,16 @@
         <v>5.32</v>
       </c>
       <c r="M540">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="N540">
-        <v>6.94</v>
+        <v>7.11</v>
       </c>
       <c r="O540">
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28555,28 +28558,28 @@
         <v>69</v>
       </c>
       <c r="C541">
-        <v>-3.954888865249114</v>
+        <v>-3.302184308580614</v>
       </c>
       <c r="D541" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E541">
-        <v>-2.496843422649964</v>
+        <v>-2.00751151980996</v>
       </c>
       <c r="F541">
         <v>1</v>
       </c>
       <c r="G541">
-        <v>0.01441488886524911</v>
+        <v>0.01376218430858061</v>
       </c>
       <c r="H541">
-        <v>0.01637684342264997</v>
+        <v>0.01556751151980996</v>
       </c>
       <c r="I541">
-        <v>1.45804544259915</v>
+        <v>1.294672788770654</v>
       </c>
       <c r="J541">
-        <v>2.29049597637135</v>
+        <v>2.127726760244542</v>
       </c>
       <c r="K541">
         <v>4.01</v>
@@ -28585,16 +28588,16 @@
         <v>5.23</v>
       </c>
       <c r="M541">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="N541">
-        <v>6.94</v>
+        <v>6.78</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28605,28 +28608,28 @@
         <v>72</v>
       </c>
       <c r="C542">
-        <v>-3.429694629738558</v>
+        <v>-2.807916224134152</v>
       </c>
       <c r="D542" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E542">
-        <v>-2.496843422649964</v>
+        <v>-2.00751151980996</v>
       </c>
       <c r="F542">
         <v>1</v>
       </c>
       <c r="G542">
-        <v>0.01406969462973856</v>
+        <v>0.01344791622413415</v>
       </c>
       <c r="H542">
-        <v>0.01637684342264997</v>
+        <v>0.01556751151980996</v>
       </c>
       <c r="I542">
-        <v>0.9328512070885937</v>
+        <v>0.8004047043241913</v>
       </c>
       <c r="J542">
-        <v>2.29049597637135</v>
+        <v>2.127726760244542</v>
       </c>
       <c r="K542">
         <v>3.82</v>
@@ -28635,16 +28638,16 @@
         <v>5.32</v>
       </c>
       <c r="M542">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="N542">
-        <v>6.94</v>
+        <v>6.78</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28655,28 +28658,28 @@
         <v>69</v>
       </c>
       <c r="C543">
-        <v>-4.162550774568617</v>
+        <v>-3.440693413369869</v>
       </c>
       <c r="D543" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E543">
-        <v>-2.558591035361685</v>
+        <v>-1.968542858624404</v>
       </c>
       <c r="F543">
         <v>1</v>
       </c>
       <c r="G543">
-        <v>0.01462255077456862</v>
+        <v>0.01390069341336987</v>
       </c>
       <c r="H543">
-        <v>0.01589859103536169</v>
+        <v>0.0158485428586244</v>
       </c>
       <c r="I543">
-        <v>1.603959739206932</v>
+        <v>1.472150554745466</v>
       </c>
       <c r="J543">
-        <v>2.342281988670478</v>
+        <v>2.162267684132137</v>
       </c>
       <c r="K543">
         <v>4.01</v>
@@ -28685,16 +28688,16 @@
         <v>5.23</v>
       </c>
       <c r="M543">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="N543">
-        <v>6.67</v>
+        <v>6.94</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28705,28 +28708,28 @@
         <v>72</v>
       </c>
       <c r="C544">
-        <v>-3.627517196721227</v>
+        <v>-2.939862553384764</v>
       </c>
       <c r="D544" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E544">
-        <v>-2.558591035361685</v>
+        <v>-1.968542858624404</v>
       </c>
       <c r="F544">
         <v>1</v>
       </c>
       <c r="G544">
-        <v>0.01426751719672123</v>
+        <v>0.01357986255338476</v>
       </c>
       <c r="H544">
-        <v>0.01589859103536169</v>
+        <v>0.0158485428586244</v>
       </c>
       <c r="I544">
-        <v>1.068926161359542</v>
+        <v>0.9713196947603597</v>
       </c>
       <c r="J544">
-        <v>2.342281988670478</v>
+        <v>2.162267684132137</v>
       </c>
       <c r="K544">
         <v>3.82</v>
@@ -28735,16 +28738,16 @@
         <v>5.32</v>
       </c>
       <c r="M544">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="N544">
-        <v>6.67</v>
+        <v>6.94</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28755,28 +28758,28 @@
         <v>69</v>
       </c>
       <c r="C545">
-        <v>-4.341021841271511</v>
+        <v>-3.668901415448289</v>
       </c>
       <c r="D545" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E545">
-        <v>-2.733946647034852</v>
+        <v>-2.203010930585275</v>
       </c>
       <c r="F545">
         <v>1</v>
       </c>
       <c r="G545">
-        <v>0.01480102184127151</v>
+        <v>0.01412890141544829</v>
       </c>
       <c r="H545">
-        <v>0.01607394664703485</v>
+        <v>0.01608301093058527</v>
       </c>
       <c r="I545">
-        <v>1.607075194236659</v>
+        <v>1.465890484863015</v>
       </c>
       <c r="J545">
-        <v>2.38678848909514</v>
+        <v>2.219177410336232</v>
       </c>
       <c r="K545">
         <v>4.01</v>
@@ -28785,16 +28788,16 @@
         <v>5.23</v>
       </c>
       <c r="M545">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="N545">
-        <v>6.67</v>
+        <v>6.94</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28805,28 +28808,28 @@
         <v>72</v>
       </c>
       <c r="C546">
-        <v>-3.797532028343435</v>
+        <v>-3.157257707484405</v>
       </c>
       <c r="D546" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E546">
-        <v>-2.733946647034852</v>
+        <v>-2.203010930585275</v>
       </c>
       <c r="F546">
         <v>1</v>
       </c>
       <c r="G546">
-        <v>0.01443753202834343</v>
+        <v>0.01379725770748441</v>
       </c>
       <c r="H546">
-        <v>0.01607394664703485</v>
+        <v>0.01608301093058527</v>
       </c>
       <c r="I546">
-        <v>1.063585381308583</v>
+        <v>0.9542467768991303</v>
       </c>
       <c r="J546">
-        <v>2.38678848909514</v>
+        <v>2.219177410336232</v>
       </c>
       <c r="K546">
         <v>3.82</v>
@@ -28835,16 +28838,16 @@
         <v>5.32</v>
       </c>
       <c r="M546">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="N546">
-        <v>6.67</v>
+        <v>6.94</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28855,28 +28858,28 @@
         <v>69</v>
       </c>
       <c r="C547">
-        <v>-4.38270256915019</v>
+        <v>-3.954888865249114</v>
       </c>
       <c r="D547" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E547">
-        <v>-2.774899781160038</v>
+        <v>-2.496843422649964</v>
       </c>
       <c r="F547">
         <v>1</v>
       </c>
       <c r="G547">
-        <v>0.01484270256915019</v>
+        <v>0.01441488886524911</v>
       </c>
       <c r="H547">
-        <v>0.01611489978116004</v>
+        <v>0.01637684342264997</v>
       </c>
       <c r="I547">
-        <v>1.607802787990153</v>
+        <v>1.45804544259915</v>
       </c>
       <c r="J547">
-        <v>2.397182685573614</v>
+        <v>2.29049597637135</v>
       </c>
       <c r="K547">
         <v>4.01</v>
@@ -28885,16 +28888,16 @@
         <v>5.23</v>
       </c>
       <c r="M547">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="N547">
-        <v>6.67</v>
+        <v>6.94</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28905,28 +28908,28 @@
         <v>72</v>
       </c>
       <c r="C548">
-        <v>-3.837237858891204</v>
+        <v>-3.429694629738558</v>
       </c>
       <c r="D548" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E548">
-        <v>-2.774899781160038</v>
+        <v>-2.496843422649964</v>
       </c>
       <c r="F548">
         <v>1</v>
       </c>
       <c r="G548">
-        <v>0.01447723785889121</v>
+        <v>0.01406969462973856</v>
       </c>
       <c r="H548">
-        <v>0.01611489978116004</v>
+        <v>0.01637684342264997</v>
       </c>
       <c r="I548">
-        <v>1.062338077731166</v>
+        <v>0.9328512070885937</v>
       </c>
       <c r="J548">
-        <v>2.397182685573614</v>
+        <v>2.29049597637135</v>
       </c>
       <c r="K548">
         <v>3.82</v>
@@ -28935,16 +28938,16 @@
         <v>5.32</v>
       </c>
       <c r="M548">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="N548">
-        <v>6.67</v>
+        <v>6.94</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28955,28 +28958,28 @@
         <v>69</v>
       </c>
       <c r="C549">
-        <v>-4.411855003341485</v>
+        <v>-4.162550774568617</v>
       </c>
       <c r="D549" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E549">
-        <v>-2.803543319991386</v>
+        <v>-2.558591035361685</v>
       </c>
       <c r="F549">
         <v>1</v>
       </c>
       <c r="G549">
-        <v>0.01487185500334148</v>
+        <v>0.01462255077456862</v>
       </c>
       <c r="H549">
-        <v>0.01614354331999139</v>
+        <v>0.01589859103536169</v>
       </c>
       <c r="I549">
-        <v>1.608311683350099</v>
+        <v>1.603959739206932</v>
       </c>
       <c r="J549">
-        <v>2.404452619287154</v>
+        <v>2.342281988670478</v>
       </c>
       <c r="K549">
         <v>4.01</v>
@@ -28994,7 +28997,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29005,28 +29008,28 @@
         <v>72</v>
       </c>
       <c r="C550">
-        <v>-3.865009005676926</v>
+        <v>-3.627517196721227</v>
       </c>
       <c r="D550" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E550">
-        <v>-2.803543319991386</v>
+        <v>-2.558591035361685</v>
       </c>
       <c r="F550">
         <v>1</v>
       </c>
       <c r="G550">
-        <v>0.01450500900567693</v>
+        <v>0.01426751719672123</v>
       </c>
       <c r="H550">
-        <v>0.01614354331999139</v>
+        <v>0.01589859103536169</v>
       </c>
       <c r="I550">
-        <v>1.06146568568554</v>
+        <v>1.068926161359542</v>
       </c>
       <c r="J550">
-        <v>2.404452619287154</v>
+        <v>2.342281988670478</v>
       </c>
       <c r="K550">
         <v>3.82</v>
@@ -29044,7 +29047,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29055,28 +29058,28 @@
         <v>69</v>
       </c>
       <c r="C551">
-        <v>-4.339272485484365</v>
+        <v>-4.341021841271511</v>
       </c>
       <c r="D551" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E551">
-        <v>-2.732227828630524</v>
+        <v>-2.733946647034852</v>
       </c>
       <c r="F551">
         <v>1</v>
       </c>
       <c r="G551">
-        <v>0.01479927248548437</v>
+        <v>0.01480102184127151</v>
       </c>
       <c r="H551">
-        <v>0.01607222782863052</v>
+        <v>0.01607394664703485</v>
       </c>
       <c r="I551">
-        <v>1.607044656853841</v>
+        <v>1.607075194236659</v>
       </c>
       <c r="J551">
-        <v>2.386352240769169</v>
+        <v>2.38678848909514</v>
       </c>
       <c r="K551">
         <v>4.01</v>
@@ -29094,7 +29097,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29105,28 +29108,28 @@
         <v>72</v>
       </c>
       <c r="C552">
-        <v>-3.795865559738223</v>
+        <v>-3.797532028343435</v>
       </c>
       <c r="D552" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E552">
-        <v>-2.732227828630524</v>
+        <v>-2.733946647034852</v>
       </c>
       <c r="F552">
         <v>1</v>
       </c>
       <c r="G552">
-        <v>0.01443586555973822</v>
+        <v>0.01443753202834343</v>
       </c>
       <c r="H552">
-        <v>0.01607222782863052</v>
+        <v>0.01607394664703485</v>
       </c>
       <c r="I552">
-        <v>1.063637731107699</v>
+        <v>1.063585381308583</v>
       </c>
       <c r="J552">
-        <v>2.386352240769169</v>
+        <v>2.38678848909514</v>
       </c>
       <c r="K552">
         <v>3.82</v>
@@ -29144,7 +29147,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29155,28 +29158,28 @@
         <v>69</v>
       </c>
       <c r="C553">
-        <v>-4.278315541383607</v>
+        <v>-4.38270256915019</v>
       </c>
       <c r="D553" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E553">
-        <v>-2.672334970835765</v>
+        <v>-2.774899781160038</v>
       </c>
       <c r="F553">
         <v>1</v>
       </c>
       <c r="G553">
-        <v>0.01473831554138361</v>
+        <v>0.01484270256915019</v>
       </c>
       <c r="H553">
-        <v>0.01601233497083577</v>
+        <v>0.01611489978116004</v>
       </c>
       <c r="I553">
-        <v>1.605980570547842</v>
+        <v>1.607802787990153</v>
       </c>
       <c r="J553">
-        <v>2.371151007826336</v>
+        <v>2.397182685573614</v>
       </c>
       <c r="K553">
         <v>4.01</v>
@@ -29194,7 +29197,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29205,28 +29208,28 @@
         <v>72</v>
       </c>
       <c r="C554">
-        <v>-3.737796849896604</v>
+        <v>-3.837237858891204</v>
       </c>
       <c r="D554" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E554">
-        <v>-2.672334970835765</v>
+        <v>-2.774899781160038</v>
       </c>
       <c r="F554">
         <v>1</v>
       </c>
       <c r="G554">
-        <v>0.0143777968498966</v>
+        <v>0.01447723785889121</v>
       </c>
       <c r="H554">
-        <v>0.01601233497083577</v>
+        <v>0.01611489978116004</v>
       </c>
       <c r="I554">
-        <v>1.065461879060839</v>
+        <v>1.062338077731166</v>
       </c>
       <c r="J554">
-        <v>2.371151007826336</v>
+        <v>2.397182685573614</v>
       </c>
       <c r="K554">
         <v>3.82</v>
@@ -29244,7 +29247,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29255,28 +29258,28 @@
         <v>69</v>
       </c>
       <c r="C555">
-        <v>-4.215673134172834</v>
+        <v>-4.411855003341485</v>
       </c>
       <c r="D555" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E555">
-        <v>-2.610786071980291</v>
+        <v>-2.803543319991386</v>
       </c>
       <c r="F555">
         <v>1</v>
       </c>
       <c r="G555">
-        <v>0.01467567313417283</v>
+        <v>0.01487185500334148</v>
       </c>
       <c r="H555">
-        <v>0.01595078607198029</v>
+        <v>0.01614354331999139</v>
       </c>
       <c r="I555">
-        <v>1.604887062192542</v>
+        <v>1.608311683350099</v>
       </c>
       <c r="J555">
-        <v>2.355529459893475</v>
+        <v>2.404452619287154</v>
       </c>
       <c r="K555">
         <v>4.01</v>
@@ -29294,7 +29297,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29305,28 +29308,28 @@
         <v>72</v>
       </c>
       <c r="C556">
-        <v>-3.678122536793074</v>
+        <v>-3.865009005676926</v>
       </c>
       <c r="D556" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E556">
-        <v>-2.610786071980291</v>
+        <v>-2.803543319991386</v>
       </c>
       <c r="F556">
         <v>1</v>
       </c>
       <c r="G556">
-        <v>0.01431812253679307</v>
+        <v>0.01450500900567693</v>
       </c>
       <c r="H556">
-        <v>0.01595078607198029</v>
+        <v>0.01614354331999139</v>
       </c>
       <c r="I556">
-        <v>1.067336464812783</v>
+        <v>1.06146568568554</v>
       </c>
       <c r="J556">
-        <v>2.355529459893475</v>
+        <v>2.404452619287154</v>
       </c>
       <c r="K556">
         <v>3.82</v>
@@ -29344,7 +29347,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29355,28 +29358,28 @@
         <v>69</v>
       </c>
       <c r="C557">
-        <v>-4.189835924124937</v>
+        <v>-4.339272485484365</v>
       </c>
       <c r="D557" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="E557">
-        <v>-2.738235413315398</v>
+        <v>-2.732227828630524</v>
       </c>
       <c r="F557">
         <v>1</v>
       </c>
       <c r="G557">
-        <v>0.01464983592412494</v>
+        <v>0.01479927248548437</v>
       </c>
       <c r="H557">
-        <v>0.0166182354133154</v>
+        <v>0.01607222782863052</v>
       </c>
       <c r="I557">
-        <v>1.451600510809539</v>
+        <v>1.607044656853841</v>
       </c>
       <c r="J557">
-        <v>2.349086265367815</v>
+        <v>2.386352240769169</v>
       </c>
       <c r="K557">
         <v>4.01</v>
@@ -29385,66 +29388,66 @@
         <v>5.23</v>
       </c>
       <c r="M557">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N557">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O557">
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="558" spans="1:16">
       <c r="A558" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B558" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C558">
-        <v>-4.089470803698397</v>
+        <v>-3.795865559738223</v>
       </c>
       <c r="D558" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="E558">
-        <v>-2.63511713497192</v>
+        <v>-2.732227828630524</v>
       </c>
       <c r="F558">
         <v>1</v>
       </c>
       <c r="G558">
-        <v>0.0145494708036984</v>
+        <v>0.01443586555973822</v>
       </c>
       <c r="H558">
-        <v>0.01651511713497192</v>
+        <v>0.01607222782863052</v>
       </c>
       <c r="I558">
-        <v>1.454353668726477</v>
+        <v>1.063637731107699</v>
       </c>
       <c r="J558">
-        <v>2.324057557032019</v>
+        <v>2.386352240769169</v>
       </c>
       <c r="K558">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L558">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M558">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N558">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O558">
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29455,28 +29458,28 @@
         <v>69</v>
       </c>
       <c r="C559">
-        <v>-4.005320296309154</v>
+        <v>-4.278315541383607</v>
       </c>
       <c r="D559" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="E559">
-        <v>-2.548658259549556</v>
+        <v>-2.672334970835765</v>
       </c>
       <c r="F559">
         <v>1</v>
       </c>
       <c r="G559">
-        <v>0.01446532029630916</v>
+        <v>0.01473831554138361</v>
       </c>
       <c r="H559">
-        <v>0.01642865825954956</v>
+        <v>0.01601233497083577</v>
       </c>
       <c r="I559">
-        <v>1.456662036759599</v>
+        <v>1.605980570547842</v>
       </c>
       <c r="J559">
-        <v>2.303072393094552</v>
+        <v>2.371151007826336</v>
       </c>
       <c r="K559">
         <v>4.01</v>
@@ -29485,66 +29488,66 @@
         <v>5.23</v>
       </c>
       <c r="M559">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N559">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O559">
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="560" spans="1:16">
       <c r="A560" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B560" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C560">
-        <v>-3.880021728113258</v>
+        <v>-3.737796849896604</v>
       </c>
       <c r="D560" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="E560">
-        <v>-2.419922573522849</v>
+        <v>-2.672334970835765</v>
       </c>
       <c r="F560">
         <v>1</v>
       </c>
       <c r="G560">
-        <v>0.01434002172811326</v>
+        <v>0.0143777968498966</v>
       </c>
       <c r="H560">
-        <v>0.01629992257352285</v>
+        <v>0.01601233497083577</v>
       </c>
       <c r="I560">
-        <v>1.460099154590409</v>
+        <v>1.065461879060839</v>
       </c>
       <c r="J560">
-        <v>2.271825867359915</v>
+        <v>2.371151007826336</v>
       </c>
       <c r="K560">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L560">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M560">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N560">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O560">
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29555,28 +29558,28 @@
         <v>69</v>
       </c>
       <c r="C561">
-        <v>-3.765867342432312</v>
+        <v>-4.215673134172834</v>
       </c>
       <c r="D561" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="E561">
-        <v>-2.302636770778338</v>
+        <v>-2.610786071980291</v>
       </c>
       <c r="F561">
         <v>1</v>
       </c>
       <c r="G561">
-        <v>0.01422586734243231</v>
+        <v>0.01467567313417283</v>
       </c>
       <c r="H561">
-        <v>0.01618263677077834</v>
+        <v>0.01595078607198029</v>
       </c>
       <c r="I561">
-        <v>1.463230571653974</v>
+        <v>1.604887062192542</v>
       </c>
       <c r="J561">
-        <v>2.243358439509305</v>
+        <v>2.355529459893475</v>
       </c>
       <c r="K561">
         <v>4.01</v>
@@ -29585,66 +29588,66 @@
         <v>5.23</v>
       </c>
       <c r="M561">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N561">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O561">
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="562" spans="1:16">
       <c r="A562" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B562" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C562">
-        <v>-3.200435821279882</v>
+        <v>-3.678122536793074</v>
       </c>
       <c r="D562" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E562">
-        <v>-1.972165273797779</v>
+        <v>-2.610786071980291</v>
       </c>
       <c r="F562">
         <v>1</v>
       </c>
       <c r="G562">
-        <v>0.01366043582127988</v>
+        <v>0.01431812253679307</v>
       </c>
       <c r="H562">
-        <v>0.01619216527379778</v>
+        <v>0.01595078607198029</v>
       </c>
       <c r="I562">
-        <v>1.228270547482103</v>
+        <v>1.067336464812783</v>
       </c>
       <c r="J562">
-        <v>2.102353072638375</v>
+        <v>2.355529459893475</v>
       </c>
       <c r="K562">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L562">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M562">
-        <v>4.32</v>
+        <v>3.94</v>
       </c>
       <c r="N562">
-        <v>7.11</v>
+        <v>6.67</v>
       </c>
       <c r="O562">
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29655,28 +29658,28 @@
         <v>69</v>
       </c>
       <c r="C563">
-        <v>-2.562371230751202</v>
+        <v>-4.189835924124937</v>
       </c>
       <c r="D563" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E563">
-        <v>-1.505427244947517</v>
+        <v>-2.585399885549192</v>
       </c>
       <c r="F563">
         <v>1</v>
       </c>
       <c r="G563">
-        <v>0.0130223712307512</v>
+        <v>0.01464983592412494</v>
       </c>
       <c r="H563">
-        <v>0.01318542724494752</v>
+        <v>0.01592539988554919</v>
       </c>
       <c r="I563">
-        <v>1.056943985803684</v>
+        <v>1.604436038575745</v>
       </c>
       <c r="J563">
-        <v>1.943234720885587</v>
+        <v>2.349086265367815</v>
       </c>
       <c r="K563">
         <v>4.01</v>
@@ -29685,16 +29688,416 @@
         <v>5.23</v>
       </c>
       <c r="M563">
+        <v>3.94</v>
+      </c>
+      <c r="N563">
+        <v>6.67</v>
+      </c>
+      <c r="O563">
+        <v>1</v>
+      </c>
+      <c r="P563" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="564" spans="1:16">
+      <c r="A564" s="1">
+        <v>1</v>
+      </c>
+      <c r="B564" t="s">
+        <v>72</v>
+      </c>
+      <c r="C564">
+        <v>-3.653509533705053</v>
+      </c>
+      <c r="D564" t="s">
+        <v>167</v>
+      </c>
+      <c r="E564">
+        <v>-2.585399885549192</v>
+      </c>
+      <c r="F564">
+        <v>1</v>
+      </c>
+      <c r="G564">
+        <v>0.01429350953370505</v>
+      </c>
+      <c r="H564">
+        <v>0.01592539988554919</v>
+      </c>
+      <c r="I564">
+        <v>1.068109648155861</v>
+      </c>
+      <c r="J564">
+        <v>2.349086265367815</v>
+      </c>
+      <c r="K564">
+        <v>3.82</v>
+      </c>
+      <c r="L564">
+        <v>5.32</v>
+      </c>
+      <c r="M564">
+        <v>3.94</v>
+      </c>
+      <c r="N564">
+        <v>6.67</v>
+      </c>
+      <c r="O564">
+        <v>1</v>
+      </c>
+      <c r="P564" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="565" spans="1:16">
+      <c r="A565" s="1">
+        <v>0</v>
+      </c>
+      <c r="B565" t="s">
+        <v>69</v>
+      </c>
+      <c r="C565">
+        <v>-4.089470803698397</v>
+      </c>
+      <c r="D565" t="s">
+        <v>70</v>
+      </c>
+      <c r="E565">
+        <v>-2.63511713497192</v>
+      </c>
+      <c r="F565">
+        <v>1</v>
+      </c>
+      <c r="G565">
+        <v>0.0145494708036984</v>
+      </c>
+      <c r="H565">
+        <v>0.01651511713497192</v>
+      </c>
+      <c r="I565">
+        <v>1.454353668726477</v>
+      </c>
+      <c r="J565">
+        <v>2.324057557032019</v>
+      </c>
+      <c r="K565">
+        <v>4.01</v>
+      </c>
+      <c r="L565">
+        <v>5.23</v>
+      </c>
+      <c r="M565">
+        <v>4.12</v>
+      </c>
+      <c r="N565">
+        <v>6.94</v>
+      </c>
+      <c r="O565">
+        <v>1</v>
+      </c>
+      <c r="P565" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="566" spans="1:16">
+      <c r="A566" s="1">
+        <v>0</v>
+      </c>
+      <c r="B566" t="s">
+        <v>69</v>
+      </c>
+      <c r="C566">
+        <v>-4.005320296309154</v>
+      </c>
+      <c r="D566" t="s">
+        <v>70</v>
+      </c>
+      <c r="E566">
+        <v>-2.548658259549556</v>
+      </c>
+      <c r="F566">
+        <v>1</v>
+      </c>
+      <c r="G566">
+        <v>0.01446532029630916</v>
+      </c>
+      <c r="H566">
+        <v>0.01642865825954956</v>
+      </c>
+      <c r="I566">
+        <v>1.456662036759599</v>
+      </c>
+      <c r="J566">
+        <v>2.303072393094552</v>
+      </c>
+      <c r="K566">
+        <v>4.01</v>
+      </c>
+      <c r="L566">
+        <v>5.23</v>
+      </c>
+      <c r="M566">
+        <v>4.12</v>
+      </c>
+      <c r="N566">
+        <v>6.94</v>
+      </c>
+      <c r="O566">
+        <v>1</v>
+      </c>
+      <c r="P566" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="567" spans="1:16">
+      <c r="A567" s="1">
+        <v>0</v>
+      </c>
+      <c r="B567" t="s">
+        <v>69</v>
+      </c>
+      <c r="C567">
+        <v>-3.880021728113258</v>
+      </c>
+      <c r="D567" t="s">
+        <v>70</v>
+      </c>
+      <c r="E567">
+        <v>-2.419922573522849</v>
+      </c>
+      <c r="F567">
+        <v>1</v>
+      </c>
+      <c r="G567">
+        <v>0.01434002172811326</v>
+      </c>
+      <c r="H567">
+        <v>0.01629992257352285</v>
+      </c>
+      <c r="I567">
+        <v>1.460099154590409</v>
+      </c>
+      <c r="J567">
+        <v>2.271825867359915</v>
+      </c>
+      <c r="K567">
+        <v>4.01</v>
+      </c>
+      <c r="L567">
+        <v>5.23</v>
+      </c>
+      <c r="M567">
+        <v>4.12</v>
+      </c>
+      <c r="N567">
+        <v>6.94</v>
+      </c>
+      <c r="O567">
+        <v>1</v>
+      </c>
+      <c r="P567" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="568" spans="1:16">
+      <c r="A568" s="1">
+        <v>0</v>
+      </c>
+      <c r="B568" t="s">
+        <v>69</v>
+      </c>
+      <c r="C568">
+        <v>-3.765867342432312</v>
+      </c>
+      <c r="D568" t="s">
+        <v>70</v>
+      </c>
+      <c r="E568">
+        <v>-2.302636770778338</v>
+      </c>
+      <c r="F568">
+        <v>1</v>
+      </c>
+      <c r="G568">
+        <v>0.01422586734243231</v>
+      </c>
+      <c r="H568">
+        <v>0.01618263677077834</v>
+      </c>
+      <c r="I568">
+        <v>1.463230571653974</v>
+      </c>
+      <c r="J568">
+        <v>2.243358439509305</v>
+      </c>
+      <c r="K568">
+        <v>4.01</v>
+      </c>
+      <c r="L568">
+        <v>5.23</v>
+      </c>
+      <c r="M568">
+        <v>4.12</v>
+      </c>
+      <c r="N568">
+        <v>6.94</v>
+      </c>
+      <c r="O568">
+        <v>1</v>
+      </c>
+      <c r="P568" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="569" spans="1:16">
+      <c r="A569" s="1">
+        <v>0</v>
+      </c>
+      <c r="B569" t="s">
+        <v>69</v>
+      </c>
+      <c r="C569">
+        <v>-3.200435821279882</v>
+      </c>
+      <c r="D569" t="s">
+        <v>165</v>
+      </c>
+      <c r="E569">
+        <v>-1.972165273797779</v>
+      </c>
+      <c r="F569">
+        <v>1</v>
+      </c>
+      <c r="G569">
+        <v>0.01366043582127988</v>
+      </c>
+      <c r="H569">
+        <v>0.01619216527379778</v>
+      </c>
+      <c r="I569">
+        <v>1.228270547482103</v>
+      </c>
+      <c r="J569">
+        <v>2.102353072638375</v>
+      </c>
+      <c r="K569">
+        <v>4.01</v>
+      </c>
+      <c r="L569">
+        <v>5.23</v>
+      </c>
+      <c r="M569">
+        <v>4.32</v>
+      </c>
+      <c r="N569">
+        <v>7.11</v>
+      </c>
+      <c r="O569">
+        <v>1</v>
+      </c>
+      <c r="P569" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="570" spans="1:16">
+      <c r="A570" s="1">
+        <v>0</v>
+      </c>
+      <c r="B570" t="s">
+        <v>69</v>
+      </c>
+      <c r="C570">
+        <v>-2.562371230751202</v>
+      </c>
+      <c r="D570" t="s">
+        <v>162</v>
+      </c>
+      <c r="E570">
+        <v>-1.505427244947517</v>
+      </c>
+      <c r="F570">
+        <v>1</v>
+      </c>
+      <c r="G570">
+        <v>0.0130223712307512</v>
+      </c>
+      <c r="H570">
+        <v>0.01318542724494752</v>
+      </c>
+      <c r="I570">
+        <v>1.056943985803684</v>
+      </c>
+      <c r="J570">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K570">
+        <v>4.01</v>
+      </c>
+      <c r="L570">
+        <v>5.23</v>
+      </c>
+      <c r="M570">
         <v>3.78</v>
       </c>
-      <c r="N563">
+      <c r="N570">
         <v>5.84</v>
       </c>
-      <c r="O563">
-        <v>1</v>
-      </c>
-      <c r="P563" t="s">
-        <v>391</v>
+      <c r="O570">
+        <v>1</v>
+      </c>
+      <c r="P570" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="571" spans="1:16">
+      <c r="A571" s="1">
+        <v>1</v>
+      </c>
+      <c r="B571" t="s">
+        <v>71</v>
+      </c>
+      <c r="C571">
+        <v>-0.7520213282006525</v>
+      </c>
+      <c r="D571" t="s">
+        <v>163</v>
+      </c>
+      <c r="E571">
+        <v>-0.9488331616943828</v>
+      </c>
+      <c r="F571">
+        <v>-1</v>
+      </c>
+      <c r="G571">
+        <v>0.01417202132820065</v>
+      </c>
+      <c r="H571">
+        <v>0.01350883316169438</v>
+      </c>
+      <c r="I571">
+        <v>0.1968118334937303</v>
+      </c>
+      <c r="J571">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K571">
+        <v>3.84</v>
+      </c>
+      <c r="L571">
+        <v>6.71</v>
+      </c>
+      <c r="M571">
+        <v>3.72</v>
+      </c>
+      <c r="N571">
+        <v>6.28</v>
+      </c>
+      <c r="O571">
+        <v>1</v>
+      </c>
+      <c r="P571" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="392">
   <si>
     <t>trade_time</t>
   </si>
@@ -505,16 +505,13 @@
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-09-16</t>
+    <t>2021-09-17</t>
   </si>
   <si>
     <t>2021-09-06</t>
   </si>
   <si>
     <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-09-10</t>
   </si>
   <si>
     <t>2021-09-14</t>
@@ -1647,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1697,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1747,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1797,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1847,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1897,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1947,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1997,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2047,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2097,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2147,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2197,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2247,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2297,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2347,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2397,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2447,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2497,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2547,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2597,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2647,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2697,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2747,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2797,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2847,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2897,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2947,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2997,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3047,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3097,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3147,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3197,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3247,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3297,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3347,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3397,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3447,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3497,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3547,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3597,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3647,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3697,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3747,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3797,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3847,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3897,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3947,7 +3944,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3997,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4047,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4097,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4147,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4197,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4247,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4297,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4347,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4397,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4447,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4497,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4547,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4597,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4647,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4697,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4747,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4797,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4847,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4897,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4947,7 +4944,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4997,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5047,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5097,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5147,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5197,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5247,7 +5244,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5297,7 +5294,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5347,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5397,7 +5394,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5447,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5497,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5547,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5597,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5647,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5697,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5747,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5797,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5847,7 +5844,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5897,7 +5894,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5947,7 +5944,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5997,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6047,7 +6044,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6097,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6147,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6197,7 +6194,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6247,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6297,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6347,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6397,7 +6394,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6447,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6497,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6547,7 +6544,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6597,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6647,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6697,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6747,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6797,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6847,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6897,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6947,7 +6944,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6997,7 +6994,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7047,7 +7044,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7097,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7147,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7197,7 +7194,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7247,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7297,7 +7294,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7347,7 +7344,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7397,7 +7394,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7447,7 +7444,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7497,7 +7494,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7547,7 +7544,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7597,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7647,7 +7644,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7697,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7747,7 +7744,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7797,7 +7794,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7847,7 +7844,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7897,7 +7894,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7947,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7997,7 +7994,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8047,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8097,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8147,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8197,7 +8194,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8247,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8297,7 +8294,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8347,7 +8344,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8397,7 +8394,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8447,7 +8444,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8497,7 +8494,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8547,7 +8544,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8647,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8697,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8747,7 +8744,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8797,7 +8794,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8847,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8897,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8947,7 +8944,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8997,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9047,7 +9044,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9097,7 +9094,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9147,7 +9144,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9197,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9247,7 +9244,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9297,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9347,7 +9344,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9397,7 +9394,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9447,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9497,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9547,7 +9544,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9597,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9697,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9747,7 +9744,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9797,7 +9794,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9947,7 +9944,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9997,7 +9994,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10047,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10097,7 +10094,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10147,7 +10144,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10197,7 +10194,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10247,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10297,7 +10294,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10397,7 +10394,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10447,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10597,7 +10594,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10647,7 +10644,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10697,7 +10694,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10747,7 +10744,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11247,7 +11244,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11297,7 +11294,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11347,7 +11344,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11397,7 +11394,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11447,7 +11444,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11497,7 +11494,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11547,7 +11544,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11597,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11647,7 +11644,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11697,7 +11694,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11747,7 +11744,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11797,7 +11794,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11847,7 +11844,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11897,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11947,7 +11944,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12747,7 +12744,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12797,7 +12794,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12847,7 +12844,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12897,7 +12894,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12947,7 +12944,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12997,7 +12994,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13047,7 +13044,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13097,7 +13094,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13147,7 +13144,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13197,7 +13194,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13247,7 +13244,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13297,7 +13294,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13347,7 +13344,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13397,7 +13394,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13447,7 +13444,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13497,7 +13494,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13547,7 +13544,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13597,7 +13594,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13647,7 +13644,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13697,7 +13694,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13847,7 +13844,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13897,7 +13894,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13947,7 +13944,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14047,7 +14044,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14197,7 +14194,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14247,7 +14244,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14297,7 +14294,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14347,7 +14344,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14397,7 +14394,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14447,7 +14444,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14497,7 +14494,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14597,7 +14594,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14647,7 +14644,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14697,7 +14694,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14747,7 +14744,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14797,7 +14794,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14847,7 +14844,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14897,7 +14894,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14947,7 +14944,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14997,7 +14994,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15047,7 +15044,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15097,7 +15094,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15147,7 +15144,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15197,7 +15194,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15247,7 +15244,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15297,7 +15294,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15347,7 +15344,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15397,7 +15394,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15447,7 +15444,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15497,7 +15494,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15547,7 +15544,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15597,7 +15594,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15647,7 +15644,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15697,7 +15694,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15747,7 +15744,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15797,7 +15794,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15847,7 +15844,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15897,7 +15894,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15947,7 +15944,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15997,7 +15994,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16047,7 +16044,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16097,7 +16094,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16147,7 +16144,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16197,7 +16194,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16247,7 +16244,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16297,7 +16294,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16347,7 +16344,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16397,7 +16394,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16447,7 +16444,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16497,7 +16494,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16547,7 +16544,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16597,7 +16594,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16647,7 +16644,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16697,7 +16694,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16747,7 +16744,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16797,7 +16794,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16847,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16897,7 +16894,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16947,7 +16944,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17147,7 +17144,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17197,7 +17194,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17247,7 +17244,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17297,7 +17294,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17347,7 +17344,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17397,7 +17394,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17447,7 +17444,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17497,7 +17494,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17547,7 +17544,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17597,7 +17594,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17647,7 +17644,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17697,7 +17694,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17747,7 +17744,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17797,7 +17794,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17847,7 +17844,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17897,7 +17894,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17947,7 +17944,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17997,7 +17994,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18047,7 +18044,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18097,7 +18094,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18147,7 +18144,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18197,7 +18194,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18247,7 +18244,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18297,7 +18294,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18347,7 +18344,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18597,7 +18594,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18647,7 +18644,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18697,7 +18694,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18747,7 +18744,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18797,7 +18794,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18847,7 +18844,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18897,7 +18894,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18947,7 +18944,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18997,7 +18994,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19047,7 +19044,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19097,7 +19094,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19147,7 +19144,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19597,7 +19594,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19647,7 +19644,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19697,7 +19694,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19747,7 +19744,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19797,7 +19794,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19847,7 +19844,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19897,7 +19894,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19947,7 +19944,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19997,7 +19994,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20047,7 +20044,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20097,7 +20094,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20147,7 +20144,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20197,7 +20194,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20247,7 +20244,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20297,7 +20294,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20347,7 +20344,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20547,7 +20544,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20597,7 +20594,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20647,7 +20644,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20697,7 +20694,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20897,7 +20894,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20947,7 +20944,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20997,7 +20994,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21047,7 +21044,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21097,7 +21094,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21147,7 +21144,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21197,7 +21194,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21247,7 +21244,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21297,7 +21294,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21347,7 +21344,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21397,7 +21394,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21447,7 +21444,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21497,7 +21494,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21547,7 +21544,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21597,7 +21594,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21647,7 +21644,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21697,7 +21694,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21747,7 +21744,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21797,7 +21794,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21847,7 +21844,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21897,7 +21894,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21947,7 +21944,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21997,7 +21994,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22047,7 +22044,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22097,7 +22094,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22147,7 +22144,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22197,7 +22194,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22247,7 +22244,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22297,7 +22294,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22347,7 +22344,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22397,7 +22394,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22447,7 +22444,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22497,7 +22494,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22697,7 +22694,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22747,7 +22744,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22797,7 +22794,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22847,7 +22844,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22897,7 +22894,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22947,7 +22944,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23147,7 +23144,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23197,7 +23194,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23247,7 +23244,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23297,7 +23294,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23347,7 +23344,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23397,7 +23394,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23447,7 +23444,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23497,7 +23494,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23547,7 +23544,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23597,7 +23594,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23647,7 +23644,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23697,7 +23694,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23747,7 +23744,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23797,7 +23794,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23847,7 +23844,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23897,7 +23894,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23947,7 +23944,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23997,7 +23994,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24047,7 +24044,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24097,7 +24094,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24147,7 +24144,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24197,7 +24194,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24247,7 +24244,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24297,7 +24294,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24347,7 +24344,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24397,7 +24394,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24447,7 +24444,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24497,7 +24494,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24547,7 +24544,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24597,7 +24594,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24647,7 +24644,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24697,7 +24694,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24747,7 +24744,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24797,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24847,7 +24844,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24897,7 +24894,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24947,7 +24944,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24997,7 +24994,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25047,7 +25044,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25097,7 +25094,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25147,7 +25144,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25197,7 +25194,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25497,7 +25494,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25547,7 +25544,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25597,7 +25594,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25647,7 +25644,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25697,7 +25694,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25747,7 +25744,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25797,7 +25794,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25847,7 +25844,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25897,7 +25894,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25947,7 +25944,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25997,7 +25994,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26047,7 +26044,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26097,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26147,7 +26144,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26197,7 +26194,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26247,7 +26244,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26297,7 +26294,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26347,7 +26344,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26397,7 +26394,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26447,7 +26444,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26497,7 +26494,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26547,7 +26544,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26597,7 +26594,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26647,7 +26644,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26697,7 +26694,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26747,7 +26744,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26797,7 +26794,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26847,7 +26844,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26897,7 +26894,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26947,7 +26944,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26997,7 +26994,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27047,7 +27044,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27097,7 +27094,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27147,7 +27144,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27197,7 +27194,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27247,7 +27244,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27297,7 +27294,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27347,7 +27344,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27397,7 +27394,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27447,7 +27444,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27497,7 +27494,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27547,7 +27544,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27597,7 +27594,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27647,7 +27644,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27664,7 +27661,7 @@
         <v>163</v>
       </c>
       <c r="E523">
-        <v>0.2816336379392261</v>
+        <v>0.3936393858075808</v>
       </c>
       <c r="F523">
         <v>-1</v>
@@ -27673,10 +27670,10 @@
         <v>0.01358335199238989</v>
       </c>
       <c r="H523">
-        <v>0.01227836636206077</v>
+        <v>0.01290636061419242</v>
       </c>
       <c r="I523">
-        <v>0.01501436967088488</v>
+        <v>-0.09699137819746984</v>
       </c>
       <c r="J523">
         <v>1.612464075822789</v>
@@ -27688,16 +27685,16 @@
         <v>6.94</v>
       </c>
       <c r="M523">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N523">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27747,7 +27744,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27764,7 +27761,7 @@
         <v>163</v>
       </c>
       <c r="E525">
-        <v>-0.2946292665855657</v>
+        <v>-0.2074090199870948</v>
       </c>
       <c r="F525">
         <v>-1</v>
@@ -27773,10 +27770,10 @@
         <v>0.01349671408163671</v>
       </c>
       <c r="H525">
-        <v>0.01285462926658557</v>
+        <v>0.0135074090199871</v>
       </c>
       <c r="I525">
-        <v>0.2179151849488532</v>
+        <v>0.1306949383503824</v>
       </c>
       <c r="J525">
         <v>1.767373458759561</v>
@@ -27788,16 +27785,16 @@
         <v>6.71</v>
       </c>
       <c r="M525">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N525">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O525">
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27847,7 +27844,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27864,7 +27861,7 @@
         <v>163</v>
       </c>
       <c r="E527">
-        <v>-0.3872292061240348</v>
+        <v>-0.3039917526239924</v>
       </c>
       <c r="F527">
         <v>-1</v>
@@ -27873,10 +27870,10 @@
         <v>0.013592301115999</v>
       </c>
       <c r="H527">
-        <v>0.01294722920612404</v>
+        <v>0.01360399175262399</v>
       </c>
       <c r="I527">
-        <v>0.2149280901250314</v>
+        <v>0.131690636624989</v>
       </c>
       <c r="J527">
         <v>1.79226591562474</v>
@@ -27888,16 +27885,16 @@
         <v>6.71</v>
       </c>
       <c r="M527">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N527">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O527">
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27947,7 +27944,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27964,7 +27961,7 @@
         <v>163</v>
       </c>
       <c r="E529">
-        <v>-0.4662452131642629</v>
+        <v>-0.3864062976014351</v>
       </c>
       <c r="F529">
         <v>-1</v>
@@ -27973,10 +27970,10 @@
         <v>0.01367386602649214</v>
       </c>
       <c r="H529">
-        <v>0.01302624521316426</v>
+        <v>0.01368640629760144</v>
       </c>
       <c r="I529">
-        <v>0.2123791866721207</v>
+        <v>0.1325402711092929</v>
       </c>
       <c r="J529">
         <v>1.813506777732329</v>
@@ -27988,16 +27985,16 @@
         <v>6.71</v>
       </c>
       <c r="M529">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N529">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O529">
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28011,10 +28008,10 @@
         <v>-2.134185588757242</v>
       </c>
       <c r="D530" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E530">
-        <v>-1.10180087917765</v>
+        <v>-0.8789550079164261</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28023,10 +28020,10 @@
         <v>0.01259418558875724</v>
       </c>
       <c r="H530">
-        <v>0.01278180087917765</v>
+        <v>0.01553895500791643</v>
       </c>
       <c r="I530">
-        <v>1.032384709579592</v>
+        <v>1.255230580840816</v>
       </c>
       <c r="J530">
         <v>1.836455259041706</v>
@@ -28038,16 +28035,16 @@
         <v>5.23</v>
       </c>
       <c r="M530">
-        <v>3.78</v>
+        <v>4.47</v>
       </c>
       <c r="N530">
-        <v>5.84</v>
+        <v>7.33</v>
       </c>
       <c r="O530">
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28064,7 +28061,7 @@
         <v>163</v>
       </c>
       <c r="E531">
-        <v>-0.5516135636351471</v>
+        <v>-0.4754464050818195</v>
       </c>
       <c r="F531">
         <v>-1</v>
@@ -28073,10 +28070,10 @@
         <v>0.01376198819472015</v>
       </c>
       <c r="H531">
-        <v>0.01311161356363515</v>
+        <v>0.01377544640508182</v>
       </c>
       <c r="I531">
-        <v>0.2096253689149954</v>
+        <v>0.1334582103616677</v>
       </c>
       <c r="J531">
         <v>1.836455259041706</v>
@@ -28088,16 +28085,16 @@
         <v>6.71</v>
       </c>
       <c r="M531">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N531">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O531">
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28147,7 +28144,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28164,7 +28161,7 @@
         <v>163</v>
       </c>
       <c r="E533">
-        <v>-0.654338489170172</v>
+        <v>-0.5825896069839418</v>
       </c>
       <c r="F533">
         <v>-1</v>
@@ -28173,10 +28170,10 @@
         <v>0.0138680268275305</v>
       </c>
       <c r="H533">
-        <v>0.01321433848917017</v>
+        <v>0.01388258960698394</v>
       </c>
       <c r="I533">
-        <v>0.2063116616396723</v>
+        <v>0.1345627794534421</v>
       </c>
       <c r="J533">
         <v>1.864069486336068</v>
@@ -28188,16 +28185,16 @@
         <v>6.71</v>
       </c>
       <c r="M533">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N533">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O533">
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28247,7 +28244,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28264,7 +28261,7 @@
         <v>163</v>
       </c>
       <c r="E535">
-        <v>-0.7901781816175806</v>
+        <v>-0.7242718668484436</v>
       </c>
       <c r="F535">
         <v>-1</v>
@@ -28273,10 +28270,10 @@
         <v>0.01400824844554073</v>
       </c>
       <c r="H535">
-        <v>0.01335017818161758</v>
+        <v>0.01402427186684845</v>
       </c>
       <c r="I535">
-        <v>0.2019297360768526</v>
+        <v>0.1360234213077156</v>
       </c>
       <c r="J535">
         <v>1.900585532692898</v>
@@ -28288,16 +28285,16 @@
         <v>6.71</v>
       </c>
       <c r="M535">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N535">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O535">
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28347,7 +28344,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28397,7 +28394,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28414,7 +28411,7 @@
         <v>163</v>
       </c>
       <c r="E538">
-        <v>-0.934121637737646</v>
+        <v>-0.8744064393607696</v>
       </c>
       <c r="F538">
         <v>-1</v>
@@ -28423,10 +28420,10 @@
         <v>0.01415683523895499</v>
       </c>
       <c r="H538">
-        <v>0.01349412163773765</v>
+        <v>0.01417440643936077</v>
       </c>
       <c r="I538">
-        <v>0.1972863987826567</v>
+        <v>0.1375712004057803</v>
       </c>
       <c r="J538">
         <v>1.939280010144528</v>
@@ -28438,16 +28435,16 @@
         <v>6.71</v>
       </c>
       <c r="M538">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N538">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28497,7 +28494,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28547,7 +28544,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28561,10 +28558,10 @@
         <v>-3.302184308580614</v>
       </c>
       <c r="D541" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="E541">
-        <v>-2.00751151980996</v>
+        <v>-1.826234252207514</v>
       </c>
       <c r="F541">
         <v>1</v>
@@ -28573,10 +28570,10 @@
         <v>0.01376218430858061</v>
       </c>
       <c r="H541">
-        <v>0.01556751151980996</v>
+        <v>0.01570623425220751</v>
       </c>
       <c r="I541">
-        <v>1.294672788770654</v>
+        <v>1.4759500563731</v>
       </c>
       <c r="J541">
         <v>2.127726760244542</v>
@@ -28588,16 +28585,16 @@
         <v>5.23</v>
       </c>
       <c r="M541">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="N541">
-        <v>6.78</v>
+        <v>6.94</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28611,10 +28608,10 @@
         <v>-2.807916224134152</v>
       </c>
       <c r="D542" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="E542">
-        <v>-2.00751151980996</v>
+        <v>-1.826234252207514</v>
       </c>
       <c r="F542">
         <v>1</v>
@@ -28623,10 +28620,10 @@
         <v>0.01344791622413415</v>
       </c>
       <c r="H542">
-        <v>0.01556751151980996</v>
+        <v>0.01570623425220751</v>
       </c>
       <c r="I542">
-        <v>0.8004047043241913</v>
+        <v>0.9816819719266379</v>
       </c>
       <c r="J542">
         <v>2.127726760244542</v>
@@ -28638,16 +28635,16 @@
         <v>5.32</v>
       </c>
       <c r="M542">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="N542">
-        <v>6.78</v>
+        <v>6.94</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28697,7 +28694,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28747,7 +28744,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28797,7 +28794,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28847,7 +28844,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28897,7 +28894,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28947,7 +28944,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28961,7 +28958,7 @@
         <v>-4.162550774568617</v>
       </c>
       <c r="D549" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E549">
         <v>-2.558591035361685</v>
@@ -28997,7 +28994,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29011,7 +29008,7 @@
         <v>-3.627517196721227</v>
       </c>
       <c r="D550" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E550">
         <v>-2.558591035361685</v>
@@ -29047,7 +29044,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29061,7 +29058,7 @@
         <v>-4.341021841271511</v>
       </c>
       <c r="D551" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E551">
         <v>-2.733946647034852</v>
@@ -29097,7 +29094,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29111,7 +29108,7 @@
         <v>-3.797532028343435</v>
       </c>
       <c r="D552" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E552">
         <v>-2.733946647034852</v>
@@ -29147,7 +29144,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29161,7 +29158,7 @@
         <v>-4.38270256915019</v>
       </c>
       <c r="D553" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E553">
         <v>-2.774899781160038</v>
@@ -29197,7 +29194,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29211,7 +29208,7 @@
         <v>-3.837237858891204</v>
       </c>
       <c r="D554" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E554">
         <v>-2.774899781160038</v>
@@ -29247,7 +29244,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29261,7 +29258,7 @@
         <v>-4.411855003341485</v>
       </c>
       <c r="D555" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E555">
         <v>-2.803543319991386</v>
@@ -29297,7 +29294,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29311,7 +29308,7 @@
         <v>-3.865009005676926</v>
       </c>
       <c r="D556" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E556">
         <v>-2.803543319991386</v>
@@ -29347,7 +29344,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29361,7 +29358,7 @@
         <v>-4.339272485484365</v>
       </c>
       <c r="D557" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E557">
         <v>-2.732227828630524</v>
@@ -29397,7 +29394,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29411,7 +29408,7 @@
         <v>-3.795865559738223</v>
       </c>
       <c r="D558" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E558">
         <v>-2.732227828630524</v>
@@ -29447,7 +29444,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29461,7 +29458,7 @@
         <v>-4.278315541383607</v>
       </c>
       <c r="D559" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E559">
         <v>-2.672334970835765</v>
@@ -29497,7 +29494,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29511,7 +29508,7 @@
         <v>-3.737796849896604</v>
       </c>
       <c r="D560" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E560">
         <v>-2.672334970835765</v>
@@ -29547,7 +29544,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29561,7 +29558,7 @@
         <v>-4.215673134172834</v>
       </c>
       <c r="D561" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E561">
         <v>-2.610786071980291</v>
@@ -29597,7 +29594,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29611,7 +29608,7 @@
         <v>-3.678122536793074</v>
       </c>
       <c r="D562" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E562">
         <v>-2.610786071980291</v>
@@ -29647,7 +29644,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29661,7 +29658,7 @@
         <v>-4.189835924124937</v>
       </c>
       <c r="D563" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E563">
         <v>-2.585399885549192</v>
@@ -29697,7 +29694,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29711,7 +29708,7 @@
         <v>-3.653509533705053</v>
       </c>
       <c r="D564" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E564">
         <v>-2.585399885549192</v>
@@ -29747,7 +29744,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29797,7 +29794,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29847,7 +29844,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29897,7 +29894,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29947,7 +29944,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29997,7 +29994,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30047,7 +30044,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30064,7 +30061,7 @@
         <v>163</v>
       </c>
       <c r="E571">
-        <v>-0.9488331616943828</v>
+        <v>-0.8897507170360761</v>
       </c>
       <c r="F571">
         <v>-1</v>
@@ -30073,10 +30070,10 @@
         <v>0.01417202132820065</v>
       </c>
       <c r="H571">
-        <v>0.01350883316169438</v>
+        <v>0.01418975071703608</v>
       </c>
       <c r="I571">
-        <v>0.1968118334937303</v>
+        <v>0.1377293888354236</v>
       </c>
       <c r="J571">
         <v>1.943234720885587</v>
@@ -30088,16 +30085,16 @@
         <v>6.71</v>
       </c>
       <c r="M571">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="N571">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="O571">
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="393">
   <si>
     <t>trade_time</t>
   </si>
@@ -226,295 +226,295 @@
     <t>2021-08-23</t>
   </si>
   <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-11-08</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-11-21</t>
+  </si>
+  <si>
+    <t>2017-10-25</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>2017-11-07</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2018-06-26</t>
+  </si>
+  <si>
+    <t>2018-06-27</t>
+  </si>
+  <si>
+    <t>2018-06-28</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-03</t>
+  </si>
+  <si>
+    <t>2018-09-14</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-09-26</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-25</t>
+  </si>
+  <si>
+    <t>2018-10-26</t>
+  </si>
+  <si>
+    <t>2018-10-29</t>
+  </si>
+  <si>
+    <t>2018-10-30</t>
+  </si>
+  <si>
+    <t>2018-10-31</t>
+  </si>
+  <si>
+    <t>2018-11-01</t>
+  </si>
+  <si>
+    <t>2018-11-02</t>
+  </si>
+  <si>
+    <t>2018-11-05</t>
+  </si>
+  <si>
+    <t>2018-11-06</t>
+  </si>
+  <si>
+    <t>2018-11-07</t>
+  </si>
+  <si>
+    <t>2018-11-08</t>
+  </si>
+  <si>
+    <t>2018-11-09</t>
+  </si>
+  <si>
+    <t>2018-11-12</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>2018-11-14</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2018-11-21</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-23</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-11-27</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-06-17</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-07-29</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-07</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-11</t>
+  </si>
+  <si>
+    <t>2020-02-12</t>
+  </si>
+  <si>
+    <t>2020-02-17</t>
+  </si>
+  <si>
+    <t>2020-02-18</t>
+  </si>
+  <si>
+    <t>2020-02-19</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-10</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-24</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-03-27</t>
+  </si>
+  <si>
+    <t>2020-03-30</t>
+  </si>
+  <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-04-02</t>
+  </si>
+  <si>
+    <t>2020-04-03</t>
+  </si>
+  <si>
+    <t>2020-04-07</t>
+  </si>
+  <si>
+    <t>2020-04-08</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-27</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
     <t>2021-09-13</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-11-08</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-11-21</t>
-  </si>
-  <si>
-    <t>2017-10-25</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-11-06</t>
-  </si>
-  <si>
-    <t>2017-11-07</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2018-06-26</t>
-  </si>
-  <si>
-    <t>2018-06-27</t>
-  </si>
-  <si>
-    <t>2018-06-28</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-03</t>
-  </si>
-  <si>
-    <t>2018-09-14</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-09-26</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-25</t>
-  </si>
-  <si>
-    <t>2018-10-26</t>
-  </si>
-  <si>
-    <t>2018-10-29</t>
-  </si>
-  <si>
-    <t>2018-10-30</t>
-  </si>
-  <si>
-    <t>2018-10-31</t>
-  </si>
-  <si>
-    <t>2018-11-01</t>
-  </si>
-  <si>
-    <t>2018-11-02</t>
-  </si>
-  <si>
-    <t>2018-11-05</t>
-  </si>
-  <si>
-    <t>2018-11-06</t>
-  </si>
-  <si>
-    <t>2018-11-07</t>
-  </si>
-  <si>
-    <t>2018-11-08</t>
-  </si>
-  <si>
-    <t>2018-11-09</t>
-  </si>
-  <si>
-    <t>2018-11-12</t>
-  </si>
-  <si>
-    <t>2018-11-13</t>
-  </si>
-  <si>
-    <t>2018-11-14</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-20</t>
-  </si>
-  <si>
-    <t>2018-11-21</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-23</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-11-27</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-06-17</t>
-  </si>
-  <si>
-    <t>2019-06-19</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-07-29</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-07</t>
-  </si>
-  <si>
-    <t>2020-02-10</t>
-  </si>
-  <si>
-    <t>2020-02-11</t>
-  </si>
-  <si>
-    <t>2020-02-12</t>
-  </si>
-  <si>
-    <t>2020-02-17</t>
-  </si>
-  <si>
-    <t>2020-02-18</t>
-  </si>
-  <si>
-    <t>2020-02-19</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-10</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-24</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-03-27</t>
-  </si>
-  <si>
-    <t>2020-03-30</t>
-  </si>
-  <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-04-02</t>
-  </si>
-  <si>
-    <t>2020-04-03</t>
-  </si>
-  <si>
-    <t>2020-04-07</t>
-  </si>
-  <si>
-    <t>2020-04-08</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-09-23</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
   </si>
   <si>
     <t>2021-09-14</t>
@@ -1550,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P571"/>
+  <dimension ref="A1:P574"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1611,7 +1611,7 @@
         <v>6.869727715272395</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2">
         <v>6.050137140894572</v>
@@ -1661,7 +1661,7 @@
         <v>6.844463593057311</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3">
         <v>6.050137140894572</v>
@@ -1711,7 +1711,7 @@
         <v>6.857637482930865</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4">
         <v>6.039233803242143</v>
@@ -1761,7 +1761,7 @@
         <v>6.83283604847594</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>6.039233803242143</v>
@@ -1811,7 +1811,7 @@
         <v>6.826153414303063</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6">
         <v>6.01084051672589</v>
@@ -1861,7 +1861,7 @@
         <v>6.802556861010267</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7">
         <v>6.01084051672589</v>
@@ -1911,7 +1911,7 @@
         <v>6.794839943414579</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8">
         <v>5.98260108041714</v>
@@ -1961,7 +1961,7 @@
         <v>6.77244174258507</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9">
         <v>5.98260108041714</v>
@@ -2011,7 +2011,7 @@
         <v>6.763675289556306</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10">
         <v>5.95449585181284</v>
@@ -2061,7 +2061,7 @@
         <v>6.742469746029192</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11">
         <v>5.95449585181284</v>
@@ -2111,7 +2111,7 @@
         <v>6.730117010025435</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E12">
         <v>5.924231979091157</v>
@@ -2161,7 +2161,7 @@
         <v>6.710195726779869</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13">
         <v>5.924231979091157</v>
@@ -2211,7 +2211,7 @@
         <v>6.693046966006446</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14">
         <v>5.890801090807809</v>
@@ -2261,7 +2261,7 @@
         <v>6.674544336691723</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15">
         <v>5.890801090807809</v>
@@ -2311,7 +2311,7 @@
         <v>6.644553392998862</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16">
         <v>5.847068118145396</v>
@@ -2361,7 +2361,7 @@
         <v>6.627906590937341</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17">
         <v>5.847068118145396</v>
@@ -2411,7 +2411,7 @@
         <v>6.617128166636995</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18">
         <v>5.822335218497922</v>
@@ -2461,7 +2461,7 @@
         <v>6.601530915667526</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19">
         <v>5.822335218497922</v>
@@ -2511,7 +2511,7 @@
         <v>6.581803978417834</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20">
         <v>5.790478795844368</v>
@@ -2561,7 +2561,7 @@
         <v>6.567558568262076</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21">
         <v>5.790478795844368</v>
@@ -2611,7 +2611,7 @@
         <v>6.554001439910648</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22">
         <v>5.765405624678154</v>
@@ -2661,7 +2661,7 @@
         <v>6.540820020413236</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23">
         <v>5.765405624678154</v>
@@ -2711,7 +2711,7 @@
         <v>6.529894038726229</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24">
         <v>5.743664840248944</v>
@@ -2761,7 +2761,7 @@
         <v>6.517635198641864</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E25">
         <v>5.743664840248944</v>
@@ -2811,7 +2811,7 @@
         <v>6.493137342079</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E26">
         <v>5.710516538114505</v>
@@ -2861,7 +2861,7 @@
         <v>6.482285164262333</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E27">
         <v>5.710516538114505</v>
@@ -2911,7 +2911,7 @@
         <v>6.444477546138163</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E28">
         <v>5.666633660577178</v>
@@ -2961,7 +2961,7 @@
         <v>6.435487556851677</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29">
         <v>5.666633660577178</v>
@@ -3011,7 +3011,7 @@
         <v>6.395287017911711</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30">
         <v>5.62227215259259</v>
@@ -3061,7 +3061,7 @@
         <v>6.388179528041545</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31">
         <v>5.62227215259259</v>
@@ -3111,7 +3111,7 @@
         <v>6.391868530229962</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E32">
         <v>5.619189256879599</v>
@@ -3161,7 +3161,7 @@
         <v>6.384891864347617</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E33">
         <v>5.619189256879599</v>
@@ -3211,7 +3211,7 @@
         <v>6.396520135507044</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E34">
         <v>5.623384215382392</v>
@@ -3261,7 +3261,7 @@
         <v>6.389365454780485</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E35">
         <v>5.623384215382392</v>
@@ -3311,7 +3311,7 @@
         <v>6.403506732043612</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E36">
         <v>5.629684939713206</v>
@@ -3361,7 +3361,7 @@
         <v>6.396084677406335</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E37">
         <v>5.629684939713206</v>
@@ -3411,7 +3411,7 @@
         <v>6.390454186369448</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E38">
         <v>5.617913758755807</v>
@@ -3461,7 +3461,7 @@
         <v>6.38353164679125</v>
       </c>
       <c r="D39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E39">
         <v>5.617913758755807</v>
@@ -3511,7 +3511,7 @@
         <v>6.385694652927858</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E40">
         <v>5.613621467365888</v>
@@ -3561,7 +3561,7 @@
         <v>6.378954258556243</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41">
         <v>5.613621467365888</v>
@@ -3611,7 +3611,7 @@
         <v>6.398324700271503</v>
       </c>
       <c r="D42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E42">
         <v>5.625011626534365</v>
@@ -3661,7 +3661,7 @@
         <v>6.39110095966211</v>
       </c>
       <c r="D43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E43">
         <v>5.625011626534365</v>
@@ -3711,7 +3711,7 @@
         <v>6.406965992917668</v>
       </c>
       <c r="D44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E44">
         <v>5.63280460592575</v>
@@ -3761,7 +3761,7 @@
         <v>6.399411553920818</v>
       </c>
       <c r="D45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E45">
         <v>5.63280460592575</v>
@@ -3811,7 +3811,7 @@
         <v>6.400651203652978</v>
       </c>
       <c r="D46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E46">
         <v>5.627109737736961</v>
@@ -3861,7 +3861,7 @@
         <v>6.393338428804362</v>
       </c>
       <c r="D47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E47">
         <v>5.627109737736961</v>
@@ -3911,7 +3911,7 @@
         <v>6.421264387742685</v>
       </c>
       <c r="D48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E48">
         <v>5.645699331375265</v>
@@ -3961,7 +3961,7 @@
         <v>6.413162755599453</v>
       </c>
       <c r="D49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E49">
         <v>5.645699331375265</v>
@@ -4011,7 +4011,7 @@
         <v>6.463467063219744</v>
       </c>
       <c r="D50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E50">
         <v>5.68375898213827</v>
@@ -4061,7 +4061,7 @@
         <v>6.45375035364561</v>
       </c>
       <c r="D51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E51">
         <v>5.68375898213827</v>
@@ -4111,7 +4111,7 @@
         <v>6.488418927255035</v>
       </c>
       <c r="D52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E52">
         <v>5.706261328739149</v>
@@ -4161,7 +4161,7 @@
         <v>6.477747321053927</v>
       </c>
       <c r="D53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E53">
         <v>5.706261328739149</v>
@@ -4211,7 +4211,7 @@
         <v>6.583255790923473</v>
       </c>
       <c r="D54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E54">
         <v>5.791788084326992</v>
@@ -4261,7 +4261,7 @@
         <v>6.440394668218746</v>
       </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E55">
         <v>5.791788084326992</v>
@@ -4311,7 +4311,7 @@
         <v>6.568954820555353</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E56">
         <v>5.791788084326992</v>
@@ -4361,7 +4361,7 @@
         <v>6.628230185262845</v>
       </c>
       <c r="D57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E57">
         <v>5.83234735509561</v>
@@ -4411,7 +4411,7 @@
         <v>6.484920066940753</v>
       </c>
       <c r="D58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E58">
         <v>5.83234735509561</v>
@@ -4461,7 +4461,7 @@
         <v>6.61220806502816</v>
       </c>
       <c r="D59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E59">
         <v>5.83234735509561</v>
@@ -4511,7 +4511,7 @@
         <v>6.646411890511949</v>
       </c>
       <c r="D60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E60">
         <v>5.84874416748332</v>
@@ -4561,7 +4561,7 @@
         <v>6.50292025766158</v>
       </c>
       <c r="D61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E61">
         <v>5.84874416748332</v>
@@ -4611,7 +4611,7 @@
         <v>6.629693964585535</v>
       </c>
       <c r="D62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E62">
         <v>5.84874416748332</v>
@@ -4661,7 +4661,7 @@
         <v>6.642559529608892</v>
       </c>
       <c r="D63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E63">
         <v>5.84526999176043</v>
@@ -4711,7 +4711,7 @@
         <v>6.499106356268371</v>
       </c>
       <c r="D64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E64">
         <v>5.84526999176043</v>
@@ -4761,7 +4761,7 @@
         <v>6.625989031803559</v>
       </c>
       <c r="D65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E65">
         <v>5.84526999176043</v>
@@ -4811,7 +4811,7 @@
         <v>6.645390633912061</v>
       </c>
       <c r="D66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E66">
         <v>5.847823167354969</v>
@@ -4861,7 +4861,7 @@
         <v>6.501909196635068</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E67">
         <v>5.847823167354969</v>
@@ -4911,7 +4911,7 @@
         <v>6.628711791016923</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E68">
         <v>5.847823167354969</v>
@@ -4961,7 +4961,7 @@
         <v>6.628009372010197</v>
       </c>
       <c r="D69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E69">
         <v>5.832148219017515</v>
@@ -5011,7 +5011,7 @@
         <v>6.611995702199492</v>
       </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E70">
         <v>5.832148219017515</v>
@@ -5061,7 +5061,7 @@
         <v>6.616738911804213</v>
       </c>
       <c r="D71" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E71">
         <v>5.821984176701968</v>
@@ -5111,7 +5111,7 @@
         <v>6.601156557442321</v>
       </c>
       <c r="D72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E72">
         <v>5.821984176701968</v>
@@ -5161,7 +5161,7 @@
         <v>6.626158243616882</v>
       </c>
       <c r="D73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E73">
         <v>5.830478815374958</v>
@@ -5211,7 +5211,7 @@
         <v>6.610215415658166</v>
       </c>
       <c r="D74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E74">
         <v>5.830478815374958</v>
@@ -5261,7 +5261,7 @@
         <v>6.650940043106316</v>
       </c>
       <c r="D75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E75">
         <v>5.85282779261834</v>
@@ -5311,7 +5311,7 @@
         <v>6.634048826814393</v>
       </c>
       <c r="D76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E76">
         <v>5.85282779261834</v>
@@ -5361,7 +5361,7 @@
         <v>6.655761178830648</v>
       </c>
       <c r="D77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E77">
         <v>5.857175638812331</v>
@@ -5411,7 +5411,7 @@
         <v>6.638685459840457</v>
       </c>
       <c r="D78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E78">
         <v>5.857175638812331</v>
@@ -5461,7 +5461,7 @@
         <v>6.682065765134389</v>
       </c>
       <c r="D79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E79">
         <v>5.880897911319199</v>
@@ -5511,7 +5511,7 @@
         <v>6.663983381443721</v>
       </c>
       <c r="D80" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E80">
         <v>5.880897911319199</v>
@@ -5561,7 +5561,7 @@
         <v>6.734829447046008</v>
       </c>
       <c r="D81" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E81">
         <v>5.928481797502389</v>
@@ -5611,7 +5611,7 @@
         <v>6.714727820952732</v>
       </c>
       <c r="D82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E82">
         <v>5.928481797502389</v>
@@ -5661,7 +5661,7 @@
         <v>6.744601630625527</v>
       </c>
       <c r="D83" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E83">
         <v>5.937294648584086</v>
@@ -5711,7 +5711,7 @@
         <v>6.72412602745683</v>
       </c>
       <c r="D84" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E84">
         <v>5.937294648584086</v>
@@ -5761,7 +5761,7 @@
         <v>6.868996803282632</v>
       </c>
       <c r="D85" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E85">
         <v>6.049477982328097</v>
@@ -5811,7 +5811,7 @@
         <v>6.723283024880476</v>
       </c>
       <c r="D86" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E86">
         <v>6.049477982328097</v>
@@ -5861,7 +5861,7 @@
         <v>6.843760652741033</v>
       </c>
       <c r="D87" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E87">
         <v>6.049477982328097</v>
@@ -5911,7 +5911,7 @@
         <v>7.461980748234559</v>
       </c>
       <c r="D88" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E88">
         <v>6.584248861136657</v>
@@ -5961,7 +5961,7 @@
         <v>7.310346997004264</v>
       </c>
       <c r="D89" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E89">
         <v>6.584248861136657</v>
@@ -6011,7 +6011,7 @@
         <v>7.414051368518428</v>
       </c>
       <c r="D90" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E90">
         <v>6.584248861136657</v>
@@ -6061,7 +6061,7 @@
         <v>7.503790226406835</v>
       </c>
       <c r="D91" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E91">
         <v>6.621953914663068</v>
@@ -6111,7 +6111,7 @@
         <v>7.351739076060011</v>
       </c>
       <c r="D92" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E92">
         <v>6.621953914663068</v>
@@ -6161,7 +6161,7 @@
         <v>7.454260816744011</v>
       </c>
       <c r="D93" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E93">
         <v>6.621953914663068</v>
@@ -6211,7 +6211,7 @@
         <v>7.442891522635139</v>
       </c>
       <c r="D94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E94">
         <v>6.567033619414717</v>
@@ -6261,7 +6261,7 @@
         <v>7.291448346036452</v>
       </c>
       <c r="D95" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E95">
         <v>6.567033619414717</v>
@@ -6311,7 +6311,7 @@
         <v>7.39569267900684</v>
       </c>
       <c r="D96" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E96">
         <v>6.567033619414717</v>
@@ -6361,7 +6361,7 @@
         <v>7.440682840908001</v>
       </c>
       <c r="D97" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E97">
         <v>6.56504176334798</v>
@@ -6411,7 +6411,7 @@
         <v>7.289261714376473</v>
       </c>
       <c r="D98" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E98">
         <v>6.56504176334798</v>
@@ -6461,7 +6461,7 @@
         <v>7.393568522537145</v>
       </c>
       <c r="D99" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E99">
         <v>6.56504176334798</v>
@@ -6511,7 +6511,7 @@
         <v>7.424306444365878</v>
       </c>
       <c r="D100" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E100">
         <v>6.550273033022139</v>
@@ -6561,7 +6561,7 @@
         <v>7.377818843333573</v>
       </c>
       <c r="D101" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E101">
         <v>6.550273033022139</v>
@@ -6611,7 +6611,7 @@
         <v>7.534499875331724</v>
       </c>
       <c r="D102" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E102">
         <v>6.649648806039591</v>
@@ -6661,7 +6661,7 @@
         <v>7.483795221200893</v>
       </c>
       <c r="D103" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E103">
         <v>6.649648806039591</v>
@@ -6711,7 +6711,7 @@
         <v>7.561436426814521</v>
       </c>
       <c r="D104" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E104">
         <v>6.673941003882645</v>
@@ -6761,7 +6761,7 @@
         <v>7.509700922959722</v>
       </c>
       <c r="D105" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E105">
         <v>6.673941003882645</v>
@@ -6811,7 +6811,7 @@
         <v>7.578789061755105</v>
       </c>
       <c r="D106" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E106">
         <v>6.689590135559512</v>
@@ -6861,7 +6861,7 @@
         <v>7.526389480356823</v>
       </c>
       <c r="D107" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E107">
         <v>6.689590135559512</v>
@@ -6911,7 +6911,7 @@
         <v>6.876779630058808</v>
       </c>
       <c r="D108" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E108">
         <v>6.056496771201121</v>
@@ -6961,7 +6961,7 @@
         <v>6.85124563423293</v>
       </c>
       <c r="D109" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E109">
         <v>6.056496771201121</v>
@@ -7011,7 +7011,7 @@
         <v>6.803309666682317</v>
       </c>
       <c r="D110" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E110">
         <v>5.990239333347446</v>
@@ -7061,7 +7061,7 @@
         <v>6.780587333348385</v>
       </c>
       <c r="D111" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E111">
         <v>5.990239333347446</v>
@@ -7111,7 +7111,7 @@
         <v>6.690125588143431</v>
       </c>
       <c r="D112" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E112">
         <v>5.88816650378326</v>
@@ -7161,7 +7161,7 @@
         <v>6.671734758647093</v>
       </c>
       <c r="D113" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E113">
         <v>5.88816650378326</v>
@@ -7211,7 +7211,7 @@
         <v>6.546850371675455</v>
       </c>
       <c r="D114" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E114">
         <v>5.758956574788845</v>
@@ -7261,7 +7261,7 @@
         <v>6.533942620346777</v>
       </c>
       <c r="D115" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E115">
         <v>5.758956574788845</v>
@@ -7311,7 +7311,7 @@
         <v>6.36581543133911</v>
       </c>
       <c r="D116" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E116">
         <v>5.595693783337433</v>
@@ -7361,7 +7361,7 @@
         <v>6.359835805846931</v>
       </c>
       <c r="D117" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E117">
         <v>5.595693783337433</v>
@@ -7411,7 +7411,7 @@
         <v>5.655118426801266</v>
       </c>
       <c r="D118" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E118">
         <v>4.954765702705966</v>
@@ -7461,7 +7461,7 @@
         <v>5.676336856391234</v>
       </c>
       <c r="D119" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E119">
         <v>4.954765702705966</v>
@@ -7511,7 +7511,7 @@
         <v>4.385984132295935</v>
       </c>
       <c r="D120" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E120">
         <v>4.515964100132926</v>
@@ -7561,7 +7561,7 @@
         <v>5.520410496630564</v>
       </c>
       <c r="D121" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E121">
         <v>4.833282011936382</v>
@@ -7611,7 +7611,7 @@
         <v>5.54678413819046</v>
       </c>
       <c r="D122" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E122">
         <v>4.833282011936382</v>
@@ -7711,7 +7711,7 @@
         <v>5.300818351460203</v>
       </c>
       <c r="D124" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E124">
         <v>4.635247165543143</v>
@@ -7761,7 +7761,7 @@
         <v>5.335595685763722</v>
       </c>
       <c r="D125" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E125">
         <v>4.635247165543143</v>
@@ -7911,7 +7911,7 @@
         <v>5.067644558031954</v>
       </c>
       <c r="D128" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E128">
         <v>4.254963977459765</v>
@@ -7961,7 +7961,7 @@
         <v>5.111345348656355</v>
       </c>
       <c r="D129" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E129">
         <v>4.254963977459765</v>
@@ -8011,7 +8011,7 @@
         <v>3.765802729769834</v>
       </c>
       <c r="D130" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E130">
         <v>3.674881815638774</v>
@@ -8061,7 +8061,7 @@
         <v>4.618291357603566</v>
       </c>
       <c r="D131" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E131">
         <v>3.650865136965114</v>
@@ -8111,7 +8111,7 @@
         <v>4.268167177296843</v>
       </c>
       <c r="D132" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E132">
         <v>3.514053115333852</v>
@@ -8161,7 +8161,7 @@
         <v>4.254037078744074</v>
       </c>
       <c r="D133" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E133">
         <v>3.510852837781765</v>
@@ -8211,7 +8211,7 @@
         <v>4.264789106547418</v>
       </c>
       <c r="D134" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E134">
         <v>3.510852837781765</v>
@@ -8261,7 +8261,7 @@
         <v>4.267776501761822</v>
       </c>
       <c r="D135" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E135">
         <v>3.523940390364364</v>
@@ -8311,7 +8311,7 @@
         <v>4.278603745384606</v>
       </c>
       <c r="D136" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E136">
         <v>3.523940390364364</v>
@@ -8361,7 +8361,7 @@
         <v>4.280771326539147</v>
       </c>
       <c r="D137" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E137">
         <v>3.485420289185799</v>
@@ -8411,7 +8411,7 @@
         <v>4.291669709713632</v>
       </c>
       <c r="D138" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E138">
         <v>3.485420289185799</v>
@@ -8461,7 +8461,7 @@
         <v>4.295828187834458</v>
       </c>
       <c r="D139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E139">
         <v>3.499680345777525</v>
@@ -8511,7 +8511,7 @@
         <v>4.306808999081727</v>
       </c>
       <c r="D140" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E140">
         <v>3.499680345777525</v>
@@ -8561,7 +8561,7 @@
         <v>4.311022789612967</v>
       </c>
       <c r="D141" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E141">
         <v>3.503649415261579</v>
@@ -8611,7 +8611,7 @@
         <v>4.306094254478001</v>
       </c>
       <c r="D142" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E142">
         <v>3.499007110842255</v>
@@ -8661,7 +8661,7 @@
         <v>4.306502251029037</v>
       </c>
       <c r="D143" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E143">
         <v>3.499391412493775</v>
@@ -8711,7 +8711,7 @@
         <v>4.318153845587818</v>
       </c>
       <c r="D144" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E144">
         <v>3.510366326424823</v>
@@ -8911,7 +8911,7 @@
         <v>2.959973514323903</v>
       </c>
       <c r="D148" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E148">
         <v>2.331565797970563</v>
@@ -8961,7 +8961,7 @@
         <v>2.954681081546583</v>
       </c>
       <c r="D149" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E149">
         <v>2.325889855571697</v>
@@ -9011,7 +9011,7 @@
         <v>2.952436806561317</v>
       </c>
       <c r="D150" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E150">
         <v>2.323482951964311</v>
@@ -9061,7 +9061,7 @@
         <v>2.939220179650368</v>
       </c>
       <c r="D151" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E151">
         <v>2.309308598465612</v>
@@ -9111,7 +9111,7 @@
         <v>2.885800805603528</v>
       </c>
       <c r="D152" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E152">
         <v>2.285985098138231</v>
@@ -9161,7 +9161,7 @@
         <v>2.882518664640946</v>
       </c>
       <c r="D153" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E153">
         <v>2.285985098138231</v>
@@ -9211,7 +9211,7 @@
         <v>2.871759791100637</v>
       </c>
       <c r="D154" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E154">
         <v>2.270895377157946</v>
@@ -9261,7 +9261,7 @@
         <v>2.868186342783224</v>
       </c>
       <c r="D155" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E155">
         <v>2.270895377157946</v>
@@ -9311,7 +9311,7 @@
         <v>2.851373977249472</v>
       </c>
       <c r="D156" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E156">
         <v>2.248986971400885</v>
@@ -9361,7 +9361,7 @@
         <v>2.813597099989564</v>
       </c>
       <c r="D157" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E157">
         <v>2.215446285791325</v>
@@ -9411,7 +9411,7 @@
         <v>2.783887421732515</v>
       </c>
       <c r="D158" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E158">
         <v>2.183719283702006</v>
@@ -9461,7 +9461,7 @@
         <v>2.721632856402064</v>
       </c>
       <c r="D159" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E159">
         <v>2.127916568873808</v>
@@ -9511,7 +9511,7 @@
         <v>2.678525715783303</v>
       </c>
       <c r="D160" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E160">
         <v>2.09532033365037</v>
@@ -9561,7 +9561,7 @@
         <v>2.69110921416971</v>
       </c>
       <c r="D161" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E161">
         <v>2.09532033365037</v>
@@ -10261,7 +10261,7 @@
         <v>0.9328900239147986</v>
       </c>
       <c r="D175" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E175">
         <v>0.9481209772972727</v>
@@ -10311,7 +10311,7 @@
         <v>0.8361716558948933</v>
       </c>
       <c r="D176" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E176">
         <v>0.9453648051842674</v>
@@ -10361,7 +10361,7 @@
         <v>1.860133746163766</v>
       </c>
       <c r="D177" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E177">
         <v>1.319668494742769</v>
@@ -10411,7 +10411,7 @@
         <v>0.8121110647030001</v>
       </c>
       <c r="D178" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E178">
         <v>0.9618784389925015</v>
@@ -10461,7 +10461,7 @@
         <v>1.83652515616036</v>
       </c>
       <c r="D179" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E179">
         <v>1.296242563075947</v>
@@ -10497,7 +10497,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10511,7 +10511,7 @@
         <v>0.787726176769115</v>
       </c>
       <c r="D180" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E180">
         <v>1.126454507889258</v>
@@ -10547,7 +10547,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10561,7 +10561,7 @@
         <v>1.791439637530079</v>
       </c>
       <c r="D181" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E181">
         <v>1.27124240240025</v>
@@ -10611,7 +10611,7 @@
         <v>1.811330062457952</v>
       </c>
       <c r="D182" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E182">
         <v>1.27124240240025</v>
@@ -10661,7 +10661,7 @@
         <v>1.791373892486802</v>
       </c>
       <c r="D183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E183">
         <v>1.27124240240025</v>
@@ -10711,7 +10711,7 @@
         <v>0.7617026177031843</v>
       </c>
       <c r="D184" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E184">
         <v>1.161198572371399</v>
@@ -10761,7 +10761,7 @@
         <v>1.756679227858482</v>
       </c>
       <c r="D185" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E185">
         <v>1.246983702650287</v>
@@ -10797,7 +10797,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10811,7 +10811,7 @@
         <v>1.786882211053019</v>
       </c>
       <c r="D186" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E186">
         <v>1.246983702650287</v>
@@ -10847,7 +10847,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10861,7 +10861,7 @@
         <v>1.766831465254384</v>
       </c>
       <c r="D187" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E187">
         <v>1.246983702650287</v>
@@ -10897,7 +10897,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10911,7 +10911,7 @@
         <v>0.7364508717646272</v>
       </c>
       <c r="D188" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E188">
         <v>1.146806092355067</v>
@@ -10947,7 +10947,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10961,7 +10961,7 @@
         <v>1.727529637465925</v>
       </c>
       <c r="D189" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E189">
         <v>1.218500388609561</v>
@@ -10997,7 +10997,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11011,7 +11011,7 @@
         <v>1.758176804895015</v>
       </c>
       <c r="D190" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E190">
         <v>1.218500388609561</v>
@@ -11047,7 +11047,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11061,7 +11061,7 @@
         <v>1.738015013037742</v>
       </c>
       <c r="D191" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E191">
         <v>1.218500388609561</v>
@@ -11097,7 +11097,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11111,7 +11111,7 @@
         <v>0.735911718893199</v>
       </c>
       <c r="D192" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E192">
         <v>1.39631619853638</v>
@@ -11147,7 +11147,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11161,7 +11161,7 @@
         <v>0.7068015741081979</v>
       </c>
       <c r="D193" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E193">
         <v>1.39631619853638</v>
@@ -11197,7 +11197,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11211,7 +11211,7 @@
         <v>1.69440254301529</v>
       </c>
       <c r="D194" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E194">
         <v>1.186130484889226</v>
@@ -11261,7 +11261,7 @@
         <v>1.725554504264581</v>
       </c>
       <c r="D195" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E195">
         <v>1.186130484889226</v>
@@ -11311,7 +11311,7 @@
         <v>1.705266513952258</v>
       </c>
       <c r="D196" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E196">
         <v>1.186130484889226</v>
@@ -11361,7 +11361,7 @@
         <v>0.7015226398920635</v>
       </c>
       <c r="D197" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E197">
         <v>1.362242615672869</v>
@@ -11411,7 +11411,7 @@
         <v>0.6731065866098378</v>
       </c>
       <c r="D198" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E198">
         <v>1.362242615672869</v>
@@ -11461,7 +11461,7 @@
         <v>1.672556215816603</v>
       </c>
       <c r="D199" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E199">
         <v>1.164783502312224</v>
@@ -11511,7 +11511,7 @@
         <v>1.70404107348035</v>
       </c>
       <c r="D200" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E200">
         <v>1.164783502312224</v>
@@ -11561,7 +11561,7 @@
         <v>1.683669859064413</v>
       </c>
       <c r="D201" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E201">
         <v>1.164783502312224</v>
@@ -11611,7 +11611,7 @@
         <v>0.6788440716572364</v>
       </c>
       <c r="D202" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E202">
         <v>1.339772107697077</v>
@@ -11661,7 +11661,7 @@
         <v>0.6508857509448882</v>
       </c>
       <c r="D203" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E203">
         <v>1.339772107697077</v>
@@ -11711,7 +11711,7 @@
         <v>1.643503437868948</v>
       </c>
       <c r="D204" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E204">
         <v>1.136394787860515</v>
@@ -11761,7 +11761,7 @@
         <v>1.675431004529993</v>
       </c>
       <c r="D205" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E205">
         <v>1.136394787860515</v>
@@ -11811,7 +11811,7 @@
         <v>1.654949112864731</v>
       </c>
       <c r="D206" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E206">
         <v>1.136394787860515</v>
@@ -11861,7 +11861,7 @@
         <v>0.648684521216337</v>
       </c>
       <c r="D207" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E207">
         <v>1.309889250379489</v>
@@ -11911,7 +11911,7 @@
         <v>0.6213349253752734</v>
       </c>
       <c r="D208" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E208">
         <v>1.309889250379489</v>
@@ -11961,7 +11961,7 @@
         <v>1.629688879456757</v>
       </c>
       <c r="D209" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E209">
         <v>1.122895990783459</v>
@@ -12011,7 +12011,7 @@
         <v>1.661826953674558</v>
       </c>
       <c r="D210" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E210">
         <v>1.122895990783459</v>
@@ -12061,7 +12061,7 @@
         <v>1.623163250060685</v>
       </c>
       <c r="D211" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E211">
         <v>1.122895990783459</v>
@@ -12111,7 +12111,7 @@
         <v>0.6343436939122524</v>
       </c>
       <c r="D212" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E212">
         <v>1.295679990298378</v>
@@ -12161,7 +12161,7 @@
         <v>0.6072835459617298</v>
       </c>
       <c r="D213" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E213">
         <v>1.295679990298378</v>
@@ -12211,7 +12211,7 @@
         <v>1.607589133113905</v>
       </c>
       <c r="D214" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E214">
         <v>1.101301381499872</v>
@@ -12247,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12261,7 +12261,7 @@
         <v>1.640063965371216</v>
       </c>
       <c r="D215" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E215">
         <v>1.101301381499872</v>
@@ -12297,7 +12297,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12311,7 +12311,7 @@
         <v>1.619445257306888</v>
       </c>
       <c r="D216" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E216">
         <v>1.101301381499872</v>
@@ -12347,7 +12347,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12361,7 +12361,7 @@
         <v>0.6114020524706252</v>
       </c>
       <c r="D217" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E217">
         <v>1.272948822631444</v>
@@ -12397,7 +12397,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12411,7 +12411,7 @@
         <v>0.5848049468244287</v>
       </c>
       <c r="D218" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E218">
         <v>1.272948822631444</v>
@@ -12447,7 +12447,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12461,7 +12461,7 @@
         <v>1.581012843353852</v>
       </c>
       <c r="D219" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E219">
         <v>1.075332549791479</v>
@@ -12497,7 +12497,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12511,7 +12511,7 @@
         <v>1.613892647645603</v>
       </c>
       <c r="D220" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E220">
         <v>1.075332549791479</v>
@@ -12547,7 +12547,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12561,7 +12561,7 @@
         <v>1.593172696572664</v>
       </c>
       <c r="D221" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E221">
         <v>1.075332549791479</v>
@@ -12597,7 +12597,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12611,7 +12611,7 @@
         <v>0.5838133326244757</v>
       </c>
       <c r="D222" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E222">
         <v>1.245613210306819</v>
@@ -12647,7 +12647,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12661,7 +12661,7 @@
         <v>0.5577730635256328</v>
       </c>
       <c r="D223" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E223">
         <v>1.245613210306819</v>
@@ -12697,7 +12697,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12711,7 +12711,7 @@
         <v>1.084913495598071</v>
       </c>
       <c r="D224" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E224">
         <v>1.231364667854545</v>
@@ -12761,7 +12761,7 @@
         <v>1.091978143921128</v>
       </c>
       <c r="D225" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E225">
         <v>1.231364667854545</v>
@@ -12861,7 +12861,7 @@
         <v>1.21869175173632</v>
       </c>
       <c r="D227" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E227">
         <v>1.069755686141992</v>
@@ -12911,7 +12911,7 @@
         <v>1.184556198440929</v>
       </c>
       <c r="D228" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E228">
         <v>1.069755686141992</v>
@@ -12961,7 +12961,7 @@
         <v>1.060519812222489</v>
       </c>
       <c r="D229" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E229">
         <v>0.9907313015562922</v>
@@ -13011,7 +13011,7 @@
         <v>1.017939761129645</v>
       </c>
       <c r="D230" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E230">
         <v>0.9907313015562922</v>
@@ -13061,7 +13061,7 @@
         <v>1.755318635505916</v>
       </c>
       <c r="D231" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E231">
         <v>1.003833585600265</v>
@@ -13111,7 +13111,7 @@
         <v>1.894053096403</v>
       </c>
       <c r="D232" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E232">
         <v>1.003833585600265</v>
@@ -13161,7 +13161,7 @@
         <v>1.97376040323609</v>
       </c>
       <c r="D233" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E233">
         <v>1.250262419204153</v>
@@ -13211,7 +13211,7 @@
         <v>2.034815821986728</v>
       </c>
       <c r="D234" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E234">
         <v>1.357988243685597</v>
@@ -13261,7 +13261,7 @@
         <v>2.10245468159479</v>
       </c>
       <c r="D235" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E235">
         <v>1.356708020256039</v>
@@ -13311,7 +13311,7 @@
         <v>2.160736912923812</v>
       </c>
       <c r="D236" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E236">
         <v>1.515238926320149</v>
@@ -13361,7 +13361,7 @@
         <v>2.25315272423952</v>
       </c>
       <c r="D237" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E237">
         <v>1.696228284995405</v>
@@ -13411,7 +13411,7 @@
         <v>2.36943391560179</v>
       </c>
       <c r="D238" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E238">
         <v>1.892500425794016</v>
@@ -13461,7 +13461,7 @@
         <v>2.474058411102812</v>
       </c>
       <c r="D239" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E239">
         <v>1.89058438855279</v>
@@ -13511,7 +13511,7 @@
         <v>2.503056313450243</v>
       </c>
       <c r="D240" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E240">
         <v>1.996322171701399</v>
@@ -13561,7 +13561,7 @@
         <v>2.525264172262913</v>
       </c>
       <c r="D241" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E241">
         <v>1.973847066177296</v>
@@ -13611,7 +13611,7 @@
         <v>2.554243076596262</v>
       </c>
       <c r="D242" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E242">
         <v>1.938989294196617</v>
@@ -13661,7 +13661,7 @@
         <v>2.598334390223854</v>
       </c>
       <c r="D243" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E243">
         <v>2.028465786771591</v>
@@ -13711,7 +13711,7 @@
         <v>2.670586589154834</v>
       </c>
       <c r="D244" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E244">
         <v>1.994395774818371</v>
@@ -13761,7 +13761,7 @@
         <v>2.717624878766997</v>
       </c>
       <c r="D245" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E245">
         <v>2.20711354567414</v>
@@ -13811,7 +13811,7 @@
         <v>2.768201130893359</v>
       </c>
       <c r="D246" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E246">
         <v>2.294068506214541</v>
@@ -13861,7 +13861,7 @@
         <v>2.800856629280805</v>
       </c>
       <c r="D247" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E247">
         <v>2.225122088576691</v>
@@ -13911,7 +13911,7 @@
         <v>2.80951643088527</v>
       </c>
       <c r="D248" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E248">
         <v>2.242646460311337</v>
@@ -13961,7 +13961,7 @@
         <v>2.799569806125956</v>
       </c>
       <c r="D249" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E249">
         <v>2.14320981989216</v>
@@ -14011,7 +14011,7 @@
         <v>2.819828844666985</v>
       </c>
       <c r="D250" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E250">
         <v>2.18506309598321</v>
@@ -14061,7 +14061,7 @@
         <v>2.819851650007405</v>
       </c>
       <c r="D251" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E251">
         <v>2.072484872689354</v>
@@ -14111,7 +14111,7 @@
         <v>2.840423697083499</v>
       </c>
       <c r="D252" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E252">
         <v>2.262963564508703</v>
@@ -14161,7 +14161,7 @@
         <v>2.908629147129241</v>
       </c>
       <c r="D253" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E253">
         <v>2.216875943157096</v>
@@ -14211,7 +14211,7 @@
         <v>3.004384252257208</v>
       </c>
       <c r="D254" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E254">
         <v>2.339997391123474</v>
@@ -14261,7 +14261,7 @@
         <v>3.088901753172625</v>
       </c>
       <c r="D255" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E255">
         <v>2.06246025697973</v>
@@ -14311,7 +14311,7 @@
         <v>3.179054845713715</v>
       </c>
       <c r="D256" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E256">
         <v>2.414075593575115</v>
@@ -14361,7 +14361,7 @@
         <v>3.299462923221598</v>
       </c>
       <c r="D257" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E257">
         <v>2.237378699869055</v>
@@ -14411,7 +14411,7 @@
         <v>3.418692237363245</v>
       </c>
       <c r="D258" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E258">
         <v>2.342027703405609</v>
@@ -14461,7 +14461,7 @@
         <v>3.512759057977069</v>
       </c>
       <c r="D259" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E259">
         <v>2.424591283628788</v>
@@ -14511,7 +14511,7 @@
         <v>3.645345160280047</v>
       </c>
       <c r="D260" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E260">
         <v>2.540963700837517</v>
@@ -14547,7 +14547,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14561,7 +14561,7 @@
         <v>3.815771971902112</v>
       </c>
       <c r="D261" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E261">
         <v>2.690549363898303</v>
@@ -14611,7 +14611,7 @@
         <v>4.010037470388323</v>
       </c>
       <c r="D262" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E262">
         <v>2.861058529236299</v>
@@ -14661,7 +14661,7 @@
         <v>4.152500561307447</v>
       </c>
       <c r="D263" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E263">
         <v>2.986100098188981</v>
@@ -14711,7 +14711,7 @@
         <v>4.227000299262723</v>
       </c>
       <c r="D264" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E264">
         <v>3.05148941454026</v>
@@ -14761,7 +14761,7 @@
         <v>3.628868452425993</v>
       </c>
       <c r="D265" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E265">
         <v>3.018868452425993</v>
@@ -14811,7 +14811,7 @@
         <v>3.56416211054958</v>
       </c>
       <c r="D266" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E266">
         <v>2.954162110549579</v>
@@ -14861,7 +14861,7 @@
         <v>3.491997735810393</v>
       </c>
       <c r="D267" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E267">
         <v>2.881997735810393</v>
@@ -14911,7 +14911,7 @@
         <v>3.304014584160329</v>
       </c>
       <c r="D268" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E268">
         <v>2.694014584160328</v>
@@ -14961,7 +14961,7 @@
         <v>3.180251695694135</v>
       </c>
       <c r="D269" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E269">
         <v>2.570251695694135</v>
@@ -15011,7 +15011,7 @@
         <v>3.152401945865307</v>
       </c>
       <c r="D270" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E270">
         <v>2.542401945865306</v>
@@ -15061,7 +15061,7 @@
         <v>2.145825454055195</v>
       </c>
       <c r="D271" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E271">
         <v>2.567272076620798</v>
@@ -15111,7 +15111,7 @@
         <v>3.117834193471839</v>
       </c>
       <c r="D272" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E272">
         <v>2.507834193471838</v>
@@ -15161,7 +15161,7 @@
         <v>2.068689520733654</v>
       </c>
       <c r="D273" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E273">
         <v>2.489975777533515</v>
@@ -15211,7 +15211,7 @@
         <v>3.048235451140136</v>
       </c>
       <c r="D274" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E274">
         <v>2.438235451140136</v>
@@ -15261,7 +15261,7 @@
         <v>1.98934486068918</v>
       </c>
       <c r="D275" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E275">
         <v>2.539161477129087</v>
@@ -15311,7 +15311,7 @@
         <v>2.976643803615602</v>
       </c>
       <c r="D276" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E276">
         <v>2.366643803615601</v>
@@ -15361,7 +15361,7 @@
         <v>1.910228381091732</v>
       </c>
       <c r="D277" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E277">
         <v>2.463005697391833</v>
@@ -15411,7 +15411,7 @@
         <v>2.905258040319775</v>
       </c>
       <c r="D278" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E278">
         <v>2.295258040319774</v>
@@ -15461,7 +15461,7 @@
         <v>1.737565923958936</v>
       </c>
       <c r="D279" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E279">
         <v>2.268709795269682</v>
@@ -15511,7 +15511,7 @@
         <v>1.733986526635413</v>
       </c>
       <c r="D280" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E280">
         <v>2.293359172208309</v>
@@ -15561,7 +15561,7 @@
         <v>2.746237323409084</v>
       </c>
       <c r="D281" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E281">
         <v>2.136237323409084</v>
@@ -15611,7 +15611,7 @@
         <v>1.537618654463894</v>
       </c>
       <c r="D282" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E282">
         <v>2.074713337366754</v>
@@ -15661,7 +15661,7 @@
         <v>1.543163834914946</v>
       </c>
       <c r="D283" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E283">
         <v>2.109677454398378</v>
@@ -15711,7 +15711,7 @@
         <v>2.574060508010575</v>
       </c>
       <c r="D284" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E284">
         <v>1.964060508010575</v>
@@ -15761,7 +15761,7 @@
         <v>1.32861267508225</v>
       </c>
       <c r="D285" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E285">
         <v>1.871927774038136</v>
@@ -15811,7 +15811,7 @@
         <v>1.343695826814607</v>
       </c>
       <c r="D286" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E286">
         <v>1.91767394556167</v>
@@ -15861,7 +15861,7 @@
         <v>2.394083136876382</v>
       </c>
       <c r="D287" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E287">
         <v>1.784083136876382</v>
@@ -15911,7 +15911,7 @@
         <v>1.270355943810468</v>
       </c>
       <c r="D288" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E288">
         <v>1.815404874054204</v>
@@ -15961,7 +15961,7 @@
         <v>1.288097636850863</v>
       </c>
       <c r="D289" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E289">
         <v>1.864156353143347</v>
@@ -16011,7 +16011,7 @@
         <v>2.343917618281236</v>
       </c>
       <c r="D290" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E290">
         <v>1.733917618281236</v>
@@ -16061,7 +16061,7 @@
         <v>1.164376800206434</v>
       </c>
       <c r="D291" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E291">
         <v>1.712579871628862</v>
@@ -16111,7 +16111,7 @@
         <v>1.186954843054156</v>
       </c>
       <c r="D292" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E292">
         <v>1.76679852876107</v>
@@ -16161,7 +16161,7 @@
         <v>2.252657800177763</v>
       </c>
       <c r="D293" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E293">
         <v>1.642657800177763</v>
@@ -16211,7 +16211,7 @@
         <v>1.095337982971794</v>
       </c>
       <c r="D294" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E294">
         <v>1.645595781097634</v>
@@ -16261,7 +16261,7 @@
         <v>1.121066606764748</v>
       </c>
       <c r="D295" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E295">
         <v>1.703375964515756</v>
@@ -16311,7 +16311,7 @@
         <v>2.193207707559045</v>
       </c>
       <c r="D296" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E296">
         <v>1.583207707559045</v>
@@ -16361,7 +16361,7 @@
         <v>0.875155284260706</v>
       </c>
       <c r="D297" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E297">
         <v>1.489897717173242</v>
@@ -16411,7 +16411,7 @@
         <v>0.9109319280345227</v>
       </c>
       <c r="D298" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E298">
         <v>1.501104953596641</v>
@@ -16461,7 +16461,7 @@
         <v>2.003605939224497</v>
       </c>
       <c r="D299" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E299">
         <v>1.393605939224496</v>
@@ -16511,7 +16511,7 @@
         <v>0.7877632879655483</v>
       </c>
       <c r="D300" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E300">
         <v>1.407881022237508</v>
@@ -16561,7 +16561,7 @@
         <v>0.8275280585544227</v>
       </c>
       <c r="D301" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E301">
         <v>1.420822226841367</v>
@@ -16611,7 +16611,7 @@
         <v>1.928351720192556</v>
       </c>
       <c r="D302" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E302">
         <v>1.318351720192555</v>
@@ -16661,7 +16661,7 @@
         <v>0.6445889510900153</v>
       </c>
       <c r="D303" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E303">
         <v>1.273513043384081</v>
@@ -16711,7 +16711,7 @@
         <v>0.6908874711791615</v>
       </c>
       <c r="D304" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E304">
         <v>1.289295008640233</v>
@@ -16761,7 +16761,7 @@
         <v>1.805062707883069</v>
       </c>
       <c r="D305" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E305">
         <v>1.195062707883069</v>
@@ -16811,7 +16811,7 @@
         <v>0.5834745700515587</v>
       </c>
       <c r="D306" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E306">
         <v>1.216157681814259</v>
@@ -16861,7 +16861,7 @@
         <v>0.6325620400690468</v>
       </c>
       <c r="D307" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E307">
         <v>1.233152233995777</v>
@@ -16911,7 +16911,7 @@
         <v>1.752436435322175</v>
       </c>
       <c r="D308" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E308">
         <v>1.142436435322175</v>
@@ -16961,7 +16961,7 @@
         <v>0.6410588642705362</v>
       </c>
       <c r="D309" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E309">
         <v>1.24133108972403</v>
@@ -16997,7 +16997,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17011,7 +17011,7 @@
         <v>0.6556505260902954</v>
       </c>
       <c r="D310" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E310">
         <v>1.24133108972403</v>
@@ -17047,7 +17047,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17061,7 +17061,7 @@
         <v>1.760103008510213</v>
       </c>
       <c r="D311" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E311">
         <v>1.150103008510213</v>
@@ -17097,7 +17097,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17111,7 +17111,7 @@
         <v>0.6538601304024763</v>
       </c>
       <c r="D312" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E312">
         <v>1.253653306395731</v>
@@ -17161,7 +17161,7 @@
         <v>0.6691703664125939</v>
       </c>
       <c r="D313" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E313">
         <v>1.253653306395731</v>
@@ -17211,7 +17211,7 @@
         <v>1.771653423273752</v>
       </c>
       <c r="D314" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E314">
         <v>1.161653423273751</v>
@@ -17261,7 +17261,7 @@
         <v>0.5994681371241404</v>
       </c>
       <c r="D315" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E315">
         <v>1.201296772325317</v>
@@ -17311,7 +17311,7 @@
         <v>0.6117251843223768</v>
       </c>
       <c r="D316" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E316">
         <v>1.201296772325317</v>
@@ -17361,7 +17361,7 @@
         <v>1.722576240149433</v>
       </c>
       <c r="D317" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E317">
         <v>1.112576240149433</v>
@@ -17411,7 +17411,7 @@
         <v>0.6080222404361217</v>
       </c>
       <c r="D318" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E318">
         <v>1.209530763663045</v>
@@ -17461,7 +17461,7 @@
         <v>0.6207594555957376</v>
       </c>
       <c r="D319" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E319">
         <v>1.209530763663045</v>
@@ -17511,7 +17511,7 @@
         <v>1.730294495528642</v>
       </c>
       <c r="D320" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E320">
         <v>1.120294495528642</v>
@@ -17561,7 +17561,7 @@
         <v>0.5618859798618736</v>
       </c>
       <c r="D321" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E321">
         <v>1.165121015958519</v>
@@ -17611,7 +17611,7 @@
         <v>0.5720334257169055</v>
       </c>
       <c r="D322" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E322">
         <v>1.165121015958519</v>
@@ -17661,7 +17661,7 @@
         <v>1.688666351892003</v>
       </c>
       <c r="D323" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E323">
         <v>1.078666351892003</v>
@@ -17711,7 +17711,7 @@
         <v>0.508437810595022</v>
       </c>
       <c r="D324" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E324">
         <v>1.11367298608211</v>
@@ -17761,7 +17761,7 @@
         <v>0.5155850473643886</v>
       </c>
       <c r="D325" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E325">
         <v>1.11367298608211</v>
@@ -17811,7 +17811,7 @@
         <v>1.640440768811309</v>
       </c>
       <c r="D326" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E326">
         <v>1.030440768811308</v>
@@ -17861,7 +17861,7 @@
         <v>0.4164767378858123</v>
       </c>
       <c r="D327" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E327">
         <v>1.025153284077196</v>
@@ -17911,7 +17911,7 @@
         <v>0.4184619185987364</v>
       </c>
       <c r="D328" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E328">
         <v>1.025153284077196</v>
@@ -17961,7 +17961,7 @@
         <v>1.557465497385535</v>
       </c>
       <c r="D329" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E329">
         <v>0.9474654973855348</v>
@@ -18011,7 +18011,7 @@
         <v>0.3644704529510241</v>
       </c>
       <c r="D330" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E330">
         <v>0.9750931802834177</v>
@@ -18061,7 +18061,7 @@
         <v>0.3635363619524323</v>
       </c>
       <c r="D331" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E331">
         <v>0.9750931802834177</v>
@@ -18111,7 +18111,7 @@
         <v>1.565054544022541</v>
       </c>
       <c r="D332" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E332">
         <v>0.9005409076522746</v>
@@ -18161,7 +18161,7 @@
         <v>0.2866150347691372</v>
       </c>
       <c r="D333" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E333">
         <v>0.9143380680881883</v>
@@ -18211,7 +18211,7 @@
         <v>0.2813106812114787</v>
       </c>
       <c r="D334" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E334">
         <v>0.9143380680881883</v>
@@ -18261,7 +18261,7 @@
         <v>0.3483831526216896</v>
       </c>
       <c r="D335" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E335">
         <v>0.9143380680881883</v>
@@ -18311,7 +18311,7 @@
         <v>1.495130343077478</v>
       </c>
       <c r="D336" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E336">
         <v>0.8302929835546884</v>
@@ -18361,7 +18361,7 @@
         <v>0.2225831635998929</v>
       </c>
       <c r="D337" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E337">
         <v>0.8619688447062037</v>
@@ -18411,7 +18411,7 @@
         <v>0.2987488573747035</v>
       </c>
       <c r="D338" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E338">
         <v>0.8619688447062037</v>
@@ -18461,7 +18461,7 @@
         <v>0.2938174275967516</v>
       </c>
       <c r="D339" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E339">
         <v>0.8619688447062037</v>
@@ -18511,7 +18511,7 @@
         <v>1.445188832037704</v>
       </c>
       <c r="D340" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E340">
         <v>0.7801202618156564</v>
@@ -18561,7 +18561,7 @@
         <v>0.3281392211768228</v>
       </c>
       <c r="D341" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E341">
         <v>0.8803786785285439</v>
@@ -18611,7 +18611,7 @@
         <v>0.3180121272020529</v>
       </c>
       <c r="D342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E342">
         <v>0.8803786785285439</v>
@@ -18661,7 +18661,7 @@
         <v>0.3129994178045763</v>
       </c>
       <c r="D343" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E343">
         <v>0.8803786785285439</v>
@@ -18711,7 +18711,7 @@
         <v>1.462745229855035</v>
       </c>
       <c r="D344" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E344">
         <v>0.7977579392525129</v>
@@ -18761,7 +18761,7 @@
         <v>0.3459316339300287</v>
       </c>
       <c r="D345" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E345">
         <v>0.8966943930572944</v>
@@ -18811,7 +18811,7 @@
         <v>0.3350841993579632</v>
       </c>
       <c r="D346" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E346">
         <v>0.8966943930572944</v>
@@ -18861,7 +18861,7 @@
         <v>0.3299994559007571</v>
       </c>
       <c r="D347" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E347">
         <v>0.8966943930572944</v>
@@ -18911,7 +18911,7 @@
         <v>1.478304586756625</v>
       </c>
       <c r="D348" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E348">
         <v>0.8133893302138313</v>
@@ -18961,7 +18961,7 @@
         <v>0.3746816311597856</v>
       </c>
       <c r="D349" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E349">
         <v>0.9230582569137313</v>
@@ -19011,7 +19011,7 @@
         <v>0.3626702290885397</v>
       </c>
       <c r="D350" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E350">
         <v>0.9230582569137313</v>
@@ -19061,7 +19061,7 @@
         <v>0.357469088881416</v>
       </c>
       <c r="D351" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E351">
         <v>0.9230582569137313</v>
@@ -19111,7 +19111,7 @@
         <v>1.503446284738923</v>
       </c>
       <c r="D352" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E352">
         <v>0.8386474249460472</v>
@@ -19161,7 +19161,7 @@
         <v>0.3609903029368784</v>
       </c>
       <c r="D353" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E353">
         <v>0.9727726579916833</v>
@@ -19211,7 +19211,7 @@
         <v>0.4278925267560636</v>
       </c>
       <c r="D354" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E354">
         <v>0.9853909591149721</v>
@@ -19261,7 +19261,7 @@
         <v>0.4224161869807217</v>
       </c>
       <c r="D355" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E355">
         <v>0.9853909591149721</v>
@@ -19311,7 +19311,7 @@
         <v>1.508365731249223</v>
       </c>
       <c r="D356" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E356">
         <v>0.898365731249223</v>
@@ -19361,7 +19361,7 @@
         <v>0.5369709001154694</v>
       </c>
       <c r="D357" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E357">
         <v>1.089636746312885</v>
@@ -19411,7 +19411,7 @@
         <v>0.531034314039033</v>
       </c>
       <c r="D358" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E358">
         <v>1.089636746312885</v>
@@ -19461,7 +19461,7 @@
         <v>1.608239178586738</v>
       </c>
       <c r="D359" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E359">
         <v>0.9982391785867382</v>
@@ -19511,7 +19511,7 @@
         <v>0.5385854937585846</v>
       </c>
       <c r="D360" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E360">
         <v>0.634839149452838</v>
@@ -19561,7 +19561,7 @@
         <v>2.009812451983092</v>
       </c>
       <c r="D361" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E361">
         <v>1.399812451983092</v>
@@ -19611,7 +19611,7 @@
         <v>0.9230051396340304</v>
       </c>
       <c r="D362" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E362">
         <v>0.9850070169538339</v>
@@ -19661,7 +19661,7 @@
         <v>0.8994749023453439</v>
       </c>
       <c r="D363" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E363">
         <v>0.9850070169538339</v>
@@ -19711,7 +19711,7 @@
         <v>2.109691017081675</v>
       </c>
       <c r="D364" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E364">
         <v>1.499691017081674</v>
@@ -19761,7 +19761,7 @@
         <v>1.015979656453909</v>
       </c>
       <c r="D365" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E365">
         <v>1.231185799135601</v>
@@ -19811,7 +19811,7 @@
         <v>0.9827837515750368</v>
       </c>
       <c r="D366" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E366">
         <v>1.231185799135601</v>
@@ -19861,7 +19861,7 @@
         <v>2.200993423621709</v>
       </c>
       <c r="D367" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E367">
         <v>1.590993423621708</v>
@@ -19911,7 +19911,7 @@
         <v>1.100970836735415</v>
       </c>
       <c r="D368" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E368">
         <v>1.303589318044656</v>
@@ -19961,7 +19961,7 @@
         <v>1.058939215094605</v>
       </c>
       <c r="D369" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E369">
         <v>1.303589318044656</v>
@@ -20011,7 +20011,7 @@
         <v>2.329644706282916</v>
       </c>
       <c r="D370" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E370">
         <v>1.719644706282915</v>
@@ -20061,7 +20061,7 @@
         <v>1.220729173590548</v>
       </c>
       <c r="D371" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E371">
         <v>1.321050696987874</v>
@@ -20111,7 +20111,7 @@
         <v>2.471463589779925</v>
       </c>
       <c r="D372" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E372">
         <v>1.861463589779925</v>
@@ -20211,7 +20211,7 @@
         <v>2.497443975683849</v>
       </c>
       <c r="D374" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E374">
         <v>1.887443975683849</v>
@@ -20361,7 +20361,7 @@
         <v>2.512308244184901</v>
       </c>
       <c r="D377" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E377">
         <v>1.9023082441849</v>
@@ -20397,7 +20397,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20411,7 +20411,7 @@
         <v>1.390766199655991</v>
       </c>
       <c r="D378" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E378">
         <v>1.47783631505106</v>
@@ -20447,7 +20447,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20461,7 +20461,7 @@
         <v>1.39783631505106</v>
       </c>
       <c r="D379" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E379">
         <v>1.47783631505106</v>
@@ -20497,7 +20497,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20511,7 +20511,7 @@
         <v>2.5135497431605</v>
       </c>
       <c r="D380" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E380">
         <v>1.903549743160499</v>
@@ -20561,7 +20561,7 @@
         <v>1.39192188073005</v>
       </c>
       <c r="D381" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E381">
         <v>1.488828942112197</v>
@@ -20611,7 +20611,7 @@
         <v>1.319642873327421</v>
       </c>
       <c r="D382" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E382">
         <v>1.488828942112197</v>
@@ -20661,7 +20661,7 @@
         <v>1.388828942112196</v>
       </c>
       <c r="D383" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E383">
         <v>1.488828942112197</v>
@@ -20711,7 +20711,7 @@
         <v>2.501566998394471</v>
       </c>
       <c r="D384" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E384">
         <v>1.891566998394471</v>
@@ -20747,7 +20747,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20761,7 +20761,7 @@
         <v>1.279594745212004</v>
       </c>
       <c r="D385" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E385">
         <v>1.519061703811337</v>
@@ -20797,7 +20797,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20811,7 +20811,7 @@
         <v>1.30964804935207</v>
       </c>
       <c r="D386" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E386">
         <v>1.519061703811337</v>
@@ -20847,7 +20847,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20861,7 +20861,7 @@
         <v>2.48573721583752</v>
       </c>
       <c r="D387" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E387">
         <v>1.875737215837519</v>
@@ -20911,7 +20911,7 @@
         <v>1.266464050003473</v>
       </c>
       <c r="D388" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E388">
         <v>1.59667031375327</v>
@@ -20961,7 +20961,7 @@
         <v>1.296444405836825</v>
       </c>
       <c r="D389" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E389">
         <v>1.59667031375327</v>
@@ -21011,7 +21011,7 @@
         <v>2.454303876936348</v>
       </c>
       <c r="D390" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E390">
         <v>1.844303876936348</v>
@@ -21061,7 +21061,7 @@
         <v>1.240390312666095</v>
       </c>
       <c r="D391" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E391">
         <v>1.592199793558723</v>
@@ -21111,7 +21111,7 @@
         <v>1.270225814403128</v>
       </c>
       <c r="D392" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E392">
         <v>1.592199793558723</v>
@@ -21161,7 +21161,7 @@
         <v>2.438801816749918</v>
       </c>
       <c r="D393" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E393">
         <v>1.828801816749918</v>
@@ -21211,7 +21211,7 @@
         <v>1.227531460898549</v>
       </c>
       <c r="D394" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E394">
         <v>1.611306442152011</v>
@@ -21261,7 +21261,7 @@
         <v>1.257295524570208</v>
       </c>
       <c r="D395" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E395">
         <v>1.611306442152011</v>
@@ -21311,7 +21311,7 @@
         <v>2.435888213210831</v>
       </c>
       <c r="D396" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E396">
         <v>1.825888213210831</v>
@@ -21361,7 +21361,7 @@
         <v>1.225114646902994</v>
       </c>
       <c r="D397" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E397">
         <v>1.589727863749075</v>
@@ -21411,7 +21411,7 @@
         <v>1.254865283830232</v>
       </c>
       <c r="D398" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E398">
         <v>1.589727863749075</v>
@@ -21461,7 +21461,7 @@
         <v>2.394557671241156</v>
       </c>
       <c r="D399" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E399">
         <v>1.784557671241155</v>
@@ -21511,7 +21511,7 @@
         <v>1.190831248034139</v>
       </c>
       <c r="D400" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E400">
         <v>1.609187949630535</v>
@@ -21561,7 +21561,7 @@
         <v>1.220391421634328</v>
       </c>
       <c r="D401" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E401">
         <v>1.609187949630535</v>
@@ -21611,7 +21611,7 @@
         <v>2.366135904185318</v>
       </c>
       <c r="D402" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E402">
         <v>1.756135904185318</v>
@@ -21661,7 +21661,7 @@
         <v>1.167255588725149</v>
       </c>
       <c r="D403" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E403">
         <v>1.578100832137494</v>
@@ -21711,7 +21711,7 @@
         <v>1.196684786440288</v>
       </c>
       <c r="D404" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E404">
         <v>1.578100832137494</v>
@@ -21761,7 +21761,7 @@
         <v>2.396096253709469</v>
       </c>
       <c r="D405" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E405">
         <v>1.786096253709469</v>
@@ -21811,7 +21811,7 @@
         <v>1.192107491556242</v>
       </c>
       <c r="D406" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E406">
         <v>1.492060423190722</v>
@@ -21861,7 +21861,7 @@
         <v>1.221674755398221</v>
       </c>
       <c r="D407" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E407">
         <v>1.492060423190722</v>
@@ -21911,7 +21911,7 @@
         <v>2.341003521520614</v>
       </c>
       <c r="D408" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E408">
         <v>1.731003521520614</v>
@@ -21961,7 +21961,7 @@
         <v>1.146408451030924</v>
       </c>
       <c r="D409" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E409">
         <v>1.603573943943295</v>
@@ -22011,7 +22011,7 @@
         <v>1.175721831314429</v>
       </c>
       <c r="D410" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E410">
         <v>1.603573943943295</v>
@@ -22061,7 +22061,7 @@
         <v>2.3387346635889</v>
       </c>
       <c r="D411" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E411">
         <v>1.7287346635889</v>
@@ -22111,7 +22111,7 @@
         <v>1.144526449059917</v>
       </c>
       <c r="D412" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E412">
         <v>1.601256255851928</v>
@@ -22161,7 +22161,7 @@
         <v>1.173829373776917</v>
       </c>
       <c r="D413" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E413">
         <v>1.601256255851928</v>
@@ -22211,7 +22211,7 @@
         <v>2.321864997704619</v>
       </c>
       <c r="D414" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E414">
         <v>1.711864997704619</v>
@@ -22261,7 +22261,7 @@
         <v>1.130533177819499</v>
       </c>
       <c r="D415" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E415">
         <v>1.628353938431452</v>
@@ -22311,7 +22311,7 @@
         <v>1.159758362140719</v>
       </c>
       <c r="D416" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E416">
         <v>1.628353938431452</v>
@@ -22361,7 +22361,7 @@
         <v>2.329307629672357</v>
       </c>
       <c r="D417" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E417">
         <v>1.719307629672357</v>
@@ -22411,7 +22411,7 @@
         <v>1.136706789589973</v>
       </c>
       <c r="D418" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E418">
         <v>1.641887405220004</v>
@@ -22461,7 +22461,7 @@
         <v>1.165966271754362</v>
       </c>
       <c r="D419" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E419">
         <v>1.641887405220004</v>
@@ -22511,7 +22511,7 @@
         <v>2.283832828965951</v>
       </c>
       <c r="D420" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E420">
         <v>1.673832828965951</v>
@@ -22561,7 +22561,7 @@
         <v>1.09898575674595</v>
       </c>
       <c r="D421" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E421">
         <v>1.611312616281895</v>
@@ -22611,7 +22611,7 @@
         <v>1.128035677616761</v>
       </c>
       <c r="D422" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E422">
         <v>1.611312616281895</v>
@@ -22661,7 +22661,7 @@
         <v>2.182831733767929</v>
       </c>
       <c r="D423" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E423">
         <v>1.572831733767929</v>
@@ -22711,7 +22711,7 @@
         <v>1.084064563230975</v>
       </c>
       <c r="D424" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E424">
         <v>1.514840661441129</v>
@@ -22761,7 +22761,7 @@
         <v>1.04379052447924</v>
       </c>
       <c r="D425" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E425">
         <v>1.514840661441129</v>
@@ -22811,7 +22811,7 @@
         <v>1.987186684521362</v>
       </c>
       <c r="D426" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E426">
         <v>1.377186684521361</v>
@@ -22861,7 +22861,7 @@
         <v>0.9019433653148159</v>
       </c>
       <c r="D427" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E427">
         <v>1.471274636039009</v>
@@ -22911,7 +22911,7 @@
         <v>0.8806027184256511</v>
       </c>
       <c r="D428" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E428">
         <v>1.471274636039009</v>
@@ -22961,7 +22961,7 @@
         <v>1.871503922012645</v>
       </c>
       <c r="D429" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E429">
         <v>1.261503922012645</v>
@@ -23011,7 +23011,7 @@
         <v>0.8271315762745894</v>
       </c>
       <c r="D430" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E430">
         <v>1.39104304268619</v>
@@ -23061,7 +23061,7 @@
         <v>0.784111566287045</v>
       </c>
       <c r="D431" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E431">
         <v>1.39104304268619</v>
@@ -23111,7 +23111,7 @@
         <v>1.725043908638261</v>
       </c>
       <c r="D432" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E432">
         <v>1.115043908638261</v>
@@ -23161,7 +23161,7 @@
         <v>0.6891081996153199</v>
       </c>
       <c r="D433" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E433">
         <v>1.208315076967225</v>
@@ -23211,7 +23211,7 @@
         <v>0.6619490666521894</v>
       </c>
       <c r="D434" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E434">
         <v>1.208315076967225</v>
@@ -23261,7 +23261,7 @@
         <v>1.603418511347999</v>
       </c>
       <c r="D435" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E435">
         <v>0.9934185113479987</v>
@@ -23311,7 +23311,7 @@
         <v>0.574488873597538</v>
       </c>
       <c r="D436" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E436">
         <v>1.108556250145786</v>
@@ -23361,7 +23361,7 @@
         <v>0.5605011546266709</v>
       </c>
       <c r="D437" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E437">
         <v>1.108556250145786</v>
@@ -23411,7 +23411,7 @@
         <v>1.504487777527864</v>
       </c>
       <c r="D438" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E438">
         <v>0.8944877775278632</v>
@@ -23461,7 +23461,7 @@
         <v>0.4812569147670418</v>
       </c>
       <c r="D439" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E439">
         <v>1.036979636275919</v>
@@ -23511,7 +23511,7 @@
         <v>0.4779828927766969</v>
       </c>
       <c r="D440" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E440">
         <v>1.036979636275919</v>
@@ -23561,7 +23561,7 @@
         <v>1.414501209603441</v>
       </c>
       <c r="D441" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E441">
         <v>0.9219355330393615</v>
@@ -23611,7 +23611,7 @@
         <v>0.3964539049027813</v>
       </c>
       <c r="D442" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E442">
         <v>0.9417865782881711</v>
@@ -23661,7 +23661,7 @@
         <v>0.4029249720655423</v>
       </c>
       <c r="D443" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E443">
         <v>0.9417865782881711</v>
@@ -23711,7 +23711,7 @@
         <v>1.374244075534095</v>
       </c>
       <c r="D444" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E444">
         <v>0.8269425846185072</v>
@@ -23761,7 +23761,7 @@
         <v>0.3063097844755669</v>
       </c>
       <c r="D445" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E445">
         <v>0.873462183832336</v>
@@ -23811,7 +23811,7 @@
         <v>0.3231397114429218</v>
       </c>
       <c r="D446" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E446">
         <v>0.873462183832336</v>
@@ -23861,7 +23861,7 @@
         <v>1.297276604707491</v>
       </c>
       <c r="D447" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E447">
         <v>0.7916599773381927</v>
@@ -23911,7 +23911,7 @@
         <v>0.233440118808713</v>
       </c>
       <c r="D448" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E448">
         <v>0.818230896896579</v>
@@ -23961,7 +23961,7 @@
         <v>0.2586438215372961</v>
       </c>
       <c r="D449" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E449">
         <v>0.818230896896579</v>
@@ -24061,7 +24061,7 @@
         <v>1.228322830557575</v>
       </c>
       <c r="D451" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E451">
         <v>0.7235042792779742</v>
@@ -24111,7 +24111,7 @@
         <v>0.1681574946714077</v>
       </c>
       <c r="D452" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E452">
         <v>0.7687501793352967</v>
@@ -24161,7 +24161,7 @@
         <v>0.2008631126431526</v>
       </c>
       <c r="D453" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E453">
         <v>0.7687501793352967</v>
@@ -24211,7 +24211,7 @@
         <v>1.23967353577152</v>
       </c>
       <c r="D454" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E454">
         <v>1.163072722956397</v>
@@ -24261,7 +24261,7 @@
         <v>1.225596128630588</v>
       </c>
       <c r="D455" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E455">
         <v>0.6905047055753135</v>
@@ -24311,7 +24311,7 @@
         <v>0.136549003700944</v>
       </c>
       <c r="D456" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E456">
         <v>0.7447926433919125</v>
@@ -24361,7 +24361,7 @@
         <v>0.172886893251202</v>
       </c>
       <c r="D457" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E457">
         <v>0.7447926433919125</v>
@@ -24461,7 +24461,7 @@
         <v>1.220200273962068</v>
       </c>
       <c r="D459" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E459">
         <v>0.6852080850156392</v>
@@ -24511,7 +24511,7 @@
         <v>0.1314756598861742</v>
       </c>
       <c r="D460" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E460">
         <v>0.7409473216741169</v>
@@ -24561,7 +24561,7 @@
         <v>0.1683965498259044</v>
       </c>
       <c r="D461" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E461">
         <v>0.7409473216741169</v>
@@ -24611,7 +24611,7 @@
         <v>1.216624069904026</v>
       </c>
       <c r="D462" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E462">
         <v>1.236624069904027</v>
@@ -24661,7 +24661,7 @@
         <v>1.283513715629472</v>
       </c>
       <c r="D463" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E463">
         <v>1.236624069904027</v>
@@ -24711,7 +24711,7 @@
         <v>1.245299916107382</v>
       </c>
       <c r="D464" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E464">
         <v>0.7098461245467869</v>
@@ -24761,7 +24761,7 @@
         <v>0.155075093535447</v>
       </c>
       <c r="D465" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E465">
         <v>0.7588344229730764</v>
@@ -24811,7 +24811,7 @@
         <v>0.1892840681169474</v>
       </c>
       <c r="D466" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E466">
         <v>0.7588344229730764</v>
@@ -24861,7 +24861,7 @@
         <v>1.346682022872791</v>
       </c>
       <c r="D467" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E467">
         <v>1.156906845444727</v>
@@ -24911,7 +24911,7 @@
         <v>1.297477194708015</v>
       </c>
       <c r="D468" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E468">
         <v>1.156906845444727</v>
@@ -24961,7 +24961,7 @@
         <v>1.297810076779093</v>
       </c>
       <c r="D469" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E469">
         <v>0.761390581114191</v>
@@ -25011,7 +25011,7 @@
         <v>0.2044467158681593</v>
       </c>
       <c r="D470" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E470">
         <v>0.7962554570149853</v>
@@ -25061,7 +25061,7 @@
         <v>0.2329821788368545</v>
       </c>
       <c r="D471" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E471">
         <v>0.7962554570149853</v>
@@ -25111,7 +25111,7 @@
         <v>1.375532432988972</v>
       </c>
       <c r="D472" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E472">
         <v>1.038262852606697</v>
@@ -25161,7 +25161,7 @@
         <v>1.326689743863311</v>
       </c>
       <c r="D473" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E473">
         <v>1.038262852606697</v>
@@ -25211,7 +25211,7 @@
         <v>1.316058735434172</v>
       </c>
       <c r="D474" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E474">
         <v>0.7793036322537743</v>
@@ -25247,7 +25247,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25261,7 +25261,7 @@
         <v>0.221604650097877</v>
       </c>
       <c r="D475" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E475">
         <v>0.8092602482404443</v>
@@ -25297,7 +25297,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25311,7 +25311,7 @@
         <v>0.2481684189130346</v>
       </c>
       <c r="D476" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E476">
         <v>0.8092602482404443</v>
@@ -25347,7 +25347,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25361,7 +25361,7 @@
         <v>1.385558707514407</v>
       </c>
       <c r="D477" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E477">
         <v>1.0151454476213</v>
@@ -25397,7 +25397,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25411,7 +25411,7 @@
         <v>1.336841871207057</v>
       </c>
       <c r="D478" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E478">
         <v>1.0151454476213</v>
@@ -25447,7 +25447,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25461,7 +25461,7 @@
         <v>1.357255810174356</v>
       </c>
       <c r="D479" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E479">
         <v>0.8197430596424145</v>
@@ -25511,7 +25511,7 @@
         <v>0.2603393709455446</v>
       </c>
       <c r="D480" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E480">
         <v>0.8673754583787305</v>
@@ -25561,7 +25561,7 @@
         <v>0.2824519615703833</v>
       </c>
       <c r="D481" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E481">
         <v>0.8673754583787305</v>
@@ -25611,7 +25611,7 @@
         <v>1.408193422141772</v>
       </c>
       <c r="D482" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E482">
         <v>1.092946268617976</v>
@@ -25661,7 +25661,7 @@
         <v>1.359760703591251</v>
       </c>
       <c r="D483" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E483">
         <v>1.092946268617976</v>
@@ -25711,7 +25711,7 @@
         <v>1.400693800028334</v>
       </c>
       <c r="D484" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E484">
         <v>0.8623821899128705</v>
@@ -25761,7 +25761,7 @@
         <v>0.3011810671530766</v>
       </c>
       <c r="D485" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E485">
         <v>0.898730697031946</v>
@@ -25811,7 +25811,7 @@
         <v>0.3186003577247281</v>
       </c>
       <c r="D486" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E486">
         <v>0.898730697031946</v>
@@ -25861,7 +25861,7 @@
         <v>1.432059352199475</v>
       </c>
       <c r="D487" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E487">
         <v>0.9910848179499889</v>
@@ -25911,7 +25911,7 @@
         <v>1.383926205992774</v>
       </c>
       <c r="D488" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E488">
         <v>0.9910848179499889</v>
@@ -25961,7 +25961,7 @@
         <v>1.389878787820437</v>
       </c>
       <c r="D489" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E489">
         <v>0.851766074481211</v>
@@ -26011,7 +26011,7 @@
         <v>0.291012469467951</v>
       </c>
       <c r="D490" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E490">
         <v>0.8909239985646367</v>
@@ -26061,7 +26061,7 @@
         <v>0.3096002785999952</v>
       </c>
       <c r="D491" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E491">
         <v>0.8909239985646367</v>
@@ -26111,7 +26111,7 @@
         <v>1.426117311009389</v>
       </c>
       <c r="D492" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E492">
         <v>1.145927272692262</v>
@@ -26161,7 +26161,7 @@
         <v>1.377909578511599</v>
       </c>
       <c r="D493" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E493">
         <v>1.145927272692262</v>
@@ -26211,7 +26211,7 @@
         <v>1.390470377742177</v>
       </c>
       <c r="D494" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E494">
         <v>0.8523467845882973</v>
@@ -26261,7 +26261,7 @@
         <v>0.2915686999920695</v>
       </c>
       <c r="D495" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E495">
         <v>0.8913510312897541</v>
@@ -26311,7 +26311,7 @@
         <v>0.3100925902130296</v>
       </c>
       <c r="D496" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E496">
         <v>0.8913510312897541</v>
@@ -26361,7 +26361,7 @@
         <v>1.426442345472138</v>
       </c>
       <c r="D497" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E497">
         <v>1.04260947236648</v>
@@ -26411,7 +26411,7 @@
         <v>1.4090266167915</v>
       </c>
       <c r="D498" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E498">
         <v>0.8705617594711974</v>
@@ -26461,7 +26461,7 @@
         <v>0.3090158305005142</v>
       </c>
       <c r="D499" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E499">
         <v>0.9047456498219102</v>
@@ -26511,7 +26511,7 @@
         <v>0.3255347937437314</v>
       </c>
       <c r="D500" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E500">
         <v>0.9047456498219102</v>
@@ -26561,7 +26561,7 @@
         <v>1.436637612444065</v>
       </c>
       <c r="D501" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E501">
         <v>1.0174159700749</v>
@@ -26611,7 +26611,7 @@
         <v>1.481023111428944</v>
       </c>
       <c r="D502" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E502">
         <v>0.9412341806440443</v>
@@ -26661,7 +26661,7 @@
         <v>0.3767090863780185</v>
       </c>
       <c r="D503" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E503">
         <v>0.9692419169592172</v>
@@ -26711,7 +26711,7 @@
         <v>0.3854491180167301</v>
       </c>
       <c r="D504" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E504">
         <v>0.9692419169592172</v>
@@ -26761,7 +26761,7 @@
         <v>1.476194307198891</v>
       </c>
       <c r="D505" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E505">
         <v>1.037981948597929</v>
@@ -26811,7 +26811,7 @@
         <v>1.566896676462016</v>
       </c>
       <c r="D506" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E506">
         <v>1.019149230451688</v>
@@ -26861,7 +26861,7 @@
         <v>0.4887054182244546</v>
       </c>
       <c r="D507" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E507">
         <v>1.141981249108951</v>
@@ -26911,7 +26911,7 @@
         <v>0.4845754557390034</v>
       </c>
       <c r="D508" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E508">
         <v>1.141981249108951</v>
@@ -26961,7 +26961,7 @@
         <v>1.575427906313638</v>
       </c>
       <c r="D509" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E509">
         <v>0.9905476528404038</v>
@@ -27011,7 +27011,7 @@
         <v>1.651922146792429</v>
       </c>
       <c r="D510" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E510">
         <v>1.103977882563743</v>
@@ -27061,7 +27061,7 @@
         <v>0.5692040695326464</v>
       </c>
       <c r="D511" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E511">
         <v>1.20122353283454</v>
@@ -27111,7 +27111,7 @@
         <v>0.5558236507843963</v>
       </c>
       <c r="D512" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E512">
         <v>1.20122353283454</v>
@@ -27161,7 +27161,7 @@
         <v>1.619515187225704</v>
       </c>
       <c r="D513" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E513">
         <v>1.044672662888699</v>
@@ -27211,7 +27211,7 @@
         <v>1.713538754440068</v>
       </c>
       <c r="D514" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E514">
         <v>1.21890599807297</v>
@@ -27261,7 +27261,7 @@
         <v>0.6782657847142568</v>
       </c>
       <c r="D515" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E515">
         <v>1.281486555498756</v>
@@ -27311,7 +27311,7 @@
         <v>0.6523526016297332</v>
       </c>
       <c r="D516" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E516">
         <v>1.281486555498756</v>
@@ -27361,7 +27361,7 @@
         <v>1.849941600908833</v>
       </c>
       <c r="D517" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E517">
         <v>1.239941600908833</v>
@@ -27411,7 +27411,7 @@
         <v>0.8068113243587849</v>
       </c>
       <c r="D518" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E518">
         <v>1.376088529662578</v>
@@ -27461,7 +27461,7 @@
         <v>0.7661264044446945</v>
       </c>
       <c r="D519" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E519">
         <v>1.376088529662578</v>
@@ -27511,7 +27511,7 @@
         <v>2.41237924775196</v>
       </c>
       <c r="D520" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E520">
         <v>1.720876564407629</v>
@@ -27561,7 +27561,7 @@
         <v>1.615923807921956</v>
       </c>
       <c r="D521" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E521">
         <v>1.035548815721295</v>
@@ -27611,7 +27611,7 @@
         <v>-1.235980944049381</v>
       </c>
       <c r="D522" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E522">
         <v>-0.2551142066101404</v>
@@ -27658,40 +27658,40 @@
         <v>70</v>
       </c>
       <c r="C523">
-        <v>0.296648007610111</v>
+        <v>0.5181379488404918</v>
       </c>
       <c r="D523" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E523">
-        <v>1.084155192445554</v>
+        <v>1.439520492917707</v>
       </c>
       <c r="F523">
         <v>-1</v>
       </c>
       <c r="G523">
-        <v>0.01358335199238989</v>
+        <v>0.01290186205115951</v>
       </c>
       <c r="H523">
-        <v>0.01501584480755445</v>
+        <v>0.01450047950708229</v>
       </c>
       <c r="I523">
-        <v>-0.7875071848354427</v>
+        <v>-0.9213825440772148</v>
       </c>
       <c r="J523">
         <v>1.612464075822789</v>
       </c>
       <c r="K523">
-        <v>4.12</v>
+        <v>3.84</v>
       </c>
       <c r="L523">
-        <v>6.94</v>
+        <v>6.71</v>
       </c>
       <c r="M523">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N523">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27708,40 +27708,40 @@
         <v>71</v>
       </c>
       <c r="C524">
-        <v>0.3936393858075808</v>
+        <v>1.084155192445554</v>
       </c>
       <c r="D524" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E524">
-        <v>1.084155192445554</v>
+        <v>1.439520492917707</v>
       </c>
       <c r="F524">
         <v>-1</v>
       </c>
       <c r="G524">
-        <v>0.01290636061419242</v>
+        <v>0.01501584480755445</v>
       </c>
       <c r="H524">
-        <v>0.01501584480755445</v>
+        <v>0.01450047950708229</v>
       </c>
       <c r="I524">
-        <v>-0.6905158066379729</v>
+        <v>-0.3553653004721529</v>
       </c>
       <c r="J524">
         <v>1.612464075822789</v>
       </c>
       <c r="K524">
-        <v>3.88</v>
+        <v>4.32</v>
       </c>
       <c r="L524">
-        <v>6.65</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M524">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N524">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27761,7 +27761,7 @@
         <v>-1.857167569625838</v>
       </c>
       <c r="D525" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E525">
         <v>-0.8406716741111389</v>
@@ -27805,16 +27805,16 @@
         <v>1</v>
       </c>
       <c r="B526" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C526">
         <v>-0.07671408163671245</v>
       </c>
       <c r="D526" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E526">
-        <v>0.4149466581586978</v>
+        <v>0.8121374920237798</v>
       </c>
       <c r="F526">
         <v>-1</v>
@@ -27823,10 +27823,10 @@
         <v>0.01349671408163671</v>
       </c>
       <c r="H526">
-        <v>0.0156850533418413</v>
+        <v>0.01512786250797622</v>
       </c>
       <c r="I526">
-        <v>-0.4916607397954103</v>
+        <v>-0.8888515736604923</v>
       </c>
       <c r="J526">
         <v>1.767373458759561</v>
@@ -27838,10 +27838,10 @@
         <v>6.71</v>
       </c>
       <c r="M526">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N526">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27858,40 +27858,40 @@
         <v>71</v>
       </c>
       <c r="C527">
-        <v>-0.2074090199870948</v>
+        <v>0.4149466581586978</v>
       </c>
       <c r="D527" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E527">
-        <v>0.4149466581586978</v>
+        <v>0.8121374920237798</v>
       </c>
       <c r="F527">
         <v>-1</v>
       </c>
       <c r="G527">
-        <v>0.0135074090199871</v>
+        <v>0.0156850533418413</v>
       </c>
       <c r="H527">
-        <v>0.0156850533418413</v>
+        <v>0.01512786250797622</v>
       </c>
       <c r="I527">
-        <v>-0.6223556781457926</v>
+        <v>-0.397190833865082</v>
       </c>
       <c r="J527">
         <v>1.767373458759561</v>
       </c>
       <c r="K527">
-        <v>3.88</v>
+        <v>4.32</v>
       </c>
       <c r="L527">
-        <v>6.65</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M527">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N527">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27911,10 +27911,10 @@
         <v>-1.956986321655209</v>
       </c>
       <c r="D528" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E528">
-        <v>-0.9347651610615184</v>
+        <v>-0.6814286428425902</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27923,10 +27923,10 @@
         <v>0.01241698632165521</v>
       </c>
       <c r="H528">
-        <v>0.01261476516106152</v>
+        <v>0.01534142864284259</v>
       </c>
       <c r="I528">
-        <v>1.02222116059369</v>
+        <v>1.275557678812619</v>
       </c>
       <c r="J528">
         <v>1.79226591562474</v>
@@ -27938,10 +27938,10 @@
         <v>5.23</v>
       </c>
       <c r="M528">
-        <v>3.78</v>
+        <v>4.47</v>
       </c>
       <c r="N528">
-        <v>5.84</v>
+        <v>7.33</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -27955,43 +27955,43 @@
         <v>1</v>
       </c>
       <c r="B529" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C529">
-        <v>-0.1723011159990033</v>
+        <v>0.3074112445011217</v>
       </c>
       <c r="D529" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E529">
-        <v>0.3074112445011217</v>
+        <v>0.7113230417198011</v>
       </c>
       <c r="F529">
         <v>-1</v>
       </c>
       <c r="G529">
-        <v>0.013592301115999</v>
+        <v>0.01579258875549888</v>
       </c>
       <c r="H529">
-        <v>0.01579258875549888</v>
+        <v>0.0152286769582802</v>
       </c>
       <c r="I529">
-        <v>-0.479712360500125</v>
+        <v>-0.4039117972186794</v>
       </c>
       <c r="J529">
         <v>1.79226591562474</v>
       </c>
       <c r="K529">
-        <v>3.84</v>
+        <v>4.32</v>
       </c>
       <c r="L529">
-        <v>6.71</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M529">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N529">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -28011,10 +28011,10 @@
         <v>-2.042162178706638</v>
       </c>
       <c r="D530" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E530">
-        <v>-1.015055619828202</v>
+        <v>-0.7763752964635096</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28023,10 +28023,10 @@
         <v>0.01250216217870664</v>
       </c>
       <c r="H530">
-        <v>0.0126950556198282</v>
+        <v>0.01543637529646351</v>
       </c>
       <c r="I530">
-        <v>1.027106558878436</v>
+        <v>1.265786882243129</v>
       </c>
       <c r="J530">
         <v>1.813506777732329</v>
@@ -28038,10 +28038,10 @@
         <v>5.23</v>
       </c>
       <c r="M530">
-        <v>3.78</v>
+        <v>4.47</v>
       </c>
       <c r="N530">
-        <v>5.84</v>
+        <v>7.33</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28055,43 +28055,43 @@
         <v>1</v>
       </c>
       <c r="B531" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C531">
-        <v>-0.2538660264921422</v>
+        <v>0.21565072019634</v>
       </c>
       <c r="D531" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E531">
-        <v>0.21565072019634</v>
+        <v>0.6252975501840687</v>
       </c>
       <c r="F531">
         <v>-1</v>
       </c>
       <c r="G531">
-        <v>0.01367386602649214</v>
+        <v>0.01588434927980366</v>
       </c>
       <c r="H531">
-        <v>0.01588434927980366</v>
+        <v>0.01531470244981593</v>
       </c>
       <c r="I531">
-        <v>-0.4695167466884822</v>
+        <v>-0.4096468299877287</v>
       </c>
       <c r="J531">
         <v>1.813506777732329</v>
       </c>
       <c r="K531">
-        <v>3.84</v>
+        <v>4.32</v>
       </c>
       <c r="L531">
-        <v>6.71</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M531">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N531">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28111,7 +28111,7 @@
         <v>-2.134185588757242</v>
       </c>
       <c r="D532" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E532">
         <v>-0.8789550079164261</v>
@@ -28155,43 +28155,43 @@
         <v>1</v>
       </c>
       <c r="B533" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C533">
-        <v>-0.3419881947201517</v>
+        <v>0.116513280939829</v>
       </c>
       <c r="D533" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E533">
-        <v>0.116513280939829</v>
+        <v>0.5323562008810896</v>
       </c>
       <c r="F533">
         <v>-1</v>
       </c>
       <c r="G533">
-        <v>0.01376198819472015</v>
+        <v>0.01598348671906017</v>
       </c>
       <c r="H533">
-        <v>0.01598348671906017</v>
+        <v>0.01540764379911891</v>
       </c>
       <c r="I533">
-        <v>-0.4585014756599808</v>
+        <v>-0.4158429199412605</v>
       </c>
       <c r="J533">
         <v>1.836455259041706</v>
       </c>
       <c r="K533">
-        <v>3.84</v>
+        <v>4.32</v>
       </c>
       <c r="L533">
-        <v>6.71</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M533">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N533">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O533">
         <v>1</v>
@@ -28211,7 +28211,7 @@
         <v>-2.24491864020763</v>
       </c>
       <c r="D534" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E534">
         <v>-1.002390603922223</v>
@@ -28255,43 +28255,43 @@
         <v>1</v>
       </c>
       <c r="B535" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C535">
-        <v>-0.4480268275304997</v>
+        <v>-0.002780180971811319</v>
       </c>
       <c r="D535" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E535">
-        <v>-0.002780180971811319</v>
+        <v>0.4205185803389266</v>
       </c>
       <c r="F535">
         <v>-1</v>
       </c>
       <c r="G535">
-        <v>0.0138680268275305</v>
+        <v>0.01610278018097181</v>
       </c>
       <c r="H535">
-        <v>0.01610278018097181</v>
+        <v>0.01551948141966107</v>
       </c>
       <c r="I535">
-        <v>-0.4452466465586884</v>
+        <v>-0.423298761310738</v>
       </c>
       <c r="J535">
         <v>1.864069486336068</v>
       </c>
       <c r="K535">
-        <v>3.84</v>
+        <v>4.32</v>
       </c>
       <c r="L535">
-        <v>6.71</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M535">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N535">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O535">
         <v>1</v>
@@ -28311,7 +28311,7 @@
         <v>-2.39134798609852</v>
       </c>
       <c r="D536" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E536">
         <v>-1.165617331137254</v>
@@ -28355,43 +28355,43 @@
         <v>1</v>
       </c>
       <c r="B537" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C537">
-        <v>-0.588248445540728</v>
+        <v>-0.1605295012333183</v>
       </c>
       <c r="D537" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E537">
-        <v>-0.1605295012333183</v>
+        <v>0.2726285925937635</v>
       </c>
       <c r="F537">
         <v>-1</v>
       </c>
       <c r="G537">
-        <v>0.01400824844554073</v>
+        <v>0.01626052950123332</v>
       </c>
       <c r="H537">
-        <v>0.01626052950123332</v>
+        <v>0.01566737140740624</v>
       </c>
       <c r="I537">
-        <v>-0.4277189443074096</v>
+        <v>-0.4331580938270818</v>
       </c>
       <c r="J537">
         <v>1.900585532692898</v>
       </c>
       <c r="K537">
-        <v>3.84</v>
+        <v>4.32</v>
       </c>
       <c r="L537">
-        <v>6.71</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M537">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N537">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="O537">
         <v>1</v>
@@ -28411,7 +28411,7 @@
         <v>-2.546512840679558</v>
       </c>
       <c r="D538" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E538">
         <v>-1.338581645346041</v>
@@ -28452,66 +28452,66 @@
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B539" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C539">
-        <v>-2.943692670373876</v>
+        <v>-0.3276896438243622</v>
       </c>
       <c r="D539" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E539">
-        <v>-1.695574148632207</v>
+        <v>0.1159159589146599</v>
       </c>
       <c r="F539">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.01340369267037388</v>
+        <v>0.01642768964382436</v>
       </c>
       <c r="H539">
-        <v>0.01591557414863221</v>
+        <v>0.01582408404108534</v>
       </c>
       <c r="I539">
-        <v>1.248118521741669</v>
+        <v>-0.4436056027390221</v>
       </c>
       <c r="J539">
-        <v>2.038327349220418</v>
+        <v>1.939280010144528</v>
       </c>
       <c r="K539">
-        <v>4.01</v>
+        <v>4.32</v>
       </c>
       <c r="L539">
-        <v>5.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M539">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="N539">
-        <v>7.11</v>
+        <v>7.97</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B540" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C540">
-        <v>-2.466410474021997</v>
+        <v>-2.943692670373876</v>
       </c>
       <c r="D540" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E540">
         <v>-1.695574148632207</v>
@@ -28520,22 +28520,22 @@
         <v>1</v>
       </c>
       <c r="G540">
-        <v>0.013106410474022</v>
+        <v>0.01340369267037388</v>
       </c>
       <c r="H540">
         <v>0.01591557414863221</v>
       </c>
       <c r="I540">
-        <v>0.7708363253897899</v>
+        <v>1.248118521741669</v>
       </c>
       <c r="J540">
         <v>2.038327349220418</v>
       </c>
       <c r="K540">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L540">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M540">
         <v>4.32</v>
@@ -28552,66 +28552,66 @@
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B541" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C541">
-        <v>-3.302184308580614</v>
+        <v>-0.7555741486322063</v>
       </c>
       <c r="D541" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="E541">
-        <v>-1.826234252207514</v>
+        <v>-0.2852257643426936</v>
       </c>
       <c r="F541">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.01376218430858061</v>
+        <v>0.01685557414863221</v>
       </c>
       <c r="H541">
-        <v>0.01570623425220751</v>
+        <v>0.01622522576434269</v>
       </c>
       <c r="I541">
-        <v>1.4759500563731</v>
+        <v>-0.4703483842895126</v>
       </c>
       <c r="J541">
-        <v>2.127726760244542</v>
+        <v>2.038327349220418</v>
       </c>
       <c r="K541">
-        <v>4.01</v>
+        <v>4.32</v>
       </c>
       <c r="L541">
-        <v>5.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M541">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="N541">
-        <v>6.94</v>
+        <v>7.97</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C542">
-        <v>-2.807916224134152</v>
+        <v>-3.302184308580614</v>
       </c>
       <c r="D542" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E542">
         <v>-1.826234252207514</v>
@@ -28620,22 +28620,22 @@
         <v>1</v>
       </c>
       <c r="G542">
-        <v>0.01344791622413415</v>
+        <v>0.01376218430858061</v>
       </c>
       <c r="H542">
         <v>0.01570623425220751</v>
       </c>
       <c r="I542">
-        <v>0.9816819719266379</v>
+        <v>1.4759500563731</v>
       </c>
       <c r="J542">
         <v>2.127726760244542</v>
       </c>
       <c r="K542">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="L542">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="M542">
         <v>4.12</v>
@@ -28652,40 +28652,40 @@
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B543" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C543">
-        <v>-3.440693413369869</v>
+        <v>-2.807916224134152</v>
       </c>
       <c r="D543" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E543">
-        <v>-1.968542858624404</v>
+        <v>-1.826234252207514</v>
       </c>
       <c r="F543">
         <v>1</v>
       </c>
       <c r="G543">
-        <v>0.01390069341336987</v>
+        <v>0.01344791622413415</v>
       </c>
       <c r="H543">
-        <v>0.0158485428586244</v>
+        <v>0.01570623425220751</v>
       </c>
       <c r="I543">
-        <v>1.472150554745466</v>
+        <v>0.9816819719266379</v>
       </c>
       <c r="J543">
-        <v>2.162267684132137</v>
+        <v>2.127726760244542</v>
       </c>
       <c r="K543">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="L543">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="M543">
         <v>4.12</v>
@@ -28697,57 +28697,57 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B544" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C544">
-        <v>-2.939862553384764</v>
+        <v>-1.141779604256424</v>
       </c>
       <c r="D544" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="E544">
-        <v>-1.968542858624404</v>
+        <v>-0.6472933789903967</v>
       </c>
       <c r="F544">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.01357986255338476</v>
+        <v>0.01724177960425642</v>
       </c>
       <c r="H544">
-        <v>0.0158485428586244</v>
+        <v>0.01658729337899039</v>
       </c>
       <c r="I544">
-        <v>0.9713196947603597</v>
+        <v>-0.4944862252660274</v>
       </c>
       <c r="J544">
-        <v>2.162267684132137</v>
+        <v>2.127726760244542</v>
       </c>
       <c r="K544">
-        <v>3.82</v>
+        <v>4.32</v>
       </c>
       <c r="L544">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M544">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="N544">
-        <v>6.94</v>
+        <v>7.97</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28758,28 +28758,28 @@
         <v>69</v>
       </c>
       <c r="C545">
-        <v>-3.668901415448289</v>
+        <v>-3.440693413369869</v>
       </c>
       <c r="D545" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E545">
-        <v>-2.203010930585275</v>
+        <v>-1.968542858624404</v>
       </c>
       <c r="F545">
         <v>1</v>
       </c>
       <c r="G545">
-        <v>0.01412890141544829</v>
+        <v>0.01390069341336987</v>
       </c>
       <c r="H545">
-        <v>0.01608301093058527</v>
+        <v>0.0158485428586244</v>
       </c>
       <c r="I545">
-        <v>1.465890484863015</v>
+        <v>1.472150554745466</v>
       </c>
       <c r="J545">
-        <v>2.219177410336232</v>
+        <v>2.162267684132137</v>
       </c>
       <c r="K545">
         <v>4.01</v>
@@ -28797,7 +28797,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28805,31 +28805,31 @@
         <v>1</v>
       </c>
       <c r="B546" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C546">
-        <v>-3.157257707484405</v>
+        <v>-2.939862553384764</v>
       </c>
       <c r="D546" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E546">
-        <v>-2.203010930585275</v>
+        <v>-1.968542858624404</v>
       </c>
       <c r="F546">
         <v>1</v>
       </c>
       <c r="G546">
-        <v>0.01379725770748441</v>
+        <v>0.01357986255338476</v>
       </c>
       <c r="H546">
-        <v>0.01608301093058527</v>
+        <v>0.0158485428586244</v>
       </c>
       <c r="I546">
-        <v>0.9542467768991303</v>
+        <v>0.9713196947603597</v>
       </c>
       <c r="J546">
-        <v>2.219177410336232</v>
+        <v>2.162267684132137</v>
       </c>
       <c r="K546">
         <v>3.82</v>
@@ -28847,7 +28847,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28858,28 +28858,28 @@
         <v>69</v>
       </c>
       <c r="C547">
-        <v>-3.954888865249114</v>
+        <v>-3.668901415448289</v>
       </c>
       <c r="D547" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E547">
-        <v>-2.496843422649964</v>
+        <v>-2.203010930585275</v>
       </c>
       <c r="F547">
         <v>1</v>
       </c>
       <c r="G547">
-        <v>0.01441488886524911</v>
+        <v>0.01412890141544829</v>
       </c>
       <c r="H547">
-        <v>0.01637684342264997</v>
+        <v>0.01608301093058527</v>
       </c>
       <c r="I547">
-        <v>1.45804544259915</v>
+        <v>1.465890484863015</v>
       </c>
       <c r="J547">
-        <v>2.29049597637135</v>
+        <v>2.219177410336232</v>
       </c>
       <c r="K547">
         <v>4.01</v>
@@ -28897,7 +28897,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28905,31 +28905,31 @@
         <v>1</v>
       </c>
       <c r="B548" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C548">
-        <v>-3.429694629738558</v>
+        <v>-3.157257707484405</v>
       </c>
       <c r="D548" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E548">
-        <v>-2.496843422649964</v>
+        <v>-2.203010930585275</v>
       </c>
       <c r="F548">
         <v>1</v>
       </c>
       <c r="G548">
-        <v>0.01406969462973856</v>
+        <v>0.01379725770748441</v>
       </c>
       <c r="H548">
-        <v>0.01637684342264997</v>
+        <v>0.01608301093058527</v>
       </c>
       <c r="I548">
-        <v>0.9328512070885937</v>
+        <v>0.9542467768991303</v>
       </c>
       <c r="J548">
-        <v>2.29049597637135</v>
+        <v>2.219177410336232</v>
       </c>
       <c r="K548">
         <v>3.82</v>
@@ -28947,7 +28947,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28958,28 +28958,28 @@
         <v>69</v>
       </c>
       <c r="C549">
-        <v>-4.162550774568617</v>
+        <v>-3.954888865249114</v>
       </c>
       <c r="D549" t="s">
         <v>167</v>
       </c>
       <c r="E549">
-        <v>-2.558591035361685</v>
+        <v>-2.354554146903121</v>
       </c>
       <c r="F549">
         <v>1</v>
       </c>
       <c r="G549">
-        <v>0.01462255077456862</v>
+        <v>0.01441488886524911</v>
       </c>
       <c r="H549">
-        <v>0.01589859103536169</v>
+        <v>0.01569455414690312</v>
       </c>
       <c r="I549">
-        <v>1.603959739206932</v>
+        <v>1.600334718345993</v>
       </c>
       <c r="J549">
-        <v>2.342281988670478</v>
+        <v>2.29049597637135</v>
       </c>
       <c r="K549">
         <v>4.01</v>
@@ -28997,7 +28997,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29005,31 +29005,31 @@
         <v>1</v>
       </c>
       <c r="B550" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C550">
-        <v>-3.627517196721227</v>
+        <v>-3.429694629738558</v>
       </c>
       <c r="D550" t="s">
         <v>167</v>
       </c>
       <c r="E550">
-        <v>-2.558591035361685</v>
+        <v>-2.354554146903121</v>
       </c>
       <c r="F550">
         <v>1</v>
       </c>
       <c r="G550">
-        <v>0.01426751719672123</v>
+        <v>0.01406969462973856</v>
       </c>
       <c r="H550">
-        <v>0.01589859103536169</v>
+        <v>0.01569455414690312</v>
       </c>
       <c r="I550">
-        <v>1.068926161359542</v>
+        <v>1.075140482835437</v>
       </c>
       <c r="J550">
-        <v>2.342281988670478</v>
+        <v>2.29049597637135</v>
       </c>
       <c r="K550">
         <v>3.82</v>
@@ -29047,7 +29047,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29058,28 +29058,28 @@
         <v>69</v>
       </c>
       <c r="C551">
-        <v>-4.341021841271511</v>
+        <v>-4.162550774568617</v>
       </c>
       <c r="D551" t="s">
         <v>167</v>
       </c>
       <c r="E551">
-        <v>-2.733946647034852</v>
+        <v>-2.558591035361685</v>
       </c>
       <c r="F551">
         <v>1</v>
       </c>
       <c r="G551">
-        <v>0.01480102184127151</v>
+        <v>0.01462255077456862</v>
       </c>
       <c r="H551">
-        <v>0.01607394664703485</v>
+        <v>0.01589859103536169</v>
       </c>
       <c r="I551">
-        <v>1.607075194236659</v>
+        <v>1.603959739206932</v>
       </c>
       <c r="J551">
-        <v>2.38678848909514</v>
+        <v>2.342281988670478</v>
       </c>
       <c r="K551">
         <v>4.01</v>
@@ -29097,7 +29097,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29105,31 +29105,31 @@
         <v>1</v>
       </c>
       <c r="B552" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C552">
-        <v>-3.797532028343435</v>
+        <v>-3.627517196721227</v>
       </c>
       <c r="D552" t="s">
         <v>167</v>
       </c>
       <c r="E552">
-        <v>-2.733946647034852</v>
+        <v>-2.558591035361685</v>
       </c>
       <c r="F552">
         <v>1</v>
       </c>
       <c r="G552">
-        <v>0.01443753202834343</v>
+        <v>0.01426751719672123</v>
       </c>
       <c r="H552">
-        <v>0.01607394664703485</v>
+        <v>0.01589859103536169</v>
       </c>
       <c r="I552">
-        <v>1.063585381308583</v>
+        <v>1.068926161359542</v>
       </c>
       <c r="J552">
-        <v>2.38678848909514</v>
+        <v>2.342281988670478</v>
       </c>
       <c r="K552">
         <v>3.82</v>
@@ -29147,7 +29147,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29158,28 +29158,28 @@
         <v>69</v>
       </c>
       <c r="C553">
-        <v>-4.38270256915019</v>
+        <v>-4.341021841271511</v>
       </c>
       <c r="D553" t="s">
         <v>167</v>
       </c>
       <c r="E553">
-        <v>-2.774899781160038</v>
+        <v>-2.733946647034852</v>
       </c>
       <c r="F553">
         <v>1</v>
       </c>
       <c r="G553">
-        <v>0.01484270256915019</v>
+        <v>0.01480102184127151</v>
       </c>
       <c r="H553">
-        <v>0.01611489978116004</v>
+        <v>0.01607394664703485</v>
       </c>
       <c r="I553">
-        <v>1.607802787990153</v>
+        <v>1.607075194236659</v>
       </c>
       <c r="J553">
-        <v>2.397182685573614</v>
+        <v>2.38678848909514</v>
       </c>
       <c r="K553">
         <v>4.01</v>
@@ -29197,7 +29197,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29205,31 +29205,31 @@
         <v>1</v>
       </c>
       <c r="B554" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C554">
-        <v>-3.837237858891204</v>
+        <v>-3.797532028343435</v>
       </c>
       <c r="D554" t="s">
         <v>167</v>
       </c>
       <c r="E554">
-        <v>-2.774899781160038</v>
+        <v>-2.733946647034852</v>
       </c>
       <c r="F554">
         <v>1</v>
       </c>
       <c r="G554">
-        <v>0.01447723785889121</v>
+        <v>0.01443753202834343</v>
       </c>
       <c r="H554">
-        <v>0.01611489978116004</v>
+        <v>0.01607394664703485</v>
       </c>
       <c r="I554">
-        <v>1.062338077731166</v>
+        <v>1.063585381308583</v>
       </c>
       <c r="J554">
-        <v>2.397182685573614</v>
+        <v>2.38678848909514</v>
       </c>
       <c r="K554">
         <v>3.82</v>
@@ -29247,7 +29247,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29258,28 +29258,28 @@
         <v>69</v>
       </c>
       <c r="C555">
-        <v>-4.411855003341485</v>
+        <v>-4.38270256915019</v>
       </c>
       <c r="D555" t="s">
         <v>167</v>
       </c>
       <c r="E555">
-        <v>-2.803543319991386</v>
+        <v>-2.774899781160038</v>
       </c>
       <c r="F555">
         <v>1</v>
       </c>
       <c r="G555">
-        <v>0.01487185500334148</v>
+        <v>0.01484270256915019</v>
       </c>
       <c r="H555">
-        <v>0.01614354331999139</v>
+        <v>0.01611489978116004</v>
       </c>
       <c r="I555">
-        <v>1.608311683350099</v>
+        <v>1.607802787990153</v>
       </c>
       <c r="J555">
-        <v>2.404452619287154</v>
+        <v>2.397182685573614</v>
       </c>
       <c r="K555">
         <v>4.01</v>
@@ -29297,7 +29297,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29305,31 +29305,31 @@
         <v>1</v>
       </c>
       <c r="B556" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C556">
-        <v>-3.865009005676926</v>
+        <v>-3.837237858891204</v>
       </c>
       <c r="D556" t="s">
         <v>167</v>
       </c>
       <c r="E556">
-        <v>-2.803543319991386</v>
+        <v>-2.774899781160038</v>
       </c>
       <c r="F556">
         <v>1</v>
       </c>
       <c r="G556">
-        <v>0.01450500900567693</v>
+        <v>0.01447723785889121</v>
       </c>
       <c r="H556">
-        <v>0.01614354331999139</v>
+        <v>0.01611489978116004</v>
       </c>
       <c r="I556">
-        <v>1.06146568568554</v>
+        <v>1.062338077731166</v>
       </c>
       <c r="J556">
-        <v>2.404452619287154</v>
+        <v>2.397182685573614</v>
       </c>
       <c r="K556">
         <v>3.82</v>
@@ -29347,7 +29347,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29358,28 +29358,28 @@
         <v>69</v>
       </c>
       <c r="C557">
-        <v>-4.339272485484365</v>
+        <v>-4.411855003341485</v>
       </c>
       <c r="D557" t="s">
         <v>167</v>
       </c>
       <c r="E557">
-        <v>-2.732227828630524</v>
+        <v>-2.803543319991386</v>
       </c>
       <c r="F557">
         <v>1</v>
       </c>
       <c r="G557">
-        <v>0.01479927248548437</v>
+        <v>0.01487185500334148</v>
       </c>
       <c r="H557">
-        <v>0.01607222782863052</v>
+        <v>0.01614354331999139</v>
       </c>
       <c r="I557">
-        <v>1.607044656853841</v>
+        <v>1.608311683350099</v>
       </c>
       <c r="J557">
-        <v>2.386352240769169</v>
+        <v>2.404452619287154</v>
       </c>
       <c r="K557">
         <v>4.01</v>
@@ -29397,7 +29397,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29405,31 +29405,31 @@
         <v>1</v>
       </c>
       <c r="B558" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C558">
-        <v>-3.795865559738223</v>
+        <v>-3.865009005676926</v>
       </c>
       <c r="D558" t="s">
         <v>167</v>
       </c>
       <c r="E558">
-        <v>-2.732227828630524</v>
+        <v>-2.803543319991386</v>
       </c>
       <c r="F558">
         <v>1</v>
       </c>
       <c r="G558">
-        <v>0.01443586555973822</v>
+        <v>0.01450500900567693</v>
       </c>
       <c r="H558">
-        <v>0.01607222782863052</v>
+        <v>0.01614354331999139</v>
       </c>
       <c r="I558">
-        <v>1.063637731107699</v>
+        <v>1.06146568568554</v>
       </c>
       <c r="J558">
-        <v>2.386352240769169</v>
+        <v>2.404452619287154</v>
       </c>
       <c r="K558">
         <v>3.82</v>
@@ -29447,7 +29447,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29458,28 +29458,28 @@
         <v>69</v>
       </c>
       <c r="C559">
-        <v>-4.278315541383607</v>
+        <v>-4.339272485484365</v>
       </c>
       <c r="D559" t="s">
         <v>167</v>
       </c>
       <c r="E559">
-        <v>-2.672334970835765</v>
+        <v>-2.732227828630524</v>
       </c>
       <c r="F559">
         <v>1</v>
       </c>
       <c r="G559">
-        <v>0.01473831554138361</v>
+        <v>0.01479927248548437</v>
       </c>
       <c r="H559">
-        <v>0.01601233497083577</v>
+        <v>0.01607222782863052</v>
       </c>
       <c r="I559">
-        <v>1.605980570547842</v>
+        <v>1.607044656853841</v>
       </c>
       <c r="J559">
-        <v>2.371151007826336</v>
+        <v>2.386352240769169</v>
       </c>
       <c r="K559">
         <v>4.01</v>
@@ -29497,7 +29497,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29505,31 +29505,31 @@
         <v>1</v>
       </c>
       <c r="B560" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C560">
-        <v>-3.737796849896604</v>
+        <v>-3.795865559738223</v>
       </c>
       <c r="D560" t="s">
         <v>167</v>
       </c>
       <c r="E560">
-        <v>-2.672334970835765</v>
+        <v>-2.732227828630524</v>
       </c>
       <c r="F560">
         <v>1</v>
       </c>
       <c r="G560">
-        <v>0.0143777968498966</v>
+        <v>0.01443586555973822</v>
       </c>
       <c r="H560">
-        <v>0.01601233497083577</v>
+        <v>0.01607222782863052</v>
       </c>
       <c r="I560">
-        <v>1.065461879060839</v>
+        <v>1.063637731107699</v>
       </c>
       <c r="J560">
-        <v>2.371151007826336</v>
+        <v>2.386352240769169</v>
       </c>
       <c r="K560">
         <v>3.82</v>
@@ -29547,7 +29547,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29558,28 +29558,28 @@
         <v>69</v>
       </c>
       <c r="C561">
-        <v>-4.215673134172834</v>
+        <v>-4.278315541383607</v>
       </c>
       <c r="D561" t="s">
         <v>167</v>
       </c>
       <c r="E561">
-        <v>-2.610786071980291</v>
+        <v>-2.672334970835765</v>
       </c>
       <c r="F561">
         <v>1</v>
       </c>
       <c r="G561">
-        <v>0.01467567313417283</v>
+        <v>0.01473831554138361</v>
       </c>
       <c r="H561">
-        <v>0.01595078607198029</v>
+        <v>0.01601233497083577</v>
       </c>
       <c r="I561">
-        <v>1.604887062192542</v>
+        <v>1.605980570547842</v>
       </c>
       <c r="J561">
-        <v>2.355529459893475</v>
+        <v>2.371151007826336</v>
       </c>
       <c r="K561">
         <v>4.01</v>
@@ -29597,7 +29597,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29605,31 +29605,31 @@
         <v>1</v>
       </c>
       <c r="B562" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C562">
-        <v>-3.678122536793074</v>
+        <v>-3.737796849896604</v>
       </c>
       <c r="D562" t="s">
         <v>167</v>
       </c>
       <c r="E562">
-        <v>-2.610786071980291</v>
+        <v>-2.672334970835765</v>
       </c>
       <c r="F562">
         <v>1</v>
       </c>
       <c r="G562">
-        <v>0.01431812253679307</v>
+        <v>0.0143777968498966</v>
       </c>
       <c r="H562">
-        <v>0.01595078607198029</v>
+        <v>0.01601233497083577</v>
       </c>
       <c r="I562">
-        <v>1.067336464812783</v>
+        <v>1.065461879060839</v>
       </c>
       <c r="J562">
-        <v>2.355529459893475</v>
+        <v>2.371151007826336</v>
       </c>
       <c r="K562">
         <v>3.82</v>
@@ -29647,7 +29647,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29658,28 +29658,28 @@
         <v>69</v>
       </c>
       <c r="C563">
-        <v>-4.189835924124937</v>
+        <v>-4.215673134172834</v>
       </c>
       <c r="D563" t="s">
         <v>167</v>
       </c>
       <c r="E563">
-        <v>-2.585399885549192</v>
+        <v>-2.610786071980291</v>
       </c>
       <c r="F563">
         <v>1</v>
       </c>
       <c r="G563">
-        <v>0.01464983592412494</v>
+        <v>0.01467567313417283</v>
       </c>
       <c r="H563">
-        <v>0.01592539988554919</v>
+        <v>0.01595078607198029</v>
       </c>
       <c r="I563">
-        <v>1.604436038575745</v>
+        <v>1.604887062192542</v>
       </c>
       <c r="J563">
-        <v>2.349086265367815</v>
+        <v>2.355529459893475</v>
       </c>
       <c r="K563">
         <v>4.01</v>
@@ -29697,7 +29697,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29705,31 +29705,31 @@
         <v>1</v>
       </c>
       <c r="B564" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C564">
-        <v>-3.653509533705053</v>
+        <v>-3.678122536793074</v>
       </c>
       <c r="D564" t="s">
         <v>167</v>
       </c>
       <c r="E564">
-        <v>-2.585399885549192</v>
+        <v>-2.610786071980291</v>
       </c>
       <c r="F564">
         <v>1</v>
       </c>
       <c r="G564">
-        <v>0.01429350953370505</v>
+        <v>0.01431812253679307</v>
       </c>
       <c r="H564">
-        <v>0.01592539988554919</v>
+        <v>0.01595078607198029</v>
       </c>
       <c r="I564">
-        <v>1.068109648155861</v>
+        <v>1.067336464812783</v>
       </c>
       <c r="J564">
-        <v>2.349086265367815</v>
+        <v>2.355529459893475</v>
       </c>
       <c r="K564">
         <v>3.82</v>
@@ -29747,7 +29747,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29758,28 +29758,28 @@
         <v>69</v>
       </c>
       <c r="C565">
-        <v>-4.089470803698397</v>
+        <v>-4.189835924124937</v>
       </c>
       <c r="D565" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="E565">
-        <v>-2.63511713497192</v>
+        <v>-2.585399885549192</v>
       </c>
       <c r="F565">
         <v>1</v>
       </c>
       <c r="G565">
-        <v>0.0145494708036984</v>
+        <v>0.01464983592412494</v>
       </c>
       <c r="H565">
-        <v>0.01651511713497192</v>
+        <v>0.01592539988554919</v>
       </c>
       <c r="I565">
-        <v>1.454353668726477</v>
+        <v>1.604436038575745</v>
       </c>
       <c r="J565">
-        <v>2.324057557032019</v>
+        <v>2.349086265367815</v>
       </c>
       <c r="K565">
         <v>4.01</v>
@@ -29788,16 +29788,16 @@
         <v>5.23</v>
       </c>
       <c r="M565">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N565">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O565">
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29805,31 +29805,31 @@
         <v>1</v>
       </c>
       <c r="B566" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C566">
-        <v>-3.557899867862314</v>
+        <v>-3.653509533705053</v>
       </c>
       <c r="D566" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="E566">
-        <v>-2.63511713497192</v>
+        <v>-2.585399885549192</v>
       </c>
       <c r="F566">
         <v>1</v>
       </c>
       <c r="G566">
-        <v>0.01419789986786231</v>
+        <v>0.01429350953370505</v>
       </c>
       <c r="H566">
-        <v>0.01651511713497192</v>
+        <v>0.01592539988554919</v>
       </c>
       <c r="I566">
-        <v>0.9227827328903944</v>
+        <v>1.068109648155861</v>
       </c>
       <c r="J566">
-        <v>2.324057557032019</v>
+        <v>2.349086265367815</v>
       </c>
       <c r="K566">
         <v>3.82</v>
@@ -29838,16 +29838,16 @@
         <v>5.32</v>
       </c>
       <c r="M566">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="N566">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="O566">
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29858,28 +29858,28 @@
         <v>69</v>
       </c>
       <c r="C567">
-        <v>-4.005320296309154</v>
+        <v>-4.089470803698397</v>
       </c>
       <c r="D567" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E567">
-        <v>-2.548658259549556</v>
+        <v>-2.63511713497192</v>
       </c>
       <c r="F567">
         <v>1</v>
       </c>
       <c r="G567">
-        <v>0.01446532029630916</v>
+        <v>0.0145494708036984</v>
       </c>
       <c r="H567">
-        <v>0.01642865825954956</v>
+        <v>0.01651511713497192</v>
       </c>
       <c r="I567">
-        <v>1.456662036759599</v>
+        <v>1.454353668726477</v>
       </c>
       <c r="J567">
-        <v>2.303072393094552</v>
+        <v>2.324057557032019</v>
       </c>
       <c r="K567">
         <v>4.01</v>
@@ -29897,7 +29897,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29908,28 +29908,28 @@
         <v>69</v>
       </c>
       <c r="C568">
-        <v>-3.880021728113258</v>
+        <v>-4.005320296309154</v>
       </c>
       <c r="D568" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E568">
-        <v>-2.419922573522849</v>
+        <v>-2.548658259549556</v>
       </c>
       <c r="F568">
         <v>1</v>
       </c>
       <c r="G568">
-        <v>0.01434002172811326</v>
+        <v>0.01446532029630916</v>
       </c>
       <c r="H568">
-        <v>0.01629992257352285</v>
+        <v>0.01642865825954956</v>
       </c>
       <c r="I568">
-        <v>1.460099154590409</v>
+        <v>1.456662036759599</v>
       </c>
       <c r="J568">
-        <v>2.271825867359915</v>
+        <v>2.303072393094552</v>
       </c>
       <c r="K568">
         <v>4.01</v>
@@ -29947,7 +29947,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29958,28 +29958,28 @@
         <v>69</v>
       </c>
       <c r="C569">
-        <v>-3.765867342432312</v>
+        <v>-3.880021728113258</v>
       </c>
       <c r="D569" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="E569">
-        <v>-2.302636770778338</v>
+        <v>-2.419922573522849</v>
       </c>
       <c r="F569">
         <v>1</v>
       </c>
       <c r="G569">
-        <v>0.01422586734243231</v>
+        <v>0.01434002172811326</v>
       </c>
       <c r="H569">
-        <v>0.01618263677077834</v>
+        <v>0.01629992257352285</v>
       </c>
       <c r="I569">
-        <v>1.463230571653974</v>
+        <v>1.460099154590409</v>
       </c>
       <c r="J569">
-        <v>2.243358439509305</v>
+        <v>2.271825867359915</v>
       </c>
       <c r="K569">
         <v>4.01</v>
@@ -29997,7 +29997,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30008,28 +30008,28 @@
         <v>69</v>
       </c>
       <c r="C570">
-        <v>-3.200435821279882</v>
+        <v>-3.765867342432312</v>
       </c>
       <c r="D570" t="s">
         <v>166</v>
       </c>
       <c r="E570">
-        <v>-1.972165273797779</v>
+        <v>-2.302636770778338</v>
       </c>
       <c r="F570">
         <v>1</v>
       </c>
       <c r="G570">
-        <v>0.01366043582127988</v>
+        <v>0.01422586734243231</v>
       </c>
       <c r="H570">
-        <v>0.01619216527379778</v>
+        <v>0.01618263677077834</v>
       </c>
       <c r="I570">
-        <v>1.228270547482103</v>
+        <v>1.463230571653974</v>
       </c>
       <c r="J570">
-        <v>2.102353072638375</v>
+        <v>2.243358439509305</v>
       </c>
       <c r="K570">
         <v>4.01</v>
@@ -30038,16 +30038,16 @@
         <v>5.23</v>
       </c>
       <c r="M570">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="N570">
-        <v>7.11</v>
+        <v>6.94</v>
       </c>
       <c r="O570">
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30058,28 +30058,28 @@
         <v>69</v>
       </c>
       <c r="C571">
-        <v>-2.562371230751202</v>
+        <v>-3.200435821279882</v>
       </c>
       <c r="D571" t="s">
         <v>165</v>
       </c>
       <c r="E571">
-        <v>-1.356259202358572</v>
+        <v>-1.972165273797779</v>
       </c>
       <c r="F571">
         <v>1</v>
       </c>
       <c r="G571">
-        <v>0.0130223712307512</v>
+        <v>0.01366043582127988</v>
       </c>
       <c r="H571">
-        <v>0.01601625920235857</v>
+        <v>0.01619216527379778</v>
       </c>
       <c r="I571">
-        <v>1.20611202839263</v>
+        <v>1.228270547482103</v>
       </c>
       <c r="J571">
-        <v>1.943234720885587</v>
+        <v>2.102353072638375</v>
       </c>
       <c r="K571">
         <v>4.01</v>
@@ -30088,15 +30088,165 @@
         <v>5.23</v>
       </c>
       <c r="M571">
+        <v>4.32</v>
+      </c>
+      <c r="N571">
+        <v>7.11</v>
+      </c>
+      <c r="O571">
+        <v>1</v>
+      </c>
+      <c r="P571" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="572" spans="1:16">
+      <c r="A572" s="1">
+        <v>1</v>
+      </c>
+      <c r="B572" t="s">
+        <v>71</v>
+      </c>
+      <c r="C572">
+        <v>-1.032165273797778</v>
+      </c>
+      <c r="D572" t="s">
+        <v>163</v>
+      </c>
+      <c r="E572">
+        <v>-0.5445299441854177</v>
+      </c>
+      <c r="F572">
+        <v>-1</v>
+      </c>
+      <c r="G572">
+        <v>0.01713216527379778</v>
+      </c>
+      <c r="H572">
+        <v>0.01648452994418542</v>
+      </c>
+      <c r="I572">
+        <v>-0.4876353296123606</v>
+      </c>
+      <c r="J572">
+        <v>2.102353072638375</v>
+      </c>
+      <c r="K572">
+        <v>4.32</v>
+      </c>
+      <c r="L572">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M572">
+        <v>4.05</v>
+      </c>
+      <c r="N572">
+        <v>7.97</v>
+      </c>
+      <c r="O572">
+        <v>1</v>
+      </c>
+      <c r="P572" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="573" spans="1:16">
+      <c r="A573" s="1">
+        <v>0</v>
+      </c>
+      <c r="B573" t="s">
+        <v>69</v>
+      </c>
+      <c r="C573">
+        <v>-2.562371230751202</v>
+      </c>
+      <c r="D573" t="s">
+        <v>164</v>
+      </c>
+      <c r="E573">
+        <v>-1.356259202358572</v>
+      </c>
+      <c r="F573">
+        <v>1</v>
+      </c>
+      <c r="G573">
+        <v>0.0130223712307512</v>
+      </c>
+      <c r="H573">
+        <v>0.01601625920235857</v>
+      </c>
+      <c r="I573">
+        <v>1.20611202839263</v>
+      </c>
+      <c r="J573">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K573">
+        <v>4.01</v>
+      </c>
+      <c r="L573">
+        <v>5.23</v>
+      </c>
+      <c r="M573">
         <v>4.47</v>
       </c>
-      <c r="N571">
+      <c r="N573">
         <v>7.33</v>
       </c>
-      <c r="O571">
-        <v>1</v>
-      </c>
-      <c r="P571" t="s">
+      <c r="O573">
+        <v>1</v>
+      </c>
+      <c r="P573" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="574" spans="1:16">
+      <c r="A574" s="1">
+        <v>1</v>
+      </c>
+      <c r="B574" t="s">
+        <v>71</v>
+      </c>
+      <c r="C574">
+        <v>-0.3447739942257346</v>
+      </c>
+      <c r="D574" t="s">
+        <v>163</v>
+      </c>
+      <c r="E574">
+        <v>0.09989938041337432</v>
+      </c>
+      <c r="F574">
+        <v>-1</v>
+      </c>
+      <c r="G574">
+        <v>0.01644477399422574</v>
+      </c>
+      <c r="H574">
+        <v>0.01584010061958662</v>
+      </c>
+      <c r="I574">
+        <v>-0.4446733746391089</v>
+      </c>
+      <c r="J574">
+        <v>1.943234720885587</v>
+      </c>
+      <c r="K574">
+        <v>4.32</v>
+      </c>
+      <c r="L574">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M574">
+        <v>4.05</v>
+      </c>
+      <c r="N574">
+        <v>7.97</v>
+      </c>
+      <c r="O574">
+        <v>1</v>
+      </c>
+      <c r="P574" t="s">
         <v>392</v>
       </c>
     </row>

--- a/s60_signal/position-00902-600011.xlsx
+++ b/s60_signal/position-00902-600011.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="393">
   <si>
     <t>trade_time</t>
   </si>
@@ -223,21 +223,21 @@
     <t>2020-11-26</t>
   </si>
   <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
     <t>2021-08-23</t>
   </si>
   <si>
-    <t>2021-08-26</t>
-  </si>
-  <si>
-    <t>2021-09-23</t>
-  </si>
-  <si>
     <t>2021-09-27</t>
   </si>
   <si>
     <t>2021-08-30</t>
   </si>
   <si>
+    <t>2021-09-29</t>
+  </si>
+  <si>
     <t>2017-06-30</t>
   </si>
   <si>
@@ -505,10 +505,7 @@
     <t>2021-01-05</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-09-29</t>
+    <t>2021-09-30</t>
   </si>
   <si>
     <t>2021-09-06</t>
@@ -1553,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P591"/>
+  <dimension ref="A1:P593"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1650,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1700,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1750,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1800,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1850,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1900,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1950,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2000,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2050,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2100,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2150,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2200,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2250,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2300,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2350,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2400,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2450,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2500,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2550,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2600,7 +2597,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2650,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2700,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2750,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2800,7 +2797,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2850,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2900,7 +2897,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2950,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3000,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3050,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3100,7 +3097,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3150,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3200,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3250,7 +3247,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3300,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3350,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3400,7 +3397,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3450,7 +3447,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3500,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3550,7 +3547,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3600,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3650,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3700,7 +3697,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3750,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3800,7 +3797,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3850,7 +3847,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3900,7 +3897,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3950,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4000,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4050,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4100,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4150,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4200,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4250,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4300,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4350,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4400,7 +4397,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4450,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4500,7 +4497,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4550,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4600,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4650,7 +4647,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4700,7 +4697,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4750,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4800,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4850,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4900,7 +4897,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4950,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5000,7 +4997,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5050,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5100,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5150,7 +5147,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5200,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5250,7 +5247,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5300,7 +5297,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5350,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5400,7 +5397,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5450,7 +5447,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5500,7 +5497,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5550,7 +5547,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5600,7 +5597,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5650,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5700,7 +5697,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5750,7 +5747,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5800,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5850,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5900,7 +5897,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5950,7 +5947,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6000,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6050,7 +6047,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6100,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6150,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6200,7 +6197,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6250,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6300,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6350,7 +6347,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6400,7 +6397,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6450,7 +6447,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6500,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6550,7 +6547,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6600,7 +6597,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6650,7 +6647,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6700,7 +6697,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6750,7 +6747,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6800,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6850,7 +6847,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6900,7 +6897,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6950,7 +6947,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7000,7 +6997,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7050,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7100,7 +7097,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7150,7 +7147,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7200,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7250,7 +7247,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7300,7 +7297,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7350,7 +7347,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7400,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7450,7 +7447,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7500,7 +7497,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7550,7 +7547,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7600,7 +7597,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7650,7 +7647,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7700,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7750,7 +7747,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7800,7 +7797,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7850,7 +7847,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7900,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7950,7 +7947,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8000,7 +7997,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8050,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8100,7 +8097,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8150,7 +8147,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8200,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8250,7 +8247,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8300,7 +8297,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8350,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8400,7 +8397,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8450,7 +8447,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8500,7 +8497,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8550,7 +8547,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8650,7 +8647,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8700,7 +8697,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8750,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8800,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8850,7 +8847,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8900,7 +8897,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8950,7 +8947,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9000,7 +8997,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9050,7 +9047,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9100,7 +9097,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9150,7 +9147,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9200,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9250,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9300,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9350,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9400,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9450,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9500,7 +9497,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9550,7 +9547,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9600,7 +9597,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9700,7 +9697,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9750,7 +9747,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9800,7 +9797,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9950,7 +9947,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10000,7 +9997,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10050,7 +10047,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10100,7 +10097,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10150,7 +10147,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10200,7 +10197,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10250,7 +10247,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10300,7 +10297,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10400,7 +10397,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10450,7 +10447,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10600,7 +10597,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10650,7 +10647,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10700,7 +10697,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10750,7 +10747,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11250,7 +11247,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11300,7 +11297,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11350,7 +11347,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11400,7 +11397,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11450,7 +11447,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11500,7 +11497,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11550,7 +11547,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11600,7 +11597,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11650,7 +11647,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11700,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11750,7 +11747,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11800,7 +11797,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11850,7 +11847,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11900,7 +11897,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11950,7 +11947,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12750,7 +12747,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12800,7 +12797,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12850,7 +12847,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12900,7 +12897,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12950,7 +12947,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13000,7 +12997,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13050,7 +13047,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13100,7 +13097,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13150,7 +13147,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13200,7 +13197,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13250,7 +13247,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13300,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13350,7 +13347,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13400,7 +13397,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13450,7 +13447,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13500,7 +13497,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13550,7 +13547,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13600,7 +13597,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13650,7 +13647,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13700,7 +13697,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13850,7 +13847,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13900,7 +13897,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13950,7 +13947,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14050,7 +14047,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14200,7 +14197,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14250,7 +14247,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14300,7 +14297,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14350,7 +14347,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14400,7 +14397,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14450,7 +14447,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14500,7 +14497,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14600,7 +14597,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14650,7 +14647,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14700,7 +14697,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14750,7 +14747,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14800,7 +14797,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14850,7 +14847,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14900,7 +14897,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14950,7 +14947,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15000,7 +14997,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15050,7 +15047,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15100,7 +15097,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15150,7 +15147,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15200,7 +15197,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15250,7 +15247,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15300,7 +15297,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15350,7 +15347,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15400,7 +15397,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15450,7 +15447,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15500,7 +15497,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15550,7 +15547,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15600,7 +15597,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15650,7 +15647,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15700,7 +15697,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15750,7 +15747,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15800,7 +15797,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15850,7 +15847,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15900,7 +15897,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15950,7 +15947,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16000,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16050,7 +16047,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16100,7 +16097,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16150,7 +16147,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16200,7 +16197,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16250,7 +16247,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16300,7 +16297,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16350,7 +16347,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16400,7 +16397,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16450,7 +16447,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16500,7 +16497,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16550,7 +16547,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16600,7 +16597,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16650,7 +16647,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16700,7 +16697,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16750,7 +16747,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16800,7 +16797,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16850,7 +16847,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16900,7 +16897,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16950,7 +16947,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17150,7 +17147,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17200,7 +17197,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17250,7 +17247,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17300,7 +17297,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17350,7 +17347,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17400,7 +17397,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17450,7 +17447,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17500,7 +17497,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17550,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17600,7 +17597,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17650,7 +17647,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17700,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17750,7 +17747,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17800,7 +17797,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17850,7 +17847,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17900,7 +17897,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17950,7 +17947,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18000,7 +17997,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18050,7 +18047,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18100,7 +18097,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18150,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18200,7 +18197,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18250,7 +18247,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18300,7 +18297,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18350,7 +18347,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18600,7 +18597,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18650,7 +18647,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>321</v>
+        